--- a/clustered_output.xlsx
+++ b/clustered_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F505"/>
+  <dimension ref="A1:J505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,26 @@
           <t>cluster</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dc_lat</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dc_long</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>distance_km</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_distance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -481,6 +501,18 @@
       <c r="F2" t="n">
         <v>3</v>
       </c>
+      <c r="G2" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H2" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I2" t="n">
+        <v>312.3476429270801</v>
+      </c>
+      <c r="J2" t="n">
+        <v>434572786.3919532</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,6 +535,18 @@
       <c r="F3" t="n">
         <v>3</v>
       </c>
+      <c r="G3" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H3" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I3" t="n">
+        <v>141.5567884198512</v>
+      </c>
+      <c r="J3" t="n">
+        <v>268110738.6573079</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -525,6 +569,18 @@
       <c r="F4" t="n">
         <v>3</v>
       </c>
+      <c r="G4" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H4" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I4" t="n">
+        <v>375.2133947621184</v>
+      </c>
+      <c r="J4" t="n">
+        <v>302492294.283843</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -547,6 +603,18 @@
       <c r="F5" t="n">
         <v>3</v>
       </c>
+      <c r="G5" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H5" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I5" t="n">
+        <v>118.9018437587613</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1189018.437587613</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -569,6 +637,18 @@
       <c r="F6" t="n">
         <v>3</v>
       </c>
+      <c r="G6" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H6" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I6" t="n">
+        <v>386.3087422339807</v>
+      </c>
+      <c r="J6" t="n">
+        <v>604905866.8219044</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -591,6 +671,18 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
+      <c r="G7" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H7" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I7" t="n">
+        <v>118.9558925056448</v>
+      </c>
+      <c r="J7" t="n">
+        <v>137962419.9610582</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -613,6 +705,18 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
+      <c r="G8" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H8" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I8" t="n">
+        <v>328.2730746713401</v>
+      </c>
+      <c r="J8" t="n">
+        <v>644682547.5397106</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -635,6 +739,18 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
+      <c r="G9" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H9" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I9" t="n">
+        <v>388.3345797490471</v>
+      </c>
+      <c r="J9" t="n">
+        <v>792947696.5547349</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -657,6 +773,18 @@
       <c r="F10" t="n">
         <v>3</v>
       </c>
+      <c r="G10" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H10" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I10" t="n">
+        <v>485.78077300261</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1191935834.584651</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -679,6 +807,18 @@
       <c r="F11" t="n">
         <v>3</v>
       </c>
+      <c r="G11" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H11" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I11" t="n">
+        <v>492.8602485423139</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1254529152.870756</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -701,6 +841,18 @@
       <c r="F12" t="n">
         <v>3</v>
       </c>
+      <c r="G12" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H12" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I12" t="n">
+        <v>133.5075553693926</v>
+      </c>
+      <c r="J12" t="n">
+        <v>320933151.6321353</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -723,6 +875,18 @@
       <c r="F13" t="n">
         <v>3</v>
       </c>
+      <c r="G13" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H13" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I13" t="n">
+        <v>138.8671569739272</v>
+      </c>
+      <c r="J13" t="n">
+        <v>213342061.7999615</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -745,6 +909,18 @@
       <c r="F14" t="n">
         <v>3</v>
       </c>
+      <c r="G14" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H14" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I14" t="n">
+        <v>153.4618793634799</v>
+      </c>
+      <c r="J14" t="n">
+        <v>443386964.9640118</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -767,6 +943,18 @@
       <c r="F15" t="n">
         <v>3</v>
       </c>
+      <c r="G15" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H15" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I15" t="n">
+        <v>431.3442798376877</v>
+      </c>
+      <c r="J15" t="n">
+        <v>761697617.1825392</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -789,6 +977,18 @@
       <c r="F16" t="n">
         <v>3</v>
       </c>
+      <c r="G16" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H16" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I16" t="n">
+        <v>424.6636155876099</v>
+      </c>
+      <c r="J16" t="n">
+        <v>971194047.1205063</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -811,6 +1011,18 @@
       <c r="F17" t="n">
         <v>3</v>
       </c>
+      <c r="G17" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H17" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I17" t="n">
+        <v>139.2049227489753</v>
+      </c>
+      <c r="J17" t="n">
+        <v>250512107.2403557</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -833,6 +1045,18 @@
       <c r="F18" t="n">
         <v>1</v>
       </c>
+      <c r="G18" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H18" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I18" t="n">
+        <v>277.9779084992091</v>
+      </c>
+      <c r="J18" t="n">
+        <v>773015286.5966681</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -855,6 +1079,18 @@
       <c r="F19" t="n">
         <v>3</v>
       </c>
+      <c r="G19" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H19" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I19" t="n">
+        <v>133.0509347923777</v>
+      </c>
+      <c r="J19" t="n">
+        <v>275201185.7609444</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -877,6 +1113,18 @@
       <c r="F20" t="n">
         <v>3</v>
       </c>
+      <c r="G20" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H20" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I20" t="n">
+        <v>168.2999938886427</v>
+      </c>
+      <c r="J20" t="n">
+        <v>265595199.8616315</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -899,6 +1147,18 @@
       <c r="F21" t="n">
         <v>1</v>
       </c>
+      <c r="G21" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H21" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I21" t="n">
+        <v>241.286644854991</v>
+      </c>
+      <c r="J21" t="n">
+        <v>479434531.6933176</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -921,6 +1181,18 @@
       <c r="F22" t="n">
         <v>3</v>
       </c>
+      <c r="G22" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H22" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I22" t="n">
+        <v>254.3489777477395</v>
+      </c>
+      <c r="J22" t="n">
+        <v>415798954.9472253</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -943,6 +1215,18 @@
       <c r="F23" t="n">
         <v>3</v>
       </c>
+      <c r="G23" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H23" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I23" t="n">
+        <v>439.8981805465693</v>
+      </c>
+      <c r="J23" t="n">
+        <v>786092567.5053902</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -965,6 +1249,18 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
+      <c r="G24" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H24" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I24" t="n">
+        <v>114.9129726884635</v>
+      </c>
+      <c r="J24" t="n">
+        <v>171505418.0488831</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -987,6 +1283,18 @@
       <c r="F25" t="n">
         <v>3</v>
       </c>
+      <c r="G25" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H25" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I25" t="n">
+        <v>408.5855438226462</v>
+      </c>
+      <c r="J25" t="n">
+        <v>681923323.6344786</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1009,6 +1317,18 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
+      <c r="G26" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H26" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I26" t="n">
+        <v>379.9781482388589</v>
+      </c>
+      <c r="J26" t="n">
+        <v>735438681.4352908</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1031,6 +1351,18 @@
       <c r="F27" t="n">
         <v>3</v>
       </c>
+      <c r="G27" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H27" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I27" t="n">
+        <v>144.8833393517898</v>
+      </c>
+      <c r="J27" t="n">
+        <v>367923881.4417396</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1053,6 +1385,18 @@
       <c r="F28" t="n">
         <v>3</v>
       </c>
+      <c r="G28" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H28" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I28" t="n">
+        <v>406.3401413649697</v>
+      </c>
+      <c r="J28" t="n">
+        <v>639809679.8469821</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1075,6 +1419,18 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
+      <c r="G29" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H29" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I29" t="n">
+        <v>183.7395365549781</v>
+      </c>
+      <c r="J29" t="n">
+        <v>220463796.587619</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1097,6 +1453,18 @@
       <c r="F30" t="n">
         <v>3</v>
       </c>
+      <c r="G30" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H30" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I30" t="n">
+        <v>280.1001551232182</v>
+      </c>
+      <c r="J30" t="n">
+        <v>731635394.5124831</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1119,6 +1487,18 @@
       <c r="F31" t="n">
         <v>3</v>
       </c>
+      <c r="G31" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H31" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I31" t="n">
+        <v>137.9850073898567</v>
+      </c>
+      <c r="J31" t="n">
+        <v>238579588.1156504</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1141,6 +1521,18 @@
       <c r="F32" t="n">
         <v>3</v>
       </c>
+      <c r="G32" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H32" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I32" t="n">
+        <v>143.1370130472784</v>
+      </c>
+      <c r="J32" t="n">
+        <v>496942240.9675898</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1163,6 +1555,18 @@
       <c r="F33" t="n">
         <v>3</v>
       </c>
+      <c r="G33" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H33" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I33" t="n">
+        <v>414.6563633974813</v>
+      </c>
+      <c r="J33" t="n">
+        <v>999377408.0337528</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1185,6 +1589,18 @@
       <c r="F34" t="n">
         <v>1</v>
       </c>
+      <c r="G34" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H34" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I34" t="n">
+        <v>231.6252831067762</v>
+      </c>
+      <c r="J34" t="n">
+        <v>188785248.9137813</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1207,6 +1623,18 @@
       <c r="F35" t="n">
         <v>3</v>
       </c>
+      <c r="G35" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H35" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I35" t="n">
+        <v>141.5202761549733</v>
+      </c>
+      <c r="J35" t="n">
+        <v>267774154.8388886</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1229,6 +1657,18 @@
       <c r="F36" t="n">
         <v>3</v>
       </c>
+      <c r="G36" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H36" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I36" t="n">
+        <v>486.7713001932132</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1141595207.663786</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1251,6 +1691,18 @@
       <c r="F37" t="n">
         <v>1</v>
       </c>
+      <c r="G37" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H37" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I37" t="n">
+        <v>115.9067835773086</v>
+      </c>
+      <c r="J37" t="n">
+        <v>247897986.8632094</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1273,6 +1725,18 @@
       <c r="F38" t="n">
         <v>3</v>
       </c>
+      <c r="G38" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H38" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I38" t="n">
+        <v>137.8672753703998</v>
+      </c>
+      <c r="J38" t="n">
+        <v>261340603.1266628</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1295,6 +1759,18 @@
       <c r="F39" t="n">
         <v>3</v>
       </c>
+      <c r="G39" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H39" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I39" t="n">
+        <v>400.3943203558753</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1383321250.326936</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1317,6 +1793,18 @@
       <c r="F40" t="n">
         <v>1</v>
       </c>
+      <c r="G40" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H40" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I40" t="n">
+        <v>367.7369200108809</v>
+      </c>
+      <c r="J40" t="n">
+        <v>884920164.2764003</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1339,6 +1827,18 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
+      <c r="G41" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H41" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I41" t="n">
+        <v>98.15468437307703</v>
+      </c>
+      <c r="J41" t="n">
+        <v>207155988.9017303</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1361,6 +1861,18 @@
       <c r="F42" t="n">
         <v>3</v>
       </c>
+      <c r="G42" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H42" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I42" t="n">
+        <v>249.876798128665</v>
+      </c>
+      <c r="J42" t="n">
+        <v>433763234.7107301</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1383,6 +1895,18 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
+      <c r="G43" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H43" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I43" t="n">
+        <v>139.6700844491425</v>
+      </c>
+      <c r="J43" t="n">
+        <v>330037252.1713947</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1405,6 +1929,18 @@
       <c r="F44" t="n">
         <v>3</v>
       </c>
+      <c r="G44" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H44" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I44" t="n">
+        <v>392.3383289461026</v>
+      </c>
+      <c r="J44" t="n">
+        <v>706644915.2968935</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1427,6 +1963,18 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
+      <c r="G45" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H45" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I45" t="n">
+        <v>360.733750681989</v>
+      </c>
+      <c r="J45" t="n">
+        <v>548649455.9245553</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1449,6 +1997,18 @@
       <c r="F46" t="n">
         <v>3</v>
       </c>
+      <c r="G46" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H46" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I46" t="n">
+        <v>380.3280875652389</v>
+      </c>
+      <c r="J46" t="n">
+        <v>436824155.3327507</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1471,6 +2031,18 @@
       <c r="F47" t="n">
         <v>3</v>
       </c>
+      <c r="G47" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H47" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I47" t="n">
+        <v>384.2953851204009</v>
+      </c>
+      <c r="J47" t="n">
+        <v>325157893.7905017</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1493,6 +2065,18 @@
       <c r="F48" t="n">
         <v>3</v>
       </c>
+      <c r="G48" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H48" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I48" t="n">
+        <v>131.7915489876928</v>
+      </c>
+      <c r="J48" t="n">
+        <v>277721668.3335178</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1515,6 +2099,18 @@
       <c r="F49" t="n">
         <v>3</v>
       </c>
+      <c r="G49" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H49" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I49" t="n">
+        <v>410.0957017648079</v>
+      </c>
+      <c r="J49" t="n">
+        <v>905769403.593977</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1537,6 +2133,18 @@
       <c r="F50" t="n">
         <v>3</v>
       </c>
+      <c r="G50" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H50" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I50" t="n">
+        <v>486.3552966158776</v>
+      </c>
+      <c r="J50" t="n">
+        <v>769457150.8713869</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1559,6 +2167,18 @@
       <c r="F51" t="n">
         <v>1</v>
       </c>
+      <c r="G51" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H51" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I51" t="n">
+        <v>327.371843717464</v>
+      </c>
+      <c r="J51" t="n">
+        <v>522685550.2797217</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1581,6 +2201,18 @@
       <c r="F52" t="n">
         <v>1</v>
       </c>
+      <c r="G52" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H52" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I52" t="n">
+        <v>126.6884221680908</v>
+      </c>
+      <c r="J52" t="n">
+        <v>215908279.8003437</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1603,6 +2235,18 @@
       <c r="F53" t="n">
         <v>3</v>
       </c>
+      <c r="G53" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H53" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I53" t="n">
+        <v>93.8415059481957</v>
+      </c>
+      <c r="J53" t="n">
+        <v>174566832.9383877</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1625,6 +2269,18 @@
       <c r="F54" t="n">
         <v>1</v>
       </c>
+      <c r="G54" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H54" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I54" t="n">
+        <v>176.4470644623666</v>
+      </c>
+      <c r="J54" t="n">
+        <v>322519604.9010931</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1647,6 +2303,18 @@
       <c r="F55" t="n">
         <v>3</v>
       </c>
+      <c r="G55" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H55" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I55" t="n">
+        <v>146.7189630432425</v>
+      </c>
+      <c r="J55" t="n">
+        <v>361510832.8661115</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1669,6 +2337,18 @@
       <c r="F56" t="n">
         <v>3</v>
       </c>
+      <c r="G56" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H56" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I56" t="n">
+        <v>481.7271018753432</v>
+      </c>
+      <c r="J56" t="n">
+        <v>656534305.6954602</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1691,6 +2371,18 @@
       <c r="F57" t="n">
         <v>3</v>
       </c>
+      <c r="G57" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H57" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I57" t="n">
+        <v>399.3315282450388</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1017901811.877296</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1713,6 +2405,18 @@
       <c r="F58" t="n">
         <v>1</v>
       </c>
+      <c r="G58" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H58" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I58" t="n">
+        <v>108.7848638752269</v>
+      </c>
+      <c r="J58" t="n">
+        <v>133544464.2462216</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1735,6 +2439,18 @@
       <c r="F59" t="n">
         <v>3</v>
       </c>
+      <c r="G59" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H59" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I59" t="n">
+        <v>147.1540323338647</v>
+      </c>
+      <c r="J59" t="n">
+        <v>327704431.7090573</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1757,6 +2473,18 @@
       <c r="F60" t="n">
         <v>3</v>
       </c>
+      <c r="G60" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H60" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I60" t="n">
+        <v>137.4222979025599</v>
+      </c>
+      <c r="J60" t="n">
+        <v>214116356.2368039</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1779,6 +2507,18 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
+      <c r="G61" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H61" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I61" t="n">
+        <v>131.6200947203843</v>
+      </c>
+      <c r="J61" t="n">
+        <v>502445340.9840756</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1801,6 +2541,18 @@
       <c r="F62" t="n">
         <v>3</v>
       </c>
+      <c r="G62" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H62" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I62" t="n">
+        <v>129.47271130013</v>
+      </c>
+      <c r="J62" t="n">
+        <v>270695463.4530621</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1823,6 +2575,18 @@
       <c r="F63" t="n">
         <v>3</v>
       </c>
+      <c r="G63" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H63" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I63" t="n">
+        <v>409.142576533964</v>
+      </c>
+      <c r="J63" t="n">
+        <v>426092477.9146523</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1845,6 +2609,18 @@
       <c r="F64" t="n">
         <v>1</v>
       </c>
+      <c r="G64" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H64" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I64" t="n">
+        <v>328.2671538715692</v>
+      </c>
+      <c r="J64" t="n">
+        <v>305496288.8836901</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1867,6 +2643,18 @@
       <c r="F65" t="n">
         <v>1</v>
       </c>
+      <c r="G65" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H65" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I65" t="n">
+        <v>137.775968778899</v>
+      </c>
+      <c r="J65" t="n">
+        <v>440352090.8424079</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1889,6 +2677,18 @@
       <c r="F66" t="n">
         <v>1</v>
       </c>
+      <c r="G66" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H66" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I66" t="n">
+        <v>382.7725994990877</v>
+      </c>
+      <c r="J66" t="n">
+        <v>340996633.3975395</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1911,6 +2711,18 @@
       <c r="F67" t="n">
         <v>3</v>
       </c>
+      <c r="G67" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H67" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I67" t="n">
+        <v>127.2148671715527</v>
+      </c>
+      <c r="J67" t="n">
+        <v>187555521.9415302</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1933,6 +2745,18 @@
       <c r="F68" t="n">
         <v>1</v>
       </c>
+      <c r="G68" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H68" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I68" t="n">
+        <v>187.1173891728598</v>
+      </c>
+      <c r="J68" t="n">
+        <v>215941326.0358255</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1955,6 +2779,18 @@
       <c r="F69" t="n">
         <v>3</v>
       </c>
+      <c r="G69" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H69" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I69" t="n">
+        <v>75.96318517921419</v>
+      </c>
+      <c r="J69" t="n">
+        <v>115059912.0098292</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1977,6 +2813,18 @@
       <c r="F70" t="n">
         <v>3</v>
       </c>
+      <c r="G70" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H70" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I70" t="n">
+        <v>143.1079901005895</v>
+      </c>
+      <c r="J70" t="n">
+        <v>191677692.7835691</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1999,6 +2847,18 @@
       <c r="F71" t="n">
         <v>1</v>
       </c>
+      <c r="G71" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H71" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I71" t="n">
+        <v>108.7848638752269</v>
+      </c>
+      <c r="J71" t="n">
+        <v>23362499.2090666</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2021,6 +2881,18 @@
       <c r="F72" t="n">
         <v>3</v>
       </c>
+      <c r="G72" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H72" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I72" t="n">
+        <v>136.4020147685627</v>
+      </c>
+      <c r="J72" t="n">
+        <v>225905154.6366454</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2043,6 +2915,18 @@
       <c r="F73" t="n">
         <v>3</v>
       </c>
+      <c r="G73" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H73" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I73" t="n">
+        <v>426.8029932126655</v>
+      </c>
+      <c r="J73" t="n">
+        <v>585650659.2674532</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2065,6 +2949,18 @@
       <c r="F74" t="n">
         <v>3</v>
       </c>
+      <c r="G74" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H74" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I74" t="n">
+        <v>134.4832099001436</v>
+      </c>
+      <c r="J74" t="n">
+        <v>404924284.60128</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2087,6 +2983,18 @@
       <c r="F75" t="n">
         <v>1</v>
       </c>
+      <c r="G75" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H75" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I75" t="n">
+        <v>124.5019625679025</v>
+      </c>
+      <c r="J75" t="n">
+        <v>298979095.0818564</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2109,6 +3017,18 @@
       <c r="F76" t="n">
         <v>3</v>
       </c>
+      <c r="G76" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H76" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I76" t="n">
+        <v>468.7426850661527</v>
+      </c>
+      <c r="J76" t="n">
+        <v>446445186.1533391</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2131,6 +3051,18 @@
       <c r="F77" t="n">
         <v>1</v>
       </c>
+      <c r="G77" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H77" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I77" t="n">
+        <v>120.9179947370747</v>
+      </c>
+      <c r="J77" t="n">
+        <v>354561896.1733279</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2153,6 +3085,18 @@
       <c r="F78" t="n">
         <v>3</v>
       </c>
+      <c r="G78" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H78" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I78" t="n">
+        <v>211.1051461597017</v>
+      </c>
+      <c r="J78" t="n">
+        <v>237894878.971307</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2175,6 +3119,18 @@
       <c r="F79" t="n">
         <v>3</v>
       </c>
+      <c r="G79" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H79" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I79" t="n">
+        <v>244.3990735124999</v>
+      </c>
+      <c r="J79" t="n">
+        <v>415645935.6074374</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2197,6 +3153,18 @@
       <c r="F80" t="n">
         <v>3</v>
       </c>
+      <c r="G80" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H80" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I80" t="n">
+        <v>151.0245141196881</v>
+      </c>
+      <c r="J80" t="n">
+        <v>322446569.7740825</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2219,6 +3187,18 @@
       <c r="F81" t="n">
         <v>3</v>
       </c>
+      <c r="G81" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H81" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I81" t="n">
+        <v>142.94381580362</v>
+      </c>
+      <c r="J81" t="n">
+        <v>471004361.7231603</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2241,6 +3221,18 @@
       <c r="F82" t="n">
         <v>3</v>
       </c>
+      <c r="G82" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H82" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I82" t="n">
+        <v>138.2916456117689</v>
+      </c>
+      <c r="J82" t="n">
+        <v>325521164.3394153</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2263,6 +3255,18 @@
       <c r="F83" t="n">
         <v>1</v>
       </c>
+      <c r="G83" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H83" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I83" t="n">
+        <v>130.4725566339279</v>
+      </c>
+      <c r="J83" t="n">
+        <v>504826859.87898</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2285,6 +3289,18 @@
       <c r="F84" t="n">
         <v>1</v>
       </c>
+      <c r="G84" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H84" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I84" t="n">
+        <v>128.654547153294</v>
+      </c>
+      <c r="J84" t="n">
+        <v>393654754.5104535</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2307,6 +3323,18 @@
       <c r="F85" t="n">
         <v>1</v>
       </c>
+      <c r="G85" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H85" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I85" t="n">
+        <v>137.7742062609717</v>
+      </c>
+      <c r="J85" t="n">
+        <v>385780500.2897983</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2329,6 +3357,18 @@
       <c r="F86" t="n">
         <v>3</v>
       </c>
+      <c r="G86" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H86" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I86" t="n">
+        <v>137.1832339917709</v>
+      </c>
+      <c r="J86" t="n">
+        <v>574372117.4927434</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2351,6 +3391,18 @@
       <c r="F87" t="n">
         <v>1</v>
       </c>
+      <c r="G87" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H87" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I87" t="n">
+        <v>381.4141464317108</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1195502826.167452</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2373,6 +3425,18 @@
       <c r="F88" t="n">
         <v>1</v>
       </c>
+      <c r="G88" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H88" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I88" t="n">
+        <v>328.2324482195975</v>
+      </c>
+      <c r="J88" t="n">
+        <v>992319545.4420509</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2395,6 +3459,18 @@
       <c r="F89" t="n">
         <v>3</v>
       </c>
+      <c r="G89" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H89" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I89" t="n">
+        <v>141.0311183501512</v>
+      </c>
+      <c r="J89" t="n">
+        <v>521232240.7699955</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2417,6 +3493,18 @@
       <c r="F90" t="n">
         <v>3</v>
       </c>
+      <c r="G90" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H90" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I90" t="n">
+        <v>141.2722471438568</v>
+      </c>
+      <c r="J90" t="n">
+        <v>252406542.2304096</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2439,6 +3527,18 @@
       <c r="F91" t="n">
         <v>3</v>
       </c>
+      <c r="G91" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H91" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I91" t="n">
+        <v>133.2782084515678</v>
+      </c>
+      <c r="J91" t="n">
+        <v>483531460.0399628</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2461,6 +3561,18 @@
       <c r="F92" t="n">
         <v>1</v>
       </c>
+      <c r="G92" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H92" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I92" t="n">
+        <v>128.5974961593128</v>
+      </c>
+      <c r="J92" t="n">
+        <v>507167113.3692197</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2483,6 +3595,18 @@
       <c r="F93" t="n">
         <v>1</v>
       </c>
+      <c r="G93" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H93" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I93" t="n">
+        <v>126.5993037082896</v>
+      </c>
+      <c r="J93" t="n">
+        <v>330011751.2649944</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2505,6 +3629,18 @@
       <c r="F94" t="n">
         <v>3</v>
       </c>
+      <c r="G94" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H94" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I94" t="n">
+        <v>140.2315491170268</v>
+      </c>
+      <c r="J94" t="n">
+        <v>265768057.1597497</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2527,6 +3663,18 @@
       <c r="F95" t="n">
         <v>1</v>
       </c>
+      <c r="G95" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H95" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I95" t="n">
+        <v>130.3110932076192</v>
+      </c>
+      <c r="J95" t="n">
+        <v>300278289.9382486</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2549,6 +3697,18 @@
       <c r="F96" t="n">
         <v>3</v>
       </c>
+      <c r="G96" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H96" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I96" t="n">
+        <v>136.5442645586296</v>
+      </c>
+      <c r="J96" t="n">
+        <v>417761373.6954661</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2571,6 +3731,18 @@
       <c r="F97" t="n">
         <v>3</v>
       </c>
+      <c r="G97" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H97" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I97" t="n">
+        <v>143.4825259368347</v>
+      </c>
+      <c r="J97" t="n">
+        <v>362711295.2393285</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2593,6 +3765,18 @@
       <c r="F98" t="n">
         <v>3</v>
       </c>
+      <c r="G98" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H98" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I98" t="n">
+        <v>135.7900799156238</v>
+      </c>
+      <c r="J98" t="n">
+        <v>346445837.9066675</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2615,6 +3799,18 @@
       <c r="F99" t="n">
         <v>3</v>
       </c>
+      <c r="G99" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H99" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I99" t="n">
+        <v>410.3726253648458</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1103755116.429729</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2637,6 +3833,18 @@
       <c r="F100" t="n">
         <v>3</v>
       </c>
+      <c r="G100" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H100" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I100" t="n">
+        <v>145.7555976740724</v>
+      </c>
+      <c r="J100" t="n">
+        <v>465867949.4307111</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2659,6 +3867,18 @@
       <c r="F101" t="n">
         <v>3</v>
       </c>
+      <c r="G101" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H101" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I101" t="n">
+        <v>132.978317893762</v>
+      </c>
+      <c r="J101" t="n">
+        <v>395216039.8889425</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2681,6 +3901,18 @@
       <c r="F102" t="n">
         <v>3</v>
       </c>
+      <c r="G102" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H102" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I102" t="n">
+        <v>123.4723396428809</v>
+      </c>
+      <c r="J102" t="n">
+        <v>444507284.2821884</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2703,6 +3935,18 @@
       <c r="F103" t="n">
         <v>3</v>
       </c>
+      <c r="G103" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H103" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I103" t="n">
+        <v>131.2088258437179</v>
+      </c>
+      <c r="J103" t="n">
+        <v>460501093.3116024</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2725,6 +3969,18 @@
       <c r="F104" t="n">
         <v>3</v>
       </c>
+      <c r="G104" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H104" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I104" t="n">
+        <v>123.8725865372433</v>
+      </c>
+      <c r="J104" t="n">
+        <v>455299707.0704404</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2747,6 +4003,18 @@
       <c r="F105" t="n">
         <v>3</v>
       </c>
+      <c r="G105" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H105" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I105" t="n">
+        <v>392.2861529735245</v>
+      </c>
+      <c r="J105" t="n">
+        <v>762311621.0035399</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2769,6 +4037,18 @@
       <c r="F106" t="n">
         <v>3</v>
       </c>
+      <c r="G106" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H106" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I106" t="n">
+        <v>282.7352857594362</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1085092294.312245</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2791,6 +4071,18 @@
       <c r="F107" t="n">
         <v>3</v>
       </c>
+      <c r="G107" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H107" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I107" t="n">
+        <v>483.0990667625962</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1008981121.173201</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2813,6 +4105,18 @@
       <c r="F108" t="n">
         <v>3</v>
       </c>
+      <c r="G108" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H108" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I108" t="n">
+        <v>406.0315877170019</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1250021026.893194</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2835,6 +4139,18 @@
       <c r="F109" t="n">
         <v>3</v>
       </c>
+      <c r="G109" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H109" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I109" t="n">
+        <v>136.4895373399047</v>
+      </c>
+      <c r="J109" t="n">
+        <v>271893360.7386461</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2857,6 +4173,18 @@
       <c r="F110" t="n">
         <v>1</v>
       </c>
+      <c r="G110" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H110" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I110" t="n">
+        <v>380.8965900937883</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1103090814.628086</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2879,6 +4207,18 @@
       <c r="F111" t="n">
         <v>3</v>
       </c>
+      <c r="G111" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H111" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I111" t="n">
+        <v>140.8386301032752</v>
+      </c>
+      <c r="J111" t="n">
+        <v>368041800.1233259</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2901,6 +4241,18 @@
       <c r="F112" t="n">
         <v>3</v>
       </c>
+      <c r="G112" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H112" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I112" t="n">
+        <v>129.4578906436336</v>
+      </c>
+      <c r="J112" t="n">
+        <v>351419927.403307</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2923,6 +4275,18 @@
       <c r="F113" t="n">
         <v>3</v>
       </c>
+      <c r="G113" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H113" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I113" t="n">
+        <v>133.6366603171619</v>
+      </c>
+      <c r="J113" t="n">
+        <v>285025496.9905946</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2945,6 +4309,18 @@
       <c r="F114" t="n">
         <v>3</v>
       </c>
+      <c r="G114" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H114" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I114" t="n">
+        <v>293.4967601443832</v>
+      </c>
+      <c r="J114" t="n">
+        <v>534131798.2743884</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2967,6 +4343,18 @@
       <c r="F115" t="n">
         <v>3</v>
       </c>
+      <c r="G115" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H115" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I115" t="n">
+        <v>380.9416346172154</v>
+      </c>
+      <c r="J115" t="n">
+        <v>733157790.0542517</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2989,6 +4377,18 @@
       <c r="F116" t="n">
         <v>3</v>
       </c>
+      <c r="G116" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H116" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I116" t="n">
+        <v>126.9811181546085</v>
+      </c>
+      <c r="J116" t="n">
+        <v>336740995.1127225</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3011,6 +4411,18 @@
       <c r="F117" t="n">
         <v>1</v>
       </c>
+      <c r="G117" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H117" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I117" t="n">
+        <v>133.5964249022822</v>
+      </c>
+      <c r="J117" t="n">
+        <v>388576232.8850923</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3033,6 +4445,18 @@
       <c r="F118" t="n">
         <v>3</v>
       </c>
+      <c r="G118" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H118" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I118" t="n">
+        <v>140.7173414264341</v>
+      </c>
+      <c r="J118" t="n">
+        <v>477273483.8930395</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3055,6 +4479,18 @@
       <c r="F119" t="n">
         <v>3</v>
       </c>
+      <c r="G119" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H119" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I119" t="n">
+        <v>483.3104400018008</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1065020966.845522</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3077,6 +4513,18 @@
       <c r="F120" t="n">
         <v>1</v>
       </c>
+      <c r="G120" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H120" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I120" t="n">
+        <v>381.2386282180768</v>
+      </c>
+      <c r="J120" t="n">
+        <v>415352482.0899945</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3099,6 +4547,18 @@
       <c r="F121" t="n">
         <v>3</v>
       </c>
+      <c r="G121" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H121" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I121" t="n">
+        <v>144.4670761581502</v>
+      </c>
+      <c r="J121" t="n">
+        <v>531031697.2212816</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3121,6 +4581,18 @@
       <c r="F122" t="n">
         <v>3</v>
       </c>
+      <c r="G122" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H122" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I122" t="n">
+        <v>133.0423815907709</v>
+      </c>
+      <c r="J122" t="n">
+        <v>210616768.7049488</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3143,6 +4615,18 @@
       <c r="F123" t="n">
         <v>1</v>
       </c>
+      <c r="G123" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H123" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I123" t="n">
+        <v>114.1266628728534</v>
+      </c>
+      <c r="J123" t="n">
+        <v>283384168.3175936</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3165,6 +4649,18 @@
       <c r="F124" t="n">
         <v>3</v>
       </c>
+      <c r="G124" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H124" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I124" t="n">
+        <v>134.3485696562654</v>
+      </c>
+      <c r="J124" t="n">
+        <v>325081259.0732917</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3187,6 +4683,18 @@
       <c r="F125" t="n">
         <v>3</v>
       </c>
+      <c r="G125" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H125" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I125" t="n">
+        <v>120.4872005564761</v>
+      </c>
+      <c r="J125" t="n">
+        <v>433447428.4698465</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3209,6 +4717,18 @@
       <c r="F126" t="n">
         <v>3</v>
       </c>
+      <c r="G126" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H126" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I126" t="n">
+        <v>125.9371768049107</v>
+      </c>
+      <c r="J126" t="n">
+        <v>236920202.9807067</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3231,6 +4751,18 @@
       <c r="F127" t="n">
         <v>3</v>
       </c>
+      <c r="G127" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H127" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I127" t="n">
+        <v>134.3759538513394</v>
+      </c>
+      <c r="J127" t="n">
+        <v>257445180.3495021</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3253,6 +4785,18 @@
       <c r="F128" t="n">
         <v>3</v>
       </c>
+      <c r="G128" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H128" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I128" t="n">
+        <v>131.3698777549343</v>
+      </c>
+      <c r="J128" t="n">
+        <v>388726582.7939128</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3275,6 +4819,18 @@
       <c r="F129" t="n">
         <v>3</v>
       </c>
+      <c r="G129" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H129" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I129" t="n">
+        <v>137.9526950784186</v>
+      </c>
+      <c r="J129" t="n">
+        <v>349962199.5409724</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3297,6 +4853,18 @@
       <c r="F130" t="n">
         <v>3</v>
       </c>
+      <c r="G130" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H130" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I130" t="n">
+        <v>136.3894994966892</v>
+      </c>
+      <c r="J130" t="n">
+        <v>427433973.9357538</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3319,6 +4887,18 @@
       <c r="F131" t="n">
         <v>3</v>
       </c>
+      <c r="G131" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H131" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I131" t="n">
+        <v>70.25768122189537</v>
+      </c>
+      <c r="J131" t="n">
+        <v>270395398.3105803</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3341,6 +4921,18 @@
       <c r="F132" t="n">
         <v>1</v>
       </c>
+      <c r="G132" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H132" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I132" t="n">
+        <v>49.97972614757656</v>
+      </c>
+      <c r="J132" t="n">
+        <v>165206870.9826172</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3363,6 +4955,18 @@
       <c r="F133" t="n">
         <v>3</v>
       </c>
+      <c r="G133" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H133" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I133" t="n">
+        <v>407.7414728579811</v>
+      </c>
+      <c r="J133" t="n">
+        <v>877509622.385289</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3385,6 +4989,18 @@
       <c r="F134" t="n">
         <v>3</v>
       </c>
+      <c r="G134" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H134" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I134" t="n">
+        <v>140.6749761342152</v>
+      </c>
+      <c r="J134" t="n">
+        <v>387461175.3917043</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3407,6 +5023,18 @@
       <c r="F135" t="n">
         <v>1</v>
       </c>
+      <c r="G135" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H135" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I135" t="n">
+        <v>242.8897244503717</v>
+      </c>
+      <c r="J135" t="n">
+        <v>823286487.3314564</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3429,6 +5057,18 @@
       <c r="F136" t="n">
         <v>1</v>
       </c>
+      <c r="G136" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H136" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I136" t="n">
+        <v>135.8054469712873</v>
+      </c>
+      <c r="J136" t="n">
+        <v>275898049.5220389</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3451,6 +5091,18 @@
       <c r="F137" t="n">
         <v>1</v>
       </c>
+      <c r="G137" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H137" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I137" t="n">
+        <v>137.3146338603078</v>
+      </c>
+      <c r="J137" t="n">
+        <v>281021046.6264049</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3473,6 +5125,18 @@
       <c r="F138" t="n">
         <v>3</v>
       </c>
+      <c r="G138" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H138" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I138" t="n">
+        <v>137.5980426536427</v>
+      </c>
+      <c r="J138" t="n">
+        <v>381722336.4515695</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3495,6 +5159,18 @@
       <c r="F139" t="n">
         <v>3</v>
       </c>
+      <c r="G139" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H139" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I139" t="n">
+        <v>126.7735021255614</v>
+      </c>
+      <c r="J139" t="n">
+        <v>459534608.759815</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3517,6 +5193,18 @@
       <c r="F140" t="n">
         <v>3</v>
       </c>
+      <c r="G140" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H140" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I140" t="n">
+        <v>404.208875401731</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1164599020.764787</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3539,6 +5227,18 @@
       <c r="F141" t="n">
         <v>3</v>
       </c>
+      <c r="G141" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H141" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I141" t="n">
+        <v>143.2619700296298</v>
+      </c>
+      <c r="J141" t="n">
+        <v>344283929.2277318</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3561,6 +5261,18 @@
       <c r="F142" t="n">
         <v>3</v>
       </c>
+      <c r="G142" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H142" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I142" t="n">
+        <v>259.3122659168254</v>
+      </c>
+      <c r="J142" t="n">
+        <v>569285671.6758258</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3583,6 +5295,18 @@
       <c r="F143" t="n">
         <v>3</v>
       </c>
+      <c r="G143" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H143" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I143" t="n">
+        <v>122.5537646253599</v>
+      </c>
+      <c r="J143" t="n">
+        <v>410216564.0734043</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3605,6 +5329,18 @@
       <c r="F144" t="n">
         <v>3</v>
       </c>
+      <c r="G144" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H144" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I144" t="n">
+        <v>108.9835170149182</v>
+      </c>
+      <c r="J144" t="n">
+        <v>310189163.4909111</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3627,6 +5363,18 @@
       <c r="F145" t="n">
         <v>3</v>
       </c>
+      <c r="G145" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H145" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I145" t="n">
+        <v>382.9364609623582</v>
+      </c>
+      <c r="J145" t="n">
+        <v>842061772.5589216</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3649,6 +5397,18 @@
       <c r="F146" t="n">
         <v>1</v>
       </c>
+      <c r="G146" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H146" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I146" t="n">
+        <v>112.9323050997713</v>
+      </c>
+      <c r="J146" t="n">
+        <v>346132247.403428</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3671,6 +5431,18 @@
       <c r="F147" t="n">
         <v>3</v>
       </c>
+      <c r="G147" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H147" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I147" t="n">
+        <v>129.9286643047488</v>
+      </c>
+      <c r="J147" t="n">
+        <v>408049397.9419455</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3693,6 +5465,18 @@
       <c r="F148" t="n">
         <v>3</v>
       </c>
+      <c r="G148" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H148" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I148" t="n">
+        <v>126.9603102938765</v>
+      </c>
+      <c r="J148" t="n">
+        <v>292996093.7469274</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3715,6 +5499,18 @@
       <c r="F149" t="n">
         <v>3</v>
       </c>
+      <c r="G149" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H149" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I149" t="n">
+        <v>139.0718628370146</v>
+      </c>
+      <c r="J149" t="n">
+        <v>469852337.7642979</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3737,6 +5533,18 @@
       <c r="F150" t="n">
         <v>3</v>
       </c>
+      <c r="G150" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H150" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I150" t="n">
+        <v>104.3207321729001</v>
+      </c>
+      <c r="J150" t="n">
+        <v>193785990.7453662</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3759,6 +5567,18 @@
       <c r="F151" t="n">
         <v>3</v>
       </c>
+      <c r="G151" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H151" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I151" t="n">
+        <v>394.1735633146689</v>
+      </c>
+      <c r="J151" t="n">
+        <v>664250086.4852109</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3781,6 +5601,18 @@
       <c r="F152" t="n">
         <v>3</v>
       </c>
+      <c r="G152" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H152" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I152" t="n">
+        <v>471.6729480562649</v>
+      </c>
+      <c r="J152" t="n">
+        <v>864033038.066195</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3803,6 +5635,18 @@
       <c r="F153" t="n">
         <v>3</v>
       </c>
+      <c r="G153" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H153" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I153" t="n">
+        <v>134.3986826020986</v>
+      </c>
+      <c r="J153" t="n">
+        <v>438884469.1313444</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3825,6 +5669,18 @@
       <c r="F154" t="n">
         <v>1</v>
       </c>
+      <c r="G154" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H154" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I154" t="n">
+        <v>100.2591398725851</v>
+      </c>
+      <c r="J154" t="n">
+        <v>279759020.3456946</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3847,6 +5703,18 @@
       <c r="F155" t="n">
         <v>3</v>
       </c>
+      <c r="G155" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H155" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I155" t="n">
+        <v>122.8495905764372</v>
+      </c>
+      <c r="J155" t="n">
+        <v>334172324.2357128</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3869,6 +5737,18 @@
       <c r="F156" t="n">
         <v>3</v>
       </c>
+      <c r="G156" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H156" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I156" t="n">
+        <v>130.088061613333</v>
+      </c>
+      <c r="J156" t="n">
+        <v>379035445.1741549</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3891,6 +5771,18 @@
       <c r="F157" t="n">
         <v>3</v>
       </c>
+      <c r="G157" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H157" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I157" t="n">
+        <v>485.9871884773702</v>
+      </c>
+      <c r="J157" t="n">
+        <v>1279696561.08788</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3913,6 +5805,18 @@
       <c r="F158" t="n">
         <v>3</v>
       </c>
+      <c r="G158" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H158" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I158" t="n">
+        <v>388.4173225360324</v>
+      </c>
+      <c r="J158" t="n">
+        <v>676329142.0374435</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3935,6 +5839,18 @@
       <c r="F159" t="n">
         <v>3</v>
       </c>
+      <c r="G159" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H159" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I159" t="n">
+        <v>149.1025029821664</v>
+      </c>
+      <c r="J159" t="n">
+        <v>467307006.466406</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3957,6 +5873,18 @@
       <c r="F160" t="n">
         <v>1</v>
       </c>
+      <c r="G160" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H160" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I160" t="n">
+        <v>378.5419582096303</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1110855466.13286</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3979,6 +5907,18 @@
       <c r="F161" t="n">
         <v>3</v>
       </c>
+      <c r="G161" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H161" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I161" t="n">
+        <v>130.6475561507304</v>
+      </c>
+      <c r="J161" t="n">
+        <v>491140998.3425772</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4001,6 +5941,18 @@
       <c r="F162" t="n">
         <v>3</v>
       </c>
+      <c r="G162" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H162" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I162" t="n">
+        <v>143.4355450702218</v>
+      </c>
+      <c r="J162" t="n">
+        <v>289918002.4943326</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4023,6 +5975,18 @@
       <c r="F163" t="n">
         <v>3</v>
       </c>
+      <c r="G163" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H163" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I163" t="n">
+        <v>68.20923825105052</v>
+      </c>
+      <c r="J163" t="n">
+        <v>243445334.8201594</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4045,6 +6009,18 @@
       <c r="F164" t="n">
         <v>3</v>
       </c>
+      <c r="G164" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H164" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I164" t="n">
+        <v>423.5281084764496</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1231472694.725534</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4067,6 +6043,18 @@
       <c r="F165" t="n">
         <v>3</v>
       </c>
+      <c r="G165" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H165" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I165" t="n">
+        <v>383.5877977344479</v>
+      </c>
+      <c r="J165" t="n">
+        <v>409209387.4131234</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4089,6 +6077,18 @@
       <c r="F166" t="n">
         <v>3</v>
       </c>
+      <c r="G166" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H166" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I166" t="n">
+        <v>326.0226848177935</v>
+      </c>
+      <c r="J166" t="n">
+        <v>684353493.9306704</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4111,6 +6111,18 @@
       <c r="F167" t="n">
         <v>3</v>
       </c>
+      <c r="G167" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H167" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I167" t="n">
+        <v>140.1897991510045</v>
+      </c>
+      <c r="J167" t="n">
+        <v>334771182.2461575</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4133,6 +6145,18 @@
       <c r="F168" t="n">
         <v>1</v>
       </c>
+      <c r="G168" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H168" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I168" t="n">
+        <v>141.3235570287463</v>
+      </c>
+      <c r="J168" t="n">
+        <v>417928960.4188234</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4155,6 +6179,18 @@
       <c r="F169" t="n">
         <v>1</v>
       </c>
+      <c r="G169" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H169" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I169" t="n">
+        <v>55.30319905350883</v>
+      </c>
+      <c r="J169" t="n">
+        <v>167716238.079846</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4177,6 +6213,18 @@
       <c r="F170" t="n">
         <v>3</v>
       </c>
+      <c r="G170" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H170" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I170" t="n">
+        <v>125.1863571233696</v>
+      </c>
+      <c r="J170" t="n">
+        <v>382282060.8402953</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4199,6 +6247,18 @@
       <c r="F171" t="n">
         <v>3</v>
       </c>
+      <c r="G171" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H171" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I171" t="n">
+        <v>416.8347839584198</v>
+      </c>
+      <c r="J171" t="n">
+        <v>773829416.5940322</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4221,6 +6281,18 @@
       <c r="F172" t="n">
         <v>3</v>
       </c>
+      <c r="G172" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H172" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I172" t="n">
+        <v>144.4377989386378</v>
+      </c>
+      <c r="J172" t="n">
+        <v>292277362.2528067</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4243,6 +6315,18 @@
       <c r="F173" t="n">
         <v>3</v>
       </c>
+      <c r="G173" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H173" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I173" t="n">
+        <v>134.3534034235337</v>
+      </c>
+      <c r="J173" t="n">
+        <v>383413509.2143389</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4265,6 +6349,18 @@
       <c r="F174" t="n">
         <v>3</v>
       </c>
+      <c r="G174" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H174" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I174" t="n">
+        <v>114.0055451393923</v>
+      </c>
+      <c r="J174" t="n">
+        <v>283819568.2329369</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4287,6 +6383,18 @@
       <c r="F175" t="n">
         <v>1</v>
       </c>
+      <c r="G175" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H175" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I175" t="n">
+        <v>124.7308673591305</v>
+      </c>
+      <c r="J175" t="n">
+        <v>409977657.170622</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4309,6 +6417,18 @@
       <c r="F176" t="n">
         <v>1</v>
       </c>
+      <c r="G176" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H176" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I176" t="n">
+        <v>279.5492674223455</v>
+      </c>
+      <c r="J176" t="n">
+        <v>925878399.0036418</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4331,6 +6451,18 @@
       <c r="F177" t="n">
         <v>3</v>
       </c>
+      <c r="G177" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H177" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I177" t="n">
+        <v>286.2681725369665</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1354728738.775376</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4353,6 +6485,18 @@
       <c r="F178" t="n">
         <v>3</v>
       </c>
+      <c r="G178" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H178" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I178" t="n">
+        <v>403.3875092325755</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1353341612.288379</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4375,6 +6519,18 @@
       <c r="F179" t="n">
         <v>3</v>
       </c>
+      <c r="G179" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H179" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I179" t="n">
+        <v>127.4899347416196</v>
+      </c>
+      <c r="J179" t="n">
+        <v>317682347.0680293</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4397,6 +6553,18 @@
       <c r="F180" t="n">
         <v>3</v>
       </c>
+      <c r="G180" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H180" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I180" t="n">
+        <v>161.0626768672974</v>
+      </c>
+      <c r="J180" t="n">
+        <v>521606623.376642</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4419,6 +6587,18 @@
       <c r="F181" t="n">
         <v>3</v>
       </c>
+      <c r="G181" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H181" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I181" t="n">
+        <v>127.0267048232512</v>
+      </c>
+      <c r="J181" t="n">
+        <v>231882233.3702717</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4441,6 +6621,18 @@
       <c r="F182" t="n">
         <v>3</v>
       </c>
+      <c r="G182" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H182" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I182" t="n">
+        <v>139.3757855483318</v>
+      </c>
+      <c r="J182" t="n">
+        <v>343119484.5614183</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4463,6 +6655,18 @@
       <c r="F183" t="n">
         <v>3</v>
       </c>
+      <c r="G183" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H183" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I183" t="n">
+        <v>139.1174159018112</v>
+      </c>
+      <c r="J183" t="n">
+        <v>340507553.3479565</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4485,6 +6689,18 @@
       <c r="F184" t="n">
         <v>3</v>
       </c>
+      <c r="G184" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H184" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I184" t="n">
+        <v>129.1647804488381</v>
+      </c>
+      <c r="J184" t="n">
+        <v>293523303.0401069</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4507,6 +6723,18 @@
       <c r="F185" t="n">
         <v>3</v>
       </c>
+      <c r="G185" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H185" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I185" t="n">
+        <v>147.3991022417724</v>
+      </c>
+      <c r="J185" t="n">
+        <v>350403916.8480017</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4529,6 +6757,18 @@
       <c r="F186" t="n">
         <v>3</v>
       </c>
+      <c r="G186" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H186" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I186" t="n">
+        <v>143.0036862149796</v>
+      </c>
+      <c r="J186" t="n">
+        <v>272368118.4300545</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4551,6 +6791,18 @@
       <c r="F187" t="n">
         <v>1</v>
       </c>
+      <c r="G187" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H187" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I187" t="n">
+        <v>131.8219351489301</v>
+      </c>
+      <c r="J187" t="n">
+        <v>272842425.2331307</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4573,6 +6825,18 @@
       <c r="F188" t="n">
         <v>3</v>
       </c>
+      <c r="G188" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H188" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I188" t="n">
+        <v>132.0778531307195</v>
+      </c>
+      <c r="J188" t="n">
+        <v>372290124.2833042</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4595,6 +6859,18 @@
       <c r="F189" t="n">
         <v>1</v>
       </c>
+      <c r="G189" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H189" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I189" t="n">
+        <v>123.3606496386461</v>
+      </c>
+      <c r="J189" t="n">
+        <v>377517736.5892903</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4617,6 +6893,18 @@
       <c r="F190" t="n">
         <v>3</v>
       </c>
+      <c r="G190" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H190" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I190" t="n">
+        <v>403.4008878879773</v>
+      </c>
+      <c r="J190" t="n">
+        <v>429339129.3062153</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4639,6 +6927,18 @@
       <c r="F191" t="n">
         <v>1</v>
       </c>
+      <c r="G191" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H191" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I191" t="n">
+        <v>52.44417237728874</v>
+      </c>
+      <c r="J191" t="n">
+        <v>84943849.07493043</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4661,6 +6961,18 @@
       <c r="F192" t="n">
         <v>3</v>
       </c>
+      <c r="G192" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H192" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I192" t="n">
+        <v>410.8985883498559</v>
+      </c>
+      <c r="J192" t="n">
+        <v>473644803.867004</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4683,6 +6995,18 @@
       <c r="F193" t="n">
         <v>3</v>
       </c>
+      <c r="G193" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H193" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I193" t="n">
+        <v>379.5971643506353</v>
+      </c>
+      <c r="J193" t="n">
+        <v>473321032.8188825</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4705,6 +7029,18 @@
       <c r="F194" t="n">
         <v>1</v>
       </c>
+      <c r="G194" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H194" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I194" t="n">
+        <v>139.1021731415539</v>
+      </c>
+      <c r="J194" t="n">
+        <v>215203351.5269811</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4727,6 +7063,18 @@
       <c r="F195" t="n">
         <v>3</v>
       </c>
+      <c r="G195" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H195" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I195" t="n">
+        <v>115.6713272323911</v>
+      </c>
+      <c r="J195" t="n">
+        <v>264436305.6260383</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4749,6 +7097,18 @@
       <c r="F196" t="n">
         <v>3</v>
       </c>
+      <c r="G196" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H196" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I196" t="n">
+        <v>129.9353063725652</v>
+      </c>
+      <c r="J196" t="n">
+        <v>149648688.255961</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4771,6 +7131,18 @@
       <c r="F197" t="n">
         <v>1</v>
       </c>
+      <c r="G197" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H197" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I197" t="n">
+        <v>112.8438318657794</v>
+      </c>
+      <c r="J197" t="n">
+        <v>124679920.9591706</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4793,6 +7165,18 @@
       <c r="F198" t="n">
         <v>1</v>
       </c>
+      <c r="G198" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H198" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I198" t="n">
+        <v>212.7765634214703</v>
+      </c>
+      <c r="J198" t="n">
+        <v>250906200.1861606</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4815,6 +7199,18 @@
       <c r="F199" t="n">
         <v>3</v>
       </c>
+      <c r="G199" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H199" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I199" t="n">
+        <v>128.0801182035454</v>
+      </c>
+      <c r="J199" t="n">
+        <v>285903872.401122</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4837,6 +7233,18 @@
       <c r="F200" t="n">
         <v>3</v>
       </c>
+      <c r="G200" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H200" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I200" t="n">
+        <v>133.1566648141351</v>
+      </c>
+      <c r="J200" t="n">
+        <v>265438230.684945</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4859,6 +7267,18 @@
       <c r="F201" t="n">
         <v>3</v>
       </c>
+      <c r="G201" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H201" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I201" t="n">
+        <v>124.8652061847382</v>
+      </c>
+      <c r="J201" t="n">
+        <v>218623935.2662004</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4881,6 +7301,18 @@
       <c r="F202" t="n">
         <v>3</v>
       </c>
+      <c r="G202" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H202" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I202" t="n">
+        <v>133.5168727607165</v>
+      </c>
+      <c r="J202" t="n">
+        <v>284573697.2095533</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4903,6 +7335,18 @@
       <c r="F203" t="n">
         <v>1</v>
       </c>
+      <c r="G203" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H203" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I203" t="n">
+        <v>20.05921122465895</v>
+      </c>
+      <c r="J203" t="n">
+        <v>21555771.60478665</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4925,6 +7369,18 @@
       <c r="F204" t="n">
         <v>3</v>
       </c>
+      <c r="G204" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H204" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I204" t="n">
+        <v>108.2994590509213</v>
+      </c>
+      <c r="J204" t="n">
+        <v>119521491.2345668</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4947,6 +7403,18 @@
       <c r="F205" t="n">
         <v>1</v>
       </c>
+      <c r="G205" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H205" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I205" t="n">
+        <v>109.4976212011855</v>
+      </c>
+      <c r="J205" t="n">
+        <v>184438354.8740738</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4969,6 +7437,18 @@
       <c r="F206" t="n">
         <v>1</v>
       </c>
+      <c r="G206" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H206" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I206" t="n">
+        <v>176.3651706464888</v>
+      </c>
+      <c r="J206" t="n">
+        <v>297415527.1927094</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4991,6 +7471,18 @@
       <c r="F207" t="n">
         <v>1</v>
       </c>
+      <c r="G207" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H207" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I207" t="n">
+        <v>133.315265358216</v>
+      </c>
+      <c r="J207" t="n">
+        <v>266875018.2481487</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5013,6 +7505,18 @@
       <c r="F208" t="n">
         <v>3</v>
       </c>
+      <c r="G208" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H208" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I208" t="n">
+        <v>170.4833860549217</v>
+      </c>
+      <c r="J208" t="n">
+        <v>217663076.0305389</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5035,6 +7539,18 @@
       <c r="F209" t="n">
         <v>3</v>
       </c>
+      <c r="G209" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H209" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I209" t="n">
+        <v>138.0374803401048</v>
+      </c>
+      <c r="J209" t="n">
+        <v>220523492.5232151</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5057,6 +7573,18 @@
       <c r="F210" t="n">
         <v>3</v>
       </c>
+      <c r="G210" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H210" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I210" t="n">
+        <v>150.5124814610589</v>
+      </c>
+      <c r="J210" t="n">
+        <v>266672603.7289957</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5079,6 +7607,18 @@
       <c r="F211" t="n">
         <v>3</v>
       </c>
+      <c r="G211" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H211" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I211" t="n">
+        <v>124.7669286489615</v>
+      </c>
+      <c r="J211" t="n">
+        <v>239304144.4531761</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5101,6 +7641,18 @@
       <c r="F212" t="n">
         <v>1</v>
       </c>
+      <c r="G212" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H212" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I212" t="n">
+        <v>130.7285006445507</v>
+      </c>
+      <c r="J212" t="n">
+        <v>446573904.997462</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5123,6 +7675,18 @@
       <c r="F213" t="n">
         <v>2</v>
       </c>
+      <c r="G213" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H213" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I213" t="n">
+        <v>237.3450700802627</v>
+      </c>
+      <c r="J213" t="n">
+        <v>255118506.125829</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5145,6 +7709,18 @@
       <c r="F214" t="n">
         <v>2</v>
       </c>
+      <c r="G214" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H214" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I214" t="n">
+        <v>142.4209975774765</v>
+      </c>
+      <c r="J214" t="n">
+        <v>153937505.5246153</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5167,6 +7743,18 @@
       <c r="F215" t="n">
         <v>2</v>
       </c>
+      <c r="G215" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H215" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I215" t="n">
+        <v>251.3431037068348</v>
+      </c>
+      <c r="J215" t="n">
+        <v>563415464.9499514</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5189,6 +7777,18 @@
       <c r="F216" t="n">
         <v>2</v>
       </c>
+      <c r="G216" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H216" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I216" t="n">
+        <v>76.24503928516523</v>
+      </c>
+      <c r="J216" t="n">
+        <v>160317804.577902</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5211,6 +7811,18 @@
       <c r="F217" t="n">
         <v>2</v>
       </c>
+      <c r="G217" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H217" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I217" t="n">
+        <v>265.8952897520346</v>
+      </c>
+      <c r="J217" t="n">
+        <v>543789216.1301517</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5233,6 +7845,18 @@
       <c r="F218" t="n">
         <v>2</v>
       </c>
+      <c r="G218" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H218" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I218" t="n">
+        <v>240.9662567092115</v>
+      </c>
+      <c r="J218" t="n">
+        <v>461731904.885516</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5255,6 +7879,18 @@
       <c r="F219" t="n">
         <v>2</v>
       </c>
+      <c r="G219" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H219" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I219" t="n">
+        <v>232.8831422498661</v>
+      </c>
+      <c r="J219" t="n">
+        <v>366902708.1497645</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5277,6 +7913,18 @@
       <c r="F220" t="n">
         <v>2</v>
       </c>
+      <c r="G220" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H220" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I220" t="n">
+        <v>247.7738698315432</v>
+      </c>
+      <c r="J220" t="n">
+        <v>628447407.5918573</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5299,6 +7947,18 @@
       <c r="F221" t="n">
         <v>2</v>
       </c>
+      <c r="G221" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H221" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I221" t="n">
+        <v>112.6602580518521</v>
+      </c>
+      <c r="J221" t="n">
+        <v>197295923.4980766</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5321,6 +7981,18 @@
       <c r="F222" t="n">
         <v>2</v>
       </c>
+      <c r="G222" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H222" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I222" t="n">
+        <v>212.0819758215432</v>
+      </c>
+      <c r="J222" t="n">
+        <v>381211639.4293283</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5343,6 +8015,18 @@
       <c r="F223" t="n">
         <v>2</v>
       </c>
+      <c r="G223" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H223" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I223" t="n">
+        <v>293.709077172085</v>
+      </c>
+      <c r="J223" t="n">
+        <v>636504142.8861978</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5365,6 +8049,18 @@
       <c r="F224" t="n">
         <v>2</v>
       </c>
+      <c r="G224" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H224" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I224" t="n">
+        <v>115.5900301533268</v>
+      </c>
+      <c r="J224" t="n">
+        <v>132132181.2092354</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5387,6 +8083,18 @@
       <c r="F225" t="n">
         <v>2</v>
       </c>
+      <c r="G225" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H225" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I225" t="n">
+        <v>271.5611334846315</v>
+      </c>
+      <c r="J225" t="n">
+        <v>706742458.2861888</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5409,6 +8117,18 @@
       <c r="F226" t="n">
         <v>2</v>
       </c>
+      <c r="G226" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H226" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I226" t="n">
+        <v>97.24423539040143</v>
+      </c>
+      <c r="J226" t="n">
+        <v>180037381.5377369</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5431,6 +8151,18 @@
       <c r="F227" t="n">
         <v>2</v>
       </c>
+      <c r="G227" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H227" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I227" t="n">
+        <v>313.550423294308</v>
+      </c>
+      <c r="J227" t="n">
+        <v>385769147.944246</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5453,6 +8185,18 @@
       <c r="F228" t="n">
         <v>2</v>
       </c>
+      <c r="G228" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H228" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I228" t="n">
+        <v>108.4127441231689</v>
+      </c>
+      <c r="J228" t="n">
+        <v>213103659.2262955</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5475,6 +8219,18 @@
       <c r="F229" t="n">
         <v>2</v>
       </c>
+      <c r="G229" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H229" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I229" t="n">
+        <v>250.6758741271072</v>
+      </c>
+      <c r="J229" t="n">
+        <v>396399151.2437602</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5497,6 +8253,18 @@
       <c r="F230" t="n">
         <v>2</v>
       </c>
+      <c r="G230" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H230" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I230" t="n">
+        <v>75.04265743794267</v>
+      </c>
+      <c r="J230" t="n">
+        <v>142450346.8103328</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5519,6 +8287,18 @@
       <c r="F231" t="n">
         <v>2</v>
       </c>
+      <c r="G231" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H231" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I231" t="n">
+        <v>246.1432344133759</v>
+      </c>
+      <c r="J231" t="n">
+        <v>665868672.6029083</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5541,6 +8321,18 @@
       <c r="F232" t="n">
         <v>2</v>
       </c>
+      <c r="G232" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H232" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I232" t="n">
+        <v>114.30192697602</v>
+      </c>
+      <c r="J232" t="n">
+        <v>405866284.3322625</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5563,6 +8355,18 @@
       <c r="F233" t="n">
         <v>2</v>
       </c>
+      <c r="G233" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H233" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I233" t="n">
+        <v>111.4629059928046</v>
+      </c>
+      <c r="J233" t="n">
+        <v>311937083.6715174</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5585,6 +8389,18 @@
       <c r="F234" t="n">
         <v>2</v>
       </c>
+      <c r="G234" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H234" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I234" t="n">
+        <v>297.2711195324988</v>
+      </c>
+      <c r="J234" t="n">
+        <v>1092737777.470173</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5607,6 +8423,18 @@
       <c r="F235" t="n">
         <v>2</v>
       </c>
+      <c r="G235" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H235" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I235" t="n">
+        <v>139.6136387191068</v>
+      </c>
+      <c r="J235" t="n">
+        <v>272340947.7954412</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5629,6 +8457,18 @@
       <c r="F236" t="n">
         <v>2</v>
       </c>
+      <c r="G236" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H236" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I236" t="n">
+        <v>110.9698302473184</v>
+      </c>
+      <c r="J236" t="n">
+        <v>193185925.992177</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5651,6 +8491,18 @@
       <c r="F237" t="n">
         <v>2</v>
       </c>
+      <c r="G237" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H237" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I237" t="n">
+        <v>248.3393938035115</v>
+      </c>
+      <c r="J237" t="n">
+        <v>964509740.2179911</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5673,6 +8525,18 @@
       <c r="F238" t="n">
         <v>2</v>
       </c>
+      <c r="G238" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H238" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I238" t="n">
+        <v>178.8354266787257</v>
+      </c>
+      <c r="J238" t="n">
+        <v>576563485.9779578</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5695,6 +8559,18 @@
       <c r="F239" t="n">
         <v>2</v>
       </c>
+      <c r="G239" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H239" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I239" t="n">
+        <v>312.1361089671532</v>
+      </c>
+      <c r="J239" t="n">
+        <v>821770414.9792442</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5717,6 +8593,18 @@
       <c r="F240" t="n">
         <v>2</v>
       </c>
+      <c r="G240" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H240" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I240" t="n">
+        <v>301.6611093529174</v>
+      </c>
+      <c r="J240" t="n">
+        <v>740451555.8724124</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5739,6 +8627,18 @@
       <c r="F241" t="n">
         <v>2</v>
       </c>
+      <c r="G241" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H241" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I241" t="n">
+        <v>269.1674756142003</v>
+      </c>
+      <c r="J241" t="n">
+        <v>690066809.8990117</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5761,6 +8661,18 @@
       <c r="F242" t="n">
         <v>2</v>
       </c>
+      <c r="G242" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H242" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I242" t="n">
+        <v>72.72870510989631</v>
+      </c>
+      <c r="J242" t="n">
+        <v>337861445.4110469</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5783,6 +8695,18 @@
       <c r="F243" t="n">
         <v>2</v>
       </c>
+      <c r="G243" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H243" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I243" t="n">
+        <v>248.0490537632104</v>
+      </c>
+      <c r="J243" t="n">
+        <v>440240280.9366871</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5805,6 +8729,18 @@
       <c r="F244" t="n">
         <v>2</v>
       </c>
+      <c r="G244" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H244" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I244" t="n">
+        <v>171.9775088426673</v>
+      </c>
+      <c r="J244" t="n">
+        <v>349123711.2534314</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5827,6 +8763,18 @@
       <c r="F245" t="n">
         <v>2</v>
       </c>
+      <c r="G245" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H245" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I245" t="n">
+        <v>106.9333808471959</v>
+      </c>
+      <c r="J245" t="n">
+        <v>218209222.0305501</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5849,6 +8797,18 @@
       <c r="F246" t="n">
         <v>2</v>
       </c>
+      <c r="G246" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H246" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I246" t="n">
+        <v>113.2379343681344</v>
+      </c>
+      <c r="J246" t="n">
+        <v>131020394.7125765</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5871,6 +8831,18 @@
       <c r="F247" t="n">
         <v>2</v>
       </c>
+      <c r="G247" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H247" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I247" t="n">
+        <v>105.4632331842252</v>
+      </c>
+      <c r="J247" t="n">
+        <v>229624100.4571438</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5893,6 +8865,18 @@
       <c r="F248" t="n">
         <v>2</v>
       </c>
+      <c r="G248" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H248" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I248" t="n">
+        <v>114.3491596408315</v>
+      </c>
+      <c r="J248" t="n">
+        <v>136324620.4800372</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5915,6 +8899,18 @@
       <c r="F249" t="n">
         <v>2</v>
       </c>
+      <c r="G249" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H249" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I249" t="n">
+        <v>245.1275395793918</v>
+      </c>
+      <c r="J249" t="n">
+        <v>401531149.049095</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5937,6 +8933,18 @@
       <c r="F250" t="n">
         <v>2</v>
       </c>
+      <c r="G250" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H250" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I250" t="n">
+        <v>260.1915026413278</v>
+      </c>
+      <c r="J250" t="n">
+        <v>311805261.7043087</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5959,6 +8967,18 @@
       <c r="F251" t="n">
         <v>2</v>
       </c>
+      <c r="G251" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H251" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I251" t="n">
+        <v>171.6099279259731</v>
+      </c>
+      <c r="J251" t="n">
+        <v>236101987.3772134</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5981,6 +9001,18 @@
       <c r="F252" t="n">
         <v>0</v>
       </c>
+      <c r="G252" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H252" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I252" t="n">
+        <v>550.2335312616356</v>
+      </c>
+      <c r="J252" t="n">
+        <v>280661160.7945638</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6003,6 +9035,18 @@
       <c r="F253" t="n">
         <v>0</v>
       </c>
+      <c r="G253" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H253" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I253" t="n">
+        <v>561.5482385892683</v>
+      </c>
+      <c r="J253" t="n">
+        <v>319366527.607164</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6025,6 +9069,18 @@
       <c r="F254" t="n">
         <v>0</v>
       </c>
+      <c r="G254" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H254" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I254" t="n">
+        <v>557.0579250598742</v>
+      </c>
+      <c r="J254" t="n">
+        <v>302810499.1490001</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6047,6 +9103,18 @@
       <c r="F255" t="n">
         <v>0</v>
       </c>
+      <c r="G255" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H255" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I255" t="n">
+        <v>700.0507512815924</v>
+      </c>
+      <c r="J255" t="n">
+        <v>748589813.1973212</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6069,6 +9137,18 @@
       <c r="F256" t="n">
         <v>0</v>
       </c>
+      <c r="G256" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H256" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I256" t="n">
+        <v>698.2315230580112</v>
+      </c>
+      <c r="J256" t="n">
+        <v>1088578393.661865</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6091,6 +9171,18 @@
       <c r="F257" t="n">
         <v>0</v>
       </c>
+      <c r="G257" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H257" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I257" t="n">
+        <v>579.0433028806783</v>
+      </c>
+      <c r="J257" t="n">
+        <v>1098044317.314311</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6113,6 +9205,18 @@
       <c r="F258" t="n">
         <v>0</v>
       </c>
+      <c r="G258" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H258" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I258" t="n">
+        <v>509.5702225252728</v>
+      </c>
+      <c r="J258" t="n">
+        <v>1000176457.998623</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6135,6 +9239,18 @@
       <c r="F259" t="n">
         <v>0</v>
       </c>
+      <c r="G259" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H259" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I259" t="n">
+        <v>844.261714845871</v>
+      </c>
+      <c r="J259" t="n">
+        <v>2055769913.687543</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6157,6 +9273,18 @@
       <c r="F260" t="n">
         <v>0</v>
       </c>
+      <c r="G260" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H260" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I260" t="n">
+        <v>1046.468721910672</v>
+      </c>
+      <c r="J260" t="n">
+        <v>1890337117.445953</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6179,6 +9307,18 @@
       <c r="F261" t="n">
         <v>0</v>
       </c>
+      <c r="G261" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H261" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I261" t="n">
+        <v>508.6605462586443</v>
+      </c>
+      <c r="J261" t="n">
+        <v>1319288422.778404</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6201,6 +9341,18 @@
       <c r="F262" t="n">
         <v>0</v>
       </c>
+      <c r="G262" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H262" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I262" t="n">
+        <v>996.6799687422387</v>
+      </c>
+      <c r="J262" t="n">
+        <v>1842773544.400351</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6223,6 +9375,18 @@
       <c r="F263" t="n">
         <v>0</v>
       </c>
+      <c r="G263" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H263" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I263" t="n">
+        <v>510.4480584785989</v>
+      </c>
+      <c r="J263" t="n">
+        <v>875364120.1024567</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6245,6 +9409,18 @@
       <c r="F264" t="n">
         <v>0</v>
       </c>
+      <c r="G264" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H264" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I264" t="n">
+        <v>513.2035290608322</v>
+      </c>
+      <c r="J264" t="n">
+        <v>1172408982.89907</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6267,6 +9443,18 @@
       <c r="F265" t="n">
         <v>0</v>
       </c>
+      <c r="G265" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H265" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I265" t="n">
+        <v>843.5142465454093</v>
+      </c>
+      <c r="J265" t="n">
+        <v>1047677878.059858</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6289,6 +9477,18 @@
       <c r="F266" t="n">
         <v>0</v>
       </c>
+      <c r="G266" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H266" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I266" t="n">
+        <v>553.8226352550597</v>
+      </c>
+      <c r="J266" t="n">
+        <v>661621583.3190528</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6311,6 +9511,18 @@
       <c r="F267" t="n">
         <v>0</v>
       </c>
+      <c r="G267" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H267" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I267" t="n">
+        <v>576.614965605559</v>
+      </c>
+      <c r="J267" t="n">
+        <v>915750204.2363192</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6333,6 +9545,18 @@
       <c r="F268" t="n">
         <v>0</v>
       </c>
+      <c r="G268" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H268" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I268" t="n">
+        <v>1085.208121862374</v>
+      </c>
+      <c r="J268" t="n">
+        <v>3180145742.401645</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6355,6 +9579,18 @@
       <c r="F269" t="n">
         <v>0</v>
       </c>
+      <c r="G269" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H269" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I269" t="n">
+        <v>1074.234516578657</v>
+      </c>
+      <c r="J269" t="n">
+        <v>2010856712.635084</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6377,6 +9613,18 @@
       <c r="F270" t="n">
         <v>0</v>
       </c>
+      <c r="G270" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H270" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I270" t="n">
+        <v>548.1254464247796</v>
+      </c>
+      <c r="J270" t="n">
+        <v>810532331.3502369</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6399,6 +9647,18 @@
       <c r="F271" t="n">
         <v>0</v>
       </c>
+      <c r="G271" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H271" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I271" t="n">
+        <v>582.3262762458045</v>
+      </c>
+      <c r="J271" t="n">
+        <v>875483881.8648489</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6421,6 +9681,18 @@
       <c r="F272" t="n">
         <v>0</v>
       </c>
+      <c r="G272" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H272" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I272" t="n">
+        <v>537.2466317410754</v>
+      </c>
+      <c r="J272" t="n">
+        <v>811783727.5177672</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6443,6 +9715,18 @@
       <c r="F273" t="n">
         <v>0</v>
       </c>
+      <c r="G273" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H273" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I273" t="n">
+        <v>515.9199484804882</v>
+      </c>
+      <c r="J273" t="n">
+        <v>1865244949.451321</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6465,6 +9749,18 @@
       <c r="F274" t="n">
         <v>0</v>
       </c>
+      <c r="G274" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H274" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I274" t="n">
+        <v>581.0252119959074</v>
+      </c>
+      <c r="J274" t="n">
+        <v>1785380964.831468</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6487,6 +9783,18 @@
       <c r="F275" t="n">
         <v>0</v>
       </c>
+      <c r="G275" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H275" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I275" t="n">
+        <v>536.8600299106262</v>
+      </c>
+      <c r="J275" t="n">
+        <v>934850985.9012996</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6509,6 +9817,18 @@
       <c r="F276" t="n">
         <v>0</v>
       </c>
+      <c r="G276" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H276" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I276" t="n">
+        <v>511.7048207086222</v>
+      </c>
+      <c r="J276" t="n">
+        <v>2090146102.678169</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6531,6 +9851,18 @@
       <c r="F277" t="n">
         <v>0</v>
       </c>
+      <c r="G277" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H277" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I277" t="n">
+        <v>510.6325809729246</v>
+      </c>
+      <c r="J277" t="n">
+        <v>1654548039.632731</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6553,6 +9885,18 @@
       <c r="F278" t="n">
         <v>0</v>
       </c>
+      <c r="G278" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H278" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I278" t="n">
+        <v>562.142259489176</v>
+      </c>
+      <c r="J278" t="n">
+        <v>774509874.4416752</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6575,6 +9919,18 @@
       <c r="F279" t="n">
         <v>0</v>
       </c>
+      <c r="G279" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H279" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I279" t="n">
+        <v>512.6701910738842</v>
+      </c>
+      <c r="J279" t="n">
+        <v>1767023595.852689</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6597,6 +9953,18 @@
       <c r="F280" t="n">
         <v>0</v>
       </c>
+      <c r="G280" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H280" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I280" t="n">
+        <v>1044.817507221502</v>
+      </c>
+      <c r="J280" t="n">
+        <v>2431430791.509889</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6619,6 +9987,18 @@
       <c r="F281" t="n">
         <v>0</v>
       </c>
+      <c r="G281" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H281" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I281" t="n">
+        <v>577.4516136517115</v>
+      </c>
+      <c r="J281" t="n">
+        <v>1109282808.808323</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6641,6 +10021,18 @@
       <c r="F282" t="n">
         <v>0</v>
       </c>
+      <c r="G282" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H282" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I282" t="n">
+        <v>516.5020371147132</v>
+      </c>
+      <c r="J282" t="n">
+        <v>900901741.6149809</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6663,6 +10055,18 @@
       <c r="F283" t="n">
         <v>0</v>
       </c>
+      <c r="G283" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H283" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I283" t="n">
+        <v>555.6912913684956</v>
+      </c>
+      <c r="J283" t="n">
+        <v>1067952168.660747</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6685,6 +10089,18 @@
       <c r="F284" t="n">
         <v>0</v>
       </c>
+      <c r="G284" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H284" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I284" t="n">
+        <v>557.0309337825607</v>
+      </c>
+      <c r="J284" t="n">
+        <v>1007126266.255105</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6707,6 +10123,18 @@
       <c r="F285" t="n">
         <v>0</v>
       </c>
+      <c r="G285" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H285" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I285" t="n">
+        <v>515.1266831373199</v>
+      </c>
+      <c r="J285" t="n">
+        <v>1068685440.7529</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6729,6 +10157,18 @@
       <c r="F286" t="n">
         <v>0</v>
       </c>
+      <c r="G286" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H286" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I286" t="n">
+        <v>581.1236556189809</v>
+      </c>
+      <c r="J286" t="n">
+        <v>873416296.3131312</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -6751,6 +10191,18 @@
       <c r="F287" t="n">
         <v>0</v>
       </c>
+      <c r="G287" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H287" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I287" t="n">
+        <v>553.5205715866714</v>
+      </c>
+      <c r="J287" t="n">
+        <v>714774215.9217983</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -6773,6 +10225,18 @@
       <c r="F288" t="n">
         <v>0</v>
       </c>
+      <c r="G288" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H288" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I288" t="n">
+        <v>807.3513364050648</v>
+      </c>
+      <c r="J288" t="n">
+        <v>1902028453.281212</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6795,6 +10259,18 @@
       <c r="F289" t="n">
         <v>0</v>
       </c>
+      <c r="G289" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H289" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I289" t="n">
+        <v>962.5966753539426</v>
+      </c>
+      <c r="J289" t="n">
+        <v>2917773035.435589</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6817,6 +10293,18 @@
       <c r="F290" t="n">
         <v>1</v>
       </c>
+      <c r="G290" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H290" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I290" t="n">
+        <v>195.8294926826765</v>
+      </c>
+      <c r="J290" t="n">
+        <v>470150206.8367577</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6839,6 +10327,18 @@
       <c r="F291" t="n">
         <v>3</v>
       </c>
+      <c r="G291" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H291" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I291" t="n">
+        <v>537.9737707618008</v>
+      </c>
+      <c r="J291" t="n">
+        <v>983113281.3143873</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6861,6 +10361,18 @@
       <c r="F292" t="n">
         <v>3</v>
       </c>
+      <c r="G292" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H292" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I292" t="n">
+        <v>325.7527379481806</v>
+      </c>
+      <c r="J292" t="n">
+        <v>794616851.8961529</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6883,6 +10395,18 @@
       <c r="F293" t="n">
         <v>1</v>
       </c>
+      <c r="G293" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H293" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I293" t="n">
+        <v>213.6074034689326</v>
+      </c>
+      <c r="J293" t="n">
+        <v>454319344.094355</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6905,6 +10429,18 @@
       <c r="F294" t="n">
         <v>3</v>
       </c>
+      <c r="G294" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H294" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I294" t="n">
+        <v>536.0748695206678</v>
+      </c>
+      <c r="J294" t="n">
+        <v>1011190934.106312</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6927,6 +10463,18 @@
       <c r="F295" t="n">
         <v>3</v>
       </c>
+      <c r="G295" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H295" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I295" t="n">
+        <v>374.8062599792478</v>
+      </c>
+      <c r="J295" t="n">
+        <v>770283682.0753205</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -6949,6 +10497,18 @@
       <c r="F296" t="n">
         <v>1</v>
       </c>
+      <c r="G296" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H296" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I296" t="n">
+        <v>66.89312229177543</v>
+      </c>
+      <c r="J296" t="n">
+        <v>125396624.4091195</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6971,6 +10531,18 @@
       <c r="F297" t="n">
         <v>3</v>
       </c>
+      <c r="G297" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H297" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I297" t="n">
+        <v>497.6277549216953</v>
+      </c>
+      <c r="J297" t="n">
+        <v>825007132.1872457</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6993,6 +10565,18 @@
       <c r="F298" t="n">
         <v>1</v>
       </c>
+      <c r="G298" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H298" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I298" t="n">
+        <v>123.1188905675009</v>
+      </c>
+      <c r="J298" t="n">
+        <v>256026749.8971543</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -7015,6 +10599,18 @@
       <c r="F299" t="n">
         <v>0</v>
       </c>
+      <c r="G299" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H299" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I299" t="n">
+        <v>627.4253330784752</v>
+      </c>
+      <c r="J299" t="n">
+        <v>587526269.447338</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -7037,6 +10633,18 @@
       <c r="F300" t="n">
         <v>1</v>
       </c>
+      <c r="G300" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H300" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I300" t="n">
+        <v>61.47167162779635</v>
+      </c>
+      <c r="J300" t="n">
+        <v>124350988.3507614</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7059,6 +10667,18 @@
       <c r="F301" t="n">
         <v>3</v>
       </c>
+      <c r="G301" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H301" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I301" t="n">
+        <v>597.7896412243185</v>
+      </c>
+      <c r="J301" t="n">
+        <v>1023802865.225128</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7081,6 +10701,18 @@
       <c r="F302" t="n">
         <v>3</v>
       </c>
+      <c r="G302" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H302" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I302" t="n">
+        <v>615.8969959031837</v>
+      </c>
+      <c r="J302" t="n">
+        <v>1027513048.323311</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -7103,6 +10735,18 @@
       <c r="F303" t="n">
         <v>0</v>
       </c>
+      <c r="G303" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H303" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I303" t="n">
+        <v>616.3496102117134</v>
+      </c>
+      <c r="J303" t="n">
+        <v>1058488401.258934</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -7125,6 +10769,18 @@
       <c r="F304" t="n">
         <v>0</v>
       </c>
+      <c r="G304" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H304" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I304" t="n">
+        <v>618.4095869413236</v>
+      </c>
+      <c r="J304" t="n">
+        <v>1571367219.039783</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -7147,6 +10803,18 @@
       <c r="F305" t="n">
         <v>0</v>
       </c>
+      <c r="G305" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H305" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I305" t="n">
+        <v>616.0961971153129</v>
+      </c>
+      <c r="J305" t="n">
+        <v>1372960292.549161</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -7169,6 +10837,18 @@
       <c r="F306" t="n">
         <v>1</v>
       </c>
+      <c r="G306" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H306" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I306" t="n">
+        <v>200.2053993384051</v>
+      </c>
+      <c r="J306" t="n">
+        <v>448615830.4942703</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7191,6 +10871,18 @@
       <c r="F307" t="n">
         <v>1</v>
       </c>
+      <c r="G307" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H307" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I307" t="n">
+        <v>271.365017209034</v>
+      </c>
+      <c r="J307" t="n">
+        <v>484423432.8671395</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -7213,6 +10905,18 @@
       <c r="F308" t="n">
         <v>1</v>
       </c>
+      <c r="G308" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H308" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I308" t="n">
+        <v>62.69887471408907</v>
+      </c>
+      <c r="J308" t="n">
+        <v>47533812.45977554</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -7235,6 +10939,18 @@
       <c r="F309" t="n">
         <v>0</v>
       </c>
+      <c r="G309" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H309" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I309" t="n">
+        <v>573.8387765074733</v>
+      </c>
+      <c r="J309" t="n">
+        <v>1203498229.281626</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -7257,6 +10973,18 @@
       <c r="F310" t="n">
         <v>3</v>
       </c>
+      <c r="G310" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H310" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I310" t="n">
+        <v>485.7432394022453</v>
+      </c>
+      <c r="J310" t="n">
+        <v>617392505.1889362</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -7279,6 +11007,18 @@
       <c r="F311" t="n">
         <v>1</v>
       </c>
+      <c r="G311" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H311" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I311" t="n">
+        <v>66.0268932691002</v>
+      </c>
+      <c r="J311" t="n">
+        <v>227213312.8931949</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7301,6 +11041,18 @@
       <c r="F312" t="n">
         <v>1</v>
       </c>
+      <c r="G312" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H312" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I312" t="n">
+        <v>198.7592680572442</v>
+      </c>
+      <c r="J312" t="n">
+        <v>701269007.7209983</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7323,6 +11075,18 @@
       <c r="F313" t="n">
         <v>1</v>
       </c>
+      <c r="G313" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H313" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I313" t="n">
+        <v>63.30485937058388</v>
+      </c>
+      <c r="J313" t="n">
+        <v>200189893.3829919</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7345,6 +11109,18 @@
       <c r="F314" t="n">
         <v>1</v>
       </c>
+      <c r="G314" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H314" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I314" t="n">
+        <v>171.2780401337388</v>
+      </c>
+      <c r="J314" t="n">
+        <v>597927768.935956</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7367,6 +11143,18 @@
       <c r="F315" t="n">
         <v>1</v>
       </c>
+      <c r="G315" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H315" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I315" t="n">
+        <v>207.2118431361766</v>
+      </c>
+      <c r="J315" t="n">
+        <v>566271113.3092823</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -7389,6 +11177,18 @@
       <c r="F316" t="n">
         <v>3</v>
       </c>
+      <c r="G316" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H316" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I316" t="n">
+        <v>596.9053902497836</v>
+      </c>
+      <c r="J316" t="n">
+        <v>1108558378.472903</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -7411,6 +11211,18 @@
       <c r="F317" t="n">
         <v>1</v>
       </c>
+      <c r="G317" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H317" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I317" t="n">
+        <v>121.7310041555266</v>
+      </c>
+      <c r="J317" t="n">
+        <v>292819579.7082998</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -7433,6 +11245,18 @@
       <c r="F318" t="n">
         <v>1</v>
       </c>
+      <c r="G318" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H318" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I318" t="n">
+        <v>49.89652576347511</v>
+      </c>
+      <c r="J318" t="n">
+        <v>116296587.9329807</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7455,6 +11279,18 @@
       <c r="F319" t="n">
         <v>3</v>
       </c>
+      <c r="G319" t="n">
+        <v>12.22678061272482</v>
+      </c>
+      <c r="H319" t="n">
+        <v>79.25786968483231</v>
+      </c>
+      <c r="I319" t="n">
+        <v>617.4279070361644</v>
+      </c>
+      <c r="J319" t="n">
+        <v>1515824014.578067</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -7477,6 +11313,18 @@
       <c r="F320" t="n">
         <v>0</v>
       </c>
+      <c r="G320" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H320" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I320" t="n">
+        <v>575.0112439592498</v>
+      </c>
+      <c r="J320" t="n">
+        <v>1317164398.766474</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7499,6 +11347,18 @@
       <c r="F321" t="n">
         <v>0</v>
       </c>
+      <c r="G321" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H321" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I321" t="n">
+        <v>619.2269057530879</v>
+      </c>
+      <c r="J321" t="n">
+        <v>1529587682.0266</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7521,6 +11381,18 @@
       <c r="F322" t="n">
         <v>1</v>
       </c>
+      <c r="G322" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H322" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I322" t="n">
+        <v>167.0822270632482</v>
+      </c>
+      <c r="J322" t="n">
+        <v>495850591.9136878</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7543,6 +11415,18 @@
       <c r="F323" t="n">
         <v>1</v>
       </c>
+      <c r="G323" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H323" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I323" t="n">
+        <v>270.1330052516413</v>
+      </c>
+      <c r="J323" t="n">
+        <v>794748406.2722214</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7565,6 +11449,18 @@
       <c r="F324" t="n">
         <v>1</v>
       </c>
+      <c r="G324" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H324" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I324" t="n">
+        <v>123.9640433675536</v>
+      </c>
+      <c r="J324" t="n">
+        <v>352437863.6378746</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7587,6 +11483,18 @@
       <c r="F325" t="n">
         <v>1</v>
       </c>
+      <c r="G325" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H325" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I325" t="n">
+        <v>185.6342827243591</v>
+      </c>
+      <c r="J325" t="n">
+        <v>356650762.2977605</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7609,6 +11517,18 @@
       <c r="F326" t="n">
         <v>1</v>
       </c>
+      <c r="G326" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H326" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I326" t="n">
+        <v>59.72511885034409</v>
+      </c>
+      <c r="J326" t="n">
+        <v>138647613.3716165</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7631,6 +11551,18 @@
       <c r="F327" t="n">
         <v>0</v>
       </c>
+      <c r="G327" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H327" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I327" t="n">
+        <v>614.1876446764838</v>
+      </c>
+      <c r="J327" t="n">
+        <v>1312276383.341184</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7653,6 +11585,18 @@
       <c r="F328" t="n">
         <v>0</v>
       </c>
+      <c r="G328" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H328" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I328" t="n">
+        <v>607.6027114558465</v>
+      </c>
+      <c r="J328" t="n">
+        <v>1952747054.75812</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7675,6 +11619,18 @@
       <c r="F329" t="n">
         <v>1</v>
       </c>
+      <c r="G329" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H329" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I329" t="n">
+        <v>241.5798000792561</v>
+      </c>
+      <c r="J329" t="n">
+        <v>390746092.2403388</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -7697,6 +11653,18 @@
       <c r="F330" t="n">
         <v>1</v>
       </c>
+      <c r="G330" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H330" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I330" t="n">
+        <v>218.3636872097339</v>
+      </c>
+      <c r="J330" t="n">
+        <v>320364219.5187925</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7719,6 +11687,18 @@
       <c r="F331" t="n">
         <v>0</v>
       </c>
+      <c r="G331" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H331" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I331" t="n">
+        <v>626.661873619375</v>
+      </c>
+      <c r="J331" t="n">
+        <v>1437071079.040261</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -7741,6 +11721,18 @@
       <c r="F332" t="n">
         <v>0</v>
       </c>
+      <c r="G332" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H332" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I332" t="n">
+        <v>533.6077234554629</v>
+      </c>
+      <c r="J332" t="n">
+        <v>1140372361.434475</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -7763,6 +11755,18 @@
       <c r="F333" t="n">
         <v>0</v>
       </c>
+      <c r="G333" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H333" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I333" t="n">
+        <v>623.878251310231</v>
+      </c>
+      <c r="J333" t="n">
+        <v>836584350.4274036</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -7785,6 +11789,18 @@
       <c r="F334" t="n">
         <v>1</v>
       </c>
+      <c r="G334" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H334" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I334" t="n">
+        <v>201.3426454253737</v>
+      </c>
+      <c r="J334" t="n">
+        <v>280794790.8983397</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -7807,6 +11823,18 @@
       <c r="F335" t="n">
         <v>1</v>
       </c>
+      <c r="G335" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H335" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I335" t="n">
+        <v>103.1380002652348</v>
+      </c>
+      <c r="J335" t="n">
+        <v>206563337.8423086</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -7829,6 +11857,18 @@
       <c r="F336" t="n">
         <v>1</v>
       </c>
+      <c r="G336" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H336" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I336" t="n">
+        <v>256.7168714137835</v>
+      </c>
+      <c r="J336" t="n">
+        <v>430043843.897183</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -7851,6 +11891,18 @@
       <c r="F337" t="n">
         <v>1</v>
       </c>
+      <c r="G337" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H337" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I337" t="n">
+        <v>95.76639060961472</v>
+      </c>
+      <c r="J337" t="n">
+        <v>133162855.8595637</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -7873,6 +11925,18 @@
       <c r="F338" t="n">
         <v>0</v>
       </c>
+      <c r="G338" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H338" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I338" t="n">
+        <v>260.3496983421461</v>
+      </c>
+      <c r="J338" t="n">
+        <v>803814984.7325741</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -7895,6 +11959,18 @@
       <c r="F339" t="n">
         <v>0</v>
       </c>
+      <c r="G339" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H339" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I339" t="n">
+        <v>339.5078169732922</v>
+      </c>
+      <c r="J339" t="n">
+        <v>890715541.3983641</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -7917,6 +11993,18 @@
       <c r="F340" t="n">
         <v>0</v>
       </c>
+      <c r="G340" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H340" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I340" t="n">
+        <v>268.4852574352886</v>
+      </c>
+      <c r="J340" t="n">
+        <v>553044213.0839599</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -7939,6 +12027,18 @@
       <c r="F341" t="n">
         <v>0</v>
       </c>
+      <c r="G341" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H341" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I341" t="n">
+        <v>246.0994041861252</v>
+      </c>
+      <c r="J341" t="n">
+        <v>435673707.4069776</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7961,6 +12061,18 @@
       <c r="F342" t="n">
         <v>0</v>
       </c>
+      <c r="G342" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H342" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I342" t="n">
+        <v>244.0803400677385</v>
+      </c>
+      <c r="J342" t="n">
+        <v>510791989.8860097</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7983,6 +12095,18 @@
       <c r="F343" t="n">
         <v>0</v>
       </c>
+      <c r="G343" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H343" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I343" t="n">
+        <v>265.1235430500931</v>
+      </c>
+      <c r="J343" t="n">
+        <v>643442165.2818481</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -8005,6 +12129,18 @@
       <c r="F344" t="n">
         <v>0</v>
       </c>
+      <c r="G344" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H344" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I344" t="n">
+        <v>220.5164664270967</v>
+      </c>
+      <c r="J344" t="n">
+        <v>558554141.5016021</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -8027,6 +12163,18 @@
       <c r="F345" t="n">
         <v>0</v>
       </c>
+      <c r="G345" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H345" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I345" t="n">
+        <v>266.4253604948988</v>
+      </c>
+      <c r="J345" t="n">
+        <v>567357107.9434592</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -8049,6 +12197,18 @@
       <c r="F346" t="n">
         <v>0</v>
       </c>
+      <c r="G346" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H346" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I346" t="n">
+        <v>262.1499381849978</v>
+      </c>
+      <c r="J346" t="n">
+        <v>484829174.5870694</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -8071,6 +12231,18 @@
       <c r="F347" t="n">
         <v>0</v>
       </c>
+      <c r="G347" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H347" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I347" t="n">
+        <v>256.6376844413774</v>
+      </c>
+      <c r="J347" t="n">
+        <v>518834466.4160201</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8093,6 +12265,18 @@
       <c r="F348" t="n">
         <v>0</v>
       </c>
+      <c r="G348" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H348" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I348" t="n">
+        <v>272.121281660024</v>
+      </c>
+      <c r="J348" t="n">
+        <v>578543799.1885346</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -8115,6 +12299,18 @@
       <c r="F349" t="n">
         <v>0</v>
       </c>
+      <c r="G349" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H349" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I349" t="n">
+        <v>123.9955394119936</v>
+      </c>
+      <c r="J349" t="n">
+        <v>204614500.4433878</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -8137,6 +12333,18 @@
       <c r="F350" t="n">
         <v>0</v>
       </c>
+      <c r="G350" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H350" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I350" t="n">
+        <v>338.753579945603</v>
+      </c>
+      <c r="J350" t="n">
+        <v>504830330.7811127</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -8159,6 +12367,18 @@
       <c r="F351" t="n">
         <v>0</v>
       </c>
+      <c r="G351" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H351" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I351" t="n">
+        <v>244.9481478563077</v>
+      </c>
+      <c r="J351" t="n">
+        <v>434256975.4891285</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -8181,6 +12401,18 @@
       <c r="F352" t="n">
         <v>0</v>
       </c>
+      <c r="G352" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H352" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I352" t="n">
+        <v>128.1288650973908</v>
+      </c>
+      <c r="J352" t="n">
+        <v>194654649.6210633</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -8203,6 +12435,18 @@
       <c r="F353" t="n">
         <v>0</v>
       </c>
+      <c r="G353" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H353" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I353" t="n">
+        <v>270.1477232966168</v>
+      </c>
+      <c r="J353" t="n">
+        <v>780615173.7214816</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -8225,6 +12469,18 @@
       <c r="F354" t="n">
         <v>0</v>
       </c>
+      <c r="G354" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H354" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I354" t="n">
+        <v>224.5097660238579</v>
+      </c>
+      <c r="J354" t="n">
+        <v>448812828.1512354</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -8247,6 +12503,18 @@
       <c r="F355" t="n">
         <v>0</v>
       </c>
+      <c r="G355" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H355" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I355" t="n">
+        <v>319.9119139195989</v>
+      </c>
+      <c r="J355" t="n">
+        <v>1290371707.666499</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -8269,6 +12537,18 @@
       <c r="F356" t="n">
         <v>0</v>
       </c>
+      <c r="G356" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H356" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I356" t="n">
+        <v>127.30602726443</v>
+      </c>
+      <c r="J356" t="n">
+        <v>289466022.1601622</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -8291,6 +12571,18 @@
       <c r="F357" t="n">
         <v>0</v>
       </c>
+      <c r="G357" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H357" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I357" t="n">
+        <v>247.0030921458697</v>
+      </c>
+      <c r="J357" t="n">
+        <v>661611854.078872</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -8313,6 +12605,18 @@
       <c r="F358" t="n">
         <v>0</v>
       </c>
+      <c r="G358" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H358" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I358" t="n">
+        <v>245.8723846358603</v>
+      </c>
+      <c r="J358" t="n">
+        <v>707239223.8248556</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -8335,6 +12639,18 @@
       <c r="F359" t="n">
         <v>0</v>
       </c>
+      <c r="G359" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H359" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I359" t="n">
+        <v>259.1175712553428</v>
+      </c>
+      <c r="J359" t="n">
+        <v>1032795200.426645</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -8357,6 +12673,18 @@
       <c r="F360" t="n">
         <v>0</v>
       </c>
+      <c r="G360" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H360" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I360" t="n">
+        <v>267.5215536520797</v>
+      </c>
+      <c r="J360" t="n">
+        <v>509289588.4970104</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -8379,6 +12707,18 @@
       <c r="F361" t="n">
         <v>0</v>
       </c>
+      <c r="G361" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H361" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I361" t="n">
+        <v>394.2085802884727</v>
+      </c>
+      <c r="J361" t="n">
+        <v>1253556684.122345</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -8401,6 +12741,18 @@
       <c r="F362" t="n">
         <v>0</v>
       </c>
+      <c r="G362" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H362" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I362" t="n">
+        <v>269.2177499230888</v>
+      </c>
+      <c r="J362" t="n">
+        <v>721867371.8158817</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -8423,6 +12775,18 @@
       <c r="F363" t="n">
         <v>0</v>
       </c>
+      <c r="G363" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H363" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I363" t="n">
+        <v>265.7120377715198</v>
+      </c>
+      <c r="J363" t="n">
+        <v>710893425.7909821</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -8445,6 +12809,18 @@
       <c r="F364" t="n">
         <v>0</v>
       </c>
+      <c r="G364" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H364" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I364" t="n">
+        <v>272.0407614309759</v>
+      </c>
+      <c r="J364" t="n">
+        <v>511795833.0234653</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -8467,6 +12843,18 @@
       <c r="F365" t="n">
         <v>0</v>
       </c>
+      <c r="G365" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H365" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I365" t="n">
+        <v>267.1609274923284</v>
+      </c>
+      <c r="J365" t="n">
+        <v>262093404.325803</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -8489,6 +12877,18 @@
       <c r="F366" t="n">
         <v>0</v>
       </c>
+      <c r="G366" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H366" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I366" t="n">
+        <v>119.9739091585612</v>
+      </c>
+      <c r="J366" t="n">
+        <v>177922924.5304417</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -8511,6 +12911,18 @@
       <c r="F367" t="n">
         <v>0</v>
       </c>
+      <c r="G367" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H367" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I367" t="n">
+        <v>393.9184922121719</v>
+      </c>
+      <c r="J367" t="n">
+        <v>578707621.5773817</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -8533,6 +12945,18 @@
       <c r="F368" t="n">
         <v>0</v>
       </c>
+      <c r="G368" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H368" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I368" t="n">
+        <v>283.3056721743233</v>
+      </c>
+      <c r="J368" t="n">
+        <v>359798550.569186</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -8555,6 +12979,18 @@
       <c r="F369" t="n">
         <v>2</v>
       </c>
+      <c r="G369" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H369" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I369" t="n">
+        <v>755.4364692614545</v>
+      </c>
+      <c r="J369" t="n">
+        <v>2543765309.674872</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -8577,6 +13013,18 @@
       <c r="F370" t="n">
         <v>2</v>
       </c>
+      <c r="G370" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H370" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I370" t="n">
+        <v>737.0602738658094</v>
+      </c>
+      <c r="J370" t="n">
+        <v>1748253812.82275</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -8599,6 +13047,18 @@
       <c r="F371" t="n">
         <v>2</v>
       </c>
+      <c r="G371" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H371" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I371" t="n">
+        <v>407.9443120675884</v>
+      </c>
+      <c r="J371" t="n">
+        <v>946652121.944988</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -8621,6 +13081,18 @@
       <c r="F372" t="n">
         <v>2</v>
       </c>
+      <c r="G372" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H372" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I372" t="n">
+        <v>879.9928298660333</v>
+      </c>
+      <c r="J372" t="n">
+        <v>1883162620.892852</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -8643,6 +13115,18 @@
       <c r="F373" t="n">
         <v>2</v>
       </c>
+      <c r="G373" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H373" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I373" t="n">
+        <v>762.9026211265187</v>
+      </c>
+      <c r="J373" t="n">
+        <v>675559929.3547159</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -8665,6 +13149,18 @@
       <c r="F374" t="n">
         <v>2</v>
       </c>
+      <c r="G374" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H374" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I374" t="n">
+        <v>767.4385075145673</v>
+      </c>
+      <c r="J374" t="n">
+        <v>2602349520.992911</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -8687,6 +13183,18 @@
       <c r="F375" t="n">
         <v>2</v>
       </c>
+      <c r="G375" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H375" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I375" t="n">
+        <v>737.3593294495913</v>
+      </c>
+      <c r="J375" t="n">
+        <v>1639844537.806281</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -8709,6 +13217,18 @@
       <c r="F376" t="n">
         <v>2</v>
       </c>
+      <c r="G376" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H376" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I376" t="n">
+        <v>732.0924029321508</v>
+      </c>
+      <c r="J376" t="n">
+        <v>1864231406.418503</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -8731,6 +13251,18 @@
       <c r="F377" t="n">
         <v>2</v>
       </c>
+      <c r="G377" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H377" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I377" t="n">
+        <v>885.0784624488344</v>
+      </c>
+      <c r="J377" t="n">
+        <v>921473871.2618241</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -8753,6 +13285,18 @@
       <c r="F378" t="n">
         <v>2</v>
       </c>
+      <c r="G378" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H378" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I378" t="n">
+        <v>883.3096566025587</v>
+      </c>
+      <c r="J378" t="n">
+        <v>1191985307.686121</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -8775,6 +13319,18 @@
       <c r="F379" t="n">
         <v>2</v>
       </c>
+      <c r="G379" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H379" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I379" t="n">
+        <v>736.889207163484</v>
+      </c>
+      <c r="J379" t="n">
+        <v>2479412876.508182</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -8797,6 +13353,18 @@
       <c r="F380" t="n">
         <v>2</v>
       </c>
+      <c r="G380" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H380" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I380" t="n">
+        <v>844.8787435615096</v>
+      </c>
+      <c r="J380" t="n">
+        <v>809006949.4576747</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -8819,6 +13387,18 @@
       <c r="F381" t="n">
         <v>2</v>
       </c>
+      <c r="G381" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H381" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I381" t="n">
+        <v>455.5450121192576</v>
+      </c>
+      <c r="J381" t="n">
+        <v>834751303.5170106</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -8841,6 +13421,18 @@
       <c r="F382" t="n">
         <v>2</v>
       </c>
+      <c r="G382" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H382" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I382" t="n">
+        <v>734.8010227130336</v>
+      </c>
+      <c r="J382" t="n">
+        <v>2077619369.923624</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -8863,6 +13455,18 @@
       <c r="F383" t="n">
         <v>2</v>
       </c>
+      <c r="G383" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H383" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I383" t="n">
+        <v>732.5636727352477</v>
+      </c>
+      <c r="J383" t="n">
+        <v>3764801545.08032</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -8885,6 +13489,18 @@
       <c r="F384" t="n">
         <v>2</v>
       </c>
+      <c r="G384" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H384" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I384" t="n">
+        <v>735.2834981467736</v>
+      </c>
+      <c r="J384" t="n">
+        <v>2813106657.827666</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -8907,6 +13523,18 @@
       <c r="F385" t="n">
         <v>2</v>
       </c>
+      <c r="G385" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H385" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I385" t="n">
+        <v>763.5216114415061</v>
+      </c>
+      <c r="J385" t="n">
+        <v>2987430169.213413</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -8929,6 +13557,18 @@
       <c r="F386" t="n">
         <v>2</v>
       </c>
+      <c r="G386" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H386" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I386" t="n">
+        <v>453.3744570574661</v>
+      </c>
+      <c r="J386" t="n">
+        <v>1271880305.541777</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -8951,6 +13591,18 @@
       <c r="F387" t="n">
         <v>2</v>
       </c>
+      <c r="G387" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H387" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I387" t="n">
+        <v>739.4024454744151</v>
+      </c>
+      <c r="J387" t="n">
+        <v>3343601907.499846</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -8973,6 +13625,18 @@
       <c r="F388" t="n">
         <v>2</v>
       </c>
+      <c r="G388" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H388" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I388" t="n">
+        <v>728.3554642433388</v>
+      </c>
+      <c r="J388" t="n">
+        <v>2072285407.222883</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -8995,6 +13659,18 @@
       <c r="F389" t="n">
         <v>2</v>
       </c>
+      <c r="G389" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H389" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I389" t="n">
+        <v>728.7075752636654</v>
+      </c>
+      <c r="J389" t="n">
+        <v>1667858633.048953</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -9017,6 +13693,18 @@
       <c r="F390" t="n">
         <v>2</v>
       </c>
+      <c r="G390" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H390" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I390" t="n">
+        <v>738.2112070147015</v>
+      </c>
+      <c r="J390" t="n">
+        <v>1507033729.565337</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -9039,6 +13727,18 @@
       <c r="F391" t="n">
         <v>2</v>
       </c>
+      <c r="G391" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H391" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I391" t="n">
+        <v>909.2151633942545</v>
+      </c>
+      <c r="J391" t="n">
+        <v>822952474.6442128</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -9061,6 +13761,18 @@
       <c r="F392" t="n">
         <v>2</v>
       </c>
+      <c r="G392" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H392" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I392" t="n">
+        <v>730.4862665823251</v>
+      </c>
+      <c r="J392" t="n">
+        <v>1732160774.948293</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -9083,6 +13795,18 @@
       <c r="F393" t="n">
         <v>2</v>
       </c>
+      <c r="G393" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H393" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I393" t="n">
+        <v>887.7534123901355</v>
+      </c>
+      <c r="J393" t="n">
+        <v>1642925318.039469</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -9105,6 +13829,18 @@
       <c r="F394" t="n">
         <v>2</v>
       </c>
+      <c r="G394" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H394" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I394" t="n">
+        <v>725.6101542216179</v>
+      </c>
+      <c r="J394" t="n">
+        <v>1259546322.788732</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -9127,6 +13863,18 @@
       <c r="F395" t="n">
         <v>2</v>
       </c>
+      <c r="G395" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H395" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I395" t="n">
+        <v>715.8419916078705</v>
+      </c>
+      <c r="J395" t="n">
+        <v>2057308702.11649</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -9149,6 +13897,18 @@
       <c r="F396" t="n">
         <v>2</v>
       </c>
+      <c r="G396" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H396" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I396" t="n">
+        <v>707.3848536348678</v>
+      </c>
+      <c r="J396" t="n">
+        <v>597093672.7867867</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -9171,6 +13931,18 @@
       <c r="F397" t="n">
         <v>1</v>
       </c>
+      <c r="G397" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H397" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I397" t="n">
+        <v>402.8528284779557</v>
+      </c>
+      <c r="J397" t="n">
+        <v>935648098.3972557</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -9193,6 +13965,18 @@
       <c r="F398" t="n">
         <v>1</v>
       </c>
+      <c r="G398" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H398" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I398" t="n">
+        <v>318.7461283580383</v>
+      </c>
+      <c r="J398" t="n">
+        <v>565386521.6497289</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -9215,6 +13999,18 @@
       <c r="F399" t="n">
         <v>2</v>
       </c>
+      <c r="G399" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H399" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I399" t="n">
+        <v>660.8614547036476</v>
+      </c>
+      <c r="J399" t="n">
+        <v>2251383204.405161</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -9237,6 +14033,18 @@
       <c r="F400" t="n">
         <v>1</v>
       </c>
+      <c r="G400" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H400" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I400" t="n">
+        <v>415.0220367356314</v>
+      </c>
+      <c r="J400" t="n">
+        <v>421964798.6581562</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -9259,6 +14067,18 @@
       <c r="F401" t="n">
         <v>1</v>
       </c>
+      <c r="G401" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H401" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I401" t="n">
+        <v>404.0941521558714</v>
+      </c>
+      <c r="J401" t="n">
+        <v>946322687.1099243</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -9281,6 +14101,18 @@
       <c r="F402" t="n">
         <v>1</v>
       </c>
+      <c r="G402" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H402" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I402" t="n">
+        <v>531.9172069611084</v>
+      </c>
+      <c r="J402" t="n">
+        <v>831825471.920835</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -9303,6 +14135,18 @@
       <c r="F403" t="n">
         <v>1</v>
       </c>
+      <c r="G403" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H403" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I403" t="n">
+        <v>408.0188493815209</v>
+      </c>
+      <c r="J403" t="n">
+        <v>473546701.6853523</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -9325,6 +14169,18 @@
       <c r="F404" t="n">
         <v>1</v>
       </c>
+      <c r="G404" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H404" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I404" t="n">
+        <v>539.6096633611475</v>
+      </c>
+      <c r="J404" t="n">
+        <v>1468257018.288518</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -9347,6 +14203,18 @@
       <c r="F405" t="n">
         <v>2</v>
       </c>
+      <c r="G405" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H405" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I405" t="n">
+        <v>703.1264574838835</v>
+      </c>
+      <c r="J405" t="n">
+        <v>2670249760.019319</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -9369,6 +14237,18 @@
       <c r="F406" t="n">
         <v>1</v>
       </c>
+      <c r="G406" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H406" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I406" t="n">
+        <v>799.0464878757987</v>
+      </c>
+      <c r="J406" t="n">
+        <v>1974447303.445765</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -9391,6 +14271,18 @@
       <c r="F407" t="n">
         <v>1</v>
       </c>
+      <c r="G407" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H407" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I407" t="n">
+        <v>403.6412926718086</v>
+      </c>
+      <c r="J407" t="n">
+        <v>840454374.9202621</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -9413,6 +14305,18 @@
       <c r="F408" t="n">
         <v>2</v>
       </c>
+      <c r="G408" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H408" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I408" t="n">
+        <v>658.928053837548</v>
+      </c>
+      <c r="J408" t="n">
+        <v>2175157697.341105</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -9435,6 +14339,18 @@
       <c r="F409" t="n">
         <v>1</v>
       </c>
+      <c r="G409" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H409" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I409" t="n">
+        <v>531.1964786528766</v>
+      </c>
+      <c r="J409" t="n">
+        <v>2339886460.019499</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -9457,6 +14373,18 @@
       <c r="F410" t="n">
         <v>2</v>
       </c>
+      <c r="G410" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H410" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I410" t="n">
+        <v>702.5680044936581</v>
+      </c>
+      <c r="J410" t="n">
+        <v>2713057932.955773</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -9479,6 +14407,18 @@
       <c r="F411" t="n">
         <v>1</v>
       </c>
+      <c r="G411" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H411" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I411" t="n">
+        <v>404.3147527355172</v>
+      </c>
+      <c r="J411" t="n">
+        <v>491772570.1637354</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -9501,6 +14441,18 @@
       <c r="F412" t="n">
         <v>1</v>
       </c>
+      <c r="G412" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H412" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I412" t="n">
+        <v>731.1957182903645</v>
+      </c>
+      <c r="J412" t="n">
+        <v>1493378524.738852</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -9523,6 +14475,18 @@
       <c r="F413" t="n">
         <v>1</v>
       </c>
+      <c r="G413" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H413" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I413" t="n">
+        <v>513.4781853654288</v>
+      </c>
+      <c r="J413" t="n">
+        <v>1355122802.999924</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -9545,6 +14509,18 @@
       <c r="F414" t="n">
         <v>2</v>
       </c>
+      <c r="G414" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H414" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I414" t="n">
+        <v>691.0893860919261</v>
+      </c>
+      <c r="J414" t="n">
+        <v>2096692743.591668</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -9567,6 +14543,18 @@
       <c r="F415" t="n">
         <v>1</v>
       </c>
+      <c r="G415" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H415" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I415" t="n">
+        <v>689.0716245778688</v>
+      </c>
+      <c r="J415" t="n">
+        <v>925201053.7212481</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -9589,6 +14577,18 @@
       <c r="F416" t="n">
         <v>1</v>
       </c>
+      <c r="G416" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H416" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I416" t="n">
+        <v>733.8647042878714</v>
+      </c>
+      <c r="J416" t="n">
+        <v>891620414.7958186</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -9611,6 +14611,18 @@
       <c r="F417" t="n">
         <v>2</v>
       </c>
+      <c r="G417" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H417" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I417" t="n">
+        <v>687.9706222615004</v>
+      </c>
+      <c r="J417" t="n">
+        <v>1123023726.05312</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -9633,6 +14645,18 @@
       <c r="F418" t="n">
         <v>0</v>
       </c>
+      <c r="G418" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H418" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I418" t="n">
+        <v>471.9688111199325</v>
+      </c>
+      <c r="J418" t="n">
+        <v>601922628.0265219</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -9655,6 +14679,18 @@
       <c r="F419" t="n">
         <v>2</v>
       </c>
+      <c r="G419" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H419" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I419" t="n">
+        <v>392.8925776521635</v>
+      </c>
+      <c r="J419" t="n">
+        <v>249140943.1176454</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -9677,6 +14713,18 @@
       <c r="F420" t="n">
         <v>0</v>
       </c>
+      <c r="G420" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H420" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I420" t="n">
+        <v>468.1659299344697</v>
+      </c>
+      <c r="J420" t="n">
+        <v>482915525.647011</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -9699,6 +14747,18 @@
       <c r="F421" t="n">
         <v>0</v>
       </c>
+      <c r="G421" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H421" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I421" t="n">
+        <v>437.6301333322829</v>
+      </c>
+      <c r="J421" t="n">
+        <v>403776252.1953589</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -9721,6 +14781,18 @@
       <c r="F422" t="n">
         <v>0</v>
       </c>
+      <c r="G422" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H422" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I422" t="n">
+        <v>469.3464139810218</v>
+      </c>
+      <c r="J422" t="n">
+        <v>255828583.5758611</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -9743,6 +14815,18 @@
       <c r="F423" t="n">
         <v>2</v>
       </c>
+      <c r="G423" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H423" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I423" t="n">
+        <v>404.1736028081135</v>
+      </c>
+      <c r="J423" t="n">
+        <v>327876498.8678573</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -9765,6 +14849,18 @@
       <c r="F424" t="n">
         <v>0</v>
       </c>
+      <c r="G424" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H424" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I424" t="n">
+        <v>475.7548095131403</v>
+      </c>
+      <c r="J424" t="n">
+        <v>1244054196.65121</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -9787,6 +14883,18 @@
       <c r="F425" t="n">
         <v>2</v>
       </c>
+      <c r="G425" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H425" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I425" t="n">
+        <v>374.4568889247058</v>
+      </c>
+      <c r="J425" t="n">
+        <v>949628203.8497303</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -9809,6 +14917,18 @@
       <c r="F426" t="n">
         <v>0</v>
       </c>
+      <c r="G426" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H426" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I426" t="n">
+        <v>398.5444258603678</v>
+      </c>
+      <c r="J426" t="n">
+        <v>951732181.3991256</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -9831,6 +14951,18 @@
       <c r="F427" t="n">
         <v>0</v>
       </c>
+      <c r="G427" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H427" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I427" t="n">
+        <v>477.6547662961582</v>
+      </c>
+      <c r="J427" t="n">
+        <v>1043369508.66872</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -9853,6 +14985,18 @@
       <c r="F428" t="n">
         <v>2</v>
       </c>
+      <c r="G428" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H428" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I428" t="n">
+        <v>372.3583100653588</v>
+      </c>
+      <c r="J428" t="n">
+        <v>711925849.031939</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -9875,6 +15019,18 @@
       <c r="F429" t="n">
         <v>2</v>
       </c>
+      <c r="G429" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H429" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I429" t="n">
+        <v>376.8661815300433</v>
+      </c>
+      <c r="J429" t="n">
+        <v>919658215.7410511</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -9897,6 +15053,18 @@
       <c r="F430" t="n">
         <v>2</v>
       </c>
+      <c r="G430" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H430" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I430" t="n">
+        <v>382.8441201566035</v>
+      </c>
+      <c r="J430" t="n">
+        <v>843896142.7244591</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -9919,6 +15087,18 @@
       <c r="F431" t="n">
         <v>2</v>
       </c>
+      <c r="G431" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H431" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I431" t="n">
+        <v>330.9711404490843</v>
+      </c>
+      <c r="J431" t="n">
+        <v>1337380027.377418</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -9941,6 +15121,18 @@
       <c r="F432" t="n">
         <v>1</v>
       </c>
+      <c r="G432" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H432" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I432" t="n">
+        <v>396.4694872636811</v>
+      </c>
+      <c r="J432" t="n">
+        <v>669745985.1679655</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -9963,6 +15155,18 @@
       <c r="F433" t="n">
         <v>2</v>
       </c>
+      <c r="G433" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H433" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I433" t="n">
+        <v>548.1075770880702</v>
+      </c>
+      <c r="J433" t="n">
+        <v>785740570.2936796</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -9985,6 +15189,18 @@
       <c r="F434" t="n">
         <v>0</v>
       </c>
+      <c r="G434" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H434" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I434" t="n">
+        <v>338.3448745348402</v>
+      </c>
+      <c r="J434" t="n">
+        <v>962461235.6686951</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -10007,6 +15223,18 @@
       <c r="F435" t="n">
         <v>2</v>
       </c>
+      <c r="G435" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H435" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I435" t="n">
+        <v>364.9139797676369</v>
+      </c>
+      <c r="J435" t="n">
+        <v>757868426.318277</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -10029,6 +15257,18 @@
       <c r="F436" t="n">
         <v>2</v>
       </c>
+      <c r="G436" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H436" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I436" t="n">
+        <v>400.3918586212197</v>
+      </c>
+      <c r="J436" t="n">
+        <v>821050787.3764163</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -10051,6 +15291,18 @@
       <c r="F437" t="n">
         <v>2</v>
       </c>
+      <c r="G437" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H437" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I437" t="n">
+        <v>379.8599159448746</v>
+      </c>
+      <c r="J437" t="n">
+        <v>423421126.9100116</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -10073,6 +15325,18 @@
       <c r="F438" t="n">
         <v>2</v>
       </c>
+      <c r="G438" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H438" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I438" t="n">
+        <v>383.8761460419659</v>
+      </c>
+      <c r="J438" t="n">
+        <v>842168505.4461706</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -10095,6 +15359,18 @@
       <c r="F439" t="n">
         <v>0</v>
       </c>
+      <c r="G439" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H439" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I439" t="n">
+        <v>523.1538446003622</v>
+      </c>
+      <c r="J439" t="n">
+        <v>825873656.9291403</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -10117,6 +15393,18 @@
       <c r="F440" t="n">
         <v>2</v>
       </c>
+      <c r="G440" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H440" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I440" t="n">
+        <v>540.4447070157765</v>
+      </c>
+      <c r="J440" t="n">
+        <v>931737008.1979972</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -10139,6 +15427,18 @@
       <c r="F441" t="n">
         <v>2</v>
       </c>
+      <c r="G441" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H441" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I441" t="n">
+        <v>541.063100766626</v>
+      </c>
+      <c r="J441" t="n">
+        <v>651083569.6479119</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -10161,6 +15461,18 @@
       <c r="F442" t="n">
         <v>2</v>
       </c>
+      <c r="G442" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H442" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I442" t="n">
+        <v>361.7951034920814</v>
+      </c>
+      <c r="J442" t="n">
+        <v>539439451.5547379</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -10183,6 +15495,18 @@
       <c r="F443" t="n">
         <v>2</v>
       </c>
+      <c r="G443" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H443" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I443" t="n">
+        <v>379.865662713909</v>
+      </c>
+      <c r="J443" t="n">
+        <v>469858812.558973</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -10205,6 +15529,18 @@
       <c r="F444" t="n">
         <v>0</v>
       </c>
+      <c r="G444" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H444" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I444" t="n">
+        <v>472.3741090501651</v>
+      </c>
+      <c r="J444" t="n">
+        <v>815767409.6798686</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -10227,6 +15563,18 @@
       <c r="F445" t="n">
         <v>0</v>
       </c>
+      <c r="G445" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H445" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I445" t="n">
+        <v>478.0656556116565</v>
+      </c>
+      <c r="J445" t="n">
+        <v>784496857.2036831</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -10249,6 +15597,18 @@
       <c r="F446" t="n">
         <v>0</v>
       </c>
+      <c r="G446" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H446" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I446" t="n">
+        <v>470.8794772176558</v>
+      </c>
+      <c r="J446" t="n">
+        <v>1392067744.553388</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -10271,6 +15631,18 @@
       <c r="F447" t="n">
         <v>2</v>
       </c>
+      <c r="G447" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H447" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I447" t="n">
+        <v>376.3643359901362</v>
+      </c>
+      <c r="J447" t="n">
+        <v>697811671.2491915</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -10293,6 +15665,18 @@
       <c r="F448" t="n">
         <v>2</v>
       </c>
+      <c r="G448" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H448" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I448" t="n">
+        <v>539.3000932963816</v>
+      </c>
+      <c r="J448" t="n">
+        <v>1248196015.710936</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -10315,6 +15699,18 @@
       <c r="F449" t="n">
         <v>2</v>
       </c>
+      <c r="G449" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H449" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I449" t="n">
+        <v>377.8027639282422</v>
+      </c>
+      <c r="J449" t="n">
+        <v>796485743.2517929</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -10337,6 +15733,18 @@
       <c r="F450" t="n">
         <v>1</v>
       </c>
+      <c r="G450" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H450" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I450" t="n">
+        <v>423.1133016556792</v>
+      </c>
+      <c r="J450" t="n">
+        <v>781795686.1481403</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -10359,6 +15767,18 @@
       <c r="F451" t="n">
         <v>0</v>
       </c>
+      <c r="G451" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H451" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I451" t="n">
+        <v>398.4308918550063</v>
+      </c>
+      <c r="J451" t="n">
+        <v>883862388.0689441</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -10381,6 +15801,18 @@
       <c r="F452" t="n">
         <v>2</v>
       </c>
+      <c r="G452" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H452" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I452" t="n">
+        <v>384.5226986211789</v>
+      </c>
+      <c r="J452" t="n">
+        <v>771174411.9457096</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -10403,6 +15835,18 @@
       <c r="F453" t="n">
         <v>0</v>
       </c>
+      <c r="G453" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H453" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I453" t="n">
+        <v>289.6683614717405</v>
+      </c>
+      <c r="J453" t="n">
+        <v>843358189.0646777</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -10425,6 +15869,18 @@
       <c r="F454" t="n">
         <v>0</v>
       </c>
+      <c r="G454" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H454" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I454" t="n">
+        <v>476.671625154577</v>
+      </c>
+      <c r="J454" t="n">
+        <v>873133816.0454352</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -10447,6 +15903,18 @@
       <c r="F455" t="n">
         <v>2</v>
       </c>
+      <c r="G455" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H455" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I455" t="n">
+        <v>379.2930854802572</v>
+      </c>
+      <c r="J455" t="n">
+        <v>1096941820.326266</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -10469,6 +15937,18 @@
       <c r="F456" t="n">
         <v>2</v>
       </c>
+      <c r="G456" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H456" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I456" t="n">
+        <v>384.8164371505356</v>
+      </c>
+      <c r="J456" t="n">
+        <v>1460096296.608544</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -10491,6 +15971,18 @@
       <c r="F457" t="n">
         <v>0</v>
       </c>
+      <c r="G457" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H457" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I457" t="n">
+        <v>471.1318091223583</v>
+      </c>
+      <c r="J457" t="n">
+        <v>460652259.3959167</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -10513,6 +16005,18 @@
       <c r="F458" t="n">
         <v>2</v>
       </c>
+      <c r="G458" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H458" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I458" t="n">
+        <v>544.1825747253724</v>
+      </c>
+      <c r="J458" t="n">
+        <v>1351136201.177172</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -10535,6 +16039,18 @@
       <c r="F459" t="n">
         <v>0</v>
       </c>
+      <c r="G459" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H459" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I459" t="n">
+        <v>399.465320450838</v>
+      </c>
+      <c r="J459" t="n">
+        <v>709938867.3252294</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -10557,6 +16073,18 @@
       <c r="F460" t="n">
         <v>2</v>
       </c>
+      <c r="G460" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H460" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I460" t="n">
+        <v>369.0119065625322</v>
+      </c>
+      <c r="J460" t="n">
+        <v>958500729.7078063</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -10579,6 +16107,18 @@
       <c r="F461" t="n">
         <v>2</v>
       </c>
+      <c r="G461" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H461" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I461" t="n">
+        <v>370.650238082961</v>
+      </c>
+      <c r="J461" t="n">
+        <v>634020581.7974335</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -10601,6 +16141,18 @@
       <c r="F462" t="n">
         <v>2</v>
       </c>
+      <c r="G462" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H462" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I462" t="n">
+        <v>333.6557619236073</v>
+      </c>
+      <c r="J462" t="n">
+        <v>940219596.3450475</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -10623,6 +16175,18 @@
       <c r="F463" t="n">
         <v>2</v>
       </c>
+      <c r="G463" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H463" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I463" t="n">
+        <v>382.0640370627376</v>
+      </c>
+      <c r="J463" t="n">
+        <v>1521144399.592213</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -10645,6 +16209,18 @@
       <c r="F464" t="n">
         <v>2</v>
       </c>
+      <c r="G464" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H464" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I464" t="n">
+        <v>362.2230741759088</v>
+      </c>
+      <c r="J464" t="n">
+        <v>972483750.2396927</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -10667,6 +16243,18 @@
       <c r="F465" t="n">
         <v>0</v>
       </c>
+      <c r="G465" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H465" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I465" t="n">
+        <v>474.2378592001739</v>
+      </c>
+      <c r="J465" t="n">
+        <v>1116267264.160622</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -10689,6 +16277,18 @@
       <c r="F466" t="n">
         <v>0</v>
       </c>
+      <c r="G466" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H466" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I466" t="n">
+        <v>401.665465879754</v>
+      </c>
+      <c r="J466" t="n">
+        <v>1124301415.125187</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -10711,6 +16311,18 @@
       <c r="F467" t="n">
         <v>2</v>
       </c>
+      <c r="G467" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H467" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I467" t="n">
+        <v>382.3170143239886</v>
+      </c>
+      <c r="J467" t="n">
+        <v>411796454.6889131</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -10733,6 +16345,18 @@
       <c r="F468" t="n">
         <v>2</v>
       </c>
+      <c r="G468" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H468" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I468" t="n">
+        <v>379.0448476203267</v>
+      </c>
+      <c r="J468" t="n">
+        <v>994451139.4708381</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -10755,6 +16379,18 @@
       <c r="F469" t="n">
         <v>2</v>
       </c>
+      <c r="G469" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H469" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I469" t="n">
+        <v>374.9042615607714</v>
+      </c>
+      <c r="J469" t="n">
+        <v>1145346029.305579</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -10777,6 +16413,18 @@
       <c r="F470" t="n">
         <v>0</v>
       </c>
+      <c r="G470" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H470" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I470" t="n">
+        <v>473.324159641636</v>
+      </c>
+      <c r="J470" t="n">
+        <v>1234778155.006184</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -10799,6 +16447,18 @@
       <c r="F471" t="n">
         <v>0</v>
       </c>
+      <c r="G471" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H471" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I471" t="n">
+        <v>480.2135545670378</v>
+      </c>
+      <c r="J471" t="n">
+        <v>1609038358.37812</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -10821,6 +16481,18 @@
       <c r="F472" t="n">
         <v>2</v>
       </c>
+      <c r="G472" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H472" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I472" t="n">
+        <v>385.2222955395411</v>
+      </c>
+      <c r="J472" t="n">
+        <v>1052148138.890338</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -10843,6 +16515,18 @@
       <c r="F473" t="n">
         <v>2</v>
       </c>
+      <c r="G473" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H473" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I473" t="n">
+        <v>367.3860009118215</v>
+      </c>
+      <c r="J473" t="n">
+        <v>748161620.3049941</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -10865,6 +16549,18 @@
       <c r="F474" t="n">
         <v>2</v>
       </c>
+      <c r="G474" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H474" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I474" t="n">
+        <v>542.1827885381606</v>
+      </c>
+      <c r="J474" t="n">
+        <v>1963498272.171976</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -10887,6 +16583,18 @@
       <c r="F475" t="n">
         <v>2</v>
       </c>
+      <c r="G475" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H475" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I475" t="n">
+        <v>381.8848835748896</v>
+      </c>
+      <c r="J475" t="n">
+        <v>758393751.9595209</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -10909,6 +16617,18 @@
       <c r="F476" t="n">
         <v>2</v>
       </c>
+      <c r="G476" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H476" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I476" t="n">
+        <v>538.5790438625913</v>
+      </c>
+      <c r="J476" t="n">
+        <v>1517383900.126907</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -10931,6 +16651,18 @@
       <c r="F477" t="n">
         <v>2</v>
       </c>
+      <c r="G477" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H477" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I477" t="n">
+        <v>368.6459573800726</v>
+      </c>
+      <c r="J477" t="n">
+        <v>1389898391.162942</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -10953,6 +16685,18 @@
       <c r="F478" t="n">
         <v>0</v>
       </c>
+      <c r="G478" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H478" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I478" t="n">
+        <v>474.7514143995931</v>
+      </c>
+      <c r="J478" t="n">
+        <v>1277924313.700184</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -10975,6 +16719,18 @@
       <c r="F479" t="n">
         <v>2</v>
       </c>
+      <c r="G479" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H479" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I479" t="n">
+        <v>373.9469958264402</v>
+      </c>
+      <c r="J479" t="n">
+        <v>1024240091.998031</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -10997,6 +16753,18 @@
       <c r="F480" t="n">
         <v>2</v>
       </c>
+      <c r="G480" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H480" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I480" t="n">
+        <v>389.8667975757295</v>
+      </c>
+      <c r="J480" t="n">
+        <v>939259848.5031502</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -11019,6 +16787,18 @@
       <c r="F481" t="n">
         <v>2</v>
       </c>
+      <c r="G481" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H481" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I481" t="n">
+        <v>356.9198182307821</v>
+      </c>
+      <c r="J481" t="n">
+        <v>713714687.0423574</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -11041,6 +16821,18 @@
       <c r="F482" t="n">
         <v>2</v>
       </c>
+      <c r="G482" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H482" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I482" t="n">
+        <v>538.4207338192327</v>
+      </c>
+      <c r="J482" t="n">
+        <v>1604672227.758023</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -11063,6 +16855,18 @@
       <c r="F483" t="n">
         <v>2</v>
       </c>
+      <c r="G483" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H483" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I483" t="n">
+        <v>486.8211826868632</v>
+      </c>
+      <c r="J483" t="n">
+        <v>1342768561.395858</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -11085,6 +16889,18 @@
       <c r="F484" t="n">
         <v>2</v>
       </c>
+      <c r="G484" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H484" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I484" t="n">
+        <v>361.6643405946432</v>
+      </c>
+      <c r="J484" t="n">
+        <v>812573153.0791017</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -11107,6 +16923,18 @@
       <c r="F485" t="n">
         <v>2</v>
       </c>
+      <c r="G485" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H485" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I485" t="n">
+        <v>401.930851393678</v>
+      </c>
+      <c r="J485" t="n">
+        <v>976415422.9768867</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -11129,6 +16957,18 @@
       <c r="F486" t="n">
         <v>0</v>
       </c>
+      <c r="G486" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H486" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I486" t="n">
+        <v>519.2538226536985</v>
+      </c>
+      <c r="J486" t="n">
+        <v>1746241819.186605</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -11151,6 +16991,18 @@
       <c r="F487" t="n">
         <v>0</v>
       </c>
+      <c r="G487" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H487" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I487" t="n">
+        <v>279.902734174244</v>
+      </c>
+      <c r="J487" t="n">
+        <v>931060767.7085143</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -11173,6 +17025,18 @@
       <c r="F488" t="n">
         <v>1</v>
       </c>
+      <c r="G488" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H488" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I488" t="n">
+        <v>421.8829865894261</v>
+      </c>
+      <c r="J488" t="n">
+        <v>803974139.8603932</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -11195,6 +17059,18 @@
       <c r="F489" t="n">
         <v>2</v>
       </c>
+      <c r="G489" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H489" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I489" t="n">
+        <v>369.4452532027314</v>
+      </c>
+      <c r="J489" t="n">
+        <v>734425762.3677343</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -11217,6 +17093,18 @@
       <c r="F490" t="n">
         <v>2</v>
       </c>
+      <c r="G490" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H490" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I490" t="n">
+        <v>378.3849475489089</v>
+      </c>
+      <c r="J490" t="n">
+        <v>954892894.618528</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -11239,6 +17127,18 @@
       <c r="F491" t="n">
         <v>1</v>
       </c>
+      <c r="G491" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H491" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I491" t="n">
+        <v>421.4524250593868</v>
+      </c>
+      <c r="J491" t="n">
+        <v>943465680.9028254</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -11261,6 +17161,18 @@
       <c r="F492" t="n">
         <v>0</v>
       </c>
+      <c r="G492" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H492" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I492" t="n">
+        <v>495.327109267422</v>
+      </c>
+      <c r="J492" t="n">
+        <v>513904571.1874155</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -11283,6 +17195,18 @@
       <c r="F493" t="n">
         <v>2</v>
       </c>
+      <c r="G493" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H493" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I493" t="n">
+        <v>357.2115310266433</v>
+      </c>
+      <c r="J493" t="n">
+        <v>426292855.6549109</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -11305,6 +17229,18 @@
       <c r="F494" t="n">
         <v>2</v>
       </c>
+      <c r="G494" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H494" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I494" t="n">
+        <v>399.4831107472828</v>
+      </c>
+      <c r="J494" t="n">
+        <v>671385005.209381</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -11327,6 +17263,18 @@
       <c r="F495" t="n">
         <v>2</v>
       </c>
+      <c r="G495" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H495" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I495" t="n">
+        <v>370.8772421201244</v>
+      </c>
+      <c r="J495" t="n">
+        <v>416092746.6563582</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -11349,6 +17297,18 @@
       <c r="F496" t="n">
         <v>1</v>
       </c>
+      <c r="G496" t="n">
+        <v>16.29770595792319</v>
+      </c>
+      <c r="H496" t="n">
+        <v>74.69841714945537</v>
+      </c>
+      <c r="I496" t="n">
+        <v>496.2179314352944</v>
+      </c>
+      <c r="J496" t="n">
+        <v>719884020.610026</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -11371,6 +17331,18 @@
       <c r="F497" t="n">
         <v>0</v>
       </c>
+      <c r="G497" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H497" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I497" t="n">
+        <v>508.6165235388352</v>
+      </c>
+      <c r="J497" t="n">
+        <v>646714108.5779886</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -11393,6 +17365,18 @@
       <c r="F498" t="n">
         <v>2</v>
       </c>
+      <c r="G498" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H498" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I498" t="n">
+        <v>320.0585897987742</v>
+      </c>
+      <c r="J498" t="n">
+        <v>622914302.445666</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -11415,6 +17399,18 @@
       <c r="F499" t="n">
         <v>2</v>
       </c>
+      <c r="G499" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H499" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I499" t="n">
+        <v>301.6603319138252</v>
+      </c>
+      <c r="J499" t="n">
+        <v>392040630.1117572</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -11437,6 +17433,18 @@
       <c r="F500" t="n">
         <v>0</v>
       </c>
+      <c r="G500" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H500" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I500" t="n">
+        <v>399.3228032090287</v>
+      </c>
+      <c r="J500" t="n">
+        <v>655981365.4343224</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -11459,6 +17467,18 @@
       <c r="F501" t="n">
         <v>0</v>
       </c>
+      <c r="G501" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H501" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I501" t="n">
+        <v>396.5711271812636</v>
+      </c>
+      <c r="J501" t="n">
+        <v>615156932.7953393</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -11481,6 +17501,18 @@
       <c r="F502" t="n">
         <v>2</v>
       </c>
+      <c r="G502" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H502" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I502" t="n">
+        <v>403.9857614874821</v>
+      </c>
+      <c r="J502" t="n">
+        <v>490505623.9815711</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -11503,6 +17535,18 @@
       <c r="F503" t="n">
         <v>0</v>
       </c>
+      <c r="G503" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H503" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I503" t="n">
+        <v>399.6670938287053</v>
+      </c>
+      <c r="J503" t="n">
+        <v>339234447.7252853</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -11525,6 +17569,18 @@
       <c r="F504" t="n">
         <v>0</v>
       </c>
+      <c r="G504" t="n">
+        <v>22.6787608535532</v>
+      </c>
+      <c r="H504" t="n">
+        <v>85.9812874870685</v>
+      </c>
+      <c r="I504" t="n">
+        <v>429.5073032500679</v>
+      </c>
+      <c r="J504" t="n">
+        <v>791874531.6747029</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -11546,6 +17602,18 @@
       </c>
       <c r="F505" t="n">
         <v>2</v>
+      </c>
+      <c r="G505" t="n">
+        <v>26.15639512632801</v>
+      </c>
+      <c r="H505" t="n">
+        <v>75.69994961106734</v>
+      </c>
+      <c r="I505" t="n">
+        <v>394.7884522559071</v>
+      </c>
+      <c r="J505" t="n">
+        <v>477365752.7358279</v>
       </c>
     </row>
   </sheetData>

--- a/clustered_output.xlsx
+++ b/clustered_output.xlsx
@@ -431,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>stores</t>
+          <t>store</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>demand_cft</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -496,7 +496,7 @@
         <v>1391311.240000001</v>
       </c>
       <c r="E2" t="n">
-        <v>13.91311240000001</v>
+        <v>41.29720544</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -530,7 +530,7 @@
         <v>1894015.410000001</v>
       </c>
       <c r="E3" t="n">
-        <v>18.94015410000001</v>
+        <v>55.87958479999999</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -564,7 +564,7 @@
         <v>806187.3549999999</v>
       </c>
       <c r="E4" t="n">
-        <v>8.061873549999998</v>
+        <v>33.26804828</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -598,7 +598,7 @@
         <v>10000</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>93.98859224</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -632,7 +632,7 @@
         <v>1565861.19</v>
       </c>
       <c r="E6" t="n">
-        <v>15.6586119</v>
+        <v>40.42737347999999</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -666,7 +666,7 @@
         <v>1159777.94</v>
       </c>
       <c r="E7" t="n">
-        <v>11.5977794</v>
+        <v>63.74664785</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -700,7 +700,7 @@
         <v>1963860.570000001</v>
       </c>
       <c r="E8" t="n">
-        <v>19.63860570000001</v>
+        <v>86.27647392</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -734,7 +734,7 @@
         <v>2041918.845000001</v>
       </c>
       <c r="E9" t="n">
-        <v>20.41918845000001</v>
+        <v>91.16850180000002</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -768,7 +768,7 @@
         <v>2453649.6725</v>
       </c>
       <c r="E10" t="n">
-        <v>24.536496725</v>
+        <v>86.99766654</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -802,7 +802,7 @@
         <v>2545405.430000002</v>
       </c>
       <c r="E11" t="n">
-        <v>25.45405430000002</v>
+        <v>82.87167607000001</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -836,7 +836,7 @@
         <v>2403857.600000001</v>
       </c>
       <c r="E12" t="n">
-        <v>24.03857600000001</v>
+        <v>113.41016794</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -870,7 +870,7 @@
         <v>1536303.230000001</v>
       </c>
       <c r="E13" t="n">
-        <v>15.36303230000001</v>
+        <v>90.7568601</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -904,7 +904,7 @@
         <v>2889231.95</v>
       </c>
       <c r="E14" t="n">
-        <v>28.8923195</v>
+        <v>129.90572294</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -938,7 +938,7 @@
         <v>1765869.290000001</v>
       </c>
       <c r="E15" t="n">
-        <v>17.65869290000001</v>
+        <v>39.66574248000001</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
@@ -972,7 +972,7 @@
         <v>2286972.586000001</v>
       </c>
       <c r="E16" t="n">
-        <v>22.86972586000001</v>
+        <v>76.75563604999999</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>1799592.301</v>
       </c>
       <c r="E17" t="n">
-        <v>17.99592301</v>
+        <v>71.55889309999998</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
@@ -1040,7 +1040,7 @@
         <v>2780851.510000003</v>
       </c>
       <c r="E18" t="n">
-        <v>27.80851510000003</v>
+        <v>112.80354775</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>2068389.72</v>
       </c>
       <c r="E19" t="n">
-        <v>20.6838972</v>
+        <v>73.57074283999999</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
@@ -1108,7 +1108,7 @@
         <v>1578105.82</v>
       </c>
       <c r="E20" t="n">
-        <v>15.7810582</v>
+        <v>48.18771840000001</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
@@ -1142,7 +1142,7 @@
         <v>1986991.580000001</v>
       </c>
       <c r="E21" t="n">
-        <v>19.86991580000001</v>
+        <v>137.72677575</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>1634757.72</v>
       </c>
       <c r="E22" t="n">
-        <v>16.3475772</v>
+        <v>61.96439013000001</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -1210,7 +1210,7 @@
         <v>1786987.540000001</v>
       </c>
       <c r="E23" t="n">
-        <v>17.86987540000001</v>
+        <v>57.01195806</v>
       </c>
       <c r="F23" t="n">
         <v>3</v>
@@ -1244,7 +1244,7 @@
         <v>1492480.91</v>
       </c>
       <c r="E24" t="n">
-        <v>14.9248091</v>
+        <v>75.03426994</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
         <v>1668985.44</v>
       </c>
       <c r="E25" t="n">
-        <v>16.6898544</v>
+        <v>45.991</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -1312,7 +1312,7 @@
         <v>1935476.25</v>
       </c>
       <c r="E26" t="n">
-        <v>19.3547625</v>
+        <v>69.51707707</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>2539449.208500001</v>
       </c>
       <c r="E27" t="n">
-        <v>25.39449208500001</v>
+        <v>118.63043667</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
@@ -1380,7 +1380,7 @@
         <v>1574566.76</v>
       </c>
       <c r="E28" t="n">
-        <v>15.7456676</v>
+        <v>39.05642559</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
@@ -1414,7 +1414,7 @@
         <v>1199871.3</v>
       </c>
       <c r="E29" t="n">
-        <v>11.998713</v>
+        <v>51.11150699</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         <v>2612049.230000002</v>
       </c>
       <c r="E30" t="n">
-        <v>26.12049230000002</v>
+        <v>90.55661511999999</v>
       </c>
       <c r="F30" t="n">
         <v>3</v>
@@ -1482,7 +1482,7 @@
         <v>1729025.440000001</v>
       </c>
       <c r="E31" t="n">
-        <v>17.29025440000001</v>
+        <v>80.49179736000001</v>
       </c>
       <c r="F31" t="n">
         <v>3</v>
@@ -1516,7 +1516,7 @@
         <v>3471794.125000003</v>
       </c>
       <c r="E32" t="n">
-        <v>34.71794125000003</v>
+        <v>137.7462625</v>
       </c>
       <c r="F32" t="n">
         <v>3</v>
@@ -1550,7 +1550,7 @@
         <v>2410134.020000001</v>
       </c>
       <c r="E33" t="n">
-        <v>24.10134020000001</v>
+        <v>82.06561287</v>
       </c>
       <c r="F33" t="n">
         <v>3</v>
@@ -1584,7 +1584,7 @@
         <v>815045.9499999998</v>
       </c>
       <c r="E34" t="n">
-        <v>8.150459499999998</v>
+        <v>40.91439332</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
         <v>1892125.723000001</v>
       </c>
       <c r="E35" t="n">
-        <v>18.92125723000001</v>
+        <v>94.20747311999999</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -1652,7 +1652,7 @@
         <v>2345239.350000001</v>
       </c>
       <c r="E36" t="n">
-        <v>23.45239350000001</v>
+        <v>51.34208147000001</v>
       </c>
       <c r="F36" t="n">
         <v>3</v>
@@ -1686,7 +1686,7 @@
         <v>2138770.305000001</v>
       </c>
       <c r="E37" t="n">
-        <v>21.38770305000001</v>
+        <v>89.43269527999999</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1720,7 +1720,7 @@
         <v>1895595.6185</v>
       </c>
       <c r="E38" t="n">
-        <v>18.955956185</v>
+        <v>87.62353223</v>
       </c>
       <c r="F38" t="n">
         <v>3</v>
@@ -1754,7 +1754,7 @@
         <v>3454897.285000004</v>
       </c>
       <c r="E39" t="n">
-        <v>34.54897285000004</v>
+        <v>113.62947597</v>
       </c>
       <c r="F39" t="n">
         <v>3</v>
@@ -1788,7 +1788,7 @@
         <v>2406394.670000001</v>
       </c>
       <c r="E40" t="n">
-        <v>24.06394670000001</v>
+        <v>97.86042042</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
         <v>2110505.374500001</v>
       </c>
       <c r="E41" t="n">
-        <v>21.10505374500001</v>
+        <v>120.70724466</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1856,7 +1856,7 @@
         <v>1735908.407500001</v>
       </c>
       <c r="E42" t="n">
-        <v>17.35908407500001</v>
+        <v>63.64605510000001</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
@@ -1890,7 +1890,7 @@
         <v>2362977.394000001</v>
       </c>
       <c r="E43" t="n">
-        <v>23.62977394000001</v>
+        <v>79.88549751000001</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -1924,7 +1924,7 @@
         <v>1801111.09</v>
       </c>
       <c r="E44" t="n">
-        <v>18.0111109</v>
+        <v>75.97018895000001</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
@@ -1958,7 +1958,7 @@
         <v>1520926.320000001</v>
       </c>
       <c r="E45" t="n">
-        <v>15.20926320000001</v>
+        <v>58.83139722999999</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>1148545.61</v>
       </c>
       <c r="E46" t="n">
-        <v>11.4854561</v>
+        <v>24.03516849</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
@@ -2026,7 +2026,7 @@
         <v>846114.4900000002</v>
       </c>
       <c r="E47" t="n">
-        <v>8.461144900000003</v>
+        <v>17.60890872</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
@@ -2060,7 +2060,7 @@
         <v>2107279.795</v>
       </c>
       <c r="E48" t="n">
-        <v>21.07279795000001</v>
+        <v>82.63783919000001</v>
       </c>
       <c r="F48" t="n">
         <v>3</v>
@@ -2094,7 +2094,7 @@
         <v>2208678.120000001</v>
       </c>
       <c r="E49" t="n">
-        <v>22.08678120000001</v>
+        <v>56.29949515999999</v>
       </c>
       <c r="F49" t="n">
         <v>3</v>
@@ -2128,7 +2128,7 @@
         <v>1582088.56</v>
       </c>
       <c r="E50" t="n">
-        <v>15.8208856</v>
+        <v>47.27391910999999</v>
       </c>
       <c r="F50" t="n">
         <v>3</v>
@@ -2162,7 +2162,7 @@
         <v>1596611.194</v>
       </c>
       <c r="E51" t="n">
-        <v>15.96611194</v>
+        <v>55.12580752</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1704246.34</v>
       </c>
       <c r="E52" t="n">
-        <v>17.0424634</v>
+        <v>70.25959358</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>1860230.515000001</v>
       </c>
       <c r="E53" t="n">
-        <v>18.60230515000001</v>
+        <v>62.59155026999998</v>
       </c>
       <c r="F53" t="n">
         <v>3</v>
@@ -2264,7 +2264,7 @@
         <v>1827854.750000001</v>
       </c>
       <c r="E54" t="n">
-        <v>18.27854750000001</v>
+        <v>78.94616125999998</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2298,7 +2298,7 @@
         <v>2463968.02</v>
       </c>
       <c r="E55" t="n">
-        <v>24.6396802</v>
+        <v>101.76988238</v>
       </c>
       <c r="F55" t="n">
         <v>3</v>
@@ -2332,7 +2332,7 @@
         <v>1362876</v>
       </c>
       <c r="E56" t="n">
-        <v>13.62876</v>
+        <v>44.19095989</v>
       </c>
       <c r="F56" t="n">
         <v>3</v>
@@ -2366,7 +2366,7 @@
         <v>2549014.390000001</v>
       </c>
       <c r="E57" t="n">
-        <v>25.49014390000001</v>
+        <v>93.80458936000001</v>
       </c>
       <c r="F57" t="n">
         <v>3</v>
@@ -2400,7 +2400,7 @@
         <v>1227601.52</v>
       </c>
       <c r="E58" t="n">
-        <v>12.2760152</v>
+        <v>49.10406079999999</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>2226948.365000001</v>
       </c>
       <c r="E59" t="n">
-        <v>22.26948365000001</v>
+        <v>99.07280474</v>
       </c>
       <c r="F59" t="n">
         <v>3</v>
@@ -2468,7 +2468,7 @@
         <v>1558090.350000001</v>
       </c>
       <c r="E60" t="n">
-        <v>15.58090350000001</v>
+        <v>69.66181495000001</v>
       </c>
       <c r="F60" t="n">
         <v>3</v>
@@ -2502,7 +2502,7 @@
         <v>3817390.817500003</v>
       </c>
       <c r="E61" t="n">
-        <v>38.17390817500003</v>
+        <v>157.49350527</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -2536,7 +2536,7 @@
         <v>2090753.030000001</v>
       </c>
       <c r="E62" t="n">
-        <v>20.90753030000001</v>
+        <v>69.61420304000001</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -2570,7 +2570,7 @@
         <v>1041427.86</v>
       </c>
       <c r="E63" t="n">
-        <v>10.4142786</v>
+        <v>15.037</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
@@ -2604,7 +2604,7 @@
         <v>930633.1300000001</v>
       </c>
       <c r="E64" t="n">
-        <v>9.306331300000002</v>
+        <v>33.56141599999999</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
         <v>3196145.850000002</v>
       </c>
       <c r="E65" t="n">
-        <v>31.96145850000002</v>
+        <v>122.2742197</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2672,7 +2672,7 @@
         <v>890859.5699999999</v>
       </c>
       <c r="E66" t="n">
-        <v>8.908595699999999</v>
+        <v>29.31689904</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>1474320.778</v>
       </c>
       <c r="E67" t="n">
-        <v>14.74320778</v>
+        <v>24.08448896</v>
       </c>
       <c r="F67" t="n">
         <v>3</v>
@@ -2740,7 +2740,7 @@
         <v>1154042</v>
       </c>
       <c r="E68" t="n">
-        <v>11.54042</v>
+        <v>59.56919848</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>1514679.93</v>
       </c>
       <c r="E69" t="n">
-        <v>15.1467993</v>
+        <v>61.17361757</v>
       </c>
       <c r="F69" t="n">
         <v>3</v>
@@ -2808,7 +2808,7 @@
         <v>1339391.97</v>
       </c>
       <c r="E70" t="n">
-        <v>13.3939197</v>
+        <v>45.19398898999999</v>
       </c>
       <c r="F70" t="n">
         <v>3</v>
@@ -2842,7 +2842,7 @@
         <v>214758.73</v>
       </c>
       <c r="E71" t="n">
-        <v>2.1475873</v>
+        <v>8.5903492</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>1656171.685</v>
       </c>
       <c r="E72" t="n">
-        <v>16.56171685</v>
+        <v>77.60705583999999</v>
       </c>
       <c r="F72" t="n">
         <v>3</v>
@@ -2910,7 +2910,7 @@
         <v>1372180.3</v>
       </c>
       <c r="E73" t="n">
-        <v>13.721803</v>
+        <v>27.84522936</v>
       </c>
       <c r="F73" t="n">
         <v>3</v>
@@ -2944,7 +2944,7 @@
         <v>3010965.345800002</v>
       </c>
       <c r="E74" t="n">
-        <v>30.10965345800002</v>
+        <v>121.24150382</v>
       </c>
       <c r="F74" t="n">
         <v>3</v>
@@ -2978,7 +2978,7 @@
         <v>2401400.660000001</v>
       </c>
       <c r="E75" t="n">
-        <v>24.01400660000001</v>
+        <v>109.77473927</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -3012,7 +3012,7 @@
         <v>952431.2600000001</v>
       </c>
       <c r="E76" t="n">
-        <v>9.524312600000002</v>
+        <v>27.96024677</v>
       </c>
       <c r="F76" t="n">
         <v>3</v>
@@ -3046,7 +3046,7 @@
         <v>2932250.877500001</v>
       </c>
       <c r="E77" t="n">
-        <v>29.32250877500001</v>
+        <v>127.09983192</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         <v>1126902.32</v>
       </c>
       <c r="E78" t="n">
-        <v>11.2690232</v>
+        <v>40.97559472</v>
       </c>
       <c r="F78" t="n">
         <v>3</v>
@@ -3114,7 +3114,7 @@
         <v>1700685.398000001</v>
       </c>
       <c r="E79" t="n">
-        <v>17.00685398000001</v>
+        <v>55.95136335999999</v>
       </c>
       <c r="F79" t="n">
         <v>3</v>
@@ -3148,7 +3148,7 @@
         <v>2135061.130000001</v>
       </c>
       <c r="E80" t="n">
-        <v>21.35061130000001</v>
+        <v>99.95687511999999</v>
       </c>
       <c r="F80" t="n">
         <v>3</v>
@@ -3182,7 +3182,7 @@
         <v>3295031.401500003</v>
       </c>
       <c r="E81" t="n">
-        <v>32.95031401500003</v>
+        <v>171.25894002</v>
       </c>
       <c r="F81" t="n">
         <v>3</v>
@@ -3216,7 +3216,7 @@
         <v>2353874.400000001</v>
       </c>
       <c r="E82" t="n">
-        <v>23.53874400000001</v>
+        <v>108.25222513</v>
       </c>
       <c r="F82" t="n">
         <v>3</v>
@@ -3250,7 +3250,7 @@
         <v>3869218.730000003</v>
       </c>
       <c r="E83" t="n">
-        <v>38.69218730000003</v>
+        <v>152.37332232</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -3284,7 +3284,7 @@
         <v>3059781.121000002</v>
       </c>
       <c r="E84" t="n">
-        <v>30.59781121000002</v>
+        <v>137.64539505</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>2800092.345000003</v>
       </c>
       <c r="E85" t="n">
-        <v>28.00092345000003</v>
+        <v>98.88650038</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3352,7 +3352,7 @@
         <v>4186897.340000003</v>
       </c>
       <c r="E86" t="n">
-        <v>41.86897340000003</v>
+        <v>174.43258149</v>
       </c>
       <c r="F86" t="n">
         <v>3</v>
@@ -3386,7 +3386,7 @@
         <v>3134395.610000001</v>
       </c>
       <c r="E87" t="n">
-        <v>31.34395610000001</v>
+        <v>131.72022438</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
         <v>3023221.960000003</v>
       </c>
       <c r="E88" t="n">
-        <v>30.23221960000003</v>
+        <v>128.67002752</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3454,7 +3454,7 @@
         <v>3695866.890000002</v>
       </c>
       <c r="E89" t="n">
-        <v>36.95866890000001</v>
+        <v>151.83197394</v>
       </c>
       <c r="F89" t="n">
         <v>3</v>
@@ -3488,7 +3488,7 @@
         <v>1786667.568</v>
       </c>
       <c r="E90" t="n">
-        <v>17.86667568</v>
+        <v>70.43858698000003</v>
       </c>
       <c r="F90" t="n">
         <v>3</v>
@@ -3522,7 +3522,7 @@
         <v>3627985.892500002</v>
       </c>
       <c r="E91" t="n">
-        <v>36.27985892500002</v>
+        <v>165.86665209</v>
       </c>
       <c r="F91" t="n">
         <v>3</v>
@@ -3556,7 +3556,7 @@
         <v>3943833.500000004</v>
       </c>
       <c r="E92" t="n">
-        <v>39.43833500000004</v>
+        <v>160.7944185</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>2606742.230000002</v>
       </c>
       <c r="E93" t="n">
-        <v>26.06742230000002</v>
+        <v>114.30460316</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
         <v>1895208.737500001</v>
       </c>
       <c r="E94" t="n">
-        <v>18.952087375</v>
+        <v>27.65862036</v>
       </c>
       <c r="F94" t="n">
         <v>3</v>
@@ -3658,7 +3658,7 @@
         <v>2304318.708000001</v>
       </c>
       <c r="E95" t="n">
-        <v>23.04318708000001</v>
+        <v>107.20581291</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
         <v>3059530.732000002</v>
       </c>
       <c r="E96" t="n">
-        <v>30.59530732000002</v>
+        <v>132.81126806</v>
       </c>
       <c r="F96" t="n">
         <v>3</v>
@@ -3726,7 +3726,7 @@
         <v>2527912.670000002</v>
       </c>
       <c r="E97" t="n">
-        <v>25.27912670000002</v>
+        <v>151.87199567</v>
       </c>
       <c r="F97" t="n">
         <v>3</v>
@@ -3760,7 +3760,7 @@
         <v>2551333.927500001</v>
       </c>
       <c r="E98" t="n">
-        <v>25.51333927500001</v>
+        <v>97.51930487999999</v>
       </c>
       <c r="F98" t="n">
         <v>3</v>
@@ -3794,7 +3794,7 @@
         <v>2689641.190000001</v>
       </c>
       <c r="E99" t="n">
-        <v>26.89641190000001</v>
+        <v>62.68683512</v>
       </c>
       <c r="F99" t="n">
         <v>3</v>
@@ -3828,7 +3828,7 @@
         <v>3196226.813000002</v>
       </c>
       <c r="E100" t="n">
-        <v>31.96226813000002</v>
+        <v>164.09465016</v>
       </c>
       <c r="F100" t="n">
         <v>3</v>
@@ -3862,7 +3862,7 @@
         <v>2972033.683000003</v>
       </c>
       <c r="E101" t="n">
-        <v>29.72033683000003</v>
+        <v>115.75139108</v>
       </c>
       <c r="F101" t="n">
         <v>3</v>
@@ -3896,7 +3896,7 @@
         <v>3600055.571700001</v>
       </c>
       <c r="E102" t="n">
-        <v>36.00055571700001</v>
+        <v>112.73454219</v>
       </c>
       <c r="F102" t="n">
         <v>3</v>
@@ -3930,7 +3930,7 @@
         <v>3509680.773000001</v>
       </c>
       <c r="E103" t="n">
-        <v>35.09680773000001</v>
+        <v>165.16716377</v>
       </c>
       <c r="F103" t="n">
         <v>3</v>
@@ -3964,7 +3964,7 @@
         <v>3675548.560000003</v>
       </c>
       <c r="E104" t="n">
-        <v>36.75548560000003</v>
+        <v>98.30353936999998</v>
       </c>
       <c r="F104" t="n">
         <v>3</v>
@@ -3998,7 +3998,7 @@
         <v>1943253.962000001</v>
       </c>
       <c r="E105" t="n">
-        <v>19.43253962000001</v>
+        <v>64.32811749000001</v>
       </c>
       <c r="F105" t="n">
         <v>3</v>
@@ -4032,7 +4032,7 @@
         <v>3837838.250000003</v>
       </c>
       <c r="E106" t="n">
-        <v>38.37838250000003</v>
+        <v>143.1621979</v>
       </c>
       <c r="F106" t="n">
         <v>3</v>
@@ -4066,7 +4066,7 @@
         <v>2088559.45</v>
       </c>
       <c r="E107" t="n">
-        <v>20.8855945</v>
+        <v>62.72158742000001</v>
       </c>
       <c r="F107" t="n">
         <v>3</v>
@@ -4100,7 +4100,7 @@
         <v>3078630.000000002</v>
       </c>
       <c r="E108" t="n">
-        <v>30.78630000000002</v>
+        <v>135.79601133</v>
       </c>
       <c r="F108" t="n">
         <v>3</v>
@@ -4134,7 +4134,7 @@
         <v>1992045.442000001</v>
       </c>
       <c r="E109" t="n">
-        <v>19.92045442000001</v>
+        <v>67.78453388</v>
       </c>
       <c r="F109" t="n">
         <v>3</v>
@@ -4168,7 +4168,7 @@
         <v>2896037.516000002</v>
       </c>
       <c r="E110" t="n">
-        <v>28.96037516000002</v>
+        <v>135.40894881</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
         <v>2613216.273500002</v>
       </c>
       <c r="E111" t="n">
-        <v>26.13216273500002</v>
+        <v>134.30264618</v>
       </c>
       <c r="F111" t="n">
         <v>3</v>
@@ -4236,7 +4236,7 @@
         <v>2714550.080000001</v>
       </c>
       <c r="E112" t="n">
-        <v>27.14550080000001</v>
+        <v>107.39169483</v>
       </c>
       <c r="F112" t="n">
         <v>3</v>
@@ -4270,7 +4270,7 @@
         <v>2132839.120000001</v>
       </c>
       <c r="E113" t="n">
-        <v>21.32839120000001</v>
+        <v>92.21966651000001</v>
       </c>
       <c r="F113" t="n">
         <v>3</v>
@@ -4304,7 +4304,7 @@
         <v>1819889.93</v>
       </c>
       <c r="E114" t="n">
-        <v>18.1988993</v>
+        <v>46.65942816</v>
       </c>
       <c r="F114" t="n">
         <v>3</v>
@@ -4338,7 +4338,7 @@
         <v>1924593.490000001</v>
       </c>
       <c r="E115" t="n">
-        <v>19.24593490000001</v>
+        <v>61.25313789</v>
       </c>
       <c r="F115" t="n">
         <v>3</v>
@@ -4372,7 +4372,7 @@
         <v>2651898.172000001</v>
       </c>
       <c r="E116" t="n">
-        <v>26.51898172000001</v>
+        <v>95.79522047999998</v>
       </c>
       <c r="F116" t="n">
         <v>3</v>
@@ -4406,7 +4406,7 @@
         <v>2908582.570000002</v>
       </c>
       <c r="E117" t="n">
-        <v>29.08582570000002</v>
+        <v>131.4488539</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -4440,7 +4440,7 @@
         <v>3391717.602500002</v>
       </c>
       <c r="E118" t="n">
-        <v>33.91717602500002</v>
+        <v>139.22461155</v>
       </c>
       <c r="F118" t="n">
         <v>3</v>
@@ -4474,7 +4474,7 @@
         <v>2203596.030000001</v>
       </c>
       <c r="E119" t="n">
-        <v>22.03596030000001</v>
+        <v>69.87724643999999</v>
       </c>
       <c r="F119" t="n">
         <v>3</v>
@@ -4508,7 +4508,7 @@
         <v>1089481.630000001</v>
       </c>
       <c r="E120" t="n">
-        <v>10.89481630000001</v>
+        <v>26.29534809</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -4542,7 +4542,7 @@
         <v>3675797.360500003</v>
       </c>
       <c r="E121" t="n">
-        <v>36.75797360500003</v>
+        <v>124.64185643</v>
       </c>
       <c r="F121" t="n">
         <v>3</v>
@@ -4576,7 +4576,7 @@
         <v>1583080.265</v>
       </c>
       <c r="E122" t="n">
-        <v>15.83080265</v>
+        <v>67.21328875</v>
       </c>
       <c r="F122" t="n">
         <v>3</v>
@@ -4610,7 +4610,7 @@
         <v>2483067.157000001</v>
       </c>
       <c r="E123" t="n">
-        <v>24.83067157000001</v>
+        <v>104.41013483</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>2419685.300000001</v>
       </c>
       <c r="E124" t="n">
-        <v>24.19685300000001</v>
+        <v>55.17039302000001</v>
       </c>
       <c r="F124" t="n">
         <v>3</v>
@@ -4678,7 +4678,7 @@
         <v>3597456.215000002</v>
       </c>
       <c r="E125" t="n">
-        <v>35.97456215000002</v>
+        <v>156.16160591</v>
       </c>
       <c r="F125" t="n">
         <v>3</v>
@@ -4712,7 +4712,7 @@
         <v>1881257.060000001</v>
       </c>
       <c r="E126" t="n">
-        <v>18.81257060000002</v>
+        <v>86.21620850000002</v>
       </c>
       <c r="F126" t="n">
         <v>3</v>
@@ -4746,7 +4746,7 @@
         <v>1915857.510000001</v>
       </c>
       <c r="E127" t="n">
-        <v>19.15857510000001</v>
+        <v>71.97972833</v>
       </c>
       <c r="F127" t="n">
         <v>3</v>
@@ -4780,7 +4780,7 @@
         <v>2959023.708000002</v>
       </c>
       <c r="E128" t="n">
-        <v>29.59023708000002</v>
+        <v>116.03335498</v>
       </c>
       <c r="F128" t="n">
         <v>3</v>
@@ -4814,7 +4814,7 @@
         <v>2536827.565000002</v>
       </c>
       <c r="E129" t="n">
-        <v>25.36827565000002</v>
+        <v>87.04857329000001</v>
       </c>
       <c r="F129" t="n">
         <v>3</v>
@@ -4848,7 +4848,7 @@
         <v>3133921.420000003</v>
       </c>
       <c r="E130" t="n">
-        <v>31.33921420000003</v>
+        <v>141.72703296</v>
       </c>
       <c r="F130" t="n">
         <v>3</v>
@@ -4882,7 +4882,7 @@
         <v>3848624.002500003</v>
       </c>
       <c r="E131" t="n">
-        <v>38.48624002500003</v>
+        <v>145.58214742</v>
       </c>
       <c r="F131" t="n">
         <v>3</v>
@@ -4916,7 +4916,7 @@
         <v>3305477.715000002</v>
       </c>
       <c r="E132" t="n">
-        <v>33.05477715000002</v>
+        <v>148.1403535</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -4950,7 +4950,7 @@
         <v>2152122.560000001</v>
       </c>
       <c r="E133" t="n">
-        <v>21.5212256</v>
+        <v>39.35975862000001</v>
       </c>
       <c r="F133" t="n">
         <v>3</v>
@@ -4984,7 +4984,7 @@
         <v>2754300.630000003</v>
       </c>
       <c r="E134" t="n">
-        <v>27.54300630000003</v>
+        <v>121.18436646</v>
       </c>
       <c r="F134" t="n">
         <v>3</v>
@@ -5018,7 +5018,7 @@
         <v>3389548.443</v>
       </c>
       <c r="E135" t="n">
-        <v>33.89548443</v>
+        <v>174.54029805</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>2031568.362500001</v>
       </c>
       <c r="E136" t="n">
-        <v>20.31568362500001</v>
+        <v>71.22344247000001</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -5086,7 +5086,7 @@
         <v>2046548.4175</v>
       </c>
       <c r="E137" t="n">
-        <v>20.465484175</v>
+        <v>86.91646299999999</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
         <v>2774184.349500003</v>
       </c>
       <c r="E138" t="n">
-        <v>27.74184349500003</v>
+        <v>113.58351808</v>
       </c>
       <c r="F138" t="n">
         <v>3</v>
@@ -5154,7 +5154,7 @@
         <v>3624847.472500003</v>
       </c>
       <c r="E139" t="n">
-        <v>36.24847472500003</v>
+        <v>130.82707128</v>
       </c>
       <c r="F139" t="n">
         <v>3</v>
@@ -5188,7 +5188,7 @@
         <v>2881181.22</v>
       </c>
       <c r="E140" t="n">
-        <v>28.8118122</v>
+        <v>83.83990669000001</v>
       </c>
       <c r="F140" t="n">
         <v>3</v>
@@ -5222,7 +5222,7 @@
         <v>2403177.404000001</v>
       </c>
       <c r="E141" t="n">
-        <v>24.03177404000001</v>
+        <v>66.93223488999999</v>
       </c>
       <c r="F141" t="n">
         <v>3</v>
@@ -5256,7 +5256,7 @@
         <v>2195367.310000001</v>
       </c>
       <c r="E142" t="n">
-        <v>21.95367310000001</v>
+        <v>94.84938579</v>
       </c>
       <c r="F142" t="n">
         <v>3</v>
@@ -5290,7 +5290,7 @@
         <v>3347237.560000002</v>
       </c>
       <c r="E143" t="n">
-        <v>33.47237560000002</v>
+        <v>145.91838293</v>
       </c>
       <c r="F143" t="n">
         <v>3</v>
@@ -5324,7 +5324,7 @@
         <v>2846202.545000002</v>
       </c>
       <c r="E144" t="n">
-        <v>28.46202545000002</v>
+        <v>148.16292628</v>
       </c>
       <c r="F144" t="n">
         <v>3</v>
@@ -5358,7 +5358,7 @@
         <v>2198959.510000001</v>
       </c>
       <c r="E145" t="n">
-        <v>21.98959510000001</v>
+        <v>22.03899181</v>
       </c>
       <c r="F145" t="n">
         <v>3</v>
@@ -5392,7 +5392,7 @@
         <v>3064953.355000002</v>
       </c>
       <c r="E146" t="n">
-        <v>30.64953355000002</v>
+        <v>169.43078549</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -5426,7 +5426,7 @@
         <v>3140564.864000002</v>
       </c>
       <c r="E147" t="n">
-        <v>31.40564864000002</v>
+        <v>115.96496099</v>
       </c>
       <c r="F147" t="n">
         <v>3</v>
@@ -5460,7 +5460,7 @@
         <v>2307777.076700001</v>
       </c>
       <c r="E148" t="n">
-        <v>23.07777076700001</v>
+        <v>97.54827051999999</v>
       </c>
       <c r="F148" t="n">
         <v>3</v>
@@ -5494,7 +5494,7 @@
         <v>3378485.972500001</v>
       </c>
       <c r="E149" t="n">
-        <v>33.784859725</v>
+        <v>171.24941356</v>
       </c>
       <c r="F149" t="n">
         <v>3</v>
@@ -5528,7 +5528,7 @@
         <v>1857598.070000001</v>
       </c>
       <c r="E150" t="n">
-        <v>18.57598070000001</v>
+        <v>79.48337347</v>
       </c>
       <c r="F150" t="n">
         <v>3</v>
@@ -5562,7 +5562,7 @@
         <v>1685171.580000001</v>
       </c>
       <c r="E151" t="n">
-        <v>16.8517158</v>
+        <v>21.38957457</v>
       </c>
       <c r="F151" t="n">
         <v>3</v>
@@ -5596,7 +5596,7 @@
         <v>1831847.770000001</v>
       </c>
       <c r="E152" t="n">
-        <v>18.31847770000001</v>
+        <v>56.00126308</v>
       </c>
       <c r="F152" t="n">
         <v>3</v>
@@ -5630,7 +5630,7 @@
         <v>3265541.452000002</v>
       </c>
       <c r="E153" t="n">
-        <v>32.65541452000002</v>
+        <v>116.54724109</v>
       </c>
       <c r="F153" t="n">
         <v>3</v>
@@ -5664,7 +5664,7 @@
         <v>2790359.270000002</v>
       </c>
       <c r="E154" t="n">
-        <v>27.90359270000002</v>
+        <v>136.56314483</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -5698,7 +5698,7 @@
         <v>2720174.505000002</v>
       </c>
       <c r="E155" t="n">
-        <v>27.20174505000002</v>
+        <v>132.34473269</v>
       </c>
       <c r="F155" t="n">
         <v>3</v>
@@ -5732,7 +5732,7 @@
         <v>2913683.550000001</v>
       </c>
       <c r="E156" t="n">
-        <v>29.13683550000001</v>
+        <v>127.67648195</v>
       </c>
       <c r="F156" t="n">
         <v>3</v>
@@ -5766,7 +5766,7 @@
         <v>2633189.910000002</v>
       </c>
       <c r="E157" t="n">
-        <v>26.33189910000002</v>
+        <v>101.97064253</v>
       </c>
       <c r="F157" t="n">
         <v>3</v>
@@ -5800,7 +5800,7 @@
         <v>1741243.510000001</v>
       </c>
       <c r="E158" t="n">
-        <v>17.41243510000001</v>
+        <v>64.40666220000001</v>
       </c>
       <c r="F158" t="n">
         <v>3</v>
@@ -5834,7 +5834,7 @@
         <v>3134132.5405</v>
       </c>
       <c r="E159" t="n">
-        <v>31.341325405</v>
+        <v>133.79668708</v>
       </c>
       <c r="F159" t="n">
         <v>3</v>
@@ -5868,7 +5868,7 @@
         <v>2934563.638300002</v>
       </c>
       <c r="E160" t="n">
-        <v>29.34563638300002</v>
+        <v>138.15013296</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -5902,7 +5902,7 @@
         <v>3759281.940000004</v>
       </c>
       <c r="E161" t="n">
-        <v>37.59281940000004</v>
+        <v>150.50007586</v>
       </c>
       <c r="F161" t="n">
         <v>3</v>
@@ -5936,7 +5936,7 @@
         <v>2021242.380000001</v>
       </c>
       <c r="E162" t="n">
-        <v>20.21242380000001</v>
+        <v>93.60651496</v>
       </c>
       <c r="F162" t="n">
         <v>3</v>
@@ -5970,7 +5970,7 @@
         <v>3569096.226000002</v>
       </c>
       <c r="E163" t="n">
-        <v>35.69096226000002</v>
+        <v>129.31327658</v>
       </c>
       <c r="F163" t="n">
         <v>3</v>
@@ -6004,7 +6004,7 @@
         <v>2907652.810000002</v>
       </c>
       <c r="E164" t="n">
-        <v>29.07652810000002</v>
+        <v>106.88348563</v>
       </c>
       <c r="F164" t="n">
         <v>3</v>
@@ -6038,7 +6038,7 @@
         <v>1066794.59</v>
       </c>
       <c r="E165" t="n">
-        <v>10.6679459</v>
+        <v>42.43144776</v>
       </c>
       <c r="F165" t="n">
         <v>3</v>
@@ -6072,7 +6072,7 @@
         <v>2099097.780000001</v>
       </c>
       <c r="E166" t="n">
-        <v>20.99097780000001</v>
+        <v>60.79293023</v>
       </c>
       <c r="F166" t="n">
         <v>3</v>
@@ -6106,7 +6106,7 @@
         <v>2387985.319000002</v>
       </c>
       <c r="E167" t="n">
-        <v>23.87985319000002</v>
+        <v>77.59270448000001</v>
       </c>
       <c r="F167" t="n">
         <v>3</v>
@@ -6140,7 +6140,7 @@
         <v>2957249.090000001</v>
       </c>
       <c r="E168" t="n">
-        <v>29.57249090000001</v>
+        <v>53.785478</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -6174,7 +6174,7 @@
         <v>3032667.927900002</v>
       </c>
       <c r="E169" t="n">
-        <v>30.32667927900002</v>
+        <v>145.0125221</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -6208,7 +6208,7 @@
         <v>3053703.851000001</v>
       </c>
       <c r="E170" t="n">
-        <v>30.53703851000001</v>
+        <v>134.76338509</v>
       </c>
       <c r="F170" t="n">
         <v>3</v>
@@ -6242,7 +6242,7 @@
         <v>1856441.560000001</v>
       </c>
       <c r="E171" t="n">
-        <v>18.56441560000001</v>
+        <v>34.09060356</v>
       </c>
       <c r="F171" t="n">
         <v>3</v>
@@ -6276,7 +6276,7 @@
         <v>2023551.760000001</v>
       </c>
       <c r="E172" t="n">
-        <v>20.23551760000001</v>
+        <v>103.95516876</v>
       </c>
       <c r="F172" t="n">
         <v>3</v>
@@ -6310,7 +6310,7 @@
         <v>2853768.490000002</v>
       </c>
       <c r="E173" t="n">
-        <v>28.53768490000002</v>
+        <v>129.96221128</v>
       </c>
       <c r="F173" t="n">
         <v>3</v>
@@ -6344,7 +6344,7 @@
         <v>2489524.241000001</v>
       </c>
       <c r="E174" t="n">
-        <v>24.89524241000001</v>
+        <v>123.25258422</v>
       </c>
       <c r="F174" t="n">
         <v>3</v>
@@ -6378,7 +6378,7 @@
         <v>3286898.150000004</v>
       </c>
       <c r="E175" t="n">
-        <v>32.86898150000004</v>
+        <v>114.2480122</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
@@ -6412,7 +6412,7 @@
         <v>3312040.155000001</v>
       </c>
       <c r="E176" t="n">
-        <v>33.12040155000001</v>
+        <v>148.70392757</v>
       </c>
       <c r="F176" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
         <v>4732376.382500001</v>
       </c>
       <c r="E177" t="n">
-        <v>47.32376382500001</v>
+        <v>164.48669544</v>
       </c>
       <c r="F177" t="n">
         <v>3</v>
@@ -6480,7 +6480,7 @@
         <v>3354941.790000003</v>
       </c>
       <c r="E178" t="n">
-        <v>33.54941790000003</v>
+        <v>149.1072418</v>
       </c>
       <c r="F178" t="n">
         <v>3</v>
@@ -6514,7 +6514,7 @@
         <v>2491822.964000001</v>
       </c>
       <c r="E179" t="n">
-        <v>24.91822964000001</v>
+        <v>114.08940098</v>
       </c>
       <c r="F179" t="n">
         <v>3</v>
@@ -6548,7 +6548,7 @@
         <v>3238531.940000001</v>
       </c>
       <c r="E180" t="n">
-        <v>32.38531940000001</v>
+        <v>112.05923696</v>
       </c>
       <c r="F180" t="n">
         <v>3</v>
@@ -6582,7 +6582,7 @@
         <v>1825460.510000001</v>
       </c>
       <c r="E181" t="n">
-        <v>18.25460510000001</v>
+        <v>64.98465548</v>
       </c>
       <c r="F181" t="n">
         <v>3</v>
@@ -6616,7 +6616,7 @@
         <v>2461829.960000001</v>
       </c>
       <c r="E182" t="n">
-        <v>24.61829960000001</v>
+        <v>72.72579613999999</v>
       </c>
       <c r="F182" t="n">
         <v>3</v>
@@ -6650,7 +6650,7 @@
         <v>2447627.072000001</v>
       </c>
       <c r="E183" t="n">
-        <v>24.47627072000001</v>
+        <v>103.13068804</v>
       </c>
       <c r="F183" t="n">
         <v>3</v>
@@ -6684,7 +6684,7 @@
         <v>2272471.660000002</v>
       </c>
       <c r="E184" t="n">
-        <v>22.72471660000001</v>
+        <v>88.39244152999999</v>
       </c>
       <c r="F184" t="n">
         <v>3</v>
@@ -6718,7 +6718,7 @@
         <v>2377245.936500001</v>
       </c>
       <c r="E185" t="n">
-        <v>23.77245936500001</v>
+        <v>111.28124526</v>
       </c>
       <c r="F185" t="n">
         <v>3</v>
@@ -6752,7 +6752,7 @@
         <v>1904623.060000002</v>
       </c>
       <c r="E186" t="n">
-        <v>19.04623060000002</v>
+        <v>77.23146711</v>
       </c>
       <c r="F186" t="n">
         <v>3</v>
@@ -6786,7 +6786,7 @@
         <v>2069780.154000001</v>
       </c>
       <c r="E187" t="n">
-        <v>20.69780154000001</v>
+        <v>87.69854039000001</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
         <v>2818717.260000001</v>
       </c>
       <c r="E188" t="n">
-        <v>28.18717260000001</v>
+        <v>104.07446787</v>
       </c>
       <c r="F188" t="n">
         <v>3</v>
@@ -6854,7 +6854,7 @@
         <v>3060276.820000002</v>
       </c>
       <c r="E189" t="n">
-        <v>30.60276820000002</v>
+        <v>135.95829359</v>
       </c>
       <c r="F189" t="n">
         <v>0</v>
@@ -6888,7 +6888,7 @@
         <v>1064298.92</v>
       </c>
       <c r="E190" t="n">
-        <v>10.6429892</v>
+        <v>14.04523848</v>
       </c>
       <c r="F190" t="n">
         <v>3</v>
@@ -6922,7 +6922,7 @@
         <v>1619700.44</v>
       </c>
       <c r="E191" t="n">
-        <v>16.1970044</v>
+        <v>84.03368023</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -6956,7 +6956,7 @@
         <v>1152704.87</v>
       </c>
       <c r="E192" t="n">
-        <v>11.5270487</v>
+        <v>37.35482578</v>
       </c>
       <c r="F192" t="n">
         <v>3</v>
@@ -6990,7 +6990,7 @@
         <v>1246903.5</v>
       </c>
       <c r="E193" t="n">
-        <v>12.46903500000001</v>
+        <v>29.02313882999999</v>
       </c>
       <c r="F193" t="n">
         <v>3</v>
@@ -7024,7 +7024,7 @@
         <v>1547088.350000001</v>
       </c>
       <c r="E194" t="n">
-        <v>15.47088350000001</v>
+        <v>69.75723010999999</v>
       </c>
       <c r="F194" t="n">
         <v>0</v>
@@ -7058,7 +7058,7 @@
         <v>2286100.730000001</v>
       </c>
       <c r="E195" t="n">
-        <v>22.86100730000001</v>
+        <v>106.29918689</v>
       </c>
       <c r="F195" t="n">
         <v>3</v>
@@ -7092,7 +7092,7 @@
         <v>1151716.9</v>
       </c>
       <c r="E196" t="n">
-        <v>11.517169</v>
+        <v>68.10364146999999</v>
       </c>
       <c r="F196" t="n">
         <v>3</v>
@@ -7126,7 +7126,7 @@
         <v>1104889.11</v>
       </c>
       <c r="E197" t="n">
-        <v>11.0488911</v>
+        <v>51.23457499999999</v>
       </c>
       <c r="F197" t="n">
         <v>0</v>
@@ -7160,7 +7160,7 @@
         <v>1179200.36</v>
       </c>
       <c r="E198" t="n">
-        <v>11.7920036</v>
+        <v>62.39533672</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
@@ -7194,7 +7194,7 @@
         <v>2232226.800000001</v>
       </c>
       <c r="E199" t="n">
-        <v>22.32226800000001</v>
+        <v>81.51284326</v>
       </c>
       <c r="F199" t="n">
         <v>3</v>
@@ -7228,7 +7228,7 @@
         <v>1993428.050000001</v>
       </c>
       <c r="E200" t="n">
-        <v>19.93428050000001</v>
+        <v>83.68685203999999</v>
       </c>
       <c r="F200" t="n">
         <v>3</v>
@@ -7262,7 +7262,7 @@
         <v>1750879.544</v>
       </c>
       <c r="E201" t="n">
-        <v>17.50879544</v>
+        <v>68.18522616</v>
       </c>
       <c r="F201" t="n">
         <v>3</v>
@@ -7296,7 +7296,7 @@
         <v>2131368.802500001</v>
       </c>
       <c r="E202" t="n">
-        <v>21.31368802500001</v>
+        <v>80.24099302</v>
       </c>
       <c r="F202" t="n">
         <v>3</v>
@@ -7330,7 +7330,7 @@
         <v>1074607.14</v>
       </c>
       <c r="E203" t="n">
-        <v>10.7460714</v>
+        <v>42.55748138000001</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
@@ -7364,7 +7364,7 @@
         <v>1103620.39</v>
       </c>
       <c r="E204" t="n">
-        <v>11.0362039</v>
+        <v>66.30837547</v>
       </c>
       <c r="F204" t="n">
         <v>3</v>
@@ -7398,7 +7398,7 @@
         <v>1684405.130000001</v>
       </c>
       <c r="E205" t="n">
-        <v>16.84405130000001</v>
+        <v>72.1073177</v>
       </c>
       <c r="F205" t="n">
         <v>0</v>
@@ -7432,7 +7432,7 @@
         <v>1686362.03</v>
       </c>
       <c r="E206" t="n">
-        <v>16.8636203</v>
+        <v>61.94020108000001</v>
       </c>
       <c r="F206" t="n">
         <v>0</v>
@@ -7466,7 +7466,7 @@
         <v>2001833.905</v>
       </c>
       <c r="E207" t="n">
-        <v>20.01833905000001</v>
+        <v>116.30465114</v>
       </c>
       <c r="F207" t="n">
         <v>0</v>
@@ -7500,7 +7500,7 @@
         <v>1276740.6905</v>
       </c>
       <c r="E208" t="n">
-        <v>12.767406905</v>
+        <v>66.85576336</v>
       </c>
       <c r="F208" t="n">
         <v>3</v>
@@ -7534,7 +7534,7 @@
         <v>1597562.43</v>
       </c>
       <c r="E209" t="n">
-        <v>15.9756243</v>
+        <v>88.47867821</v>
       </c>
       <c r="F209" t="n">
         <v>3</v>
@@ -7568,7 +7568,7 @@
         <v>1771764.05</v>
       </c>
       <c r="E210" t="n">
-        <v>17.71764049999999</v>
+        <v>75.59825791</v>
       </c>
       <c r="F210" t="n">
         <v>3</v>
@@ -7602,7 +7602,7 @@
         <v>1918009.420000001</v>
       </c>
       <c r="E211" t="n">
-        <v>19.18009420000001</v>
+        <v>112.48154805</v>
       </c>
       <c r="F211" t="n">
         <v>3</v>
@@ -7636,7 +7636,7 @@
         <v>3416040.900000003</v>
       </c>
       <c r="E212" t="n">
-        <v>34.16040900000003</v>
+        <v>105.4919814</v>
       </c>
       <c r="F212" t="n">
         <v>0</v>
@@ -7670,7 +7670,7 @@
         <v>1074884.37</v>
       </c>
       <c r="E213" t="n">
-        <v>10.7488437</v>
+        <v>42.46075999999999</v>
       </c>
       <c r="F213" t="n">
         <v>2</v>
@@ -7704,7 +7704,7 @@
         <v>1080862.43</v>
       </c>
       <c r="E214" t="n">
-        <v>10.8086243</v>
+        <v>46.7305</v>
       </c>
       <c r="F214" t="n">
         <v>2</v>
@@ -7738,7 +7738,7 @@
         <v>2241618.952900001</v>
       </c>
       <c r="E215" t="n">
-        <v>22.41618952900001</v>
+        <v>131.7189</v>
       </c>
       <c r="F215" t="n">
         <v>2</v>
@@ -7772,7 +7772,7 @@
         <v>2102665.381000001</v>
       </c>
       <c r="E216" t="n">
-        <v>21.02665381000001</v>
+        <v>114.2557</v>
       </c>
       <c r="F216" t="n">
         <v>2</v>
@@ -7806,7 +7806,7 @@
         <v>2045125.420000001</v>
       </c>
       <c r="E217" t="n">
-        <v>20.45125420000001</v>
+        <v>84.18970000000002</v>
       </c>
       <c r="F217" t="n">
         <v>2</v>
@@ -7840,7 +7840,7 @@
         <v>1916168.31</v>
       </c>
       <c r="E218" t="n">
-        <v>19.1616831</v>
+        <v>91.4577</v>
       </c>
       <c r="F218" t="n">
         <v>2</v>
@@ -7874,7 +7874,7 @@
         <v>1575479.8935</v>
       </c>
       <c r="E219" t="n">
-        <v>15.75479893500001</v>
+        <v>70.68070499999999</v>
       </c>
       <c r="F219" t="n">
         <v>2</v>
@@ -7908,7 +7908,7 @@
         <v>2536374.8325</v>
       </c>
       <c r="E220" t="n">
-        <v>25.363748325</v>
+        <v>126.098</v>
       </c>
       <c r="F220" t="n">
         <v>2</v>
@@ -7942,7 +7942,7 @@
         <v>1751246.863</v>
       </c>
       <c r="E221" t="n">
-        <v>17.51246863</v>
+        <v>82.72490000000002</v>
       </c>
       <c r="F221" t="n">
         <v>2</v>
@@ -7976,7 +7976,7 @@
         <v>1797473.066500001</v>
       </c>
       <c r="E222" t="n">
-        <v>17.97473066500001</v>
+        <v>86.91192750000002</v>
       </c>
       <c r="F222" t="n">
         <v>2</v>
@@ -8010,7 +8010,7 @@
         <v>2167124.52</v>
       </c>
       <c r="E223" t="n">
-        <v>21.6712452</v>
+        <v>111.2847575</v>
       </c>
       <c r="F223" t="n">
         <v>2</v>
@@ -8044,7 +8044,7 @@
         <v>1143110.535</v>
       </c>
       <c r="E224" t="n">
-        <v>11.43110535</v>
+        <v>56.31709999999999</v>
       </c>
       <c r="F224" t="n">
         <v>2</v>
@@ -8078,7 +8078,7 @@
         <v>2602516.97</v>
       </c>
       <c r="E225" t="n">
-        <v>26.0251697</v>
+        <v>83.71700000000001</v>
       </c>
       <c r="F225" t="n">
         <v>2</v>
@@ -8112,7 +8112,7 @@
         <v>1851393.8725</v>
       </c>
       <c r="E226" t="n">
-        <v>18.513938725</v>
+        <v>86.1181</v>
       </c>
       <c r="F226" t="n">
         <v>2</v>
@@ -8146,7 +8146,7 @@
         <v>1230325.7125</v>
       </c>
       <c r="E227" t="n">
-        <v>12.303257125</v>
+        <v>65.836</v>
       </c>
       <c r="F227" t="n">
         <v>5</v>
@@ -8180,7 +8180,7 @@
         <v>1965669.82</v>
       </c>
       <c r="E228" t="n">
-        <v>19.6566982</v>
+        <v>93.57170000000001</v>
       </c>
       <c r="F228" t="n">
         <v>2</v>
@@ -8214,7 +8214,7 @@
         <v>1581321.5078</v>
       </c>
       <c r="E229" t="n">
-        <v>15.813215078</v>
+        <v>84.7475</v>
       </c>
       <c r="F229" t="n">
         <v>2</v>
@@ -8248,7 +8248,7 @@
         <v>1898258.293</v>
       </c>
       <c r="E230" t="n">
-        <v>18.98258293</v>
+        <v>107.6923</v>
       </c>
       <c r="F230" t="n">
         <v>2</v>
@@ -8282,7 +8282,7 @@
         <v>2705208.104500002</v>
       </c>
       <c r="E231" t="n">
-        <v>27.05208104500002</v>
+        <v>139.3029</v>
       </c>
       <c r="F231" t="n">
         <v>2</v>
@@ -8316,7 +8316,7 @@
         <v>3550826.264000004</v>
       </c>
       <c r="E232" t="n">
-        <v>35.50826264000003</v>
+        <v>157.0891</v>
       </c>
       <c r="F232" t="n">
         <v>2</v>
@@ -8350,7 +8350,7 @@
         <v>2798573.040000001</v>
       </c>
       <c r="E233" t="n">
-        <v>27.9857304</v>
+        <v>136.7598</v>
       </c>
       <c r="F233" t="n">
         <v>2</v>
@@ -8384,7 +8384,7 @@
         <v>3675896.195999999</v>
       </c>
       <c r="E234" t="n">
-        <v>36.75896195999999</v>
+        <v>165.7064075</v>
       </c>
       <c r="F234" t="n">
         <v>2</v>
@@ -8418,7 +8418,7 @@
         <v>1950675.810000001</v>
       </c>
       <c r="E235" t="n">
-        <v>19.50675810000001</v>
+        <v>75.54960000000001</v>
       </c>
       <c r="F235" t="n">
         <v>2</v>
@@ -8452,7 +8452,7 @@
         <v>1740886.92</v>
       </c>
       <c r="E236" t="n">
-        <v>17.4088692</v>
+        <v>78.35300000000001</v>
       </c>
       <c r="F236" t="n">
         <v>2</v>
@@ -8486,7 +8486,7 @@
         <v>3883837.056400002</v>
       </c>
       <c r="E237" t="n">
-        <v>38.83837056400002</v>
+        <v>200.3232</v>
       </c>
       <c r="F237" t="n">
         <v>2</v>
@@ -8520,7 +8520,7 @@
         <v>3223989.21</v>
       </c>
       <c r="E238" t="n">
-        <v>32.2398921</v>
+        <v>68.56739999999999</v>
       </c>
       <c r="F238" t="n">
         <v>2</v>
@@ -8554,7 +8554,7 @@
         <v>2632731.015000002</v>
       </c>
       <c r="E239" t="n">
-        <v>26.32731015000002</v>
+        <v>111.0064</v>
       </c>
       <c r="F239" t="n">
         <v>5</v>
@@ -8588,7 +8588,7 @@
         <v>2454580.762700001</v>
       </c>
       <c r="E240" t="n">
-        <v>24.54580762700001</v>
+        <v>126.10768</v>
       </c>
       <c r="F240" t="n">
         <v>2</v>
@@ -8622,7 +8622,7 @@
         <v>2563707.997500001</v>
       </c>
       <c r="E241" t="n">
-        <v>25.63707997500001</v>
+        <v>115.5759</v>
       </c>
       <c r="F241" t="n">
         <v>2</v>
@@ -8656,7 +8656,7 @@
         <v>4645503.380000004</v>
       </c>
       <c r="E242" t="n">
-        <v>46.45503380000004</v>
+        <v>215.0096</v>
       </c>
       <c r="F242" t="n">
         <v>2</v>
@@ -8690,7 +8690,7 @@
         <v>1774811.37</v>
       </c>
       <c r="E243" t="n">
-        <v>17.7481137</v>
+        <v>83.30775</v>
       </c>
       <c r="F243" t="n">
         <v>2</v>
@@ -8724,7 +8724,7 @@
         <v>2030054.474000001</v>
       </c>
       <c r="E244" t="n">
-        <v>20.30054474000001</v>
+        <v>101.468</v>
       </c>
       <c r="F244" t="n">
         <v>2</v>
@@ -8758,7 +8758,7 @@
         <v>2040609.025000001</v>
       </c>
       <c r="E245" t="n">
-        <v>20.40609025000001</v>
+        <v>102.4148</v>
       </c>
       <c r="F245" t="n">
         <v>2</v>
@@ -8792,7 +8792,7 @@
         <v>1157036.248</v>
       </c>
       <c r="E246" t="n">
-        <v>11.57036248</v>
+        <v>85.72189999999999</v>
       </c>
       <c r="F246" t="n">
         <v>2</v>
@@ -8826,7 +8826,7 @@
         <v>2177290.545</v>
       </c>
       <c r="E247" t="n">
-        <v>21.77290545</v>
+        <v>75.19390000000001</v>
       </c>
       <c r="F247" t="n">
         <v>2</v>
@@ -8860,7 +8860,7 @@
         <v>1192178.595</v>
       </c>
       <c r="E248" t="n">
-        <v>11.92178595</v>
+        <v>60.35279999999999</v>
       </c>
       <c r="F248" t="n">
         <v>2</v>
@@ -8894,7 +8894,7 @@
         <v>1638049.93</v>
       </c>
       <c r="E249" t="n">
-        <v>16.3804993</v>
+        <v>77.68439999999998</v>
       </c>
       <c r="F249" t="n">
         <v>2</v>
@@ -8928,7 +8928,7 @@
         <v>1198368.35</v>
       </c>
       <c r="E250" t="n">
-        <v>11.9836835</v>
+        <v>56.0851</v>
       </c>
       <c r="F250" t="n">
         <v>2</v>
@@ -8962,7 +8962,7 @@
         <v>1375806.11</v>
       </c>
       <c r="E251" t="n">
-        <v>13.7580611</v>
+        <v>53.74859999999999</v>
       </c>
       <c r="F251" t="n">
         <v>2</v>
@@ -8996,7 +8996,7 @@
         <v>510076.44</v>
       </c>
       <c r="E252" t="n">
-        <v>5.1007644</v>
+        <v>22.082508</v>
       </c>
       <c r="F252" t="n">
         <v>4</v>
@@ -9030,7 +9030,7 @@
         <v>568725.01</v>
       </c>
       <c r="E253" t="n">
-        <v>5.6872501</v>
+        <v>26.1654</v>
       </c>
       <c r="F253" t="n">
         <v>4</v>
@@ -9064,7 +9064,7 @@
         <v>543588.8899999999</v>
       </c>
       <c r="E254" t="n">
-        <v>5.435888899999999</v>
+        <v>41.9052</v>
       </c>
       <c r="F254" t="n">
         <v>4</v>
@@ -9098,7 +9098,7 @@
         <v>1069336.49</v>
       </c>
       <c r="E255" t="n">
-        <v>10.6933649</v>
+        <v>898.0380000000002</v>
       </c>
       <c r="F255" t="n">
         <v>4</v>
@@ -9132,7 +9132,7 @@
         <v>1559050.77</v>
       </c>
       <c r="E256" t="n">
-        <v>15.5905077</v>
+        <v>13.4594</v>
       </c>
       <c r="F256" t="n">
         <v>4</v>
@@ -9166,7 +9166,7 @@
         <v>1896307.775000001</v>
       </c>
       <c r="E257" t="n">
-        <v>18.96307775000001</v>
+        <v>109.8696</v>
       </c>
       <c r="F257" t="n">
         <v>4</v>
@@ -9200,7 +9200,7 @@
         <v>1962784.350000001</v>
       </c>
       <c r="E258" t="n">
-        <v>19.62784350000001</v>
+        <v>128.60566</v>
       </c>
       <c r="F258" t="n">
         <v>4</v>
@@ -9234,7 +9234,7 @@
         <v>2434991.280000001</v>
       </c>
       <c r="E259" t="n">
-        <v>24.34991280000001</v>
+        <v>571.5419999999999</v>
       </c>
       <c r="F259" t="n">
         <v>4</v>
@@ -9268,7 +9268,7 @@
         <v>1806396.195000001</v>
       </c>
       <c r="E260" t="n">
-        <v>18.06396195000001</v>
+        <v>122.977441</v>
       </c>
       <c r="F260" t="n">
         <v>4</v>
@@ -9302,7 +9302,7 @@
         <v>2593651.960000001</v>
       </c>
       <c r="E261" t="n">
-        <v>25.93651960000001</v>
+        <v>131.0654675</v>
       </c>
       <c r="F261" t="n">
         <v>4</v>
@@ -9336,7 +9336,7 @@
         <v>1848911.990000001</v>
       </c>
       <c r="E262" t="n">
-        <v>18.48911990000001</v>
+        <v>95.62609999999999</v>
       </c>
       <c r="F262" t="n">
         <v>4</v>
@@ -9370,7 +9370,7 @@
         <v>1714893.622500001</v>
       </c>
       <c r="E263" t="n">
-        <v>17.14893622500001</v>
+        <v>106.7479</v>
       </c>
       <c r="F263" t="n">
         <v>4</v>
@@ -9404,7 +9404,7 @@
         <v>2284491.272000001</v>
       </c>
       <c r="E264" t="n">
-        <v>22.84491272000001</v>
+        <v>123.2049255</v>
       </c>
       <c r="F264" t="n">
         <v>4</v>
@@ -9438,7 +9438,7 @@
         <v>1242039.34</v>
       </c>
       <c r="E265" t="n">
-        <v>12.4203934</v>
+        <v>284.046</v>
       </c>
       <c r="F265" t="n">
         <v>4</v>
@@ -9472,7 +9472,7 @@
         <v>1194645.255</v>
       </c>
       <c r="E266" t="n">
-        <v>11.94645255</v>
+        <v>995.3472000000002</v>
       </c>
       <c r="F266" t="n">
         <v>4</v>
@@ -9506,7 +9506,7 @@
         <v>1588148.52</v>
       </c>
       <c r="E267" t="n">
-        <v>15.8814852</v>
+        <v>56.9948</v>
       </c>
       <c r="F267" t="n">
         <v>4</v>
@@ -9540,7 +9540,7 @@
         <v>2930447.790000001</v>
       </c>
       <c r="E268" t="n">
-        <v>29.30447790000001</v>
+        <v>162.227688</v>
       </c>
       <c r="F268" t="n">
         <v>4</v>
@@ -9574,7 +9574,7 @@
         <v>1871897.32</v>
       </c>
       <c r="E269" t="n">
-        <v>18.7189732</v>
+        <v>93.85904950000001</v>
       </c>
       <c r="F269" t="n">
         <v>4</v>
@@ -9608,7 +9608,7 @@
         <v>1478735.09</v>
       </c>
       <c r="E270" t="n">
-        <v>14.7873509</v>
+        <v>72.16600000000001</v>
       </c>
       <c r="F270" t="n">
         <v>4</v>
@@ -9642,7 +9642,7 @@
         <v>1503425</v>
       </c>
       <c r="E271" t="n">
-        <v>15.03425000000001</v>
+        <v>77.25859999999999</v>
       </c>
       <c r="F271" t="n">
         <v>4</v>
@@ -9676,7 +9676,7 @@
         <v>1511007.57</v>
       </c>
       <c r="E272" t="n">
-        <v>15.1100757</v>
+        <v>72.49699999999999</v>
       </c>
       <c r="F272" t="n">
         <v>4</v>
@@ -9710,7 +9710,7 @@
         <v>3615376.678000004</v>
       </c>
       <c r="E273" t="n">
-        <v>36.15376678000004</v>
+        <v>186.4224215</v>
       </c>
       <c r="F273" t="n">
         <v>4</v>
@@ -9744,7 +9744,7 @@
         <v>3072811.520000002</v>
       </c>
       <c r="E274" t="n">
-        <v>30.72811520000002</v>
+        <v>150.1102</v>
       </c>
       <c r="F274" t="n">
         <v>4</v>
@@ -9778,7 +9778,7 @@
         <v>1741330.950000001</v>
       </c>
       <c r="E275" t="n">
-        <v>17.41330950000001</v>
+        <v>71.23049999999999</v>
       </c>
       <c r="F275" t="n">
         <v>4</v>
@@ -9812,7 +9812,7 @@
         <v>4084671.510000004</v>
       </c>
       <c r="E276" t="n">
-        <v>40.84671510000004</v>
+        <v>222.122161</v>
       </c>
       <c r="F276" t="n">
         <v>4</v>
@@ -9846,7 +9846,7 @@
         <v>3240192.853500002</v>
       </c>
       <c r="E277" t="n">
-        <v>32.40192853500002</v>
+        <v>243.76794</v>
       </c>
       <c r="F277" t="n">
         <v>4</v>
@@ -9880,7 +9880,7 @@
         <v>1377782.69</v>
       </c>
       <c r="E278" t="n">
-        <v>13.7778269</v>
+        <v>59.30860000000001</v>
       </c>
       <c r="F278" t="n">
         <v>4</v>
@@ -9914,7 +9914,7 @@
         <v>3446706.336000002</v>
       </c>
       <c r="E279" t="n">
-        <v>34.46706336000003</v>
+        <v>200.4813</v>
       </c>
       <c r="F279" t="n">
         <v>4</v>
@@ -9948,7 +9948,7 @@
         <v>2327134.427500001</v>
       </c>
       <c r="E280" t="n">
-        <v>23.27134427500001</v>
+        <v>152.1270185</v>
       </c>
       <c r="F280" t="n">
         <v>4</v>
@@ -9982,7 +9982,7 @@
         <v>1920996.985</v>
       </c>
       <c r="E281" t="n">
-        <v>19.20996985</v>
+        <v>100.023278</v>
       </c>
       <c r="F281" t="n">
         <v>4</v>
@@ -10016,7 +10016,7 @@
         <v>1744236.570000002</v>
       </c>
       <c r="E282" t="n">
-        <v>17.44236570000002</v>
+        <v>65.61912249999999</v>
       </c>
       <c r="F282" t="n">
         <v>4</v>
@@ -10050,7 +10050,7 @@
         <v>1921844.350000001</v>
       </c>
       <c r="E283" t="n">
-        <v>19.21844350000001</v>
+        <v>59.61479999999999</v>
       </c>
       <c r="F283" t="n">
         <v>4</v>
@@ -10084,7 +10084,7 @@
         <v>1808025.74</v>
       </c>
       <c r="E284" t="n">
-        <v>18.0802574</v>
+        <v>92.10120000000001</v>
       </c>
       <c r="F284" t="n">
         <v>4</v>
@@ -10118,7 +10118,7 @@
         <v>2074607.035000001</v>
       </c>
       <c r="E285" t="n">
-        <v>20.74607035000001</v>
+        <v>87.2212</v>
       </c>
       <c r="F285" t="n">
         <v>4</v>
@@ -10152,7 +10152,7 @@
         <v>1502978.390000001</v>
       </c>
       <c r="E286" t="n">
-        <v>15.02978390000001</v>
+        <v>44.383</v>
       </c>
       <c r="F286" t="n">
         <v>4</v>
@@ -10186,7 +10186,7 @@
         <v>1291323.67</v>
       </c>
       <c r="E287" t="n">
-        <v>12.9132367</v>
+        <v>72.4555</v>
       </c>
       <c r="F287" t="n">
         <v>4</v>
@@ -10220,7 +10220,7 @@
         <v>2355886.92</v>
       </c>
       <c r="E288" t="n">
-        <v>23.5588692</v>
+        <v>228.606</v>
       </c>
       <c r="F288" t="n">
         <v>4</v>
@@ -10254,7 +10254,7 @@
         <v>3031148.050000003</v>
       </c>
       <c r="E289" t="n">
-        <v>30.31148050000003</v>
+        <v>106.680992</v>
       </c>
       <c r="F289" t="n">
         <v>4</v>
@@ -10288,7 +10288,7 @@
         <v>2400814.098000001</v>
       </c>
       <c r="E290" t="n">
-        <v>24.00814098000001</v>
+        <v>118.29098</v>
       </c>
       <c r="F290" t="n">
         <v>0</v>
@@ -10322,7 +10322,7 @@
         <v>1827437.2</v>
       </c>
       <c r="E291" t="n">
-        <v>18.274372</v>
+        <v>56.55883999999998</v>
       </c>
       <c r="F291" t="n">
         <v>1</v>
@@ -10356,7 +10356,7 @@
         <v>2439325.167</v>
       </c>
       <c r="E292" t="n">
-        <v>24.39325167</v>
+        <v>99.75030000000001</v>
       </c>
       <c r="F292" t="n">
         <v>0</v>
@@ -10390,7 +10390,7 @@
         <v>2126889.502500001</v>
       </c>
       <c r="E293" t="n">
-        <v>21.26889502500001</v>
+        <v>76.35709999999999</v>
       </c>
       <c r="F293" t="n">
         <v>0</v>
@@ -10424,7 +10424,7 @@
         <v>1886286.770000001</v>
       </c>
       <c r="E294" t="n">
-        <v>18.86286770000001</v>
+        <v>65.98963999999999</v>
       </c>
       <c r="F294" t="n">
         <v>1</v>
@@ -10458,7 +10458,7 @@
         <v>2055151.592500001</v>
       </c>
       <c r="E295" t="n">
-        <v>20.55151592500001</v>
+        <v>70.17684000000001</v>
       </c>
       <c r="F295" t="n">
         <v>3</v>
@@ -10492,7 +10492,7 @@
         <v>1874581.7225</v>
       </c>
       <c r="E296" t="n">
-        <v>18.745817225</v>
+        <v>80.12326000000002</v>
       </c>
       <c r="F296" t="n">
         <v>0</v>
@@ -10526,7 +10526,7 @@
         <v>1657880.06</v>
       </c>
       <c r="E297" t="n">
-        <v>16.5788006</v>
+        <v>73.27007999999999</v>
       </c>
       <c r="F297" t="n">
         <v>3</v>
@@ -10560,7 +10560,7 @@
         <v>2079508.26</v>
       </c>
       <c r="E298" t="n">
-        <v>20.7950826</v>
+        <v>113.30992</v>
       </c>
       <c r="F298" t="n">
         <v>0</v>
@@ -10594,7 +10594,7 @@
         <v>936408.2679999999</v>
       </c>
       <c r="E299" t="n">
-        <v>9.364082679999999</v>
+        <v>43.52612</v>
       </c>
       <c r="F299" t="n">
         <v>1</v>
@@ -10628,7 +10628,7 @@
         <v>2022899.086000001</v>
       </c>
       <c r="E300" t="n">
-        <v>20.22899086000001</v>
+        <v>108.32342</v>
       </c>
       <c r="F300" t="n">
         <v>0</v>
@@ -10662,7 +10662,7 @@
         <v>1712647.384</v>
       </c>
       <c r="E301" t="n">
-        <v>17.12647384</v>
+        <v>51.79328</v>
       </c>
       <c r="F301" t="n">
         <v>1</v>
@@ -10696,7 +10696,7 @@
         <v>1668319.63</v>
       </c>
       <c r="E302" t="n">
-        <v>16.6831963</v>
+        <v>68.9781</v>
       </c>
       <c r="F302" t="n">
         <v>1</v>
@@ -10730,7 +10730,7 @@
         <v>1717350.646</v>
       </c>
       <c r="E303" t="n">
-        <v>17.17350646</v>
+        <v>69.73756</v>
       </c>
       <c r="F303" t="n">
         <v>1</v>
@@ -10764,7 +10764,7 @@
         <v>2540981.337000002</v>
       </c>
       <c r="E304" t="n">
-        <v>25.40981337000002</v>
+        <v>116.13984</v>
       </c>
       <c r="F304" t="n">
         <v>1</v>
@@ -10798,7 +10798,7 @@
         <v>2228483.634500001</v>
       </c>
       <c r="E305" t="n">
-        <v>22.28483634500001</v>
+        <v>100.22104</v>
       </c>
       <c r="F305" t="n">
         <v>1</v>
@@ -10832,7 +10832,7 @@
         <v>2240777.881000001</v>
       </c>
       <c r="E306" t="n">
-        <v>22.40777881</v>
+        <v>124.95866</v>
       </c>
       <c r="F306" t="n">
         <v>0</v>
@@ -10866,7 +10866,7 @@
         <v>1785135.895000001</v>
       </c>
       <c r="E307" t="n">
-        <v>17.85135895000001</v>
+        <v>106.6222</v>
       </c>
       <c r="F307" t="n">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>758128.6375</v>
       </c>
       <c r="E308" t="n">
-        <v>7.581286374999999</v>
+        <v>37.92908</v>
       </c>
       <c r="F308" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
         <v>2097275.887500001</v>
       </c>
       <c r="E309" t="n">
-        <v>20.97275887500001</v>
+        <v>76.79181999999999</v>
       </c>
       <c r="F309" t="n">
         <v>1</v>
@@ -10968,7 +10968,7 @@
         <v>1271026.450000001</v>
       </c>
       <c r="E310" t="n">
-        <v>12.71026450000001</v>
+        <v>47.35968</v>
       </c>
       <c r="F310" t="n">
         <v>3</v>
@@ -11002,7 +11002,7 @@
         <v>3441223.744500001</v>
       </c>
       <c r="E311" t="n">
-        <v>34.41223744500002</v>
+        <v>153.85138</v>
       </c>
       <c r="F311" t="n">
         <v>0</v>
@@ -11036,7 +11036,7 @@
         <v>3528232.9955</v>
       </c>
       <c r="E312" t="n">
-        <v>35.282329955</v>
+        <v>178.5294</v>
       </c>
       <c r="F312" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>3162314.795000001</v>
       </c>
       <c r="E313" t="n">
-        <v>31.62314795000001</v>
+        <v>138.3113</v>
       </c>
       <c r="F313" t="n">
         <v>0</v>
@@ -11104,7 +11104,7 @@
         <v>3490977.410000002</v>
       </c>
       <c r="E314" t="n">
-        <v>34.90977410000002</v>
+        <v>148.35608</v>
       </c>
       <c r="F314" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>2732812.491500001</v>
       </c>
       <c r="E315" t="n">
-        <v>27.32812491500001</v>
+        <v>137.84592</v>
       </c>
       <c r="F315" t="n">
         <v>0</v>
@@ -11172,7 +11172,7 @@
         <v>1857176.0225</v>
       </c>
       <c r="E316" t="n">
-        <v>18.571760225</v>
+        <v>71.19014000000001</v>
       </c>
       <c r="F316" t="n">
         <v>1</v>
@@ -11206,7 +11206,7 @@
         <v>2405464.259000001</v>
       </c>
       <c r="E317" t="n">
-        <v>24.05464259000001</v>
+        <v>106.50236</v>
       </c>
       <c r="F317" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
         <v>2330755.221000001</v>
       </c>
       <c r="E318" t="n">
-        <v>23.30755221000001</v>
+        <v>97.77134</v>
       </c>
       <c r="F318" t="n">
         <v>0</v>
@@ -11274,7 +11274,7 @@
         <v>2455062.360000001</v>
       </c>
       <c r="E319" t="n">
-        <v>24.55062360000001</v>
+        <v>80.68743999999998</v>
       </c>
       <c r="F319" t="n">
         <v>1</v>
@@ -11308,7 +11308,7 @@
         <v>2290675.900000001</v>
       </c>
       <c r="E320" t="n">
-        <v>22.90675900000001</v>
+        <v>92.23769999999999</v>
       </c>
       <c r="F320" t="n">
         <v>1</v>
@@ -11342,7 +11342,7 @@
         <v>2470157.010000001</v>
       </c>
       <c r="E321" t="n">
-        <v>24.70157010000001</v>
+        <v>111.7828</v>
       </c>
       <c r="F321" t="n">
         <v>1</v>
@@ -11376,7 +11376,7 @@
         <v>2967703.99</v>
       </c>
       <c r="E322" t="n">
-        <v>29.6770399</v>
+        <v>120.6901</v>
       </c>
       <c r="F322" t="n">
         <v>0</v>
@@ -11410,7 +11410,7 @@
         <v>2942063.320000001</v>
       </c>
       <c r="E323" t="n">
-        <v>29.42063320000001</v>
+        <v>51.7548</v>
       </c>
       <c r="F323" t="n">
         <v>0</v>
@@ -11444,7 +11444,7 @@
         <v>2843065.247500001</v>
       </c>
       <c r="E324" t="n">
-        <v>28.43065247500001</v>
+        <v>162.11432</v>
       </c>
       <c r="F324" t="n">
         <v>0</v>
@@ -11478,7 +11478,7 @@
         <v>1921254.830000001</v>
       </c>
       <c r="E325" t="n">
-        <v>19.21254830000001</v>
+        <v>70.43834</v>
       </c>
       <c r="F325" t="n">
         <v>0</v>
@@ -11512,7 +11512,7 @@
         <v>2321428.840000001</v>
       </c>
       <c r="E326" t="n">
-        <v>23.21428840000001</v>
+        <v>97.17318</v>
       </c>
       <c r="F326" t="n">
         <v>0</v>
@@ -11546,7 +11546,7 @@
         <v>2136604.985</v>
       </c>
       <c r="E327" t="n">
-        <v>21.36604985</v>
+        <v>96.64926</v>
       </c>
       <c r="F327" t="n">
         <v>1</v>
@@ -11580,7 +11580,7 @@
         <v>3213855.070000002</v>
       </c>
       <c r="E328" t="n">
-        <v>32.13855070000002</v>
+        <v>136.70414</v>
       </c>
       <c r="F328" t="n">
         <v>1</v>
@@ -11614,7 +11614,7 @@
         <v>1617461.775000001</v>
       </c>
       <c r="E329" t="n">
-        <v>16.17461775000001</v>
+        <v>55.98389999999999</v>
       </c>
       <c r="F329" t="n">
         <v>0</v>
@@ -11648,7 +11648,7 @@
         <v>1467113.07</v>
       </c>
       <c r="E330" t="n">
-        <v>14.6711307</v>
+        <v>57.27579999999999</v>
       </c>
       <c r="F330" t="n">
         <v>0</v>
@@ -11682,7 +11682,7 @@
         <v>2293216.070000001</v>
       </c>
       <c r="E331" t="n">
-        <v>22.93216070000001</v>
+        <v>100.51814</v>
       </c>
       <c r="F331" t="n">
         <v>1</v>
@@ -11716,7 +11716,7 @@
         <v>2137098.680000001</v>
       </c>
       <c r="E332" t="n">
-        <v>21.37098680000001</v>
+        <v>72.68213999999999</v>
       </c>
       <c r="F332" t="n">
         <v>1</v>
@@ -11750,7 +11750,7 @@
         <v>1340941.68</v>
       </c>
       <c r="E333" t="n">
-        <v>13.4094168</v>
+        <v>53.00724</v>
       </c>
       <c r="F333" t="n">
         <v>1</v>
@@ -11784,7 +11784,7 @@
         <v>1394611.61</v>
       </c>
       <c r="E334" t="n">
-        <v>13.9461161</v>
+        <v>84.78078000000001</v>
       </c>
       <c r="F334" t="n">
         <v>0</v>
@@ -11818,7 +11818,7 @@
         <v>2002785.950000001</v>
       </c>
       <c r="E335" t="n">
-        <v>20.02785950000001</v>
+        <v>97.36683999999997</v>
       </c>
       <c r="F335" t="n">
         <v>0</v>
@@ -11852,7 +11852,7 @@
         <v>1675167.828</v>
       </c>
       <c r="E336" t="n">
-        <v>16.75167828</v>
+        <v>81.07180000000001</v>
       </c>
       <c r="F336" t="n">
         <v>0</v>
@@ -11886,7 +11886,7 @@
         <v>1390496.76</v>
       </c>
       <c r="E337" t="n">
-        <v>13.9049676</v>
+        <v>51.87629999999999</v>
       </c>
       <c r="F337" t="n">
         <v>0</v>
@@ -11920,7 +11920,7 @@
         <v>3087443.503300001</v>
       </c>
       <c r="E338" t="n">
-        <v>30.87443503300002</v>
+        <v>164.81286</v>
       </c>
       <c r="F338" t="n">
         <v>1</v>
@@ -11954,7 +11954,7 @@
         <v>2623549.435</v>
       </c>
       <c r="E339" t="n">
-        <v>26.23549435</v>
+        <v>137.11044</v>
       </c>
       <c r="F339" t="n">
         <v>4</v>
@@ -11988,7 +11988,7 @@
         <v>2059868.085</v>
       </c>
       <c r="E340" t="n">
-        <v>20.59868085</v>
+        <v>105.60097665</v>
       </c>
       <c r="F340" t="n">
         <v>1</v>
@@ -12022,7 +12022,7 @@
         <v>1770315.978</v>
       </c>
       <c r="E341" t="n">
-        <v>17.70315978</v>
+        <v>85.30447965</v>
       </c>
       <c r="F341" t="n">
         <v>1</v>
@@ -12056,7 +12056,7 @@
         <v>2092720.740000001</v>
       </c>
       <c r="E342" t="n">
-        <v>20.92720740000001</v>
+        <v>105.13692</v>
       </c>
       <c r="F342" t="n">
         <v>1</v>
@@ -12090,7 +12090,7 @@
         <v>2426952.197000002</v>
       </c>
       <c r="E343" t="n">
-        <v>24.26952197000002</v>
+        <v>119.39315505</v>
       </c>
       <c r="F343" t="n">
         <v>1</v>
@@ -12124,7 +12124,7 @@
         <v>2532936.2045</v>
       </c>
       <c r="E344" t="n">
-        <v>25.329362045</v>
+        <v>135.2097</v>
       </c>
       <c r="F344" t="n">
         <v>1</v>
@@ -12158,7 +12158,7 @@
         <v>2129516.15</v>
       </c>
       <c r="E345" t="n">
-        <v>21.2951615</v>
+        <v>103.2224895</v>
       </c>
       <c r="F345" t="n">
         <v>1</v>
@@ -12192,7 +12192,7 @@
         <v>1849434.632500001</v>
       </c>
       <c r="E346" t="n">
-        <v>18.49434632500001</v>
+        <v>105.68844</v>
       </c>
       <c r="F346" t="n">
         <v>1</v>
@@ -12226,7 +12226,7 @@
         <v>2021661.2675</v>
       </c>
       <c r="E347" t="n">
-        <v>20.216612675</v>
+        <v>92.92085999999999</v>
       </c>
       <c r="F347" t="n">
         <v>1</v>
@@ -12260,7 +12260,7 @@
         <v>2126051.28</v>
       </c>
       <c r="E348" t="n">
-        <v>21.2605128</v>
+        <v>105.6147144</v>
       </c>
       <c r="F348" t="n">
         <v>1</v>
@@ -12294,7 +12294,7 @@
         <v>1650176.3</v>
       </c>
       <c r="E349" t="n">
-        <v>16.501763</v>
+        <v>96.36005999999999</v>
       </c>
       <c r="F349" t="n">
         <v>1</v>
@@ -12328,7 +12328,7 @@
         <v>1490258.29</v>
       </c>
       <c r="E350" t="n">
-        <v>14.9025829</v>
+        <v>81.90635999999998</v>
       </c>
       <c r="F350" t="n">
         <v>4</v>
@@ -12362,7 +12362,7 @@
         <v>1772852.66</v>
       </c>
       <c r="E351" t="n">
-        <v>17.7285266</v>
+        <v>103.29378</v>
       </c>
       <c r="F351" t="n">
         <v>1</v>
@@ -12396,7 +12396,7 @@
         <v>1519209.972500001</v>
       </c>
       <c r="E352" t="n">
-        <v>15.19209972500001</v>
+        <v>69.66414</v>
       </c>
       <c r="F352" t="n">
         <v>1</v>
@@ -12430,7 +12430,7 @@
         <v>2889586.350000002</v>
       </c>
       <c r="E353" t="n">
-        <v>28.89586350000003</v>
+        <v>133.07976</v>
       </c>
       <c r="F353" t="n">
         <v>1</v>
@@ -12464,7 +12464,7 @@
         <v>1999079.31</v>
       </c>
       <c r="E354" t="n">
-        <v>19.9907931</v>
+        <v>99.53225999999999</v>
       </c>
       <c r="F354" t="n">
         <v>1</v>
@@ -12498,7 +12498,7 @@
         <v>4033521.890000003</v>
       </c>
       <c r="E355" t="n">
-        <v>40.33521890000004</v>
+        <v>174.81366</v>
       </c>
       <c r="F355" t="n">
         <v>1</v>
@@ -12532,7 +12532,7 @@
         <v>2273780.970000001</v>
       </c>
       <c r="E356" t="n">
-        <v>22.73780970000001</v>
+        <v>123.87336</v>
       </c>
       <c r="F356" t="n">
         <v>1</v>
@@ -12566,7 +12566,7 @@
         <v>2678556.970000001</v>
       </c>
       <c r="E357" t="n">
-        <v>26.78556970000001</v>
+        <v>147.74808</v>
       </c>
       <c r="F357" t="n">
         <v>1</v>
@@ -12600,7 +12600,7 @@
         <v>2876448.385500001</v>
       </c>
       <c r="E358" t="n">
-        <v>28.76448385500001</v>
+        <v>148.73862</v>
       </c>
       <c r="F358" t="n">
         <v>1</v>
@@ -12634,7 +12634,7 @@
         <v>3985816.922500002</v>
       </c>
       <c r="E359" t="n">
-        <v>39.85816922500002</v>
+        <v>273.06534</v>
       </c>
       <c r="F359" t="n">
         <v>1</v>
@@ -12668,7 +12668,7 @@
         <v>1903732.92</v>
       </c>
       <c r="E360" t="n">
-        <v>19.0373292</v>
+        <v>108.07158</v>
       </c>
       <c r="F360" t="n">
         <v>1</v>
@@ -12702,7 +12702,7 @@
         <v>3179932.52</v>
       </c>
       <c r="E361" t="n">
-        <v>31.79932519999999</v>
+        <v>154.62948</v>
       </c>
       <c r="F361" t="n">
         <v>1</v>
@@ -12736,7 +12736,7 @@
         <v>2681351.330000001</v>
       </c>
       <c r="E362" t="n">
-        <v>26.81351330000001</v>
+        <v>133.61611575</v>
       </c>
       <c r="F362" t="n">
         <v>1</v>
@@ -12770,7 +12770,7 @@
         <v>2675428.000000001</v>
       </c>
       <c r="E363" t="n">
-        <v>26.75428000000002</v>
+        <v>107.2794</v>
       </c>
       <c r="F363" t="n">
         <v>1</v>
@@ -12804,7 +12804,7 @@
         <v>1881320.396000001</v>
       </c>
       <c r="E364" t="n">
-        <v>18.81320396000001</v>
+        <v>90.89004</v>
       </c>
       <c r="F364" t="n">
         <v>1</v>
@@ -12838,7 +12838,7 @@
         <v>981031.9450000001</v>
       </c>
       <c r="E365" t="n">
-        <v>9.810319450000001</v>
+        <v>65.39706</v>
       </c>
       <c r="F365" t="n">
         <v>1</v>
@@ -12872,7 +12872,7 @@
         <v>1483013.48</v>
       </c>
       <c r="E366" t="n">
-        <v>14.8301348</v>
+        <v>93.90606000000002</v>
       </c>
       <c r="F366" t="n">
         <v>1</v>
@@ -12906,7 +12906,7 @@
         <v>1469104.9875</v>
       </c>
       <c r="E367" t="n">
-        <v>14.691049875</v>
+        <v>102.0003</v>
       </c>
       <c r="F367" t="n">
         <v>4</v>
@@ -12940,7 +12940,7 @@
         <v>1270001.2245</v>
       </c>
       <c r="E368" t="n">
-        <v>12.700012245</v>
+        <v>69.34979999999999</v>
       </c>
       <c r="F368" t="n">
         <v>1</v>
@@ -12974,7 +12974,7 @@
         <v>3367278.935000002</v>
       </c>
       <c r="E369" t="n">
-        <v>33.67278935000002</v>
+        <v>147.48796146</v>
       </c>
       <c r="F369" t="n">
         <v>5</v>
@@ -13008,7 +13008,7 @@
         <v>2371927.880000001</v>
       </c>
       <c r="E370" t="n">
-        <v>23.71927880000001</v>
+        <v>81.62645259999999</v>
       </c>
       <c r="F370" t="n">
         <v>5</v>
@@ -13042,7 +13042,7 @@
         <v>2320542.52</v>
       </c>
       <c r="E371" t="n">
-        <v>23.2054252</v>
+        <v>125.7125763</v>
       </c>
       <c r="F371" t="n">
         <v>5</v>
@@ -13076,7 +13076,7 @@
         <v>2139974.96</v>
       </c>
       <c r="E372" t="n">
-        <v>21.3997496</v>
+        <v>118.30654686</v>
       </c>
       <c r="F372" t="n">
         <v>5</v>
@@ -13110,7 +13110,7 @@
         <v>885512.6600000001</v>
       </c>
       <c r="E373" t="n">
-        <v>8.855126600000002</v>
+        <v>46.7992934</v>
       </c>
       <c r="F373" t="n">
         <v>5</v>
@@ -13144,7 +13144,7 @@
         <v>3390955.100000001</v>
       </c>
       <c r="E374" t="n">
-        <v>33.90955100000001</v>
+        <v>135.638204</v>
       </c>
       <c r="F374" t="n">
         <v>5</v>
@@ -13178,7 +13178,7 @@
         <v>2223942.2115</v>
       </c>
       <c r="E375" t="n">
-        <v>22.239422115</v>
+        <v>82.8659857</v>
       </c>
       <c r="F375" t="n">
         <v>5</v>
@@ -13212,7 +13212,7 @@
         <v>2546442.770000001</v>
       </c>
       <c r="E376" t="n">
-        <v>25.46442770000001</v>
+        <v>105.553257</v>
       </c>
       <c r="F376" t="n">
         <v>5</v>
@@ -13246,7 +13246,7 @@
         <v>1041121.11</v>
       </c>
       <c r="E377" t="n">
-        <v>10.4112111</v>
+        <v>71.35351295999999</v>
       </c>
       <c r="F377" t="n">
         <v>5</v>
@@ -13280,7 +13280,7 @@
         <v>1349453.5</v>
       </c>
       <c r="E378" t="n">
-        <v>13.494535</v>
+        <v>102.73411212</v>
       </c>
       <c r="F378" t="n">
         <v>5</v>
@@ -13314,7 +13314,7 @@
         <v>3364702.390000002</v>
       </c>
       <c r="E379" t="n">
-        <v>33.64702390000002</v>
+        <v>128.5971056</v>
       </c>
       <c r="F379" t="n">
         <v>5</v>
@@ -13348,7 +13348,7 @@
         <v>957542.0800000002</v>
       </c>
       <c r="E380" t="n">
-        <v>9.575420800000002</v>
+        <v>62.78045063999999</v>
       </c>
       <c r="F380" t="n">
         <v>5</v>
@@ -13382,7 +13382,7 @@
         <v>1832423.320000001</v>
       </c>
       <c r="E381" t="n">
-        <v>18.32423320000001</v>
+        <v>109.3731514</v>
       </c>
       <c r="F381" t="n">
         <v>5</v>
@@ -13416,7 +13416,7 @@
         <v>2827458.462500003</v>
       </c>
       <c r="E382" t="n">
-        <v>28.27458462500003</v>
+        <v>119.1499458</v>
       </c>
       <c r="F382" t="n">
         <v>5</v>
@@ -13450,7 +13450,7 @@
         <v>5139214.085000006</v>
       </c>
       <c r="E383" t="n">
-        <v>51.39214085000007</v>
+        <v>213.5551645</v>
       </c>
       <c r="F383" t="n">
         <v>5</v>
@@ -13484,7 +13484,7 @@
         <v>3825880.310000004</v>
       </c>
       <c r="E384" t="n">
-        <v>38.25880310000004</v>
+        <v>187.0876349</v>
       </c>
       <c r="F384" t="n">
         <v>5</v>
@@ -13518,7 +13518,7 @@
         <v>3912698.900000005</v>
       </c>
       <c r="E385" t="n">
-        <v>39.12698900000005</v>
+        <v>149.1235557</v>
       </c>
       <c r="F385" t="n">
         <v>5</v>
@@ -13552,7 +13552,7 @@
         <v>2805363.835000002</v>
       </c>
       <c r="E386" t="n">
-        <v>28.05363835000002</v>
+        <v>170.141426</v>
       </c>
       <c r="F386" t="n">
         <v>5</v>
@@ -13586,7 +13586,7 @@
         <v>4522032.525000003</v>
       </c>
       <c r="E387" t="n">
-        <v>45.22032525000003</v>
+        <v>168.952343</v>
       </c>
       <c r="F387" t="n">
         <v>5</v>
@@ -13620,7 +13620,7 @@
         <v>2845156.670000002</v>
       </c>
       <c r="E388" t="n">
-        <v>28.45156670000002</v>
+        <v>107.310147</v>
       </c>
       <c r="F388" t="n">
         <v>5</v>
@@ -13654,7 +13654,7 @@
         <v>2288790.030000002</v>
       </c>
       <c r="E389" t="n">
-        <v>22.88790030000002</v>
+        <v>111.302101</v>
       </c>
       <c r="F389" t="n">
         <v>5</v>
@@ -13688,7 +13688,7 @@
         <v>2041466.880000001</v>
       </c>
       <c r="E390" t="n">
-        <v>20.41466880000001</v>
+        <v>77.23364369999999</v>
       </c>
       <c r="F390" t="n">
         <v>5</v>
@@ -13722,7 +13722,7 @@
         <v>905124.0099999999</v>
       </c>
       <c r="E391" t="n">
-        <v>9.051240099999999</v>
+        <v>53.22112451999999</v>
       </c>
       <c r="F391" t="n">
         <v>5</v>
@@ -13756,7 +13756,7 @@
         <v>2371243.450000002</v>
       </c>
       <c r="E392" t="n">
-        <v>23.71243450000001</v>
+        <v>110.9159485</v>
       </c>
       <c r="F392" t="n">
         <v>5</v>
@@ -13790,7 +13790,7 @@
         <v>1850655.030000001</v>
       </c>
       <c r="E393" t="n">
-        <v>18.50655030000001</v>
+        <v>95.37692682000001</v>
       </c>
       <c r="F393" t="n">
         <v>5</v>
@@ -13824,7 +13824,7 @@
         <v>1735844.400000001</v>
       </c>
       <c r="E394" t="n">
-        <v>17.35844400000001</v>
+        <v>54.18531179999999</v>
       </c>
       <c r="F394" t="n">
         <v>5</v>
@@ -13858,7 +13858,7 @@
         <v>2873970.410000003</v>
       </c>
       <c r="E395" t="n">
-        <v>28.73970410000003</v>
+        <v>111.9413228</v>
       </c>
       <c r="F395" t="n">
         <v>5</v>
@@ -13892,7 +13892,7 @@
         <v>844086.03</v>
       </c>
       <c r="E396" t="n">
-        <v>8.440860300000001</v>
+        <v>38.27594000000001</v>
       </c>
       <c r="F396" t="n">
         <v>2</v>
@@ -13926,7 +13926,7 @@
         <v>2322555.614000001</v>
       </c>
       <c r="E397" t="n">
-        <v>23.22555614000002</v>
+        <v>120.77989</v>
       </c>
       <c r="F397" t="n">
         <v>2</v>
@@ -13960,7 +13960,7 @@
         <v>1773783.181500001</v>
       </c>
       <c r="E398" t="n">
-        <v>17.73783181500001</v>
+        <v>88.73139999999999</v>
       </c>
       <c r="F398" t="n">
         <v>0</v>
@@ -13994,7 +13994,7 @@
         <v>3406740.079000003</v>
       </c>
       <c r="E399" t="n">
-        <v>34.06740079000003</v>
+        <v>161.85019</v>
       </c>
       <c r="F399" t="n">
         <v>2</v>
@@ -14028,7 +14028,7 @@
         <v>1016728.6585</v>
       </c>
       <c r="E400" t="n">
-        <v>10.167286585</v>
+        <v>27.36499</v>
       </c>
       <c r="F400" t="n">
         <v>2</v>
@@ -14062,7 +14062,7 @@
         <v>2341837.124</v>
       </c>
       <c r="E401" t="n">
-        <v>23.41837124</v>
+        <v>116.77227</v>
       </c>
       <c r="F401" t="n">
         <v>2</v>
@@ -14096,7 +14096,7 @@
         <v>1563825.086</v>
       </c>
       <c r="E402" t="n">
-        <v>15.63825086</v>
+        <v>75.02567782</v>
       </c>
       <c r="F402" t="n">
         <v>2</v>
@@ -14130,7 +14130,7 @@
         <v>1160600.0615</v>
       </c>
       <c r="E403" t="n">
-        <v>11.606000615</v>
+        <v>59.45515</v>
       </c>
       <c r="F403" t="n">
         <v>2</v>
@@ -14164,7 +14164,7 @@
         <v>2720961.3133</v>
       </c>
       <c r="E404" t="n">
-        <v>27.20961313299999</v>
+        <v>126.89930723</v>
       </c>
       <c r="F404" t="n">
         <v>2</v>
@@ -14198,7 +14198,7 @@
         <v>3797680.675500003</v>
       </c>
       <c r="E405" t="n">
-        <v>37.97680675500003</v>
+        <v>186.60781</v>
       </c>
       <c r="F405" t="n">
         <v>2</v>
@@ -14232,7 +14232,7 @@
         <v>2471004.295000001</v>
       </c>
       <c r="E406" t="n">
-        <v>24.71004295000001</v>
+        <v>118.61613</v>
       </c>
       <c r="F406" t="n">
         <v>2</v>
@@ -14266,7 +14266,7 @@
         <v>2082181.358000001</v>
       </c>
       <c r="E407" t="n">
-        <v>20.82181358000001</v>
+        <v>99.67066999999997</v>
       </c>
       <c r="F407" t="n">
         <v>2</v>
@@ -14300,7 +14300,7 @@
         <v>3301054.925000003</v>
       </c>
       <c r="E408" t="n">
-        <v>33.01054925000003</v>
+        <v>156.26261</v>
       </c>
       <c r="F408" t="n">
         <v>2</v>
@@ -14334,7 +14334,7 @@
         <v>4404935.94</v>
       </c>
       <c r="E409" t="n">
-        <v>44.04935940000001</v>
+        <v>221.48973368</v>
       </c>
       <c r="F409" t="n">
         <v>2</v>
@@ -14368,7 +14368,7 @@
         <v>3861630.355500003</v>
       </c>
       <c r="E410" t="n">
-        <v>38.61630355500003</v>
+        <v>200.46183</v>
       </c>
       <c r="F410" t="n">
         <v>2</v>
@@ -14402,7 +14402,7 @@
         <v>1216311.22</v>
       </c>
       <c r="E411" t="n">
-        <v>12.1631122</v>
+        <v>12.82508</v>
       </c>
       <c r="F411" t="n">
         <v>2</v>
@@ -14436,7 +14436,7 @@
         <v>2042378.651000002</v>
       </c>
       <c r="E412" t="n">
-        <v>20.42378651000002</v>
+        <v>104.69023</v>
       </c>
       <c r="F412" t="n">
         <v>2</v>
@@ -14470,7 +14470,7 @@
         <v>2639104.915500002</v>
       </c>
       <c r="E413" t="n">
-        <v>26.39104915500002</v>
+        <v>131.63062668</v>
       </c>
       <c r="F413" t="n">
         <v>2</v>
@@ -14504,7 +14504,7 @@
         <v>3033895.160000002</v>
       </c>
       <c r="E414" t="n">
-        <v>30.33895160000003</v>
+        <v>136.36787</v>
       </c>
       <c r="F414" t="n">
         <v>2</v>
@@ -14538,7 +14538,7 @@
         <v>1342677.627000001</v>
       </c>
       <c r="E415" t="n">
-        <v>13.42677627</v>
+        <v>57.31582</v>
       </c>
       <c r="F415" t="n">
         <v>2</v>
@@ -14572,7 +14572,7 @@
         <v>1214965.66</v>
       </c>
       <c r="E416" t="n">
-        <v>12.1496566</v>
+        <v>53.89304</v>
       </c>
       <c r="F416" t="n">
         <v>2</v>
@@ -14606,7 +14606,7 @@
         <v>1632371.630000001</v>
       </c>
       <c r="E417" t="n">
-        <v>16.32371630000001</v>
+        <v>65.84545999999999</v>
       </c>
       <c r="F417" t="n">
         <v>2</v>
@@ -14640,7 +14640,7 @@
         <v>1275344.0775</v>
       </c>
       <c r="E418" t="n">
-        <v>12.753440775</v>
+        <v>44.69123999999999</v>
       </c>
       <c r="F418" t="n">
         <v>1</v>
@@ -14674,7 +14674,7 @@
         <v>634119.7499999998</v>
       </c>
       <c r="E419" t="n">
-        <v>6.341197499999998</v>
+        <v>26.44715</v>
       </c>
       <c r="F419" t="n">
         <v>2</v>
@@ -14708,7 +14708,7 @@
         <v>1031505.06</v>
       </c>
       <c r="E420" t="n">
-        <v>10.3150506</v>
+        <v>30.97999</v>
       </c>
       <c r="F420" t="n">
         <v>1</v>
@@ -14742,7 +14742,7 @@
         <v>922642.7100000001</v>
       </c>
       <c r="E421" t="n">
-        <v>9.2264271</v>
+        <v>38.67852</v>
       </c>
       <c r="F421" t="n">
         <v>1</v>
@@ -14776,7 +14776,7 @@
         <v>545074.1199999999</v>
       </c>
       <c r="E422" t="n">
-        <v>5.450741199999999</v>
+        <v>22.78917</v>
       </c>
       <c r="F422" t="n">
         <v>1</v>
@@ -14810,7 +14810,7 @@
         <v>811226.9000000003</v>
       </c>
       <c r="E423" t="n">
-        <v>8.112269000000003</v>
+        <v>35.23107055</v>
       </c>
       <c r="F423" t="n">
         <v>2</v>
@@ -14844,7 +14844,7 @@
         <v>2614906.190700001</v>
       </c>
       <c r="E424" t="n">
-        <v>26.14906190700001</v>
+        <v>125.73253</v>
       </c>
       <c r="F424" t="n">
         <v>1</v>
@@ -14878,7 +14878,7 @@
         <v>2536014.777500001</v>
       </c>
       <c r="E425" t="n">
-        <v>25.36014777500001</v>
+        <v>130.00548581</v>
       </c>
       <c r="F425" t="n">
         <v>2</v>
@@ -14912,7 +14912,7 @@
         <v>2388020.305</v>
       </c>
       <c r="E426" t="n">
-        <v>23.88020305</v>
+        <v>144.26477</v>
       </c>
       <c r="F426" t="n">
         <v>1</v>
@@ -14946,7 +14946,7 @@
         <v>2184359.044000001</v>
       </c>
       <c r="E427" t="n">
-        <v>21.84359044000001</v>
+        <v>109.89436</v>
       </c>
       <c r="F427" t="n">
         <v>1</v>
@@ -14980,7 +14980,7 @@
         <v>1911937.5875</v>
       </c>
       <c r="E428" t="n">
-        <v>19.119375875</v>
+        <v>108.37224</v>
       </c>
       <c r="F428" t="n">
         <v>2</v>
@@ -15014,7 +15014,7 @@
         <v>2440277.904500001</v>
       </c>
       <c r="E429" t="n">
-        <v>24.40277904500001</v>
+        <v>120.83489913</v>
       </c>
       <c r="F429" t="n">
         <v>2</v>
@@ -15048,7 +15048,7 @@
         <v>2204281.320500001</v>
       </c>
       <c r="E430" t="n">
-        <v>22.04281320500001</v>
+        <v>98.41355000000001</v>
       </c>
       <c r="F430" t="n">
         <v>2</v>
@@ -15082,7 +15082,7 @@
         <v>4040775.354500001</v>
       </c>
       <c r="E431" t="n">
-        <v>40.40775354500001</v>
+        <v>192.78007139</v>
       </c>
       <c r="F431" t="n">
         <v>2</v>
@@ -15116,7 +15116,7 @@
         <v>1689274.980000001</v>
       </c>
       <c r="E432" t="n">
-        <v>16.89274980000001</v>
+        <v>49.8474</v>
       </c>
       <c r="F432" t="n">
         <v>0</v>
@@ -15150,7 +15150,7 @@
         <v>1433551.739</v>
       </c>
       <c r="E433" t="n">
-        <v>14.33551739</v>
+        <v>56.77137180999998</v>
       </c>
       <c r="F433" t="n">
         <v>1</v>
@@ -15184,7 +15184,7 @@
         <v>2844615.976500002</v>
       </c>
       <c r="E434" t="n">
-        <v>28.44615976500002</v>
+        <v>138.73463</v>
       </c>
       <c r="F434" t="n">
         <v>1</v>
@@ -15218,7 +15218,7 @@
         <v>2076841.306000001</v>
       </c>
       <c r="E435" t="n">
-        <v>20.76841306000001</v>
+        <v>79.70254</v>
       </c>
       <c r="F435" t="n">
         <v>2</v>
@@ -15252,7 +15252,7 @@
         <v>2050618.087500001</v>
       </c>
       <c r="E436" t="n">
-        <v>20.50618087500001</v>
+        <v>79.38280632999999</v>
       </c>
       <c r="F436" t="n">
         <v>2</v>
@@ -15286,7 +15286,7 @@
         <v>1114677.0405</v>
       </c>
       <c r="E437" t="n">
-        <v>11.146770405</v>
+        <v>52.55348000000001</v>
       </c>
       <c r="F437" t="n">
         <v>2</v>
@@ -15320,7 +15320,7 @@
         <v>2193854.747500001</v>
       </c>
       <c r="E438" t="n">
-        <v>21.93854747500001</v>
+        <v>99.50590866000003</v>
       </c>
       <c r="F438" t="n">
         <v>2</v>
@@ -15354,7 +15354,7 @@
         <v>1578643.96</v>
       </c>
       <c r="E439" t="n">
-        <v>15.7864396</v>
+        <v>95.54351964</v>
       </c>
       <c r="F439" t="n">
         <v>1</v>
@@ -15388,7 +15388,7 @@
         <v>1724019.120000001</v>
       </c>
       <c r="E440" t="n">
-        <v>17.24019120000001</v>
+        <v>79.42373506000001</v>
       </c>
       <c r="F440" t="n">
         <v>1</v>
@@ -15422,7 +15422,7 @@
         <v>1203341.29</v>
       </c>
       <c r="E441" t="n">
-        <v>12.0334129</v>
+        <v>72.21539426</v>
       </c>
       <c r="F441" t="n">
         <v>2</v>
@@ -15456,7 +15456,7 @@
         <v>1491008.16</v>
       </c>
       <c r="E442" t="n">
-        <v>14.9100816</v>
+        <v>78.73100000000001</v>
       </c>
       <c r="F442" t="n">
         <v>2</v>
@@ -15490,7 +15490,7 @@
         <v>1236907.83</v>
       </c>
       <c r="E443" t="n">
-        <v>12.3690783</v>
+        <v>49.06175000000001</v>
       </c>
       <c r="F443" t="n">
         <v>2</v>
@@ -15524,7 +15524,7 @@
         <v>1726951.994300001</v>
       </c>
       <c r="E444" t="n">
-        <v>17.26951994300001</v>
+        <v>86.38211000000001</v>
       </c>
       <c r="F444" t="n">
         <v>1</v>
@@ -15558,7 +15558,7 @@
         <v>1640981.4175</v>
       </c>
       <c r="E445" t="n">
-        <v>16.409814175</v>
+        <v>90.25793999999999</v>
       </c>
       <c r="F445" t="n">
         <v>1</v>
@@ -15592,7 +15592,7 @@
         <v>2956314.326500003</v>
       </c>
       <c r="E446" t="n">
-        <v>29.56314326500003</v>
+        <v>142.70429</v>
       </c>
       <c r="F446" t="n">
         <v>1</v>
@@ -15626,7 +15626,7 @@
         <v>1854085.535</v>
       </c>
       <c r="E447" t="n">
-        <v>18.54085535</v>
+        <v>96.81982000000001</v>
       </c>
       <c r="F447" t="n">
         <v>2</v>
@@ -15660,7 +15660,7 @@
         <v>2314473.947300002</v>
       </c>
       <c r="E448" t="n">
-        <v>23.14473947300002</v>
+        <v>119.03817194</v>
       </c>
       <c r="F448" t="n">
         <v>1</v>
@@ -15694,7 +15694,7 @@
         <v>2108205.178200001</v>
       </c>
       <c r="E449" t="n">
-        <v>21.08205178200001</v>
+        <v>88.97014999999999</v>
       </c>
       <c r="F449" t="n">
         <v>2</v>
@@ -15728,7 +15728,7 @@
         <v>1847721.835</v>
       </c>
       <c r="E450" t="n">
-        <v>18.47721835</v>
+        <v>81.9524</v>
       </c>
       <c r="F450" t="n">
         <v>0</v>
@@ -15762,7 +15762,7 @@
         <v>2218358.0795</v>
       </c>
       <c r="E451" t="n">
-        <v>22.183580795</v>
+        <v>129.72508</v>
       </c>
       <c r="F451" t="n">
         <v>1</v>
@@ -15796,7 +15796,7 @@
         <v>2005536.772500001</v>
       </c>
       <c r="E452" t="n">
-        <v>20.05536772500001</v>
+        <v>97.62965</v>
       </c>
       <c r="F452" t="n">
         <v>2</v>
@@ -15830,7 +15830,7 @@
         <v>2911461.178500001</v>
       </c>
       <c r="E453" t="n">
-        <v>29.11461178500001</v>
+        <v>137.67475</v>
       </c>
       <c r="F453" t="n">
         <v>1</v>
@@ -15864,7 +15864,7 @@
         <v>1831730.210000001</v>
       </c>
       <c r="E454" t="n">
-        <v>18.31730210000001</v>
+        <v>91.25033126999999</v>
       </c>
       <c r="F454" t="n">
         <v>1</v>
@@ -15898,7 +15898,7 @@
         <v>2892069.121000002</v>
       </c>
       <c r="E455" t="n">
-        <v>28.92069121000002</v>
+        <v>114.76295</v>
       </c>
       <c r="F455" t="n">
         <v>2</v>
@@ -15932,7 +15932,7 @@
         <v>3794266.969000004</v>
       </c>
       <c r="E456" t="n">
-        <v>37.94266969000005</v>
+        <v>182.79795222</v>
       </c>
       <c r="F456" t="n">
         <v>2</v>
@@ -15966,7 +15966,7 @@
         <v>977756.6500000004</v>
       </c>
       <c r="E457" t="n">
-        <v>9.777566500000004</v>
+        <v>33.4468</v>
       </c>
       <c r="F457" t="n">
         <v>1</v>
@@ -16000,7 +16000,7 @@
         <v>2482872.962000001</v>
       </c>
       <c r="E458" t="n">
-        <v>24.82872962000001</v>
+        <v>124.24486528</v>
       </c>
       <c r="F458" t="n">
         <v>1</v>
@@ -16034,7 +16034,7 @@
         <v>1777222.780000001</v>
       </c>
       <c r="E459" t="n">
-        <v>17.77222780000001</v>
+        <v>99.37579999999998</v>
       </c>
       <c r="F459" t="n">
         <v>1</v>
@@ -16068,7 +16068,7 @@
         <v>2597479.14</v>
       </c>
       <c r="E460" t="n">
-        <v>25.9747914</v>
+        <v>97.32721341</v>
       </c>
       <c r="F460" t="n">
         <v>2</v>
@@ -16102,7 +16102,7 @@
         <v>1710562.996200001</v>
       </c>
       <c r="E461" t="n">
-        <v>17.10562996200001</v>
+        <v>73.07991107000001</v>
       </c>
       <c r="F461" t="n">
         <v>2</v>
@@ -16136,7 +16136,7 @@
         <v>2817933.042500003</v>
       </c>
       <c r="E462" t="n">
-        <v>28.17933042500003</v>
+        <v>130.30602041</v>
       </c>
       <c r="F462" t="n">
         <v>2</v>
@@ -16170,7 +16170,7 @@
         <v>3981385.977300005</v>
       </c>
       <c r="E463" t="n">
-        <v>39.81385977300005</v>
+        <v>187.41045626</v>
       </c>
       <c r="F463" t="n">
         <v>2</v>
@@ -16204,7 +16204,7 @@
         <v>2684764.775000002</v>
       </c>
       <c r="E464" t="n">
-        <v>26.84764775000002</v>
+        <v>121.20383</v>
       </c>
       <c r="F464" t="n">
         <v>2</v>
@@ -16238,7 +16238,7 @@
         <v>2353813.055000002</v>
       </c>
       <c r="E465" t="n">
-        <v>23.53813055000002</v>
+        <v>97.37148000000001</v>
       </c>
       <c r="F465" t="n">
         <v>1</v>
@@ -16272,7 +16272,7 @@
         <v>2799099.028000001</v>
       </c>
       <c r="E466" t="n">
-        <v>27.99099028000001</v>
+        <v>130.5938</v>
       </c>
       <c r="F466" t="n">
         <v>1</v>
@@ -16306,7 +16306,7 @@
         <v>1077107.32</v>
       </c>
       <c r="E467" t="n">
-        <v>10.7710732</v>
+        <v>38.55294999999999</v>
       </c>
       <c r="F467" t="n">
         <v>2</v>
@@ -16340,7 +16340,7 @@
         <v>2623571.183500001</v>
       </c>
       <c r="E468" t="n">
-        <v>26.23571183500001</v>
+        <v>125.94</v>
       </c>
       <c r="F468" t="n">
         <v>2</v>
@@ -16374,7 +16374,7 @@
         <v>3055036.036500002</v>
       </c>
       <c r="E469" t="n">
-        <v>30.55036036500002</v>
+        <v>124.82256731</v>
       </c>
       <c r="F469" t="n">
         <v>2</v>
@@ -16408,7 +16408,7 @@
         <v>2608736.803000001</v>
       </c>
       <c r="E470" t="n">
-        <v>26.08736803000001</v>
+        <v>123.36434</v>
       </c>
       <c r="F470" t="n">
         <v>1</v>
@@ -16442,7 +16442,7 @@
         <v>3350672.514500002</v>
       </c>
       <c r="E471" t="n">
-        <v>33.50672514500002</v>
+        <v>173.58828</v>
       </c>
       <c r="F471" t="n">
         <v>1</v>
@@ -16476,7 +16476,7 @@
         <v>2731275.295000002</v>
       </c>
       <c r="E472" t="n">
-        <v>27.31275295000002</v>
+        <v>131.28461</v>
       </c>
       <c r="F472" t="n">
         <v>2</v>
@@ -16510,7 +16510,7 @@
         <v>2036445.641500001</v>
       </c>
       <c r="E473" t="n">
-        <v>20.36445641500001</v>
+        <v>98.05121718000002</v>
       </c>
       <c r="F473" t="n">
         <v>2</v>
@@ -16544,7 +16544,7 @@
         <v>3621469.205</v>
       </c>
       <c r="E474" t="n">
-        <v>36.21469205</v>
+        <v>156.22850862</v>
       </c>
       <c r="F474" t="n">
         <v>1</v>
@@ -16578,7 +16578,7 @@
         <v>1985922.419500001</v>
       </c>
       <c r="E475" t="n">
-        <v>19.85922419500001</v>
+        <v>108.78155</v>
       </c>
       <c r="F475" t="n">
         <v>2</v>
@@ -16612,7 +16612,7 @@
         <v>2817383.850000001</v>
       </c>
       <c r="E476" t="n">
-        <v>28.17383850000001</v>
+        <v>147.33710398</v>
       </c>
       <c r="F476" t="n">
         <v>1</v>
@@ -16646,7 +16646,7 @@
         <v>3770279.758500002</v>
       </c>
       <c r="E477" t="n">
-        <v>37.70279758500002</v>
+        <v>191.04122</v>
       </c>
       <c r="F477" t="n">
         <v>2</v>
@@ -16680,7 +16680,7 @@
         <v>2691775.685000001</v>
       </c>
       <c r="E478" t="n">
-        <v>26.91775685000001</v>
+        <v>115.35392</v>
       </c>
       <c r="F478" t="n">
         <v>1</v>
@@ -16714,7 +16714,7 @@
         <v>2738998.049000001</v>
       </c>
       <c r="E479" t="n">
-        <v>27.38998049000001</v>
+        <v>125.61114</v>
       </c>
       <c r="F479" t="n">
         <v>2</v>
@@ -16748,7 +16748,7 @@
         <v>2409181.429000001</v>
       </c>
       <c r="E480" t="n">
-        <v>24.09181429000001</v>
+        <v>142.23318404</v>
       </c>
       <c r="F480" t="n">
         <v>2</v>
@@ -16782,7 +16782,7 @@
         <v>1999649.923</v>
       </c>
       <c r="E481" t="n">
-        <v>19.99649923</v>
+        <v>90.83478997000002</v>
       </c>
       <c r="F481" t="n">
         <v>2</v>
@@ -16816,7 +16816,7 @@
         <v>2980331.4155</v>
       </c>
       <c r="E482" t="n">
-        <v>29.803314155</v>
+        <v>133.14993041</v>
       </c>
       <c r="F482" t="n">
         <v>1</v>
@@ -16850,7 +16850,7 @@
         <v>2758237.745500001</v>
       </c>
       <c r="E483" t="n">
-        <v>27.58237745500001</v>
+        <v>127.76054</v>
       </c>
       <c r="F483" t="n">
         <v>2</v>
@@ -16884,7 +16884,7 @@
         <v>2246760.495500001</v>
       </c>
       <c r="E484" t="n">
-        <v>22.46760495500001</v>
+        <v>109.79968</v>
       </c>
       <c r="F484" t="n">
         <v>2</v>
@@ -16918,7 +16918,7 @@
         <v>2429311.9565</v>
       </c>
       <c r="E485" t="n">
-        <v>24.293119565</v>
+        <v>131.96288887</v>
       </c>
       <c r="F485" t="n">
         <v>2</v>
@@ -16952,7 +16952,7 @@
         <v>3362983.078800001</v>
       </c>
       <c r="E486" t="n">
-        <v>33.62983078800001</v>
+        <v>175.2077001</v>
       </c>
       <c r="F486" t="n">
         <v>1</v>
@@ -16986,7 +16986,7 @@
         <v>3326372.536000001</v>
       </c>
       <c r="E487" t="n">
-        <v>33.26372536000001</v>
+        <v>168.87164</v>
       </c>
       <c r="F487" t="n">
         <v>1</v>
@@ -17020,7 +17020,7 @@
         <v>1905680.402900001</v>
       </c>
       <c r="E488" t="n">
-        <v>19.05680402900001</v>
+        <v>66.75664999999999</v>
       </c>
       <c r="F488" t="n">
         <v>0</v>
@@ -17054,7 +17054,7 @@
         <v>1987915.005000001</v>
       </c>
       <c r="E489" t="n">
-        <v>19.87915005000001</v>
+        <v>126.85732686</v>
       </c>
       <c r="F489" t="n">
         <v>2</v>
@@ -17088,7 +17088,7 @@
         <v>2523601.694000001</v>
       </c>
       <c r="E490" t="n">
-        <v>25.23601694000001</v>
+        <v>115.03028</v>
       </c>
       <c r="F490" t="n">
         <v>2</v>
@@ -17122,7 +17122,7 @@
         <v>2238605.415000001</v>
       </c>
       <c r="E491" t="n">
-        <v>22.38605415000001</v>
+        <v>89.62715</v>
       </c>
       <c r="F491" t="n">
         <v>0</v>
@@ -17156,7 +17156,7 @@
         <v>1037505.4415</v>
       </c>
       <c r="E492" t="n">
-        <v>10.375054415</v>
+        <v>43.78264999999999</v>
       </c>
       <c r="F492" t="n">
         <v>1</v>
@@ -17190,7 +17190,7 @@
         <v>1193390.5225</v>
       </c>
       <c r="E493" t="n">
-        <v>11.933905225</v>
+        <v>60.0933</v>
       </c>
       <c r="F493" t="n">
         <v>2</v>
@@ -17224,7 +17224,7 @@
         <v>1680634.2675</v>
       </c>
       <c r="E494" t="n">
-        <v>16.806342675</v>
+        <v>76.39164923000001</v>
       </c>
       <c r="F494" t="n">
         <v>2</v>
@@ -17258,7 +17258,7 @@
         <v>1121915.015</v>
       </c>
       <c r="E495" t="n">
-        <v>11.21915015</v>
+        <v>54.11192668</v>
       </c>
       <c r="F495" t="n">
         <v>2</v>
@@ -17292,7 +17292,7 @@
         <v>1450741.65</v>
       </c>
       <c r="E496" t="n">
-        <v>14.5074165</v>
+        <v>59.60680000000001</v>
       </c>
       <c r="F496" t="n">
         <v>2</v>
@@ -17326,7 +17326,7 @@
         <v>1271516.12</v>
       </c>
       <c r="E497" t="n">
-        <v>12.7151612</v>
+        <v>61.33865</v>
       </c>
       <c r="F497" t="n">
         <v>1</v>
@@ -17360,7 +17360,7 @@
         <v>1946250.850000001</v>
       </c>
       <c r="E498" t="n">
-        <v>19.46250850000001</v>
+        <v>64.45888206000001</v>
       </c>
       <c r="F498" t="n">
         <v>2</v>
@@ -17394,7 +17394,7 @@
         <v>1299609.49</v>
       </c>
       <c r="E499" t="n">
-        <v>12.9960949</v>
+        <v>63.66179793000001</v>
       </c>
       <c r="F499" t="n">
         <v>2</v>
@@ -17428,7 +17428,7 @@
         <v>1642734.55</v>
       </c>
       <c r="E500" t="n">
-        <v>16.4273455</v>
+        <v>97.11096000000002</v>
       </c>
       <c r="F500" t="n">
         <v>1</v>
@@ -17462,7 +17462,7 @@
         <v>1551189.41</v>
       </c>
       <c r="E501" t="n">
-        <v>15.5118941</v>
+        <v>77.12655000000001</v>
       </c>
       <c r="F501" t="n">
         <v>1</v>
@@ -17496,7 +17496,7 @@
         <v>1214165.6235</v>
       </c>
       <c r="E502" t="n">
-        <v>12.141656235</v>
+        <v>63.69543999999999</v>
       </c>
       <c r="F502" t="n">
         <v>2</v>
@@ -17530,7 +17530,7 @@
         <v>848792.5400000004</v>
       </c>
       <c r="E503" t="n">
-        <v>8.487925400000004</v>
+        <v>39.40545</v>
       </c>
       <c r="F503" t="n">
         <v>1</v>
@@ -17564,7 +17564,7 @@
         <v>1843681.18</v>
       </c>
       <c r="E504" t="n">
-        <v>18.4368118</v>
+        <v>51.32812</v>
       </c>
       <c r="F504" t="n">
         <v>1</v>
@@ -17598,7 +17598,7 @@
         <v>1209168.48</v>
       </c>
       <c r="E505" t="n">
-        <v>12.0916848</v>
+        <v>48.43592</v>
       </c>
       <c r="F505" t="n">
         <v>2</v>

--- a/clustered_output.xlsx
+++ b/clustered_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J505"/>
+  <dimension ref="A1:I505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,11 +474,6 @@
           <t>distance_km</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>weighted_distance</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -510,9 +505,6 @@
       <c r="I2" t="n">
         <v>330.9635282855404</v>
       </c>
-      <c r="J2" t="n">
-        <v>460473276.9337305</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,9 +536,6 @@
       <c r="I3" t="n">
         <v>117.9924090723754</v>
       </c>
-      <c r="J3" t="n">
-        <v>223479441.0461029</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -578,9 +567,6 @@
       <c r="I4" t="n">
         <v>426.9669887847988</v>
       </c>
-      <c r="J4" t="n">
-        <v>344215387.3607316</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -612,9 +598,6 @@
       <c r="I5" t="n">
         <v>121.6518811104223</v>
       </c>
-      <c r="J5" t="n">
-        <v>1216518.811104223</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -646,9 +629,6 @@
       <c r="I6" t="n">
         <v>420.4712712853633</v>
       </c>
-      <c r="J6" t="n">
-        <v>658399645.215712</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -680,9 +660,6 @@
       <c r="I7" t="n">
         <v>108.1103102442499</v>
       </c>
-      <c r="J7" t="n">
-        <v>125383952.907837</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -714,9 +691,6 @@
       <c r="I8" t="n">
         <v>236.9722186769305</v>
       </c>
-      <c r="J8" t="n">
-        <v>465380396.4450415</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -748,9 +722,6 @@
       <c r="I9" t="n">
         <v>295.3716828864031</v>
       </c>
-      <c r="J9" t="n">
-        <v>603125005.5651108</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -782,9 +753,6 @@
       <c r="I10" t="n">
         <v>495.1232190037021</v>
       </c>
-      <c r="J10" t="n">
-        <v>1214858924.15558</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -816,9 +784,6 @@
       <c r="I11" t="n">
         <v>492.2082518359087</v>
       </c>
-      <c r="J11" t="n">
-        <v>1252869556.91393</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -850,9 +815,6 @@
       <c r="I12" t="n">
         <v>128.9441347688719</v>
       </c>
-      <c r="J12" t="n">
-        <v>309963338.3395771</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -884,9 +846,6 @@
       <c r="I13" t="n">
         <v>130.2855787087994</v>
       </c>
-      <c r="J13" t="n">
-        <v>200158155.3927479</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -918,9 +877,6 @@
       <c r="I14" t="n">
         <v>146.4901253335264</v>
       </c>
-      <c r="J14" t="n">
-        <v>423243950.4731287</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -952,9 +908,6 @@
       <c r="I15" t="n">
         <v>453.1047927312811</v>
       </c>
-      <c r="J15" t="n">
-        <v>800123838.6359847</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -986,9 +939,6 @@
       <c r="I16" t="n">
         <v>401.849670130051</v>
       </c>
-      <c r="J16" t="n">
-        <v>919019179.2805699</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1020,9 +970,6 @@
       <c r="I17" t="n">
         <v>128.5054911990155</v>
       </c>
-      <c r="J17" t="n">
-        <v>231257492.5979716</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1054,9 +1001,6 @@
       <c r="I18" t="n">
         <v>179.8330479062113</v>
       </c>
-      <c r="J18" t="n">
-        <v>500089002.8178904</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1088,9 +1032,6 @@
       <c r="I19" t="n">
         <v>130.5207868271966</v>
       </c>
-      <c r="J19" t="n">
-        <v>269967853.7196849</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1122,9 +1063,6 @@
       <c r="I20" t="n">
         <v>170.3468154702016</v>
       </c>
-      <c r="J20" t="n">
-        <v>268825300.9119912</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1156,9 +1094,6 @@
       <c r="I21" t="n">
         <v>147.6369671603444</v>
       </c>
-      <c r="J21" t="n">
-        <v>293353410.644341</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1190,9 +1125,6 @@
       <c r="I22" t="n">
         <v>276.1174878980499</v>
       </c>
-      <c r="J22" t="n">
-        <v>451385194.9683438</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1224,9 +1156,6 @@
       <c r="I23" t="n">
         <v>465.5664978287974</v>
       </c>
-      <c r="J23" t="n">
-        <v>831961530.6614984</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1258,9 +1187,6 @@
       <c r="I24" t="n">
         <v>20.47034300213973</v>
       </c>
-      <c r="J24" t="n">
-        <v>30551596.15184564</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1292,9 +1218,6 @@
       <c r="I25" t="n">
         <v>440.6263987667413</v>
       </c>
-      <c r="J25" t="n">
-        <v>735399044.0213252</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1326,9 +1249,6 @@
       <c r="I26" t="n">
         <v>287.0633257945925</v>
       </c>
-      <c r="J26" t="n">
-        <v>555604249.3214462</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1360,9 +1280,6 @@
       <c r="I27" t="n">
         <v>137.5875559259532</v>
       </c>
-      <c r="J27" t="n">
-        <v>349396609.9956116</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1394,9 +1311,6 @@
       <c r="I28" t="n">
         <v>437.5011742973805</v>
       </c>
-      <c r="J28" t="n">
-        <v>688874806.5096216</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1428,9 +1342,6 @@
       <c r="I29" t="n">
         <v>86.28571933028022</v>
       </c>
-      <c r="J29" t="n">
-        <v>103531758.2242584</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1462,9 +1373,6 @@
       <c r="I30" t="n">
         <v>285.2711516650368</v>
       </c>
-      <c r="J30" t="n">
-        <v>745142292.0478731</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1496,9 +1404,6 @@
       <c r="I31" t="n">
         <v>137.8003887622026</v>
       </c>
-      <c r="J31" t="n">
-        <v>238260377.8117385</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1530,9 +1435,6 @@
       <c r="I32" t="n">
         <v>139.3399391111659</v>
       </c>
-      <c r="J32" t="n">
-        <v>483759581.984004</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1564,9 +1466,6 @@
       <c r="I33" t="n">
         <v>446.4715004339711</v>
       </c>
-      <c r="J33" t="n">
-        <v>1076056152.156359</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1598,9 +1497,6 @@
       <c r="I34" t="n">
         <v>137.0910817780116</v>
       </c>
-      <c r="J34" t="n">
-        <v>111735530.9842872</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1632,9 +1528,6 @@
       <c r="I35" t="n">
         <v>137.1927821035483</v>
       </c>
-      <c r="J35" t="n">
-        <v>259585992.0280579</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1666,9 +1559,6 @@
       <c r="I36" t="n">
         <v>495.716185770717</v>
       </c>
-      <c r="J36" t="n">
-        <v>1162573105.301396</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1700,9 +1590,6 @@
       <c r="I37" t="n">
         <v>20.19869826917071</v>
       </c>
-      <c r="J37" t="n">
-        <v>43200376.05775722</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1734,9 +1621,6 @@
       <c r="I38" t="n">
         <v>132.5567661736015</v>
       </c>
-      <c r="J38" t="n">
-        <v>251274025.161208</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1768,9 +1652,6 @@
       <c r="I39" t="n">
         <v>432.38924585193</v>
       </c>
-      <c r="J39" t="n">
-        <v>1493860431.557032</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1802,9 +1683,6 @@
       <c r="I40" t="n">
         <v>275.726143177566</v>
       </c>
-      <c r="J40" t="n">
-        <v>663505921.322152</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1836,9 +1714,6 @@
       <c r="I41" t="n">
         <v>0</v>
       </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1870,9 +1745,6 @@
       <c r="I42" t="n">
         <v>265.3216686549943</v>
       </c>
-      <c r="J42" t="n">
-        <v>460574115.3101339</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1904,9 +1776,6 @@
       <c r="I43" t="n">
         <v>113.2095459182907</v>
       </c>
-      <c r="J43" t="n">
-        <v>267511597.7899261</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1938,9 +1807,6 @@
       <c r="I44" t="n">
         <v>444.1175443051316</v>
       </c>
-      <c r="J44" t="n">
-        <v>799905034.3115389</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1972,9 +1838,6 @@
       <c r="I45" t="n">
         <v>266.6468275894603</v>
       </c>
-      <c r="J45" t="n">
-        <v>405550178.2253124</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2006,9 +1869,6 @@
       <c r="I46" t="n">
         <v>407.277294246931</v>
       </c>
-      <c r="J46" t="n">
-        <v>467776548.359991</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2040,9 +1900,6 @@
       <c r="I47" t="n">
         <v>413.8102117955148</v>
       </c>
-      <c r="J47" t="n">
-        <v>350130816.3101541</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2074,9 +1931,6 @@
       <c r="I48" t="n">
         <v>122.8011678761479</v>
       </c>
-      <c r="J48" t="n">
-        <v>258776419.8678095</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2108,9 +1962,6 @@
       <c r="I49" t="n">
         <v>442.4265618572776</v>
       </c>
-      <c r="J49" t="n">
-        <v>977177866.8809961</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2142,9 +1993,6 @@
       <c r="I50" t="n">
         <v>494.2392037869573</v>
       </c>
-      <c r="J50" t="n">
-        <v>781930190.214854</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2176,9 +2024,6 @@
       <c r="I51" t="n">
         <v>235.567208404973</v>
       </c>
-      <c r="J51" t="n">
-        <v>376109241.8787109</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2210,9 +2055,6 @@
       <c r="I52" t="n">
         <v>127.9311147058719</v>
       </c>
-      <c r="J52" t="n">
-        <v>218026134.0096025</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2244,9 +2086,6 @@
       <c r="I53" t="n">
         <v>85.96947799636601</v>
       </c>
-      <c r="J53" t="n">
-        <v>159923046.3274612</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2278,9 +2117,6 @@
       <c r="I54" t="n">
         <v>118.4108809723095</v>
       </c>
-      <c r="J54" t="n">
-        <v>216437891.2369206</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2312,9 +2148,6 @@
       <c r="I55" t="n">
         <v>141.7811728221151</v>
       </c>
-      <c r="J55" t="n">
-        <v>349344275.6717849</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2346,9 +2179,6 @@
       <c r="I56" t="n">
         <v>490.0243432034919</v>
       </c>
-      <c r="J56" t="n">
-        <v>667842416.7678022</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2380,9 +2210,6 @@
       <c r="I57" t="n">
         <v>392.1441159670266</v>
       </c>
-      <c r="J57" t="n">
-        <v>999580994.5537798</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2414,9 +2241,6 @@
       <c r="I58" t="n">
         <v>124.8455044460658</v>
       </c>
-      <c r="J58" t="n">
-        <v>153260531.0231571</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2448,9 +2272,6 @@
       <c r="I59" t="n">
         <v>145.9883362263176</v>
       </c>
-      <c r="J59" t="n">
-        <v>325108486.6682684</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2482,9 +2303,6 @@
       <c r="I60" t="n">
         <v>133.1781377095647</v>
       </c>
-      <c r="J60" t="n">
-        <v>207503571.196244</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2516,9 +2334,6 @@
       <c r="I61" t="n">
         <v>132.4012953218188</v>
       </c>
-      <c r="J61" t="n">
-        <v>505427488.9866171</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2550,9 +2365,6 @@
       <c r="I62" t="n">
         <v>123.0549928591128</v>
       </c>
-      <c r="J62" t="n">
-        <v>257277599.1768185</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2584,9 +2396,6 @@
       <c r="I63" t="n">
         <v>440.5761630353377</v>
       </c>
-      <c r="J63" t="n">
-        <v>458828290.6369029</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2618,9 +2427,6 @@
       <c r="I64" t="n">
         <v>237.0082605430272</v>
       </c>
-      <c r="J64" t="n">
-        <v>220567739.3450129</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2652,9 +2458,6 @@
       <c r="I65" t="n">
         <v>112.1216799225184</v>
       </c>
-      <c r="J65" t="n">
-        <v>358357241.9793857</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2686,9 +2489,6 @@
       <c r="I66" t="n">
         <v>290.2997824974207</v>
       </c>
-      <c r="J66" t="n">
-        <v>258616339.4067457</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2720,9 +2520,6 @@
       <c r="I67" t="n">
         <v>120.0711060212944</v>
       </c>
-      <c r="J67" t="n">
-        <v>177023326.4446352</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2754,9 +2551,6 @@
       <c r="I68" t="n">
         <v>95.52643598416643</v>
       </c>
-      <c r="J68" t="n">
-        <v>110241519.2360394</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2788,9 +2582,6 @@
       <c r="I69" t="n">
         <v>20.41596783227257</v>
       </c>
-      <c r="J69" t="n">
-        <v>30923656.72706887</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2822,9 +2613,6 @@
       <c r="I70" t="n">
         <v>134.7397854755224</v>
       </c>
-      <c r="J70" t="n">
-        <v>180469386.7054374</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2856,9 +2644,6 @@
       <c r="I71" t="n">
         <v>124.8455044460658</v>
       </c>
-      <c r="J71" t="n">
-        <v>26811661.98104644</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2890,9 +2675,6 @@
       <c r="I72" t="n">
         <v>126.3772556143692</v>
       </c>
-      <c r="J72" t="n">
-        <v>209302432.3765256</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2924,9 +2706,6 @@
       <c r="I73" t="n">
         <v>449.7586404666938</v>
       </c>
-      <c r="J73" t="n">
-        <v>617149946.20318</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2958,9 +2737,6 @@
       <c r="I74" t="n">
         <v>127.1359911457164</v>
       </c>
-      <c r="J74" t="n">
-        <v>382802063.5436879</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2992,9 +2768,6 @@
       <c r="I75" t="n">
         <v>118.9906694931409</v>
       </c>
-      <c r="J75" t="n">
-        <v>285744272.2546705</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3026,9 +2799,6 @@
       <c r="I76" t="n">
         <v>483.7945945807476</v>
       </c>
-      <c r="J76" t="n">
-        <v>460781095.2977307</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3060,9 +2830,6 @@
       <c r="I77" t="n">
         <v>127.0006139161995</v>
       </c>
-      <c r="J77" t="n">
-        <v>372397661.5988148</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3094,9 +2861,6 @@
       <c r="I78" t="n">
         <v>203.6346669013843</v>
       </c>
-      <c r="J78" t="n">
-        <v>229476378.5635972</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3128,9 +2892,6 @@
       <c r="I79" t="n">
         <v>234.5085396974142</v>
       </c>
-      <c r="J79" t="n">
-        <v>398825249.1696959</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3162,9 +2923,6 @@
       <c r="I80" t="n">
         <v>143.7534492312146</v>
       </c>
-      <c r="J80" t="n">
-        <v>306922401.7569948</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3196,9 +2954,6 @@
       <c r="I81" t="n">
         <v>133.7006511831521</v>
       </c>
-      <c r="J81" t="n">
-        <v>440547844.0494847</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3230,9 +2985,6 @@
       <c r="I82" t="n">
         <v>128.6823365844351</v>
       </c>
-      <c r="J82" t="n">
-        <v>302902057.8182853</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3264,9 +3016,6 @@
       <c r="I83" t="n">
         <v>132.6130702067358</v>
       </c>
-      <c r="J83" t="n">
-        <v>513108975.0867074</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3298,9 +3047,6 @@
       <c r="I84" t="n">
         <v>125.6521233991047</v>
       </c>
-      <c r="J84" t="n">
-        <v>384467994.9901433</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3332,9 +3078,6 @@
       <c r="I85" t="n">
         <v>113.4975601647661</v>
       </c>
-      <c r="J85" t="n">
-        <v>317803649.3935389</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3366,9 +3109,6 @@
       <c r="I86" t="n">
         <v>130.2231289710547</v>
       </c>
-      <c r="J86" t="n">
-        <v>545230872.2953863</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3400,9 +3140,6 @@
       <c r="I87" t="n">
         <v>288.7402552400748</v>
       </c>
-      <c r="J87" t="n">
-        <v>905026188.4547702</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3434,9 +3171,6 @@
       <c r="I88" t="n">
         <v>236.5461713897413</v>
       </c>
-      <c r="J88" t="n">
-        <v>715131579.8993905</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3468,9 +3202,6 @@
       <c r="I89" t="n">
         <v>135.6068269194521</v>
       </c>
-      <c r="J89" t="n">
-        <v>501184781.6695638</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3502,9 +3233,6 @@
       <c r="I90" t="n">
         <v>133.4495554787986</v>
       </c>
-      <c r="J90" t="n">
-        <v>238429992.7379862</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3536,9 +3264,6 @@
       <c r="I91" t="n">
         <v>124.0579963162462</v>
       </c>
-      <c r="J91" t="n">
-        <v>450080660.4871586</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3570,9 +3295,6 @@
       <c r="I92" t="n">
         <v>134.3726052010849</v>
       </c>
-      <c r="J92" t="n">
-        <v>529943181.8743134</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3604,9 +3326,6 @@
       <c r="I93" t="n">
         <v>125.8855478394724</v>
       </c>
-      <c r="J93" t="n">
-        <v>328151173.6998383</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3638,9 +3357,6 @@
       <c r="I94" t="n">
         <v>131.7009008617561</v>
       </c>
-      <c r="J94" t="n">
-        <v>249600698.0498216</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3672,9 +3388,6 @@
       <c r="I95" t="n">
         <v>133.9028375627812</v>
       </c>
-      <c r="J95" t="n">
-        <v>308554813.650202</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3706,9 +3419,6 @@
       <c r="I96" t="n">
         <v>133.3419133050184</v>
       </c>
-      <c r="J96" t="n">
-        <v>407963681.6203839</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3740,9 +3450,6 @@
       <c r="I97" t="n">
         <v>136.3714144979849</v>
       </c>
-      <c r="J97" t="n">
-        <v>344735026.535278</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3774,9 +3481,6 @@
       <c r="I98" t="n">
         <v>130.4915498302243</v>
       </c>
-      <c r="J98" t="n">
-        <v>332927518.3339083</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3808,9 +3512,6 @@
       <c r="I99" t="n">
         <v>442.2738823209808</v>
       </c>
-      <c r="J99" t="n">
-        <v>1189558051.151723</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3842,9 +3543,6 @@
       <c r="I100" t="n">
         <v>139.9394903277591</v>
       </c>
-      <c r="J100" t="n">
-        <v>447278351.1831381</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3876,9 +3574,6 @@
       <c r="I101" t="n">
         <v>128.2753586164148</v>
       </c>
-      <c r="J101" t="n">
-        <v>381238686.5068893</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3910,9 +3605,6 @@
       <c r="I102" t="n">
         <v>116.0060286591594</v>
       </c>
-      <c r="J102" t="n">
-        <v>417628149.8251969</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3944,9 +3636,6 @@
       <c r="I103" t="n">
         <v>119.7946518548475</v>
       </c>
-      <c r="J103" t="n">
-        <v>420440986.3231872</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3978,9 +3667,6 @@
       <c r="I104" t="n">
         <v>117.7208691827655</v>
       </c>
-      <c r="J104" t="n">
-        <v>432688771.2066624</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4012,9 +3698,6 @@
       <c r="I105" t="n">
         <v>443.7056571528461</v>
       </c>
-      <c r="J105" t="n">
-        <v>862232776.2240825</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4046,9 +3729,6 @@
       <c r="I106" t="n">
         <v>287.2407268146017</v>
       </c>
-      <c r="J106" t="n">
-        <v>1102383448.32688</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4080,9 +3760,6 @@
       <c r="I107" t="n">
         <v>491.1606421189047</v>
       </c>
-      <c r="J107" t="n">
-        <v>1025818200.565507</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4114,9 +3791,6 @@
       <c r="I108" t="n">
         <v>438.3360268021133</v>
       </c>
-      <c r="J108" t="n">
-        <v>1349474442.193791</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4148,9 +3822,6 @@
       <c r="I109" t="n">
         <v>128.4727129154797</v>
       </c>
-      <c r="J109" t="n">
-        <v>255923482.1846561</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4182,9 +3853,6 @@
       <c r="I110" t="n">
         <v>288.3934749946374</v>
       </c>
-      <c r="J110" t="n">
-        <v>835198322.9540783</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4216,9 +3884,6 @@
       <c r="I111" t="n">
         <v>131.4380690737538</v>
       </c>
-      <c r="J111" t="n">
-        <v>343476101.0609506</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4250,9 +3915,6 @@
       <c r="I112" t="n">
         <v>121.1765276823574</v>
       </c>
-      <c r="J112" t="n">
-        <v>328939752.9142656</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4284,9 +3946,6 @@
       <c r="I113" t="n">
         <v>121.6051186359468</v>
       </c>
-      <c r="J113" t="n">
-        <v>259364154.2189884</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4318,9 +3977,6 @@
       <c r="I114" t="n">
         <v>315.3898871045468</v>
       </c>
-      <c r="J114" t="n">
-        <v>573974879.5654017</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4352,9 +4008,6 @@
       <c r="I115" t="n">
         <v>420.9097798142605</v>
       </c>
-      <c r="J115" t="n">
-        <v>810080222.1078596</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4386,9 +4039,6 @@
       <c r="I116" t="n">
         <v>117.1189359683959</v>
       </c>
-      <c r="J116" t="n">
-        <v>310587492.2011742</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4420,9 +4070,6 @@
       <c r="I117" t="n">
         <v>128.1772702393585</v>
       </c>
-      <c r="J117" t="n">
-        <v>372814174.0883783</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4454,9 +4101,6 @@
       <c r="I118" t="n">
         <v>134.3931990270278</v>
       </c>
-      <c r="J118" t="n">
-        <v>455823778.7962564</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4488,9 +4132,6 @@
       <c r="I119" t="n">
         <v>491.9232670955004</v>
       </c>
-      <c r="J119" t="n">
-        <v>1084000158.436275</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4522,9 +4163,6 @@
       <c r="I120" t="n">
         <v>288.7137580132629</v>
       </c>
-      <c r="J120" t="n">
-        <v>314548335.6837153</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4556,9 +4194,6 @@
       <c r="I121" t="n">
         <v>139.8497216179582</v>
       </c>
-      <c r="J121" t="n">
-        <v>514059237.5899508</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4590,9 +4225,6 @@
       <c r="I122" t="n">
         <v>127.549787869981</v>
       </c>
-      <c r="J122" t="n">
-        <v>201921551.9819033</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4624,9 +4256,6 @@
       <c r="I123" t="n">
         <v>17.16754590109464</v>
       </c>
-      <c r="J123" t="n">
-        <v>42628169.39329808</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4658,9 +4287,6 @@
       <c r="I124" t="n">
         <v>125.9160263320814</v>
       </c>
-      <c r="J124" t="n">
-        <v>304677157.9501505</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4692,9 +4318,6 @@
       <c r="I125" t="n">
         <v>115.1672335283907</v>
       </c>
-      <c r="J125" t="n">
-        <v>414309080.0210657</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4726,9 +4349,6 @@
       <c r="I126" t="n">
         <v>111.8178194902709</v>
       </c>
-      <c r="J126" t="n">
-        <v>210358062.3498779</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4760,9 +4380,6 @@
       <c r="I127" t="n">
         <v>131.1888744670751</v>
       </c>
-      <c r="J127" t="n">
-        <v>251339190.3761932</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4794,9 +4411,6 @@
       <c r="I128" t="n">
         <v>123.935072258068</v>
       </c>
-      <c r="J128" t="n">
-        <v>366726817.0643165</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4828,9 +4442,6 @@
       <c r="I129" t="n">
         <v>131.6487906909689</v>
       </c>
-      <c r="J129" t="n">
-        <v>333970281.1237655</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4862,9 +4473,6 @@
       <c r="I130" t="n">
         <v>130.381237786289</v>
       </c>
-      <c r="J130" t="n">
-        <v>408604553.8645649</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4896,9 +4504,6 @@
       <c r="I131" t="n">
         <v>2.524349787145492</v>
       </c>
-      <c r="J131" t="n">
-        <v>9715273.181513913</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4930,9 +4535,6 @@
       <c r="I132" t="n">
         <v>69.52376245901762</v>
       </c>
-      <c r="J132" t="n">
-        <v>229809247.4712365</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4964,9 +4566,6 @@
       <c r="I133" t="n">
         <v>439.4150303327746</v>
       </c>
-      <c r="J133" t="n">
-        <v>945674999.9822487</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4998,9 +4597,6 @@
       <c r="I134" t="n">
         <v>132.7490468314282</v>
       </c>
-      <c r="J134" t="n">
-        <v>365630783.3197024</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5032,9 +4628,6 @@
       <c r="I135" t="n">
         <v>149.1626153246674</v>
       </c>
-      <c r="J135" t="n">
-        <v>505593910.5275345</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5066,9 +4659,6 @@
       <c r="I136" t="n">
         <v>123.6480037344783</v>
       </c>
-      <c r="J136" t="n">
-        <v>251199372.473248</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5100,9 +4690,6 @@
       <c r="I137" t="n">
         <v>126.8999961435841</v>
       </c>
-      <c r="J137" t="n">
-        <v>259706986.2884083</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5134,9 +4721,6 @@
       <c r="I138" t="n">
         <v>127.3032429697211</v>
       </c>
-      <c r="J138" t="n">
-        <v>353162664.2871966</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5168,9 +4752,6 @@
       <c r="I139" t="n">
         <v>121.1956400146447</v>
       </c>
-      <c r="J139" t="n">
-        <v>439315709.385105</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5202,9 +4783,6 @@
       <c r="I140" t="n">
         <v>436.7912830403555</v>
       </c>
-      <c r="J140" t="n">
-        <v>1258474841.755577</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5236,9 +4814,6 @@
       <c r="I141" t="n">
         <v>135.4344329345909</v>
       </c>
-      <c r="J141" t="n">
-        <v>325472968.9519624</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5270,9 +4845,6 @@
       <c r="I142" t="n">
         <v>280.444170825078</v>
       </c>
-      <c r="J142" t="n">
-        <v>615677964.9094322</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5304,9 +4876,6 @@
       <c r="I143" t="n">
         <v>106.2678263285794</v>
       </c>
-      <c r="J143" t="n">
-        <v>355703659.7065783</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5338,9 +4907,6 @@
       <c r="I144" t="n">
         <v>103.5750652214989</v>
       </c>
-      <c r="J144" t="n">
-        <v>294795614.2319715</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5372,9 +4938,6 @@
       <c r="I145" t="n">
         <v>423.1317561742813</v>
       </c>
-      <c r="J145" t="n">
-        <v>930449599.2224375</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5406,9 +4969,6 @@
       <c r="I146" t="n">
         <v>16.86922051279774</v>
       </c>
-      <c r="J146" t="n">
-        <v>51703374.00693428</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5440,9 +5000,6 @@
       <c r="I147" t="n">
         <v>120.0628786795913</v>
       </c>
-      <c r="J147" t="n">
-        <v>377065258.2518194</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5474,9 +5031,6 @@
       <c r="I148" t="n">
         <v>127.0843658238061</v>
       </c>
-      <c r="J148" t="n">
-        <v>293282386.2551367</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5508,9 +5062,6 @@
       <c r="I149" t="n">
         <v>137.6740764380879</v>
       </c>
-      <c r="J149" t="n">
-        <v>465129936.0229728</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5542,9 +5093,6 @@
       <c r="I150" t="n">
         <v>98.92679672304133</v>
       </c>
-      <c r="J150" t="n">
-        <v>183766226.664004</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5576,9 +5124,6 @@
       <c r="I151" t="n">
         <v>427.5095658720282</v>
       </c>
-      <c r="J151" t="n">
-        <v>720426970.5856801</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5610,9 +5155,6 @@
       <c r="I152" t="n">
         <v>487.5368227657868</v>
       </c>
-      <c r="J152" t="n">
-        <v>893093241.5763921</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5644,9 +5186,6 @@
       <c r="I153" t="n">
         <v>123.5184011830669</v>
       </c>
-      <c r="J153" t="n">
-        <v>403354459.148071</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5678,9 +5217,6 @@
       <c r="I154" t="n">
         <v>2.195284483350534</v>
       </c>
-      <c r="J154" t="n">
-        <v>6125632.408404327</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5712,9 +5248,6 @@
       <c r="I155" t="n">
         <v>115.0570084748459</v>
       </c>
-      <c r="J155" t="n">
-        <v>312975141.0748451</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5746,9 +5279,6 @@
       <c r="I156" t="n">
         <v>126.05341869692</v>
       </c>
-      <c r="J156" t="n">
-        <v>367279772.4784784</v>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5780,9 +5310,6 @@
       <c r="I157" t="n">
         <v>494.1176797046688</v>
       </c>
-      <c r="J157" t="n">
-        <v>1301105688.550946</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5814,9 +5341,6 @@
       <c r="I158" t="n">
         <v>439.6105513810847</v>
       </c>
-      <c r="J158" t="n">
-        <v>765469019.5198357</v>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5848,9 +5372,6 @@
       <c r="I159" t="n">
         <v>141.1308776121495</v>
       </c>
-      <c r="J159" t="n">
-        <v>442322875.9935607</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5882,9 +5403,6 @@
       <c r="I160" t="n">
         <v>286.0952964076756</v>
       </c>
-      <c r="J160" t="n">
-        <v>839564853.9266261</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5916,9 +5434,6 @@
       <c r="I161" t="n">
         <v>128.2123748624244</v>
       </c>
-      <c r="J161" t="n">
-        <v>481986465.3048227</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5950,9 +5465,6 @@
       <c r="I162" t="n">
         <v>137.7535479338831</v>
       </c>
-      <c r="J162" t="n">
-        <v>278433309.079326</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5984,9 +5496,6 @@
       <c r="I163" t="n">
         <v>0</v>
       </c>
-      <c r="J163" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6018,9 +5527,6 @@
       <c r="I164" t="n">
         <v>422.87760814889</v>
       </c>
-      <c r="J164" t="n">
-        <v>1229581265.6202</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6052,9 +5558,6 @@
       <c r="I165" t="n">
         <v>424.1932020833065</v>
       </c>
-      <c r="J165" t="n">
-        <v>452527013.0972483</v>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6086,9 +5589,6 @@
       <c r="I166" t="n">
         <v>366.8659341721198</v>
       </c>
-      <c r="J166" t="n">
-        <v>770087467.9783232</v>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6120,9 +5620,6 @@
       <c r="I167" t="n">
         <v>136.6273011118156</v>
       </c>
-      <c r="J167" t="n">
-        <v>326263989.2296082</v>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6154,9 +5651,6 @@
       <c r="I168" t="n">
         <v>116.8619030719691</v>
       </c>
-      <c r="J168" t="n">
-        <v>345589756.5152489</v>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6188,9 +5682,6 @@
       <c r="I169" t="n">
         <v>67.14739972868296</v>
       </c>
-      <c r="J169" t="n">
-        <v>203635765.5990581</v>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6222,9 +5713,6 @@
       <c r="I170" t="n">
         <v>110.0155394868578</v>
       </c>
-      <c r="J170" t="n">
-        <v>335954876.6008602</v>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6256,9 +5744,6 @@
       <c r="I171" t="n">
         <v>441.4650566886497</v>
       </c>
-      <c r="J171" t="n">
-        <v>819554078.5245657</v>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6290,9 +5775,6 @@
       <c r="I172" t="n">
         <v>135.8642245783005</v>
       </c>
-      <c r="J172" t="n">
-        <v>274928290.7664554</v>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6324,9 +5806,6 @@
       <c r="I173" t="n">
         <v>135.5652887863286</v>
       </c>
-      <c r="J173" t="n">
-        <v>386871949.4761751</v>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6358,9 +5837,6 @@
       <c r="I174" t="n">
         <v>108.3634492007963</v>
       </c>
-      <c r="J174" t="n">
-        <v>269773433.6237547</v>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6392,9 +5868,6 @@
       <c r="I175" t="n">
         <v>133.6289924038313</v>
       </c>
-      <c r="J175" t="n">
-        <v>439224887.9185178</v>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6426,9 +5899,6 @@
       <c r="I176" t="n">
         <v>181.4012272520388</v>
       </c>
-      <c r="J176" t="n">
-        <v>600808148.8250329</v>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6460,9 +5930,6 @@
       <c r="I177" t="n">
         <v>291.7330142189344</v>
       </c>
-      <c r="J177" t="n">
-        <v>1380590426.485222</v>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6494,9 +5961,6 @@
       <c r="I178" t="n">
         <v>436.0282594747227</v>
       </c>
-      <c r="J178" t="n">
-        <v>1462849429.332712</v>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6528,9 +5992,6 @@
       <c r="I179" t="n">
         <v>116.4654686920483</v>
       </c>
-      <c r="J179" t="n">
-        <v>290211329.3998691</v>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6562,9 +6023,6 @@
       <c r="I180" t="n">
         <v>147.1133911629679</v>
       </c>
-      <c r="J180" t="n">
-        <v>476431416.0829854</v>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6596,9 +6054,6 @@
       <c r="I181" t="n">
         <v>112.1407207819316</v>
       </c>
-      <c r="J181" t="n">
-        <v>204708457.3503526</v>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6630,9 +6085,6 @@
       <c r="I182" t="n">
         <v>134.5946867737809</v>
       </c>
-      <c r="J182" t="n">
-        <v>331349232.3565096</v>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6664,9 +6116,6 @@
       <c r="I183" t="n">
         <v>134.9979401079424</v>
       </c>
-      <c r="J183" t="n">
-        <v>330424612.8724344</v>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6698,9 +6147,6 @@
       <c r="I184" t="n">
         <v>116.9610396796634</v>
       </c>
-      <c r="J184" t="n">
-        <v>265790647.9961707</v>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6732,9 +6178,6 @@
       <c r="I185" t="n">
         <v>141.1914671328136</v>
       </c>
-      <c r="J185" t="n">
-        <v>335646841.5099547</v>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6766,9 +6209,6 @@
       <c r="I186" t="n">
         <v>134.8274477844502</v>
       </c>
-      <c r="J186" t="n">
-        <v>256795466.17121</v>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6800,9 +6240,6 @@
       <c r="I187" t="n">
         <v>115.5589954023719</v>
       </c>
-      <c r="J187" t="n">
-        <v>239181715.3000067</v>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6834,9 +6271,6 @@
       <c r="I188" t="n">
         <v>124.0243692895168</v>
       </c>
-      <c r="J188" t="n">
-        <v>349589630.3769751</v>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6868,9 +6302,6 @@
       <c r="I189" t="n">
         <v>128.3784927693047</v>
       </c>
-      <c r="J189" t="n">
-        <v>392873725.6084411</v>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6902,9 +6333,6 @@
       <c r="I190" t="n">
         <v>438.2231249765429</v>
       </c>
-      <c r="J190" t="n">
-        <v>466400398.6315597</v>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6936,9 +6364,6 @@
       <c r="I191" t="n">
         <v>68.87078381624423</v>
       </c>
-      <c r="J191" t="n">
-        <v>111550038.8503157</v>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6970,9 +6395,6 @@
       <c r="I192" t="n">
         <v>436.3721841702692</v>
       </c>
-      <c r="J192" t="n">
-        <v>503008341.825606</v>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7004,9 +6426,6 @@
       <c r="I193" t="n">
         <v>418.9682152063426</v>
       </c>
-      <c r="J193" t="n">
-        <v>522412933.9295419</v>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7038,9 +6457,6 @@
       <c r="I194" t="n">
         <v>66.87147235620471</v>
       </c>
-      <c r="J194" t="n">
-        <v>103456075.8296314</v>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7072,9 +6488,6 @@
       <c r="I195" t="n">
         <v>111.7612942561259</v>
       </c>
-      <c r="J195" t="n">
-        <v>255497576.3846743</v>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7106,9 +6519,6 @@
       <c r="I196" t="n">
         <v>134.711526205172</v>
       </c>
-      <c r="J196" t="n">
-        <v>155149541.3552894</v>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7140,9 +6550,6 @@
       <c r="I197" t="n">
         <v>113.9739665090551</v>
       </c>
-      <c r="J197" t="n">
-        <v>125928594.4193597</v>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7174,9 +6581,6 @@
       <c r="I198" t="n">
         <v>116.9153879128728</v>
       </c>
-      <c r="J198" t="n">
-        <v>137866667.5163992</v>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7208,9 +6612,6 @@
       <c r="I199" t="n">
         <v>119.4607446504558</v>
       </c>
-      <c r="J199" t="n">
-        <v>266663475.7567043</v>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7242,9 +6643,6 @@
       <c r="I200" t="n">
         <v>128.1223886851244</v>
       </c>
-      <c r="J200" t="n">
-        <v>255402763.4379297</v>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7276,9 +6674,6 @@
       <c r="I201" t="n">
         <v>114.3936628670256</v>
       </c>
-      <c r="J201" t="n">
-        <v>200289524.2771075</v>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7310,9 +6705,6 @@
       <c r="I202" t="n">
         <v>133.3570028934936</v>
       </c>
-      <c r="J202" t="n">
-        <v>284232955.5620946</v>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7344,9 +6736,6 @@
       <c r="I203" t="n">
         <v>80.39050753268133</v>
       </c>
-      <c r="J203" t="n">
-        <v>86388213.38284315</v>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7378,9 +6767,6 @@
       <c r="I204" t="n">
         <v>102.4988016091568</v>
       </c>
-      <c r="J204" t="n">
-        <v>113119767.4064303</v>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7412,9 +6798,6 @@
       <c r="I205" t="n">
         <v>104.8494011357226</v>
       </c>
-      <c r="J205" t="n">
-        <v>176608869.150439</v>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7446,9 +6829,6 @@
       <c r="I206" t="n">
         <v>159.4643923886767</v>
       </c>
-      <c r="J206" t="n">
-        <v>268914696.4612855</v>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7480,9 +6860,6 @@
       <c r="I207" t="n">
         <v>120.0040682159923</v>
       </c>
-      <c r="J207" t="n">
-        <v>240228212.4927063</v>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7514,9 +6891,6 @@
       <c r="I208" t="n">
         <v>169.6926348159986</v>
       </c>
-      <c r="J208" t="n">
-        <v>216653491.7477424</v>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7548,9 +6922,6 @@
       <c r="I209" t="n">
         <v>136.2060012010795</v>
       </c>
-      <c r="J209" t="n">
-        <v>217597590.2593796</v>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7582,9 +6953,6 @@
       <c r="I210" t="n">
         <v>145.4749115339448</v>
       </c>
-      <c r="J210" t="n">
-        <v>257747218.4327737</v>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7616,9 +6984,6 @@
       <c r="I211" t="n">
         <v>122.4259668926803</v>
       </c>
-      <c r="J211" t="n">
-        <v>234814157.7527691</v>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7650,9 +7015,6 @@
       <c r="I212" t="n">
         <v>108.1882747316393</v>
       </c>
-      <c r="J212" t="n">
-        <v>369575571.3837166</v>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7684,9 +7046,6 @@
       <c r="I213" t="n">
         <v>229.8607558359462</v>
       </c>
-      <c r="J213" t="n">
-        <v>247073733.7244449</v>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7718,9 +7077,6 @@
       <c r="I214" t="n">
         <v>225.064995129652</v>
       </c>
-      <c r="J214" t="n">
-        <v>243264297.5437737</v>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7752,9 +7108,6 @@
       <c r="I215" t="n">
         <v>419.672814067605</v>
       </c>
-      <c r="J215" t="n">
-        <v>940746534.0308216</v>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7786,9 +7139,6 @@
       <c r="I216" t="n">
         <v>377.8634954661895</v>
       </c>
-      <c r="J216" t="n">
-        <v>794520490.6604074</v>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7820,9 +7170,6 @@
       <c r="I217" t="n">
         <v>397.4782412309082</v>
       </c>
-      <c r="J217" t="n">
-        <v>812892855.0382229</v>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7854,9 +7201,6 @@
       <c r="I218" t="n">
         <v>333.5404278771352</v>
       </c>
-      <c r="J218" t="n">
-        <v>639119598.0020072</v>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7888,9 +7232,6 @@
       <c r="I219" t="n">
         <v>230.3482592715248</v>
       </c>
-      <c r="J219" t="n">
-        <v>362909050.9850124</v>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7922,9 +7263,6 @@
       <c r="I220" t="n">
         <v>415.1807710422817</v>
       </c>
-      <c r="J220" t="n">
-        <v>1053054058.609588</v>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7956,9 +7294,6 @@
       <c r="I221" t="n">
         <v>193.1966175896344</v>
       </c>
-      <c r="J221" t="n">
-        <v>338334970.4960579</v>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7990,9 +7325,6 @@
       <c r="I222" t="n">
         <v>314.0855088794886</v>
       </c>
-      <c r="J222" t="n">
-        <v>564560242.7888275</v>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8024,9 +7356,6 @@
       <c r="I223" t="n">
         <v>384.9642702937756</v>
       </c>
-      <c r="J223" t="n">
-        <v>834265509.4775488</v>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8058,9 +7387,6 @@
       <c r="I224" t="n">
         <v>189.8516782079799</v>
       </c>
-      <c r="J224" t="n">
-        <v>217021453.4469716</v>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8092,9 +7418,6 @@
       <c r="I225" t="n">
         <v>396.8570901951181</v>
       </c>
-      <c r="J225" t="n">
-        <v>1032827311.897616</v>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8126,9 +7449,6 @@
       <c r="I226" t="n">
         <v>352.345793583056</v>
       </c>
-      <c r="J226" t="n">
-        <v>652330843.2408198</v>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8160,9 +7480,6 @@
       <c r="I227" t="n">
         <v>537.3485840089204</v>
       </c>
-      <c r="J227" t="n">
-        <v>661113779.4816409</v>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8194,9 +7511,6 @@
       <c r="I228" t="n">
         <v>338.7538155998406</v>
       </c>
-      <c r="J228" t="n">
-        <v>665878151.7344519</v>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8228,9 +7542,6 @@
       <c r="I229" t="n">
         <v>417.4720974985719</v>
       </c>
-      <c r="J229" t="n">
-        <v>660157606.6808705</v>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8262,9 +7573,6 @@
       <c r="I230" t="n">
         <v>376.6730883738524</v>
       </c>
-      <c r="J230" t="n">
-        <v>715022813.7555872</v>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8296,9 +7604,6 @@
       <c r="I231" t="n">
         <v>412.7090821028135</v>
       </c>
-      <c r="J231" t="n">
-        <v>1116463953.705288</v>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8330,9 +7635,6 @@
       <c r="I232" t="n">
         <v>192.1475305672869</v>
       </c>
-      <c r="J232" t="n">
-        <v>682282498.1010659</v>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8364,9 +7666,6 @@
       <c r="I233" t="n">
         <v>344.0143888267083</v>
       </c>
-      <c r="J233" t="n">
-        <v>962749393.9425033</v>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8398,9 +7697,6 @@
       <c r="I234" t="n">
         <v>387.4842357033926</v>
       </c>
-      <c r="J234" t="n">
-        <v>1424351828.032068</v>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8432,9 +7728,6 @@
       <c r="I235" t="n">
         <v>224.5517052120445</v>
       </c>
-      <c r="J235" t="n">
-        <v>438027579.4513863</v>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8466,9 +7759,6 @@
       <c r="I236" t="n">
         <v>195.3516669208213</v>
       </c>
-      <c r="J236" t="n">
-        <v>340085161.7426546</v>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8500,9 +7790,6 @@
       <c r="I237" t="n">
         <v>414.2812049218847</v>
       </c>
-      <c r="J237" t="n">
-        <v>1609000695.445659</v>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8534,9 +7821,6 @@
       <c r="I238" t="n">
         <v>177.962552569528</v>
       </c>
-      <c r="J238" t="n">
-        <v>573749349.268216</v>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8568,9 +7852,6 @@
       <c r="I239" t="n">
         <v>536.8344550885704</v>
       </c>
-      <c r="J239" t="n">
-        <v>1413340719.832305</v>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8602,9 +7883,6 @@
       <c r="I240" t="n">
         <v>391.7037606540575</v>
       </c>
-      <c r="J240" t="n">
-        <v>961468515.5786951</v>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8636,9 +7914,6 @@
       <c r="I241" t="n">
         <v>397.5562571974353</v>
       </c>
-      <c r="J241" t="n">
-        <v>1019218156.033232</v>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8670,9 +7945,6 @@
       <c r="I242" t="n">
         <v>374.2917936817031</v>
       </c>
-      <c r="J242" t="n">
-        <v>1738773792.654616</v>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8704,9 +7976,6 @@
       <c r="I243" t="n">
         <v>414.4853399375517</v>
       </c>
-      <c r="J243" t="n">
-        <v>735633294.0194818</v>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8738,9 +8007,6 @@
       <c r="I244" t="n">
         <v>464.1934089637818</v>
       </c>
-      <c r="J244" t="n">
-        <v>942337906.6682376</v>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8772,9 +8038,6 @@
       <c r="I245" t="n">
         <v>198.5647588025095</v>
       </c>
-      <c r="J245" t="n">
-        <v>405193038.8593491</v>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8806,9 +8069,6 @@
       <c r="I246" t="n">
         <v>349.3139158828723</v>
       </c>
-      <c r="J246" t="n">
-        <v>404168862.607306</v>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8840,9 +8100,6 @@
       <c r="I247" t="n">
         <v>201.5696038015792</v>
       </c>
-      <c r="J247" t="n">
-        <v>438875592.5165746</v>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8874,9 +8131,6 @@
       <c r="I248" t="n">
         <v>345.1333457202122</v>
       </c>
-      <c r="J248" t="n">
-        <v>411460587.1883718</v>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8908,9 +8162,6 @@
       <c r="I249" t="n">
         <v>410.8883422646456</v>
       </c>
-      <c r="J249" t="n">
-        <v>673055620.2844189</v>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8942,9 +8193,6 @@
       <c r="I250" t="n">
         <v>408.8581684202446</v>
       </c>
-      <c r="J250" t="n">
-        <v>489962688.6737907</v>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8976,9 +8224,6 @@
       <c r="I251" t="n">
         <v>464.582298371576</v>
       </c>
-      <c r="J251" t="n">
-        <v>639175164.6974573</v>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9010,9 +8255,6 @@
       <c r="I252" t="n">
         <v>32.60451440507697</v>
       </c>
-      <c r="J252" t="n">
-        <v>16630794.63567038</v>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9044,9 +8286,6 @@
       <c r="I253" t="n">
         <v>94.35960271226369</v>
       </c>
-      <c r="J253" t="n">
-        <v>53664665.99612819</v>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9078,9 +8317,6 @@
       <c r="I254" t="n">
         <v>384.5799275406081</v>
       </c>
-      <c r="J254" t="n">
-        <v>209053375.9280795</v>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9112,9 +8348,6 @@
       <c r="I255" t="n">
         <v>482.00735820496</v>
       </c>
-      <c r="J255" t="n">
-        <v>515428056.5770648</v>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9146,9 +8379,6 @@
       <c r="I256" t="n">
         <v>482.4906943718859</v>
       </c>
-      <c r="J256" t="n">
-        <v>752227488.5783231</v>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9180,9 +8410,6 @@
       <c r="I257" t="n">
         <v>92.64544990077594</v>
       </c>
-      <c r="J257" t="n">
-        <v>175684286.9652145</v>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9214,9 +8441,6 @@
       <c r="I258" t="n">
         <v>75.2899228366535</v>
       </c>
-      <c r="J258" t="n">
-        <v>147777882.2564912</v>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9248,9 +8472,6 @@
       <c r="I259" t="n">
         <v>508.8891223415916</v>
       </c>
-      <c r="J259" t="n">
-        <v>1239140575.388629</v>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9282,9 +8503,6 @@
       <c r="I260" t="n">
         <v>552.3573847787909</v>
       </c>
-      <c r="J260" t="n">
-        <v>997776278.1445593</v>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9316,9 +8534,6 @@
       <c r="I261" t="n">
         <v>102.3489899239865</v>
       </c>
-      <c r="J261" t="n">
-        <v>265457658.320368</v>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9350,9 +8565,6 @@
       <c r="I262" t="n">
         <v>522.1664319142777</v>
       </c>
-      <c r="J262" t="n">
-        <v>965439776.7418271</v>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9384,9 +8596,6 @@
       <c r="I263" t="n">
         <v>95.57020709971071</v>
       </c>
-      <c r="J263" t="n">
-        <v>163892738.6562982</v>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9418,9 +8627,6 @@
       <c r="I264" t="n">
         <v>96.70476762895548</v>
       </c>
-      <c r="J264" t="n">
-        <v>220921197.6091371</v>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9452,9 +8658,6 @@
       <c r="I265" t="n">
         <v>510.5175932013258</v>
       </c>
-      <c r="J265" t="n">
-        <v>634082934.5181634</v>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9486,9 +8689,6 @@
       <c r="I266" t="n">
         <v>390.1597548737963</v>
       </c>
-      <c r="J266" t="n">
-        <v>466102499.851944</v>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9520,9 +8720,6 @@
       <c r="I267" t="n">
         <v>92.28373519837209</v>
       </c>
-      <c r="J267" t="n">
-        <v>146560277.4753665</v>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9554,9 +8751,6 @@
       <c r="I268" t="n">
         <v>595.7184877137429</v>
       </c>
-      <c r="J268" t="n">
-        <v>1745721925.782881</v>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9588,9 +8782,6 @@
       <c r="I269" t="n">
         <v>589.7659034972133</v>
       </c>
-      <c r="J269" t="n">
-        <v>1103981214.183812</v>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9622,9 +8813,6 @@
       <c r="I270" t="n">
         <v>93.68564527290076</v>
       </c>
-      <c r="J270" t="n">
-        <v>138536251.094331</v>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9656,9 +8844,6 @@
       <c r="I271" t="n">
         <v>94.17527792394209</v>
       </c>
-      <c r="J271" t="n">
-        <v>141585467.2128027</v>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9690,9 +8875,6 @@
       <c r="I272" t="n">
         <v>112.4783746360528</v>
       </c>
-      <c r="J272" t="n">
-        <v>169955675.5363718</v>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9724,9 +8906,6 @@
       <c r="I273" t="n">
         <v>94.45839254828898</v>
       </c>
-      <c r="J273" t="n">
-        <v>341502669.4604534</v>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9758,9 +8937,6 @@
       <c r="I274" t="n">
         <v>92.67265559598945</v>
       </c>
-      <c r="J274" t="n">
-        <v>284765603.704349</v>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9792,9 +8968,6 @@
       <c r="I275" t="n">
         <v>112.6132028265503</v>
       </c>
-      <c r="J275" t="n">
-        <v>196096855.4604997</v>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9826,9 +8999,6 @@
       <c r="I276" t="n">
         <v>99.02980389832064</v>
       </c>
-      <c r="J276" t="n">
-        <v>404504218.6243576</v>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9860,9 +9030,6 @@
       <c r="I277" t="n">
         <v>97.27427688122583</v>
       </c>
-      <c r="J277" t="n">
-        <v>315187416.7799284</v>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9894,9 +9061,6 @@
       <c r="I278" t="n">
         <v>91.50333000873195</v>
       </c>
-      <c r="J278" t="n">
-        <v>126071704.1633885</v>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9928,9 +9092,6 @@
       <c r="I279" t="n">
         <v>95.99397161868814</v>
       </c>
-      <c r="J279" t="n">
-        <v>330863030.1959368</v>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9962,9 +9123,6 @@
       <c r="I280" t="n">
         <v>550.7295808016556</v>
       </c>
-      <c r="J280" t="n">
-        <v>1281621767.726177</v>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9996,9 +9154,6 @@
       <c r="I281" t="n">
         <v>0</v>
       </c>
-      <c r="J281" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10030,9 +9185,6 @@
       <c r="I282" t="n">
         <v>94.37343372652148</v>
       </c>
-      <c r="J282" t="n">
-        <v>164609594.3422703</v>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10064,9 +9216,6 @@
       <c r="I283" t="n">
         <v>386.5114632433878</v>
       </c>
-      <c r="J283" t="n">
-        <v>742814871.8445377</v>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10098,9 +9247,6 @@
       <c r="I284" t="n">
         <v>384.2393599367526</v>
       </c>
-      <c r="J284" t="n">
-        <v>694714653.0867735</v>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10132,9 +9278,6 @@
       <c r="I285" t="n">
         <v>99.63501088455672</v>
       </c>
-      <c r="J285" t="n">
-        <v>206703494.513403</v>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10166,9 +9309,6 @@
       <c r="I286" t="n">
         <v>92.73566034601555</v>
       </c>
-      <c r="J286" t="n">
-        <v>139379693.4824414</v>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10200,9 +9340,6 @@
       <c r="I287" t="n">
         <v>106.8588974613416</v>
       </c>
-      <c r="J287" t="n">
-        <v>137989423.6419333</v>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10234,9 +9371,6 @@
       <c r="I288" t="n">
         <v>515.496387359597</v>
       </c>
-      <c r="J288" t="n">
-        <v>1214451196.287728</v>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10268,9 +9402,6 @@
       <c r="I289" t="n">
         <v>469.4482391051256</v>
       </c>
-      <c r="J289" t="n">
-        <v>1422967114.539437</v>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10302,9 +9433,6 @@
       <c r="I290" t="n">
         <v>259.5176719658174</v>
       </c>
-      <c r="J290" t="n">
-        <v>623053685.5356742</v>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10336,9 +9464,6 @@
       <c r="I291" t="n">
         <v>605.7632706899564</v>
       </c>
-      <c r="J291" t="n">
-        <v>1106994335.252496</v>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10370,9 +9495,6 @@
       <c r="I292" t="n">
         <v>293.1002567845545</v>
       </c>
-      <c r="J292" t="n">
-        <v>714966832.8287262</v>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10404,9 +9526,6 @@
       <c r="I293" t="n">
         <v>150.3854486811032</v>
       </c>
-      <c r="J293" t="n">
-        <v>319853232.1285909</v>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10438,9 +9557,6 @@
       <c r="I294" t="n">
         <v>609.8136359579141</v>
       </c>
-      <c r="J294" t="n">
-        <v>1150283393.67301</v>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10472,9 +9588,6 @@
       <c r="I295" t="n">
         <v>398.8320502782476</v>
       </c>
-      <c r="J295" t="n">
-        <v>819660323.2693808</v>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10506,9 +9619,6 @@
       <c r="I296" t="n">
         <v>159.1709720886669</v>
       </c>
-      <c r="J296" t="n">
-        <v>298378995.0299726</v>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10540,9 +9650,6 @@
       <c r="I297" t="n">
         <v>514.7670845213308</v>
       </c>
-      <c r="J297" t="n">
-        <v>853422084.9722492</v>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10574,9 +9681,6 @@
       <c r="I298" t="n">
         <v>168.3179946113131</v>
       </c>
-      <c r="J298" t="n">
-        <v>350018660.1008611</v>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10608,9 +9712,6 @@
       <c r="I299" t="n">
         <v>428.7166743978141</v>
       </c>
-      <c r="J299" t="n">
-        <v>401453838.5355771</v>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10642,9 +9743,6 @@
       <c r="I300" t="n">
         <v>159.0016671290651</v>
       </c>
-      <c r="J300" t="n">
-        <v>321644327.1078622</v>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10676,9 +9774,6 @@
       <c r="I301" t="n">
         <v>546.1529639801837</v>
       </c>
-      <c r="J301" t="n">
-        <v>935367445.0245079</v>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10710,9 +9805,6 @@
       <c r="I302" t="n">
         <v>533.9820761041468</v>
       </c>
-      <c r="J302" t="n">
-        <v>890852779.6327021</v>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10744,9 +9836,6 @@
       <c r="I303" t="n">
         <v>418.1241507146969</v>
       </c>
-      <c r="J303" t="n">
-        <v>718065780.338086</v>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10778,9 +9867,6 @@
       <c r="I304" t="n">
         <v>423.8519858386172</v>
       </c>
-      <c r="J304" t="n">
-        <v>1076999985.666315</v>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10812,9 +9898,6 @@
       <c r="I305" t="n">
         <v>421.0250492420701</v>
       </c>
-      <c r="J305" t="n">
-        <v>938247431.9505104</v>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -10846,9 +9929,6 @@
       <c r="I306" t="n">
         <v>264.9868752387629</v>
       </c>
-      <c r="J306" t="n">
-        <v>593776728.7903267</v>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10880,9 +9960,6 @@
       <c r="I307" t="n">
         <v>210.2618162320152</v>
       </c>
-      <c r="J307" t="n">
-        <v>375345915.5036641</v>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -10914,9 +9991,6 @@
       <c r="I308" t="n">
         <v>156.6116107346159</v>
       </c>
-      <c r="J308" t="n">
-        <v>118731747.0629147</v>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10948,9 +10022,6 @@
       <c r="I309" t="n">
         <v>334.4914004993488</v>
       </c>
-      <c r="J309" t="n">
-        <v>701520748.8433901</v>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10982,9 +10053,6 @@
       <c r="I310" t="n">
         <v>495.4572343240575</v>
       </c>
-      <c r="J310" t="n">
-        <v>629739249.6697253</v>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11016,9 +10084,6 @@
       <c r="I311" t="n">
         <v>159.3858112034838</v>
       </c>
-      <c r="J311" t="n">
-        <v>548482238.0498228</v>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11050,9 +10115,6 @@
       <c r="I312" t="n">
         <v>262.7876734784617</v>
       </c>
-      <c r="J312" t="n">
-        <v>927176140.3773887</v>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11084,9 +10146,6 @@
       <c r="I313" t="n">
         <v>161.1344693495137</v>
       </c>
-      <c r="J313" t="n">
-        <v>509557916.4084415</v>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11118,9 +10177,6 @@
       <c r="I314" t="n">
         <v>269.070535269441</v>
       </c>
-      <c r="J314" t="n">
-        <v>939319160.3222274</v>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11152,9 +10208,6 @@
       <c r="I315" t="n">
         <v>302.8133964563956</v>
       </c>
-      <c r="J315" t="n">
-        <v>827532232.42958</v>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11186,9 +10239,6 @@
       <c r="I316" t="n">
         <v>546.9836780811395</v>
       </c>
-      <c r="J316" t="n">
-        <v>1015844971.631151</v>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11220,9 +10270,6 @@
       <c r="I317" t="n">
         <v>219.3930996632319</v>
       </c>
-      <c r="J317" t="n">
-        <v>527742259.9111296</v>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11254,9 +10301,6 @@
       <c r="I318" t="n">
         <v>147.6196537445319</v>
       </c>
-      <c r="J318" t="n">
-        <v>344065278.6872801</v>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11288,9 +10332,6 @@
       <c r="I319" t="n">
         <v>532.3398390756205</v>
       </c>
-      <c r="J319" t="n">
-        <v>1306927501.643014</v>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11322,9 +10363,6 @@
       <c r="I320" t="n">
         <v>378.8590788971603</v>
       </c>
-      <c r="J320" t="n">
-        <v>867843361.5259238</v>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11356,9 +10394,6 @@
       <c r="I321" t="n">
         <v>421.7867030321074</v>
       </c>
-      <c r="J321" t="n">
-        <v>1041879381.219549</v>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11390,9 +10425,6 @@
       <c r="I322" t="n">
         <v>247.9904061596499</v>
       </c>
-      <c r="J322" t="n">
-        <v>735962117.8417134</v>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -11424,9 +10456,6 @@
       <c r="I323" t="n">
         <v>209.2437086968674</v>
       </c>
-      <c r="J323" t="n">
-        <v>615608240.2978188</v>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -11458,9 +10487,6 @@
       <c r="I324" t="n">
         <v>171.5610975856906</v>
       </c>
-      <c r="J324" t="n">
-        <v>487759394.3688334</v>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11492,9 +10518,6 @@
       <c r="I325" t="n">
         <v>278.4183922634941</v>
       </c>
-      <c r="J325" t="n">
-        <v>534912680.8970729</v>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -11526,9 +10549,6 @@
       <c r="I326" t="n">
         <v>156.8727092762293</v>
       </c>
-      <c r="J326" t="n">
-        <v>364168831.5227745</v>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11560,9 +10580,6 @@
       <c r="I327" t="n">
         <v>419.9714842742374</v>
       </c>
-      <c r="J327" t="n">
-        <v>897313166.8581848</v>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11594,9 +10611,6 @@
       <c r="I328" t="n">
         <v>413.2442366380896</v>
       </c>
-      <c r="J328" t="n">
-        <v>1328107085.067605</v>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -11628,9 +10642,6 @@
       <c r="I329" t="n">
         <v>177.6925516581376</v>
       </c>
-      <c r="J329" t="n">
-        <v>287410910.0092505</v>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -11662,9 +10673,6 @@
       <c r="I330" t="n">
         <v>164.433344750549</v>
       </c>
-      <c r="J330" t="n">
-        <v>241242309.2273463</v>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11696,9 +10704,6 @@
       <c r="I331" t="n">
         <v>428.9474955583875</v>
       </c>
-      <c r="J331" t="n">
-        <v>983669290.0007484</v>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11730,9 +10735,6 @@
       <c r="I332" t="n">
         <v>353.350985394453</v>
       </c>
-      <c r="J332" t="n">
-        <v>755145924.4631851</v>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11764,9 +10766,6 @@
       <c r="I333" t="n">
         <v>427.7753898421324</v>
       </c>
-      <c r="J333" t="n">
-        <v>573621849.9175642</v>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11798,9 +10797,6 @@
       <c r="I334" t="n">
         <v>264.8709808666407</v>
       </c>
-      <c r="J334" t="n">
-        <v>369392145.0687051</v>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11832,9 +10828,6 @@
       <c r="I335" t="n">
         <v>105.7153231447665</v>
       </c>
-      <c r="J335" t="n">
-        <v>211725163.8940482</v>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11866,9 +10859,6 @@
       <c r="I336" t="n">
         <v>325.683184610459</v>
       </c>
-      <c r="J336" t="n">
-        <v>545573992.9800258</v>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11900,9 +10890,6 @@
       <c r="I337" t="n">
         <v>193.1659403726651</v>
       </c>
-      <c r="J337" t="n">
-        <v>268596614.2305441</v>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11934,9 +10921,6 @@
       <c r="I338" t="n">
         <v>228.6386816114776</v>
       </c>
-      <c r="J338" t="n">
-        <v>705909012.1444341</v>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11968,9 +10952,6 @@
       <c r="I339" t="n">
         <v>239.9271333422346</v>
       </c>
-      <c r="J339" t="n">
-        <v>629460695.1211892</v>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -12002,9 +10983,6 @@
       <c r="I340" t="n">
         <v>234.2369337173518</v>
       </c>
-      <c r="J340" t="n">
-        <v>482497184.0926335</v>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -12036,9 +11014,6 @@
       <c r="I341" t="n">
         <v>226.8159864422877</v>
       </c>
-      <c r="J341" t="n">
-        <v>401535964.8646133</v>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -12070,9 +11045,6 @@
       <c r="I342" t="n">
         <v>3.05245814029515</v>
       </c>
-      <c r="J342" t="n">
-        <v>6387942.458177493</v>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -12104,9 +11076,6 @@
       <c r="I343" t="n">
         <v>232.7606295976149</v>
       </c>
-      <c r="J343" t="n">
-        <v>564898921.377035</v>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -12138,9 +11107,6 @@
       <c r="I344" t="n">
         <v>44.63230629408451</v>
       </c>
-      <c r="J344" t="n">
-        <v>113050784.5026199</v>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -12172,9 +11138,6 @@
       <c r="I345" t="n">
         <v>235.6425339063696</v>
       </c>
-      <c r="J345" t="n">
-        <v>501804581.5805366</v>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -12206,9 +11169,6 @@
       <c r="I346" t="n">
         <v>236.3926209841623</v>
       </c>
-      <c r="J346" t="n">
-        <v>437192700.1155562</v>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -12240,9 +11200,6 @@
       <c r="I347" t="n">
         <v>228.7898553040338</v>
       </c>
-      <c r="J347" t="n">
-        <v>462535588.8650946</v>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -12274,9 +11231,6 @@
       <c r="I348" t="n">
         <v>238.3826140048343</v>
       </c>
-      <c r="J348" t="n">
-        <v>506813661.6347239</v>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -12308,9 +11262,6 @@
       <c r="I349" t="n">
         <v>126.9259514787582</v>
       </c>
-      <c r="J349" t="n">
-        <v>209450196.9851967</v>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -12342,9 +11293,6 @@
       <c r="I350" t="n">
         <v>240.990457513337</v>
       </c>
-      <c r="J350" t="n">
-        <v>359138027.1201433</v>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -12376,9 +11324,6 @@
       <c r="I351" t="n">
         <v>221.672979833551</v>
       </c>
-      <c r="J351" t="n">
-        <v>392993531.9480373</v>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -12410,9 +11355,6 @@
       <c r="I352" t="n">
         <v>123.2451849638042</v>
       </c>
-      <c r="J352" t="n">
-        <v>187235314.0596184</v>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -12444,9 +11386,6 @@
       <c r="I353" t="n">
         <v>232.446583431369</v>
       </c>
-      <c r="J353" t="n">
-        <v>671674474.5874207</v>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -12478,9 +11417,6 @@
       <c r="I354" t="n">
         <v>135.9227728142532</v>
       </c>
-      <c r="J354" t="n">
-        <v>271720402.8908041</v>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -12512,9 +11448,6 @@
       <c r="I355" t="n">
         <v>268.5129992494262</v>
       </c>
-      <c r="J355" t="n">
-        <v>1083053060.222115</v>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -12546,9 +11479,6 @@
       <c r="I356" t="n">
         <v>123.2245237075969</v>
       </c>
-      <c r="J356" t="n">
-        <v>280185577.0436478</v>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -12580,9 +11510,6 @@
       <c r="I357" t="n">
         <v>0</v>
       </c>
-      <c r="J357" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -12614,9 +11541,6 @@
       <c r="I358" t="n">
         <v>229.2048316902433</v>
       </c>
-      <c r="J358" t="n">
-        <v>659295868.0641998</v>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -12648,9 +11572,6 @@
       <c r="I359" t="n">
         <v>229.5926036582196</v>
       </c>
-      <c r="J359" t="n">
-        <v>915114084.9417677</v>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -12682,9 +11603,6 @@
       <c r="I360" t="n">
         <v>231.8062255945751</v>
       </c>
-      <c r="J360" t="n">
-        <v>441297142.7253392</v>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -12716,9 +11634,6 @@
       <c r="I361" t="n">
         <v>254.7217919902353</v>
       </c>
-      <c r="J361" t="n">
-        <v>809998109.9024247</v>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -12750,9 +11665,6 @@
       <c r="I362" t="n">
         <v>236.9675286822333</v>
       </c>
-      <c r="J362" t="n">
-        <v>635393198.1989195</v>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -12784,9 +11696,6 @@
       <c r="I363" t="n">
         <v>236.042639746664</v>
       </c>
-      <c r="J363" t="n">
-        <v>631515087.572138</v>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12818,9 +11727,6 @@
       <c r="I364" t="n">
         <v>231.0797650168059</v>
       </c>
-      <c r="J364" t="n">
-        <v>434735075.0290045</v>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -12852,9 +11758,6 @@
       <c r="I365" t="n">
         <v>236.7708126174289</v>
       </c>
-      <c r="J365" t="n">
-        <v>232279730.8213068</v>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -12886,9 +11789,6 @@
       <c r="I366" t="n">
         <v>130.1980141958676</v>
       </c>
-      <c r="J366" t="n">
-        <v>193085410.1217031</v>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -12920,9 +11820,6 @@
       <c r="I367" t="n">
         <v>184.798244502207</v>
       </c>
-      <c r="J367" t="n">
-        <v>271488022.6794367</v>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -12954,9 +11851,6 @@
       <c r="I368" t="n">
         <v>229.820113327984</v>
       </c>
-      <c r="J368" t="n">
-        <v>291871825.3412684</v>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12988,9 +11882,6 @@
       <c r="I369" t="n">
         <v>39.15438497735472</v>
       </c>
-      <c r="J369" t="n">
-        <v>131843735.7471271</v>
-      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -13022,9 +11913,6 @@
       <c r="I370" t="n">
         <v>12.57090271495102</v>
       </c>
-      <c r="J370" t="n">
-        <v>29817274.62636004</v>
-      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -13056,9 +11944,6 @@
       <c r="I371" t="n">
         <v>342.4939796860908</v>
       </c>
-      <c r="J371" t="n">
-        <v>794771842.70559</v>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -13090,9 +11975,6 @@
       <c r="I372" t="n">
         <v>154.5296365267789</v>
       </c>
-      <c r="J372" t="n">
-        <v>330689552.7452082</v>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -13124,9 +12006,6 @@
       <c r="I373" t="n">
         <v>37.91710526660902</v>
       </c>
-      <c r="J373" t="n">
-        <v>33576076.74413497</v>
-      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -13158,9 +12037,6 @@
       <c r="I374" t="n">
         <v>42.66602307691792</v>
       </c>
-      <c r="J374" t="n">
-        <v>144678568.5493926</v>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -13192,9 +12068,6 @@
       <c r="I375" t="n">
         <v>13.54667643358147</v>
       </c>
-      <c r="J375" t="n">
-        <v>30127025.54617411</v>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -13226,9 +12099,6 @@
       <c r="I376" t="n">
         <v>6.482501230056271</v>
       </c>
-      <c r="J376" t="n">
-        <v>16507318.3887929</v>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -13260,9 +12130,6 @@
       <c r="I377" t="n">
         <v>159.5564405282327</v>
       </c>
-      <c r="J377" t="n">
-        <v>166117578.4704027</v>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -13294,9 +12161,6 @@
       <c r="I378" t="n">
         <v>157.9057503839281</v>
       </c>
-      <c r="J378" t="n">
-        <v>213086467.5257182</v>
-      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -13328,9 +12192,6 @@
       <c r="I379" t="n">
         <v>11.61629237416503</v>
       </c>
-      <c r="J379" t="n">
-        <v>39085366.71429186</v>
-      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -13362,9 +12223,6 @@
       <c r="I380" t="n">
         <v>123.5969250984457</v>
       </c>
-      <c r="J380" t="n">
-        <v>118349256.7403699</v>
-      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -13396,9 +12254,6 @@
       <c r="I381" t="n">
         <v>318.263518593437</v>
       </c>
-      <c r="J381" t="n">
-        <v>583193493.3758678</v>
-      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -13430,9 +12285,6 @@
       <c r="I382" t="n">
         <v>9.701676387079416</v>
       </c>
-      <c r="J382" t="n">
-        <v>27431087.00108415</v>
-      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -13464,9 +12316,6 @@
       <c r="I383" t="n">
         <v>7.275330297290545</v>
       </c>
-      <c r="J383" t="n">
-        <v>37389479.93686286</v>
-      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -13498,9 +12347,6 @@
       <c r="I384" t="n">
         <v>10.61135848297473</v>
       </c>
-      <c r="J384" t="n">
-        <v>40597787.48236452</v>
-      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -13532,9 +12378,6 @@
       <c r="I385" t="n">
         <v>38.42775221604786</v>
       </c>
-      <c r="J385" t="n">
-        <v>150356223.8252032</v>
-      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -13566,9 +12409,6 @@
       <c r="I386" t="n">
         <v>319.5538914584326</v>
       </c>
-      <c r="J386" t="n">
-        <v>896464930.431003</v>
-      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -13600,9 +12440,6 @@
       <c r="I387" t="n">
         <v>14.41067480414424</v>
       </c>
-      <c r="J387" t="n">
-        <v>65165540.17153829</v>
-      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -13634,9 +12471,6 @@
       <c r="I388" t="n">
         <v>2.798523869312165</v>
       </c>
-      <c r="J388" t="n">
-        <v>7962238.852927721</v>
-      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -13668,9 +12502,6 @@
       <c r="I389" t="n">
         <v>4.086812362410984</v>
       </c>
-      <c r="J389" t="n">
-        <v>9353855.389567014</v>
-      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -13702,9 +12533,6 @@
       <c r="I390" t="n">
         <v>12.82877227690499</v>
       </c>
-      <c r="J390" t="n">
-        <v>26189513.71436374</v>
-      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -13736,9 +12564,6 @@
       <c r="I391" t="n">
         <v>184.5265200028921</v>
       </c>
-      <c r="J391" t="n">
-        <v>167019383.7363629</v>
-      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -13770,9 +12595,6 @@
       <c r="I392" t="n">
         <v>4.91155522905192</v>
       </c>
-      <c r="J392" t="n">
-        <v>11646493.16620262</v>
-      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -13804,9 +12626,6 @@
       <c r="I393" t="n">
         <v>162.3569820648295</v>
       </c>
-      <c r="J393" t="n">
-        <v>300466765.5138966</v>
-      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -13838,9 +12657,6 @@
       <c r="I394" t="n">
         <v>0</v>
       </c>
-      <c r="J394" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -13872,9 +12688,6 @@
       <c r="I395" t="n">
         <v>14.12354157257625</v>
       </c>
-      <c r="J395" t="n">
-        <v>40590640.56398907</v>
-      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -13906,9 +12719,6 @@
       <c r="I396" t="n">
         <v>562.9329183211324</v>
       </c>
-      <c r="J396" t="n">
-        <v>475163812.181999</v>
-      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -13940,9 +12750,6 @@
       <c r="I397" t="n">
         <v>399.0386805781686</v>
       </c>
-      <c r="J397" t="n">
-        <v>926789527.7799788</v>
-      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -13974,9 +12781,6 @@
       <c r="I398" t="n">
         <v>399.2933407902202</v>
       </c>
-      <c r="J398" t="n">
-        <v>708259812.3786409</v>
-      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -14008,9 +12812,6 @@
       <c r="I399" t="n">
         <v>544.8395540952689</v>
       </c>
-      <c r="J399" t="n">
-        <v>1856126745.560843</v>
-      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -14042,9 +12843,6 @@
       <c r="I400" t="n">
         <v>404.1985816893753</v>
       </c>
-      <c r="J400" t="n">
-        <v>410960281.7286412</v>
-      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -14076,9 +12874,6 @@
       <c r="I401" t="n">
         <v>398.0133220468219</v>
       </c>
-      <c r="J401" t="n">
-        <v>932082373.4158154</v>
-      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -14110,9 +12905,6 @@
       <c r="I402" t="n">
         <v>271.698348756485</v>
       </c>
-      <c r="J402" t="n">
-        <v>424888693.6101682</v>
-      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -14144,9 +12936,6 @@
       <c r="I403" t="n">
         <v>393.8114777969823</v>
       </c>
-      <c r="J403" t="n">
-        <v>457057625.3505835</v>
-      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -14178,9 +12967,6 @@
       <c r="I404" t="n">
         <v>270.9129282531802</v>
       </c>
-      <c r="J404" t="n">
-        <v>737143597.0497218</v>
-      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -14212,9 +12998,6 @@
       <c r="I405" t="n">
         <v>559.6269996577513</v>
       </c>
-      <c r="J405" t="n">
-        <v>2125284642.088289</v>
-      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -14246,9 +13029,6 @@
       <c r="I406" t="n">
         <v>629.6244910605436</v>
       </c>
-      <c r="J406" t="n">
-        <v>1555804821.647793</v>
-      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -14280,9 +13060,6 @@
       <c r="I407" t="n">
         <v>398.0612564570309</v>
       </c>
-      <c r="J407" t="n">
-        <v>828835727.536887</v>
-      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -14314,9 +13091,6 @@
       <c r="I408" t="n">
         <v>541.9030864968256</v>
       </c>
-      <c r="J408" t="n">
-        <v>1788851852.553049</v>
-      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -14348,9 +13122,6 @@
       <c r="I409" t="n">
         <v>272.9139635372408</v>
       </c>
-      <c r="J409" t="n">
-        <v>1202168526.513041</v>
-      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -14382,9 +13153,6 @@
       <c r="I410" t="n">
         <v>560.2114394204164</v>
       </c>
-      <c r="J410" t="n">
-        <v>2163329499.964231</v>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -14416,9 +13184,6 @@
       <c r="I411" t="n">
         <v>397.8931264225789</v>
       </c>
-      <c r="J411" t="n">
-        <v>483961874.0286612</v>
-      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -14450,9 +13215,6 @@
       <c r="I412" t="n">
         <v>553.9746287176301</v>
       </c>
-      <c r="J412" t="n">
-        <v>1131425954.88854</v>
-      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -14484,9 +13246,6 @@
       <c r="I413" t="n">
         <v>290.325695922037</v>
       </c>
-      <c r="J413" t="n">
-        <v>766199971.2038066</v>
-      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -14518,9 +13277,6 @@
       <c r="I414" t="n">
         <v>589.205834795844</v>
       </c>
-      <c r="J414" t="n">
-        <v>1787588730.430872</v>
-      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -14552,9 +13308,6 @@
       <c r="I415" t="n">
         <v>592.9623348517237</v>
       </c>
-      <c r="J415" t="n">
-        <v>796157260.6590921</v>
-      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -14586,9 +13339,6 @@
       <c r="I416" t="n">
         <v>556.1763395240313</v>
       </c>
-      <c r="J416" t="n">
-        <v>675735153.4261988</v>
-      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -14620,9 +13370,6 @@
       <c r="I417" t="n">
         <v>585.6363666275724</v>
       </c>
-      <c r="J417" t="n">
-        <v>955976190.3791287</v>
-      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -14654,9 +13401,6 @@
       <c r="I418" t="n">
         <v>237.6201381750443</v>
       </c>
-      <c r="J418" t="n">
-        <v>303047435.9162744</v>
-      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -14688,9 +13432,6 @@
       <c r="I419" t="n">
         <v>99.7038613045038</v>
       </c>
-      <c r="J419" t="n">
-        <v>63224187.6044466</v>
-      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -14722,9 +13463,6 @@
       <c r="I420" t="n">
         <v>234.764391484706</v>
       </c>
-      <c r="J420" t="n">
-        <v>242160657.7242953</v>
-      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -14756,9 +13494,6 @@
       <c r="I421" t="n">
         <v>198.7765567384305</v>
       </c>
-      <c r="J421" t="n">
-        <v>183399740.9936143</v>
-      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -14790,9 +13525,6 @@
       <c r="I422" t="n">
         <v>237.0983883977419</v>
       </c>
-      <c r="J422" t="n">
-        <v>129236195.4093173</v>
-      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -14824,9 +13556,6 @@
       <c r="I423" t="n">
         <v>109.2974339087442</v>
       </c>
-      <c r="J423" t="n">
-        <v>88665018.48774549</v>
-      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -14858,9 +13587,6 @@
       <c r="I424" t="n">
         <v>243.3057882043767</v>
       </c>
-      <c r="J424" t="n">
-        <v>636221811.8087677</v>
-      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -14892,9 +13618,6 @@
       <c r="I425" t="n">
         <v>205.8332451562206</v>
       </c>
-      <c r="J425" t="n">
-        <v>521996151.416956</v>
-      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -14926,9 +13649,6 @@
       <c r="I426" t="n">
         <v>199.5832316516953</v>
       </c>
-      <c r="J426" t="n">
-        <v>476608809.7217672</v>
-      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -14960,9 +13680,6 @@
       <c r="I427" t="n">
         <v>244.77544899438</v>
       </c>
-      <c r="J427" t="n">
-        <v>534677465.7600347</v>
-      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -14994,9 +13711,6 @@
       <c r="I428" t="n">
         <v>212.5040539822774</v>
       </c>
-      <c r="J428" t="n">
-        <v>406294488.3048453</v>
-      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -15028,9 +13742,6 @@
       <c r="I429" t="n">
         <v>90.0980258920742</v>
       </c>
-      <c r="J429" t="n">
-        <v>219864221.8234977</v>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -15062,9 +13773,6 @@
       <c r="I430" t="n">
         <v>93.9900122522893</v>
       </c>
-      <c r="J430" t="n">
-        <v>207180428.3212875</v>
-      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -15096,9 +13804,6 @@
       <c r="I431" t="n">
         <v>48.06033700014402</v>
       </c>
-      <c r="J431" t="n">
-        <v>194201025.2791465</v>
-      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -15130,9 +13835,6 @@
       <c r="I432" t="n">
         <v>462.3370152351604</v>
       </c>
-      <c r="J432" t="n">
-        <v>781014352.1646359</v>
-      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -15164,9 +13866,6 @@
       <c r="I433" t="n">
         <v>449.9853559453078</v>
       </c>
-      <c r="J433" t="n">
-        <v>645077289.5399299</v>
-      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -15198,9 +13897,6 @@
       <c r="I434" t="n">
         <v>162.993792613938</v>
       </c>
-      <c r="J434" t="n">
-        <v>463654746.5399359</v>
-      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -15232,9 +13928,6 @@
       <c r="I435" t="n">
         <v>203.4341665162504</v>
       </c>
-      <c r="J435" t="n">
-        <v>422500480.0726312</v>
-      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -15266,9 +13959,6 @@
       <c r="I436" t="n">
         <v>105.6809195503245</v>
       </c>
-      <c r="J436" t="n">
-        <v>216711205.1335278</v>
-      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -15300,9 +13990,6 @@
       <c r="I437" t="n">
         <v>90.3683577034153</v>
       </c>
-      <c r="J437" t="n">
-        <v>100731533.5196884</v>
-      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -15334,9 +14021,6 @@
       <c r="I438" t="n">
         <v>94.08847476823729</v>
       </c>
-      <c r="J438" t="n">
-        <v>206416447.0553314</v>
-      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -15368,9 +14052,6 @@
       <c r="I439" t="n">
         <v>439.1031686450011</v>
       </c>
-      <c r="J439" t="n">
-        <v>693187564.9982923</v>
-      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -15402,9 +14083,6 @@
       <c r="I440" t="n">
         <v>456.135414208522</v>
       </c>
-      <c r="J440" t="n">
-        <v>786386175.4046118</v>
-      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -15436,9 +14114,6 @@
       <c r="I441" t="n">
         <v>251.7742107462432</v>
       </c>
-      <c r="J441" t="n">
-        <v>302970303.5481162</v>
-      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -15470,9 +14145,6 @@
       <c r="I442" t="n">
         <v>242.6207437871402</v>
       </c>
-      <c r="J442" t="n">
-        <v>361749508.7718955</v>
-      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -15504,9 +14176,6 @@
       <c r="I443" t="n">
         <v>94.55157049759576</v>
       </c>
-      <c r="J443" t="n">
-        <v>116951577.8872732</v>
-      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -15538,9 +14207,6 @@
       <c r="I444" t="n">
         <v>239.2033432876943</v>
       </c>
-      <c r="J444" t="n">
-        <v>413092690.7339114</v>
-      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -15572,9 +14238,6 @@
       <c r="I445" t="n">
         <v>244.7042980601115</v>
       </c>
-      <c r="J445" t="n">
-        <v>401555205.8990244</v>
-      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -15606,9 +14269,6 @@
       <c r="I446" t="n">
         <v>238.517141078303</v>
       </c>
-      <c r="J446" t="n">
-        <v>705131641.2856094</v>
-      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -15640,9 +14300,6 @@
       <c r="I447" t="n">
         <v>212.7492079575601</v>
       </c>
-      <c r="J447" t="n">
-        <v>394455229.0568191</v>
-      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -15674,9 +14331,6 @@
       <c r="I448" t="n">
         <v>459.7575073825284</v>
       </c>
-      <c r="J448" t="n">
-        <v>1064096772.91245</v>
-      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -15708,9 +14362,6 @@
       <c r="I449" t="n">
         <v>90.29583703329229</v>
       </c>
-      <c r="J449" t="n">
-        <v>190362151.2034903</v>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -15742,9 +14393,6 @@
       <c r="I450" t="n">
         <v>480.4430992225687</v>
       </c>
-      <c r="J450" t="n">
-        <v>887725204.9086119</v>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -15776,9 +14424,6 @@
       <c r="I451" t="n">
         <v>198.0643498726504</v>
       </c>
-      <c r="J451" t="n">
-        <v>439377650.800909</v>
-      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -15810,9 +14455,6 @@
       <c r="I452" t="n">
         <v>97.55387968687192</v>
       </c>
-      <c r="J452" t="n">
-        <v>195647893.0120625</v>
-      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -15844,9 +14486,6 @@
       <c r="I453" t="n">
         <v>199.5974651940966</v>
       </c>
-      <c r="J453" t="n">
-        <v>581120271.2396173</v>
-      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -15878,9 +14517,6 @@
       <c r="I454" t="n">
         <v>335.0619337748118</v>
       </c>
-      <c r="J454" t="n">
-        <v>613743066.3163427</v>
-      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -15912,9 +14548,6 @@
       <c r="I455" t="n">
         <v>92.01053017070051</v>
       </c>
-      <c r="J455" t="n">
-        <v>266100813.113522</v>
-      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -15946,9 +14579,6 @@
       <c r="I456" t="n">
         <v>95.45167583039947</v>
       </c>
-      <c r="J456" t="n">
-        <v>362169140.7389808</v>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -15980,9 +14610,6 @@
       <c r="I457" t="n">
         <v>237.9422131497212</v>
       </c>
-      <c r="J457" t="n">
-        <v>232649581.2228574</v>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -16014,9 +14641,6 @@
       <c r="I458" t="n">
         <v>454.4354598273687</v>
       </c>
-      <c r="J458" t="n">
-        <v>1128305516.179411</v>
-      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -16048,9 +14672,6 @@
       <c r="I459" t="n">
         <v>199.2811750116876</v>
       </c>
-      <c r="J459" t="n">
-        <v>354167043.8559381</v>
-      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -16082,9 +14703,6 @@
       <c r="I460" t="n">
         <v>206.0759102960201</v>
       </c>
-      <c r="J460" t="n">
-        <v>535277878.2504233</v>
-      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -16116,9 +14734,6 @@
       <c r="I461" t="n">
         <v>205.4737074015495</v>
       </c>
-      <c r="J461" t="n">
-        <v>351475720.5731168</v>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -16150,9 +14765,6 @@
       <c r="I462" t="n">
         <v>50.25644795082248</v>
       </c>
-      <c r="J462" t="n">
-        <v>141619305.2793042</v>
-      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -16184,9 +14796,6 @@
       <c r="I463" t="n">
         <v>94.34029263720771</v>
       </c>
-      <c r="J463" t="n">
-        <v>375605118.2001577</v>
-      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -16218,9 +14827,6 @@
       <c r="I464" t="n">
         <v>199.6572089693678</v>
       </c>
-      <c r="J464" t="n">
-        <v>536032641.7157732</v>
-      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -16252,9 +14858,6 @@
       <c r="I465" t="n">
         <v>241.6691407618989</v>
       </c>
-      <c r="J465" t="n">
-        <v>568843978.5159906</v>
-      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -16286,9 +14889,6 @@
       <c r="I466" t="n">
         <v>202.3400634650289</v>
       </c>
-      <c r="J466" t="n">
-        <v>566369874.970421</v>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -16320,9 +14920,6 @@
       <c r="I467" t="n">
         <v>93.80687191812108</v>
       </c>
-      <c r="J467" t="n">
-        <v>101040068.4093107</v>
-      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -16354,9 +14951,6 @@
       <c r="I468" t="n">
         <v>91.55369369176938</v>
       </c>
-      <c r="J468" t="n">
-        <v>240197632.512712</v>
-      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -16388,9 +14982,6 @@
       <c r="I469" t="n">
         <v>207.7644881052486</v>
       </c>
-      <c r="J469" t="n">
-        <v>634727998.2665105</v>
-      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -16422,9 +15013,6 @@
       <c r="I470" t="n">
         <v>240.297222012738</v>
       </c>
-      <c r="J470" t="n">
-        <v>626872206.7232918</v>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -16456,9 +15044,6 @@
       <c r="I471" t="n">
         <v>248.1144254000412</v>
       </c>
-      <c r="J471" t="n">
-        <v>831350185.6388791</v>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -16490,9 +15075,6 @@
       <c r="I472" t="n">
         <v>94.17249277637561</v>
       </c>
-      <c r="J472" t="n">
-        <v>257211002.9886808</v>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -16524,9 +15106,6 @@
       <c r="I473" t="n">
         <v>203.1957489360825</v>
       </c>
-      <c r="J473" t="n">
-        <v>413797097.2922137</v>
-      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -16558,9 +15137,6 @@
       <c r="I474" t="n">
         <v>455.2583033426945</v>
       </c>
-      <c r="J474" t="n">
-        <v>1648703925.876117</v>
-      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -16592,9 +15168,6 @@
       <c r="I475" t="n">
         <v>91.13841375349979</v>
       </c>
-      <c r="J475" t="n">
-        <v>180993819.1507425</v>
-      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -16626,9 +15199,6 @@
       <c r="I476" t="n">
         <v>458.674922905298</v>
       </c>
-      <c r="J476" t="n">
-        <v>1292263320.193382</v>
-      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -16660,9 +15230,6 @@
       <c r="I477" t="n">
         <v>208.7746257080976</v>
       </c>
-      <c r="J477" t="n">
-        <v>787138745.3956547</v>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -16694,9 +15261,6 @@
       <c r="I478" t="n">
         <v>241.1319183450053</v>
       </c>
-      <c r="J478" t="n">
-        <v>649073034.6784911</v>
-      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -16728,9 +15292,6 @@
       <c r="I479" t="n">
         <v>208.8093372115301</v>
       </c>
-      <c r="J479" t="n">
-        <v>571928367.2353643</v>
-      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -16762,9 +15323,6 @@
       <c r="I480" t="n">
         <v>98.09423920156364</v>
       </c>
-      <c r="J480" t="n">
-        <v>236326819.376291</v>
-      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -16796,9 +15354,6 @@
       <c r="I481" t="n">
         <v>83.86170948034218</v>
       </c>
-      <c r="J481" t="n">
-        <v>167694060.9050146</v>
-      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -16830,9 +15385,6 @@
       <c r="I482" t="n">
         <v>451.2518729527299</v>
       </c>
-      <c r="J482" t="n">
-        <v>1344880133.264235</v>
-      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -16864,9 +15416,6 @@
       <c r="I483" t="n">
         <v>205.0075027925476</v>
       </c>
-      <c r="J483" t="n">
-        <v>565459432.3131018</v>
-      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -16898,9 +15447,6 @@
       <c r="I484" t="n">
         <v>204.411680816876</v>
       </c>
-      <c r="J484" t="n">
-        <v>459264089.2781122</v>
-      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -16932,9 +15478,6 @@
       <c r="I485" t="n">
         <v>342.6902945712899</v>
       </c>
-      <c r="J485" t="n">
-        <v>832501629.9785419</v>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -16966,9 +15509,6 @@
       <c r="I486" t="n">
         <v>436.7125282091822</v>
       </c>
-      <c r="J486" t="n">
-        <v>1468656842.667448</v>
-      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -17000,9 +15540,6 @@
       <c r="I487" t="n">
         <v>75.4651024189595</v>
       </c>
-      <c r="J487" t="n">
-        <v>251025044.1128542</v>
-      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -17034,9 +15571,6 @@
       <c r="I488" t="n">
         <v>478.9435636984282</v>
       </c>
-      <c r="J488" t="n">
-        <v>912713363.4351829</v>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -17068,9 +15602,6 @@
       <c r="I489" t="n">
         <v>206.7994832782831</v>
       </c>
-      <c r="J489" t="n">
-        <v>411099795.8351458</v>
-      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -17102,9 +15633,6 @@
       <c r="I490" t="n">
         <v>93.00717953846529</v>
       </c>
-      <c r="J490" t="n">
-        <v>234713075.8374332</v>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -17136,9 +15664,6 @@
       <c r="I491" t="n">
         <v>478.129089313604</v>
       </c>
-      <c r="J491" t="n">
-        <v>1070342368.406453</v>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -17170,9 +15695,6 @@
       <c r="I492" t="n">
         <v>262.869810262483</v>
       </c>
-      <c r="J492" t="n">
-        <v>272728858.5533987</v>
-      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -17204,9 +15726,6 @@
       <c r="I493" t="n">
         <v>173.614929625572</v>
       </c>
-      <c r="J493" t="n">
-        <v>207190411.5796621</v>
-      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -17238,9 +15757,6 @@
       <c r="I494" t="n">
         <v>340.0263864003297</v>
       </c>
-      <c r="J494" t="n">
-        <v>571459996.83859</v>
-      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -17272,9 +15788,6 @@
       <c r="I495" t="n">
         <v>206.5414340971641</v>
       </c>
-      <c r="J495" t="n">
-        <v>231721936.1332415</v>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -17306,9 +15819,6 @@
       <c r="I496" t="n">
         <v>334.3077432722394</v>
       </c>
-      <c r="J496" t="n">
-        <v>484994167.0825451</v>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -17340,9 +15850,6 @@
       <c r="I497" t="n">
         <v>265.9757361101167</v>
       </c>
-      <c r="J497" t="n">
-        <v>338192435.9928795</v>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -17374,9 +15881,6 @@
       <c r="I498" t="n">
         <v>40.28803578428388</v>
       </c>
-      <c r="J498" t="n">
-        <v>78410623.88999297</v>
-      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -17408,9 +15912,6 @@
       <c r="I499" t="n">
         <v>0</v>
       </c>
-      <c r="J499" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -17442,9 +15943,6 @@
       <c r="I500" t="n">
         <v>198.4169489828125</v>
       </c>
-      <c r="J500" t="n">
-        <v>325946377.3996535</v>
-      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -17476,9 +15974,6 @@
       <c r="I501" t="n">
         <v>197.2457940055387</v>
       </c>
-      <c r="J501" t="n">
-        <v>305965586.8284332</v>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -17510,9 +16005,6 @@
       <c r="I502" t="n">
         <v>114.9391757734247</v>
       </c>
-      <c r="J502" t="n">
-        <v>139555196.0175163</v>
-      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -17544,9 +16036,6 @@
       <c r="I503" t="n">
         <v>199.1949041175324</v>
       </c>
-      <c r="J503" t="n">
-        <v>169075148.6209769</v>
-      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -17578,9 +16067,6 @@
       <c r="I504" t="n">
         <v>212.3623313996765</v>
       </c>
-      <c r="J504" t="n">
-        <v>391528433.7425066</v>
-      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -17611,9 +16097,6 @@
       </c>
       <c r="I505" t="n">
         <v>98.10985974597351</v>
-      </c>
-      <c r="J505" t="n">
-        <v>118631349.982052</v>
       </c>
     </row>
   </sheetData>

--- a/clustered_output.xlsx
+++ b/clustered_output.xlsx
@@ -680,16 +680,16 @@
         <v>86.27647392</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H8" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>236.9722186769305</v>
+        <v>313.8902207082496</v>
       </c>
     </row>
     <row r="9">
@@ -711,16 +711,16 @@
         <v>91.16850180000002</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H9" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>295.3716828864031</v>
+        <v>373.4412154910133</v>
       </c>
     </row>
     <row r="10">
@@ -928,16 +928,16 @@
         <v>76.75563604999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>15.464</v>
+        <v>11.932</v>
       </c>
       <c r="H16" t="n">
-        <v>75</v>
+        <v>79.80800000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>401.849670130051</v>
+        <v>482.9249057213582</v>
       </c>
     </row>
     <row r="17">
@@ -990,16 +990,16 @@
         <v>112.80354775</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H18" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>179.8330479062113</v>
+        <v>259.8066720323735</v>
       </c>
     </row>
     <row r="19">
@@ -1083,16 +1083,16 @@
         <v>137.72677575</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H21" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>147.6369671603444</v>
+        <v>221.6520820103549</v>
       </c>
     </row>
     <row r="22">
@@ -1176,16 +1176,16 @@
         <v>75.03426994</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H24" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>20.47034300213973</v>
+        <v>96.0979610302295</v>
       </c>
     </row>
     <row r="25">
@@ -1238,16 +1238,16 @@
         <v>69.51707707</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H26" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>287.0633257945925</v>
+        <v>365.094204846208</v>
       </c>
     </row>
     <row r="27">
@@ -1331,16 +1331,16 @@
         <v>51.11150699</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H29" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>86.28571933028022</v>
+        <v>165.0508502095769</v>
       </c>
     </row>
     <row r="30">
@@ -1486,16 +1486,16 @@
         <v>40.91439332</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H34" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>137.0910817780116</v>
+        <v>212.1199935801126</v>
       </c>
     </row>
     <row r="35">
@@ -1579,16 +1579,16 @@
         <v>89.43269527999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H37" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>20.19869826917071</v>
+        <v>97.24880694316984</v>
       </c>
     </row>
     <row r="38">
@@ -1672,16 +1672,16 @@
         <v>97.86042042</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H40" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>275.726143177566</v>
+        <v>353.1698387461005</v>
       </c>
     </row>
     <row r="41">
@@ -1703,16 +1703,16 @@
         <v>120.70724466</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H41" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>80.39050753268133</v>
       </c>
     </row>
     <row r="42">
@@ -1765,16 +1765,16 @@
         <v>79.88549751000001</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H43" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>113.2095459182907</v>
+        <v>137.0103170103804</v>
       </c>
     </row>
     <row r="44">
@@ -1827,16 +1827,16 @@
         <v>58.83139722999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H45" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>266.6468275894603</v>
+        <v>345.3721164033507</v>
       </c>
     </row>
     <row r="46">
@@ -2013,16 +2013,16 @@
         <v>55.12580752</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H51" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>235.567208404973</v>
+        <v>312.8152737420051</v>
       </c>
     </row>
     <row r="52">
@@ -2044,16 +2044,16 @@
         <v>70.25959358</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H52" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>127.9311147058719</v>
+        <v>129.237268082056</v>
       </c>
     </row>
     <row r="53">
@@ -2106,16 +2106,16 @@
         <v>78.94616125999998</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H54" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>118.4108809723095</v>
+        <v>168.7100665885474</v>
       </c>
     </row>
     <row r="55">
@@ -2230,16 +2230,16 @@
         <v>49.10406079999999</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H58" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>124.8455044460658</v>
+        <v>113.6078870195936</v>
       </c>
     </row>
     <row r="59">
@@ -2323,16 +2323,16 @@
         <v>157.49350527</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H61" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>132.4012953218188</v>
+        <v>134.3181781165763</v>
       </c>
     </row>
     <row r="62">
@@ -2416,16 +2416,16 @@
         <v>33.56141599999999</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H64" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>237.0082605430272</v>
+        <v>313.8984511692369</v>
       </c>
     </row>
     <row r="65">
@@ -2447,16 +2447,16 @@
         <v>122.2742197</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H65" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>112.1216799225184</v>
+        <v>135.1903379520044</v>
       </c>
     </row>
     <row r="66">
@@ -2478,16 +2478,16 @@
         <v>29.31689904</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H66" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>290.2997824974207</v>
+        <v>368.0564818651708</v>
       </c>
     </row>
     <row r="67">
@@ -2540,16 +2540,16 @@
         <v>59.56919848</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H68" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>95.52643598416643</v>
+        <v>172.1305810020439</v>
       </c>
     </row>
     <row r="69">
@@ -2633,16 +2633,16 @@
         <v>8.5903492</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H71" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>124.8455044460658</v>
+        <v>113.6078870195936</v>
       </c>
     </row>
     <row r="72">
@@ -2757,16 +2757,16 @@
         <v>109.77473927</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H75" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>118.9906694931409</v>
+        <v>125.4618836507752</v>
       </c>
     </row>
     <row r="76">
@@ -2819,16 +2819,16 @@
         <v>127.09983192</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H77" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>127.0006139161995</v>
+        <v>124.2161967924599</v>
       </c>
     </row>
     <row r="78">
@@ -3005,16 +3005,16 @@
         <v>152.37332232</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H83" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>132.6130702067358</v>
+        <v>133.4087432163412</v>
       </c>
     </row>
     <row r="84">
@@ -3036,16 +3036,16 @@
         <v>137.64539505</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H84" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>125.6521233991047</v>
+        <v>130.3854760775766</v>
       </c>
     </row>
     <row r="85">
@@ -3067,16 +3067,16 @@
         <v>98.88650038</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H85" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>113.4975601647661</v>
+        <v>135.4730310847455</v>
       </c>
     </row>
     <row r="86">
@@ -3129,16 +3129,16 @@
         <v>131.72022438</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H87" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>288.7402552400748</v>
+        <v>366.6220584731958</v>
       </c>
     </row>
     <row r="88">
@@ -3160,16 +3160,16 @@
         <v>128.67002752</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H88" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>236.5461713897413</v>
+        <v>313.7181966978334</v>
       </c>
     </row>
     <row r="89">
@@ -3284,16 +3284,16 @@
         <v>160.7944185</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H92" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>134.3726052010849</v>
+        <v>132.2317631445825</v>
       </c>
     </row>
     <row r="93">
@@ -3315,16 +3315,16 @@
         <v>114.30460316</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H93" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I93" t="n">
-        <v>125.8855478394724</v>
+        <v>128.717486213771</v>
       </c>
     </row>
     <row r="94">
@@ -3377,16 +3377,16 @@
         <v>107.20581291</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H95" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>133.9028375627812</v>
+        <v>133.5541028711692</v>
       </c>
     </row>
     <row r="96">
@@ -3842,16 +3842,16 @@
         <v>135.40894881</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H110" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>288.3934749946374</v>
+        <v>366.1671710516097</v>
       </c>
     </row>
     <row r="111">
@@ -4059,16 +4059,16 @@
         <v>131.4488539</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H117" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I117" t="n">
-        <v>128.1772702393585</v>
+        <v>135.0580930295541</v>
       </c>
     </row>
     <row r="118">
@@ -4152,16 +4152,16 @@
         <v>26.29534809</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H120" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>288.7137580132629</v>
+        <v>366.5015755172517</v>
       </c>
     </row>
     <row r="121">
@@ -4245,16 +4245,16 @@
         <v>104.41013483</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H123" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I123" t="n">
-        <v>17.16754590109464</v>
+        <v>95.7324236102036</v>
       </c>
     </row>
     <row r="124">
@@ -4524,16 +4524,16 @@
         <v>148.1403535</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H132" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I132" t="n">
-        <v>69.52376245901762</v>
+        <v>45.92423917331701</v>
       </c>
     </row>
     <row r="133">
@@ -4617,16 +4617,16 @@
         <v>174.54029805</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H135" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>149.1626153246674</v>
+        <v>223.2616339193195</v>
       </c>
     </row>
     <row r="136">
@@ -4648,16 +4648,16 @@
         <v>71.22344247000001</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H136" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>123.6480037344783</v>
+        <v>135.9422927738292</v>
       </c>
     </row>
     <row r="137">
@@ -4679,16 +4679,16 @@
         <v>86.91646299999999</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H137" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I137" t="n">
-        <v>126.8999961435841</v>
+        <v>137.8924794813661</v>
       </c>
     </row>
     <row r="138">
@@ -4958,16 +4958,16 @@
         <v>169.43078549</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H146" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I146" t="n">
-        <v>16.86922051279774</v>
+        <v>94.38920284780231</v>
       </c>
     </row>
     <row r="147">
@@ -5206,16 +5206,16 @@
         <v>136.56314483</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H154" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I154" t="n">
-        <v>2.195284483350534</v>
+        <v>82.41961808376361</v>
       </c>
     </row>
     <row r="155">
@@ -5392,16 +5392,16 @@
         <v>138.15013296</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H160" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I160" t="n">
-        <v>286.0952964076756</v>
+        <v>363.830579906318</v>
       </c>
     </row>
     <row r="161">
@@ -5640,16 +5640,16 @@
         <v>53.785478</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H168" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I168" t="n">
-        <v>116.8619030719691</v>
+        <v>139.1536339413091</v>
       </c>
     </row>
     <row r="169">
@@ -5671,16 +5671,16 @@
         <v>145.0125221</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H169" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>67.14739972868296</v>
+        <v>50.54469560972741</v>
       </c>
     </row>
     <row r="170">
@@ -5857,16 +5857,16 @@
         <v>114.2480122</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G175" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H175" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>133.6289924038313</v>
+        <v>128.8557097613833</v>
       </c>
     </row>
     <row r="176">
@@ -5888,16 +5888,16 @@
         <v>148.70392757</v>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H176" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I176" t="n">
-        <v>181.4012272520388</v>
+        <v>261.3949162110506</v>
       </c>
     </row>
     <row r="177">
@@ -6229,16 +6229,16 @@
         <v>87.69854039000001</v>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H187" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>115.5589954023719</v>
+        <v>130.8889150933765</v>
       </c>
     </row>
     <row r="188">
@@ -6291,16 +6291,16 @@
         <v>135.95829359</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H189" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>128.3784927693047</v>
+        <v>126.5585470698784</v>
       </c>
     </row>
     <row r="190">
@@ -6353,16 +6353,16 @@
         <v>84.03368023</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H191" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I191" t="n">
-        <v>68.87078381624423</v>
+        <v>48.24146554135529</v>
       </c>
     </row>
     <row r="192">
@@ -6446,16 +6446,16 @@
         <v>69.75723010999999</v>
       </c>
       <c r="F194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G194" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H194" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I194" t="n">
-        <v>66.87147235620471</v>
+        <v>119.0492898577379</v>
       </c>
     </row>
     <row r="195">
@@ -6539,16 +6539,16 @@
         <v>51.23457499999999</v>
       </c>
       <c r="F197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H197" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I197" t="n">
-        <v>113.9739665090551</v>
+        <v>114.5356707531311</v>
       </c>
     </row>
     <row r="198">
@@ -6570,16 +6570,16 @@
         <v>62.39533672</v>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H198" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I198" t="n">
-        <v>116.9153879128728</v>
+        <v>193.5390688888536</v>
       </c>
     </row>
     <row r="199">
@@ -6725,16 +6725,16 @@
         <v>42.55748138000001</v>
       </c>
       <c r="F203" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" t="n">
+        <v>16.168</v>
+      </c>
+      <c r="H203" t="n">
+        <v>74.82899999999999</v>
+      </c>
+      <c r="I203" t="n">
         <v>0</v>
-      </c>
-      <c r="G203" t="n">
-        <v>15.464</v>
-      </c>
-      <c r="H203" t="n">
-        <v>75</v>
-      </c>
-      <c r="I203" t="n">
-        <v>80.39050753268133</v>
       </c>
     </row>
     <row r="204">
@@ -6787,16 +6787,16 @@
         <v>72.1073177</v>
       </c>
       <c r="F205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G205" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H205" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>104.8494011357226</v>
+        <v>109.6498692303138</v>
       </c>
     </row>
     <row r="206">
@@ -6818,16 +6818,16 @@
         <v>61.94020108000001</v>
       </c>
       <c r="F206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H206" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>159.4643923886767</v>
+        <v>177.0070370007507</v>
       </c>
     </row>
     <row r="207">
@@ -6849,16 +6849,16 @@
         <v>116.30465114</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H207" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I207" t="n">
-        <v>120.0040682159923</v>
+        <v>133.083631777126</v>
       </c>
     </row>
     <row r="208">
@@ -7004,16 +7004,16 @@
         <v>105.4919814</v>
       </c>
       <c r="F212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G212" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H212" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I212" t="n">
-        <v>108.1882747316393</v>
+        <v>128.4198979733378</v>
       </c>
     </row>
     <row r="213">
@@ -7038,13 +7038,13 @@
         <v>2</v>
       </c>
       <c r="G213" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H213" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I213" t="n">
-        <v>229.8607558359462</v>
+        <v>293.0078099324624</v>
       </c>
     </row>
     <row r="214">
@@ -7069,13 +7069,13 @@
         <v>2</v>
       </c>
       <c r="G214" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H214" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I214" t="n">
-        <v>225.064995129652</v>
+        <v>202.5074104591879</v>
       </c>
     </row>
     <row r="215">
@@ -7100,13 +7100,13 @@
         <v>2</v>
       </c>
       <c r="G215" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H215" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I215" t="n">
-        <v>419.672814067605</v>
+        <v>247.1484952508124</v>
       </c>
     </row>
     <row r="216">
@@ -7131,13 +7131,13 @@
         <v>2</v>
       </c>
       <c r="G216" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H216" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I216" t="n">
-        <v>377.8634954661895</v>
+        <v>7.877625454614061</v>
       </c>
     </row>
     <row r="217">
@@ -7162,13 +7162,13 @@
         <v>2</v>
       </c>
       <c r="G217" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H217" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I217" t="n">
-        <v>397.4782412309082</v>
+        <v>281.2353818778071</v>
       </c>
     </row>
     <row r="218">
@@ -7193,13 +7193,13 @@
         <v>2</v>
       </c>
       <c r="G218" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H218" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I218" t="n">
-        <v>333.5404278771352</v>
+        <v>272.7502614006317</v>
       </c>
     </row>
     <row r="219">
@@ -7224,13 +7224,13 @@
         <v>2</v>
       </c>
       <c r="G219" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H219" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I219" t="n">
-        <v>230.3482592715248</v>
+        <v>283.2494890916812</v>
       </c>
     </row>
     <row r="220">
@@ -7255,13 +7255,13 @@
         <v>2</v>
       </c>
       <c r="G220" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H220" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I220" t="n">
-        <v>415.1807710422817</v>
+        <v>244.5433569933228</v>
       </c>
     </row>
     <row r="221">
@@ -7286,13 +7286,13 @@
         <v>2</v>
       </c>
       <c r="G221" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H221" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I221" t="n">
-        <v>193.1966175896344</v>
+        <v>183.716888108934</v>
       </c>
     </row>
     <row r="222">
@@ -7317,13 +7317,13 @@
         <v>2</v>
       </c>
       <c r="G222" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H222" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I222" t="n">
-        <v>314.0855088794886</v>
+        <v>239.8845366495564</v>
       </c>
     </row>
     <row r="223">
@@ -7348,13 +7348,13 @@
         <v>2</v>
       </c>
       <c r="G223" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H223" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I223" t="n">
-        <v>384.9642702937756</v>
+        <v>310.008385160804</v>
       </c>
     </row>
     <row r="224">
@@ -7379,13 +7379,13 @@
         <v>2</v>
       </c>
       <c r="G224" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H224" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I224" t="n">
-        <v>189.8516782079799</v>
+        <v>186.8134948945622</v>
       </c>
     </row>
     <row r="225">
@@ -7410,13 +7410,13 @@
         <v>2</v>
       </c>
       <c r="G225" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H225" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I225" t="n">
-        <v>396.8570901951181</v>
+        <v>288.1586060236781</v>
       </c>
     </row>
     <row r="226">
@@ -7441,13 +7441,13 @@
         <v>2</v>
       </c>
       <c r="G226" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H226" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I226" t="n">
-        <v>352.345793583056</v>
+        <v>98.92707015264052</v>
       </c>
     </row>
     <row r="227">
@@ -7469,16 +7469,16 @@
         <v>65.836</v>
       </c>
       <c r="F227" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G227" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H227" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I227" t="n">
-        <v>537.3485840089204</v>
+        <v>280.6157282157816</v>
       </c>
     </row>
     <row r="228">
@@ -7503,13 +7503,13 @@
         <v>2</v>
       </c>
       <c r="G228" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H228" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I228" t="n">
-        <v>338.7538155998406</v>
+        <v>122.6538617562854</v>
       </c>
     </row>
     <row r="229">
@@ -7534,13 +7534,13 @@
         <v>2</v>
       </c>
       <c r="G229" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H229" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I229" t="n">
-        <v>417.4720974985719</v>
+        <v>247.2103171220905</v>
       </c>
     </row>
     <row r="230">
@@ -7565,13 +7565,13 @@
         <v>2</v>
       </c>
       <c r="G230" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H230" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I230" t="n">
-        <v>376.6730883738524</v>
+        <v>3.010294257504305</v>
       </c>
     </row>
     <row r="231">
@@ -7596,13 +7596,13 @@
         <v>2</v>
       </c>
       <c r="G231" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H231" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I231" t="n">
-        <v>412.7090821028135</v>
+        <v>243.5290276604762</v>
       </c>
     </row>
     <row r="232">
@@ -7627,13 +7627,13 @@
         <v>2</v>
       </c>
       <c r="G232" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H232" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I232" t="n">
-        <v>192.1475305672869</v>
+        <v>185.1941899725348</v>
       </c>
     </row>
     <row r="233">
@@ -7658,13 +7658,13 @@
         <v>2</v>
       </c>
       <c r="G233" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H233" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I233" t="n">
-        <v>344.0143888267083</v>
+        <v>122.5932704758844</v>
       </c>
     </row>
     <row r="234">
@@ -7689,13 +7689,13 @@
         <v>2</v>
       </c>
       <c r="G234" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H234" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I234" t="n">
-        <v>387.4842357033926</v>
+        <v>313.3976962041365</v>
       </c>
     </row>
     <row r="235">
@@ -7720,13 +7720,13 @@
         <v>2</v>
       </c>
       <c r="G235" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H235" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I235" t="n">
-        <v>224.5517052120445</v>
+        <v>200.1426029670162</v>
       </c>
     </row>
     <row r="236">
@@ -7751,13 +7751,13 @@
         <v>2</v>
       </c>
       <c r="G236" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H236" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I236" t="n">
-        <v>195.3516669208213</v>
+        <v>181.8544965050952</v>
       </c>
     </row>
     <row r="237">
@@ -7782,13 +7782,13 @@
         <v>2</v>
       </c>
       <c r="G237" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H237" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I237" t="n">
-        <v>414.2812049218847</v>
+        <v>245.6061953817163</v>
       </c>
     </row>
     <row r="238">
@@ -7813,13 +7813,13 @@
         <v>2</v>
       </c>
       <c r="G238" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H238" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I238" t="n">
-        <v>177.962552569528</v>
+        <v>245.0419989878996</v>
       </c>
     </row>
     <row r="239">
@@ -7841,16 +7841,16 @@
         <v>111.0064</v>
       </c>
       <c r="F239" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G239" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H239" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I239" t="n">
-        <v>536.8344550885704</v>
+        <v>278.9705714377981</v>
       </c>
     </row>
     <row r="240">
@@ -7875,13 +7875,13 @@
         <v>2</v>
       </c>
       <c r="G240" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H240" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I240" t="n">
-        <v>391.7037606540575</v>
+        <v>317.2531958489987</v>
       </c>
     </row>
     <row r="241">
@@ -7906,13 +7906,13 @@
         <v>2</v>
       </c>
       <c r="G241" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H241" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I241" t="n">
-        <v>397.5562571974353</v>
+        <v>285.0912735432133</v>
       </c>
     </row>
     <row r="242">
@@ -7937,13 +7937,13 @@
         <v>2</v>
       </c>
       <c r="G242" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H242" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I242" t="n">
-        <v>374.2917936817031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -7968,13 +7968,13 @@
         <v>2</v>
       </c>
       <c r="G243" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H243" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I243" t="n">
-        <v>414.4853399375517</v>
+        <v>245.1650961673219</v>
       </c>
     </row>
     <row r="244">
@@ -7999,13 +7999,13 @@
         <v>2</v>
       </c>
       <c r="G244" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H244" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I244" t="n">
-        <v>464.1934089637818</v>
+        <v>112.2709331769165</v>
       </c>
     </row>
     <row r="245">
@@ -8030,13 +8030,13 @@
         <v>2</v>
       </c>
       <c r="G245" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H245" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I245" t="n">
-        <v>198.5647588025095</v>
+        <v>178.0354467291626</v>
       </c>
     </row>
     <row r="246">
@@ -8061,13 +8061,13 @@
         <v>2</v>
       </c>
       <c r="G246" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H246" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I246" t="n">
-        <v>349.3139158828723</v>
+        <v>121.0099901785983</v>
       </c>
     </row>
     <row r="247">
@@ -8092,13 +8092,13 @@
         <v>2</v>
       </c>
       <c r="G247" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H247" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I247" t="n">
-        <v>201.5696038015792</v>
+        <v>176.0265855097184</v>
       </c>
     </row>
     <row r="248">
@@ -8123,13 +8123,13 @@
         <v>2</v>
       </c>
       <c r="G248" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H248" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I248" t="n">
-        <v>345.1333457202122</v>
+        <v>125.2053853727172</v>
       </c>
     </row>
     <row r="249">
@@ -8154,13 +8154,13 @@
         <v>2</v>
       </c>
       <c r="G249" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H249" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I249" t="n">
-        <v>410.8883422646456</v>
+        <v>243.0126961907182</v>
       </c>
     </row>
     <row r="250">
@@ -8185,13 +8185,13 @@
         <v>2</v>
       </c>
       <c r="G250" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H250" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I250" t="n">
-        <v>408.8581684202446</v>
+        <v>270.3924113793491</v>
       </c>
     </row>
     <row r="251">
@@ -8216,13 +8216,13 @@
         <v>2</v>
       </c>
       <c r="G251" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H251" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I251" t="n">
-        <v>464.582298371576</v>
+        <v>111.0756270606496</v>
       </c>
     </row>
     <row r="252">
@@ -8244,16 +8244,16 @@
         <v>22.082508</v>
       </c>
       <c r="F252" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G252" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H252" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I252" t="n">
-        <v>32.60451440507697</v>
+        <v>654.0495989705499</v>
       </c>
     </row>
     <row r="253">
@@ -8275,16 +8275,16 @@
         <v>26.1654</v>
       </c>
       <c r="F253" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H253" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I253" t="n">
-        <v>94.35960271226369</v>
+        <v>657.2556533005184</v>
       </c>
     </row>
     <row r="254">
@@ -8306,16 +8306,16 @@
         <v>41.9052</v>
       </c>
       <c r="F254" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H254" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I254" t="n">
-        <v>384.5799275406081</v>
+        <v>675.9752592101149</v>
       </c>
     </row>
     <row r="255">
@@ -8337,16 +8337,16 @@
         <v>898.0380000000002</v>
       </c>
       <c r="F255" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H255" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I255" t="n">
-        <v>482.00735820496</v>
+        <v>817.8434851869102</v>
       </c>
     </row>
     <row r="256">
@@ -8368,16 +8368,16 @@
         <v>13.4594</v>
       </c>
       <c r="F256" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G256" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H256" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I256" t="n">
-        <v>482.4906943718859</v>
+        <v>815.968363029575</v>
       </c>
     </row>
     <row r="257">
@@ -8399,16 +8399,16 @@
         <v>109.8696</v>
       </c>
       <c r="F257" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G257" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H257" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I257" t="n">
-        <v>92.64544990077594</v>
+        <v>674.8402225814028</v>
       </c>
     </row>
     <row r="258">
@@ -8430,16 +8430,16 @@
         <v>128.60566</v>
       </c>
       <c r="F258" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G258" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H258" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I258" t="n">
-        <v>75.2899228366535</v>
+        <v>612.0341294292925</v>
       </c>
     </row>
     <row r="259">
@@ -8461,16 +8461,16 @@
         <v>571.5419999999999</v>
       </c>
       <c r="F259" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H259" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I259" t="n">
-        <v>508.8891223415916</v>
+        <v>963.8383437771967</v>
       </c>
     </row>
     <row r="260">
@@ -8492,16 +8492,16 @@
         <v>122.977441</v>
       </c>
       <c r="F260" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H260" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I260" t="n">
-        <v>552.3573847787909</v>
+        <v>1164.946296812177</v>
       </c>
     </row>
     <row r="261">
@@ -8523,16 +8523,16 @@
         <v>131.0654675</v>
       </c>
       <c r="F261" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H261" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I261" t="n">
-        <v>102.3489899239865</v>
+        <v>606.305712694481</v>
       </c>
     </row>
     <row r="262">
@@ -8554,16 +8554,16 @@
         <v>95.62609999999999</v>
       </c>
       <c r="F262" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H262" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I262" t="n">
-        <v>522.1664319142777</v>
+        <v>1115.734345326284</v>
       </c>
     </row>
     <row r="263">
@@ -8585,16 +8585,16 @@
         <v>106.7479</v>
       </c>
       <c r="F263" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H263" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I263" t="n">
-        <v>95.57020709971071</v>
+        <v>608.9859326801146</v>
       </c>
     </row>
     <row r="264">
@@ -8616,16 +8616,16 @@
         <v>123.2049255</v>
       </c>
       <c r="F264" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G264" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H264" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I264" t="n">
-        <v>96.70476762895548</v>
+        <v>611.2631367385069</v>
       </c>
     </row>
     <row r="265">
@@ -8647,16 +8647,16 @@
         <v>284.046</v>
       </c>
       <c r="F265" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H265" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I265" t="n">
-        <v>510.5175932013258</v>
+        <v>963.0548320685086</v>
       </c>
     </row>
     <row r="266">
@@ -8678,16 +8678,16 @@
         <v>995.3472000000002</v>
       </c>
       <c r="F266" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H266" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I266" t="n">
-        <v>390.1597548737963</v>
+        <v>672.5567599657647</v>
       </c>
     </row>
     <row r="267">
@@ -8709,16 +8709,16 @@
         <v>56.9948</v>
       </c>
       <c r="F267" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G267" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H267" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I267" t="n">
-        <v>92.28373519837209</v>
+        <v>672.4465575073634</v>
       </c>
     </row>
     <row r="268">
@@ -8740,16 +8740,16 @@
         <v>162.227688</v>
       </c>
       <c r="F268" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G268" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H268" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I268" t="n">
-        <v>595.7184877137429</v>
+        <v>1203.997132895375</v>
       </c>
     </row>
     <row r="269">
@@ -8771,16 +8771,16 @@
         <v>93.85904950000001</v>
       </c>
       <c r="F269" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H269" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I269" t="n">
-        <v>589.7659034972133</v>
+        <v>1193.182341268439</v>
       </c>
     </row>
     <row r="270">
@@ -8802,16 +8802,16 @@
         <v>72.16600000000001</v>
       </c>
       <c r="F270" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H270" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I270" t="n">
-        <v>93.68564527290076</v>
+        <v>644.2755978585902</v>
       </c>
     </row>
     <row r="271">
@@ -8833,16 +8833,16 @@
         <v>77.25859999999999</v>
       </c>
       <c r="F271" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H271" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I271" t="n">
-        <v>94.17527792394209</v>
+        <v>677.9672674443422</v>
       </c>
     </row>
     <row r="272">
@@ -8864,16 +8864,16 @@
         <v>72.49699999999999</v>
       </c>
       <c r="F272" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H272" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I272" t="n">
-        <v>112.4783746360528</v>
+        <v>631.4230938985899</v>
       </c>
     </row>
     <row r="273">
@@ -8895,16 +8895,16 @@
         <v>186.4224215</v>
       </c>
       <c r="F273" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H273" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I273" t="n">
-        <v>94.45839254828898</v>
+        <v>614.0519087916215</v>
       </c>
     </row>
     <row r="274">
@@ -8926,16 +8926,16 @@
         <v>150.1102</v>
       </c>
       <c r="F274" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H274" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I274" t="n">
-        <v>92.67265559598945</v>
+        <v>676.8304565487422</v>
       </c>
     </row>
     <row r="275">
@@ -8957,16 +8957,16 @@
         <v>71.23049999999999</v>
       </c>
       <c r="F275" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H275" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I275" t="n">
-        <v>112.6132028265503</v>
+        <v>631.0355120310412</v>
       </c>
     </row>
     <row r="276">
@@ -8988,16 +8988,16 @@
         <v>222.122161</v>
       </c>
       <c r="F276" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G276" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H276" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I276" t="n">
-        <v>99.02980389832064</v>
+        <v>609.5555961033466</v>
       </c>
     </row>
     <row r="277">
@@ -9019,16 +9019,16 @@
         <v>243.76794</v>
       </c>
       <c r="F277" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H277" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I277" t="n">
-        <v>97.27427688122583</v>
+        <v>608.8754363832121</v>
       </c>
     </row>
     <row r="278">
@@ -9050,16 +9050,16 @@
         <v>59.30860000000001</v>
       </c>
       <c r="F278" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H278" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I278" t="n">
-        <v>91.50333000873195</v>
+        <v>658.1793923461422</v>
       </c>
     </row>
     <row r="279">
@@ -9081,16 +9081,16 @@
         <v>200.4813</v>
       </c>
       <c r="F279" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H279" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I279" t="n">
-        <v>95.99397161868814</v>
+        <v>610.8968516256235</v>
       </c>
     </row>
     <row r="280">
@@ -9112,16 +9112,16 @@
         <v>152.1270185</v>
       </c>
       <c r="F280" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H280" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I280" t="n">
-        <v>550.7295808016556</v>
+        <v>1163.290649839514</v>
       </c>
     </row>
     <row r="281">
@@ -9143,16 +9143,16 @@
         <v>100.023278</v>
       </c>
       <c r="F281" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H281" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>682.8607730764215</v>
       </c>
     </row>
     <row r="282">
@@ -9174,16 +9174,16 @@
         <v>65.61912249999999</v>
       </c>
       <c r="F282" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H282" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I282" t="n">
-        <v>94.37343372652148</v>
+        <v>614.5896566494074</v>
       </c>
     </row>
     <row r="283">
@@ -9205,16 +9205,16 @@
         <v>59.61479999999999</v>
       </c>
       <c r="F283" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H283" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I283" t="n">
-        <v>386.5114632433878</v>
+        <v>674.5450306216281</v>
       </c>
     </row>
     <row r="284">
@@ -9236,16 +9236,16 @@
         <v>92.10120000000001</v>
       </c>
       <c r="F284" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H284" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I284" t="n">
-        <v>384.2393599367526</v>
+        <v>675.9572730490926</v>
       </c>
     </row>
     <row r="285">
@@ -9267,16 +9267,16 @@
         <v>87.2212</v>
       </c>
       <c r="F285" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H285" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I285" t="n">
-        <v>99.63501088455672</v>
+        <v>612.5478935079946</v>
       </c>
     </row>
     <row r="286">
@@ -9298,16 +9298,16 @@
         <v>44.383</v>
       </c>
       <c r="F286" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H286" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I286" t="n">
-        <v>92.73566034601555</v>
+        <v>676.9222917950851</v>
       </c>
     </row>
     <row r="287">
@@ -9329,16 +9329,16 @@
         <v>72.4555</v>
       </c>
       <c r="F287" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G287" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H287" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I287" t="n">
-        <v>106.8588974613416</v>
+        <v>647.8696570805542</v>
       </c>
     </row>
     <row r="288">
@@ -9360,16 +9360,16 @@
         <v>228.606</v>
       </c>
       <c r="F288" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H288" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I288" t="n">
-        <v>515.496387359597</v>
+        <v>926.223743210367</v>
       </c>
     </row>
     <row r="289">
@@ -9391,16 +9391,16 @@
         <v>106.680992</v>
       </c>
       <c r="F289" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H289" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I289" t="n">
-        <v>469.4482391051256</v>
+        <v>1080.796368673745</v>
       </c>
     </row>
     <row r="290">
@@ -9422,16 +9422,16 @@
         <v>118.29098</v>
       </c>
       <c r="F290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G290" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H290" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I290" t="n">
-        <v>259.5176719658174</v>
+        <v>198.7340174551869</v>
       </c>
     </row>
     <row r="291">
@@ -9453,16 +9453,16 @@
         <v>56.55883999999998</v>
       </c>
       <c r="F291" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G291" t="n">
-        <v>21.473</v>
+        <v>11.932</v>
       </c>
       <c r="H291" t="n">
-        <v>83.968</v>
+        <v>79.80800000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>605.7632706899564</v>
+        <v>544.7410571565025</v>
       </c>
     </row>
     <row r="292">
@@ -9484,16 +9484,16 @@
         <v>99.75030000000001</v>
       </c>
       <c r="F292" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G292" t="n">
-        <v>15.464</v>
+        <v>11.932</v>
       </c>
       <c r="H292" t="n">
-        <v>75</v>
+        <v>79.80800000000001</v>
       </c>
       <c r="I292" t="n">
-        <v>293.1002567845545</v>
+        <v>387.1866027474242</v>
       </c>
     </row>
     <row r="293">
@@ -9515,16 +9515,16 @@
         <v>76.35709999999999</v>
       </c>
       <c r="F293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H293" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I293" t="n">
-        <v>150.3854486811032</v>
+        <v>194.2098531519203</v>
       </c>
     </row>
     <row r="294">
@@ -9546,16 +9546,16 @@
         <v>65.98963999999999</v>
       </c>
       <c r="F294" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G294" t="n">
-        <v>21.473</v>
+        <v>11.932</v>
       </c>
       <c r="H294" t="n">
-        <v>83.968</v>
+        <v>79.80800000000001</v>
       </c>
       <c r="I294" t="n">
-        <v>609.8136359579141</v>
+        <v>548.8846081556392</v>
       </c>
     </row>
     <row r="295">
@@ -9608,16 +9608,16 @@
         <v>80.12326000000002</v>
       </c>
       <c r="F296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H296" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I296" t="n">
-        <v>159.1709720886669</v>
+        <v>86.85520254824165</v>
       </c>
     </row>
     <row r="297">
@@ -9670,16 +9670,16 @@
         <v>113.30992</v>
       </c>
       <c r="F298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G298" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H298" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>168.3179946113131</v>
+        <v>119.0213435784231</v>
       </c>
     </row>
     <row r="299">
@@ -9701,16 +9701,16 @@
         <v>43.52612</v>
       </c>
       <c r="F299" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G299" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H299" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I299" t="n">
-        <v>428.7166743978141</v>
+        <v>538.8914330460158</v>
       </c>
     </row>
     <row r="300">
@@ -9732,16 +9732,16 @@
         <v>108.32342</v>
       </c>
       <c r="F300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H300" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I300" t="n">
-        <v>159.0016671290651</v>
+        <v>78.71036800981535</v>
       </c>
     </row>
     <row r="301">
@@ -9763,16 +9763,16 @@
         <v>51.79328</v>
       </c>
       <c r="F301" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G301" t="n">
-        <v>21.473</v>
+        <v>11.932</v>
       </c>
       <c r="H301" t="n">
-        <v>83.968</v>
+        <v>79.80800000000001</v>
       </c>
       <c r="I301" t="n">
-        <v>546.1529639801837</v>
+        <v>603.7872090098596</v>
       </c>
     </row>
     <row r="302">
@@ -9794,16 +9794,16 @@
         <v>68.9781</v>
       </c>
       <c r="F302" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G302" t="n">
-        <v>21.473</v>
+        <v>11.932</v>
       </c>
       <c r="H302" t="n">
-        <v>83.968</v>
+        <v>79.80800000000001</v>
       </c>
       <c r="I302" t="n">
-        <v>533.9820761041468</v>
+        <v>616.9081733070692</v>
       </c>
     </row>
     <row r="303">
@@ -9825,16 +9825,16 @@
         <v>69.73756</v>
       </c>
       <c r="F303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G303" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H303" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I303" t="n">
-        <v>418.1241507146969</v>
+        <v>527.9392354103214</v>
       </c>
     </row>
     <row r="304">
@@ -9856,16 +9856,16 @@
         <v>116.13984</v>
       </c>
       <c r="F304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G304" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H304" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I304" t="n">
-        <v>423.8519858386172</v>
+        <v>531.8289470141855</v>
       </c>
     </row>
     <row r="305">
@@ -9887,16 +9887,16 @@
         <v>100.22104</v>
       </c>
       <c r="F305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H305" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I305" t="n">
-        <v>421.0250492420701</v>
+        <v>529.237097246131</v>
       </c>
     </row>
     <row r="306">
@@ -9918,16 +9918,16 @@
         <v>124.95866</v>
       </c>
       <c r="F306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H306" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I306" t="n">
-        <v>264.9868752387629</v>
+        <v>203.4974733212369</v>
       </c>
     </row>
     <row r="307">
@@ -9949,16 +9949,16 @@
         <v>106.6222</v>
       </c>
       <c r="F307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G307" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H307" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I307" t="n">
-        <v>210.2618162320152</v>
+        <v>252.3661619701822</v>
       </c>
     </row>
     <row r="308">
@@ -9980,16 +9980,16 @@
         <v>37.92908</v>
       </c>
       <c r="F308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H308" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I308" t="n">
-        <v>156.6116107346159</v>
+        <v>82.74655715101427</v>
       </c>
     </row>
     <row r="309">
@@ -10011,16 +10011,16 @@
         <v>76.79181999999999</v>
       </c>
       <c r="F309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G309" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H309" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I309" t="n">
-        <v>334.4914004993488</v>
+        <v>463.2446918697619</v>
       </c>
     </row>
     <row r="310">
@@ -10073,16 +10073,16 @@
         <v>153.85138</v>
       </c>
       <c r="F311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H311" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I311" t="n">
-        <v>159.3858112034838</v>
+        <v>86.05735771627984</v>
       </c>
     </row>
     <row r="312">
@@ -10104,16 +10104,16 @@
         <v>178.5294</v>
       </c>
       <c r="F312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H312" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I312" t="n">
-        <v>262.7876734784617</v>
+        <v>201.8025101671006</v>
       </c>
     </row>
     <row r="313">
@@ -10135,16 +10135,16 @@
         <v>138.3113</v>
       </c>
       <c r="F313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G313" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H313" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I313" t="n">
-        <v>161.1344693495137</v>
+        <v>80.97729077071845</v>
       </c>
     </row>
     <row r="314">
@@ -10166,16 +10166,16 @@
         <v>148.35608</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H314" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I314" t="n">
-        <v>269.070535269441</v>
+        <v>190.3923763892437</v>
       </c>
     </row>
     <row r="315">
@@ -10197,16 +10197,16 @@
         <v>137.84592</v>
       </c>
       <c r="F315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H315" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I315" t="n">
-        <v>302.8133964563956</v>
+        <v>222.8034198030452</v>
       </c>
     </row>
     <row r="316">
@@ -10228,16 +10228,16 @@
         <v>71.19014000000001</v>
       </c>
       <c r="F316" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G316" t="n">
-        <v>21.473</v>
+        <v>11.932</v>
       </c>
       <c r="H316" t="n">
-        <v>83.968</v>
+        <v>79.80800000000001</v>
       </c>
       <c r="I316" t="n">
-        <v>546.9836780811395</v>
+        <v>603.0193547423979</v>
       </c>
     </row>
     <row r="317">
@@ -10259,16 +10259,16 @@
         <v>106.50236</v>
       </c>
       <c r="F317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G317" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H317" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I317" t="n">
-        <v>219.3930996632319</v>
+        <v>141.0264587247838</v>
       </c>
     </row>
     <row r="318">
@@ -10290,16 +10290,16 @@
         <v>97.77134</v>
       </c>
       <c r="F318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H318" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I318" t="n">
-        <v>147.6196537445319</v>
+        <v>69.42924372265375</v>
       </c>
     </row>
     <row r="319">
@@ -10321,16 +10321,16 @@
         <v>80.68743999999998</v>
       </c>
       <c r="F319" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G319" t="n">
-        <v>21.473</v>
+        <v>11.932</v>
       </c>
       <c r="H319" t="n">
-        <v>83.968</v>
+        <v>79.80800000000001</v>
       </c>
       <c r="I319" t="n">
-        <v>532.3398390756205</v>
+        <v>618.5065503160432</v>
       </c>
     </row>
     <row r="320">
@@ -10352,16 +10352,16 @@
         <v>92.23769999999999</v>
       </c>
       <c r="F320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G320" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H320" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I320" t="n">
-        <v>378.8590788971603</v>
+        <v>487.1237354251166</v>
       </c>
     </row>
     <row r="321">
@@ -10383,16 +10383,16 @@
         <v>111.7828</v>
       </c>
       <c r="F321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H321" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I321" t="n">
-        <v>421.7867030321074</v>
+        <v>531.2351788345484</v>
       </c>
     </row>
     <row r="322">
@@ -10414,16 +10414,16 @@
         <v>120.6901</v>
       </c>
       <c r="F322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H322" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I322" t="n">
-        <v>247.9904061596499</v>
+        <v>186.2355242450767</v>
       </c>
     </row>
     <row r="323">
@@ -10445,16 +10445,16 @@
         <v>51.7548</v>
       </c>
       <c r="F323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G323" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H323" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I323" t="n">
-        <v>209.2437086968674</v>
+        <v>251.1461470689249</v>
       </c>
     </row>
     <row r="324">
@@ -10476,16 +10476,16 @@
         <v>162.11432</v>
       </c>
       <c r="F324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H324" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I324" t="n">
-        <v>171.5610975856906</v>
+        <v>120.577629179741</v>
       </c>
     </row>
     <row r="325">
@@ -10507,16 +10507,16 @@
         <v>70.43834</v>
       </c>
       <c r="F325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G325" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H325" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I325" t="n">
-        <v>278.4183922634941</v>
+        <v>205.6885865734318</v>
       </c>
     </row>
     <row r="326">
@@ -10538,16 +10538,16 @@
         <v>97.17318</v>
       </c>
       <c r="F326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H326" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I326" t="n">
-        <v>156.8727092762293</v>
+        <v>76.50570748630093</v>
       </c>
     </row>
     <row r="327">
@@ -10569,16 +10569,16 @@
         <v>96.64926</v>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H327" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I327" t="n">
-        <v>419.9714842742374</v>
+        <v>527.7266766298554</v>
       </c>
     </row>
     <row r="328">
@@ -10600,16 +10600,16 @@
         <v>136.70414</v>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G328" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H328" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I328" t="n">
-        <v>413.2442366380896</v>
+        <v>520.9953547597188</v>
       </c>
     </row>
     <row r="329">
@@ -10631,16 +10631,16 @@
         <v>55.98389999999999</v>
       </c>
       <c r="F329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H329" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I329" t="n">
-        <v>177.6925516581376</v>
+        <v>222.2658331540372</v>
       </c>
     </row>
     <row r="330">
@@ -10662,16 +10662,16 @@
         <v>57.27579999999999</v>
       </c>
       <c r="F330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H330" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I330" t="n">
-        <v>164.433344750549</v>
+        <v>199.6643731663934</v>
       </c>
     </row>
     <row r="331">
@@ -10693,16 +10693,16 @@
         <v>100.51814</v>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G331" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H331" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I331" t="n">
-        <v>428.9474955583875</v>
+        <v>538.6129929671619</v>
       </c>
     </row>
     <row r="332">
@@ -10724,16 +10724,16 @@
         <v>72.68213999999999</v>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H332" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I332" t="n">
-        <v>353.350985394453</v>
+        <v>452.6327905269922</v>
       </c>
     </row>
     <row r="333">
@@ -10755,16 +10755,16 @@
         <v>53.00724</v>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G333" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H333" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I333" t="n">
-        <v>427.7753898421324</v>
+        <v>536.5966643261706</v>
       </c>
     </row>
     <row r="334">
@@ -10786,16 +10786,16 @@
         <v>84.78078000000001</v>
       </c>
       <c r="F334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G334" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H334" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I334" t="n">
-        <v>264.8709808666407</v>
+        <v>204.2617751928779</v>
       </c>
     </row>
     <row r="335">
@@ -10817,16 +10817,16 @@
         <v>97.36683999999997</v>
       </c>
       <c r="F335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H335" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I335" t="n">
-        <v>105.7153231447665</v>
+        <v>88.32300385715907</v>
       </c>
     </row>
     <row r="336">
@@ -10848,16 +10848,16 @@
         <v>81.07180000000001</v>
       </c>
       <c r="F336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H336" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I336" t="n">
-        <v>325.683184610459</v>
+        <v>261.7827362413553</v>
       </c>
     </row>
     <row r="337">
@@ -10879,16 +10879,16 @@
         <v>51.87629999999999</v>
       </c>
       <c r="F337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G337" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H337" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I337" t="n">
-        <v>193.1659403726651</v>
+        <v>115.2811620794281</v>
       </c>
     </row>
     <row r="338">
@@ -10910,16 +10910,16 @@
         <v>164.81286</v>
       </c>
       <c r="F338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H338" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I338" t="n">
-        <v>228.6386816114776</v>
+        <v>232.0059275504088</v>
       </c>
     </row>
     <row r="339">
@@ -10941,16 +10941,16 @@
         <v>137.11044</v>
       </c>
       <c r="F339" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H339" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I339" t="n">
-        <v>239.9271333422346</v>
+        <v>449.5295655318793</v>
       </c>
     </row>
     <row r="340">
@@ -10972,16 +10972,16 @@
         <v>105.60097665</v>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H340" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I340" t="n">
-        <v>234.2369337173518</v>
+        <v>240.0194910557429</v>
       </c>
     </row>
     <row r="341">
@@ -11003,16 +11003,16 @@
         <v>85.30447965</v>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H341" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I341" t="n">
-        <v>226.8159864422877</v>
+        <v>222.1309978696864</v>
       </c>
     </row>
     <row r="342">
@@ -11034,16 +11034,16 @@
         <v>105.13692</v>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H342" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I342" t="n">
-        <v>3.05245814029515</v>
+        <v>127.1752096431898</v>
       </c>
     </row>
     <row r="343">
@@ -11065,16 +11065,16 @@
         <v>119.39315505</v>
       </c>
       <c r="F343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H343" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I343" t="n">
-        <v>232.7606295976149</v>
+        <v>237.1583322501107</v>
       </c>
     </row>
     <row r="344">
@@ -11096,16 +11096,16 @@
         <v>135.2097</v>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H344" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I344" t="n">
-        <v>44.63230629408451</v>
+        <v>100.561335805435</v>
       </c>
     </row>
     <row r="345">
@@ -11127,16 +11127,16 @@
         <v>103.2224895</v>
       </c>
       <c r="F345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H345" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I345" t="n">
-        <v>235.6425339063696</v>
+        <v>239.4850953574745</v>
       </c>
     </row>
     <row r="346">
@@ -11158,16 +11158,16 @@
         <v>105.68844</v>
       </c>
       <c r="F346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H346" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I346" t="n">
-        <v>236.3926209841623</v>
+        <v>237.2460590733673</v>
       </c>
     </row>
     <row r="347">
@@ -11189,16 +11189,16 @@
         <v>92.92085999999999</v>
       </c>
       <c r="F347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H347" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I347" t="n">
-        <v>228.7898553040338</v>
+        <v>229.7705905025527</v>
       </c>
     </row>
     <row r="348">
@@ -11220,16 +11220,16 @@
         <v>105.6147144</v>
       </c>
       <c r="F348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H348" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I348" t="n">
-        <v>238.3826140048343</v>
+        <v>244.4377595014983</v>
       </c>
     </row>
     <row r="349">
@@ -11251,16 +11251,16 @@
         <v>96.36005999999999</v>
       </c>
       <c r="F349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H349" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I349" t="n">
-        <v>126.9259514787582</v>
+        <v>4.323769153544565</v>
       </c>
     </row>
     <row r="350">
@@ -11282,16 +11282,16 @@
         <v>81.90635999999998</v>
       </c>
       <c r="F350" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H350" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I350" t="n">
-        <v>240.990457513337</v>
+        <v>449.0060316398882</v>
       </c>
     </row>
     <row r="351">
@@ -11313,16 +11313,16 @@
         <v>103.29378</v>
       </c>
       <c r="F351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H351" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I351" t="n">
-        <v>221.672979833551</v>
+        <v>218.5983957853651</v>
       </c>
     </row>
     <row r="352">
@@ -11344,16 +11344,16 @@
         <v>69.66414</v>
       </c>
       <c r="F352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H352" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I352" t="n">
-        <v>123.2451849638042</v>
+        <v>8.425493051359885</v>
       </c>
     </row>
     <row r="353">
@@ -11375,16 +11375,16 @@
         <v>133.07976</v>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H353" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I353" t="n">
-        <v>232.446583431369</v>
+        <v>240.1142041561907</v>
       </c>
     </row>
     <row r="354">
@@ -11406,16 +11406,16 @@
         <v>99.53225999999999</v>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H354" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I354" t="n">
-        <v>135.9227728142532</v>
+        <v>158.5486842150996</v>
       </c>
     </row>
     <row r="355">
@@ -11437,16 +11437,16 @@
         <v>174.81366</v>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H355" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I355" t="n">
-        <v>268.5129992494262</v>
+        <v>288.7749920793257</v>
       </c>
     </row>
     <row r="356">
@@ -11468,16 +11468,16 @@
         <v>123.87336</v>
       </c>
       <c r="F356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H356" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I356" t="n">
-        <v>123.2245237075969</v>
+        <v>7.332740432389794</v>
       </c>
     </row>
     <row r="357">
@@ -11499,16 +11499,16 @@
         <v>147.74808</v>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H357" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I357" t="n">
-        <v>0</v>
+        <v>130.1980141958676</v>
       </c>
     </row>
     <row r="358">
@@ -11530,16 +11530,16 @@
         <v>148.73862</v>
       </c>
       <c r="F358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G358" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H358" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I358" t="n">
-        <v>229.2048316902433</v>
+        <v>223.2984791795251</v>
       </c>
     </row>
     <row r="359">
@@ -11561,16 +11561,16 @@
         <v>273.06534</v>
       </c>
       <c r="F359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H359" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I359" t="n">
-        <v>229.5926036582196</v>
+        <v>231.7447165935054</v>
       </c>
     </row>
     <row r="360">
@@ -11592,16 +11592,16 @@
         <v>108.07158</v>
       </c>
       <c r="F360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H360" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I360" t="n">
-        <v>231.8062255945751</v>
+        <v>238.1460451158673</v>
       </c>
     </row>
     <row r="361">
@@ -11623,16 +11623,16 @@
         <v>154.62948</v>
       </c>
       <c r="F361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H361" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I361" t="n">
-        <v>254.7217919902353</v>
+        <v>327.1629857666452</v>
       </c>
     </row>
     <row r="362">
@@ -11654,16 +11654,16 @@
         <v>133.61611575</v>
       </c>
       <c r="F362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G362" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H362" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I362" t="n">
-        <v>236.9675286822333</v>
+        <v>241.906309273428</v>
       </c>
     </row>
     <row r="363">
@@ -11685,16 +11685,16 @@
         <v>107.2794</v>
       </c>
       <c r="F363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H363" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I363" t="n">
-        <v>236.042639746664</v>
+        <v>239.2561349257448</v>
       </c>
     </row>
     <row r="364">
@@ -11716,16 +11716,16 @@
         <v>90.89004</v>
       </c>
       <c r="F364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H364" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I364" t="n">
-        <v>231.0797650168059</v>
+        <v>240.5813123263519</v>
       </c>
     </row>
     <row r="365">
@@ -11747,16 +11747,16 @@
         <v>65.39706</v>
       </c>
       <c r="F365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H365" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I365" t="n">
-        <v>236.7708126174289</v>
+        <v>240.5344159522229</v>
       </c>
     </row>
     <row r="366">
@@ -11778,16 +11778,16 @@
         <v>93.90606000000002</v>
       </c>
       <c r="F366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H366" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I366" t="n">
-        <v>130.1980141958676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -11809,16 +11809,16 @@
         <v>102.0003</v>
       </c>
       <c r="F367" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>26.855</v>
+        <v>22.254</v>
       </c>
       <c r="H367" t="n">
-        <v>89.38200000000001</v>
+        <v>84.908</v>
       </c>
       <c r="I367" t="n">
-        <v>184.798244502207</v>
+        <v>498.0659858878445</v>
       </c>
     </row>
     <row r="368">
@@ -11840,16 +11840,16 @@
         <v>69.34979999999999</v>
       </c>
       <c r="F368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H368" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I368" t="n">
-        <v>229.820113327984</v>
+        <v>246.9743443515833</v>
       </c>
     </row>
     <row r="369">
@@ -11871,16 +11871,16 @@
         <v>147.48796146</v>
       </c>
       <c r="F369" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G369" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H369" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I369" t="n">
-        <v>39.15438497735472</v>
+        <v>684.6377060686082</v>
       </c>
     </row>
     <row r="370">
@@ -11902,16 +11902,16 @@
         <v>81.62645259999999</v>
       </c>
       <c r="F370" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G370" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H370" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I370" t="n">
-        <v>12.57090271495102</v>
+        <v>667.059677017294</v>
       </c>
     </row>
     <row r="371">
@@ -11933,16 +11933,16 @@
         <v>125.7125763</v>
       </c>
       <c r="F371" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G371" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H371" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I371" t="n">
-        <v>342.4939796860908</v>
+        <v>345.4761940888005</v>
       </c>
     </row>
     <row r="372">
@@ -11964,16 +11964,16 @@
         <v>118.30654686</v>
       </c>
       <c r="F372" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G372" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H372" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I372" t="n">
-        <v>154.5296365267789</v>
+        <v>809.6372609406922</v>
       </c>
     </row>
     <row r="373">
@@ -11995,16 +11995,16 @@
         <v>46.7992934</v>
       </c>
       <c r="F373" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G373" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H373" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I373" t="n">
-        <v>37.91710526660902</v>
+        <v>692.5646945749191</v>
       </c>
     </row>
     <row r="374">
@@ -12026,16 +12026,16 @@
         <v>135.638204</v>
       </c>
       <c r="F374" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G374" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H374" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I374" t="n">
-        <v>42.66602307691792</v>
+        <v>697.059202201161</v>
       </c>
     </row>
     <row r="375">
@@ -12057,16 +12057,16 @@
         <v>82.8659857</v>
       </c>
       <c r="F375" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G375" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H375" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I375" t="n">
-        <v>13.54667643358147</v>
+        <v>667.4029191074147</v>
       </c>
     </row>
     <row r="376">
@@ -12088,16 +12088,16 @@
         <v>105.553257</v>
       </c>
       <c r="F376" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G376" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H376" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I376" t="n">
-        <v>6.482501230056271</v>
+        <v>661.9466054945206</v>
       </c>
     </row>
     <row r="377">
@@ -12119,16 +12119,16 @@
         <v>71.35351295999999</v>
       </c>
       <c r="F377" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G377" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H377" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I377" t="n">
-        <v>159.5564405282327</v>
+        <v>814.7567434639592</v>
       </c>
     </row>
     <row r="378">
@@ -12150,16 +12150,16 @@
         <v>102.73411212</v>
       </c>
       <c r="F378" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G378" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H378" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I378" t="n">
-        <v>157.9057503839281</v>
+        <v>812.9217188777502</v>
       </c>
     </row>
     <row r="379">
@@ -12181,16 +12181,16 @@
         <v>128.5971056</v>
       </c>
       <c r="F379" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G379" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H379" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I379" t="n">
-        <v>11.61629237416503</v>
+        <v>666.8206222346315</v>
       </c>
     </row>
     <row r="380">
@@ -12212,16 +12212,16 @@
         <v>62.78045063999999</v>
       </c>
       <c r="F380" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G380" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H380" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I380" t="n">
-        <v>123.5969250984457</v>
+        <v>773.9366265170798</v>
       </c>
     </row>
     <row r="381">
@@ -12243,16 +12243,16 @@
         <v>109.3731514</v>
       </c>
       <c r="F381" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G381" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H381" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I381" t="n">
-        <v>318.263518593437</v>
+        <v>395.2977564697037</v>
       </c>
     </row>
     <row r="382">
@@ -12274,16 +12274,16 @@
         <v>119.1499458</v>
       </c>
       <c r="F382" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G382" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H382" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I382" t="n">
-        <v>9.701676387079416</v>
+        <v>664.7425871489152</v>
       </c>
     </row>
     <row r="383">
@@ -12305,16 +12305,16 @@
         <v>213.5551645</v>
       </c>
       <c r="F383" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G383" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H383" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I383" t="n">
-        <v>7.275330297290545</v>
+        <v>662.4790379911934</v>
       </c>
     </row>
     <row r="384">
@@ -12336,16 +12336,16 @@
         <v>187.0876349</v>
       </c>
       <c r="F384" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G384" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H384" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I384" t="n">
-        <v>10.61135848297473</v>
+        <v>665.2603110236071</v>
       </c>
     </row>
     <row r="385">
@@ -12367,16 +12367,16 @@
         <v>149.1235557</v>
       </c>
       <c r="F385" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G385" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H385" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I385" t="n">
-        <v>38.42775221604786</v>
+        <v>693.1986315605174</v>
       </c>
     </row>
     <row r="386">
@@ -12398,16 +12398,16 @@
         <v>170.141426</v>
       </c>
       <c r="F386" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G386" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H386" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I386" t="n">
-        <v>319.5538914584326</v>
+        <v>393.0868703259844</v>
       </c>
     </row>
     <row r="387">
@@ -12429,16 +12429,16 @@
         <v>168.952343</v>
       </c>
       <c r="F387" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G387" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H387" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I387" t="n">
-        <v>14.41067480414424</v>
+        <v>669.3720454415242</v>
       </c>
     </row>
     <row r="388">
@@ -12460,16 +12460,16 @@
         <v>107.310147</v>
       </c>
       <c r="F388" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G388" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H388" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I388" t="n">
-        <v>2.798523869312165</v>
+        <v>658.2278498242672</v>
       </c>
     </row>
     <row r="389">
@@ -12491,16 +12491,16 @@
         <v>111.302101</v>
       </c>
       <c r="F389" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G389" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H389" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I389" t="n">
-        <v>4.086812362410984</v>
+        <v>658.6394579412456</v>
       </c>
     </row>
     <row r="390">
@@ -12522,16 +12522,16 @@
         <v>77.23364369999999</v>
       </c>
       <c r="F390" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G390" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H390" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I390" t="n">
-        <v>12.82877227690499</v>
+        <v>667.9985859330366</v>
       </c>
     </row>
     <row r="391">
@@ -12553,16 +12553,16 @@
         <v>53.22112451999999</v>
       </c>
       <c r="F391" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G391" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H391" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I391" t="n">
-        <v>184.5265200028921</v>
+        <v>839.4870454669223</v>
       </c>
     </row>
     <row r="392">
@@ -12584,16 +12584,16 @@
         <v>110.9159485</v>
       </c>
       <c r="F392" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G392" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H392" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I392" t="n">
-        <v>4.91155522905192</v>
+        <v>660.3590825727019</v>
       </c>
     </row>
     <row r="393">
@@ -12615,16 +12615,16 @@
         <v>95.37692682000001</v>
       </c>
       <c r="F393" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G393" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H393" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I393" t="n">
-        <v>162.3569820648295</v>
+        <v>817.3587322788459</v>
       </c>
     </row>
     <row r="394">
@@ -12646,16 +12646,16 @@
         <v>54.18531179999999</v>
       </c>
       <c r="F394" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G394" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H394" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I394" t="n">
-        <v>0</v>
+        <v>655.4684498885089</v>
       </c>
     </row>
     <row r="395">
@@ -12677,16 +12677,16 @@
         <v>111.9413228</v>
       </c>
       <c r="F395" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G395" t="n">
-        <v>32.645</v>
+        <v>26.803</v>
       </c>
       <c r="H395" t="n">
-        <v>74.90300000000001</v>
+        <v>75.81</v>
       </c>
       <c r="I395" t="n">
-        <v>14.12354157257625</v>
+        <v>645.4247065034406</v>
       </c>
     </row>
     <row r="396">
@@ -12711,13 +12711,13 @@
         <v>2</v>
       </c>
       <c r="G396" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H396" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I396" t="n">
-        <v>562.9329183211324</v>
+        <v>759.096649040336</v>
       </c>
     </row>
     <row r="397">
@@ -12739,16 +12739,16 @@
         <v>120.77989</v>
       </c>
       <c r="F397" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H397" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I397" t="n">
-        <v>399.0386805781686</v>
+        <v>415.009614916183</v>
       </c>
     </row>
     <row r="398">
@@ -12770,16 +12770,16 @@
         <v>88.73139999999999</v>
       </c>
       <c r="F398" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G398" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H398" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I398" t="n">
-        <v>399.2933407902202</v>
+        <v>327.9025730956491</v>
       </c>
     </row>
     <row r="399">
@@ -12804,13 +12804,13 @@
         <v>2</v>
       </c>
       <c r="G399" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H399" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I399" t="n">
-        <v>544.8395540952689</v>
+        <v>708.5556326549978</v>
       </c>
     </row>
     <row r="400">
@@ -12832,16 +12832,16 @@
         <v>27.36499</v>
       </c>
       <c r="F400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G400" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H400" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I400" t="n">
-        <v>404.1985816893753</v>
+        <v>424.8576969456294</v>
       </c>
     </row>
     <row r="401">
@@ -12863,16 +12863,16 @@
         <v>116.77227</v>
       </c>
       <c r="F401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H401" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I401" t="n">
-        <v>398.0133220468219</v>
+        <v>416.2005603092672</v>
       </c>
     </row>
     <row r="402">
@@ -12894,16 +12894,16 @@
         <v>75.02567782</v>
       </c>
       <c r="F402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H402" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I402" t="n">
-        <v>271.698348756485</v>
+        <v>544.0754229492221</v>
       </c>
     </row>
     <row r="403">
@@ -12925,16 +12925,16 @@
         <v>59.45515</v>
       </c>
       <c r="F403" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H403" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I403" t="n">
-        <v>393.8114777969823</v>
+        <v>420.202670184769</v>
       </c>
     </row>
     <row r="404">
@@ -12956,16 +12956,16 @@
         <v>126.89930723</v>
       </c>
       <c r="F404" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H404" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I404" t="n">
-        <v>270.9129282531802</v>
+        <v>551.0550366523886</v>
       </c>
     </row>
     <row r="405">
@@ -12990,13 +12990,13 @@
         <v>2</v>
       </c>
       <c r="G405" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H405" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I405" t="n">
-        <v>559.6269996577513</v>
+        <v>754.7512233039906</v>
       </c>
     </row>
     <row r="406">
@@ -13018,16 +13018,16 @@
         <v>118.61613</v>
       </c>
       <c r="F406" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H406" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I406" t="n">
-        <v>629.6244910605436</v>
+        <v>819.081017682002</v>
       </c>
     </row>
     <row r="407">
@@ -13049,16 +13049,16 @@
         <v>99.67066999999997</v>
       </c>
       <c r="F407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H407" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I407" t="n">
-        <v>398.0612564570309</v>
+        <v>415.8483188672218</v>
       </c>
     </row>
     <row r="408">
@@ -13083,13 +13083,13 @@
         <v>2</v>
       </c>
       <c r="G408" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H408" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I408" t="n">
-        <v>541.9030864968256</v>
+        <v>706.8435802078126</v>
       </c>
     </row>
     <row r="409">
@@ -13111,16 +13111,16 @@
         <v>221.48973368</v>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H409" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I409" t="n">
-        <v>272.9139635372408</v>
+        <v>543.2854203611975</v>
       </c>
     </row>
     <row r="410">
@@ -13145,13 +13145,13 @@
         <v>2</v>
       </c>
       <c r="G410" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H410" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I410" t="n">
-        <v>560.2114394204164</v>
+        <v>754.0080682376204</v>
       </c>
     </row>
     <row r="411">
@@ -13173,16 +13173,16 @@
         <v>12.82508</v>
       </c>
       <c r="F411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H411" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I411" t="n">
-        <v>397.8931264225789</v>
+        <v>416.3976600846781</v>
       </c>
     </row>
     <row r="412">
@@ -13204,16 +13204,16 @@
         <v>104.69023</v>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H412" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I412" t="n">
-        <v>553.9746287176301</v>
+        <v>751.1032541835341</v>
       </c>
     </row>
     <row r="413">
@@ -13235,16 +13235,16 @@
         <v>131.63062668</v>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G413" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H413" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I413" t="n">
-        <v>290.325695922037</v>
+        <v>527.8764943638412</v>
       </c>
     </row>
     <row r="414">
@@ -13269,13 +13269,13 @@
         <v>2</v>
       </c>
       <c r="G414" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H414" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I414" t="n">
-        <v>589.205834795844</v>
+        <v>735.5434827869196</v>
       </c>
     </row>
     <row r="415">
@@ -13297,16 +13297,16 @@
         <v>57.31582</v>
       </c>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H415" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I415" t="n">
-        <v>592.9623348517237</v>
+        <v>709.1028726243128</v>
       </c>
     </row>
     <row r="416">
@@ -13328,16 +13328,16 @@
         <v>53.89304</v>
       </c>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H416" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I416" t="n">
-        <v>556.1763395240313</v>
+        <v>753.7774386585002</v>
       </c>
     </row>
     <row r="417">
@@ -13362,13 +13362,13 @@
         <v>2</v>
       </c>
       <c r="G417" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H417" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I417" t="n">
-        <v>585.6363666275724</v>
+        <v>732.5765480359983</v>
       </c>
     </row>
     <row r="418">
@@ -13390,16 +13390,16 @@
         <v>44.69123999999999</v>
       </c>
       <c r="F418" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G418" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H418" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I418" t="n">
-        <v>237.6201381750443</v>
+        <v>352.2708032599324</v>
       </c>
     </row>
     <row r="419">
@@ -13424,13 +13424,13 @@
         <v>2</v>
       </c>
       <c r="G419" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H419" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I419" t="n">
-        <v>99.7038613045038</v>
+        <v>464.6875588235764</v>
       </c>
     </row>
     <row r="420">
@@ -13452,16 +13452,16 @@
         <v>30.97999</v>
       </c>
       <c r="F420" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G420" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H420" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I420" t="n">
-        <v>234.764391484706</v>
+        <v>348.5444294950024</v>
       </c>
     </row>
     <row r="421">
@@ -13483,16 +13483,16 @@
         <v>38.67852</v>
       </c>
       <c r="F421" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G421" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H421" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I421" t="n">
-        <v>198.7765567384305</v>
+        <v>317.6587842948209</v>
       </c>
     </row>
     <row r="422">
@@ -13514,16 +13514,16 @@
         <v>22.78917</v>
       </c>
       <c r="F422" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G422" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H422" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I422" t="n">
-        <v>237.0983883977419</v>
+        <v>349.8429211656053</v>
       </c>
     </row>
     <row r="423">
@@ -13548,13 +13548,13 @@
         <v>2</v>
       </c>
       <c r="G423" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H423" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I423" t="n">
-        <v>109.2974339087442</v>
+        <v>476.0512132923942</v>
       </c>
     </row>
     <row r="424">
@@ -13576,16 +13576,16 @@
         <v>125.73253</v>
       </c>
       <c r="F424" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G424" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H424" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I424" t="n">
-        <v>243.3057882043767</v>
+        <v>356.2488929966848</v>
       </c>
     </row>
     <row r="425">
@@ -13610,13 +13610,13 @@
         <v>2</v>
       </c>
       <c r="G425" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H425" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I425" t="n">
-        <v>205.8332451562206</v>
+        <v>435.0067517631766</v>
       </c>
     </row>
     <row r="426">
@@ -13638,16 +13638,16 @@
         <v>144.26477</v>
       </c>
       <c r="F426" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G426" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H426" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I426" t="n">
-        <v>199.5832316516953</v>
+        <v>283.899039519618</v>
       </c>
     </row>
     <row r="427">
@@ -13669,16 +13669,16 @@
         <v>109.89436</v>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G427" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H427" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I427" t="n">
-        <v>244.77544899438</v>
+        <v>358.1093333865317</v>
       </c>
     </row>
     <row r="428">
@@ -13703,13 +13703,13 @@
         <v>2</v>
       </c>
       <c r="G428" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H428" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I428" t="n">
-        <v>212.5040539822774</v>
+        <v>431.9211572336359</v>
       </c>
     </row>
     <row r="429">
@@ -13734,13 +13734,13 @@
         <v>2</v>
       </c>
       <c r="G429" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H429" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I429" t="n">
-        <v>90.0980258920742</v>
+        <v>448.3167262042315</v>
       </c>
     </row>
     <row r="430">
@@ -13765,13 +13765,13 @@
         <v>2</v>
       </c>
       <c r="G430" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H430" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I430" t="n">
-        <v>93.9900122522893</v>
+        <v>454.3869696018361</v>
       </c>
     </row>
     <row r="431">
@@ -13796,13 +13796,13 @@
         <v>2</v>
       </c>
       <c r="G431" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H431" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I431" t="n">
-        <v>48.06033700014402</v>
+        <v>402.7535822110416</v>
       </c>
     </row>
     <row r="432">
@@ -13824,16 +13824,16 @@
         <v>49.8474</v>
       </c>
       <c r="F432" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G432" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H432" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I432" t="n">
-        <v>462.3370152351604</v>
+        <v>401.2120384632639</v>
       </c>
     </row>
     <row r="433">
@@ -13855,16 +13855,16 @@
         <v>56.77137180999998</v>
       </c>
       <c r="F433" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G433" t="n">
-        <v>21.473</v>
+        <v>26.803</v>
       </c>
       <c r="H433" t="n">
-        <v>83.968</v>
+        <v>75.81</v>
       </c>
       <c r="I433" t="n">
-        <v>449.9853559453078</v>
+        <v>586.2836841079591</v>
       </c>
     </row>
     <row r="434">
@@ -13886,16 +13886,16 @@
         <v>138.73463</v>
       </c>
       <c r="F434" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G434" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H434" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I434" t="n">
-        <v>162.993792613938</v>
+        <v>226.8076077869137</v>
       </c>
     </row>
     <row r="435">
@@ -13920,13 +13920,13 @@
         <v>2</v>
       </c>
       <c r="G435" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H435" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I435" t="n">
-        <v>203.4341665162504</v>
+        <v>425.1245783437258</v>
       </c>
     </row>
     <row r="436">
@@ -13951,13 +13951,13 @@
         <v>2</v>
       </c>
       <c r="G436" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H436" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I436" t="n">
-        <v>105.6809195503245</v>
+        <v>472.2718542108274</v>
       </c>
     </row>
     <row r="437">
@@ -13982,13 +13982,13 @@
         <v>2</v>
       </c>
       <c r="G437" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H437" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I437" t="n">
-        <v>90.3683577034153</v>
+        <v>451.4703665004056</v>
       </c>
     </row>
     <row r="438">
@@ -14013,13 +14013,13 @@
         <v>2</v>
       </c>
       <c r="G438" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H438" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I438" t="n">
-        <v>94.08847476823729</v>
+        <v>455.4770701428037</v>
       </c>
     </row>
     <row r="439">
@@ -14041,16 +14041,16 @@
         <v>95.54351964</v>
       </c>
       <c r="F439" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G439" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H439" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I439" t="n">
-        <v>439.1031686450011</v>
+        <v>450.3268626159437</v>
       </c>
     </row>
     <row r="440">
@@ -14072,16 +14072,16 @@
         <v>79.42373506000001</v>
       </c>
       <c r="F440" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G440" t="n">
-        <v>21.473</v>
+        <v>26.803</v>
       </c>
       <c r="H440" t="n">
-        <v>83.968</v>
+        <v>75.81</v>
       </c>
       <c r="I440" t="n">
-        <v>456.135414208522</v>
+        <v>578.1346100863037</v>
       </c>
     </row>
     <row r="441">
@@ -14106,13 +14106,13 @@
         <v>2</v>
       </c>
       <c r="G441" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H441" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I441" t="n">
-        <v>251.7742107462432</v>
+        <v>611.7791003545207</v>
       </c>
     </row>
     <row r="442">
@@ -14137,13 +14137,13 @@
         <v>2</v>
       </c>
       <c r="G442" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H442" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I442" t="n">
-        <v>242.6207437871402</v>
+        <v>416.4094642418626</v>
       </c>
     </row>
     <row r="443">
@@ -14168,13 +14168,13 @@
         <v>2</v>
       </c>
       <c r="G443" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H443" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I443" t="n">
-        <v>94.55157049759576</v>
+        <v>451.1887238220515</v>
       </c>
     </row>
     <row r="444">
@@ -14196,16 +14196,16 @@
         <v>86.38211000000001</v>
       </c>
       <c r="F444" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G444" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H444" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I444" t="n">
-        <v>239.2033432876943</v>
+        <v>352.7855567219063</v>
       </c>
     </row>
     <row r="445">
@@ -14227,16 +14227,16 @@
         <v>90.25793999999999</v>
       </c>
       <c r="F445" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G445" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H445" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I445" t="n">
-        <v>244.7042980601115</v>
+        <v>358.4728944274564</v>
       </c>
     </row>
     <row r="446">
@@ -14258,16 +14258,16 @@
         <v>142.70429</v>
       </c>
       <c r="F446" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G446" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H446" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I446" t="n">
-        <v>238.517141078303</v>
+        <v>351.3685656234222</v>
       </c>
     </row>
     <row r="447">
@@ -14292,13 +14292,13 @@
         <v>2</v>
       </c>
       <c r="G447" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H447" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I447" t="n">
-        <v>212.7492079575601</v>
+        <v>436.1780495857403</v>
       </c>
     </row>
     <row r="448">
@@ -14320,16 +14320,16 @@
         <v>119.03817194</v>
       </c>
       <c r="F448" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G448" t="n">
-        <v>21.473</v>
+        <v>26.803</v>
       </c>
       <c r="H448" t="n">
-        <v>83.968</v>
+        <v>75.81</v>
       </c>
       <c r="I448" t="n">
-        <v>459.7575073825284</v>
+        <v>578.0481855500648</v>
       </c>
     </row>
     <row r="449">
@@ -14354,13 +14354,13 @@
         <v>2</v>
       </c>
       <c r="G449" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H449" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I449" t="n">
-        <v>90.29583703329229</v>
+        <v>449.294709209044</v>
       </c>
     </row>
     <row r="450">
@@ -14382,16 +14382,16 @@
         <v>81.9524</v>
       </c>
       <c r="F450" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G450" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H450" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I450" t="n">
-        <v>480.4430992225687</v>
+        <v>425.5718368268057</v>
       </c>
     </row>
     <row r="451">
@@ -14413,16 +14413,16 @@
         <v>129.72508</v>
       </c>
       <c r="F451" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G451" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H451" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I451" t="n">
-        <v>198.0643498726504</v>
+        <v>283.4912379185273</v>
       </c>
     </row>
     <row r="452">
@@ -14447,13 +14447,13 @@
         <v>2</v>
       </c>
       <c r="G452" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H452" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I452" t="n">
-        <v>97.55387968687192</v>
+        <v>455.918363936613</v>
       </c>
     </row>
     <row r="453">
@@ -14475,16 +14475,16 @@
         <v>137.67475</v>
       </c>
       <c r="F453" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G453" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H453" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I453" t="n">
-        <v>199.5974651940966</v>
+        <v>200.4257883708335</v>
       </c>
     </row>
     <row r="454">
@@ -14506,16 +14506,16 @@
         <v>91.25033126999999</v>
       </c>
       <c r="F454" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G454" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H454" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I454" t="n">
-        <v>335.0619337748118</v>
+        <v>380.4815627908063</v>
       </c>
     </row>
     <row r="455">
@@ -14540,13 +14540,13 @@
         <v>2</v>
       </c>
       <c r="G455" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H455" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I455" t="n">
-        <v>92.01053017070051</v>
+        <v>450.7566097914254</v>
       </c>
     </row>
     <row r="456">
@@ -14571,13 +14571,13 @@
         <v>2</v>
       </c>
       <c r="G456" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H456" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I456" t="n">
-        <v>95.45167583039947</v>
+        <v>456.3802514478284</v>
       </c>
     </row>
     <row r="457">
@@ -14599,16 +14599,16 @@
         <v>33.4468</v>
       </c>
       <c r="F457" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G457" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H457" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I457" t="n">
-        <v>237.9422131497212</v>
+        <v>351.5381900550315</v>
       </c>
     </row>
     <row r="458">
@@ -14630,16 +14630,16 @@
         <v>124.24486528</v>
       </c>
       <c r="F458" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G458" t="n">
-        <v>21.473</v>
+        <v>26.803</v>
       </c>
       <c r="H458" t="n">
-        <v>83.968</v>
+        <v>75.81</v>
       </c>
       <c r="I458" t="n">
-        <v>454.4354598273687</v>
+        <v>582.6519633070533</v>
       </c>
     </row>
     <row r="459">
@@ -14661,16 +14661,16 @@
         <v>99.37579999999998</v>
       </c>
       <c r="F459" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G459" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H459" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I459" t="n">
-        <v>199.2811750116876</v>
+        <v>284.5859852288383</v>
       </c>
     </row>
     <row r="460">
@@ -14695,13 +14695,13 @@
         <v>2</v>
       </c>
       <c r="G460" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H460" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I460" t="n">
-        <v>206.0759102960201</v>
+        <v>429.1619622263655</v>
       </c>
     </row>
     <row r="461">
@@ -14726,13 +14726,13 @@
         <v>2</v>
       </c>
       <c r="G461" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H461" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I461" t="n">
-        <v>205.4737074015495</v>
+        <v>430.9858397127605</v>
       </c>
     </row>
     <row r="462">
@@ -14757,13 +14757,13 @@
         <v>2</v>
       </c>
       <c r="G462" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H462" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I462" t="n">
-        <v>50.25644795082248</v>
+        <v>405.4195200853111</v>
       </c>
     </row>
     <row r="463">
@@ -14788,13 +14788,13 @@
         <v>2</v>
       </c>
       <c r="G463" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H463" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I463" t="n">
-        <v>94.34029263720771</v>
+        <v>453.5340661688839</v>
       </c>
     </row>
     <row r="464">
@@ -14819,13 +14819,13 @@
         <v>2</v>
       </c>
       <c r="G464" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H464" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I464" t="n">
-        <v>199.6572089693678</v>
+        <v>422.731244131476</v>
       </c>
     </row>
     <row r="465">
@@ -14847,16 +14847,16 @@
         <v>97.37148000000001</v>
       </c>
       <c r="F465" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G465" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H465" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I465" t="n">
-        <v>241.6691407618989</v>
+        <v>354.7151027063582</v>
       </c>
     </row>
     <row r="466">
@@ -14878,16 +14878,16 @@
         <v>130.5938</v>
       </c>
       <c r="F466" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G466" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H466" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I466" t="n">
-        <v>202.3400634650289</v>
+        <v>287.0135807377067</v>
       </c>
     </row>
     <row r="467">
@@ -14912,13 +14912,13 @@
         <v>2</v>
       </c>
       <c r="G467" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H467" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I467" t="n">
-        <v>93.80687191812108</v>
+        <v>453.8399374598185</v>
       </c>
     </row>
     <row r="468">
@@ -14943,13 +14943,13 @@
         <v>2</v>
       </c>
       <c r="G468" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H468" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I468" t="n">
-        <v>91.55369369176938</v>
+        <v>450.5248209684561</v>
       </c>
     </row>
     <row r="469">
@@ -14974,13 +14974,13 @@
         <v>2</v>
       </c>
       <c r="G469" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H469" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I469" t="n">
-        <v>207.7644881052486</v>
+        <v>435.244557042524</v>
       </c>
     </row>
     <row r="470">
@@ -15002,16 +15002,16 @@
         <v>123.36434</v>
       </c>
       <c r="F470" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G470" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H470" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I470" t="n">
-        <v>240.297222012738</v>
+        <v>353.7522909453127</v>
       </c>
     </row>
     <row r="471">
@@ -15033,16 +15033,16 @@
         <v>173.58828</v>
       </c>
       <c r="F471" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G471" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H471" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I471" t="n">
-        <v>248.1144254000412</v>
+        <v>360.7583208996892</v>
       </c>
     </row>
     <row r="472">
@@ -15067,13 +15067,13 @@
         <v>2</v>
       </c>
       <c r="G472" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H472" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I472" t="n">
-        <v>94.17249277637561</v>
+        <v>456.9039792535207</v>
       </c>
     </row>
     <row r="473">
@@ -15098,13 +15098,13 @@
         <v>2</v>
       </c>
       <c r="G473" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H473" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I473" t="n">
-        <v>203.1957489360825</v>
+        <v>427.7880442510906</v>
       </c>
     </row>
     <row r="474">
@@ -15126,16 +15126,16 @@
         <v>156.22850862</v>
       </c>
       <c r="F474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G474" t="n">
-        <v>21.473</v>
+        <v>26.803</v>
       </c>
       <c r="H474" t="n">
-        <v>83.968</v>
+        <v>75.81</v>
       </c>
       <c r="I474" t="n">
-        <v>455.2583033426945</v>
+        <v>580.2128763417709</v>
       </c>
     </row>
     <row r="475">
@@ -15160,13 +15160,13 @@
         <v>2</v>
       </c>
       <c r="G475" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H475" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I475" t="n">
-        <v>91.13841375349979</v>
+        <v>453.5677445825671</v>
       </c>
     </row>
     <row r="476">
@@ -15188,16 +15188,16 @@
         <v>147.33710398</v>
       </c>
       <c r="F476" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G476" t="n">
-        <v>21.473</v>
+        <v>26.803</v>
       </c>
       <c r="H476" t="n">
-        <v>83.968</v>
+        <v>75.81</v>
       </c>
       <c r="I476" t="n">
-        <v>458.674922905298</v>
+        <v>576.6039326034715</v>
       </c>
     </row>
     <row r="477">
@@ -15222,13 +15222,13 @@
         <v>2</v>
       </c>
       <c r="G477" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H477" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I477" t="n">
-        <v>208.7746257080976</v>
+        <v>428.4301854542218</v>
       </c>
     </row>
     <row r="478">
@@ -15250,16 +15250,16 @@
         <v>115.35392</v>
       </c>
       <c r="F478" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G478" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H478" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I478" t="n">
-        <v>241.1319183450053</v>
+        <v>355.125656142387</v>
       </c>
     </row>
     <row r="479">
@@ -15284,13 +15284,13 @@
         <v>2</v>
       </c>
       <c r="G479" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H479" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I479" t="n">
-        <v>208.8093372115301</v>
+        <v>434.0899258943054</v>
       </c>
     </row>
     <row r="480">
@@ -15315,13 +15315,13 @@
         <v>2</v>
       </c>
       <c r="G480" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H480" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I480" t="n">
-        <v>98.09423920156364</v>
+        <v>461.5717305808931</v>
       </c>
     </row>
     <row r="481">
@@ -15346,13 +15346,13 @@
         <v>2</v>
       </c>
       <c r="G481" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H481" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I481" t="n">
-        <v>83.86170948034218</v>
+        <v>427.7622499115371</v>
       </c>
     </row>
     <row r="482">
@@ -15374,16 +15374,16 @@
         <v>133.14993041</v>
       </c>
       <c r="F482" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G482" t="n">
-        <v>21.473</v>
+        <v>26.803</v>
       </c>
       <c r="H482" t="n">
-        <v>83.968</v>
+        <v>75.81</v>
       </c>
       <c r="I482" t="n">
-        <v>451.2518729527299</v>
+        <v>566.5589634993504</v>
       </c>
     </row>
     <row r="483">
@@ -15408,13 +15408,13 @@
         <v>2</v>
       </c>
       <c r="G483" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H483" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I483" t="n">
-        <v>205.0075027925476</v>
+        <v>556.9390920324611</v>
       </c>
     </row>
     <row r="484">
@@ -15439,13 +15439,13 @@
         <v>2</v>
       </c>
       <c r="G484" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H484" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I484" t="n">
-        <v>204.411680816876</v>
+        <v>421.5417486600601</v>
       </c>
     </row>
     <row r="485">
@@ -15470,13 +15470,13 @@
         <v>2</v>
       </c>
       <c r="G485" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H485" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I485" t="n">
-        <v>342.6902945712899</v>
+        <v>443.3249832811464</v>
       </c>
     </row>
     <row r="486">
@@ -15498,16 +15498,16 @@
         <v>175.2077001</v>
       </c>
       <c r="F486" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G486" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H486" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I486" t="n">
-        <v>436.7125282091822</v>
+        <v>446.9389947794505</v>
       </c>
     </row>
     <row r="487">
@@ -15529,16 +15529,16 @@
         <v>168.87164</v>
       </c>
       <c r="F487" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G487" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H487" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I487" t="n">
-        <v>75.4651024189595</v>
+        <v>160.8340261318925</v>
       </c>
     </row>
     <row r="488">
@@ -15560,16 +15560,16 @@
         <v>66.75664999999999</v>
       </c>
       <c r="F488" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G488" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H488" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I488" t="n">
-        <v>478.9435636984282</v>
+        <v>424.2660712055792</v>
       </c>
     </row>
     <row r="489">
@@ -15594,13 +15594,13 @@
         <v>2</v>
       </c>
       <c r="G489" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H489" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I489" t="n">
-        <v>206.7994832782831</v>
+        <v>429.5334567222677</v>
       </c>
     </row>
     <row r="490">
@@ -15625,13 +15625,13 @@
         <v>2</v>
       </c>
       <c r="G490" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H490" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I490" t="n">
-        <v>93.00717953846529</v>
+        <v>449.7269075445288</v>
       </c>
     </row>
     <row r="491">
@@ -15653,16 +15653,16 @@
         <v>89.62715</v>
       </c>
       <c r="F491" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G491" t="n">
-        <v>15.464</v>
+        <v>16.168</v>
       </c>
       <c r="H491" t="n">
-        <v>75</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I491" t="n">
-        <v>478.129089313604</v>
+        <v>423.7322331023271</v>
       </c>
     </row>
     <row r="492">
@@ -15684,16 +15684,16 @@
         <v>43.78264999999999</v>
       </c>
       <c r="F492" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G492" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H492" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I492" t="n">
-        <v>262.869810262483</v>
+        <v>375.8744742030584</v>
       </c>
     </row>
     <row r="493">
@@ -15718,13 +15718,13 @@
         <v>2</v>
       </c>
       <c r="G493" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H493" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I493" t="n">
-        <v>173.614929625572</v>
+        <v>420.4656003310083</v>
       </c>
     </row>
     <row r="494">
@@ -15749,13 +15749,13 @@
         <v>2</v>
       </c>
       <c r="G494" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H494" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I494" t="n">
-        <v>340.0263864003297</v>
+        <v>441.0949801553826</v>
       </c>
     </row>
     <row r="495">
@@ -15780,13 +15780,13 @@
         <v>2</v>
       </c>
       <c r="G495" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H495" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I495" t="n">
-        <v>206.5414340971641</v>
+        <v>431.0946313417494</v>
       </c>
     </row>
     <row r="496">
@@ -15808,16 +15808,16 @@
         <v>59.60680000000001</v>
       </c>
       <c r="F496" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G496" t="n">
-        <v>23.455</v>
+        <v>16.168</v>
       </c>
       <c r="H496" t="n">
-        <v>75.425</v>
+        <v>74.82899999999999</v>
       </c>
       <c r="I496" t="n">
-        <v>334.3077432722394</v>
+        <v>505.8755371911598</v>
       </c>
     </row>
     <row r="497">
@@ -15839,16 +15839,16 @@
         <v>61.33865</v>
       </c>
       <c r="F497" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G497" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H497" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I497" t="n">
-        <v>265.9757361101167</v>
+        <v>388.7157686271636</v>
       </c>
     </row>
     <row r="498">
@@ -15873,13 +15873,13 @@
         <v>2</v>
       </c>
       <c r="G498" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H498" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I498" t="n">
-        <v>40.28803578428388</v>
+        <v>392.6881253176529</v>
       </c>
     </row>
     <row r="499">
@@ -15904,13 +15904,13 @@
         <v>2</v>
       </c>
       <c r="G499" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H499" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I499" t="n">
-        <v>0</v>
+        <v>374.2917936817031</v>
       </c>
     </row>
     <row r="500">
@@ -15932,16 +15932,16 @@
         <v>97.11096000000002</v>
       </c>
       <c r="F500" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G500" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H500" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I500" t="n">
-        <v>198.4169489828125</v>
+        <v>284.291894084992</v>
       </c>
     </row>
     <row r="501">
@@ -15963,16 +15963,16 @@
         <v>77.12655000000001</v>
       </c>
       <c r="F501" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G501" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H501" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I501" t="n">
-        <v>197.2457940055387</v>
+        <v>281.8049758887568</v>
       </c>
     </row>
     <row r="502">
@@ -15997,13 +15997,13 @@
         <v>2</v>
       </c>
       <c r="G502" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H502" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I502" t="n">
-        <v>114.9391757734247</v>
+        <v>475.3866029147773</v>
       </c>
     </row>
     <row r="503">
@@ -16025,16 +16025,16 @@
         <v>39.40545</v>
       </c>
       <c r="F503" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G503" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H503" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I503" t="n">
-        <v>199.1949041175324</v>
+        <v>284.7327150864167</v>
       </c>
     </row>
     <row r="504">
@@ -16056,16 +16056,16 @@
         <v>51.32812</v>
       </c>
       <c r="F504" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G504" t="n">
-        <v>21.473</v>
+        <v>22.254</v>
       </c>
       <c r="H504" t="n">
-        <v>83.968</v>
+        <v>84.908</v>
       </c>
       <c r="I504" t="n">
-        <v>212.3623313996765</v>
+        <v>311.8954044587077</v>
       </c>
     </row>
     <row r="505">
@@ -16090,13 +16090,13 @@
         <v>2</v>
       </c>
       <c r="G505" t="n">
-        <v>23.455</v>
+        <v>26.803</v>
       </c>
       <c r="H505" t="n">
-        <v>75.425</v>
+        <v>75.81</v>
       </c>
       <c r="I505" t="n">
-        <v>98.10985974597351</v>
+        <v>466.8530609246752</v>
       </c>
     </row>
   </sheetData>

--- a/clustered_output.xlsx
+++ b/clustered_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I505"/>
+  <dimension ref="A1:G505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dc_lat</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dc_long</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>distance_km</t>
+          <t>assigned_dc</t>
         </is>
       </c>
     </row>
@@ -496,14 +486,10 @@
       <c r="F2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H2" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>330.9635282855404</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -527,14 +513,10 @@
       <c r="F3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H3" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>117.9924090723754</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -558,14 +540,10 @@
       <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H4" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>426.9669887847988</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -589,14 +567,10 @@
       <c r="F5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H5" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>121.6518811104223</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -620,14 +594,10 @@
       <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H6" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>420.4712712853633</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -651,14 +621,10 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H7" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>108.1103102442499</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -682,14 +648,10 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H8" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>313.8902207082496</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -713,14 +675,10 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H9" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>373.4412154910133</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -744,14 +702,10 @@
       <c r="F10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H10" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>495.1232190037021</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -775,14 +729,10 @@
       <c r="F11" t="n">
         <v>3</v>
       </c>
-      <c r="G11" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H11" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>492.2082518359087</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -806,14 +756,10 @@
       <c r="F12" t="n">
         <v>3</v>
       </c>
-      <c r="G12" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H12" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>128.9441347688719</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -837,14 +783,10 @@
       <c r="F13" t="n">
         <v>3</v>
       </c>
-      <c r="G13" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H13" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>130.2855787087994</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -868,14 +810,10 @@
       <c r="F14" t="n">
         <v>3</v>
       </c>
-      <c r="G14" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H14" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>146.4901253335264</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -899,14 +837,10 @@
       <c r="F15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H15" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>453.1047927312811</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -930,14 +864,10 @@
       <c r="F16" t="n">
         <v>3</v>
       </c>
-      <c r="G16" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H16" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>482.9249057213582</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -961,14 +891,10 @@
       <c r="F17" t="n">
         <v>3</v>
       </c>
-      <c r="G17" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H17" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>128.5054911990155</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -992,14 +918,10 @@
       <c r="F18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H18" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>259.8066720323735</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1023,14 +945,10 @@
       <c r="F19" t="n">
         <v>3</v>
       </c>
-      <c r="G19" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H19" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>130.5207868271966</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1054,14 +972,10 @@
       <c r="F20" t="n">
         <v>3</v>
       </c>
-      <c r="G20" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H20" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>170.3468154702016</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1085,14 +999,10 @@
       <c r="F21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H21" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>221.6520820103549</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1116,14 +1026,10 @@
       <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H22" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>276.1174878980499</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1147,14 +1053,10 @@
       <c r="F23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H23" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>465.5664978287974</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1178,14 +1080,10 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H24" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>96.0979610302295</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1209,14 +1107,10 @@
       <c r="F25" t="n">
         <v>3</v>
       </c>
-      <c r="G25" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H25" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>440.6263987667413</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1240,14 +1134,10 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H26" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>365.094204846208</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1271,14 +1161,10 @@
       <c r="F27" t="n">
         <v>3</v>
       </c>
-      <c r="G27" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H27" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>137.5875559259532</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1302,14 +1188,10 @@
       <c r="F28" t="n">
         <v>3</v>
       </c>
-      <c r="G28" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H28" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I28" t="n">
-        <v>437.5011742973805</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1333,14 +1215,10 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H29" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>165.0508502095769</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1364,14 +1242,10 @@
       <c r="F30" t="n">
         <v>3</v>
       </c>
-      <c r="G30" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H30" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I30" t="n">
-        <v>285.2711516650368</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1395,14 +1269,10 @@
       <c r="F31" t="n">
         <v>3</v>
       </c>
-      <c r="G31" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H31" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I31" t="n">
-        <v>137.8003887622026</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1426,14 +1296,10 @@
       <c r="F32" t="n">
         <v>3</v>
       </c>
-      <c r="G32" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H32" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I32" t="n">
-        <v>139.3399391111659</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1457,14 +1323,10 @@
       <c r="F33" t="n">
         <v>3</v>
       </c>
-      <c r="G33" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H33" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I33" t="n">
-        <v>446.4715004339711</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1488,14 +1350,10 @@
       <c r="F34" t="n">
         <v>1</v>
       </c>
-      <c r="G34" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H34" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>212.1199935801126</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1519,14 +1377,10 @@
       <c r="F35" t="n">
         <v>3</v>
       </c>
-      <c r="G35" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H35" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>137.1927821035483</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1550,14 +1404,10 @@
       <c r="F36" t="n">
         <v>3</v>
       </c>
-      <c r="G36" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H36" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>495.716185770717</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1581,14 +1431,10 @@
       <c r="F37" t="n">
         <v>1</v>
       </c>
-      <c r="G37" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H37" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>97.24880694316984</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1612,14 +1458,10 @@
       <c r="F38" t="n">
         <v>3</v>
       </c>
-      <c r="G38" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H38" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>132.5567661736015</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1643,14 +1485,10 @@
       <c r="F39" t="n">
         <v>3</v>
       </c>
-      <c r="G39" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H39" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>432.38924585193</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1674,14 +1512,10 @@
       <c r="F40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H40" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>353.1698387461005</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1705,14 +1539,10 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H41" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I41" t="n">
-        <v>80.39050753268133</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1736,14 +1566,10 @@
       <c r="F42" t="n">
         <v>3</v>
       </c>
-      <c r="G42" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H42" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I42" t="n">
-        <v>265.3216686549943</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1767,14 +1593,10 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H43" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I43" t="n">
-        <v>137.0103170103804</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1798,14 +1620,10 @@
       <c r="F44" t="n">
         <v>3</v>
       </c>
-      <c r="G44" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H44" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I44" t="n">
-        <v>444.1175443051316</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1829,14 +1647,10 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H45" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I45" t="n">
-        <v>345.3721164033507</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1860,14 +1674,10 @@
       <c r="F46" t="n">
         <v>3</v>
       </c>
-      <c r="G46" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H46" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I46" t="n">
-        <v>407.277294246931</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1891,14 +1701,10 @@
       <c r="F47" t="n">
         <v>3</v>
       </c>
-      <c r="G47" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H47" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I47" t="n">
-        <v>413.8102117955148</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1922,14 +1728,10 @@
       <c r="F48" t="n">
         <v>3</v>
       </c>
-      <c r="G48" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H48" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I48" t="n">
-        <v>122.8011678761479</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1953,14 +1755,10 @@
       <c r="F49" t="n">
         <v>3</v>
       </c>
-      <c r="G49" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H49" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>442.4265618572776</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1984,14 +1782,10 @@
       <c r="F50" t="n">
         <v>3</v>
       </c>
-      <c r="G50" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H50" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I50" t="n">
-        <v>494.2392037869573</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -2015,14 +1809,10 @@
       <c r="F51" t="n">
         <v>1</v>
       </c>
-      <c r="G51" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H51" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I51" t="n">
-        <v>312.8152737420051</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -2046,14 +1836,10 @@
       <c r="F52" t="n">
         <v>1</v>
       </c>
-      <c r="G52" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H52" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I52" t="n">
-        <v>129.237268082056</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -2077,14 +1863,10 @@
       <c r="F53" t="n">
         <v>3</v>
       </c>
-      <c r="G53" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H53" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I53" t="n">
-        <v>85.96947799636601</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -2108,14 +1890,10 @@
       <c r="F54" t="n">
         <v>1</v>
       </c>
-      <c r="G54" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H54" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>168.7100665885474</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -2139,14 +1917,10 @@
       <c r="F55" t="n">
         <v>3</v>
       </c>
-      <c r="G55" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H55" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I55" t="n">
-        <v>141.7811728221151</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -2170,14 +1944,10 @@
       <c r="F56" t="n">
         <v>3</v>
       </c>
-      <c r="G56" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H56" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I56" t="n">
-        <v>490.0243432034919</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -2201,14 +1971,10 @@
       <c r="F57" t="n">
         <v>3</v>
       </c>
-      <c r="G57" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H57" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I57" t="n">
-        <v>392.1441159670266</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -2232,14 +1998,10 @@
       <c r="F58" t="n">
         <v>1</v>
       </c>
-      <c r="G58" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H58" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I58" t="n">
-        <v>113.6078870195936</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -2263,14 +2025,10 @@
       <c r="F59" t="n">
         <v>3</v>
       </c>
-      <c r="G59" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H59" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I59" t="n">
-        <v>145.9883362263176</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -2294,14 +2052,10 @@
       <c r="F60" t="n">
         <v>3</v>
       </c>
-      <c r="G60" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H60" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I60" t="n">
-        <v>133.1781377095647</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -2325,14 +2079,10 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H61" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I61" t="n">
-        <v>134.3181781165763</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -2356,14 +2106,10 @@
       <c r="F62" t="n">
         <v>3</v>
       </c>
-      <c r="G62" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H62" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I62" t="n">
-        <v>123.0549928591128</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -2387,14 +2133,10 @@
       <c r="F63" t="n">
         <v>3</v>
       </c>
-      <c r="G63" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H63" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I63" t="n">
-        <v>440.5761630353377</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -2418,14 +2160,10 @@
       <c r="F64" t="n">
         <v>1</v>
       </c>
-      <c r="G64" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H64" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I64" t="n">
-        <v>313.8984511692369</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -2449,14 +2187,10 @@
       <c r="F65" t="n">
         <v>1</v>
       </c>
-      <c r="G65" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H65" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I65" t="n">
-        <v>135.1903379520044</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -2480,14 +2214,10 @@
       <c r="F66" t="n">
         <v>1</v>
       </c>
-      <c r="G66" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H66" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I66" t="n">
-        <v>368.0564818651708</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -2511,14 +2241,10 @@
       <c r="F67" t="n">
         <v>3</v>
       </c>
-      <c r="G67" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H67" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I67" t="n">
-        <v>120.0711060212944</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -2542,14 +2268,10 @@
       <c r="F68" t="n">
         <v>1</v>
       </c>
-      <c r="G68" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H68" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I68" t="n">
-        <v>172.1305810020439</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -2573,14 +2295,10 @@
       <c r="F69" t="n">
         <v>3</v>
       </c>
-      <c r="G69" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H69" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I69" t="n">
-        <v>20.41596783227257</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -2604,14 +2322,10 @@
       <c r="F70" t="n">
         <v>3</v>
       </c>
-      <c r="G70" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H70" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I70" t="n">
-        <v>134.7397854755224</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -2635,14 +2349,10 @@
       <c r="F71" t="n">
         <v>1</v>
       </c>
-      <c r="G71" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H71" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I71" t="n">
-        <v>113.6078870195936</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -2666,14 +2376,10 @@
       <c r="F72" t="n">
         <v>3</v>
       </c>
-      <c r="G72" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H72" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I72" t="n">
-        <v>126.3772556143692</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -2697,14 +2403,10 @@
       <c r="F73" t="n">
         <v>3</v>
       </c>
-      <c r="G73" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H73" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I73" t="n">
-        <v>449.7586404666938</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -2728,14 +2430,10 @@
       <c r="F74" t="n">
         <v>3</v>
       </c>
-      <c r="G74" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H74" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I74" t="n">
-        <v>127.1359911457164</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -2759,14 +2457,10 @@
       <c r="F75" t="n">
         <v>1</v>
       </c>
-      <c r="G75" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H75" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I75" t="n">
-        <v>125.4618836507752</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -2790,14 +2484,10 @@
       <c r="F76" t="n">
         <v>3</v>
       </c>
-      <c r="G76" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H76" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I76" t="n">
-        <v>483.7945945807476</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -2821,14 +2511,10 @@
       <c r="F77" t="n">
         <v>1</v>
       </c>
-      <c r="G77" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H77" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I77" t="n">
-        <v>124.2161967924599</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -2852,14 +2538,10 @@
       <c r="F78" t="n">
         <v>3</v>
       </c>
-      <c r="G78" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H78" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I78" t="n">
-        <v>203.6346669013843</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -2883,14 +2565,10 @@
       <c r="F79" t="n">
         <v>3</v>
       </c>
-      <c r="G79" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H79" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I79" t="n">
-        <v>234.5085396974142</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -2914,14 +2592,10 @@
       <c r="F80" t="n">
         <v>3</v>
       </c>
-      <c r="G80" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H80" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I80" t="n">
-        <v>143.7534492312146</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -2945,14 +2619,10 @@
       <c r="F81" t="n">
         <v>3</v>
       </c>
-      <c r="G81" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H81" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I81" t="n">
-        <v>133.7006511831521</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -2976,14 +2646,10 @@
       <c r="F82" t="n">
         <v>3</v>
       </c>
-      <c r="G82" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H82" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I82" t="n">
-        <v>128.6823365844351</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -3007,14 +2673,10 @@
       <c r="F83" t="n">
         <v>1</v>
       </c>
-      <c r="G83" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H83" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I83" t="n">
-        <v>133.4087432163412</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -3038,14 +2700,10 @@
       <c r="F84" t="n">
         <v>1</v>
       </c>
-      <c r="G84" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H84" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I84" t="n">
-        <v>130.3854760775766</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -3069,14 +2727,10 @@
       <c r="F85" t="n">
         <v>1</v>
       </c>
-      <c r="G85" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H85" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I85" t="n">
-        <v>135.4730310847455</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -3100,14 +2754,10 @@
       <c r="F86" t="n">
         <v>3</v>
       </c>
-      <c r="G86" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H86" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I86" t="n">
-        <v>130.2231289710547</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -3131,14 +2781,10 @@
       <c r="F87" t="n">
         <v>1</v>
       </c>
-      <c r="G87" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H87" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I87" t="n">
-        <v>366.6220584731958</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -3162,14 +2808,10 @@
       <c r="F88" t="n">
         <v>1</v>
       </c>
-      <c r="G88" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H88" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I88" t="n">
-        <v>313.7181966978334</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -3193,14 +2835,10 @@
       <c r="F89" t="n">
         <v>3</v>
       </c>
-      <c r="G89" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H89" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I89" t="n">
-        <v>135.6068269194521</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -3224,14 +2862,10 @@
       <c r="F90" t="n">
         <v>3</v>
       </c>
-      <c r="G90" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H90" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I90" t="n">
-        <v>133.4495554787986</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -3255,14 +2889,10 @@
       <c r="F91" t="n">
         <v>3</v>
       </c>
-      <c r="G91" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H91" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I91" t="n">
-        <v>124.0579963162462</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -3286,14 +2916,10 @@
       <c r="F92" t="n">
         <v>1</v>
       </c>
-      <c r="G92" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H92" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I92" t="n">
-        <v>132.2317631445825</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -3317,14 +2943,10 @@
       <c r="F93" t="n">
         <v>1</v>
       </c>
-      <c r="G93" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H93" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I93" t="n">
-        <v>128.717486213771</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -3348,14 +2970,10 @@
       <c r="F94" t="n">
         <v>3</v>
       </c>
-      <c r="G94" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H94" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I94" t="n">
-        <v>131.7009008617561</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -3379,14 +2997,10 @@
       <c r="F95" t="n">
         <v>1</v>
       </c>
-      <c r="G95" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H95" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I95" t="n">
-        <v>133.5541028711692</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -3410,14 +3024,10 @@
       <c r="F96" t="n">
         <v>3</v>
       </c>
-      <c r="G96" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H96" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I96" t="n">
-        <v>133.3419133050184</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -3441,14 +3051,10 @@
       <c r="F97" t="n">
         <v>3</v>
       </c>
-      <c r="G97" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H97" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I97" t="n">
-        <v>136.3714144979849</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -3472,14 +3078,10 @@
       <c r="F98" t="n">
         <v>3</v>
       </c>
-      <c r="G98" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H98" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I98" t="n">
-        <v>130.4915498302243</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -3503,14 +3105,10 @@
       <c r="F99" t="n">
         <v>3</v>
       </c>
-      <c r="G99" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H99" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I99" t="n">
-        <v>442.2738823209808</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -3534,14 +3132,10 @@
       <c r="F100" t="n">
         <v>3</v>
       </c>
-      <c r="G100" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H100" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I100" t="n">
-        <v>139.9394903277591</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -3565,14 +3159,10 @@
       <c r="F101" t="n">
         <v>3</v>
       </c>
-      <c r="G101" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H101" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I101" t="n">
-        <v>128.2753586164148</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -3596,14 +3186,10 @@
       <c r="F102" t="n">
         <v>3</v>
       </c>
-      <c r="G102" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H102" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I102" t="n">
-        <v>116.0060286591594</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -3627,14 +3213,10 @@
       <c r="F103" t="n">
         <v>3</v>
       </c>
-      <c r="G103" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H103" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I103" t="n">
-        <v>119.7946518548475</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -3658,14 +3240,10 @@
       <c r="F104" t="n">
         <v>3</v>
       </c>
-      <c r="G104" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H104" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I104" t="n">
-        <v>117.7208691827655</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -3689,14 +3267,10 @@
       <c r="F105" t="n">
         <v>3</v>
       </c>
-      <c r="G105" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H105" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I105" t="n">
-        <v>443.7056571528461</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -3720,14 +3294,10 @@
       <c r="F106" t="n">
         <v>3</v>
       </c>
-      <c r="G106" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H106" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I106" t="n">
-        <v>287.2407268146017</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -3751,14 +3321,10 @@
       <c r="F107" t="n">
         <v>3</v>
       </c>
-      <c r="G107" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H107" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I107" t="n">
-        <v>491.1606421189047</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -3782,14 +3348,10 @@
       <c r="F108" t="n">
         <v>3</v>
       </c>
-      <c r="G108" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H108" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I108" t="n">
-        <v>438.3360268021133</v>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -3813,14 +3375,10 @@
       <c r="F109" t="n">
         <v>3</v>
       </c>
-      <c r="G109" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H109" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I109" t="n">
-        <v>128.4727129154797</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -3844,14 +3402,10 @@
       <c r="F110" t="n">
         <v>1</v>
       </c>
-      <c r="G110" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H110" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I110" t="n">
-        <v>366.1671710516097</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -3875,14 +3429,10 @@
       <c r="F111" t="n">
         <v>3</v>
       </c>
-      <c r="G111" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H111" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I111" t="n">
-        <v>131.4380690737538</v>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -3906,14 +3456,10 @@
       <c r="F112" t="n">
         <v>3</v>
       </c>
-      <c r="G112" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H112" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I112" t="n">
-        <v>121.1765276823574</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -3937,14 +3483,10 @@
       <c r="F113" t="n">
         <v>3</v>
       </c>
-      <c r="G113" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H113" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I113" t="n">
-        <v>121.6051186359468</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -3968,14 +3510,10 @@
       <c r="F114" t="n">
         <v>3</v>
       </c>
-      <c r="G114" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H114" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I114" t="n">
-        <v>315.3898871045468</v>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -3999,14 +3537,10 @@
       <c r="F115" t="n">
         <v>3</v>
       </c>
-      <c r="G115" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H115" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I115" t="n">
-        <v>420.9097798142605</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -4030,14 +3564,10 @@
       <c r="F116" t="n">
         <v>3</v>
       </c>
-      <c r="G116" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H116" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I116" t="n">
-        <v>117.1189359683959</v>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -4061,14 +3591,10 @@
       <c r="F117" t="n">
         <v>1</v>
       </c>
-      <c r="G117" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H117" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I117" t="n">
-        <v>135.0580930295541</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -4092,14 +3618,10 @@
       <c r="F118" t="n">
         <v>3</v>
       </c>
-      <c r="G118" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H118" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I118" t="n">
-        <v>134.3931990270278</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -4123,14 +3645,10 @@
       <c r="F119" t="n">
         <v>3</v>
       </c>
-      <c r="G119" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H119" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I119" t="n">
-        <v>491.9232670955004</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -4154,14 +3672,10 @@
       <c r="F120" t="n">
         <v>1</v>
       </c>
-      <c r="G120" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H120" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I120" t="n">
-        <v>366.5015755172517</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -4185,14 +3699,10 @@
       <c r="F121" t="n">
         <v>3</v>
       </c>
-      <c r="G121" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H121" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I121" t="n">
-        <v>139.8497216179582</v>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -4216,14 +3726,10 @@
       <c r="F122" t="n">
         <v>3</v>
       </c>
-      <c r="G122" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H122" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I122" t="n">
-        <v>127.549787869981</v>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -4247,14 +3753,10 @@
       <c r="F123" t="n">
         <v>1</v>
       </c>
-      <c r="G123" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H123" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I123" t="n">
-        <v>95.7324236102036</v>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -4278,14 +3780,10 @@
       <c r="F124" t="n">
         <v>3</v>
       </c>
-      <c r="G124" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H124" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I124" t="n">
-        <v>125.9160263320814</v>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -4309,14 +3807,10 @@
       <c r="F125" t="n">
         <v>3</v>
       </c>
-      <c r="G125" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H125" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I125" t="n">
-        <v>115.1672335283907</v>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -4340,14 +3834,10 @@
       <c r="F126" t="n">
         <v>3</v>
       </c>
-      <c r="G126" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H126" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I126" t="n">
-        <v>111.8178194902709</v>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -4371,14 +3861,10 @@
       <c r="F127" t="n">
         <v>3</v>
       </c>
-      <c r="G127" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H127" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I127" t="n">
-        <v>131.1888744670751</v>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -4402,14 +3888,10 @@
       <c r="F128" t="n">
         <v>3</v>
       </c>
-      <c r="G128" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H128" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I128" t="n">
-        <v>123.935072258068</v>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -4433,14 +3915,10 @@
       <c r="F129" t="n">
         <v>3</v>
       </c>
-      <c r="G129" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H129" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I129" t="n">
-        <v>131.6487906909689</v>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -4464,14 +3942,10 @@
       <c r="F130" t="n">
         <v>3</v>
       </c>
-      <c r="G130" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H130" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I130" t="n">
-        <v>130.381237786289</v>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -4495,14 +3969,10 @@
       <c r="F131" t="n">
         <v>3</v>
       </c>
-      <c r="G131" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H131" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I131" t="n">
-        <v>2.524349787145492</v>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -4526,14 +3996,10 @@
       <c r="F132" t="n">
         <v>1</v>
       </c>
-      <c r="G132" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H132" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I132" t="n">
-        <v>45.92423917331701</v>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -4557,14 +4023,10 @@
       <c r="F133" t="n">
         <v>3</v>
       </c>
-      <c r="G133" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H133" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I133" t="n">
-        <v>439.4150303327746</v>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -4588,14 +4050,10 @@
       <c r="F134" t="n">
         <v>3</v>
       </c>
-      <c r="G134" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H134" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I134" t="n">
-        <v>132.7490468314282</v>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -4619,14 +4077,10 @@
       <c r="F135" t="n">
         <v>1</v>
       </c>
-      <c r="G135" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H135" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I135" t="n">
-        <v>223.2616339193195</v>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -4650,14 +4104,10 @@
       <c r="F136" t="n">
         <v>1</v>
       </c>
-      <c r="G136" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H136" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I136" t="n">
-        <v>135.9422927738292</v>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -4681,14 +4131,10 @@
       <c r="F137" t="n">
         <v>1</v>
       </c>
-      <c r="G137" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H137" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I137" t="n">
-        <v>137.8924794813661</v>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -4712,14 +4158,10 @@
       <c r="F138" t="n">
         <v>3</v>
       </c>
-      <c r="G138" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H138" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I138" t="n">
-        <v>127.3032429697211</v>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -4743,14 +4185,10 @@
       <c r="F139" t="n">
         <v>3</v>
       </c>
-      <c r="G139" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H139" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I139" t="n">
-        <v>121.1956400146447</v>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -4774,14 +4212,10 @@
       <c r="F140" t="n">
         <v>3</v>
       </c>
-      <c r="G140" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H140" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I140" t="n">
-        <v>436.7912830403555</v>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -4805,14 +4239,10 @@
       <c r="F141" t="n">
         <v>3</v>
       </c>
-      <c r="G141" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H141" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I141" t="n">
-        <v>135.4344329345909</v>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -4836,14 +4266,10 @@
       <c r="F142" t="n">
         <v>3</v>
       </c>
-      <c r="G142" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H142" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I142" t="n">
-        <v>280.444170825078</v>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -4867,14 +4293,10 @@
       <c r="F143" t="n">
         <v>3</v>
       </c>
-      <c r="G143" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H143" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I143" t="n">
-        <v>106.2678263285794</v>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -4898,14 +4320,10 @@
       <c r="F144" t="n">
         <v>3</v>
       </c>
-      <c r="G144" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H144" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I144" t="n">
-        <v>103.5750652214989</v>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -4929,14 +4347,10 @@
       <c r="F145" t="n">
         <v>3</v>
       </c>
-      <c r="G145" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H145" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I145" t="n">
-        <v>423.1317561742813</v>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -4960,14 +4374,10 @@
       <c r="F146" t="n">
         <v>1</v>
       </c>
-      <c r="G146" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H146" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I146" t="n">
-        <v>94.38920284780231</v>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -4991,14 +4401,10 @@
       <c r="F147" t="n">
         <v>3</v>
       </c>
-      <c r="G147" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H147" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I147" t="n">
-        <v>120.0628786795913</v>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -5022,14 +4428,10 @@
       <c r="F148" t="n">
         <v>3</v>
       </c>
-      <c r="G148" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H148" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I148" t="n">
-        <v>127.0843658238061</v>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -5053,14 +4455,10 @@
       <c r="F149" t="n">
         <v>3</v>
       </c>
-      <c r="G149" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H149" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I149" t="n">
-        <v>137.6740764380879</v>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -5084,14 +4482,10 @@
       <c r="F150" t="n">
         <v>3</v>
       </c>
-      <c r="G150" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H150" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I150" t="n">
-        <v>98.92679672304133</v>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -5115,14 +4509,10 @@
       <c r="F151" t="n">
         <v>3</v>
       </c>
-      <c r="G151" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H151" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I151" t="n">
-        <v>427.5095658720282</v>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -5146,14 +4536,10 @@
       <c r="F152" t="n">
         <v>3</v>
       </c>
-      <c r="G152" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H152" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I152" t="n">
-        <v>487.5368227657868</v>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -5177,14 +4563,10 @@
       <c r="F153" t="n">
         <v>3</v>
       </c>
-      <c r="G153" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H153" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I153" t="n">
-        <v>123.5184011830669</v>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -5208,14 +4590,10 @@
       <c r="F154" t="n">
         <v>1</v>
       </c>
-      <c r="G154" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H154" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I154" t="n">
-        <v>82.41961808376361</v>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -5239,14 +4617,10 @@
       <c r="F155" t="n">
         <v>3</v>
       </c>
-      <c r="G155" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H155" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I155" t="n">
-        <v>115.0570084748459</v>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -5270,14 +4644,10 @@
       <c r="F156" t="n">
         <v>3</v>
       </c>
-      <c r="G156" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H156" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I156" t="n">
-        <v>126.05341869692</v>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -5301,14 +4671,10 @@
       <c r="F157" t="n">
         <v>3</v>
       </c>
-      <c r="G157" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H157" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I157" t="n">
-        <v>494.1176797046688</v>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -5332,14 +4698,10 @@
       <c r="F158" t="n">
         <v>3</v>
       </c>
-      <c r="G158" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H158" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I158" t="n">
-        <v>439.6105513810847</v>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -5363,14 +4725,10 @@
       <c r="F159" t="n">
         <v>3</v>
       </c>
-      <c r="G159" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H159" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I159" t="n">
-        <v>141.1308776121495</v>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -5394,14 +4752,10 @@
       <c r="F160" t="n">
         <v>1</v>
       </c>
-      <c r="G160" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H160" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I160" t="n">
-        <v>363.830579906318</v>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -5425,14 +4779,10 @@
       <c r="F161" t="n">
         <v>3</v>
       </c>
-      <c r="G161" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H161" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I161" t="n">
-        <v>128.2123748624244</v>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -5456,14 +4806,10 @@
       <c r="F162" t="n">
         <v>3</v>
       </c>
-      <c r="G162" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H162" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I162" t="n">
-        <v>137.7535479338831</v>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -5487,14 +4833,10 @@
       <c r="F163" t="n">
         <v>3</v>
       </c>
-      <c r="G163" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H163" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I163" t="n">
-        <v>0</v>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -5518,14 +4860,10 @@
       <c r="F164" t="n">
         <v>3</v>
       </c>
-      <c r="G164" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H164" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I164" t="n">
-        <v>422.87760814889</v>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -5549,14 +4887,10 @@
       <c r="F165" t="n">
         <v>3</v>
       </c>
-      <c r="G165" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H165" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I165" t="n">
-        <v>424.1932020833065</v>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -5580,14 +4914,10 @@
       <c r="F166" t="n">
         <v>3</v>
       </c>
-      <c r="G166" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H166" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I166" t="n">
-        <v>366.8659341721198</v>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -5611,14 +4941,10 @@
       <c r="F167" t="n">
         <v>3</v>
       </c>
-      <c r="G167" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H167" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I167" t="n">
-        <v>136.6273011118156</v>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -5642,14 +4968,10 @@
       <c r="F168" t="n">
         <v>1</v>
       </c>
-      <c r="G168" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H168" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I168" t="n">
-        <v>139.1536339413091</v>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -5673,14 +4995,10 @@
       <c r="F169" t="n">
         <v>1</v>
       </c>
-      <c r="G169" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H169" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I169" t="n">
-        <v>50.54469560972741</v>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -5704,14 +5022,10 @@
       <c r="F170" t="n">
         <v>3</v>
       </c>
-      <c r="G170" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H170" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I170" t="n">
-        <v>110.0155394868578</v>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -5735,14 +5049,10 @@
       <c r="F171" t="n">
         <v>3</v>
       </c>
-      <c r="G171" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H171" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I171" t="n">
-        <v>441.4650566886497</v>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -5766,14 +5076,10 @@
       <c r="F172" t="n">
         <v>3</v>
       </c>
-      <c r="G172" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H172" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I172" t="n">
-        <v>135.8642245783005</v>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="173">
@@ -5797,14 +5103,10 @@
       <c r="F173" t="n">
         <v>3</v>
       </c>
-      <c r="G173" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H173" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I173" t="n">
-        <v>135.5652887863286</v>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -5828,14 +5130,10 @@
       <c r="F174" t="n">
         <v>3</v>
       </c>
-      <c r="G174" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H174" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I174" t="n">
-        <v>108.3634492007963</v>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -5859,14 +5157,10 @@
       <c r="F175" t="n">
         <v>1</v>
       </c>
-      <c r="G175" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H175" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I175" t="n">
-        <v>128.8557097613833</v>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -5890,14 +5184,10 @@
       <c r="F176" t="n">
         <v>1</v>
       </c>
-      <c r="G176" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H176" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I176" t="n">
-        <v>261.3949162110506</v>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -5921,14 +5211,10 @@
       <c r="F177" t="n">
         <v>3</v>
       </c>
-      <c r="G177" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H177" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I177" t="n">
-        <v>291.7330142189344</v>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -5952,14 +5238,10 @@
       <c r="F178" t="n">
         <v>3</v>
       </c>
-      <c r="G178" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H178" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I178" t="n">
-        <v>436.0282594747227</v>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -5983,14 +5265,10 @@
       <c r="F179" t="n">
         <v>3</v>
       </c>
-      <c r="G179" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H179" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I179" t="n">
-        <v>116.4654686920483</v>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="180">
@@ -6014,14 +5292,10 @@
       <c r="F180" t="n">
         <v>3</v>
       </c>
-      <c r="G180" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H180" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I180" t="n">
-        <v>147.1133911629679</v>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -6045,14 +5319,10 @@
       <c r="F181" t="n">
         <v>3</v>
       </c>
-      <c r="G181" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H181" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I181" t="n">
-        <v>112.1407207819316</v>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -6076,14 +5346,10 @@
       <c r="F182" t="n">
         <v>3</v>
       </c>
-      <c r="G182" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H182" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I182" t="n">
-        <v>134.5946867737809</v>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="183">
@@ -6107,14 +5373,10 @@
       <c r="F183" t="n">
         <v>3</v>
       </c>
-      <c r="G183" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H183" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I183" t="n">
-        <v>134.9979401079424</v>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="184">
@@ -6138,14 +5400,10 @@
       <c r="F184" t="n">
         <v>3</v>
       </c>
-      <c r="G184" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H184" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I184" t="n">
-        <v>116.9610396796634</v>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="185">
@@ -6169,14 +5427,10 @@
       <c r="F185" t="n">
         <v>3</v>
       </c>
-      <c r="G185" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H185" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I185" t="n">
-        <v>141.1914671328136</v>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -6200,14 +5454,10 @@
       <c r="F186" t="n">
         <v>3</v>
       </c>
-      <c r="G186" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H186" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I186" t="n">
-        <v>134.8274477844502</v>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="187">
@@ -6231,14 +5481,10 @@
       <c r="F187" t="n">
         <v>1</v>
       </c>
-      <c r="G187" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H187" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I187" t="n">
-        <v>130.8889150933765</v>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="188">
@@ -6262,14 +5508,10 @@
       <c r="F188" t="n">
         <v>3</v>
       </c>
-      <c r="G188" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H188" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I188" t="n">
-        <v>124.0243692895168</v>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -6293,14 +5535,10 @@
       <c r="F189" t="n">
         <v>1</v>
       </c>
-      <c r="G189" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H189" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I189" t="n">
-        <v>126.5585470698784</v>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="190">
@@ -6324,14 +5562,10 @@
       <c r="F190" t="n">
         <v>3</v>
       </c>
-      <c r="G190" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H190" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I190" t="n">
-        <v>438.2231249765429</v>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -6355,14 +5589,10 @@
       <c r="F191" t="n">
         <v>1</v>
       </c>
-      <c r="G191" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H191" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I191" t="n">
-        <v>48.24146554135529</v>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -6386,14 +5616,10 @@
       <c r="F192" t="n">
         <v>3</v>
       </c>
-      <c r="G192" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H192" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I192" t="n">
-        <v>436.3721841702692</v>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -6417,14 +5643,10 @@
       <c r="F193" t="n">
         <v>3</v>
       </c>
-      <c r="G193" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H193" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I193" t="n">
-        <v>418.9682152063426</v>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -6448,14 +5670,10 @@
       <c r="F194" t="n">
         <v>1</v>
       </c>
-      <c r="G194" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H194" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I194" t="n">
-        <v>119.0492898577379</v>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="195">
@@ -6479,14 +5697,10 @@
       <c r="F195" t="n">
         <v>3</v>
       </c>
-      <c r="G195" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H195" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I195" t="n">
-        <v>111.7612942561259</v>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -6510,14 +5724,10 @@
       <c r="F196" t="n">
         <v>3</v>
       </c>
-      <c r="G196" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H196" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I196" t="n">
-        <v>134.711526205172</v>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -6541,14 +5751,10 @@
       <c r="F197" t="n">
         <v>1</v>
       </c>
-      <c r="G197" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H197" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I197" t="n">
-        <v>114.5356707531311</v>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -6572,14 +5778,10 @@
       <c r="F198" t="n">
         <v>1</v>
       </c>
-      <c r="G198" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H198" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I198" t="n">
-        <v>193.5390688888536</v>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="199">
@@ -6603,14 +5805,10 @@
       <c r="F199" t="n">
         <v>3</v>
       </c>
-      <c r="G199" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H199" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I199" t="n">
-        <v>119.4607446504558</v>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="200">
@@ -6634,14 +5832,10 @@
       <c r="F200" t="n">
         <v>3</v>
       </c>
-      <c r="G200" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H200" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I200" t="n">
-        <v>128.1223886851244</v>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="201">
@@ -6665,14 +5859,10 @@
       <c r="F201" t="n">
         <v>3</v>
       </c>
-      <c r="G201" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H201" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I201" t="n">
-        <v>114.3936628670256</v>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -6696,14 +5886,10 @@
       <c r="F202" t="n">
         <v>3</v>
       </c>
-      <c r="G202" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H202" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I202" t="n">
-        <v>133.3570028934936</v>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="203">
@@ -6727,14 +5913,10 @@
       <c r="F203" t="n">
         <v>1</v>
       </c>
-      <c r="G203" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H203" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I203" t="n">
-        <v>0</v>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -6758,14 +5940,10 @@
       <c r="F204" t="n">
         <v>3</v>
       </c>
-      <c r="G204" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H204" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I204" t="n">
-        <v>102.4988016091568</v>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -6789,14 +5967,10 @@
       <c r="F205" t="n">
         <v>1</v>
       </c>
-      <c r="G205" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H205" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I205" t="n">
-        <v>109.6498692303138</v>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -6820,14 +5994,10 @@
       <c r="F206" t="n">
         <v>1</v>
       </c>
-      <c r="G206" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H206" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I206" t="n">
-        <v>177.0070370007507</v>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -6851,14 +6021,10 @@
       <c r="F207" t="n">
         <v>1</v>
       </c>
-      <c r="G207" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H207" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I207" t="n">
-        <v>133.083631777126</v>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -6882,14 +6048,10 @@
       <c r="F208" t="n">
         <v>3</v>
       </c>
-      <c r="G208" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H208" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I208" t="n">
-        <v>169.6926348159986</v>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -6913,14 +6075,10 @@
       <c r="F209" t="n">
         <v>3</v>
       </c>
-      <c r="G209" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H209" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I209" t="n">
-        <v>136.2060012010795</v>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -6944,14 +6102,10 @@
       <c r="F210" t="n">
         <v>3</v>
       </c>
-      <c r="G210" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H210" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I210" t="n">
-        <v>145.4749115339448</v>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -6975,14 +6129,10 @@
       <c r="F211" t="n">
         <v>3</v>
       </c>
-      <c r="G211" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H211" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I211" t="n">
-        <v>122.4259668926803</v>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -7006,14 +6156,10 @@
       <c r="F212" t="n">
         <v>1</v>
       </c>
-      <c r="G212" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H212" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I212" t="n">
-        <v>128.4198979733378</v>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -7037,14 +6183,10 @@
       <c r="F213" t="n">
         <v>2</v>
       </c>
-      <c r="G213" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H213" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I213" t="n">
-        <v>293.0078099324624</v>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -7068,14 +6210,10 @@
       <c r="F214" t="n">
         <v>2</v>
       </c>
-      <c r="G214" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H214" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I214" t="n">
-        <v>202.5074104591879</v>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="215">
@@ -7099,14 +6237,10 @@
       <c r="F215" t="n">
         <v>2</v>
       </c>
-      <c r="G215" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H215" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I215" t="n">
-        <v>247.1484952508124</v>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -7130,14 +6264,10 @@
       <c r="F216" t="n">
         <v>2</v>
       </c>
-      <c r="G216" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H216" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I216" t="n">
-        <v>7.877625454614061</v>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="217">
@@ -7161,14 +6291,10 @@
       <c r="F217" t="n">
         <v>2</v>
       </c>
-      <c r="G217" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H217" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I217" t="n">
-        <v>281.2353818778071</v>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -7192,14 +6318,10 @@
       <c r="F218" t="n">
         <v>2</v>
       </c>
-      <c r="G218" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H218" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I218" t="n">
-        <v>272.7502614006317</v>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="219">
@@ -7223,14 +6345,10 @@
       <c r="F219" t="n">
         <v>2</v>
       </c>
-      <c r="G219" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H219" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I219" t="n">
-        <v>283.2494890916812</v>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -7254,14 +6372,10 @@
       <c r="F220" t="n">
         <v>2</v>
       </c>
-      <c r="G220" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H220" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I220" t="n">
-        <v>244.5433569933228</v>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="221">
@@ -7285,14 +6399,10 @@
       <c r="F221" t="n">
         <v>2</v>
       </c>
-      <c r="G221" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H221" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I221" t="n">
-        <v>183.716888108934</v>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -7316,14 +6426,10 @@
       <c r="F222" t="n">
         <v>2</v>
       </c>
-      <c r="G222" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H222" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I222" t="n">
-        <v>239.8845366495564</v>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -7347,14 +6453,10 @@
       <c r="F223" t="n">
         <v>2</v>
       </c>
-      <c r="G223" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H223" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I223" t="n">
-        <v>310.008385160804</v>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="224">
@@ -7378,14 +6480,10 @@
       <c r="F224" t="n">
         <v>2</v>
       </c>
-      <c r="G224" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H224" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I224" t="n">
-        <v>186.8134948945622</v>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -7409,14 +6507,10 @@
       <c r="F225" t="n">
         <v>2</v>
       </c>
-      <c r="G225" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H225" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I225" t="n">
-        <v>288.1586060236781</v>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="226">
@@ -7440,14 +6534,10 @@
       <c r="F226" t="n">
         <v>2</v>
       </c>
-      <c r="G226" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H226" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I226" t="n">
-        <v>98.92707015264052</v>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="227">
@@ -7471,14 +6561,10 @@
       <c r="F227" t="n">
         <v>2</v>
       </c>
-      <c r="G227" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H227" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I227" t="n">
-        <v>280.6157282157816</v>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="228">
@@ -7502,14 +6588,10 @@
       <c r="F228" t="n">
         <v>2</v>
       </c>
-      <c r="G228" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H228" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I228" t="n">
-        <v>122.6538617562854</v>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="229">
@@ -7533,14 +6615,10 @@
       <c r="F229" t="n">
         <v>2</v>
       </c>
-      <c r="G229" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H229" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I229" t="n">
-        <v>247.2103171220905</v>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="230">
@@ -7564,14 +6642,10 @@
       <c r="F230" t="n">
         <v>2</v>
       </c>
-      <c r="G230" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H230" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I230" t="n">
-        <v>3.010294257504305</v>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="231">
@@ -7595,14 +6669,10 @@
       <c r="F231" t="n">
         <v>2</v>
       </c>
-      <c r="G231" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H231" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I231" t="n">
-        <v>243.5290276604762</v>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -7626,14 +6696,10 @@
       <c r="F232" t="n">
         <v>2</v>
       </c>
-      <c r="G232" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H232" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I232" t="n">
-        <v>185.1941899725348</v>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="233">
@@ -7657,14 +6723,10 @@
       <c r="F233" t="n">
         <v>2</v>
       </c>
-      <c r="G233" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H233" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I233" t="n">
-        <v>122.5932704758844</v>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -7688,14 +6750,10 @@
       <c r="F234" t="n">
         <v>2</v>
       </c>
-      <c r="G234" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H234" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I234" t="n">
-        <v>313.3976962041365</v>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="235">
@@ -7719,14 +6777,10 @@
       <c r="F235" t="n">
         <v>2</v>
       </c>
-      <c r="G235" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H235" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I235" t="n">
-        <v>200.1426029670162</v>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -7750,14 +6804,10 @@
       <c r="F236" t="n">
         <v>2</v>
       </c>
-      <c r="G236" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H236" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I236" t="n">
-        <v>181.8544965050952</v>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="237">
@@ -7781,14 +6831,10 @@
       <c r="F237" t="n">
         <v>2</v>
       </c>
-      <c r="G237" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H237" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I237" t="n">
-        <v>245.6061953817163</v>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="238">
@@ -7812,14 +6858,10 @@
       <c r="F238" t="n">
         <v>2</v>
       </c>
-      <c r="G238" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H238" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I238" t="n">
-        <v>245.0419989878996</v>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="239">
@@ -7843,14 +6885,10 @@
       <c r="F239" t="n">
         <v>2</v>
       </c>
-      <c r="G239" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H239" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I239" t="n">
-        <v>278.9705714377981</v>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="240">
@@ -7874,14 +6912,10 @@
       <c r="F240" t="n">
         <v>2</v>
       </c>
-      <c r="G240" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H240" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I240" t="n">
-        <v>317.2531958489987</v>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="241">
@@ -7905,14 +6939,10 @@
       <c r="F241" t="n">
         <v>2</v>
       </c>
-      <c r="G241" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H241" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I241" t="n">
-        <v>285.0912735432133</v>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="242">
@@ -7936,14 +6966,10 @@
       <c r="F242" t="n">
         <v>2</v>
       </c>
-      <c r="G242" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H242" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I242" t="n">
-        <v>0</v>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="243">
@@ -7967,14 +6993,10 @@
       <c r="F243" t="n">
         <v>2</v>
       </c>
-      <c r="G243" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H243" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I243" t="n">
-        <v>245.1650961673219</v>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="244">
@@ -7998,14 +7020,10 @@
       <c r="F244" t="n">
         <v>2</v>
       </c>
-      <c r="G244" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H244" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I244" t="n">
-        <v>112.2709331769165</v>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -8029,14 +7047,10 @@
       <c r="F245" t="n">
         <v>2</v>
       </c>
-      <c r="G245" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H245" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I245" t="n">
-        <v>178.0354467291626</v>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="246">
@@ -8060,14 +7074,10 @@
       <c r="F246" t="n">
         <v>2</v>
       </c>
-      <c r="G246" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H246" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I246" t="n">
-        <v>121.0099901785983</v>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="247">
@@ -8091,14 +7101,10 @@
       <c r="F247" t="n">
         <v>2</v>
       </c>
-      <c r="G247" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H247" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I247" t="n">
-        <v>176.0265855097184</v>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="248">
@@ -8122,14 +7128,10 @@
       <c r="F248" t="n">
         <v>2</v>
       </c>
-      <c r="G248" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H248" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I248" t="n">
-        <v>125.2053853727172</v>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="249">
@@ -8153,14 +7155,10 @@
       <c r="F249" t="n">
         <v>2</v>
       </c>
-      <c r="G249" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H249" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I249" t="n">
-        <v>243.0126961907182</v>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="250">
@@ -8184,14 +7182,10 @@
       <c r="F250" t="n">
         <v>2</v>
       </c>
-      <c r="G250" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H250" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I250" t="n">
-        <v>270.3924113793491</v>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -8215,14 +7209,10 @@
       <c r="F251" t="n">
         <v>2</v>
       </c>
-      <c r="G251" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H251" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I251" t="n">
-        <v>111.0756270606496</v>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="252">
@@ -8246,14 +7236,10 @@
       <c r="F252" t="n">
         <v>0</v>
       </c>
-      <c r="G252" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H252" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I252" t="n">
-        <v>654.0495989705499</v>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="253">
@@ -8277,14 +7263,10 @@
       <c r="F253" t="n">
         <v>0</v>
       </c>
-      <c r="G253" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H253" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I253" t="n">
-        <v>657.2556533005184</v>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="254">
@@ -8308,14 +7290,10 @@
       <c r="F254" t="n">
         <v>0</v>
       </c>
-      <c r="G254" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H254" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I254" t="n">
-        <v>675.9752592101149</v>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="255">
@@ -8339,14 +7317,10 @@
       <c r="F255" t="n">
         <v>0</v>
       </c>
-      <c r="G255" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H255" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I255" t="n">
-        <v>817.8434851869102</v>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="256">
@@ -8370,14 +7344,10 @@
       <c r="F256" t="n">
         <v>0</v>
       </c>
-      <c r="G256" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H256" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I256" t="n">
-        <v>815.968363029575</v>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="257">
@@ -8401,14 +7371,10 @@
       <c r="F257" t="n">
         <v>0</v>
       </c>
-      <c r="G257" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H257" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I257" t="n">
-        <v>674.8402225814028</v>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="258">
@@ -8432,14 +7398,10 @@
       <c r="F258" t="n">
         <v>0</v>
       </c>
-      <c r="G258" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H258" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I258" t="n">
-        <v>612.0341294292925</v>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="259">
@@ -8463,14 +7425,10 @@
       <c r="F259" t="n">
         <v>0</v>
       </c>
-      <c r="G259" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H259" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I259" t="n">
-        <v>963.8383437771967</v>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="260">
@@ -8494,14 +7452,10 @@
       <c r="F260" t="n">
         <v>0</v>
       </c>
-      <c r="G260" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H260" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I260" t="n">
-        <v>1164.946296812177</v>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="261">
@@ -8525,14 +7479,10 @@
       <c r="F261" t="n">
         <v>0</v>
       </c>
-      <c r="G261" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H261" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I261" t="n">
-        <v>606.305712694481</v>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="262">
@@ -8556,14 +7506,10 @@
       <c r="F262" t="n">
         <v>0</v>
       </c>
-      <c r="G262" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H262" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I262" t="n">
-        <v>1115.734345326284</v>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="263">
@@ -8587,14 +7533,10 @@
       <c r="F263" t="n">
         <v>0</v>
       </c>
-      <c r="G263" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H263" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I263" t="n">
-        <v>608.9859326801146</v>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -8618,14 +7560,10 @@
       <c r="F264" t="n">
         <v>0</v>
       </c>
-      <c r="G264" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H264" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I264" t="n">
-        <v>611.2631367385069</v>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="265">
@@ -8649,14 +7587,10 @@
       <c r="F265" t="n">
         <v>0</v>
       </c>
-      <c r="G265" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H265" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I265" t="n">
-        <v>963.0548320685086</v>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="266">
@@ -8680,14 +7614,10 @@
       <c r="F266" t="n">
         <v>0</v>
       </c>
-      <c r="G266" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H266" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I266" t="n">
-        <v>672.5567599657647</v>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -8711,14 +7641,10 @@
       <c r="F267" t="n">
         <v>0</v>
       </c>
-      <c r="G267" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H267" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I267" t="n">
-        <v>672.4465575073634</v>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="268">
@@ -8742,14 +7668,10 @@
       <c r="F268" t="n">
         <v>0</v>
       </c>
-      <c r="G268" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H268" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I268" t="n">
-        <v>1203.997132895375</v>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="269">
@@ -8773,14 +7695,10 @@
       <c r="F269" t="n">
         <v>0</v>
       </c>
-      <c r="G269" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H269" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I269" t="n">
-        <v>1193.182341268439</v>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="270">
@@ -8804,14 +7722,10 @@
       <c r="F270" t="n">
         <v>0</v>
       </c>
-      <c r="G270" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H270" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I270" t="n">
-        <v>644.2755978585902</v>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="271">
@@ -8835,14 +7749,10 @@
       <c r="F271" t="n">
         <v>0</v>
       </c>
-      <c r="G271" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H271" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I271" t="n">
-        <v>677.9672674443422</v>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="272">
@@ -8866,14 +7776,10 @@
       <c r="F272" t="n">
         <v>0</v>
       </c>
-      <c r="G272" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H272" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I272" t="n">
-        <v>631.4230938985899</v>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="273">
@@ -8897,14 +7803,10 @@
       <c r="F273" t="n">
         <v>0</v>
       </c>
-      <c r="G273" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H273" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I273" t="n">
-        <v>614.0519087916215</v>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="274">
@@ -8928,14 +7830,10 @@
       <c r="F274" t="n">
         <v>0</v>
       </c>
-      <c r="G274" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H274" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I274" t="n">
-        <v>676.8304565487422</v>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="275">
@@ -8959,14 +7857,10 @@
       <c r="F275" t="n">
         <v>0</v>
       </c>
-      <c r="G275" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H275" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I275" t="n">
-        <v>631.0355120310412</v>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="276">
@@ -8990,14 +7884,10 @@
       <c r="F276" t="n">
         <v>0</v>
       </c>
-      <c r="G276" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H276" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I276" t="n">
-        <v>609.5555961033466</v>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="277">
@@ -9021,14 +7911,10 @@
       <c r="F277" t="n">
         <v>0</v>
       </c>
-      <c r="G277" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H277" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I277" t="n">
-        <v>608.8754363832121</v>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="278">
@@ -9052,14 +7938,10 @@
       <c r="F278" t="n">
         <v>0</v>
       </c>
-      <c r="G278" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H278" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I278" t="n">
-        <v>658.1793923461422</v>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="279">
@@ -9083,14 +7965,10 @@
       <c r="F279" t="n">
         <v>0</v>
       </c>
-      <c r="G279" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H279" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I279" t="n">
-        <v>610.8968516256235</v>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="280">
@@ -9114,14 +7992,10 @@
       <c r="F280" t="n">
         <v>0</v>
       </c>
-      <c r="G280" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H280" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I280" t="n">
-        <v>1163.290649839514</v>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="281">
@@ -9145,14 +8019,10 @@
       <c r="F281" t="n">
         <v>0</v>
       </c>
-      <c r="G281" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H281" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I281" t="n">
-        <v>682.8607730764215</v>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="282">
@@ -9176,14 +8046,10 @@
       <c r="F282" t="n">
         <v>0</v>
       </c>
-      <c r="G282" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H282" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I282" t="n">
-        <v>614.5896566494074</v>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="283">
@@ -9207,14 +8073,10 @@
       <c r="F283" t="n">
         <v>0</v>
       </c>
-      <c r="G283" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H283" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I283" t="n">
-        <v>674.5450306216281</v>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="284">
@@ -9238,14 +8100,10 @@
       <c r="F284" t="n">
         <v>0</v>
       </c>
-      <c r="G284" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H284" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I284" t="n">
-        <v>675.9572730490926</v>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="285">
@@ -9269,14 +8127,10 @@
       <c r="F285" t="n">
         <v>0</v>
       </c>
-      <c r="G285" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H285" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I285" t="n">
-        <v>612.5478935079946</v>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="286">
@@ -9300,14 +8154,10 @@
       <c r="F286" t="n">
         <v>0</v>
       </c>
-      <c r="G286" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H286" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I286" t="n">
-        <v>676.9222917950851</v>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="287">
@@ -9331,14 +8181,10 @@
       <c r="F287" t="n">
         <v>0</v>
       </c>
-      <c r="G287" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H287" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I287" t="n">
-        <v>647.8696570805542</v>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="288">
@@ -9362,14 +8208,10 @@
       <c r="F288" t="n">
         <v>0</v>
       </c>
-      <c r="G288" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H288" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I288" t="n">
-        <v>926.223743210367</v>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="289">
@@ -9393,14 +8235,10 @@
       <c r="F289" t="n">
         <v>0</v>
       </c>
-      <c r="G289" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H289" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I289" t="n">
-        <v>1080.796368673745</v>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="290">
@@ -9424,14 +8262,10 @@
       <c r="F290" t="n">
         <v>1</v>
       </c>
-      <c r="G290" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H290" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I290" t="n">
-        <v>198.7340174551869</v>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="291">
@@ -9455,14 +8289,10 @@
       <c r="F291" t="n">
         <v>3</v>
       </c>
-      <c r="G291" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H291" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I291" t="n">
-        <v>544.7410571565025</v>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="292">
@@ -9486,14 +8316,10 @@
       <c r="F292" t="n">
         <v>3</v>
       </c>
-      <c r="G292" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H292" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I292" t="n">
-        <v>387.1866027474242</v>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="293">
@@ -9517,14 +8343,10 @@
       <c r="F293" t="n">
         <v>1</v>
       </c>
-      <c r="G293" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H293" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I293" t="n">
-        <v>194.2098531519203</v>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="294">
@@ -9548,14 +8370,10 @@
       <c r="F294" t="n">
         <v>3</v>
       </c>
-      <c r="G294" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H294" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I294" t="n">
-        <v>548.8846081556392</v>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="295">
@@ -9579,14 +8397,10 @@
       <c r="F295" t="n">
         <v>3</v>
       </c>
-      <c r="G295" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H295" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I295" t="n">
-        <v>398.8320502782476</v>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="296">
@@ -9610,14 +8424,10 @@
       <c r="F296" t="n">
         <v>1</v>
       </c>
-      <c r="G296" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H296" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I296" t="n">
-        <v>86.85520254824165</v>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="297">
@@ -9641,14 +8451,10 @@
       <c r="F297" t="n">
         <v>3</v>
       </c>
-      <c r="G297" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H297" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I297" t="n">
-        <v>514.7670845213308</v>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="298">
@@ -9672,14 +8478,10 @@
       <c r="F298" t="n">
         <v>1</v>
       </c>
-      <c r="G298" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H298" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I298" t="n">
-        <v>119.0213435784231</v>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="299">
@@ -9703,14 +8505,10 @@
       <c r="F299" t="n">
         <v>0</v>
       </c>
-      <c r="G299" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H299" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I299" t="n">
-        <v>538.8914330460158</v>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="300">
@@ -9734,14 +8532,10 @@
       <c r="F300" t="n">
         <v>1</v>
       </c>
-      <c r="G300" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H300" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I300" t="n">
-        <v>78.71036800981535</v>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="301">
@@ -9765,14 +8559,10 @@
       <c r="F301" t="n">
         <v>3</v>
       </c>
-      <c r="G301" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H301" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I301" t="n">
-        <v>603.7872090098596</v>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="302">
@@ -9796,14 +8586,10 @@
       <c r="F302" t="n">
         <v>3</v>
       </c>
-      <c r="G302" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H302" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I302" t="n">
-        <v>616.9081733070692</v>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="303">
@@ -9827,14 +8613,10 @@
       <c r="F303" t="n">
         <v>0</v>
       </c>
-      <c r="G303" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H303" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I303" t="n">
-        <v>527.9392354103214</v>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="304">
@@ -9858,14 +8640,10 @@
       <c r="F304" t="n">
         <v>0</v>
       </c>
-      <c r="G304" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H304" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I304" t="n">
-        <v>531.8289470141855</v>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="305">
@@ -9889,14 +8667,10 @@
       <c r="F305" t="n">
         <v>0</v>
       </c>
-      <c r="G305" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H305" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I305" t="n">
-        <v>529.237097246131</v>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="306">
@@ -9920,14 +8694,10 @@
       <c r="F306" t="n">
         <v>1</v>
       </c>
-      <c r="G306" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H306" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I306" t="n">
-        <v>203.4974733212369</v>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="307">
@@ -9951,14 +8721,10 @@
       <c r="F307" t="n">
         <v>1</v>
       </c>
-      <c r="G307" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H307" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I307" t="n">
-        <v>252.3661619701822</v>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="308">
@@ -9982,14 +8748,10 @@
       <c r="F308" t="n">
         <v>1</v>
       </c>
-      <c r="G308" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H308" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I308" t="n">
-        <v>82.74655715101427</v>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="309">
@@ -10013,14 +8775,10 @@
       <c r="F309" t="n">
         <v>0</v>
       </c>
-      <c r="G309" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H309" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I309" t="n">
-        <v>463.2446918697619</v>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="310">
@@ -10044,14 +8802,10 @@
       <c r="F310" t="n">
         <v>3</v>
       </c>
-      <c r="G310" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H310" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I310" t="n">
-        <v>495.4572343240575</v>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="311">
@@ -10075,14 +8829,10 @@
       <c r="F311" t="n">
         <v>1</v>
       </c>
-      <c r="G311" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H311" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I311" t="n">
-        <v>86.05735771627984</v>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="312">
@@ -10106,14 +8856,10 @@
       <c r="F312" t="n">
         <v>1</v>
       </c>
-      <c r="G312" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H312" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I312" t="n">
-        <v>201.8025101671006</v>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="313">
@@ -10137,14 +8883,10 @@
       <c r="F313" t="n">
         <v>1</v>
       </c>
-      <c r="G313" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H313" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I313" t="n">
-        <v>80.97729077071845</v>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="314">
@@ -10168,14 +8910,10 @@
       <c r="F314" t="n">
         <v>1</v>
       </c>
-      <c r="G314" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H314" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I314" t="n">
-        <v>190.3923763892437</v>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="315">
@@ -10199,14 +8937,10 @@
       <c r="F315" t="n">
         <v>1</v>
       </c>
-      <c r="G315" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H315" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I315" t="n">
-        <v>222.8034198030452</v>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="316">
@@ -10230,14 +8964,10 @@
       <c r="F316" t="n">
         <v>3</v>
       </c>
-      <c r="G316" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H316" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I316" t="n">
-        <v>603.0193547423979</v>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="317">
@@ -10261,14 +8991,10 @@
       <c r="F317" t="n">
         <v>1</v>
       </c>
-      <c r="G317" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H317" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I317" t="n">
-        <v>141.0264587247838</v>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="318">
@@ -10292,14 +9018,10 @@
       <c r="F318" t="n">
         <v>1</v>
       </c>
-      <c r="G318" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H318" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I318" t="n">
-        <v>69.42924372265375</v>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="319">
@@ -10323,14 +9045,10 @@
       <c r="F319" t="n">
         <v>3</v>
       </c>
-      <c r="G319" t="n">
-        <v>11.932</v>
-      </c>
-      <c r="H319" t="n">
-        <v>79.80800000000001</v>
-      </c>
-      <c r="I319" t="n">
-        <v>618.5065503160432</v>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>DC_4</t>
+        </is>
       </c>
     </row>
     <row r="320">
@@ -10354,14 +9072,10 @@
       <c r="F320" t="n">
         <v>0</v>
       </c>
-      <c r="G320" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H320" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I320" t="n">
-        <v>487.1237354251166</v>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="321">
@@ -10385,14 +9099,10 @@
       <c r="F321" t="n">
         <v>0</v>
       </c>
-      <c r="G321" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H321" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I321" t="n">
-        <v>531.2351788345484</v>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="322">
@@ -10416,14 +9126,10 @@
       <c r="F322" t="n">
         <v>1</v>
       </c>
-      <c r="G322" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H322" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I322" t="n">
-        <v>186.2355242450767</v>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="323">
@@ -10447,14 +9153,10 @@
       <c r="F323" t="n">
         <v>1</v>
       </c>
-      <c r="G323" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H323" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I323" t="n">
-        <v>251.1461470689249</v>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="324">
@@ -10478,14 +9180,10 @@
       <c r="F324" t="n">
         <v>1</v>
       </c>
-      <c r="G324" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H324" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I324" t="n">
-        <v>120.577629179741</v>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="325">
@@ -10509,14 +9207,10 @@
       <c r="F325" t="n">
         <v>1</v>
       </c>
-      <c r="G325" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H325" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I325" t="n">
-        <v>205.6885865734318</v>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="326">
@@ -10540,14 +9234,10 @@
       <c r="F326" t="n">
         <v>1</v>
       </c>
-      <c r="G326" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H326" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I326" t="n">
-        <v>76.50570748630093</v>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="327">
@@ -10571,14 +9261,10 @@
       <c r="F327" t="n">
         <v>0</v>
       </c>
-      <c r="G327" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H327" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I327" t="n">
-        <v>527.7266766298554</v>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="328">
@@ -10602,14 +9288,10 @@
       <c r="F328" t="n">
         <v>0</v>
       </c>
-      <c r="G328" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H328" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I328" t="n">
-        <v>520.9953547597188</v>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="329">
@@ -10633,14 +9315,10 @@
       <c r="F329" t="n">
         <v>1</v>
       </c>
-      <c r="G329" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H329" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I329" t="n">
-        <v>222.2658331540372</v>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="330">
@@ -10664,14 +9342,10 @@
       <c r="F330" t="n">
         <v>1</v>
       </c>
-      <c r="G330" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H330" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I330" t="n">
-        <v>199.6643731663934</v>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="331">
@@ -10695,14 +9369,10 @@
       <c r="F331" t="n">
         <v>0</v>
       </c>
-      <c r="G331" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H331" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I331" t="n">
-        <v>538.6129929671619</v>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="332">
@@ -10726,14 +9396,10 @@
       <c r="F332" t="n">
         <v>0</v>
       </c>
-      <c r="G332" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H332" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I332" t="n">
-        <v>452.6327905269922</v>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="333">
@@ -10757,14 +9423,10 @@
       <c r="F333" t="n">
         <v>0</v>
       </c>
-      <c r="G333" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H333" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I333" t="n">
-        <v>536.5966643261706</v>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="334">
@@ -10788,14 +9450,10 @@
       <c r="F334" t="n">
         <v>1</v>
       </c>
-      <c r="G334" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H334" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I334" t="n">
-        <v>204.2617751928779</v>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="335">
@@ -10819,14 +9477,10 @@
       <c r="F335" t="n">
         <v>1</v>
       </c>
-      <c r="G335" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H335" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I335" t="n">
-        <v>88.32300385715907</v>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="336">
@@ -10850,14 +9504,10 @@
       <c r="F336" t="n">
         <v>1</v>
       </c>
-      <c r="G336" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H336" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I336" t="n">
-        <v>261.7827362413553</v>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="337">
@@ -10881,14 +9531,10 @@
       <c r="F337" t="n">
         <v>1</v>
       </c>
-      <c r="G337" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H337" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I337" t="n">
-        <v>115.2811620794281</v>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -10912,14 +9558,10 @@
       <c r="F338" t="n">
         <v>0</v>
       </c>
-      <c r="G338" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H338" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I338" t="n">
-        <v>232.0059275504088</v>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="339">
@@ -10943,14 +9585,10 @@
       <c r="F339" t="n">
         <v>0</v>
       </c>
-      <c r="G339" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H339" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I339" t="n">
-        <v>449.5295655318793</v>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="340">
@@ -10974,14 +9612,10 @@
       <c r="F340" t="n">
         <v>0</v>
       </c>
-      <c r="G340" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H340" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I340" t="n">
-        <v>240.0194910557429</v>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="341">
@@ -11005,14 +9639,10 @@
       <c r="F341" t="n">
         <v>0</v>
       </c>
-      <c r="G341" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H341" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I341" t="n">
-        <v>222.1309978696864</v>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="342">
@@ -11036,14 +9666,10 @@
       <c r="F342" t="n">
         <v>0</v>
       </c>
-      <c r="G342" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H342" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I342" t="n">
-        <v>127.1752096431898</v>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="343">
@@ -11067,14 +9693,10 @@
       <c r="F343" t="n">
         <v>0</v>
       </c>
-      <c r="G343" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H343" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I343" t="n">
-        <v>237.1583322501107</v>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="344">
@@ -11098,14 +9720,10 @@
       <c r="F344" t="n">
         <v>0</v>
       </c>
-      <c r="G344" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H344" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I344" t="n">
-        <v>100.561335805435</v>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="345">
@@ -11129,14 +9747,10 @@
       <c r="F345" t="n">
         <v>0</v>
       </c>
-      <c r="G345" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H345" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I345" t="n">
-        <v>239.4850953574745</v>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="346">
@@ -11160,14 +9774,10 @@
       <c r="F346" t="n">
         <v>0</v>
       </c>
-      <c r="G346" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H346" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I346" t="n">
-        <v>237.2460590733673</v>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="347">
@@ -11191,14 +9801,10 @@
       <c r="F347" t="n">
         <v>0</v>
       </c>
-      <c r="G347" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H347" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I347" t="n">
-        <v>229.7705905025527</v>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="348">
@@ -11222,14 +9828,10 @@
       <c r="F348" t="n">
         <v>0</v>
       </c>
-      <c r="G348" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H348" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I348" t="n">
-        <v>244.4377595014983</v>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="349">
@@ -11253,14 +9855,10 @@
       <c r="F349" t="n">
         <v>0</v>
       </c>
-      <c r="G349" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H349" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I349" t="n">
-        <v>4.323769153544565</v>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="350">
@@ -11284,14 +9882,10 @@
       <c r="F350" t="n">
         <v>0</v>
       </c>
-      <c r="G350" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H350" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I350" t="n">
-        <v>449.0060316398882</v>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="351">
@@ -11315,14 +9909,10 @@
       <c r="F351" t="n">
         <v>0</v>
       </c>
-      <c r="G351" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H351" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I351" t="n">
-        <v>218.5983957853651</v>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="352">
@@ -11346,14 +9936,10 @@
       <c r="F352" t="n">
         <v>0</v>
       </c>
-      <c r="G352" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H352" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I352" t="n">
-        <v>8.425493051359885</v>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="353">
@@ -11377,14 +9963,10 @@
       <c r="F353" t="n">
         <v>0</v>
       </c>
-      <c r="G353" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H353" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I353" t="n">
-        <v>240.1142041561907</v>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="354">
@@ -11408,14 +9990,10 @@
       <c r="F354" t="n">
         <v>0</v>
       </c>
-      <c r="G354" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H354" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I354" t="n">
-        <v>158.5486842150996</v>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="355">
@@ -11439,14 +10017,10 @@
       <c r="F355" t="n">
         <v>0</v>
       </c>
-      <c r="G355" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H355" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I355" t="n">
-        <v>288.7749920793257</v>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="356">
@@ -11470,14 +10044,10 @@
       <c r="F356" t="n">
         <v>0</v>
       </c>
-      <c r="G356" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H356" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I356" t="n">
-        <v>7.332740432389794</v>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="357">
@@ -11501,14 +10071,10 @@
       <c r="F357" t="n">
         <v>0</v>
       </c>
-      <c r="G357" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H357" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I357" t="n">
-        <v>130.1980141958676</v>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="358">
@@ -11532,14 +10098,10 @@
       <c r="F358" t="n">
         <v>0</v>
       </c>
-      <c r="G358" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H358" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I358" t="n">
-        <v>223.2984791795251</v>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="359">
@@ -11563,14 +10125,10 @@
       <c r="F359" t="n">
         <v>0</v>
       </c>
-      <c r="G359" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H359" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I359" t="n">
-        <v>231.7447165935054</v>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="360">
@@ -11594,14 +10152,10 @@
       <c r="F360" t="n">
         <v>0</v>
       </c>
-      <c r="G360" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H360" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I360" t="n">
-        <v>238.1460451158673</v>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="361">
@@ -11625,14 +10179,10 @@
       <c r="F361" t="n">
         <v>0</v>
       </c>
-      <c r="G361" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H361" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I361" t="n">
-        <v>327.1629857666452</v>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="362">
@@ -11656,14 +10206,10 @@
       <c r="F362" t="n">
         <v>0</v>
       </c>
-      <c r="G362" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H362" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I362" t="n">
-        <v>241.906309273428</v>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="363">
@@ -11687,14 +10233,10 @@
       <c r="F363" t="n">
         <v>0</v>
       </c>
-      <c r="G363" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H363" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I363" t="n">
-        <v>239.2561349257448</v>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="364">
@@ -11718,14 +10260,10 @@
       <c r="F364" t="n">
         <v>0</v>
       </c>
-      <c r="G364" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H364" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I364" t="n">
-        <v>240.5813123263519</v>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="365">
@@ -11749,14 +10287,10 @@
       <c r="F365" t="n">
         <v>0</v>
       </c>
-      <c r="G365" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H365" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I365" t="n">
-        <v>240.5344159522229</v>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="366">
@@ -11780,14 +10314,10 @@
       <c r="F366" t="n">
         <v>0</v>
       </c>
-      <c r="G366" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H366" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I366" t="n">
-        <v>0</v>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="367">
@@ -11811,14 +10341,10 @@
       <c r="F367" t="n">
         <v>0</v>
       </c>
-      <c r="G367" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H367" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I367" t="n">
-        <v>498.0659858878445</v>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="368">
@@ -11842,14 +10368,10 @@
       <c r="F368" t="n">
         <v>0</v>
       </c>
-      <c r="G368" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H368" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I368" t="n">
-        <v>246.9743443515833</v>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="369">
@@ -11873,14 +10395,10 @@
       <c r="F369" t="n">
         <v>2</v>
       </c>
-      <c r="G369" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H369" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I369" t="n">
-        <v>684.6377060686082</v>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="370">
@@ -11904,14 +10422,10 @@
       <c r="F370" t="n">
         <v>2</v>
       </c>
-      <c r="G370" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H370" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I370" t="n">
-        <v>667.059677017294</v>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="371">
@@ -11935,14 +10449,10 @@
       <c r="F371" t="n">
         <v>2</v>
       </c>
-      <c r="G371" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H371" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I371" t="n">
-        <v>345.4761940888005</v>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="372">
@@ -11966,14 +10476,10 @@
       <c r="F372" t="n">
         <v>2</v>
       </c>
-      <c r="G372" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H372" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I372" t="n">
-        <v>809.6372609406922</v>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="373">
@@ -11997,14 +10503,10 @@
       <c r="F373" t="n">
         <v>2</v>
       </c>
-      <c r="G373" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H373" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I373" t="n">
-        <v>692.5646945749191</v>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="374">
@@ -12028,14 +10530,10 @@
       <c r="F374" t="n">
         <v>2</v>
       </c>
-      <c r="G374" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H374" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I374" t="n">
-        <v>697.059202201161</v>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="375">
@@ -12059,14 +10557,10 @@
       <c r="F375" t="n">
         <v>2</v>
       </c>
-      <c r="G375" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H375" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I375" t="n">
-        <v>667.4029191074147</v>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="376">
@@ -12090,14 +10584,10 @@
       <c r="F376" t="n">
         <v>2</v>
       </c>
-      <c r="G376" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H376" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I376" t="n">
-        <v>661.9466054945206</v>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="377">
@@ -12121,14 +10611,10 @@
       <c r="F377" t="n">
         <v>2</v>
       </c>
-      <c r="G377" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H377" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I377" t="n">
-        <v>814.7567434639592</v>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="378">
@@ -12152,14 +10638,10 @@
       <c r="F378" t="n">
         <v>2</v>
       </c>
-      <c r="G378" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H378" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I378" t="n">
-        <v>812.9217188777502</v>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="379">
@@ -12183,14 +10665,10 @@
       <c r="F379" t="n">
         <v>2</v>
       </c>
-      <c r="G379" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H379" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I379" t="n">
-        <v>666.8206222346315</v>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="380">
@@ -12214,14 +10692,10 @@
       <c r="F380" t="n">
         <v>2</v>
       </c>
-      <c r="G380" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H380" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I380" t="n">
-        <v>773.9366265170798</v>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="381">
@@ -12245,14 +10719,10 @@
       <c r="F381" t="n">
         <v>2</v>
       </c>
-      <c r="G381" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H381" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I381" t="n">
-        <v>395.2977564697037</v>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="382">
@@ -12276,14 +10746,10 @@
       <c r="F382" t="n">
         <v>2</v>
       </c>
-      <c r="G382" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H382" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I382" t="n">
-        <v>664.7425871489152</v>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="383">
@@ -12307,14 +10773,10 @@
       <c r="F383" t="n">
         <v>2</v>
       </c>
-      <c r="G383" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H383" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I383" t="n">
-        <v>662.4790379911934</v>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="384">
@@ -12338,14 +10800,10 @@
       <c r="F384" t="n">
         <v>2</v>
       </c>
-      <c r="G384" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H384" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I384" t="n">
-        <v>665.2603110236071</v>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="385">
@@ -12369,14 +10827,10 @@
       <c r="F385" t="n">
         <v>2</v>
       </c>
-      <c r="G385" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H385" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I385" t="n">
-        <v>693.1986315605174</v>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="386">
@@ -12400,14 +10854,10 @@
       <c r="F386" t="n">
         <v>2</v>
       </c>
-      <c r="G386" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H386" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I386" t="n">
-        <v>393.0868703259844</v>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="387">
@@ -12431,14 +10881,10 @@
       <c r="F387" t="n">
         <v>2</v>
       </c>
-      <c r="G387" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H387" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I387" t="n">
-        <v>669.3720454415242</v>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="388">
@@ -12462,14 +10908,10 @@
       <c r="F388" t="n">
         <v>2</v>
       </c>
-      <c r="G388" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H388" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I388" t="n">
-        <v>658.2278498242672</v>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="389">
@@ -12493,14 +10935,10 @@
       <c r="F389" t="n">
         <v>2</v>
       </c>
-      <c r="G389" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H389" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I389" t="n">
-        <v>658.6394579412456</v>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="390">
@@ -12524,14 +10962,10 @@
       <c r="F390" t="n">
         <v>2</v>
       </c>
-      <c r="G390" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H390" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I390" t="n">
-        <v>667.9985859330366</v>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="391">
@@ -12555,14 +10989,10 @@
       <c r="F391" t="n">
         <v>2</v>
       </c>
-      <c r="G391" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H391" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I391" t="n">
-        <v>839.4870454669223</v>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="392">
@@ -12586,14 +11016,10 @@
       <c r="F392" t="n">
         <v>2</v>
       </c>
-      <c r="G392" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H392" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I392" t="n">
-        <v>660.3590825727019</v>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="393">
@@ -12617,14 +11043,10 @@
       <c r="F393" t="n">
         <v>2</v>
       </c>
-      <c r="G393" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H393" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I393" t="n">
-        <v>817.3587322788459</v>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="394">
@@ -12648,14 +11070,10 @@
       <c r="F394" t="n">
         <v>2</v>
       </c>
-      <c r="G394" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H394" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I394" t="n">
-        <v>655.4684498885089</v>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="395">
@@ -12679,14 +11097,10 @@
       <c r="F395" t="n">
         <v>2</v>
       </c>
-      <c r="G395" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H395" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I395" t="n">
-        <v>645.4247065034406</v>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="396">
@@ -12710,14 +11124,10 @@
       <c r="F396" t="n">
         <v>2</v>
       </c>
-      <c r="G396" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H396" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I396" t="n">
-        <v>759.096649040336</v>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="397">
@@ -12741,14 +11151,10 @@
       <c r="F397" t="n">
         <v>1</v>
       </c>
-      <c r="G397" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H397" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I397" t="n">
-        <v>415.009614916183</v>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="398">
@@ -12772,14 +11178,10 @@
       <c r="F398" t="n">
         <v>1</v>
       </c>
-      <c r="G398" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H398" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I398" t="n">
-        <v>327.9025730956491</v>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="399">
@@ -12803,14 +11205,10 @@
       <c r="F399" t="n">
         <v>2</v>
       </c>
-      <c r="G399" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H399" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I399" t="n">
-        <v>708.5556326549978</v>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="400">
@@ -12834,14 +11232,10 @@
       <c r="F400" t="n">
         <v>1</v>
       </c>
-      <c r="G400" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H400" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I400" t="n">
-        <v>424.8576969456294</v>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="401">
@@ -12865,14 +11259,10 @@
       <c r="F401" t="n">
         <v>1</v>
       </c>
-      <c r="G401" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H401" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I401" t="n">
-        <v>416.2005603092672</v>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="402">
@@ -12896,14 +11286,10 @@
       <c r="F402" t="n">
         <v>1</v>
       </c>
-      <c r="G402" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H402" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I402" t="n">
-        <v>544.0754229492221</v>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="403">
@@ -12927,14 +11313,10 @@
       <c r="F403" t="n">
         <v>1</v>
       </c>
-      <c r="G403" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H403" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I403" t="n">
-        <v>420.202670184769</v>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="404">
@@ -12958,14 +11340,10 @@
       <c r="F404" t="n">
         <v>1</v>
       </c>
-      <c r="G404" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H404" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I404" t="n">
-        <v>551.0550366523886</v>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="405">
@@ -12989,14 +11367,10 @@
       <c r="F405" t="n">
         <v>2</v>
       </c>
-      <c r="G405" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H405" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I405" t="n">
-        <v>754.7512233039906</v>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="406">
@@ -13020,14 +11394,10 @@
       <c r="F406" t="n">
         <v>1</v>
       </c>
-      <c r="G406" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H406" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I406" t="n">
-        <v>819.081017682002</v>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="407">
@@ -13051,14 +11421,10 @@
       <c r="F407" t="n">
         <v>1</v>
       </c>
-      <c r="G407" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H407" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I407" t="n">
-        <v>415.8483188672218</v>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="408">
@@ -13082,14 +11448,10 @@
       <c r="F408" t="n">
         <v>2</v>
       </c>
-      <c r="G408" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H408" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I408" t="n">
-        <v>706.8435802078126</v>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="409">
@@ -13113,14 +11475,10 @@
       <c r="F409" t="n">
         <v>1</v>
       </c>
-      <c r="G409" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H409" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I409" t="n">
-        <v>543.2854203611975</v>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="410">
@@ -13144,14 +11502,10 @@
       <c r="F410" t="n">
         <v>2</v>
       </c>
-      <c r="G410" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H410" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I410" t="n">
-        <v>754.0080682376204</v>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="411">
@@ -13175,14 +11529,10 @@
       <c r="F411" t="n">
         <v>1</v>
       </c>
-      <c r="G411" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H411" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I411" t="n">
-        <v>416.3976600846781</v>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="412">
@@ -13206,14 +11556,10 @@
       <c r="F412" t="n">
         <v>1</v>
       </c>
-      <c r="G412" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H412" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I412" t="n">
-        <v>751.1032541835341</v>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="413">
@@ -13237,14 +11583,10 @@
       <c r="F413" t="n">
         <v>1</v>
       </c>
-      <c r="G413" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H413" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I413" t="n">
-        <v>527.8764943638412</v>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="414">
@@ -13268,14 +11610,10 @@
       <c r="F414" t="n">
         <v>2</v>
       </c>
-      <c r="G414" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H414" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I414" t="n">
-        <v>735.5434827869196</v>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="415">
@@ -13299,14 +11637,10 @@
       <c r="F415" t="n">
         <v>1</v>
       </c>
-      <c r="G415" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H415" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I415" t="n">
-        <v>709.1028726243128</v>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="416">
@@ -13330,14 +11664,10 @@
       <c r="F416" t="n">
         <v>1</v>
       </c>
-      <c r="G416" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H416" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I416" t="n">
-        <v>753.7774386585002</v>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="417">
@@ -13361,14 +11691,10 @@
       <c r="F417" t="n">
         <v>2</v>
       </c>
-      <c r="G417" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H417" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I417" t="n">
-        <v>732.5765480359983</v>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="418">
@@ -13392,14 +11718,10 @@
       <c r="F418" t="n">
         <v>0</v>
       </c>
-      <c r="G418" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H418" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I418" t="n">
-        <v>352.2708032599324</v>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="419">
@@ -13423,14 +11745,10 @@
       <c r="F419" t="n">
         <v>2</v>
       </c>
-      <c r="G419" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H419" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I419" t="n">
-        <v>464.6875588235764</v>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="420">
@@ -13454,14 +11772,10 @@
       <c r="F420" t="n">
         <v>0</v>
       </c>
-      <c r="G420" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H420" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I420" t="n">
-        <v>348.5444294950024</v>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="421">
@@ -13485,14 +11799,10 @@
       <c r="F421" t="n">
         <v>0</v>
       </c>
-      <c r="G421" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H421" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I421" t="n">
-        <v>317.6587842948209</v>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="422">
@@ -13516,14 +11826,10 @@
       <c r="F422" t="n">
         <v>0</v>
       </c>
-      <c r="G422" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H422" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I422" t="n">
-        <v>349.8429211656053</v>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="423">
@@ -13547,14 +11853,10 @@
       <c r="F423" t="n">
         <v>2</v>
       </c>
-      <c r="G423" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H423" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I423" t="n">
-        <v>476.0512132923942</v>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="424">
@@ -13578,14 +11880,10 @@
       <c r="F424" t="n">
         <v>0</v>
       </c>
-      <c r="G424" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H424" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I424" t="n">
-        <v>356.2488929966848</v>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="425">
@@ -13609,14 +11907,10 @@
       <c r="F425" t="n">
         <v>2</v>
       </c>
-      <c r="G425" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H425" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I425" t="n">
-        <v>435.0067517631766</v>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="426">
@@ -13640,14 +11934,10 @@
       <c r="F426" t="n">
         <v>0</v>
       </c>
-      <c r="G426" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H426" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I426" t="n">
-        <v>283.899039519618</v>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="427">
@@ -13671,14 +11961,10 @@
       <c r="F427" t="n">
         <v>0</v>
       </c>
-      <c r="G427" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H427" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I427" t="n">
-        <v>358.1093333865317</v>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="428">
@@ -13702,14 +11988,10 @@
       <c r="F428" t="n">
         <v>2</v>
       </c>
-      <c r="G428" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H428" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I428" t="n">
-        <v>431.9211572336359</v>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="429">
@@ -13733,14 +12015,10 @@
       <c r="F429" t="n">
         <v>2</v>
       </c>
-      <c r="G429" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H429" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I429" t="n">
-        <v>448.3167262042315</v>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="430">
@@ -13764,14 +12042,10 @@
       <c r="F430" t="n">
         <v>2</v>
       </c>
-      <c r="G430" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H430" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I430" t="n">
-        <v>454.3869696018361</v>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="431">
@@ -13795,14 +12069,10 @@
       <c r="F431" t="n">
         <v>2</v>
       </c>
-      <c r="G431" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H431" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I431" t="n">
-        <v>402.7535822110416</v>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="432">
@@ -13826,14 +12096,10 @@
       <c r="F432" t="n">
         <v>1</v>
       </c>
-      <c r="G432" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H432" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I432" t="n">
-        <v>401.2120384632639</v>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="433">
@@ -13857,14 +12123,10 @@
       <c r="F433" t="n">
         <v>2</v>
       </c>
-      <c r="G433" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H433" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I433" t="n">
-        <v>586.2836841079591</v>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="434">
@@ -13888,14 +12150,10 @@
       <c r="F434" t="n">
         <v>0</v>
       </c>
-      <c r="G434" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H434" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I434" t="n">
-        <v>226.8076077869137</v>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="435">
@@ -13919,14 +12177,10 @@
       <c r="F435" t="n">
         <v>2</v>
       </c>
-      <c r="G435" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H435" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I435" t="n">
-        <v>425.1245783437258</v>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="436">
@@ -13950,14 +12204,10 @@
       <c r="F436" t="n">
         <v>2</v>
       </c>
-      <c r="G436" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H436" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I436" t="n">
-        <v>472.2718542108274</v>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="437">
@@ -13981,14 +12231,10 @@
       <c r="F437" t="n">
         <v>2</v>
       </c>
-      <c r="G437" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H437" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I437" t="n">
-        <v>451.4703665004056</v>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="438">
@@ -14012,14 +12258,10 @@
       <c r="F438" t="n">
         <v>2</v>
       </c>
-      <c r="G438" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H438" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I438" t="n">
-        <v>455.4770701428037</v>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="439">
@@ -14043,14 +12285,10 @@
       <c r="F439" t="n">
         <v>0</v>
       </c>
-      <c r="G439" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H439" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I439" t="n">
-        <v>450.3268626159437</v>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="440">
@@ -14074,14 +12312,10 @@
       <c r="F440" t="n">
         <v>2</v>
       </c>
-      <c r="G440" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H440" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I440" t="n">
-        <v>578.1346100863037</v>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="441">
@@ -14105,14 +12339,10 @@
       <c r="F441" t="n">
         <v>2</v>
       </c>
-      <c r="G441" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H441" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I441" t="n">
-        <v>611.7791003545207</v>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="442">
@@ -14136,14 +12366,10 @@
       <c r="F442" t="n">
         <v>2</v>
       </c>
-      <c r="G442" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H442" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I442" t="n">
-        <v>416.4094642418626</v>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="443">
@@ -14167,14 +12393,10 @@
       <c r="F443" t="n">
         <v>2</v>
       </c>
-      <c r="G443" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H443" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I443" t="n">
-        <v>451.1887238220515</v>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="444">
@@ -14198,14 +12420,10 @@
       <c r="F444" t="n">
         <v>0</v>
       </c>
-      <c r="G444" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H444" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I444" t="n">
-        <v>352.7855567219063</v>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="445">
@@ -14229,14 +12447,10 @@
       <c r="F445" t="n">
         <v>0</v>
       </c>
-      <c r="G445" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H445" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I445" t="n">
-        <v>358.4728944274564</v>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="446">
@@ -14260,14 +12474,10 @@
       <c r="F446" t="n">
         <v>0</v>
       </c>
-      <c r="G446" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H446" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I446" t="n">
-        <v>351.3685656234222</v>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="447">
@@ -14291,14 +12501,10 @@
       <c r="F447" t="n">
         <v>2</v>
       </c>
-      <c r="G447" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H447" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I447" t="n">
-        <v>436.1780495857403</v>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="448">
@@ -14322,14 +12528,10 @@
       <c r="F448" t="n">
         <v>2</v>
       </c>
-      <c r="G448" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H448" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I448" t="n">
-        <v>578.0481855500648</v>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="449">
@@ -14353,14 +12555,10 @@
       <c r="F449" t="n">
         <v>2</v>
       </c>
-      <c r="G449" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H449" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I449" t="n">
-        <v>449.294709209044</v>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="450">
@@ -14384,14 +12582,10 @@
       <c r="F450" t="n">
         <v>1</v>
       </c>
-      <c r="G450" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H450" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I450" t="n">
-        <v>425.5718368268057</v>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="451">
@@ -14415,14 +12609,10 @@
       <c r="F451" t="n">
         <v>0</v>
       </c>
-      <c r="G451" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H451" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I451" t="n">
-        <v>283.4912379185273</v>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="452">
@@ -14446,14 +12636,10 @@
       <c r="F452" t="n">
         <v>2</v>
       </c>
-      <c r="G452" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H452" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I452" t="n">
-        <v>455.918363936613</v>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="453">
@@ -14477,14 +12663,10 @@
       <c r="F453" t="n">
         <v>0</v>
       </c>
-      <c r="G453" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H453" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I453" t="n">
-        <v>200.4257883708335</v>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="454">
@@ -14508,14 +12690,10 @@
       <c r="F454" t="n">
         <v>0</v>
       </c>
-      <c r="G454" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H454" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I454" t="n">
-        <v>380.4815627908063</v>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="455">
@@ -14539,14 +12717,10 @@
       <c r="F455" t="n">
         <v>2</v>
       </c>
-      <c r="G455" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H455" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I455" t="n">
-        <v>450.7566097914254</v>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="456">
@@ -14570,14 +12744,10 @@
       <c r="F456" t="n">
         <v>2</v>
       </c>
-      <c r="G456" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H456" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I456" t="n">
-        <v>456.3802514478284</v>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="457">
@@ -14601,14 +12771,10 @@
       <c r="F457" t="n">
         <v>0</v>
       </c>
-      <c r="G457" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H457" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I457" t="n">
-        <v>351.5381900550315</v>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="458">
@@ -14632,14 +12798,10 @@
       <c r="F458" t="n">
         <v>2</v>
       </c>
-      <c r="G458" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H458" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I458" t="n">
-        <v>582.6519633070533</v>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="459">
@@ -14663,14 +12825,10 @@
       <c r="F459" t="n">
         <v>0</v>
       </c>
-      <c r="G459" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H459" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I459" t="n">
-        <v>284.5859852288383</v>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="460">
@@ -14694,14 +12852,10 @@
       <c r="F460" t="n">
         <v>2</v>
       </c>
-      <c r="G460" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H460" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I460" t="n">
-        <v>429.1619622263655</v>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="461">
@@ -14725,14 +12879,10 @@
       <c r="F461" t="n">
         <v>2</v>
       </c>
-      <c r="G461" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H461" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I461" t="n">
-        <v>430.9858397127605</v>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="462">
@@ -14756,14 +12906,10 @@
       <c r="F462" t="n">
         <v>2</v>
       </c>
-      <c r="G462" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H462" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I462" t="n">
-        <v>405.4195200853111</v>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="463">
@@ -14787,14 +12933,10 @@
       <c r="F463" t="n">
         <v>2</v>
       </c>
-      <c r="G463" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H463" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I463" t="n">
-        <v>453.5340661688839</v>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="464">
@@ -14818,14 +12960,10 @@
       <c r="F464" t="n">
         <v>2</v>
       </c>
-      <c r="G464" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H464" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I464" t="n">
-        <v>422.731244131476</v>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="465">
@@ -14849,14 +12987,10 @@
       <c r="F465" t="n">
         <v>0</v>
       </c>
-      <c r="G465" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H465" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I465" t="n">
-        <v>354.7151027063582</v>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="466">
@@ -14880,14 +13014,10 @@
       <c r="F466" t="n">
         <v>0</v>
       </c>
-      <c r="G466" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H466" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I466" t="n">
-        <v>287.0135807377067</v>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="467">
@@ -14911,14 +13041,10 @@
       <c r="F467" t="n">
         <v>2</v>
       </c>
-      <c r="G467" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H467" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I467" t="n">
-        <v>453.8399374598185</v>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="468">
@@ -14942,14 +13068,10 @@
       <c r="F468" t="n">
         <v>2</v>
       </c>
-      <c r="G468" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H468" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I468" t="n">
-        <v>450.5248209684561</v>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="469">
@@ -14973,14 +13095,10 @@
       <c r="F469" t="n">
         <v>2</v>
       </c>
-      <c r="G469" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H469" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I469" t="n">
-        <v>435.244557042524</v>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="470">
@@ -15004,14 +13122,10 @@
       <c r="F470" t="n">
         <v>0</v>
       </c>
-      <c r="G470" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H470" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I470" t="n">
-        <v>353.7522909453127</v>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="471">
@@ -15035,14 +13149,10 @@
       <c r="F471" t="n">
         <v>0</v>
       </c>
-      <c r="G471" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H471" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I471" t="n">
-        <v>360.7583208996892</v>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="472">
@@ -15066,14 +13176,10 @@
       <c r="F472" t="n">
         <v>2</v>
       </c>
-      <c r="G472" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H472" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I472" t="n">
-        <v>456.9039792535207</v>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="473">
@@ -15097,14 +13203,10 @@
       <c r="F473" t="n">
         <v>2</v>
       </c>
-      <c r="G473" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H473" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I473" t="n">
-        <v>427.7880442510906</v>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="474">
@@ -15128,14 +13230,10 @@
       <c r="F474" t="n">
         <v>2</v>
       </c>
-      <c r="G474" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H474" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I474" t="n">
-        <v>580.2128763417709</v>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="475">
@@ -15159,14 +13257,10 @@
       <c r="F475" t="n">
         <v>2</v>
       </c>
-      <c r="G475" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H475" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I475" t="n">
-        <v>453.5677445825671</v>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="476">
@@ -15190,14 +13284,10 @@
       <c r="F476" t="n">
         <v>2</v>
       </c>
-      <c r="G476" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H476" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I476" t="n">
-        <v>576.6039326034715</v>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="477">
@@ -15221,14 +13311,10 @@
       <c r="F477" t="n">
         <v>2</v>
       </c>
-      <c r="G477" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H477" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I477" t="n">
-        <v>428.4301854542218</v>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="478">
@@ -15252,14 +13338,10 @@
       <c r="F478" t="n">
         <v>0</v>
       </c>
-      <c r="G478" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H478" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I478" t="n">
-        <v>355.125656142387</v>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="479">
@@ -15283,14 +13365,10 @@
       <c r="F479" t="n">
         <v>2</v>
       </c>
-      <c r="G479" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H479" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I479" t="n">
-        <v>434.0899258943054</v>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="480">
@@ -15314,14 +13392,10 @@
       <c r="F480" t="n">
         <v>2</v>
       </c>
-      <c r="G480" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H480" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I480" t="n">
-        <v>461.5717305808931</v>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="481">
@@ -15345,14 +13419,10 @@
       <c r="F481" t="n">
         <v>2</v>
       </c>
-      <c r="G481" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H481" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I481" t="n">
-        <v>427.7622499115371</v>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="482">
@@ -15376,14 +13446,10 @@
       <c r="F482" t="n">
         <v>2</v>
       </c>
-      <c r="G482" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H482" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I482" t="n">
-        <v>566.5589634993504</v>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="483">
@@ -15407,14 +13473,10 @@
       <c r="F483" t="n">
         <v>2</v>
       </c>
-      <c r="G483" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H483" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I483" t="n">
-        <v>556.9390920324611</v>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="484">
@@ -15438,14 +13500,10 @@
       <c r="F484" t="n">
         <v>2</v>
       </c>
-      <c r="G484" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H484" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I484" t="n">
-        <v>421.5417486600601</v>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="485">
@@ -15469,14 +13527,10 @@
       <c r="F485" t="n">
         <v>2</v>
       </c>
-      <c r="G485" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H485" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I485" t="n">
-        <v>443.3249832811464</v>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="486">
@@ -15500,14 +13554,10 @@
       <c r="F486" t="n">
         <v>0</v>
       </c>
-      <c r="G486" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H486" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I486" t="n">
-        <v>446.9389947794505</v>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="487">
@@ -15531,14 +13581,10 @@
       <c r="F487" t="n">
         <v>0</v>
       </c>
-      <c r="G487" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H487" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I487" t="n">
-        <v>160.8340261318925</v>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="488">
@@ -15562,14 +13608,10 @@
       <c r="F488" t="n">
         <v>1</v>
       </c>
-      <c r="G488" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H488" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I488" t="n">
-        <v>424.2660712055792</v>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="489">
@@ -15593,14 +13635,10 @@
       <c r="F489" t="n">
         <v>2</v>
       </c>
-      <c r="G489" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H489" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I489" t="n">
-        <v>429.5334567222677</v>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="490">
@@ -15624,14 +13662,10 @@
       <c r="F490" t="n">
         <v>2</v>
       </c>
-      <c r="G490" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H490" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I490" t="n">
-        <v>449.7269075445288</v>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="491">
@@ -15655,14 +13689,10 @@
       <c r="F491" t="n">
         <v>1</v>
       </c>
-      <c r="G491" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H491" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I491" t="n">
-        <v>423.7322331023271</v>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="492">
@@ -15686,14 +13716,10 @@
       <c r="F492" t="n">
         <v>0</v>
       </c>
-      <c r="G492" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H492" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I492" t="n">
-        <v>375.8744742030584</v>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="493">
@@ -15717,14 +13743,10 @@
       <c r="F493" t="n">
         <v>2</v>
       </c>
-      <c r="G493" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H493" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I493" t="n">
-        <v>420.4656003310083</v>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="494">
@@ -15748,14 +13770,10 @@
       <c r="F494" t="n">
         <v>2</v>
       </c>
-      <c r="G494" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H494" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I494" t="n">
-        <v>441.0949801553826</v>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="495">
@@ -15779,14 +13797,10 @@
       <c r="F495" t="n">
         <v>2</v>
       </c>
-      <c r="G495" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H495" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I495" t="n">
-        <v>431.0946313417494</v>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="496">
@@ -15810,14 +13824,10 @@
       <c r="F496" t="n">
         <v>1</v>
       </c>
-      <c r="G496" t="n">
-        <v>16.168</v>
-      </c>
-      <c r="H496" t="n">
-        <v>74.82899999999999</v>
-      </c>
-      <c r="I496" t="n">
-        <v>505.8755371911598</v>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
       </c>
     </row>
     <row r="497">
@@ -15841,14 +13851,10 @@
       <c r="F497" t="n">
         <v>0</v>
       </c>
-      <c r="G497" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H497" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I497" t="n">
-        <v>388.7157686271636</v>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="498">
@@ -15872,14 +13878,10 @@
       <c r="F498" t="n">
         <v>2</v>
       </c>
-      <c r="G498" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H498" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I498" t="n">
-        <v>392.6881253176529</v>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="499">
@@ -15903,14 +13905,10 @@
       <c r="F499" t="n">
         <v>2</v>
       </c>
-      <c r="G499" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H499" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I499" t="n">
-        <v>374.2917936817031</v>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="500">
@@ -15934,14 +13932,10 @@
       <c r="F500" t="n">
         <v>0</v>
       </c>
-      <c r="G500" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H500" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I500" t="n">
-        <v>284.291894084992</v>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="501">
@@ -15965,14 +13959,10 @@
       <c r="F501" t="n">
         <v>0</v>
       </c>
-      <c r="G501" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H501" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I501" t="n">
-        <v>281.8049758887568</v>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="502">
@@ -15996,14 +13986,10 @@
       <c r="F502" t="n">
         <v>2</v>
       </c>
-      <c r="G502" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H502" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I502" t="n">
-        <v>475.3866029147773</v>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
     <row r="503">
@@ -16027,14 +14013,10 @@
       <c r="F503" t="n">
         <v>0</v>
       </c>
-      <c r="G503" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H503" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I503" t="n">
-        <v>284.7327150864167</v>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="504">
@@ -16058,14 +14040,10 @@
       <c r="F504" t="n">
         <v>0</v>
       </c>
-      <c r="G504" t="n">
-        <v>22.254</v>
-      </c>
-      <c r="H504" t="n">
-        <v>84.908</v>
-      </c>
-      <c r="I504" t="n">
-        <v>311.8954044587077</v>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>DC_1</t>
+        </is>
       </c>
     </row>
     <row r="505">
@@ -16089,14 +14067,10 @@
       <c r="F505" t="n">
         <v>2</v>
       </c>
-      <c r="G505" t="n">
-        <v>26.803</v>
-      </c>
-      <c r="H505" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="I505" t="n">
-        <v>466.8530609246752</v>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>DC_3</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/clustered_output.xlsx
+++ b/clustered_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G505"/>
+  <dimension ref="A1:H505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>assigned_dc</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>distance_to_dc_km</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -484,12 +489,15 @@
         <v>41.29720544</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>293.8460057247369</v>
       </c>
     </row>
     <row r="3">
@@ -511,12 +519,15 @@
         <v>55.87958479999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>122.4928162679067</v>
       </c>
     </row>
     <row r="4">
@@ -538,12 +549,15 @@
         <v>33.26804828</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>365.5697738719786</v>
       </c>
     </row>
     <row r="5">
@@ -565,12 +579,15 @@
         <v>93.98859224</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>137.1836921009171</v>
       </c>
     </row>
     <row r="6">
@@ -592,12 +609,15 @@
         <v>40.42737347999999</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>370.9274282971861</v>
       </c>
     </row>
     <row r="7">
@@ -619,12 +639,15 @@
         <v>63.74664785</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>135.1668889158399</v>
       </c>
     </row>
     <row r="8">
@@ -646,12 +669,15 @@
         <v>86.27647392</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>245.074598671275</v>
       </c>
     </row>
     <row r="9">
@@ -673,12 +699,15 @@
         <v>91.16850180000002</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>304.8226550499002</v>
       </c>
     </row>
     <row r="10">
@@ -700,12 +729,15 @@
         <v>86.99766654</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>466.4283882980909</v>
       </c>
     </row>
     <row r="11">
@@ -727,12 +759,15 @@
         <v>82.87167607000001</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>472.7473727202855</v>
       </c>
     </row>
     <row r="12">
@@ -754,12 +789,15 @@
         <v>113.41016794</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>151.0314023786419</v>
       </c>
     </row>
     <row r="13">
@@ -781,12 +819,15 @@
         <v>90.7568601</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>155.8689391528941</v>
       </c>
     </row>
     <row r="14">
@@ -808,12 +849,15 @@
         <v>129.90572294</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>170.9279161682704</v>
       </c>
     </row>
     <row r="15">
@@ -835,12 +879,15 @@
         <v>39.66574248000001</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>413.5495142717604</v>
       </c>
     </row>
     <row r="16">
@@ -869,6 +916,9 @@
           <t>DC_4</t>
         </is>
       </c>
+      <c r="H16" t="n">
+        <v>414.1680610379193</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,12 +939,15 @@
         <v>71.55889309999998</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>155.8711978103603</v>
       </c>
     </row>
     <row r="18">
@@ -916,12 +969,15 @@
         <v>112.80354775</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>197.3786891663952</v>
       </c>
     </row>
     <row r="19">
@@ -943,12 +999,15 @@
         <v>73.57074283999999</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>150.8606934652393</v>
       </c>
     </row>
     <row r="20">
@@ -970,12 +1029,15 @@
         <v>48.18771840000001</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>147.942072551742</v>
       </c>
     </row>
     <row r="21">
@@ -997,12 +1059,15 @@
         <v>137.72677575</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>170.0748304559448</v>
       </c>
     </row>
     <row r="22">
@@ -1024,12 +1089,15 @@
         <v>61.96439013000001</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>274.7525032714101</v>
       </c>
     </row>
     <row r="23">
@@ -1051,12 +1119,15 @@
         <v>57.01195806</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>422.7970840515572</v>
       </c>
     </row>
     <row r="24">
@@ -1078,12 +1149,15 @@
         <v>75.03426994</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>44.80763566563145</v>
       </c>
     </row>
     <row r="25">
@@ -1105,12 +1179,15 @@
         <v>45.991</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>392.7470920930622</v>
       </c>
     </row>
     <row r="26">
@@ -1132,12 +1209,15 @@
         <v>69.51707707</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>296.4696464613529</v>
       </c>
     </row>
     <row r="27">
@@ -1159,12 +1239,15 @@
         <v>118.63043667</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>162.1806222902383</v>
       </c>
     </row>
     <row r="28">
@@ -1186,12 +1269,15 @@
         <v>39.05642559</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>390.3002980085579</v>
       </c>
     </row>
     <row r="29">
@@ -1213,12 +1299,15 @@
         <v>51.11150699</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>106.6790260503075</v>
       </c>
     </row>
     <row r="30">
@@ -1240,12 +1329,15 @@
         <v>90.55661511999999</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>260.1363480138145</v>
       </c>
     </row>
     <row r="31">
@@ -1267,12 +1359,15 @@
         <v>80.49179736000001</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>156.190021202696</v>
       </c>
     </row>
     <row r="32">
@@ -1294,12 +1389,15 @@
         <v>137.7462625</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>160.9219624355327</v>
       </c>
     </row>
     <row r="33">
@@ -1321,12 +1419,15 @@
         <v>82.06561287</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>398.7773663232627</v>
       </c>
     </row>
     <row r="34">
@@ -1348,12 +1449,15 @@
         <v>40.91439332</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>159.2187052602542</v>
       </c>
     </row>
     <row r="35">
@@ -1375,12 +1479,15 @@
         <v>94.20747311999999</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>159.2061091161018</v>
       </c>
     </row>
     <row r="36">
@@ -1402,12 +1509,15 @@
         <v>51.34208147000001</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>467.3803848016624</v>
       </c>
     </row>
     <row r="37">
@@ -1429,12 +1539,15 @@
         <v>89.43269527999999</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>44.22068792538425</v>
       </c>
     </row>
     <row r="38">
@@ -1456,12 +1569,15 @@
         <v>87.62353223</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>155.3531487189899</v>
       </c>
     </row>
     <row r="39">
@@ -1483,12 +1599,15 @@
         <v>113.62947597</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>384.5306082334927</v>
       </c>
     </row>
     <row r="40">
@@ -1510,12 +1629,15 @@
         <v>97.86042042</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>284.4129910582891</v>
       </c>
     </row>
     <row r="41">
@@ -1537,12 +1659,15 @@
         <v>120.70724466</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>24.49259868729828</v>
       </c>
     </row>
     <row r="42">
@@ -1564,12 +1689,15 @@
         <v>63.64605510000001</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>230.7789116574628</v>
       </c>
     </row>
     <row r="43">
@@ -1591,12 +1719,15 @@
         <v>79.88549751000001</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>94.04767826631056</v>
       </c>
     </row>
     <row r="44">
@@ -1618,12 +1749,15 @@
         <v>75.97018895000001</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>382.7309042653473</v>
       </c>
     </row>
     <row r="45">
@@ -1645,12 +1779,15 @@
         <v>58.83139722999999</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>277.0434321345084</v>
       </c>
     </row>
     <row r="46">
@@ -1672,12 +1809,15 @@
         <v>24.03516849</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>363.3676583725137</v>
       </c>
     </row>
     <row r="47">
@@ -1699,12 +1839,15 @@
         <v>17.60890872</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>367.859288993661</v>
       </c>
     </row>
     <row r="48">
@@ -1726,12 +1869,15 @@
         <v>82.63783919000001</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>148.5993207899491</v>
       </c>
     </row>
     <row r="49">
@@ -1753,12 +1899,15 @@
         <v>56.29949515999999</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>394.3261874511825</v>
       </c>
     </row>
     <row r="50">
@@ -1780,12 +1929,15 @@
         <v>47.27391910999999</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>466.862664902199</v>
       </c>
     </row>
     <row r="51">
@@ -1807,12 +1959,15 @@
         <v>55.12580752</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>244.0476712680346</v>
       </c>
     </row>
     <row r="52">
@@ -1834,12 +1989,15 @@
         <v>70.25959358</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>105.0335556921193</v>
       </c>
     </row>
     <row r="53">
@@ -1861,12 +2019,15 @@
         <v>62.59155026999998</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>109.7389620112709</v>
       </c>
     </row>
     <row r="54">
@@ -1888,12 +2049,15 @@
         <v>78.94616125999998</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>108.6104453741741</v>
       </c>
     </row>
     <row r="55">
@@ -1915,12 +2079,15 @@
         <v>101.76988238</v>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>164.3915028407905</v>
       </c>
     </row>
     <row r="56">
@@ -1942,12 +2109,15 @@
         <v>44.19095989</v>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>462.2694883273145</v>
       </c>
     </row>
     <row r="57">
@@ -1969,12 +2139,15 @@
         <v>93.80458936000001</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>378.9423803573275</v>
       </c>
     </row>
     <row r="58">
@@ -1996,12 +2169,15 @@
         <v>49.10406079999999</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>100.7259767775823</v>
       </c>
     </row>
     <row r="59">
@@ -2023,12 +2199,15 @@
         <v>99.07280474</v>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>165.351606625248</v>
       </c>
     </row>
     <row r="60">
@@ -2050,12 +2229,15 @@
         <v>69.66181495000001</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>155.0573123555761</v>
       </c>
     </row>
     <row r="61">
@@ -2077,12 +2259,15 @@
         <v>157.49350527</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>109.6785426341018</v>
       </c>
     </row>
     <row r="62">
@@ -2104,12 +2289,15 @@
         <v>69.61420304000001</v>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>146.6430460690046</v>
       </c>
     </row>
     <row r="63">
@@ -2131,12 +2319,15 @@
         <v>15.037</v>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>393.1682837749015</v>
       </c>
     </row>
     <row r="64">
@@ -2158,12 +2349,15 @@
         <v>33.56141599999999</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>245.079558964301</v>
       </c>
     </row>
     <row r="65">
@@ -2185,12 +2379,15 @@
         <v>122.2742197</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>92.73717022738394</v>
       </c>
     </row>
     <row r="66">
@@ -2212,12 +2409,15 @@
         <v>29.31689904</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>299.3569840336716</v>
       </c>
     </row>
     <row r="67">
@@ -2239,12 +2439,15 @@
         <v>24.08448896</v>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>144.2270060908566</v>
       </c>
     </row>
     <row r="68">
@@ -2266,12 +2469,15 @@
         <v>59.56919848</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>103.496349890505</v>
       </c>
     </row>
     <row r="69">
@@ -2293,12 +2499,15 @@
         <v>61.17361757</v>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>68.27692687408248</v>
       </c>
     </row>
     <row r="70">
@@ -2320,12 +2529,15 @@
         <v>45.19398898999999</v>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>160.2128384245894</v>
       </c>
     </row>
     <row r="71">
@@ -2347,12 +2559,15 @@
         <v>8.5903492</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>100.7259767775823</v>
       </c>
     </row>
     <row r="72">
@@ -2374,12 +2589,15 @@
         <v>77.60705583999999</v>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>153.1285040266745</v>
       </c>
     </row>
     <row r="73">
@@ -2401,12 +2619,15 @@
         <v>27.84522936</v>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>409.2001225630211</v>
       </c>
     </row>
     <row r="74">
@@ -2428,12 +2649,15 @@
         <v>121.24150382</v>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>151.6020550227136</v>
       </c>
     </row>
     <row r="75">
@@ -2455,12 +2679,15 @@
         <v>109.77473927</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>96.58126533093416</v>
       </c>
     </row>
     <row r="76">
@@ -2482,12 +2709,15 @@
         <v>27.96024677</v>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>450.0229442223006</v>
       </c>
     </row>
     <row r="77">
@@ -2509,12 +2739,15 @@
         <v>127.09983192</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>103.6119916373755</v>
       </c>
     </row>
     <row r="78">
@@ -2536,12 +2769,15 @@
         <v>40.97559472</v>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>190.6825132721265</v>
       </c>
     </row>
     <row r="79">
@@ -2563,12 +2799,15 @@
         <v>55.95136335999999</v>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>223.9844703950944</v>
       </c>
     </row>
     <row r="80">
@@ -2590,12 +2829,15 @@
         <v>99.95687511999999</v>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>168.4133991841169</v>
       </c>
     </row>
     <row r="81">
@@ -2617,12 +2859,15 @@
         <v>171.25894002</v>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>159.9084196272836</v>
       </c>
     </row>
     <row r="82">
@@ -2644,12 +2889,15 @@
         <v>108.25222513</v>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>155.1193933778405</v>
       </c>
     </row>
     <row r="83">
@@ -2671,12 +2919,15 @@
         <v>152.37332232</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>109.7499568719103</v>
       </c>
     </row>
     <row r="84">
@@ -2698,12 +2949,15 @@
         <v>137.64539505</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>103.1628998334891</v>
       </c>
     </row>
     <row r="85">
@@ -2725,12 +2979,15 @@
         <v>98.88650038</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>93.89827386045394</v>
       </c>
     </row>
     <row r="86">
@@ -2752,12 +3009,15 @@
         <v>174.43258149</v>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>154.4089620521199</v>
       </c>
     </row>
     <row r="87">
@@ -2779,12 +3039,15 @@
         <v>131.72022438</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>297.954671485222</v>
       </c>
     </row>
     <row r="88">
@@ -2806,12 +3069,15 @@
         <v>128.67002752</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>244.9376359487637</v>
       </c>
     </row>
     <row r="89">
@@ -2833,12 +3099,15 @@
         <v>151.83197394</v>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>158.5499688032886</v>
       </c>
     </row>
     <row r="90">
@@ -2860,12 +3129,15 @@
         <v>70.43858698000003</v>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>158.4325457480821</v>
       </c>
     </row>
     <row r="91">
@@ -2887,12 +3159,15 @@
         <v>165.86665209</v>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>150.0773248273609</v>
       </c>
     </row>
     <row r="92">
@@ -2914,12 +3189,15 @@
         <v>160.7944185</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>111.1930211145544</v>
       </c>
     </row>
     <row r="93">
@@ -2941,12 +3219,15 @@
         <v>114.30460316</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>103.1395370676297</v>
       </c>
     </row>
     <row r="94">
@@ -2968,12 +3249,15 @@
         <v>27.65862036</v>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>157.2643207295644</v>
       </c>
     </row>
     <row r="95">
@@ -2995,12 +3279,15 @@
         <v>107.20581291</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>110.9238212584267</v>
       </c>
     </row>
     <row r="96">
@@ -3022,12 +3309,15 @@
         <v>132.81126806</v>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>154.3148811061609</v>
       </c>
     </row>
     <row r="97">
@@ -3049,12 +3339,15 @@
         <v>151.87199567</v>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>160.7866229667267</v>
       </c>
     </row>
     <row r="98">
@@ -3076,12 +3369,15 @@
         <v>97.51930487999999</v>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>153.2436065110408</v>
       </c>
     </row>
     <row r="99">
@@ -3103,12 +3399,15 @@
         <v>62.68683512</v>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>394.5056466031788</v>
       </c>
     </row>
     <row r="100">
@@ -3130,12 +3429,15 @@
         <v>164.09465016</v>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>163.2868500698719</v>
       </c>
     </row>
     <row r="101">
@@ -3157,12 +3459,15 @@
         <v>115.75139108</v>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>150.4724269081669</v>
       </c>
     </row>
     <row r="102">
@@ -3184,12 +3489,15 @@
         <v>112.73454219</v>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>140.3539978684227</v>
       </c>
     </row>
     <row r="103">
@@ -3211,12 +3519,15 @@
         <v>165.16716377</v>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>147.6036965257908</v>
       </c>
     </row>
     <row r="104">
@@ -3238,12 +3549,15 @@
         <v>98.30353936999998</v>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>140.9713963838633</v>
       </c>
     </row>
     <row r="105">
@@ -3265,12 +3579,15 @@
         <v>64.32811749000001</v>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>382.5222745361521</v>
       </c>
     </row>
     <row r="106">
@@ -3292,12 +3609,15 @@
         <v>143.1621979</v>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>262.7324413613346</v>
       </c>
     </row>
     <row r="107">
@@ -3319,12 +3639,15 @@
         <v>62.72158742000001</v>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>463.6203705187395</v>
       </c>
     </row>
     <row r="108">
@@ -3346,12 +3669,15 @@
         <v>135.79601133</v>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>390.2487772391969</v>
       </c>
     </row>
     <row r="109">
@@ -3373,12 +3699,15 @@
         <v>67.78453388</v>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>153.539195695105</v>
       </c>
     </row>
     <row r="110">
@@ -3400,12 +3729,15 @@
         <v>135.40894881</v>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>297.4728206135632</v>
       </c>
     </row>
     <row r="111">
@@ -3427,12 +3759,15 @@
         <v>134.30264618</v>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>157.7435654334739</v>
       </c>
     </row>
     <row r="112">
@@ -3454,12 +3789,15 @@
         <v>107.39169483</v>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>146.3339933783038</v>
       </c>
     </row>
     <row r="113">
@@ -3481,12 +3819,15 @@
         <v>92.21966651000001</v>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>149.9757318464934</v>
       </c>
     </row>
     <row r="114">
@@ -3508,12 +3849,15 @@
         <v>46.65942816</v>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>275.4336495404298</v>
       </c>
     </row>
     <row r="115">
@@ -3535,12 +3879,15 @@
         <v>61.25313789</v>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>367.0969959282192</v>
       </c>
     </row>
     <row r="116">
@@ -3562,12 +3909,15 @@
         <v>95.79522047999998</v>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>143.5474732221657</v>
       </c>
     </row>
     <row r="117">
@@ -3589,12 +3939,15 @@
         <v>131.4488539</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>106.0711509208065</v>
       </c>
     </row>
     <row r="118">
@@ -3616,12 +3969,15 @@
         <v>139.22461155</v>
       </c>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>158.0974000785128</v>
       </c>
     </row>
     <row r="119">
@@ -3643,12 +3999,15 @@
         <v>69.87724643999999</v>
       </c>
       <c r="F119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>463.8843261091552</v>
       </c>
     </row>
     <row r="120">
@@ -3670,12 +4029,15 @@
         <v>26.29534809</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>297.8104472791561</v>
       </c>
     </row>
     <row r="121">
@@ -3697,12 +4059,15 @@
         <v>124.64185643</v>
       </c>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>162.1540802945918</v>
       </c>
     </row>
     <row r="122">
@@ -3724,12 +4089,15 @@
         <v>67.21328875</v>
       </c>
       <c r="F122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>150.4196753751032</v>
       </c>
     </row>
     <row r="123">
@@ -3751,12 +4119,15 @@
         <v>104.41013483</v>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>40.73116379217367</v>
       </c>
     </row>
     <row r="124">
@@ -3778,12 +4149,15 @@
         <v>55.17039302000001</v>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>151.2941074551429</v>
       </c>
     </row>
     <row r="125">
@@ -3805,12 +4179,15 @@
         <v>156.16160591</v>
       </c>
       <c r="F125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>137.6423599800942</v>
       </c>
     </row>
     <row r="126">
@@ -3832,12 +4209,15 @@
         <v>86.21620850000002</v>
       </c>
       <c r="F126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>141.7442910967588</v>
       </c>
     </row>
     <row r="127">
@@ -3859,12 +4239,15 @@
         <v>71.97972833</v>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>152.1140732346485</v>
       </c>
     </row>
     <row r="128">
@@ -3886,12 +4269,15 @@
         <v>116.03335498</v>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>148.417679040193</v>
       </c>
     </row>
     <row r="129">
@@ -3913,12 +4299,15 @@
         <v>87.04857329000001</v>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>155.2912736366582</v>
       </c>
     </row>
     <row r="130">
@@ -3940,12 +4329,15 @@
         <v>141.72703296</v>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>153.7467056988309</v>
       </c>
     </row>
     <row r="131">
@@ -3967,12 +4359,15 @@
         <v>145.58214742</v>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>68.55822665796128</v>
       </c>
     </row>
     <row r="132">
@@ -3994,12 +4389,15 @@
         <v>148.1403535</v>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>47.08708195175153</v>
       </c>
     </row>
     <row r="133">
@@ -4021,12 +4419,15 @@
         <v>39.35975862000001</v>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>391.8184530774033</v>
       </c>
     </row>
     <row r="134">
@@ -4048,12 +4449,15 @@
         <v>121.18436646</v>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>157.8095881689238</v>
       </c>
     </row>
     <row r="135">
@@ -4075,12 +4479,15 @@
         <v>174.54029805</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>171.5590778179512</v>
       </c>
     </row>
     <row r="136">
@@ -4102,12 +4509,15 @@
         <v>71.22344247000001</v>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>102.338791598857</v>
       </c>
     </row>
     <row r="137">
@@ -4129,12 +4539,15 @@
         <v>86.91646299999999</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>105.4461159483704</v>
       </c>
     </row>
     <row r="138">
@@ -4156,12 +4569,15 @@
         <v>113.58351808</v>
       </c>
       <c r="F138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>154.3020684321744</v>
       </c>
     </row>
     <row r="139">
@@ -4183,12 +4599,15 @@
         <v>130.82707128</v>
       </c>
       <c r="F139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>144.0207040191272</v>
       </c>
     </row>
     <row r="140">
@@ -4210,12 +4629,15 @@
         <v>83.83990669000001</v>
       </c>
       <c r="F140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>388.4867996322367</v>
       </c>
     </row>
     <row r="141">
@@ -4237,12 +4659,15 @@
         <v>66.93223488999999</v>
       </c>
       <c r="F141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>160.4530529800002</v>
       </c>
     </row>
     <row r="142">
@@ -4264,12 +4689,15 @@
         <v>94.84938579</v>
       </c>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>279.7075176862222</v>
       </c>
     </row>
     <row r="143">
@@ -4291,12 +4719,15 @@
         <v>145.91838293</v>
       </c>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>137.8802470023848</v>
       </c>
     </row>
     <row r="144">
@@ -4318,12 +4749,15 @@
         <v>148.16292628</v>
       </c>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>125.8355096270716</v>
       </c>
     </row>
     <row r="145">
@@ -4345,12 +4779,15 @@
         <v>22.03899181</v>
       </c>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>369.1622100435767</v>
       </c>
     </row>
     <row r="146">
@@ -4372,12 +4809,15 @@
         <v>169.43078549</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>40.93402369732947</v>
       </c>
     </row>
     <row r="147">
@@ -4399,12 +4839,15 @@
         <v>115.96496099</v>
       </c>
       <c r="F147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>146.5562506993173</v>
       </c>
     </row>
     <row r="148">
@@ -4426,12 +4869,15 @@
         <v>97.54827051999999</v>
       </c>
       <c r="F148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>145.0353621763646</v>
       </c>
     </row>
     <row r="149">
@@ -4453,12 +4899,15 @@
         <v>171.24941356</v>
       </c>
       <c r="F149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>157.1304892525723</v>
       </c>
     </row>
     <row r="150">
@@ -4480,12 +4929,15 @@
         <v>79.48337347</v>
       </c>
       <c r="F150" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>121.03539755116</v>
       </c>
     </row>
     <row r="151">
@@ -4507,12 +4959,15 @@
         <v>21.38957457</v>
       </c>
       <c r="F151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>378.6092271739076</v>
       </c>
     </row>
     <row r="152">
@@ -4534,12 +4989,15 @@
         <v>56.00126308</v>
       </c>
       <c r="F152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>453.0618631701936</v>
       </c>
     </row>
     <row r="153">
@@ -4561,12 +5019,15 @@
         <v>116.54724109</v>
       </c>
       <c r="F153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>150.9465552515387</v>
       </c>
     </row>
     <row r="154">
@@ -4588,12 +5049,15 @@
         <v>136.56314483</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>26.39503825315914</v>
       </c>
     </row>
     <row r="155">
@@ -4615,12 +5079,15 @@
         <v>132.34473269</v>
       </c>
       <c r="F155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>139.6648102466222</v>
       </c>
     </row>
     <row r="156">
@@ -4642,12 +5109,15 @@
         <v>127.67648195</v>
       </c>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>147.6298806526679</v>
       </c>
     </row>
     <row r="157">
@@ -4669,12 +5139,15 @@
         <v>101.97064253</v>
       </c>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>466.5173357135325</v>
       </c>
     </row>
     <row r="158">
@@ -4696,12 +5169,15 @@
         <v>64.40666220000001</v>
       </c>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>378.5505972995411</v>
       </c>
     </row>
     <row r="159">
@@ -4723,12 +5199,15 @@
         <v>133.79668708</v>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>166.3585398305499</v>
       </c>
     </row>
     <row r="160">
@@ -4750,12 +5229,15 @@
         <v>138.15013296</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>295.1284815246919</v>
       </c>
     </row>
     <row r="161">
@@ -4777,12 +5259,15 @@
         <v>150.50007586</v>
       </c>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>148.430521977768</v>
       </c>
     </row>
     <row r="162">
@@ -4804,12 +5289,15 @@
         <v>93.60651496</v>
       </c>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>160.9527014377235</v>
       </c>
     </row>
     <row r="163">
@@ -4831,12 +5319,15 @@
         <v>129.31327658</v>
       </c>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>66.16610374030769</v>
       </c>
     </row>
     <row r="164">
@@ -4858,12 +5349,15 @@
         <v>106.88348563</v>
       </c>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>403.3770685462418</v>
       </c>
     </row>
     <row r="165">
@@ -4885,12 +5379,15 @@
         <v>42.43144776</v>
       </c>
       <c r="F165" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>369.9360371615572</v>
       </c>
     </row>
     <row r="166">
@@ -4912,12 +5409,15 @@
         <v>60.79293023</v>
       </c>
       <c r="F166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>312.3121417069709</v>
       </c>
     </row>
     <row r="167">
@@ -4939,12 +5439,15 @@
         <v>77.59270448000001</v>
       </c>
       <c r="F167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>157.9650373618147</v>
       </c>
     </row>
     <row r="168">
@@ -4966,12 +5469,15 @@
         <v>53.785478</v>
       </c>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>97.45824180501572</v>
       </c>
     </row>
     <row r="169">
@@ -4993,12 +5499,15 @@
         <v>145.0125221</v>
       </c>
       <c r="F169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>43.97404253119719</v>
       </c>
     </row>
     <row r="170">
@@ -5020,12 +5529,15 @@
         <v>134.76338509</v>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>140.7851946362896</v>
       </c>
     </row>
     <row r="171">
@@ -5047,12 +5559,15 @@
         <v>34.09060356</v>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>399.5083708833428</v>
       </c>
     </row>
     <row r="172">
@@ -5074,12 +5589,15 @@
         <v>103.95516876</v>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>161.5314469475466</v>
       </c>
     </row>
     <row r="173">
@@ -5101,12 +5619,15 @@
         <v>129.96221128</v>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>152.6882497958964</v>
       </c>
     </row>
     <row r="174">
@@ -5128,12 +5649,15 @@
         <v>123.25258422</v>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>130.9552456548431</v>
       </c>
     </row>
     <row r="175">
@@ -5155,12 +5679,15 @@
         <v>114.2480122</v>
       </c>
       <c r="F175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>110.1578374848856</v>
       </c>
     </row>
     <row r="176">
@@ -5182,12 +5709,15 @@
         <v>148.70392757</v>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>198.8890780199291</v>
       </c>
     </row>
     <row r="177">
@@ -5209,12 +5739,15 @@
         <v>164.48669544</v>
       </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>266.3355288928579</v>
       </c>
     </row>
     <row r="178">
@@ -5236,12 +5769,15 @@
         <v>149.1072418</v>
       </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>387.6774496753766</v>
       </c>
     </row>
     <row r="179">
@@ -5263,12 +5799,15 @@
         <v>114.08940098</v>
       </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>143.8721470076325</v>
       </c>
     </row>
     <row r="180">
@@ -5290,12 +5829,15 @@
         <v>112.05923696</v>
       </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>140.9664354752053</v>
       </c>
     </row>
     <row r="181">
@@ -5317,12 +5859,15 @@
         <v>64.98465548</v>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>142.7213522013847</v>
       </c>
     </row>
     <row r="182">
@@ -5344,12 +5889,15 @@
         <v>72.72579613999999</v>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>156.9633839319166</v>
       </c>
     </row>
     <row r="183">
@@ -5371,12 +5919,15 @@
         <v>103.13068804</v>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>156.7968949445768</v>
       </c>
     </row>
     <row r="184">
@@ -5398,12 +5949,15 @@
         <v>88.39244152999999</v>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>145.3817134522845</v>
       </c>
     </row>
     <row r="185">
@@ -5425,12 +5979,15 @@
         <v>111.28124526</v>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>164.8960223765515</v>
       </c>
     </row>
     <row r="186">
@@ -5452,12 +6009,15 @@
         <v>77.23146711</v>
       </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>160.1367601744726</v>
       </c>
     </row>
     <row r="187">
@@ -5479,12 +6039,15 @@
         <v>87.69854039000001</v>
       </c>
       <c r="F187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>94.57825916665728</v>
       </c>
     </row>
     <row r="188">
@@ -5506,12 +6069,15 @@
         <v>104.07446787</v>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>149.0413074483496</v>
       </c>
     </row>
     <row r="189">
@@ -5533,12 +6099,15 @@
         <v>135.95829359</v>
       </c>
       <c r="F189" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>105.1204904123371</v>
       </c>
     </row>
     <row r="190">
@@ -5560,12 +6129,15 @@
         <v>14.04523848</v>
       </c>
       <c r="F190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>388.2139984601232</v>
       </c>
     </row>
     <row r="191">
@@ -5587,12 +6159,15 @@
         <v>84.03368023</v>
       </c>
       <c r="F191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>46.05181255247427</v>
       </c>
     </row>
     <row r="192">
@@ -5614,12 +6189,15 @@
         <v>37.35482578</v>
       </c>
       <c r="F192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>393.715675009759</v>
       </c>
     </row>
     <row r="193">
@@ -5641,12 +6219,15 @@
         <v>29.02313882999999</v>
       </c>
       <c r="F193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>365.5773635412867</v>
       </c>
     </row>
     <row r="194">
@@ -5668,12 +6249,15 @@
         <v>69.75723010999999</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>90.42836908835832</v>
       </c>
     </row>
     <row r="195">
@@ -5695,12 +6279,15 @@
         <v>106.29918689</v>
       </c>
       <c r="F195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>132.9341213620754</v>
       </c>
     </row>
     <row r="196">
@@ -5722,12 +6309,15 @@
         <v>68.10364146999999</v>
       </c>
       <c r="F196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>148.6479009466308</v>
       </c>
     </row>
     <row r="197">
@@ -5749,12 +6339,15 @@
         <v>51.23457499999999</v>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>90.66046051512869</v>
       </c>
     </row>
     <row r="198">
@@ -5776,12 +6369,15 @@
         <v>62.39533672</v>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>138.4670632375975</v>
       </c>
     </row>
     <row r="199">
@@ -5803,12 +6399,15 @@
         <v>81.51284326</v>
       </c>
       <c r="F199" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>144.8737354091315</v>
       </c>
     </row>
     <row r="200">
@@ -5830,12 +6429,15 @@
         <v>83.68685203999999</v>
       </c>
       <c r="F200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>150.6046320137467</v>
       </c>
     </row>
     <row r="201">
@@ -5857,12 +6459,15 @@
         <v>68.18522616</v>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>141.2826203035115</v>
       </c>
     </row>
     <row r="202">
@@ -5884,12 +6489,15 @@
         <v>80.24099302</v>
       </c>
       <c r="F202" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>151.6595942303774</v>
       </c>
     </row>
     <row r="203">
@@ -5911,12 +6519,15 @@
         <v>42.55748138000001</v>
       </c>
       <c r="F203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>68.87397011120331</v>
       </c>
     </row>
     <row r="204">
@@ -5938,12 +6549,15 @@
         <v>66.30837547</v>
       </c>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>125.0677805919528</v>
       </c>
     </row>
     <row r="205">
@@ -5965,12 +6579,15 @@
         <v>72.1073177</v>
       </c>
       <c r="F205" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>81.78595913441407</v>
       </c>
     </row>
     <row r="206">
@@ -5992,12 +6609,15 @@
         <v>61.94020108000001</v>
       </c>
       <c r="F206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>140.0590297326085</v>
       </c>
     </row>
     <row r="207">
@@ -6019,12 +6639,15 @@
         <v>116.30465114</v>
       </c>
       <c r="F207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>98.7323172694025</v>
       </c>
     </row>
     <row r="208">
@@ -6046,12 +6669,15 @@
         <v>66.85576336</v>
       </c>
       <c r="F208" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>150.0719903546772</v>
       </c>
     </row>
     <row r="209">
@@ -6073,12 +6699,15 @@
         <v>88.47867821</v>
       </c>
       <c r="F209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>156.0220450976014</v>
       </c>
     </row>
     <row r="210">
@@ -6100,12 +6729,15 @@
         <v>75.59825791</v>
       </c>
       <c r="F210" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>168.2216933394938</v>
       </c>
     </row>
     <row r="211">
@@ -6127,12 +6759,15 @@
         <v>112.48154805</v>
       </c>
       <c r="F211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>142.4573195186641</v>
       </c>
     </row>
     <row r="212">
@@ -6154,12 +6789,15 @@
         <v>105.4919814</v>
       </c>
       <c r="F212" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>87.98069974649448</v>
       </c>
     </row>
     <row r="213">
@@ -6188,6 +6826,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H213" t="n">
+        <v>244.4547600179641</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6215,6 +6856,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H214" t="n">
+        <v>224.1347950788545</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6242,6 +6886,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H215" t="n">
+        <v>383.9683452505717</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6269,6 +6916,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H216" t="n">
+        <v>358.6786998752949</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6296,6 +6946,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H217" t="n">
+        <v>405.3050657897217</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6323,6 +6976,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H218" t="n">
+        <v>343.1529027900015</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6350,6 +7006,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H219" t="n">
+        <v>192.2969368458551</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6377,6 +7036,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H220" t="n">
+        <v>379.5007289420488</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6404,6 +7066,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H221" t="n">
+        <v>170.9482929019636</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6431,6 +7096,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H222" t="n">
+        <v>277.5254540437227</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6458,6 +7126,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H223" t="n">
+        <v>346.976523051831</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6485,6 +7156,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H224" t="n">
+        <v>167.7758876733445</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6512,6 +7186,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H225" t="n">
+        <v>405.4342490665469</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6539,6 +7216,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H226" t="n">
+        <v>342.2257220137689</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6559,12 +7239,15 @@
         <v>65.836</v>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>511.3525973892623</v>
       </c>
     </row>
     <row r="228">
@@ -6593,6 +7276,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H228" t="n">
+        <v>331.1662139980003</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6620,6 +7306,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H229" t="n">
+        <v>381.7256943903093</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -6647,6 +7336,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H230" t="n">
+        <v>357.0246673916196</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6674,6 +7366,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H231" t="n">
+        <v>377.0267809314404</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -6701,6 +7396,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H232" t="n">
+        <v>169.5897000840959</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6728,6 +7426,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H233" t="n">
+        <v>336.4473247808326</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -6755,6 +7456,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H234" t="n">
+        <v>349.4569968094802</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6782,6 +7486,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H235" t="n">
+        <v>223.0922603127969</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6809,6 +7516,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H236" t="n">
+        <v>172.9088095760513</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6836,6 +7546,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H237" t="n">
+        <v>378.5427318889581</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -6863,6 +7576,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H238" t="n">
+        <v>181.6944955579513</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -6883,12 +7599,15 @@
         <v>111.0064</v>
       </c>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>510.8703195477742</v>
       </c>
     </row>
     <row r="240">
@@ -6917,6 +7636,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H240" t="n">
+        <v>353.6441013146468</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -6944,6 +7666,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H241" t="n">
+        <v>405.779922177717</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6971,6 +7696,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H242" t="n">
+        <v>354.4869959095565</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6998,6 +7726,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H243" t="n">
+        <v>378.7680856783614</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7025,6 +7756,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H244" t="n">
+        <v>449.7335626017817</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7052,6 +7786,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H245" t="n">
+        <v>176.5776307618488</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7079,6 +7816,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H246" t="n">
+        <v>341.5759657726773</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7106,6 +7846,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H247" t="n">
+        <v>178.9192601996842</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7133,6 +7876,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H248" t="n">
+        <v>337.8575499479376</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7160,6 +7906,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H249" t="n">
+        <v>375.1955729779149</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7187,6 +7936,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H250" t="n">
+        <v>414.9905506571422</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7214,6 +7966,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H251" t="n">
+        <v>449.8968435611127</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -7234,12 +7989,15 @@
         <v>22.082508</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H252" t="n">
+        <v>128.9049887187745</v>
       </c>
     </row>
     <row r="253">
@@ -7261,12 +8019,15 @@
         <v>26.1654</v>
       </c>
       <c r="F253" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H253" t="n">
+        <v>199.9453164122694</v>
       </c>
     </row>
     <row r="254">
@@ -7288,12 +8049,15 @@
         <v>41.9052</v>
       </c>
       <c r="F254" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
+        <v>295.4992140148996</v>
       </c>
     </row>
     <row r="255">
@@ -7315,12 +8079,15 @@
         <v>898.0380000000002</v>
       </c>
       <c r="F255" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>379.6069181231939</v>
       </c>
     </row>
     <row r="256">
@@ -7342,12 +8109,15 @@
         <v>13.4594</v>
       </c>
       <c r="F256" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H256" t="n">
+        <v>380.258306252376</v>
       </c>
     </row>
     <row r="257">
@@ -7369,12 +8139,15 @@
         <v>109.8696</v>
       </c>
       <c r="F257" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H257" t="n">
+        <v>198.7566561597725</v>
       </c>
     </row>
     <row r="258">
@@ -7396,12 +8169,15 @@
         <v>128.60566</v>
       </c>
       <c r="F258" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H258" t="n">
+        <v>157.6723325326645</v>
       </c>
     </row>
     <row r="259">
@@ -7423,12 +8199,15 @@
         <v>571.5419999999999</v>
       </c>
       <c r="F259" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H259" t="n">
+        <v>403.5081622823314</v>
       </c>
     </row>
     <row r="260">
@@ -7450,12 +8229,15 @@
         <v>122.977441</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H260" t="n">
+        <v>475.9405988279751</v>
       </c>
     </row>
     <row r="261">
@@ -7477,12 +8259,15 @@
         <v>131.0654675</v>
       </c>
       <c r="F261" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H261" t="n">
+        <v>195.7083783065673</v>
       </c>
     </row>
     <row r="262">
@@ -7504,12 +8289,15 @@
         <v>95.62609999999999</v>
       </c>
       <c r="F262" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H262" t="n">
+        <v>438.5077834249905</v>
       </c>
     </row>
     <row r="263">
@@ -7531,12 +8319,15 @@
         <v>106.7479</v>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H263" t="n">
+        <v>188.2066440310786</v>
       </c>
     </row>
     <row r="264">
@@ -7558,12 +8349,15 @@
         <v>123.2049255</v>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H264" t="n">
+        <v>190.9071943197909</v>
       </c>
     </row>
     <row r="265">
@@ -7585,12 +8379,15 @@
         <v>284.046</v>
       </c>
       <c r="F265" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>405.0565056120583</v>
       </c>
     </row>
     <row r="266">
@@ -7612,12 +8409,15 @@
         <v>995.3472000000002</v>
       </c>
       <c r="F266" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
+        <v>301.8636096550673</v>
       </c>
     </row>
     <row r="267">
@@ -7639,12 +8439,15 @@
         <v>56.9948</v>
       </c>
       <c r="F267" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>198.4266612290852</v>
       </c>
     </row>
     <row r="268">
@@ -7666,12 +8469,15 @@
         <v>162.227688</v>
       </c>
       <c r="F268" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>518.4040578096872</v>
       </c>
     </row>
     <row r="269">
@@ -7693,12 +8499,15 @@
         <v>93.85904950000001</v>
       </c>
       <c r="F269" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>510.6400033426321</v>
       </c>
     </row>
     <row r="270">
@@ -7720,12 +8529,15 @@
         <v>72.16600000000001</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>197.6583203948707</v>
       </c>
     </row>
     <row r="271">
@@ -7747,12 +8559,15 @@
         <v>77.25859999999999</v>
       </c>
       <c r="F271" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>200.1952793995961</v>
       </c>
     </row>
     <row r="272">
@@ -7774,12 +8589,15 @@
         <v>72.49699999999999</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>215.1429120314576</v>
       </c>
     </row>
     <row r="273">
@@ -7801,12 +8619,15 @@
         <v>186.4224215</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>189.4037922176628</v>
       </c>
     </row>
     <row r="274">
@@ -7828,12 +8649,15 @@
         <v>150.1102</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>198.7324288034695</v>
       </c>
     </row>
     <row r="275">
@@ -7855,12 +8679,15 @@
         <v>71.23049999999999</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>215.2126130343853</v>
       </c>
     </row>
     <row r="276">
@@ -7882,12 +8709,15 @@
         <v>222.122161</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>193.0481946178191</v>
       </c>
     </row>
     <row r="277">
@@ -7909,12 +8739,15 @@
         <v>243.76794</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>190.414855387531</v>
       </c>
     </row>
     <row r="278">
@@ -7936,12 +8769,15 @@
         <v>59.30860000000001</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>197.1251076937621</v>
       </c>
     </row>
     <row r="279">
@@ -7963,12 +8799,15 @@
         <v>200.4813</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>189.8007120211021</v>
       </c>
     </row>
     <row r="280">
@@ -7990,12 +8829,15 @@
         <v>152.1270185</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>474.2739396380379</v>
       </c>
     </row>
     <row r="281">
@@ -8017,12 +8859,15 @@
         <v>100.023278</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>106.1462563154388</v>
       </c>
     </row>
     <row r="282">
@@ -8044,12 +8889,15 @@
         <v>65.61912249999999</v>
       </c>
       <c r="F282" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H282" t="n">
+        <v>189.5541092308563</v>
       </c>
     </row>
     <row r="283">
@@ -8071,12 +8919,15 @@
         <v>59.61479999999999</v>
       </c>
       <c r="F283" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H283" t="n">
+        <v>297.7463062317671</v>
       </c>
     </row>
     <row r="284">
@@ -8098,12 +8949,15 @@
         <v>92.10120000000001</v>
       </c>
       <c r="F284" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H284" t="n">
+        <v>295.1508308036504</v>
       </c>
     </row>
     <row r="285">
@@ -8125,12 +8979,15 @@
         <v>87.2212</v>
       </c>
       <c r="F285" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
+        <v>195.2004775661288</v>
       </c>
     </row>
     <row r="286">
@@ -8152,12 +9009,15 @@
         <v>44.383</v>
       </c>
       <c r="F286" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H286" t="n">
+        <v>198.792485816512</v>
       </c>
     </row>
     <row r="287">
@@ -8179,12 +9039,15 @@
         <v>72.4555</v>
       </c>
       <c r="F287" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H287" t="n">
+        <v>211.7593814876636</v>
       </c>
     </row>
     <row r="288">
@@ -8206,12 +9069,15 @@
         <v>228.606</v>
       </c>
       <c r="F288" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H288" t="n">
+        <v>409.3578444052795</v>
       </c>
     </row>
     <row r="289">
@@ -8233,12 +9099,15 @@
         <v>106.680992</v>
       </c>
       <c r="F289" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H289" t="n">
+        <v>390.9140081015669</v>
       </c>
     </row>
     <row r="290">
@@ -8260,12 +9129,15 @@
         <v>118.29098</v>
       </c>
       <c r="F290" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H290" t="n">
+        <v>260.0725060296554</v>
       </c>
     </row>
     <row r="291">
@@ -8287,12 +9159,15 @@
         <v>56.55883999999998</v>
       </c>
       <c r="F291" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H291" t="n">
+        <v>478.6929063561986</v>
       </c>
     </row>
     <row r="292">
@@ -8321,6 +9196,9 @@
           <t>DC_4</t>
         </is>
       </c>
+      <c r="H292" t="n">
+        <v>317.4733968405083</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -8341,12 +9219,15 @@
         <v>76.35709999999999</v>
       </c>
       <c r="F293" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H293" t="n">
+        <v>174.1455252776595</v>
       </c>
     </row>
     <row r="294">
@@ -8368,12 +9249,15 @@
         <v>65.98963999999999</v>
       </c>
       <c r="F294" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H294" t="n">
+        <v>483.6949449878604</v>
       </c>
     </row>
     <row r="295">
@@ -8395,12 +9279,15 @@
         <v>70.17684000000001</v>
       </c>
       <c r="F295" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H295" t="n">
+        <v>395.2279755294658</v>
       </c>
     </row>
     <row r="296">
@@ -8422,12 +9309,15 @@
         <v>80.12326000000002</v>
       </c>
       <c r="F296" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H296" t="n">
+        <v>139.904278070824</v>
       </c>
     </row>
     <row r="297">
@@ -8449,12 +9339,15 @@
         <v>73.27007999999999</v>
       </c>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H297" t="n">
+        <v>518.017243909774</v>
       </c>
     </row>
     <row r="298">
@@ -8476,12 +9369,15 @@
         <v>113.30992</v>
       </c>
       <c r="F298" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H298" t="n">
+        <v>171.8836861734805</v>
       </c>
     </row>
     <row r="299">
@@ -8503,12 +9399,15 @@
         <v>43.52612</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H299" t="n">
+        <v>305.6066734773577</v>
       </c>
     </row>
     <row r="300">
@@ -8530,12 +9429,15 @@
         <v>108.32342</v>
       </c>
       <c r="F300" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H300" t="n">
+        <v>145.1818212920968</v>
       </c>
     </row>
     <row r="301">
@@ -8557,12 +9459,15 @@
         <v>51.79328</v>
       </c>
       <c r="F301" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H301" t="n">
+        <v>419.036129462474</v>
       </c>
     </row>
     <row r="302">
@@ -8584,12 +9489,15 @@
         <v>68.9781</v>
       </c>
       <c r="F302" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H302" t="n">
+        <v>407.1102990416741</v>
       </c>
     </row>
     <row r="303">
@@ -8611,12 +9519,15 @@
         <v>69.73756</v>
       </c>
       <c r="F303" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H303" t="n">
+        <v>295.353133364184</v>
       </c>
     </row>
     <row r="304">
@@ -8638,12 +9549,15 @@
         <v>116.13984</v>
       </c>
       <c r="F304" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H304" t="n">
+        <v>302.21659388239</v>
       </c>
     </row>
     <row r="305">
@@ -8665,12 +9579,15 @@
         <v>100.22104</v>
       </c>
       <c r="F305" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H305" t="n">
+        <v>299.2683693566714</v>
       </c>
     </row>
     <row r="306">
@@ -8692,12 +9609,15 @@
         <v>124.95866</v>
       </c>
       <c r="F306" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H306" t="n">
+        <v>265.2849324520069</v>
       </c>
     </row>
     <row r="307">
@@ -8719,12 +9639,15 @@
         <v>106.6222</v>
       </c>
       <c r="F307" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H307" t="n">
+        <v>234.1539906552349</v>
       </c>
     </row>
     <row r="308">
@@ -8746,12 +9669,15 @@
         <v>37.92908</v>
       </c>
       <c r="F308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H308" t="n">
+        <v>137.9645027339064</v>
       </c>
     </row>
     <row r="309">
@@ -8773,12 +9699,15 @@
         <v>76.79181999999999</v>
       </c>
       <c r="F309" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H309" t="n">
+        <v>213.5800407661942</v>
       </c>
     </row>
     <row r="310">
@@ -8800,12 +9729,15 @@
         <v>47.35968</v>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="H310" t="n">
+        <v>505.864554707247</v>
       </c>
     </row>
     <row r="311">
@@ -8827,12 +9759,15 @@
         <v>153.85138</v>
       </c>
       <c r="F311" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>140.4766831106095</v>
       </c>
     </row>
     <row r="312">
@@ -8854,12 +9789,15 @@
         <v>178.5294</v>
       </c>
       <c r="F312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>263.2808293594302</v>
       </c>
     </row>
     <row r="313">
@@ -8881,12 +9819,15 @@
         <v>138.3113</v>
       </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H313" t="n">
+        <v>146.8970220930177</v>
       </c>
     </row>
     <row r="314">
@@ -8908,12 +9849,15 @@
         <v>148.35608</v>
       </c>
       <c r="F314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H314" t="n">
+        <v>252.0220765832538</v>
       </c>
     </row>
     <row r="315">
@@ -8935,12 +9879,15 @@
         <v>137.84592</v>
       </c>
       <c r="F315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H315" t="n">
+        <v>290.8446586327354</v>
       </c>
     </row>
     <row r="316">
@@ -8962,12 +9909,15 @@
         <v>71.19014000000001</v>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H316" t="n">
+        <v>419.8748338969282</v>
       </c>
     </row>
     <row r="317">
@@ -8989,12 +9939,15 @@
         <v>106.50236</v>
       </c>
       <c r="F317" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H317" t="n">
+        <v>202.3745627430987</v>
       </c>
     </row>
     <row r="318">
@@ -9016,12 +9969,15 @@
         <v>97.77134</v>
       </c>
       <c r="F318" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H318" t="n">
+        <v>131.3767754580934</v>
       </c>
     </row>
     <row r="319">
@@ -9043,12 +9999,15 @@
         <v>80.68743999999998</v>
       </c>
       <c r="F319" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DC_4</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H319" t="n">
+        <v>405.4616480532131</v>
       </c>
     </row>
     <row r="320">
@@ -9070,12 +10029,15 @@
         <v>92.23769999999999</v>
       </c>
       <c r="F320" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H320" t="n">
+        <v>257.7202175042919</v>
       </c>
     </row>
     <row r="321">
@@ -9097,12 +10059,15 @@
         <v>111.7828</v>
       </c>
       <c r="F321" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H321" t="n">
+        <v>299.2069770829289</v>
       </c>
     </row>
     <row r="322">
@@ -9124,12 +10089,15 @@
         <v>120.6901</v>
       </c>
       <c r="F322" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H322" t="n">
+        <v>225.2118983559744</v>
       </c>
     </row>
     <row r="323">
@@ -9151,12 +10119,15 @@
         <v>51.7548</v>
       </c>
       <c r="F323" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H323" t="n">
+        <v>233.1156151535796</v>
       </c>
     </row>
     <row r="324">
@@ -9178,12 +10149,15 @@
         <v>162.11432</v>
       </c>
       <c r="F324" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H324" t="n">
+        <v>174.6437031880509</v>
       </c>
     </row>
     <row r="325">
@@ -9205,12 +10179,15 @@
         <v>70.43834</v>
       </c>
       <c r="F325" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H325" t="n">
+        <v>258.0969226234916</v>
       </c>
     </row>
     <row r="326">
@@ -9232,12 +10209,15 @@
         <v>97.17318</v>
       </c>
       <c r="F326" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H326" t="n">
+        <v>143.4559287228808</v>
       </c>
     </row>
     <row r="327">
@@ -9259,12 +10239,15 @@
         <v>96.64926</v>
       </c>
       <c r="F327" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H327" t="n">
+        <v>298.5405184854939</v>
       </c>
     </row>
     <row r="328">
@@ -9286,12 +10269,15 @@
         <v>136.70414</v>
       </c>
       <c r="F328" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H328" t="n">
+        <v>291.9125166681933</v>
       </c>
     </row>
     <row r="329">
@@ -9313,12 +10299,15 @@
         <v>55.98389999999999</v>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H329" t="n">
+        <v>201.6634020843782</v>
       </c>
     </row>
     <row r="330">
@@ -9340,12 +10329,15 @@
         <v>57.27579999999999</v>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H330" t="n">
+        <v>187.3472114739193</v>
       </c>
     </row>
     <row r="331">
@@ -9367,12 +10359,15 @@
         <v>100.51814</v>
       </c>
       <c r="F331" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H331" t="n">
+        <v>306.1498650987936</v>
       </c>
     </row>
     <row r="332">
@@ -9394,12 +10389,15 @@
         <v>72.68213999999999</v>
       </c>
       <c r="F332" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H332" t="n">
+        <v>240.6553957539271</v>
       </c>
     </row>
     <row r="333">
@@ -9421,12 +10419,15 @@
         <v>53.00724</v>
       </c>
       <c r="F333" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H333" t="n">
+        <v>305.5297858281983</v>
       </c>
     </row>
     <row r="334">
@@ -9448,12 +10449,15 @@
         <v>84.78078000000001</v>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H334" t="n">
+        <v>265.5314730786209</v>
       </c>
     </row>
     <row r="335">
@@ -9475,12 +10479,15 @@
         <v>97.36683999999997</v>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H335" t="n">
+        <v>115.8620035916273</v>
       </c>
     </row>
     <row r="336">
@@ -9502,12 +10509,15 @@
         <v>81.07180000000001</v>
       </c>
       <c r="F336" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H336" t="n">
+        <v>325.2162572181462</v>
       </c>
     </row>
     <row r="337">
@@ -9529,12 +10539,15 @@
         <v>51.87629999999999</v>
       </c>
       <c r="F337" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H337" t="n">
+        <v>176.0201727541978</v>
       </c>
     </row>
     <row r="338">
@@ -9556,12 +10569,15 @@
         <v>164.81286</v>
       </c>
       <c r="F338" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H338" t="n">
+        <v>242.8334230268776</v>
       </c>
     </row>
     <row r="339">
@@ -9583,12 +10599,15 @@
         <v>137.11044</v>
       </c>
       <c r="F339" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H339" t="n">
+        <v>262.5364558361898</v>
       </c>
     </row>
     <row r="340">
@@ -9610,12 +10629,15 @@
         <v>105.60097665</v>
       </c>
       <c r="F340" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H340" t="n">
+        <v>244.4815171214456</v>
       </c>
     </row>
     <row r="341">
@@ -9637,12 +10659,15 @@
         <v>85.30447965</v>
       </c>
       <c r="F341" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H341" t="n">
+        <v>249.0720943022942</v>
       </c>
     </row>
     <row r="342">
@@ -9664,12 +10689,15 @@
         <v>105.13692</v>
       </c>
       <c r="F342" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H342" t="n">
+        <v>130.0982456924606</v>
       </c>
     </row>
     <row r="343">
@@ -9691,12 +10719,15 @@
         <v>119.39315505</v>
       </c>
       <c r="F343" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H343" t="n">
+        <v>244.7649577139401</v>
       </c>
     </row>
     <row r="344">
@@ -9718,12 +10749,15 @@
         <v>135.2097</v>
       </c>
       <c r="F344" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H344" t="n">
+        <v>170.4849151475579</v>
       </c>
     </row>
     <row r="345">
@@ -9745,12 +10779,15 @@
         <v>103.2224895</v>
       </c>
       <c r="F345" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H345" t="n">
+        <v>247.3589627515343</v>
       </c>
     </row>
     <row r="346">
@@ -9772,12 +10809,15 @@
         <v>105.68844</v>
       </c>
       <c r="F346" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H346" t="n">
+        <v>250.7518419947306</v>
       </c>
     </row>
     <row r="347">
@@ -9799,12 +10839,15 @@
         <v>92.92085999999999</v>
       </c>
       <c r="F347" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H347" t="n">
+        <v>245.2020554131428</v>
       </c>
     </row>
     <row r="348">
@@ -9826,12 +10869,15 @@
         <v>105.6147144</v>
       </c>
       <c r="F348" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H348" t="n">
+        <v>247.1939855447183</v>
       </c>
     </row>
     <row r="349">
@@ -9853,12 +10899,15 @@
         <v>96.36005999999999</v>
       </c>
       <c r="F349" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H349" t="n">
+        <v>248.9481718440073</v>
       </c>
     </row>
     <row r="350">
@@ -9880,12 +10929,15 @@
         <v>81.90635999999998</v>
       </c>
       <c r="F350" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H350" t="n">
+        <v>262.8258537407512</v>
       </c>
     </row>
     <row r="351">
@@ -9907,12 +10959,15 @@
         <v>103.29378</v>
       </c>
       <c r="F351" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H351" t="n">
+        <v>243.9905079930992</v>
       </c>
     </row>
     <row r="352">
@@ -9934,12 +10989,15 @@
         <v>69.66414</v>
       </c>
       <c r="F352" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H352" t="n">
+        <v>245.7263957483557</v>
       </c>
     </row>
     <row r="353">
@@ -9961,12 +11019,15 @@
         <v>133.07976</v>
       </c>
       <c r="F353" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H353" t="n">
+        <v>241.3758450983825</v>
       </c>
     </row>
     <row r="354">
@@ -9988,12 +11049,15 @@
         <v>99.53225999999999</v>
       </c>
       <c r="F354" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H354" t="n">
+        <v>173.6480917764453</v>
       </c>
     </row>
     <row r="355">
@@ -10015,12 +11079,15 @@
         <v>174.81366</v>
       </c>
       <c r="F355" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H355" t="n">
+        <v>255.3696671481475</v>
       </c>
     </row>
     <row r="356">
@@ -10042,12 +11109,15 @@
         <v>123.87336</v>
       </c>
       <c r="F356" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H356" t="n">
+        <v>245.2199955591135</v>
       </c>
     </row>
     <row r="357">
@@ -10069,12 +11139,15 @@
         <v>147.74808</v>
       </c>
       <c r="F357" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H357" t="n">
+        <v>127.1680167975757</v>
       </c>
     </row>
     <row r="358">
@@ -10096,12 +11169,15 @@
         <v>148.73862</v>
       </c>
       <c r="F358" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H358" t="n">
+        <v>251.8859543154234</v>
       </c>
     </row>
     <row r="359">
@@ -10123,12 +11199,15 @@
         <v>273.06534</v>
       </c>
       <c r="F359" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H359" t="n">
+        <v>244.6616573423616</v>
       </c>
     </row>
     <row r="360">
@@ -10150,12 +11229,15 @@
         <v>108.07158</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H360" t="n">
+        <v>242.2130875979642</v>
       </c>
     </row>
     <row r="361">
@@ -10177,12 +11259,15 @@
         <v>154.62948</v>
       </c>
       <c r="F361" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H361" t="n">
+        <v>184.1323231692768</v>
       </c>
     </row>
     <row r="362">
@@ -10204,12 +11289,15 @@
         <v>133.61611575</v>
       </c>
       <c r="F362" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H362" t="n">
+        <v>247.2555998483565</v>
       </c>
     </row>
     <row r="363">
@@ -10231,12 +11319,15 @@
         <v>107.2794</v>
       </c>
       <c r="F363" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H363" t="n">
+        <v>248.2500861193687</v>
       </c>
     </row>
     <row r="364">
@@ -10258,12 +11349,15 @@
         <v>90.89004</v>
       </c>
       <c r="F364" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H364" t="n">
+        <v>238.6138624870473</v>
       </c>
     </row>
     <row r="365">
@@ -10285,12 +11379,15 @@
         <v>65.39706</v>
       </c>
       <c r="F365" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H365" t="n">
+        <v>248.2464578486703</v>
       </c>
     </row>
     <row r="366">
@@ -10312,12 +11409,15 @@
         <v>93.90606000000002</v>
       </c>
       <c r="F366" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H366" t="n">
+        <v>251.572927532271</v>
       </c>
     </row>
     <row r="367">
@@ -10339,12 +11439,15 @@
         <v>102.0003</v>
       </c>
       <c r="F367" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="H367" t="n">
+        <v>230.4299203347763</v>
       </c>
     </row>
     <row r="368">
@@ -10366,12 +11469,15 @@
         <v>69.34979999999999</v>
       </c>
       <c r="F368" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H368" t="n">
+        <v>230.0711370582394</v>
       </c>
     </row>
     <row r="369">
@@ -10393,12 +11499,15 @@
         <v>147.48796146</v>
       </c>
       <c r="F369" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H369" t="n">
+        <v>66.73815255783093</v>
       </c>
     </row>
     <row r="370">
@@ -10420,12 +11529,15 @@
         <v>81.62645259999999</v>
       </c>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H370" t="n">
+        <v>34.52345300414044</v>
       </c>
     </row>
     <row r="371">
@@ -10447,12 +11559,15 @@
         <v>125.7125763</v>
       </c>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H371" t="n">
+        <v>317.946630304663</v>
       </c>
     </row>
     <row r="372">
@@ -10474,12 +11589,15 @@
         <v>118.30654686</v>
       </c>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H372" t="n">
+        <v>176.6888667503275</v>
       </c>
     </row>
     <row r="373">
@@ -10501,12 +11619,15 @@
         <v>46.7992934</v>
       </c>
       <c r="F373" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H373" t="n">
+        <v>63.09525674037218</v>
       </c>
     </row>
     <row r="374">
@@ -10528,12 +11649,15 @@
         <v>135.638204</v>
       </c>
       <c r="F374" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H374" t="n">
+        <v>67.88592045568444</v>
       </c>
     </row>
     <row r="375">
@@ -10555,12 +11679,15 @@
         <v>82.8659857</v>
       </c>
       <c r="F375" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H375" t="n">
+        <v>34.2181840897848</v>
       </c>
     </row>
     <row r="376">
@@ -10582,12 +11709,15 @@
         <v>105.553257</v>
       </c>
       <c r="F376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H376" t="n">
+        <v>32.70858238462002</v>
       </c>
     </row>
     <row r="377">
@@ -10609,12 +11739,15 @@
         <v>71.35351295999999</v>
       </c>
       <c r="F377" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H377" t="n">
+        <v>181.5158062914187</v>
       </c>
     </row>
     <row r="378">
@@ -10636,12 +11769,15 @@
         <v>102.73411212</v>
       </c>
       <c r="F378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H378" t="n">
+        <v>180.1765995943753</v>
       </c>
     </row>
     <row r="379">
@@ -10663,12 +11799,15 @@
         <v>128.5971056</v>
       </c>
       <c r="F379" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H379" t="n">
+        <v>35.38984638379532</v>
       </c>
     </row>
     <row r="380">
@@ -10690,12 +11829,15 @@
         <v>62.78045063999999</v>
       </c>
       <c r="F380" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H380" t="n">
+        <v>148.9146243709701</v>
       </c>
     </row>
     <row r="381">
@@ -10717,12 +11859,15 @@
         <v>109.3731514</v>
       </c>
       <c r="F381" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H381" t="n">
+        <v>292.1082656735446</v>
       </c>
     </row>
     <row r="382">
@@ -10744,12 +11889,15 @@
         <v>119.1499458</v>
       </c>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H382" t="n">
+        <v>33.3796757686011</v>
       </c>
     </row>
     <row r="383">
@@ -10771,12 +11919,15 @@
         <v>213.5551645</v>
       </c>
       <c r="F383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H383" t="n">
+        <v>31.90591786876936</v>
       </c>
     </row>
     <row r="384">
@@ -10798,12 +11949,15 @@
         <v>187.0876349</v>
       </c>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H384" t="n">
+        <v>33.24458419572206</v>
       </c>
     </row>
     <row r="385">
@@ -10825,12 +11979,15 @@
         <v>149.1235557</v>
       </c>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H385" t="n">
+        <v>63.43243743125071</v>
       </c>
     </row>
     <row r="386">
@@ -10852,12 +12009,15 @@
         <v>170.141426</v>
       </c>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H386" t="n">
+        <v>293.4508617519292</v>
       </c>
     </row>
     <row r="387">
@@ -10879,12 +12039,15 @@
         <v>168.952343</v>
       </c>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H387" t="n">
+        <v>37.08142664821583</v>
       </c>
     </row>
     <row r="388">
@@ -10906,12 +12069,15 @@
         <v>107.310147</v>
       </c>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H388" t="n">
+        <v>29.33806901372546</v>
       </c>
     </row>
     <row r="389">
@@ -10933,12 +12099,15 @@
         <v>111.302101</v>
       </c>
       <c r="F389" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H389" t="n">
+        <v>28.37001636872408</v>
       </c>
     </row>
     <row r="390">
@@ -10960,12 +12129,15 @@
         <v>77.23364369999999</v>
       </c>
       <c r="F390" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H390" t="n">
+        <v>39.11561759641163</v>
       </c>
     </row>
     <row r="391">
@@ -10987,12 +12159,15 @@
         <v>53.22112451999999</v>
       </c>
       <c r="F391" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H391" t="n">
+        <v>203.8019484784353</v>
       </c>
     </row>
     <row r="392">
@@ -11014,12 +12189,15 @@
         <v>110.9159485</v>
       </c>
       <c r="F392" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H392" t="n">
+        <v>31.02089893886271</v>
       </c>
     </row>
     <row r="393">
@@ -11041,12 +12219,15 @@
         <v>95.37692682000001</v>
       </c>
       <c r="F393" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H393" t="n">
+        <v>184.6131265113243</v>
       </c>
     </row>
     <row r="394">
@@ -11068,12 +12249,15 @@
         <v>54.18531179999999</v>
       </c>
       <c r="F394" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H394" t="n">
+        <v>27.58568935880062</v>
       </c>
     </row>
     <row r="395">
@@ -11095,12 +12279,15 @@
         <v>111.9413228</v>
       </c>
       <c r="F395" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_1</t>
+        </is>
+      </c>
+      <c r="H395" t="n">
+        <v>30.56895919515435</v>
       </c>
     </row>
     <row r="396">
@@ -11129,6 +12316,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H396" t="n">
+        <v>599.7685658275938</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -11149,12 +12339,15 @@
         <v>120.77989</v>
       </c>
       <c r="F397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H397" t="n">
+        <v>418.910619457074</v>
       </c>
     </row>
     <row r="398">
@@ -11176,12 +12369,15 @@
         <v>88.73139999999999</v>
       </c>
       <c r="F398" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H398" t="n">
+        <v>395.1452104601061</v>
       </c>
     </row>
     <row r="399">
@@ -11210,6 +12406,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H399" t="n">
+        <v>580.0655393103883</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -11230,12 +12429,15 @@
         <v>27.36499</v>
       </c>
       <c r="F400" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H400" t="n">
+        <v>419.2014824656533</v>
       </c>
     </row>
     <row r="401">
@@ -11257,12 +12459,15 @@
         <v>116.77227</v>
       </c>
       <c r="F401" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H401" t="n">
+        <v>417.7719448167981</v>
       </c>
     </row>
     <row r="402">
@@ -11284,12 +12489,15 @@
         <v>75.02567782</v>
       </c>
       <c r="F402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H402" t="n">
+        <v>290.1088194372147</v>
       </c>
     </row>
     <row r="403">
@@ -11311,12 +12519,15 @@
         <v>59.45515</v>
       </c>
       <c r="F403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H403" t="n">
+        <v>413.7000010176697</v>
       </c>
     </row>
     <row r="404">
@@ -11338,12 +12549,15 @@
         <v>126.89930723</v>
       </c>
       <c r="F404" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H404" t="n">
+        <v>286.2644628689006</v>
       </c>
     </row>
     <row r="405">
@@ -11372,6 +12586,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H405" t="n">
+        <v>596.4055858326795</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -11392,12 +12609,15 @@
         <v>118.61613</v>
       </c>
       <c r="F406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H406" t="n">
+        <v>667.4815881169878</v>
       </c>
     </row>
     <row r="407">
@@ -11419,12 +12639,15 @@
         <v>99.67066999999997</v>
       </c>
       <c r="F407" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H407" t="n">
+        <v>418.0305093436396</v>
       </c>
     </row>
     <row r="408">
@@ -11453,6 +12676,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H408" t="n">
+        <v>577.1715434059126</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -11473,12 +12699,15 @@
         <v>221.48973368</v>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H409" t="n">
+        <v>291.0608337402675</v>
       </c>
     </row>
     <row r="410">
@@ -11507,6 +12736,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H410" t="n">
+        <v>596.9387958350218</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -11527,12 +12759,15 @@
         <v>12.82508</v>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H411" t="n">
+        <v>417.601541343521</v>
       </c>
     </row>
     <row r="412">
@@ -11554,12 +12789,15 @@
         <v>104.69023</v>
       </c>
       <c r="F412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H412" t="n">
+        <v>592.2228066044695</v>
       </c>
     </row>
     <row r="413">
@@ -11581,12 +12819,15 @@
         <v>131.63062668</v>
       </c>
       <c r="F413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H413" t="n">
+        <v>316.9706336802632</v>
       </c>
     </row>
     <row r="414">
@@ -11615,6 +12856,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H414" t="n">
+        <v>623.8236912874983</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -11635,12 +12879,15 @@
         <v>57.31582</v>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H415" t="n">
+        <v>631.3880668617128</v>
       </c>
     </row>
     <row r="416">
@@ -11662,12 +12909,15 @@
         <v>53.89304</v>
       </c>
       <c r="F416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H416" t="n">
+        <v>594.4100784430385</v>
       </c>
     </row>
     <row r="417">
@@ -11696,6 +12946,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H417" t="n">
+        <v>620.2615824043411</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -11716,12 +12969,15 @@
         <v>44.69123999999999</v>
       </c>
       <c r="F418" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H418" t="n">
+        <v>204.5305974443592</v>
       </c>
     </row>
     <row r="419">
@@ -11750,6 +13006,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H419" t="n">
+        <v>110.2827409697895</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -11770,12 +13029,15 @@
         <v>30.97999</v>
       </c>
       <c r="F420" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H420" t="n">
+        <v>204.4596365169506</v>
       </c>
     </row>
     <row r="421">
@@ -11797,12 +13059,15 @@
         <v>38.67852</v>
       </c>
       <c r="F421" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H421" t="n">
+        <v>163.7742200848483</v>
       </c>
     </row>
     <row r="422">
@@ -11824,12 +13089,15 @@
         <v>22.78917</v>
       </c>
       <c r="F422" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H422" t="n">
+        <v>208.7913962749197</v>
       </c>
     </row>
     <row r="423">
@@ -11858,6 +13126,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H423" t="n">
+        <v>121.5759418094487</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -11878,12 +13149,15 @@
         <v>125.73253</v>
       </c>
       <c r="F424" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H424" t="n">
+        <v>213.2182452585202</v>
       </c>
     </row>
     <row r="425">
@@ -11912,6 +13186,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H425" t="n">
+        <v>176.2503739454197</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -11932,12 +13209,15 @@
         <v>144.26477</v>
       </c>
       <c r="F426" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H426" t="n">
+        <v>231.1188408667959</v>
       </c>
     </row>
     <row r="427">
@@ -11959,12 +13239,15 @@
         <v>109.89436</v>
       </c>
       <c r="F427" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H427" t="n">
+        <v>213.4509778017186</v>
       </c>
     </row>
     <row r="428">
@@ -11993,6 +13276,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H428" t="n">
+        <v>181.948223952247</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -12020,6 +13306,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H429" t="n">
+        <v>94.86397367730432</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -12047,6 +13336,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H430" t="n">
+        <v>100.5714524373624</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -12074,6 +13366,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H431" t="n">
+        <v>48.39588948557887</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -12094,12 +13389,15 @@
         <v>49.8474</v>
       </c>
       <c r="F432" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H432" t="n">
+        <v>463.4459507527332</v>
       </c>
     </row>
     <row r="433">
@@ -12128,6 +13426,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H433" t="n">
+        <v>433.5621327582323</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -12148,12 +13449,15 @@
         <v>138.73463</v>
       </c>
       <c r="F434" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H434" t="n">
+        <v>229.0852832585927</v>
       </c>
     </row>
     <row r="435">
@@ -12182,6 +13486,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H435" t="n">
+        <v>172.6159711788848</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -12209,6 +13516,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H436" t="n">
+        <v>117.7951780549381</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -12236,6 +13546,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H437" t="n">
+        <v>97.45745982829436</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -12263,6 +13576,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H438" t="n">
+        <v>101.481381795035</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -12283,12 +13599,15 @@
         <v>95.54351964</v>
       </c>
       <c r="F439" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H439" t="n">
+        <v>510.997654198796</v>
       </c>
     </row>
     <row r="440">
@@ -12317,6 +13636,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H440" t="n">
+        <v>429.4902768901852</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -12344,6 +13666,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H441" t="n">
+        <v>260.2853585002077</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -12371,6 +13696,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H442" t="n">
+        <v>208.5962880424154</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -12398,6 +13726,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H443" t="n">
+        <v>98.25808763279977</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -12418,12 +13749,15 @@
         <v>86.38211000000001</v>
       </c>
       <c r="F444" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H444" t="n">
+        <v>208.4277253435319</v>
       </c>
     </row>
     <row r="445">
@@ -12445,12 +13779,15 @@
         <v>90.25793999999999</v>
       </c>
       <c r="F445" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H445" t="n">
+        <v>212.3386261781216</v>
       </c>
     </row>
     <row r="446">
@@ -12472,12 +13809,15 @@
         <v>142.70429</v>
       </c>
       <c r="F446" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H446" t="n">
+        <v>209.6504118209775</v>
       </c>
     </row>
     <row r="447">
@@ -12506,6 +13846,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H447" t="n">
+        <v>182.7667459903581</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -12533,6 +13876,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H448" t="n">
+        <v>423.5769488863627</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -12560,6 +13906,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H449" t="n">
+        <v>95.67790461919937</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -12580,12 +13929,15 @@
         <v>81.9524</v>
       </c>
       <c r="F450" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H450" t="n">
+        <v>484.1532863787845</v>
       </c>
     </row>
     <row r="451">
@@ -12607,12 +13959,15 @@
         <v>129.72508</v>
       </c>
       <c r="F451" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H451" t="n">
+        <v>228.5218675824255</v>
       </c>
     </row>
     <row r="452">
@@ -12641,6 +13996,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H452" t="n">
+        <v>102.6353178628117</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -12661,12 +14019,15 @@
         <v>137.67475</v>
       </c>
       <c r="F453" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H453" t="n">
+        <v>301.0507133735346</v>
       </c>
     </row>
     <row r="454">
@@ -12688,12 +14049,15 @@
         <v>91.25033126999999</v>
       </c>
       <c r="F454" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H454" t="n">
+        <v>386.2146034980639</v>
       </c>
     </row>
     <row r="455">
@@ -12722,6 +14086,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H455" t="n">
+        <v>97.23843853479993</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -12749,6 +14116,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H456" t="n">
+        <v>102.4918480857375</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -12769,12 +14139,15 @@
         <v>33.4468</v>
       </c>
       <c r="F457" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H457" t="n">
+        <v>207.4009137645875</v>
       </c>
     </row>
     <row r="458">
@@ -12803,6 +14176,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H458" t="n">
+        <v>428.9279411296831</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -12823,12 +14199,15 @@
         <v>99.37579999999998</v>
       </c>
       <c r="F459" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H459" t="n">
+        <v>229.5591365467445</v>
       </c>
     </row>
     <row r="460">
@@ -12857,6 +14236,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H460" t="n">
+        <v>175.6247251323167</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -12884,6 +14266,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H461" t="n">
+        <v>175.3296764752763</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -12911,6 +14296,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H462" t="n">
+        <v>51.09998502013926</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -12938,6 +14326,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H463" t="n">
+        <v>99.97599824829125</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -12965,6 +14356,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H464" t="n">
+        <v>168.7811319371953</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -12985,12 +14379,15 @@
         <v>97.37148000000001</v>
       </c>
       <c r="F465" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H465" t="n">
+        <v>211.6732813870892</v>
       </c>
     </row>
     <row r="466">
@@ -13012,12 +14409,15 @@
         <v>130.5938</v>
       </c>
       <c r="F466" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H466" t="n">
+        <v>232.6220725104062</v>
       </c>
     </row>
     <row r="467">
@@ -13046,6 +14446,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H467" t="n">
+        <v>100.092607826785</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -13073,6 +14476,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H468" t="n">
+        <v>96.94585824993405</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -13100,6 +14506,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H469" t="n">
+        <v>178.0547726996159</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -13120,12 +14529,15 @@
         <v>123.36434</v>
       </c>
       <c r="F470" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H470" t="n">
+        <v>209.6007710482695</v>
       </c>
     </row>
     <row r="471">
@@ -13147,12 +14559,15 @@
         <v>173.58828</v>
       </c>
       <c r="F471" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H471" t="n">
+        <v>217.769738655443</v>
       </c>
     </row>
     <row r="472">
@@ -13181,6 +14596,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H472" t="n">
+        <v>102.700602997662</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -13208,6 +14626,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H473" t="n">
+        <v>172.7706883374275</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -13235,6 +14656,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H474" t="n">
+        <v>429.3340900803877</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -13262,6 +14686,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H475" t="n">
+        <v>99.365783649566</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -13289,6 +14716,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H476" t="n">
+        <v>426.3835440125061</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -13316,6 +14746,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H477" t="n">
+        <v>178.0194198959729</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -13336,12 +14769,15 @@
         <v>115.35392</v>
       </c>
       <c r="F478" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H478" t="n">
+        <v>208.9435669676058</v>
       </c>
     </row>
     <row r="479">
@@ -13370,6 +14806,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H479" t="n">
+        <v>178.8457234807114</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -13397,6 +14836,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H480" t="n">
+        <v>107.3145602966586</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -13424,6 +14866,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H481" t="n">
+        <v>78.34448568653632</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -13444,12 +14889,15 @@
         <v>133.14993041</v>
       </c>
       <c r="F482" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>DC_3</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H482" t="n">
+        <v>494.2465546328309</v>
       </c>
     </row>
     <row r="483">
@@ -13478,6 +14926,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H483" t="n">
+        <v>208.6719006944995</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -13505,6 +14956,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H484" t="n">
+        <v>173.0380180324195</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -13532,6 +14986,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H485" t="n">
+        <v>306.8243085037814</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -13552,12 +15009,15 @@
         <v>175.2077001</v>
       </c>
       <c r="F486" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H486" t="n">
+        <v>509.5008732297528</v>
       </c>
     </row>
     <row r="487">
@@ -13579,12 +15039,15 @@
         <v>168.87164</v>
       </c>
       <c r="F487" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H487" t="n">
+        <v>163.7335498059527</v>
       </c>
     </row>
     <row r="488">
@@ -13606,12 +15069,15 @@
         <v>66.75664999999999</v>
       </c>
       <c r="F488" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H488" t="n">
+        <v>482.7255904190506</v>
       </c>
     </row>
     <row r="489">
@@ -13640,6 +15106,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H489" t="n">
+        <v>176.3452400412433</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -13667,6 +15136,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H490" t="n">
+        <v>96.72437721924653</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -13687,12 +15159,15 @@
         <v>89.62715</v>
       </c>
       <c r="F491" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_4</t>
+        </is>
+      </c>
+      <c r="H491" t="n">
+        <v>482.017426840228</v>
       </c>
     </row>
     <row r="492">
@@ -13714,12 +15189,15 @@
         <v>43.78264999999999</v>
       </c>
       <c r="F492" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H492" t="n">
+        <v>228.9300086027407</v>
       </c>
     </row>
     <row r="493">
@@ -13748,6 +15226,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H493" t="n">
+        <v>144.5352295904483</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -13775,6 +15256,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H494" t="n">
+        <v>304.1258562519051</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -13802,6 +15286,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H495" t="n">
+        <v>176.328593549544</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -13822,12 +15309,15 @@
         <v>59.60680000000001</v>
       </c>
       <c r="F496" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>DC_2</t>
-        </is>
+          <t>DC_3</t>
+        </is>
+      </c>
+      <c r="H496" t="n">
+        <v>345.6396454305997</v>
       </c>
     </row>
     <row r="497">
@@ -13849,12 +15339,15 @@
         <v>61.33865</v>
       </c>
       <c r="F497" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H497" t="n">
+        <v>204.2468831622038</v>
       </c>
     </row>
     <row r="498">
@@ -13883,6 +15376,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H498" t="n">
+        <v>78.46596702303529</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -13910,6 +15406,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H499" t="n">
+        <v>38.42670238202552</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -13930,12 +15429,15 @@
         <v>97.11096000000002</v>
       </c>
       <c r="F500" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H500" t="n">
+        <v>228.1579527766796</v>
       </c>
     </row>
     <row r="501">
@@ -13957,12 +15459,15 @@
         <v>77.12655000000001</v>
       </c>
       <c r="F501" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H501" t="n">
+        <v>229.1174983035737</v>
       </c>
     </row>
     <row r="502">
@@ -13991,6 +15496,9 @@
           <t>DC_3</t>
         </is>
       </c>
+      <c r="H502" t="n">
+        <v>121.9724126682299</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -14011,12 +15519,15 @@
         <v>39.40545</v>
       </c>
       <c r="F503" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H503" t="n">
+        <v>229.178044449383</v>
       </c>
     </row>
     <row r="504">
@@ -14038,12 +15549,15 @@
         <v>51.32812</v>
       </c>
       <c r="F504" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>DC_1</t>
-        </is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H504" t="n">
+        <v>216.9896041973278</v>
       </c>
     </row>
     <row r="505">
@@ -14071,6 +15585,9 @@
         <is>
           <t>DC_3</t>
         </is>
+      </c>
+      <c r="H505" t="n">
+        <v>112.4827109906133</v>
       </c>
     </row>
   </sheetData>

--- a/clustered_output.xlsx
+++ b/clustered_output.xlsx
@@ -489,15 +489,15 @@
         <v>41.29720544</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>293.8460057247369</v>
+        <v>312.3476429270801</v>
       </c>
     </row>
     <row r="3">
@@ -519,15 +519,15 @@
         <v>55.87958479999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>122.4928162679067</v>
+        <v>141.5567884198512</v>
       </c>
     </row>
     <row r="4">
@@ -549,15 +549,15 @@
         <v>33.26804828</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>365.5697738719786</v>
+        <v>375.2133947621184</v>
       </c>
     </row>
     <row r="5">
@@ -579,15 +579,15 @@
         <v>93.98859224</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>137.1836921009171</v>
+        <v>118.9018437587613</v>
       </c>
     </row>
     <row r="6">
@@ -609,15 +609,15 @@
         <v>40.42737347999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>370.9274282971861</v>
+        <v>386.3087422339807</v>
       </c>
     </row>
     <row r="7">
@@ -639,15 +639,15 @@
         <v>63.74664785</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>135.1668889158399</v>
+        <v>118.9558925056448</v>
       </c>
     </row>
     <row r="8">
@@ -669,15 +669,15 @@
         <v>86.27647392</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>245.074598671275</v>
+        <v>328.2730746713401</v>
       </c>
     </row>
     <row r="9">
@@ -699,15 +699,15 @@
         <v>91.16850180000002</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>304.8226550499002</v>
+        <v>388.3345797490471</v>
       </c>
     </row>
     <row r="10">
@@ -729,15 +729,15 @@
         <v>86.99766654</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>466.4283882980909</v>
+        <v>485.78077300261</v>
       </c>
     </row>
     <row r="11">
@@ -759,15 +759,15 @@
         <v>82.87167607000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>472.7473727202855</v>
+        <v>492.8602485423139</v>
       </c>
     </row>
     <row r="12">
@@ -789,15 +789,15 @@
         <v>113.41016794</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>151.0314023786419</v>
+        <v>133.5075553693926</v>
       </c>
     </row>
     <row r="13">
@@ -819,15 +819,15 @@
         <v>90.7568601</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>155.8689391528941</v>
+        <v>138.8671569739272</v>
       </c>
     </row>
     <row r="14">
@@ -849,15 +849,15 @@
         <v>129.90572294</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>170.9279161682704</v>
+        <v>153.4618793634799</v>
       </c>
     </row>
     <row r="15">
@@ -879,15 +879,15 @@
         <v>39.66574248000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>413.5495142717604</v>
+        <v>431.3442798376877</v>
       </c>
     </row>
     <row r="16">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>414.1680610379193</v>
+        <v>424.6636155876099</v>
       </c>
     </row>
     <row r="17">
@@ -939,15 +939,15 @@
         <v>71.55889309999998</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>155.8711978103603</v>
+        <v>139.2049227489753</v>
       </c>
     </row>
     <row r="18">
@@ -969,15 +969,15 @@
         <v>112.80354775</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>197.3786891663952</v>
+        <v>277.9779084992091</v>
       </c>
     </row>
     <row r="19">
@@ -999,15 +999,15 @@
         <v>73.57074283999999</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>150.8606934652393</v>
+        <v>133.0509347923777</v>
       </c>
     </row>
     <row r="20">
@@ -1029,15 +1029,15 @@
         <v>48.18771840000001</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>147.942072551742</v>
+        <v>168.2999938886427</v>
       </c>
     </row>
     <row r="21">
@@ -1059,15 +1059,15 @@
         <v>137.72677575</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>170.0748304559448</v>
+        <v>241.286644854991</v>
       </c>
     </row>
     <row r="22">
@@ -1089,15 +1089,15 @@
         <v>61.96439013000001</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>274.7525032714101</v>
+        <v>254.3489777477395</v>
       </c>
     </row>
     <row r="23">
@@ -1119,15 +1119,15 @@
         <v>57.01195806</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>422.7970840515572</v>
+        <v>439.8981805465693</v>
       </c>
     </row>
     <row r="24">
@@ -1149,15 +1149,15 @@
         <v>75.03426994</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>44.80763566563145</v>
+        <v>114.9129726884635</v>
       </c>
     </row>
     <row r="25">
@@ -1179,15 +1179,15 @@
         <v>45.991</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>392.7470920930622</v>
+        <v>408.5855438226462</v>
       </c>
     </row>
     <row r="26">
@@ -1209,15 +1209,15 @@
         <v>69.51707707</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>296.4696464613529</v>
+        <v>379.9781482388589</v>
       </c>
     </row>
     <row r="27">
@@ -1239,15 +1239,15 @@
         <v>118.63043667</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>162.1806222902383</v>
+        <v>144.8833393517898</v>
       </c>
     </row>
     <row r="28">
@@ -1269,15 +1269,15 @@
         <v>39.05642559</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>390.3002980085579</v>
+        <v>406.3401413649697</v>
       </c>
     </row>
     <row r="29">
@@ -1299,15 +1299,15 @@
         <v>51.11150699</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>106.6790260503075</v>
+        <v>183.7395365549781</v>
       </c>
     </row>
     <row r="30">
@@ -1329,15 +1329,15 @@
         <v>90.55661511999999</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>260.1363480138145</v>
+        <v>280.1001551232182</v>
       </c>
     </row>
     <row r="31">
@@ -1359,15 +1359,15 @@
         <v>80.49179736000001</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>156.190021202696</v>
+        <v>137.9850073898567</v>
       </c>
     </row>
     <row r="32">
@@ -1389,15 +1389,15 @@
         <v>137.7462625</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>160.9219624355327</v>
+        <v>143.1370130472784</v>
       </c>
     </row>
     <row r="33">
@@ -1419,15 +1419,15 @@
         <v>82.06561287</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>398.7773663232627</v>
+        <v>414.6563633974813</v>
       </c>
     </row>
     <row r="34">
@@ -1449,15 +1449,15 @@
         <v>40.91439332</v>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>159.2187052602542</v>
+        <v>231.6252831067762</v>
       </c>
     </row>
     <row r="35">
@@ -1479,15 +1479,15 @@
         <v>94.20747311999999</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>159.2061091161018</v>
+        <v>141.5202761549733</v>
       </c>
     </row>
     <row r="36">
@@ -1509,15 +1509,15 @@
         <v>51.34208147000001</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>467.3803848016624</v>
+        <v>486.7713001932132</v>
       </c>
     </row>
     <row r="37">
@@ -1539,15 +1539,15 @@
         <v>89.43269527999999</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>44.22068792538425</v>
+        <v>115.9067835773086</v>
       </c>
     </row>
     <row r="38">
@@ -1569,15 +1569,15 @@
         <v>87.62353223</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>155.3531487189899</v>
+        <v>137.8672753703998</v>
       </c>
     </row>
     <row r="39">
@@ -1599,15 +1599,15 @@
         <v>113.62947597</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>384.5306082334927</v>
+        <v>400.3943203558753</v>
       </c>
     </row>
     <row r="40">
@@ -1629,15 +1629,15 @@
         <v>97.86042042</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>284.4129910582891</v>
+        <v>367.7369200108809</v>
       </c>
     </row>
     <row r="41">
@@ -1659,15 +1659,15 @@
         <v>120.70724466</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>24.49259868729828</v>
+        <v>98.15468437307703</v>
       </c>
     </row>
     <row r="42">
@@ -1689,15 +1689,15 @@
         <v>63.64605510000001</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>230.7789116574628</v>
+        <v>249.876798128665</v>
       </c>
     </row>
     <row r="43">
@@ -1719,15 +1719,15 @@
         <v>79.88549751000001</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>94.04767826631056</v>
+        <v>139.6700844491425</v>
       </c>
     </row>
     <row r="44">
@@ -1749,15 +1749,15 @@
         <v>75.97018895000001</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>382.7309042653473</v>
+        <v>392.3383289461026</v>
       </c>
     </row>
     <row r="45">
@@ -1779,15 +1779,15 @@
         <v>58.83139722999999</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>277.0434321345084</v>
+        <v>360.733750681989</v>
       </c>
     </row>
     <row r="46">
@@ -1809,15 +1809,15 @@
         <v>24.03516849</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>363.3676583725137</v>
+        <v>380.3280875652389</v>
       </c>
     </row>
     <row r="47">
@@ -1839,15 +1839,15 @@
         <v>17.60890872</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>367.859288993661</v>
+        <v>384.2953851204009</v>
       </c>
     </row>
     <row r="48">
@@ -1869,15 +1869,15 @@
         <v>82.63783919000001</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>148.5993207899491</v>
+        <v>131.7915489876928</v>
       </c>
     </row>
     <row r="49">
@@ -1899,15 +1899,15 @@
         <v>56.29949515999999</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>394.3261874511825</v>
+        <v>410.0957017648079</v>
       </c>
     </row>
     <row r="50">
@@ -1929,15 +1929,15 @@
         <v>47.27391910999999</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>466.862664902199</v>
+        <v>486.3552966158776</v>
       </c>
     </row>
     <row r="51">
@@ -1959,15 +1959,15 @@
         <v>55.12580752</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>244.0476712680346</v>
+        <v>327.371843717464</v>
       </c>
     </row>
     <row r="52">
@@ -1989,15 +1989,15 @@
         <v>70.25959358</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>105.0335556921193</v>
+        <v>126.6884221680908</v>
       </c>
     </row>
     <row r="53">
@@ -2019,15 +2019,15 @@
         <v>62.59155026999998</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>109.7389620112709</v>
+        <v>93.8415059481957</v>
       </c>
     </row>
     <row r="54">
@@ -2049,15 +2049,15 @@
         <v>78.94616125999998</v>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>108.6104453741741</v>
+        <v>176.4470644623666</v>
       </c>
     </row>
     <row r="55">
@@ -2079,15 +2079,15 @@
         <v>101.76988238</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>164.3915028407905</v>
+        <v>146.7189630432425</v>
       </c>
     </row>
     <row r="56">
@@ -2109,15 +2109,15 @@
         <v>44.19095989</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>462.2694883273145</v>
+        <v>481.7271018753432</v>
       </c>
     </row>
     <row r="57">
@@ -2139,15 +2139,15 @@
         <v>93.80458936000001</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>378.9423803573275</v>
+        <v>399.3315282450388</v>
       </c>
     </row>
     <row r="58">
@@ -2169,15 +2169,15 @@
         <v>49.10406079999999</v>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>100.7259767775823</v>
+        <v>108.7848638752269</v>
       </c>
     </row>
     <row r="59">
@@ -2199,15 +2199,15 @@
         <v>99.07280474</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>165.351606625248</v>
+        <v>147.1540323338647</v>
       </c>
     </row>
     <row r="60">
@@ -2229,15 +2229,15 @@
         <v>69.66181495000001</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>155.0573123555761</v>
+        <v>137.4222979025599</v>
       </c>
     </row>
     <row r="61">
@@ -2259,15 +2259,15 @@
         <v>157.49350527</v>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>109.6785426341018</v>
+        <v>131.6200947203843</v>
       </c>
     </row>
     <row r="62">
@@ -2289,15 +2289,15 @@
         <v>69.61420304000001</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>146.6430460690046</v>
+        <v>129.47271130013</v>
       </c>
     </row>
     <row r="63">
@@ -2319,15 +2319,15 @@
         <v>15.037</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>393.1682837749015</v>
+        <v>409.142576533964</v>
       </c>
     </row>
     <row r="64">
@@ -2349,15 +2349,15 @@
         <v>33.56141599999999</v>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>245.079558964301</v>
+        <v>328.2671538715692</v>
       </c>
     </row>
     <row r="65">
@@ -2379,15 +2379,15 @@
         <v>122.2742197</v>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>92.73717022738394</v>
+        <v>137.775968778899</v>
       </c>
     </row>
     <row r="66">
@@ -2409,15 +2409,15 @@
         <v>29.31689904</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>299.3569840336716</v>
+        <v>382.7725994990877</v>
       </c>
     </row>
     <row r="67">
@@ -2439,15 +2439,15 @@
         <v>24.08448896</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>144.2270060908566</v>
+        <v>127.2148671715527</v>
       </c>
     </row>
     <row r="68">
@@ -2469,15 +2469,15 @@
         <v>59.56919848</v>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>103.496349890505</v>
+        <v>187.1173891728598</v>
       </c>
     </row>
     <row r="69">
@@ -2499,15 +2499,15 @@
         <v>61.17361757</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>68.27692687408248</v>
+        <v>75.96318517921419</v>
       </c>
     </row>
     <row r="70">
@@ -2529,15 +2529,15 @@
         <v>45.19398898999999</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>160.2128384245894</v>
+        <v>143.1079901005895</v>
       </c>
     </row>
     <row r="71">
@@ -2559,15 +2559,15 @@
         <v>8.5903492</v>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>100.7259767775823</v>
+        <v>108.7848638752269</v>
       </c>
     </row>
     <row r="72">
@@ -2589,15 +2589,15 @@
         <v>77.60705583999999</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>153.1285040266745</v>
+        <v>136.4020147685627</v>
       </c>
     </row>
     <row r="73">
@@ -2619,15 +2619,15 @@
         <v>27.84522936</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>409.2001225630211</v>
+        <v>426.8029932126655</v>
       </c>
     </row>
     <row r="74">
@@ -2649,15 +2649,15 @@
         <v>121.24150382</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>151.6020550227136</v>
+        <v>134.4832099001436</v>
       </c>
     </row>
     <row r="75">
@@ -2679,15 +2679,15 @@
         <v>109.77473927</v>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>96.58126533093416</v>
+        <v>124.5019625679025</v>
       </c>
     </row>
     <row r="76">
@@ -2709,15 +2709,15 @@
         <v>27.96024677</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>450.0229442223006</v>
+        <v>468.7426850661527</v>
       </c>
     </row>
     <row r="77">
@@ -2739,15 +2739,15 @@
         <v>127.09983192</v>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>103.6119916373755</v>
+        <v>120.9179947370747</v>
       </c>
     </row>
     <row r="78">
@@ -2769,15 +2769,15 @@
         <v>40.97559472</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>190.6825132721265</v>
+        <v>211.1051461597017</v>
       </c>
     </row>
     <row r="79">
@@ -2799,15 +2799,15 @@
         <v>55.95136335999999</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>223.9844703950944</v>
+        <v>244.3990735124999</v>
       </c>
     </row>
     <row r="80">
@@ -2829,15 +2829,15 @@
         <v>99.95687511999999</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>168.4133991841169</v>
+        <v>151.0245141196881</v>
       </c>
     </row>
     <row r="81">
@@ -2859,15 +2859,15 @@
         <v>171.25894002</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>159.9084196272836</v>
+        <v>142.94381580362</v>
       </c>
     </row>
     <row r="82">
@@ -2889,15 +2889,15 @@
         <v>108.25222513</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>155.1193933778405</v>
+        <v>138.2916456117689</v>
       </c>
     </row>
     <row r="83">
@@ -2919,15 +2919,15 @@
         <v>152.37332232</v>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>109.7499568719103</v>
+        <v>130.4725566339279</v>
       </c>
     </row>
     <row r="84">
@@ -2949,15 +2949,15 @@
         <v>137.64539505</v>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>103.1628998334891</v>
+        <v>128.654547153294</v>
       </c>
     </row>
     <row r="85">
@@ -2979,15 +2979,15 @@
         <v>98.88650038</v>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>93.89827386045394</v>
+        <v>137.7742062609717</v>
       </c>
     </row>
     <row r="86">
@@ -3009,15 +3009,15 @@
         <v>174.43258149</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>154.4089620521199</v>
+        <v>137.1832339917709</v>
       </c>
     </row>
     <row r="87">
@@ -3039,15 +3039,15 @@
         <v>131.72022438</v>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>297.954671485222</v>
+        <v>381.4141464317108</v>
       </c>
     </row>
     <row r="88">
@@ -3069,15 +3069,15 @@
         <v>128.67002752</v>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>244.9376359487637</v>
+        <v>328.2324482195975</v>
       </c>
     </row>
     <row r="89">
@@ -3099,15 +3099,15 @@
         <v>151.83197394</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>158.5499688032886</v>
+        <v>141.0311183501512</v>
       </c>
     </row>
     <row r="90">
@@ -3129,15 +3129,15 @@
         <v>70.43858698000003</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>158.4325457480821</v>
+        <v>141.2722471438568</v>
       </c>
     </row>
     <row r="91">
@@ -3159,15 +3159,15 @@
         <v>165.86665209</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>150.0773248273609</v>
+        <v>133.2782084515678</v>
       </c>
     </row>
     <row r="92">
@@ -3189,15 +3189,15 @@
         <v>160.7944185</v>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>111.1930211145544</v>
+        <v>128.5974961593128</v>
       </c>
     </row>
     <row r="93">
@@ -3219,15 +3219,15 @@
         <v>114.30460316</v>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>103.1395370676297</v>
+        <v>126.5993037082896</v>
       </c>
     </row>
     <row r="94">
@@ -3249,15 +3249,15 @@
         <v>27.65862036</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>157.2643207295644</v>
+        <v>140.2315491170268</v>
       </c>
     </row>
     <row r="95">
@@ -3279,15 +3279,15 @@
         <v>107.20581291</v>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>110.9238212584267</v>
+        <v>130.3110932076192</v>
       </c>
     </row>
     <row r="96">
@@ -3309,15 +3309,15 @@
         <v>132.81126806</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>154.3148811061609</v>
+        <v>136.5442645586296</v>
       </c>
     </row>
     <row r="97">
@@ -3339,15 +3339,15 @@
         <v>151.87199567</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>160.7866229667267</v>
+        <v>143.4825259368347</v>
       </c>
     </row>
     <row r="98">
@@ -3369,15 +3369,15 @@
         <v>97.51930487999999</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>153.2436065110408</v>
+        <v>135.7900799156238</v>
       </c>
     </row>
     <row r="99">
@@ -3399,15 +3399,15 @@
         <v>62.68683512</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>394.5056466031788</v>
+        <v>410.3726253648458</v>
       </c>
     </row>
     <row r="100">
@@ -3429,15 +3429,15 @@
         <v>164.09465016</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>163.2868500698719</v>
+        <v>145.7555976740724</v>
       </c>
     </row>
     <row r="101">
@@ -3459,15 +3459,15 @@
         <v>115.75139108</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>150.4724269081669</v>
+        <v>132.978317893762</v>
       </c>
     </row>
     <row r="102">
@@ -3489,15 +3489,15 @@
         <v>112.73454219</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>140.3539978684227</v>
+        <v>123.4723396428809</v>
       </c>
     </row>
     <row r="103">
@@ -3519,15 +3519,15 @@
         <v>165.16716377</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>147.6036965257908</v>
+        <v>131.2088258437179</v>
       </c>
     </row>
     <row r="104">
@@ -3549,15 +3549,15 @@
         <v>98.30353936999998</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>140.9713963838633</v>
+        <v>123.8725865372433</v>
       </c>
     </row>
     <row r="105">
@@ -3579,15 +3579,15 @@
         <v>64.32811749000001</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>382.5222745361521</v>
+        <v>392.2861529735245</v>
       </c>
     </row>
     <row r="106">
@@ -3609,15 +3609,15 @@
         <v>143.1621979</v>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>262.7324413613346</v>
+        <v>282.7352857594362</v>
       </c>
     </row>
     <row r="107">
@@ -3639,15 +3639,15 @@
         <v>62.72158742000001</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>463.6203705187395</v>
+        <v>483.0990667625962</v>
       </c>
     </row>
     <row r="108">
@@ -3669,15 +3669,15 @@
         <v>135.79601133</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>390.2487772391969</v>
+        <v>406.0315877170019</v>
       </c>
     </row>
     <row r="109">
@@ -3699,15 +3699,15 @@
         <v>67.78453388</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>153.539195695105</v>
+        <v>136.4895373399047</v>
       </c>
     </row>
     <row r="110">
@@ -3729,15 +3729,15 @@
         <v>135.40894881</v>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>297.4728206135632</v>
+        <v>380.8965900937883</v>
       </c>
     </row>
     <row r="111">
@@ -3759,15 +3759,15 @@
         <v>134.30264618</v>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>157.7435654334739</v>
+        <v>140.8386301032752</v>
       </c>
     </row>
     <row r="112">
@@ -3789,15 +3789,15 @@
         <v>107.39169483</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>146.3339933783038</v>
+        <v>129.4578906436336</v>
       </c>
     </row>
     <row r="113">
@@ -3819,15 +3819,15 @@
         <v>92.21966651000001</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>149.9757318464934</v>
+        <v>133.6366603171619</v>
       </c>
     </row>
     <row r="114">
@@ -3849,15 +3849,15 @@
         <v>46.65942816</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>275.4336495404298</v>
+        <v>293.4967601443832</v>
       </c>
     </row>
     <row r="115">
@@ -3879,15 +3879,15 @@
         <v>61.25313789</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>367.0969959282192</v>
+        <v>380.9416346172154</v>
       </c>
     </row>
     <row r="116">
@@ -3909,15 +3909,15 @@
         <v>95.79522047999998</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>143.5474732221657</v>
+        <v>126.9811181546085</v>
       </c>
     </row>
     <row r="117">
@@ -3939,15 +3939,15 @@
         <v>131.4488539</v>
       </c>
       <c r="F117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>106.0711509208065</v>
+        <v>133.5964249022822</v>
       </c>
     </row>
     <row r="118">
@@ -3969,15 +3969,15 @@
         <v>139.22461155</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>158.0974000785128</v>
+        <v>140.7173414264341</v>
       </c>
     </row>
     <row r="119">
@@ -3999,15 +3999,15 @@
         <v>69.87724643999999</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>463.8843261091552</v>
+        <v>483.3104400018008</v>
       </c>
     </row>
     <row r="120">
@@ -4029,15 +4029,15 @@
         <v>26.29534809</v>
       </c>
       <c r="F120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>297.8104472791561</v>
+        <v>381.2386282180768</v>
       </c>
     </row>
     <row r="121">
@@ -4059,15 +4059,15 @@
         <v>124.64185643</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>162.1540802945918</v>
+        <v>144.4670761581502</v>
       </c>
     </row>
     <row r="122">
@@ -4089,15 +4089,15 @@
         <v>67.21328875</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>150.4196753751032</v>
+        <v>133.0423815907709</v>
       </c>
     </row>
     <row r="123">
@@ -4119,15 +4119,15 @@
         <v>104.41013483</v>
       </c>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>40.73116379217367</v>
+        <v>114.1266628728534</v>
       </c>
     </row>
     <row r="124">
@@ -4149,15 +4149,15 @@
         <v>55.17039302000001</v>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>151.2941074551429</v>
+        <v>134.3485696562654</v>
       </c>
     </row>
     <row r="125">
@@ -4179,15 +4179,15 @@
         <v>156.16160591</v>
       </c>
       <c r="F125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>137.6423599800942</v>
+        <v>120.4872005564761</v>
       </c>
     </row>
     <row r="126">
@@ -4209,15 +4209,15 @@
         <v>86.21620850000002</v>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>141.7442910967588</v>
+        <v>125.9371768049107</v>
       </c>
     </row>
     <row r="127">
@@ -4239,15 +4239,15 @@
         <v>71.97972833</v>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>152.1140732346485</v>
+        <v>134.3759538513394</v>
       </c>
     </row>
     <row r="128">
@@ -4269,15 +4269,15 @@
         <v>116.03335498</v>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>148.417679040193</v>
+        <v>131.3698777549343</v>
       </c>
     </row>
     <row r="129">
@@ -4299,15 +4299,15 @@
         <v>87.04857329000001</v>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>155.2912736366582</v>
+        <v>137.9526950784186</v>
       </c>
     </row>
     <row r="130">
@@ -4329,15 +4329,15 @@
         <v>141.72703296</v>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>153.7467056988309</v>
+        <v>136.3894994966892</v>
       </c>
     </row>
     <row r="131">
@@ -4359,15 +4359,15 @@
         <v>145.58214742</v>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>68.55822665796128</v>
+        <v>70.25768122189537</v>
       </c>
     </row>
     <row r="132">
@@ -4389,15 +4389,15 @@
         <v>148.1403535</v>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>47.08708195175153</v>
+        <v>49.97972614757656</v>
       </c>
     </row>
     <row r="133">
@@ -4419,15 +4419,15 @@
         <v>39.35975862000001</v>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>391.8184530774033</v>
+        <v>407.7414728579811</v>
       </c>
     </row>
     <row r="134">
@@ -4449,15 +4449,15 @@
         <v>121.18436646</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>157.8095881689238</v>
+        <v>140.6749761342152</v>
       </c>
     </row>
     <row r="135">
@@ -4479,15 +4479,15 @@
         <v>174.54029805</v>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>171.5590778179512</v>
+        <v>242.8897244503717</v>
       </c>
     </row>
     <row r="136">
@@ -4509,15 +4509,15 @@
         <v>71.22344247000001</v>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>102.338791598857</v>
+        <v>135.8054469712873</v>
       </c>
     </row>
     <row r="137">
@@ -4539,15 +4539,15 @@
         <v>86.91646299999999</v>
       </c>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>105.4461159483704</v>
+        <v>137.3146338603078</v>
       </c>
     </row>
     <row r="138">
@@ -4569,15 +4569,15 @@
         <v>113.58351808</v>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>154.3020684321744</v>
+        <v>137.5980426536427</v>
       </c>
     </row>
     <row r="139">
@@ -4599,15 +4599,15 @@
         <v>130.82707128</v>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>144.0207040191272</v>
+        <v>126.7735021255614</v>
       </c>
     </row>
     <row r="140">
@@ -4629,15 +4629,15 @@
         <v>83.83990669000001</v>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>388.4867996322367</v>
+        <v>404.208875401731</v>
       </c>
     </row>
     <row r="141">
@@ -4659,15 +4659,15 @@
         <v>66.93223488999999</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>160.4530529800002</v>
+        <v>143.2619700296298</v>
       </c>
     </row>
     <row r="142">
@@ -4689,15 +4689,15 @@
         <v>94.84938579</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>279.7075176862222</v>
+        <v>259.3122659168254</v>
       </c>
     </row>
     <row r="143">
@@ -4719,15 +4719,15 @@
         <v>145.91838293</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>137.8802470023848</v>
+        <v>122.5537646253599</v>
       </c>
     </row>
     <row r="144">
@@ -4749,15 +4749,15 @@
         <v>148.16292628</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>125.8355096270716</v>
+        <v>108.9835170149182</v>
       </c>
     </row>
     <row r="145">
@@ -4779,15 +4779,15 @@
         <v>22.03899181</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>369.1622100435767</v>
+        <v>382.9364609623582</v>
       </c>
     </row>
     <row r="146">
@@ -4809,15 +4809,15 @@
         <v>169.43078549</v>
       </c>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>40.93402369732947</v>
+        <v>112.9323050997713</v>
       </c>
     </row>
     <row r="147">
@@ -4839,15 +4839,15 @@
         <v>115.96496099</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>146.5562506993173</v>
+        <v>129.9286643047488</v>
       </c>
     </row>
     <row r="148">
@@ -4869,15 +4869,15 @@
         <v>97.54827051999999</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>145.0353621763646</v>
+        <v>126.9603102938765</v>
       </c>
     </row>
     <row r="149">
@@ -4899,15 +4899,15 @@
         <v>171.24941356</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>157.1304892525723</v>
+        <v>139.0718628370146</v>
       </c>
     </row>
     <row r="150">
@@ -4929,15 +4929,15 @@
         <v>79.48337347</v>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>121.03539755116</v>
+        <v>104.3207321729001</v>
       </c>
     </row>
     <row r="151">
@@ -4959,15 +4959,15 @@
         <v>21.38957457</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>378.6092271739076</v>
+        <v>394.1735633146689</v>
       </c>
     </row>
     <row r="152">
@@ -4989,15 +4989,15 @@
         <v>56.00126308</v>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>453.0618631701936</v>
+        <v>471.6729480562649</v>
       </c>
     </row>
     <row r="153">
@@ -5019,15 +5019,15 @@
         <v>116.54724109</v>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>150.9465552515387</v>
+        <v>134.3986826020986</v>
       </c>
     </row>
     <row r="154">
@@ -5049,15 +5049,15 @@
         <v>136.56314483</v>
       </c>
       <c r="F154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>26.39503825315914</v>
+        <v>100.2591398725851</v>
       </c>
     </row>
     <row r="155">
@@ -5079,15 +5079,15 @@
         <v>132.34473269</v>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>139.6648102466222</v>
+        <v>122.8495905764372</v>
       </c>
     </row>
     <row r="156">
@@ -5109,15 +5109,15 @@
         <v>127.67648195</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>147.6298806526679</v>
+        <v>130.088061613333</v>
       </c>
     </row>
     <row r="157">
@@ -5139,15 +5139,15 @@
         <v>101.97064253</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>466.5173357135325</v>
+        <v>485.9871884773702</v>
       </c>
     </row>
     <row r="158">
@@ -5169,15 +5169,15 @@
         <v>64.40666220000001</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>378.5505972995411</v>
+        <v>388.4173225360324</v>
       </c>
     </row>
     <row r="159">
@@ -5199,15 +5199,15 @@
         <v>133.79668708</v>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>166.3585398305499</v>
+        <v>149.1025029821664</v>
       </c>
     </row>
     <row r="160">
@@ -5229,15 +5229,15 @@
         <v>138.15013296</v>
       </c>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>295.1284815246919</v>
+        <v>378.5419582096303</v>
       </c>
     </row>
     <row r="161">
@@ -5259,15 +5259,15 @@
         <v>150.50007586</v>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>148.430521977768</v>
+        <v>130.6475561507304</v>
       </c>
     </row>
     <row r="162">
@@ -5289,15 +5289,15 @@
         <v>93.60651496</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>160.9527014377235</v>
+        <v>143.4355450702218</v>
       </c>
     </row>
     <row r="163">
@@ -5319,15 +5319,15 @@
         <v>129.31327658</v>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>66.16610374030769</v>
+        <v>68.20923825105052</v>
       </c>
     </row>
     <row r="164">
@@ -5349,15 +5349,15 @@
         <v>106.88348563</v>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>403.3770685462418</v>
+        <v>423.5281084764496</v>
       </c>
     </row>
     <row r="165">
@@ -5379,15 +5379,15 @@
         <v>42.43144776</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>369.9360371615572</v>
+        <v>383.5877977344479</v>
       </c>
     </row>
     <row r="166">
@@ -5409,15 +5409,15 @@
         <v>60.79293023</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>312.3121417069709</v>
+        <v>326.0226848177935</v>
       </c>
     </row>
     <row r="167">
@@ -5439,15 +5439,15 @@
         <v>77.59270448000001</v>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>157.9650373618147</v>
+        <v>140.1897991510045</v>
       </c>
     </row>
     <row r="168">
@@ -5469,15 +5469,15 @@
         <v>53.785478</v>
       </c>
       <c r="F168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>97.45824180501572</v>
+        <v>141.3235570287463</v>
       </c>
     </row>
     <row r="169">
@@ -5499,15 +5499,15 @@
         <v>145.0125221</v>
       </c>
       <c r="F169" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>43.97404253119719</v>
+        <v>55.30319905350883</v>
       </c>
     </row>
     <row r="170">
@@ -5529,15 +5529,15 @@
         <v>134.76338509</v>
       </c>
       <c r="F170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>140.7851946362896</v>
+        <v>125.1863571233696</v>
       </c>
     </row>
     <row r="171">
@@ -5559,15 +5559,15 @@
         <v>34.09060356</v>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>399.5083708833428</v>
+        <v>416.8347839584198</v>
       </c>
     </row>
     <row r="172">
@@ -5589,15 +5589,15 @@
         <v>103.95516876</v>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>161.5314469475466</v>
+        <v>144.4377989386378</v>
       </c>
     </row>
     <row r="173">
@@ -5619,15 +5619,15 @@
         <v>129.96221128</v>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>152.6882497958964</v>
+        <v>134.3534034235337</v>
       </c>
     </row>
     <row r="174">
@@ -5649,15 +5649,15 @@
         <v>123.25258422</v>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H174" t="n">
-        <v>130.9552456548431</v>
+        <v>114.0055451393923</v>
       </c>
     </row>
     <row r="175">
@@ -5679,15 +5679,15 @@
         <v>114.2480122</v>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H175" t="n">
-        <v>110.1578374848856</v>
+        <v>124.7308673591305</v>
       </c>
     </row>
     <row r="176">
@@ -5709,15 +5709,15 @@
         <v>148.70392757</v>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H176" t="n">
-        <v>198.8890780199291</v>
+        <v>279.5492674223455</v>
       </c>
     </row>
     <row r="177">
@@ -5739,15 +5739,15 @@
         <v>164.48669544</v>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>266.3355288928579</v>
+        <v>286.2681725369665</v>
       </c>
     </row>
     <row r="178">
@@ -5769,15 +5769,15 @@
         <v>149.1072418</v>
       </c>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H178" t="n">
-        <v>387.6774496753766</v>
+        <v>403.3875092325755</v>
       </c>
     </row>
     <row r="179">
@@ -5799,15 +5799,15 @@
         <v>114.08940098</v>
       </c>
       <c r="F179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>143.8721470076325</v>
+        <v>127.4899347416196</v>
       </c>
     </row>
     <row r="180">
@@ -5829,15 +5829,15 @@
         <v>112.05923696</v>
       </c>
       <c r="F180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H180" t="n">
-        <v>140.9664354752053</v>
+        <v>161.0626768672974</v>
       </c>
     </row>
     <row r="181">
@@ -5859,15 +5859,15 @@
         <v>64.98465548</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>142.7213522013847</v>
+        <v>127.0267048232512</v>
       </c>
     </row>
     <row r="182">
@@ -5889,15 +5889,15 @@
         <v>72.72579613999999</v>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H182" t="n">
-        <v>156.9633839319166</v>
+        <v>139.3757855483318</v>
       </c>
     </row>
     <row r="183">
@@ -5919,15 +5919,15 @@
         <v>103.13068804</v>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>156.7968949445768</v>
+        <v>139.1174159018112</v>
       </c>
     </row>
     <row r="184">
@@ -5949,15 +5949,15 @@
         <v>88.39244152999999</v>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H184" t="n">
-        <v>145.3817134522845</v>
+        <v>129.1647804488381</v>
       </c>
     </row>
     <row r="185">
@@ -5979,15 +5979,15 @@
         <v>111.28124526</v>
       </c>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H185" t="n">
-        <v>164.8960223765515</v>
+        <v>147.3991022417724</v>
       </c>
     </row>
     <row r="186">
@@ -6009,15 +6009,15 @@
         <v>77.23146711</v>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H186" t="n">
-        <v>160.1367601744726</v>
+        <v>143.0036862149796</v>
       </c>
     </row>
     <row r="187">
@@ -6039,15 +6039,15 @@
         <v>87.69854039000001</v>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H187" t="n">
-        <v>94.57825916665728</v>
+        <v>131.8219351489301</v>
       </c>
     </row>
     <row r="188">
@@ -6069,15 +6069,15 @@
         <v>104.07446787</v>
       </c>
       <c r="F188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H188" t="n">
-        <v>149.0413074483496</v>
+        <v>132.0778531307195</v>
       </c>
     </row>
     <row r="189">
@@ -6099,15 +6099,15 @@
         <v>135.95829359</v>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H189" t="n">
-        <v>105.1204904123371</v>
+        <v>123.3606496386461</v>
       </c>
     </row>
     <row r="190">
@@ -6129,15 +6129,15 @@
         <v>14.04523848</v>
       </c>
       <c r="F190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H190" t="n">
-        <v>388.2139984601232</v>
+        <v>403.4008878879773</v>
       </c>
     </row>
     <row r="191">
@@ -6159,15 +6159,15 @@
         <v>84.03368023</v>
       </c>
       <c r="F191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H191" t="n">
-        <v>46.05181255247427</v>
+        <v>52.44417237728874</v>
       </c>
     </row>
     <row r="192">
@@ -6189,15 +6189,15 @@
         <v>37.35482578</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>393.715675009759</v>
+        <v>410.8985883498559</v>
       </c>
     </row>
     <row r="193">
@@ -6219,15 +6219,15 @@
         <v>29.02313882999999</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>365.5773635412867</v>
+        <v>379.5971643506353</v>
       </c>
     </row>
     <row r="194">
@@ -6249,15 +6249,15 @@
         <v>69.75723010999999</v>
       </c>
       <c r="F194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H194" t="n">
-        <v>90.42836908835832</v>
+        <v>139.1021731415539</v>
       </c>
     </row>
     <row r="195">
@@ -6279,15 +6279,15 @@
         <v>106.29918689</v>
       </c>
       <c r="F195" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H195" t="n">
-        <v>132.9341213620754</v>
+        <v>115.6713272323911</v>
       </c>
     </row>
     <row r="196">
@@ -6309,15 +6309,15 @@
         <v>68.10364146999999</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H196" t="n">
-        <v>148.6479009466308</v>
+        <v>129.9353063725652</v>
       </c>
     </row>
     <row r="197">
@@ -6339,15 +6339,15 @@
         <v>51.23457499999999</v>
       </c>
       <c r="F197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H197" t="n">
-        <v>90.66046051512869</v>
+        <v>112.8438318657794</v>
       </c>
     </row>
     <row r="198">
@@ -6369,15 +6369,15 @@
         <v>62.39533672</v>
       </c>
       <c r="F198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H198" t="n">
-        <v>138.4670632375975</v>
+        <v>212.7765634214703</v>
       </c>
     </row>
     <row r="199">
@@ -6399,15 +6399,15 @@
         <v>81.51284326</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>144.8737354091315</v>
+        <v>128.0801182035454</v>
       </c>
     </row>
     <row r="200">
@@ -6429,15 +6429,15 @@
         <v>83.68685203999999</v>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>150.6046320137467</v>
+        <v>133.1566648141351</v>
       </c>
     </row>
     <row r="201">
@@ -6459,15 +6459,15 @@
         <v>68.18522616</v>
       </c>
       <c r="F201" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H201" t="n">
-        <v>141.2826203035115</v>
+        <v>124.8652061847382</v>
       </c>
     </row>
     <row r="202">
@@ -6489,15 +6489,15 @@
         <v>80.24099302</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H202" t="n">
-        <v>151.6595942303774</v>
+        <v>133.5168727607165</v>
       </c>
     </row>
     <row r="203">
@@ -6519,15 +6519,15 @@
         <v>42.55748138000001</v>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H203" t="n">
-        <v>68.87397011120331</v>
+        <v>20.05921122465895</v>
       </c>
     </row>
     <row r="204">
@@ -6549,15 +6549,15 @@
         <v>66.30837547</v>
       </c>
       <c r="F204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H204" t="n">
-        <v>125.0677805919528</v>
+        <v>108.2994590509213</v>
       </c>
     </row>
     <row r="205">
@@ -6579,15 +6579,15 @@
         <v>72.1073177</v>
       </c>
       <c r="F205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H205" t="n">
-        <v>81.78595913441407</v>
+        <v>109.4976212011855</v>
       </c>
     </row>
     <row r="206">
@@ -6609,15 +6609,15 @@
         <v>61.94020108000001</v>
       </c>
       <c r="F206" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H206" t="n">
-        <v>140.0590297326085</v>
+        <v>176.3651706464888</v>
       </c>
     </row>
     <row r="207">
@@ -6639,15 +6639,15 @@
         <v>116.30465114</v>
       </c>
       <c r="F207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H207" t="n">
-        <v>98.7323172694025</v>
+        <v>133.315265358216</v>
       </c>
     </row>
     <row r="208">
@@ -6669,15 +6669,15 @@
         <v>66.85576336</v>
       </c>
       <c r="F208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H208" t="n">
-        <v>150.0719903546772</v>
+        <v>170.4833860549217</v>
       </c>
     </row>
     <row r="209">
@@ -6699,15 +6699,15 @@
         <v>88.47867821</v>
       </c>
       <c r="F209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H209" t="n">
-        <v>156.0220450976014</v>
+        <v>138.0374803401048</v>
       </c>
     </row>
     <row r="210">
@@ -6729,15 +6729,15 @@
         <v>75.59825791</v>
       </c>
       <c r="F210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H210" t="n">
-        <v>168.2216933394938</v>
+        <v>150.5124814610589</v>
       </c>
     </row>
     <row r="211">
@@ -6759,15 +6759,15 @@
         <v>112.48154805</v>
       </c>
       <c r="F211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H211" t="n">
-        <v>142.4573195186641</v>
+        <v>124.7669286489615</v>
       </c>
     </row>
     <row r="212">
@@ -6789,15 +6789,15 @@
         <v>105.4919814</v>
       </c>
       <c r="F212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H212" t="n">
-        <v>87.98069974649448</v>
+        <v>130.7285006445507</v>
       </c>
     </row>
     <row r="213">
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>244.4547600179641</v>
+        <v>237.3450700802627</v>
       </c>
     </row>
     <row r="214">
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>224.1347950788545</v>
+        <v>142.4209975774765</v>
       </c>
     </row>
     <row r="215">
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>383.9683452505717</v>
+        <v>251.3431037068348</v>
       </c>
     </row>
     <row r="216">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>358.6786998752949</v>
+        <v>76.24503928516523</v>
       </c>
     </row>
     <row r="217">
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>405.3050657897217</v>
+        <v>265.8952897520346</v>
       </c>
     </row>
     <row r="218">
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>343.1529027900015</v>
+        <v>240.9662567092115</v>
       </c>
     </row>
     <row r="219">
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>192.2969368458551</v>
+        <v>232.8831422498661</v>
       </c>
     </row>
     <row r="220">
@@ -7037,7 +7037,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>379.5007289420488</v>
+        <v>247.7738698315432</v>
       </c>
     </row>
     <row r="221">
@@ -7067,7 +7067,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>170.9482929019636</v>
+        <v>112.6602580518521</v>
       </c>
     </row>
     <row r="222">
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>277.5254540437227</v>
+        <v>212.0819758215432</v>
       </c>
     </row>
     <row r="223">
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>346.976523051831</v>
+        <v>293.709077172085</v>
       </c>
     </row>
     <row r="224">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>167.7758876733445</v>
+        <v>115.5900301533268</v>
       </c>
     </row>
     <row r="225">
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>405.4342490665469</v>
+        <v>271.5611334846315</v>
       </c>
     </row>
     <row r="226">
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>342.2257220137689</v>
+        <v>97.24423539040143</v>
       </c>
     </row>
     <row r="227">
@@ -7239,15 +7239,15 @@
         <v>65.836</v>
       </c>
       <c r="F227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H227" t="n">
-        <v>511.3525973892623</v>
+        <v>313.550423294308</v>
       </c>
     </row>
     <row r="228">
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>331.1662139980003</v>
+        <v>108.4127441231689</v>
       </c>
     </row>
     <row r="229">
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>381.7256943903093</v>
+        <v>250.6758741271072</v>
       </c>
     </row>
     <row r="230">
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>357.0246673916196</v>
+        <v>75.04265743794267</v>
       </c>
     </row>
     <row r="231">
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>377.0267809314404</v>
+        <v>246.1432344133759</v>
       </c>
     </row>
     <row r="232">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>169.5897000840959</v>
+        <v>114.30192697602</v>
       </c>
     </row>
     <row r="233">
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>336.4473247808326</v>
+        <v>111.4629059928046</v>
       </c>
     </row>
     <row r="234">
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>349.4569968094802</v>
+        <v>297.2711195324988</v>
       </c>
     </row>
     <row r="235">
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>223.0922603127969</v>
+        <v>139.6136387191068</v>
       </c>
     </row>
     <row r="236">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>172.9088095760513</v>
+        <v>110.9698302473184</v>
       </c>
     </row>
     <row r="237">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>378.5427318889581</v>
+        <v>248.3393938035115</v>
       </c>
     </row>
     <row r="238">
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>181.6944955579513</v>
+        <v>178.8354266787257</v>
       </c>
     </row>
     <row r="239">
@@ -7599,15 +7599,15 @@
         <v>111.0064</v>
       </c>
       <c r="F239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H239" t="n">
-        <v>510.8703195477742</v>
+        <v>312.1361089671532</v>
       </c>
     </row>
     <row r="240">
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>353.6441013146468</v>
+        <v>301.6611093529174</v>
       </c>
     </row>
     <row r="241">
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>405.779922177717</v>
+        <v>269.1674756142003</v>
       </c>
     </row>
     <row r="242">
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>354.4869959095565</v>
+        <v>72.72870510989631</v>
       </c>
     </row>
     <row r="243">
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>378.7680856783614</v>
+        <v>248.0490537632104</v>
       </c>
     </row>
     <row r="244">
@@ -7757,7 +7757,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>449.7335626017817</v>
+        <v>171.9775088426673</v>
       </c>
     </row>
     <row r="245">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>176.5776307618488</v>
+        <v>106.9333808471959</v>
       </c>
     </row>
     <row r="246">
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>341.5759657726773</v>
+        <v>113.2379343681344</v>
       </c>
     </row>
     <row r="247">
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>178.9192601996842</v>
+        <v>105.4632331842252</v>
       </c>
     </row>
     <row r="248">
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>337.8575499479376</v>
+        <v>114.3491596408315</v>
       </c>
     </row>
     <row r="249">
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>375.1955729779149</v>
+        <v>245.1275395793918</v>
       </c>
     </row>
     <row r="250">
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>414.9905506571422</v>
+        <v>260.1915026413278</v>
       </c>
     </row>
     <row r="251">
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>449.8968435611127</v>
+        <v>171.6099279259731</v>
       </c>
     </row>
     <row r="252">
@@ -7989,15 +7989,15 @@
         <v>22.082508</v>
       </c>
       <c r="F252" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H252" t="n">
-        <v>128.9049887187745</v>
+        <v>550.2335312616356</v>
       </c>
     </row>
     <row r="253">
@@ -8019,15 +8019,15 @@
         <v>26.1654</v>
       </c>
       <c r="F253" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H253" t="n">
-        <v>199.9453164122694</v>
+        <v>561.5482385892683</v>
       </c>
     </row>
     <row r="254">
@@ -8049,15 +8049,15 @@
         <v>41.9052</v>
       </c>
       <c r="F254" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H254" t="n">
-        <v>295.4992140148996</v>
+        <v>557.0579250598742</v>
       </c>
     </row>
     <row r="255">
@@ -8079,15 +8079,15 @@
         <v>898.0380000000002</v>
       </c>
       <c r="F255" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H255" t="n">
-        <v>379.6069181231939</v>
+        <v>700.0507512815924</v>
       </c>
     </row>
     <row r="256">
@@ -8109,15 +8109,15 @@
         <v>13.4594</v>
       </c>
       <c r="F256" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H256" t="n">
-        <v>380.258306252376</v>
+        <v>698.2315230580112</v>
       </c>
     </row>
     <row r="257">
@@ -8139,15 +8139,15 @@
         <v>109.8696</v>
       </c>
       <c r="F257" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H257" t="n">
-        <v>198.7566561597725</v>
+        <v>579.0433028806783</v>
       </c>
     </row>
     <row r="258">
@@ -8169,15 +8169,15 @@
         <v>128.60566</v>
       </c>
       <c r="F258" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H258" t="n">
-        <v>157.6723325326645</v>
+        <v>509.5702225252728</v>
       </c>
     </row>
     <row r="259">
@@ -8199,15 +8199,15 @@
         <v>571.5419999999999</v>
       </c>
       <c r="F259" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H259" t="n">
-        <v>403.5081622823314</v>
+        <v>844.261714845871</v>
       </c>
     </row>
     <row r="260">
@@ -8229,15 +8229,15 @@
         <v>122.977441</v>
       </c>
       <c r="F260" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H260" t="n">
-        <v>475.9405988279751</v>
+        <v>1046.468721910672</v>
       </c>
     </row>
     <row r="261">
@@ -8259,15 +8259,15 @@
         <v>131.0654675</v>
       </c>
       <c r="F261" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H261" t="n">
-        <v>195.7083783065673</v>
+        <v>508.6605462586443</v>
       </c>
     </row>
     <row r="262">
@@ -8289,15 +8289,15 @@
         <v>95.62609999999999</v>
       </c>
       <c r="F262" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H262" t="n">
-        <v>438.5077834249905</v>
+        <v>996.6799687422387</v>
       </c>
     </row>
     <row r="263">
@@ -8319,15 +8319,15 @@
         <v>106.7479</v>
       </c>
       <c r="F263" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H263" t="n">
-        <v>188.2066440310786</v>
+        <v>510.4480584785989</v>
       </c>
     </row>
     <row r="264">
@@ -8349,15 +8349,15 @@
         <v>123.2049255</v>
       </c>
       <c r="F264" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H264" t="n">
-        <v>190.9071943197909</v>
+        <v>513.2035290608322</v>
       </c>
     </row>
     <row r="265">
@@ -8379,15 +8379,15 @@
         <v>284.046</v>
       </c>
       <c r="F265" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H265" t="n">
-        <v>405.0565056120583</v>
+        <v>843.5142465454093</v>
       </c>
     </row>
     <row r="266">
@@ -8409,15 +8409,15 @@
         <v>995.3472000000002</v>
       </c>
       <c r="F266" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H266" t="n">
-        <v>301.8636096550673</v>
+        <v>553.8226352550597</v>
       </c>
     </row>
     <row r="267">
@@ -8439,15 +8439,15 @@
         <v>56.9948</v>
       </c>
       <c r="F267" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H267" t="n">
-        <v>198.4266612290852</v>
+        <v>576.614965605559</v>
       </c>
     </row>
     <row r="268">
@@ -8469,15 +8469,15 @@
         <v>162.227688</v>
       </c>
       <c r="F268" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H268" t="n">
-        <v>518.4040578096872</v>
+        <v>1085.208121862374</v>
       </c>
     </row>
     <row r="269">
@@ -8499,15 +8499,15 @@
         <v>93.85904950000001</v>
       </c>
       <c r="F269" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H269" t="n">
-        <v>510.6400033426321</v>
+        <v>1074.234516578657</v>
       </c>
     </row>
     <row r="270">
@@ -8529,15 +8529,15 @@
         <v>72.16600000000001</v>
       </c>
       <c r="F270" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H270" t="n">
-        <v>197.6583203948707</v>
+        <v>548.1254464247796</v>
       </c>
     </row>
     <row r="271">
@@ -8559,15 +8559,15 @@
         <v>77.25859999999999</v>
       </c>
       <c r="F271" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H271" t="n">
-        <v>200.1952793995961</v>
+        <v>582.3262762458045</v>
       </c>
     </row>
     <row r="272">
@@ -8589,15 +8589,15 @@
         <v>72.49699999999999</v>
       </c>
       <c r="F272" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H272" t="n">
-        <v>215.1429120314576</v>
+        <v>537.2466317410754</v>
       </c>
     </row>
     <row r="273">
@@ -8619,15 +8619,15 @@
         <v>186.4224215</v>
       </c>
       <c r="F273" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H273" t="n">
-        <v>189.4037922176628</v>
+        <v>515.9199484804882</v>
       </c>
     </row>
     <row r="274">
@@ -8649,15 +8649,15 @@
         <v>150.1102</v>
       </c>
       <c r="F274" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H274" t="n">
-        <v>198.7324288034695</v>
+        <v>581.0252119959074</v>
       </c>
     </row>
     <row r="275">
@@ -8679,15 +8679,15 @@
         <v>71.23049999999999</v>
       </c>
       <c r="F275" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H275" t="n">
-        <v>215.2126130343853</v>
+        <v>536.8600299106262</v>
       </c>
     </row>
     <row r="276">
@@ -8709,15 +8709,15 @@
         <v>222.122161</v>
       </c>
       <c r="F276" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H276" t="n">
-        <v>193.0481946178191</v>
+        <v>511.7048207086222</v>
       </c>
     </row>
     <row r="277">
@@ -8739,15 +8739,15 @@
         <v>243.76794</v>
       </c>
       <c r="F277" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H277" t="n">
-        <v>190.414855387531</v>
+        <v>510.6325809729246</v>
       </c>
     </row>
     <row r="278">
@@ -8769,15 +8769,15 @@
         <v>59.30860000000001</v>
       </c>
       <c r="F278" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H278" t="n">
-        <v>197.1251076937621</v>
+        <v>562.142259489176</v>
       </c>
     </row>
     <row r="279">
@@ -8799,15 +8799,15 @@
         <v>200.4813</v>
       </c>
       <c r="F279" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H279" t="n">
-        <v>189.8007120211021</v>
+        <v>512.6701910738842</v>
       </c>
     </row>
     <row r="280">
@@ -8829,15 +8829,15 @@
         <v>152.1270185</v>
       </c>
       <c r="F280" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H280" t="n">
-        <v>474.2739396380379</v>
+        <v>1044.817507221502</v>
       </c>
     </row>
     <row r="281">
@@ -8859,15 +8859,15 @@
         <v>100.023278</v>
       </c>
       <c r="F281" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H281" t="n">
-        <v>106.1462563154388</v>
+        <v>577.4516136517115</v>
       </c>
     </row>
     <row r="282">
@@ -8889,15 +8889,15 @@
         <v>65.61912249999999</v>
       </c>
       <c r="F282" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H282" t="n">
-        <v>189.5541092308563</v>
+        <v>516.5020371147132</v>
       </c>
     </row>
     <row r="283">
@@ -8919,15 +8919,15 @@
         <v>59.61479999999999</v>
       </c>
       <c r="F283" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H283" t="n">
-        <v>297.7463062317671</v>
+        <v>555.6912913684956</v>
       </c>
     </row>
     <row r="284">
@@ -8949,15 +8949,15 @@
         <v>92.10120000000001</v>
       </c>
       <c r="F284" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H284" t="n">
-        <v>295.1508308036504</v>
+        <v>557.0309337825607</v>
       </c>
     </row>
     <row r="285">
@@ -8979,15 +8979,15 @@
         <v>87.2212</v>
       </c>
       <c r="F285" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H285" t="n">
-        <v>195.2004775661288</v>
+        <v>515.1266831373199</v>
       </c>
     </row>
     <row r="286">
@@ -9009,15 +9009,15 @@
         <v>44.383</v>
       </c>
       <c r="F286" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H286" t="n">
-        <v>198.792485816512</v>
+        <v>581.1236556189809</v>
       </c>
     </row>
     <row r="287">
@@ -9039,15 +9039,15 @@
         <v>72.4555</v>
       </c>
       <c r="F287" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H287" t="n">
-        <v>211.7593814876636</v>
+        <v>553.5205715866714</v>
       </c>
     </row>
     <row r="288">
@@ -9069,15 +9069,15 @@
         <v>228.606</v>
       </c>
       <c r="F288" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H288" t="n">
-        <v>409.3578444052795</v>
+        <v>807.3513364050648</v>
       </c>
     </row>
     <row r="289">
@@ -9099,15 +9099,15 @@
         <v>106.680992</v>
       </c>
       <c r="F289" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H289" t="n">
-        <v>390.9140081015669</v>
+        <v>962.5966753539426</v>
       </c>
     </row>
     <row r="290">
@@ -9129,15 +9129,15 @@
         <v>118.29098</v>
       </c>
       <c r="F290" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H290" t="n">
-        <v>260.0725060296554</v>
+        <v>195.8294926826765</v>
       </c>
     </row>
     <row r="291">
@@ -9159,15 +9159,15 @@
         <v>56.55883999999998</v>
       </c>
       <c r="F291" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H291" t="n">
-        <v>478.6929063561986</v>
+        <v>537.9737707618008</v>
       </c>
     </row>
     <row r="292">
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>317.4733968405083</v>
+        <v>325.7527379481806</v>
       </c>
     </row>
     <row r="293">
@@ -9219,15 +9219,15 @@
         <v>76.35709999999999</v>
       </c>
       <c r="F293" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H293" t="n">
-        <v>174.1455252776595</v>
+        <v>213.6074034689326</v>
       </c>
     </row>
     <row r="294">
@@ -9249,15 +9249,15 @@
         <v>65.98963999999999</v>
       </c>
       <c r="F294" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H294" t="n">
-        <v>483.6949449878604</v>
+        <v>536.0748695206678</v>
       </c>
     </row>
     <row r="295">
@@ -9279,15 +9279,15 @@
         <v>70.17684000000001</v>
       </c>
       <c r="F295" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H295" t="n">
-        <v>395.2279755294658</v>
+        <v>374.8062599792478</v>
       </c>
     </row>
     <row r="296">
@@ -9309,15 +9309,15 @@
         <v>80.12326000000002</v>
       </c>
       <c r="F296" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H296" t="n">
-        <v>139.904278070824</v>
+        <v>66.89312229177543</v>
       </c>
     </row>
     <row r="297">
@@ -9339,15 +9339,15 @@
         <v>73.27007999999999</v>
       </c>
       <c r="F297" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H297" t="n">
-        <v>518.017243909774</v>
+        <v>497.6277549216953</v>
       </c>
     </row>
     <row r="298">
@@ -9369,15 +9369,15 @@
         <v>113.30992</v>
       </c>
       <c r="F298" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H298" t="n">
-        <v>171.8836861734805</v>
+        <v>123.1188905675009</v>
       </c>
     </row>
     <row r="299">
@@ -9399,15 +9399,15 @@
         <v>43.52612</v>
       </c>
       <c r="F299" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H299" t="n">
-        <v>305.6066734773577</v>
+        <v>627.4253330784752</v>
       </c>
     </row>
     <row r="300">
@@ -9429,15 +9429,15 @@
         <v>108.32342</v>
       </c>
       <c r="F300" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H300" t="n">
-        <v>145.1818212920968</v>
+        <v>61.47167162779635</v>
       </c>
     </row>
     <row r="301">
@@ -9459,15 +9459,15 @@
         <v>51.79328</v>
       </c>
       <c r="F301" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H301" t="n">
-        <v>419.036129462474</v>
+        <v>597.7896412243185</v>
       </c>
     </row>
     <row r="302">
@@ -9489,15 +9489,15 @@
         <v>68.9781</v>
       </c>
       <c r="F302" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H302" t="n">
-        <v>407.1102990416741</v>
+        <v>615.8969959031837</v>
       </c>
     </row>
     <row r="303">
@@ -9519,15 +9519,15 @@
         <v>69.73756</v>
       </c>
       <c r="F303" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H303" t="n">
-        <v>295.353133364184</v>
+        <v>616.3496102117134</v>
       </c>
     </row>
     <row r="304">
@@ -9549,15 +9549,15 @@
         <v>116.13984</v>
       </c>
       <c r="F304" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H304" t="n">
-        <v>302.21659388239</v>
+        <v>618.4095869413236</v>
       </c>
     </row>
     <row r="305">
@@ -9579,15 +9579,15 @@
         <v>100.22104</v>
       </c>
       <c r="F305" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H305" t="n">
-        <v>299.2683693566714</v>
+        <v>616.0961971153129</v>
       </c>
     </row>
     <row r="306">
@@ -9609,15 +9609,15 @@
         <v>124.95866</v>
       </c>
       <c r="F306" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H306" t="n">
-        <v>265.2849324520069</v>
+        <v>200.2053993384051</v>
       </c>
     </row>
     <row r="307">
@@ -9639,15 +9639,15 @@
         <v>106.6222</v>
       </c>
       <c r="F307" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H307" t="n">
-        <v>234.1539906552349</v>
+        <v>271.365017209034</v>
       </c>
     </row>
     <row r="308">
@@ -9669,15 +9669,15 @@
         <v>37.92908</v>
       </c>
       <c r="F308" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H308" t="n">
-        <v>137.9645027339064</v>
+        <v>62.69887471408907</v>
       </c>
     </row>
     <row r="309">
@@ -9699,15 +9699,15 @@
         <v>76.79181999999999</v>
       </c>
       <c r="F309" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H309" t="n">
-        <v>213.5800407661942</v>
+        <v>573.8387765074733</v>
       </c>
     </row>
     <row r="310">
@@ -9729,15 +9729,15 @@
         <v>47.35968</v>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H310" t="n">
-        <v>505.864554707247</v>
+        <v>485.7432394022453</v>
       </c>
     </row>
     <row r="311">
@@ -9759,15 +9759,15 @@
         <v>153.85138</v>
       </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H311" t="n">
-        <v>140.4766831106095</v>
+        <v>66.0268932691002</v>
       </c>
     </row>
     <row r="312">
@@ -9789,15 +9789,15 @@
         <v>178.5294</v>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H312" t="n">
-        <v>263.2808293594302</v>
+        <v>198.7592680572442</v>
       </c>
     </row>
     <row r="313">
@@ -9819,15 +9819,15 @@
         <v>138.3113</v>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H313" t="n">
-        <v>146.8970220930177</v>
+        <v>63.30485937058388</v>
       </c>
     </row>
     <row r="314">
@@ -9849,15 +9849,15 @@
         <v>148.35608</v>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H314" t="n">
-        <v>252.0220765832538</v>
+        <v>171.2780401337388</v>
       </c>
     </row>
     <row r="315">
@@ -9879,15 +9879,15 @@
         <v>137.84592</v>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H315" t="n">
-        <v>290.8446586327354</v>
+        <v>207.2118431361766</v>
       </c>
     </row>
     <row r="316">
@@ -9909,15 +9909,15 @@
         <v>71.19014000000001</v>
       </c>
       <c r="F316" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H316" t="n">
-        <v>419.8748338969282</v>
+        <v>596.9053902497836</v>
       </c>
     </row>
     <row r="317">
@@ -9939,15 +9939,15 @@
         <v>106.50236</v>
       </c>
       <c r="F317" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H317" t="n">
-        <v>202.3745627430987</v>
+        <v>121.7310041555266</v>
       </c>
     </row>
     <row r="318">
@@ -9969,15 +9969,15 @@
         <v>97.77134</v>
       </c>
       <c r="F318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H318" t="n">
-        <v>131.3767754580934</v>
+        <v>49.89652576347511</v>
       </c>
     </row>
     <row r="319">
@@ -9999,15 +9999,15 @@
         <v>80.68743999999998</v>
       </c>
       <c r="F319" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H319" t="n">
-        <v>405.4616480532131</v>
+        <v>617.4279070361644</v>
       </c>
     </row>
     <row r="320">
@@ -10029,15 +10029,15 @@
         <v>92.23769999999999</v>
       </c>
       <c r="F320" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H320" t="n">
-        <v>257.7202175042919</v>
+        <v>575.0112439592498</v>
       </c>
     </row>
     <row r="321">
@@ -10059,15 +10059,15 @@
         <v>111.7828</v>
       </c>
       <c r="F321" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H321" t="n">
-        <v>299.2069770829289</v>
+        <v>619.2269057530879</v>
       </c>
     </row>
     <row r="322">
@@ -10089,15 +10089,15 @@
         <v>120.6901</v>
       </c>
       <c r="F322" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H322" t="n">
-        <v>225.2118983559744</v>
+        <v>167.0822270632482</v>
       </c>
     </row>
     <row r="323">
@@ -10119,15 +10119,15 @@
         <v>51.7548</v>
       </c>
       <c r="F323" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H323" t="n">
-        <v>233.1156151535796</v>
+        <v>270.1330052516413</v>
       </c>
     </row>
     <row r="324">
@@ -10149,15 +10149,15 @@
         <v>162.11432</v>
       </c>
       <c r="F324" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H324" t="n">
-        <v>174.6437031880509</v>
+        <v>123.9640433675536</v>
       </c>
     </row>
     <row r="325">
@@ -10179,15 +10179,15 @@
         <v>70.43834</v>
       </c>
       <c r="F325" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H325" t="n">
-        <v>258.0969226234916</v>
+        <v>185.6342827243591</v>
       </c>
     </row>
     <row r="326">
@@ -10209,15 +10209,15 @@
         <v>97.17318</v>
       </c>
       <c r="F326" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H326" t="n">
-        <v>143.4559287228808</v>
+        <v>59.72511885034409</v>
       </c>
     </row>
     <row r="327">
@@ -10239,15 +10239,15 @@
         <v>96.64926</v>
       </c>
       <c r="F327" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H327" t="n">
-        <v>298.5405184854939</v>
+        <v>614.1876446764838</v>
       </c>
     </row>
     <row r="328">
@@ -10269,15 +10269,15 @@
         <v>136.70414</v>
       </c>
       <c r="F328" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H328" t="n">
-        <v>291.9125166681933</v>
+        <v>607.6027114558465</v>
       </c>
     </row>
     <row r="329">
@@ -10299,15 +10299,15 @@
         <v>55.98389999999999</v>
       </c>
       <c r="F329" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H329" t="n">
-        <v>201.6634020843782</v>
+        <v>241.5798000792561</v>
       </c>
     </row>
     <row r="330">
@@ -10329,15 +10329,15 @@
         <v>57.27579999999999</v>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H330" t="n">
-        <v>187.3472114739193</v>
+        <v>218.3636872097339</v>
       </c>
     </row>
     <row r="331">
@@ -10359,15 +10359,15 @@
         <v>100.51814</v>
       </c>
       <c r="F331" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H331" t="n">
-        <v>306.1498650987936</v>
+        <v>626.661873619375</v>
       </c>
     </row>
     <row r="332">
@@ -10389,15 +10389,15 @@
         <v>72.68213999999999</v>
       </c>
       <c r="F332" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H332" t="n">
-        <v>240.6553957539271</v>
+        <v>533.6077234554629</v>
       </c>
     </row>
     <row r="333">
@@ -10419,15 +10419,15 @@
         <v>53.00724</v>
       </c>
       <c r="F333" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H333" t="n">
-        <v>305.5297858281983</v>
+        <v>623.878251310231</v>
       </c>
     </row>
     <row r="334">
@@ -10449,15 +10449,15 @@
         <v>84.78078000000001</v>
       </c>
       <c r="F334" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H334" t="n">
-        <v>265.5314730786209</v>
+        <v>201.3426454253737</v>
       </c>
     </row>
     <row r="335">
@@ -10479,15 +10479,15 @@
         <v>97.36683999999997</v>
       </c>
       <c r="F335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H335" t="n">
-        <v>115.8620035916273</v>
+        <v>103.1380002652348</v>
       </c>
     </row>
     <row r="336">
@@ -10509,15 +10509,15 @@
         <v>81.07180000000001</v>
       </c>
       <c r="F336" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H336" t="n">
-        <v>325.2162572181462</v>
+        <v>256.7168714137835</v>
       </c>
     </row>
     <row r="337">
@@ -10539,15 +10539,15 @@
         <v>51.87629999999999</v>
       </c>
       <c r="F337" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H337" t="n">
-        <v>176.0201727541978</v>
+        <v>95.76639060961472</v>
       </c>
     </row>
     <row r="338">
@@ -10569,15 +10569,15 @@
         <v>164.81286</v>
       </c>
       <c r="F338" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H338" t="n">
-        <v>242.8334230268776</v>
+        <v>260.3496983421461</v>
       </c>
     </row>
     <row r="339">
@@ -10599,15 +10599,15 @@
         <v>137.11044</v>
       </c>
       <c r="F339" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H339" t="n">
-        <v>262.5364558361898</v>
+        <v>339.5078169732922</v>
       </c>
     </row>
     <row r="340">
@@ -10629,15 +10629,15 @@
         <v>105.60097665</v>
       </c>
       <c r="F340" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H340" t="n">
-        <v>244.4815171214456</v>
+        <v>268.4852574352886</v>
       </c>
     </row>
     <row r="341">
@@ -10659,15 +10659,15 @@
         <v>85.30447965</v>
       </c>
       <c r="F341" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H341" t="n">
-        <v>249.0720943022942</v>
+        <v>246.0994041861252</v>
       </c>
     </row>
     <row r="342">
@@ -10689,15 +10689,15 @@
         <v>105.13692</v>
       </c>
       <c r="F342" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H342" t="n">
-        <v>130.0982456924606</v>
+        <v>244.0803400677385</v>
       </c>
     </row>
     <row r="343">
@@ -10719,15 +10719,15 @@
         <v>119.39315505</v>
       </c>
       <c r="F343" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H343" t="n">
-        <v>244.7649577139401</v>
+        <v>265.1235430500931</v>
       </c>
     </row>
     <row r="344">
@@ -10749,15 +10749,15 @@
         <v>135.2097</v>
       </c>
       <c r="F344" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H344" t="n">
-        <v>170.4849151475579</v>
+        <v>220.5164664270967</v>
       </c>
     </row>
     <row r="345">
@@ -10779,15 +10779,15 @@
         <v>103.2224895</v>
       </c>
       <c r="F345" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H345" t="n">
-        <v>247.3589627515343</v>
+        <v>266.4253604948988</v>
       </c>
     </row>
     <row r="346">
@@ -10809,15 +10809,15 @@
         <v>105.68844</v>
       </c>
       <c r="F346" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H346" t="n">
-        <v>250.7518419947306</v>
+        <v>262.1499381849978</v>
       </c>
     </row>
     <row r="347">
@@ -10839,15 +10839,15 @@
         <v>92.92085999999999</v>
       </c>
       <c r="F347" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H347" t="n">
-        <v>245.2020554131428</v>
+        <v>256.6376844413774</v>
       </c>
     </row>
     <row r="348">
@@ -10869,15 +10869,15 @@
         <v>105.6147144</v>
       </c>
       <c r="F348" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H348" t="n">
-        <v>247.1939855447183</v>
+        <v>272.121281660024</v>
       </c>
     </row>
     <row r="349">
@@ -10899,15 +10899,15 @@
         <v>96.36005999999999</v>
       </c>
       <c r="F349" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H349" t="n">
-        <v>248.9481718440073</v>
+        <v>123.9955394119936</v>
       </c>
     </row>
     <row r="350">
@@ -10929,15 +10929,15 @@
         <v>81.90635999999998</v>
       </c>
       <c r="F350" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H350" t="n">
-        <v>262.8258537407512</v>
+        <v>338.753579945603</v>
       </c>
     </row>
     <row r="351">
@@ -10959,15 +10959,15 @@
         <v>103.29378</v>
       </c>
       <c r="F351" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H351" t="n">
-        <v>243.9905079930992</v>
+        <v>244.9481478563077</v>
       </c>
     </row>
     <row r="352">
@@ -10989,15 +10989,15 @@
         <v>69.66414</v>
       </c>
       <c r="F352" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H352" t="n">
-        <v>245.7263957483557</v>
+        <v>128.1288650973908</v>
       </c>
     </row>
     <row r="353">
@@ -11019,15 +11019,15 @@
         <v>133.07976</v>
       </c>
       <c r="F353" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H353" t="n">
-        <v>241.3758450983825</v>
+        <v>270.1477232966168</v>
       </c>
     </row>
     <row r="354">
@@ -11049,15 +11049,15 @@
         <v>99.53225999999999</v>
       </c>
       <c r="F354" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H354" t="n">
-        <v>173.6480917764453</v>
+        <v>224.5097660238579</v>
       </c>
     </row>
     <row r="355">
@@ -11079,15 +11079,15 @@
         <v>174.81366</v>
       </c>
       <c r="F355" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H355" t="n">
-        <v>255.3696671481475</v>
+        <v>319.9119139195989</v>
       </c>
     </row>
     <row r="356">
@@ -11109,15 +11109,15 @@
         <v>123.87336</v>
       </c>
       <c r="F356" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H356" t="n">
-        <v>245.2199955591135</v>
+        <v>127.30602726443</v>
       </c>
     </row>
     <row r="357">
@@ -11139,15 +11139,15 @@
         <v>147.74808</v>
       </c>
       <c r="F357" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H357" t="n">
-        <v>127.1680167975757</v>
+        <v>247.0030921458697</v>
       </c>
     </row>
     <row r="358">
@@ -11169,15 +11169,15 @@
         <v>148.73862</v>
       </c>
       <c r="F358" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H358" t="n">
-        <v>251.8859543154234</v>
+        <v>245.8723846358603</v>
       </c>
     </row>
     <row r="359">
@@ -11199,15 +11199,15 @@
         <v>273.06534</v>
       </c>
       <c r="F359" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H359" t="n">
-        <v>244.6616573423616</v>
+        <v>259.1175712553428</v>
       </c>
     </row>
     <row r="360">
@@ -11229,15 +11229,15 @@
         <v>108.07158</v>
       </c>
       <c r="F360" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H360" t="n">
-        <v>242.2130875979642</v>
+        <v>267.5215536520797</v>
       </c>
     </row>
     <row r="361">
@@ -11259,15 +11259,15 @@
         <v>154.62948</v>
       </c>
       <c r="F361" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H361" t="n">
-        <v>184.1323231692768</v>
+        <v>394.2085802884727</v>
       </c>
     </row>
     <row r="362">
@@ -11289,15 +11289,15 @@
         <v>133.61611575</v>
       </c>
       <c r="F362" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H362" t="n">
-        <v>247.2555998483565</v>
+        <v>269.2177499230888</v>
       </c>
     </row>
     <row r="363">
@@ -11319,15 +11319,15 @@
         <v>107.2794</v>
       </c>
       <c r="F363" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H363" t="n">
-        <v>248.2500861193687</v>
+        <v>265.7120377715198</v>
       </c>
     </row>
     <row r="364">
@@ -11349,15 +11349,15 @@
         <v>90.89004</v>
       </c>
       <c r="F364" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H364" t="n">
-        <v>238.6138624870473</v>
+        <v>272.0407614309759</v>
       </c>
     </row>
     <row r="365">
@@ -11379,15 +11379,15 @@
         <v>65.39706</v>
       </c>
       <c r="F365" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H365" t="n">
-        <v>248.2464578486703</v>
+        <v>267.1609274923284</v>
       </c>
     </row>
     <row r="366">
@@ -11409,15 +11409,15 @@
         <v>93.90606000000002</v>
       </c>
       <c r="F366" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H366" t="n">
-        <v>251.572927532271</v>
+        <v>119.9739091585612</v>
       </c>
     </row>
     <row r="367">
@@ -11439,15 +11439,15 @@
         <v>102.0003</v>
       </c>
       <c r="F367" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H367" t="n">
-        <v>230.4299203347763</v>
+        <v>393.9184922121719</v>
       </c>
     </row>
     <row r="368">
@@ -11469,15 +11469,15 @@
         <v>69.34979999999999</v>
       </c>
       <c r="F368" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H368" t="n">
-        <v>230.0711370582394</v>
+        <v>283.3056721743233</v>
       </c>
     </row>
     <row r="369">
@@ -11499,15 +11499,15 @@
         <v>147.48796146</v>
       </c>
       <c r="F369" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H369" t="n">
-        <v>66.73815255783093</v>
+        <v>755.4364692614545</v>
       </c>
     </row>
     <row r="370">
@@ -11529,15 +11529,15 @@
         <v>81.62645259999999</v>
       </c>
       <c r="F370" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H370" t="n">
-        <v>34.52345300414044</v>
+        <v>737.0602738658094</v>
       </c>
     </row>
     <row r="371">
@@ -11559,15 +11559,15 @@
         <v>125.7125763</v>
       </c>
       <c r="F371" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H371" t="n">
-        <v>317.946630304663</v>
+        <v>407.9443120675884</v>
       </c>
     </row>
     <row r="372">
@@ -11589,15 +11589,15 @@
         <v>118.30654686</v>
       </c>
       <c r="F372" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H372" t="n">
-        <v>176.6888667503275</v>
+        <v>879.9928298660333</v>
       </c>
     </row>
     <row r="373">
@@ -11619,15 +11619,15 @@
         <v>46.7992934</v>
       </c>
       <c r="F373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H373" t="n">
-        <v>63.09525674037218</v>
+        <v>762.9026211265187</v>
       </c>
     </row>
     <row r="374">
@@ -11649,15 +11649,15 @@
         <v>135.638204</v>
       </c>
       <c r="F374" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H374" t="n">
-        <v>67.88592045568444</v>
+        <v>767.4385075145673</v>
       </c>
     </row>
     <row r="375">
@@ -11679,15 +11679,15 @@
         <v>82.8659857</v>
       </c>
       <c r="F375" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H375" t="n">
-        <v>34.2181840897848</v>
+        <v>737.3593294495913</v>
       </c>
     </row>
     <row r="376">
@@ -11709,15 +11709,15 @@
         <v>105.553257</v>
       </c>
       <c r="F376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H376" t="n">
-        <v>32.70858238462002</v>
+        <v>732.0924029321508</v>
       </c>
     </row>
     <row r="377">
@@ -11739,15 +11739,15 @@
         <v>71.35351295999999</v>
       </c>
       <c r="F377" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H377" t="n">
-        <v>181.5158062914187</v>
+        <v>885.0784624488344</v>
       </c>
     </row>
     <row r="378">
@@ -11769,15 +11769,15 @@
         <v>102.73411212</v>
       </c>
       <c r="F378" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H378" t="n">
-        <v>180.1765995943753</v>
+        <v>883.3096566025587</v>
       </c>
     </row>
     <row r="379">
@@ -11799,15 +11799,15 @@
         <v>128.5971056</v>
       </c>
       <c r="F379" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H379" t="n">
-        <v>35.38984638379532</v>
+        <v>736.889207163484</v>
       </c>
     </row>
     <row r="380">
@@ -11829,15 +11829,15 @@
         <v>62.78045063999999</v>
       </c>
       <c r="F380" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H380" t="n">
-        <v>148.9146243709701</v>
+        <v>844.8787435615096</v>
       </c>
     </row>
     <row r="381">
@@ -11859,15 +11859,15 @@
         <v>109.3731514</v>
       </c>
       <c r="F381" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H381" t="n">
-        <v>292.1082656735446</v>
+        <v>455.5450121192576</v>
       </c>
     </row>
     <row r="382">
@@ -11889,15 +11889,15 @@
         <v>119.1499458</v>
       </c>
       <c r="F382" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H382" t="n">
-        <v>33.3796757686011</v>
+        <v>734.8010227130336</v>
       </c>
     </row>
     <row r="383">
@@ -11919,15 +11919,15 @@
         <v>213.5551645</v>
       </c>
       <c r="F383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H383" t="n">
-        <v>31.90591786876936</v>
+        <v>732.5636727352477</v>
       </c>
     </row>
     <row r="384">
@@ -11949,15 +11949,15 @@
         <v>187.0876349</v>
       </c>
       <c r="F384" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H384" t="n">
-        <v>33.24458419572206</v>
+        <v>735.2834981467736</v>
       </c>
     </row>
     <row r="385">
@@ -11979,15 +11979,15 @@
         <v>149.1235557</v>
       </c>
       <c r="F385" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H385" t="n">
-        <v>63.43243743125071</v>
+        <v>763.5216114415061</v>
       </c>
     </row>
     <row r="386">
@@ -12009,15 +12009,15 @@
         <v>170.141426</v>
       </c>
       <c r="F386" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H386" t="n">
-        <v>293.4508617519292</v>
+        <v>453.3744570574661</v>
       </c>
     </row>
     <row r="387">
@@ -12039,15 +12039,15 @@
         <v>168.952343</v>
       </c>
       <c r="F387" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H387" t="n">
-        <v>37.08142664821583</v>
+        <v>739.4024454744151</v>
       </c>
     </row>
     <row r="388">
@@ -12069,15 +12069,15 @@
         <v>107.310147</v>
       </c>
       <c r="F388" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H388" t="n">
-        <v>29.33806901372546</v>
+        <v>728.3554642433388</v>
       </c>
     </row>
     <row r="389">
@@ -12099,15 +12099,15 @@
         <v>111.302101</v>
       </c>
       <c r="F389" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H389" t="n">
-        <v>28.37001636872408</v>
+        <v>728.7075752636654</v>
       </c>
     </row>
     <row r="390">
@@ -12129,15 +12129,15 @@
         <v>77.23364369999999</v>
       </c>
       <c r="F390" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H390" t="n">
-        <v>39.11561759641163</v>
+        <v>738.2112070147015</v>
       </c>
     </row>
     <row r="391">
@@ -12159,15 +12159,15 @@
         <v>53.22112451999999</v>
       </c>
       <c r="F391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H391" t="n">
-        <v>203.8019484784353</v>
+        <v>909.2151633942545</v>
       </c>
     </row>
     <row r="392">
@@ -12189,15 +12189,15 @@
         <v>110.9159485</v>
       </c>
       <c r="F392" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H392" t="n">
-        <v>31.02089893886271</v>
+        <v>730.4862665823251</v>
       </c>
     </row>
     <row r="393">
@@ -12219,15 +12219,15 @@
         <v>95.37692682000001</v>
       </c>
       <c r="F393" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H393" t="n">
-        <v>184.6131265113243</v>
+        <v>887.7534123901355</v>
       </c>
     </row>
     <row r="394">
@@ -12249,15 +12249,15 @@
         <v>54.18531179999999</v>
       </c>
       <c r="F394" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H394" t="n">
-        <v>27.58568935880062</v>
+        <v>725.6101542216179</v>
       </c>
     </row>
     <row r="395">
@@ -12279,15 +12279,15 @@
         <v>111.9413228</v>
       </c>
       <c r="F395" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H395" t="n">
-        <v>30.56895919515435</v>
+        <v>715.8419916078705</v>
       </c>
     </row>
     <row r="396">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>599.7685658275938</v>
+        <v>707.3848536348678</v>
       </c>
     </row>
     <row r="397">
@@ -12339,15 +12339,15 @@
         <v>120.77989</v>
       </c>
       <c r="F397" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H397" t="n">
-        <v>418.910619457074</v>
+        <v>402.8528284779557</v>
       </c>
     </row>
     <row r="398">
@@ -12369,15 +12369,15 @@
         <v>88.73139999999999</v>
       </c>
       <c r="F398" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H398" t="n">
-        <v>395.1452104601061</v>
+        <v>318.7461283580383</v>
       </c>
     </row>
     <row r="399">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>580.0655393103883</v>
+        <v>660.8614547036476</v>
       </c>
     </row>
     <row r="400">
@@ -12429,15 +12429,15 @@
         <v>27.36499</v>
       </c>
       <c r="F400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H400" t="n">
-        <v>419.2014824656533</v>
+        <v>415.0220367356314</v>
       </c>
     </row>
     <row r="401">
@@ -12459,15 +12459,15 @@
         <v>116.77227</v>
       </c>
       <c r="F401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H401" t="n">
-        <v>417.7719448167981</v>
+        <v>404.0941521558714</v>
       </c>
     </row>
     <row r="402">
@@ -12489,15 +12489,15 @@
         <v>75.02567782</v>
       </c>
       <c r="F402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H402" t="n">
-        <v>290.1088194372147</v>
+        <v>531.9172069611084</v>
       </c>
     </row>
     <row r="403">
@@ -12519,15 +12519,15 @@
         <v>59.45515</v>
       </c>
       <c r="F403" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H403" t="n">
-        <v>413.7000010176697</v>
+        <v>408.0188493815209</v>
       </c>
     </row>
     <row r="404">
@@ -12549,15 +12549,15 @@
         <v>126.89930723</v>
       </c>
       <c r="F404" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H404" t="n">
-        <v>286.2644628689006</v>
+        <v>539.6096633611475</v>
       </c>
     </row>
     <row r="405">
@@ -12587,7 +12587,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>596.4055858326795</v>
+        <v>703.1264574838835</v>
       </c>
     </row>
     <row r="406">
@@ -12609,15 +12609,15 @@
         <v>118.61613</v>
       </c>
       <c r="F406" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H406" t="n">
-        <v>667.4815881169878</v>
+        <v>799.0464878757987</v>
       </c>
     </row>
     <row r="407">
@@ -12639,15 +12639,15 @@
         <v>99.67066999999997</v>
       </c>
       <c r="F407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H407" t="n">
-        <v>418.0305093436396</v>
+        <v>403.6412926718086</v>
       </c>
     </row>
     <row r="408">
@@ -12677,7 +12677,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>577.1715434059126</v>
+        <v>658.928053837548</v>
       </c>
     </row>
     <row r="409">
@@ -12699,15 +12699,15 @@
         <v>221.48973368</v>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H409" t="n">
-        <v>291.0608337402675</v>
+        <v>531.1964786528766</v>
       </c>
     </row>
     <row r="410">
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>596.9387958350218</v>
+        <v>702.5680044936581</v>
       </c>
     </row>
     <row r="411">
@@ -12759,15 +12759,15 @@
         <v>12.82508</v>
       </c>
       <c r="F411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H411" t="n">
-        <v>417.601541343521</v>
+        <v>404.3147527355172</v>
       </c>
     </row>
     <row r="412">
@@ -12789,15 +12789,15 @@
         <v>104.69023</v>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H412" t="n">
-        <v>592.2228066044695</v>
+        <v>731.1957182903645</v>
       </c>
     </row>
     <row r="413">
@@ -12819,15 +12819,15 @@
         <v>131.63062668</v>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H413" t="n">
-        <v>316.9706336802632</v>
+        <v>513.4781853654288</v>
       </c>
     </row>
     <row r="414">
@@ -12857,7 +12857,7 @@
         </is>
       </c>
       <c r="H414" t="n">
-        <v>623.8236912874983</v>
+        <v>691.0893860919261</v>
       </c>
     </row>
     <row r="415">
@@ -12879,15 +12879,15 @@
         <v>57.31582</v>
       </c>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H415" t="n">
-        <v>631.3880668617128</v>
+        <v>689.0716245778688</v>
       </c>
     </row>
     <row r="416">
@@ -12909,15 +12909,15 @@
         <v>53.89304</v>
       </c>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H416" t="n">
-        <v>594.4100784430385</v>
+        <v>733.8647042878714</v>
       </c>
     </row>
     <row r="417">
@@ -12947,7 +12947,7 @@
         </is>
       </c>
       <c r="H417" t="n">
-        <v>620.2615824043411</v>
+        <v>687.9706222615004</v>
       </c>
     </row>
     <row r="418">
@@ -12969,15 +12969,15 @@
         <v>44.69123999999999</v>
       </c>
       <c r="F418" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H418" t="n">
-        <v>204.5305974443592</v>
+        <v>471.9688111199325</v>
       </c>
     </row>
     <row r="419">
@@ -13007,7 +13007,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>110.2827409697895</v>
+        <v>392.8925776521635</v>
       </c>
     </row>
     <row r="420">
@@ -13029,15 +13029,15 @@
         <v>30.97999</v>
       </c>
       <c r="F420" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H420" t="n">
-        <v>204.4596365169506</v>
+        <v>468.1659299344697</v>
       </c>
     </row>
     <row r="421">
@@ -13059,15 +13059,15 @@
         <v>38.67852</v>
       </c>
       <c r="F421" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H421" t="n">
-        <v>163.7742200848483</v>
+        <v>437.6301333322829</v>
       </c>
     </row>
     <row r="422">
@@ -13089,15 +13089,15 @@
         <v>22.78917</v>
       </c>
       <c r="F422" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H422" t="n">
-        <v>208.7913962749197</v>
+        <v>469.3464139810218</v>
       </c>
     </row>
     <row r="423">
@@ -13127,7 +13127,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>121.5759418094487</v>
+        <v>404.1736028081135</v>
       </c>
     </row>
     <row r="424">
@@ -13149,15 +13149,15 @@
         <v>125.73253</v>
       </c>
       <c r="F424" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H424" t="n">
-        <v>213.2182452585202</v>
+        <v>475.7548095131403</v>
       </c>
     </row>
     <row r="425">
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>176.2503739454197</v>
+        <v>374.4568889247058</v>
       </c>
     </row>
     <row r="426">
@@ -13209,15 +13209,15 @@
         <v>144.26477</v>
       </c>
       <c r="F426" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H426" t="n">
-        <v>231.1188408667959</v>
+        <v>398.5444258603678</v>
       </c>
     </row>
     <row r="427">
@@ -13239,15 +13239,15 @@
         <v>109.89436</v>
       </c>
       <c r="F427" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H427" t="n">
-        <v>213.4509778017186</v>
+        <v>477.6547662961582</v>
       </c>
     </row>
     <row r="428">
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>181.948223952247</v>
+        <v>372.3583100653588</v>
       </c>
     </row>
     <row r="429">
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>94.86397367730432</v>
+        <v>376.8661815300433</v>
       </c>
     </row>
     <row r="430">
@@ -13337,7 +13337,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>100.5714524373624</v>
+        <v>382.8441201566035</v>
       </c>
     </row>
     <row r="431">
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>48.39588948557887</v>
+        <v>330.9711404490843</v>
       </c>
     </row>
     <row r="432">
@@ -13389,15 +13389,15 @@
         <v>49.8474</v>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H432" t="n">
-        <v>463.4459507527332</v>
+        <v>396.4694872636811</v>
       </c>
     </row>
     <row r="433">
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>433.5621327582323</v>
+        <v>548.1075770880702</v>
       </c>
     </row>
     <row r="434">
@@ -13449,15 +13449,15 @@
         <v>138.73463</v>
       </c>
       <c r="F434" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H434" t="n">
-        <v>229.0852832585927</v>
+        <v>338.3448745348402</v>
       </c>
     </row>
     <row r="435">
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>172.6159711788848</v>
+        <v>364.9139797676369</v>
       </c>
     </row>
     <row r="436">
@@ -13517,7 +13517,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>117.7951780549381</v>
+        <v>400.3918586212197</v>
       </c>
     </row>
     <row r="437">
@@ -13547,7 +13547,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>97.45745982829436</v>
+        <v>379.8599159448746</v>
       </c>
     </row>
     <row r="438">
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>101.481381795035</v>
+        <v>383.8761460419659</v>
       </c>
     </row>
     <row r="439">
@@ -13599,15 +13599,15 @@
         <v>95.54351964</v>
       </c>
       <c r="F439" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H439" t="n">
-        <v>510.997654198796</v>
+        <v>523.1538446003622</v>
       </c>
     </row>
     <row r="440">
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>429.4902768901852</v>
+        <v>540.4447070157765</v>
       </c>
     </row>
     <row r="441">
@@ -13667,7 +13667,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>260.2853585002077</v>
+        <v>541.063100766626</v>
       </c>
     </row>
     <row r="442">
@@ -13697,7 +13697,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>208.5962880424154</v>
+        <v>361.7951034920814</v>
       </c>
     </row>
     <row r="443">
@@ -13727,7 +13727,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>98.25808763279977</v>
+        <v>379.865662713909</v>
       </c>
     </row>
     <row r="444">
@@ -13749,15 +13749,15 @@
         <v>86.38211000000001</v>
       </c>
       <c r="F444" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H444" t="n">
-        <v>208.4277253435319</v>
+        <v>472.3741090501651</v>
       </c>
     </row>
     <row r="445">
@@ -13779,15 +13779,15 @@
         <v>90.25793999999999</v>
       </c>
       <c r="F445" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H445" t="n">
-        <v>212.3386261781216</v>
+        <v>478.0656556116565</v>
       </c>
     </row>
     <row r="446">
@@ -13809,15 +13809,15 @@
         <v>142.70429</v>
       </c>
       <c r="F446" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H446" t="n">
-        <v>209.6504118209775</v>
+        <v>470.8794772176558</v>
       </c>
     </row>
     <row r="447">
@@ -13847,7 +13847,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>182.7667459903581</v>
+        <v>376.3643359901362</v>
       </c>
     </row>
     <row r="448">
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>423.5769488863627</v>
+        <v>539.3000932963816</v>
       </c>
     </row>
     <row r="449">
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>95.67790461919937</v>
+        <v>377.8027639282422</v>
       </c>
     </row>
     <row r="450">
@@ -13929,15 +13929,15 @@
         <v>81.9524</v>
       </c>
       <c r="F450" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H450" t="n">
-        <v>484.1532863787845</v>
+        <v>423.1133016556792</v>
       </c>
     </row>
     <row r="451">
@@ -13959,15 +13959,15 @@
         <v>129.72508</v>
       </c>
       <c r="F451" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H451" t="n">
-        <v>228.5218675824255</v>
+        <v>398.4308918550063</v>
       </c>
     </row>
     <row r="452">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>102.6353178628117</v>
+        <v>384.5226986211789</v>
       </c>
     </row>
     <row r="453">
@@ -14019,15 +14019,15 @@
         <v>137.67475</v>
       </c>
       <c r="F453" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H453" t="n">
-        <v>301.0507133735346</v>
+        <v>289.6683614717405</v>
       </c>
     </row>
     <row r="454">
@@ -14049,15 +14049,15 @@
         <v>91.25033126999999</v>
       </c>
       <c r="F454" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H454" t="n">
-        <v>386.2146034980639</v>
+        <v>476.671625154577</v>
       </c>
     </row>
     <row r="455">
@@ -14087,7 +14087,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>97.23843853479993</v>
+        <v>379.2930854802572</v>
       </c>
     </row>
     <row r="456">
@@ -14117,7 +14117,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>102.4918480857375</v>
+        <v>384.8164371505356</v>
       </c>
     </row>
     <row r="457">
@@ -14139,15 +14139,15 @@
         <v>33.4468</v>
       </c>
       <c r="F457" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H457" t="n">
-        <v>207.4009137645875</v>
+        <v>471.1318091223583</v>
       </c>
     </row>
     <row r="458">
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>428.9279411296831</v>
+        <v>544.1825747253724</v>
       </c>
     </row>
     <row r="459">
@@ -14199,15 +14199,15 @@
         <v>99.37579999999998</v>
       </c>
       <c r="F459" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H459" t="n">
-        <v>229.5591365467445</v>
+        <v>399.465320450838</v>
       </c>
     </row>
     <row r="460">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>175.6247251323167</v>
+        <v>369.0119065625322</v>
       </c>
     </row>
     <row r="461">
@@ -14267,7 +14267,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>175.3296764752763</v>
+        <v>370.650238082961</v>
       </c>
     </row>
     <row r="462">
@@ -14297,7 +14297,7 @@
         </is>
       </c>
       <c r="H462" t="n">
-        <v>51.09998502013926</v>
+        <v>333.6557619236073</v>
       </c>
     </row>
     <row r="463">
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>99.97599824829125</v>
+        <v>382.0640370627376</v>
       </c>
     </row>
     <row r="464">
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>168.7811319371953</v>
+        <v>362.2230741759088</v>
       </c>
     </row>
     <row r="465">
@@ -14379,15 +14379,15 @@
         <v>97.37148000000001</v>
       </c>
       <c r="F465" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H465" t="n">
-        <v>211.6732813870892</v>
+        <v>474.2378592001739</v>
       </c>
     </row>
     <row r="466">
@@ -14409,15 +14409,15 @@
         <v>130.5938</v>
       </c>
       <c r="F466" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H466" t="n">
-        <v>232.6220725104062</v>
+        <v>401.665465879754</v>
       </c>
     </row>
     <row r="467">
@@ -14447,7 +14447,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>100.092607826785</v>
+        <v>382.3170143239886</v>
       </c>
     </row>
     <row r="468">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>96.94585824993405</v>
+        <v>379.0448476203267</v>
       </c>
     </row>
     <row r="469">
@@ -14507,7 +14507,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>178.0547726996159</v>
+        <v>374.9042615607714</v>
       </c>
     </row>
     <row r="470">
@@ -14529,15 +14529,15 @@
         <v>123.36434</v>
       </c>
       <c r="F470" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H470" t="n">
-        <v>209.6007710482695</v>
+        <v>473.324159641636</v>
       </c>
     </row>
     <row r="471">
@@ -14559,15 +14559,15 @@
         <v>173.58828</v>
       </c>
       <c r="F471" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H471" t="n">
-        <v>217.769738655443</v>
+        <v>480.2135545670378</v>
       </c>
     </row>
     <row r="472">
@@ -14597,7 +14597,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>102.700602997662</v>
+        <v>385.2222955395411</v>
       </c>
     </row>
     <row r="473">
@@ -14627,7 +14627,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>172.7706883374275</v>
+        <v>367.3860009118215</v>
       </c>
     </row>
     <row r="474">
@@ -14657,7 +14657,7 @@
         </is>
       </c>
       <c r="H474" t="n">
-        <v>429.3340900803877</v>
+        <v>542.1827885381606</v>
       </c>
     </row>
     <row r="475">
@@ -14687,7 +14687,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>99.365783649566</v>
+        <v>381.8848835748896</v>
       </c>
     </row>
     <row r="476">
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>426.3835440125061</v>
+        <v>538.5790438625913</v>
       </c>
     </row>
     <row r="477">
@@ -14747,7 +14747,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>178.0194198959729</v>
+        <v>368.6459573800726</v>
       </c>
     </row>
     <row r="478">
@@ -14769,15 +14769,15 @@
         <v>115.35392</v>
       </c>
       <c r="F478" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H478" t="n">
-        <v>208.9435669676058</v>
+        <v>474.7514143995931</v>
       </c>
     </row>
     <row r="479">
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>178.8457234807114</v>
+        <v>373.9469958264402</v>
       </c>
     </row>
     <row r="480">
@@ -14837,7 +14837,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>107.3145602966586</v>
+        <v>389.8667975757295</v>
       </c>
     </row>
     <row r="481">
@@ -14867,7 +14867,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>78.34448568653632</v>
+        <v>356.9198182307821</v>
       </c>
     </row>
     <row r="482">
@@ -14889,15 +14889,15 @@
         <v>133.14993041</v>
       </c>
       <c r="F482" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H482" t="n">
-        <v>494.2465546328309</v>
+        <v>538.4207338192327</v>
       </c>
     </row>
     <row r="483">
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>208.6719006944995</v>
+        <v>486.8211826868632</v>
       </c>
     </row>
     <row r="484">
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>173.0380180324195</v>
+        <v>361.6643405946432</v>
       </c>
     </row>
     <row r="485">
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>306.8243085037814</v>
+        <v>401.930851393678</v>
       </c>
     </row>
     <row r="486">
@@ -15009,15 +15009,15 @@
         <v>175.2077001</v>
       </c>
       <c r="F486" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H486" t="n">
-        <v>509.5008732297528</v>
+        <v>519.2538226536985</v>
       </c>
     </row>
     <row r="487">
@@ -15039,15 +15039,15 @@
         <v>168.87164</v>
       </c>
       <c r="F487" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H487" t="n">
-        <v>163.7335498059527</v>
+        <v>279.902734174244</v>
       </c>
     </row>
     <row r="488">
@@ -15069,15 +15069,15 @@
         <v>66.75664999999999</v>
       </c>
       <c r="F488" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H488" t="n">
-        <v>482.7255904190506</v>
+        <v>421.8829865894261</v>
       </c>
     </row>
     <row r="489">
@@ -15107,7 +15107,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>176.3452400412433</v>
+        <v>369.4452532027314</v>
       </c>
     </row>
     <row r="490">
@@ -15137,7 +15137,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>96.72437721924653</v>
+        <v>378.3849475489089</v>
       </c>
     </row>
     <row r="491">
@@ -15159,15 +15159,15 @@
         <v>89.62715</v>
       </c>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H491" t="n">
-        <v>482.017426840228</v>
+        <v>421.4524250593868</v>
       </c>
     </row>
     <row r="492">
@@ -15189,15 +15189,15 @@
         <v>43.78264999999999</v>
       </c>
       <c r="F492" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H492" t="n">
-        <v>228.9300086027407</v>
+        <v>495.327109267422</v>
       </c>
     </row>
     <row r="493">
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>144.5352295904483</v>
+        <v>357.2115310266433</v>
       </c>
     </row>
     <row r="494">
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>304.1258562519051</v>
+        <v>399.4831107472828</v>
       </c>
     </row>
     <row r="495">
@@ -15287,7 +15287,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>176.328593549544</v>
+        <v>370.8772421201244</v>
       </c>
     </row>
     <row r="496">
@@ -15309,15 +15309,15 @@
         <v>59.60680000000001</v>
       </c>
       <c r="F496" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H496" t="n">
-        <v>345.6396454305997</v>
+        <v>496.2179314352944</v>
       </c>
     </row>
     <row r="497">
@@ -15339,15 +15339,15 @@
         <v>61.33865</v>
       </c>
       <c r="F497" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H497" t="n">
-        <v>204.2468831622038</v>
+        <v>508.6165235388352</v>
       </c>
     </row>
     <row r="498">
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>78.46596702303529</v>
+        <v>320.0585897987742</v>
       </c>
     </row>
     <row r="499">
@@ -15407,7 +15407,7 @@
         </is>
       </c>
       <c r="H499" t="n">
-        <v>38.42670238202552</v>
+        <v>301.6603319138252</v>
       </c>
     </row>
     <row r="500">
@@ -15429,15 +15429,15 @@
         <v>97.11096000000002</v>
       </c>
       <c r="F500" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H500" t="n">
-        <v>228.1579527766796</v>
+        <v>399.3228032090287</v>
       </c>
     </row>
     <row r="501">
@@ -15459,15 +15459,15 @@
         <v>77.12655000000001</v>
       </c>
       <c r="F501" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H501" t="n">
-        <v>229.1174983035737</v>
+        <v>396.5711271812636</v>
       </c>
     </row>
     <row r="502">
@@ -15497,7 +15497,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>121.9724126682299</v>
+        <v>403.9857614874821</v>
       </c>
     </row>
     <row r="503">
@@ -15519,15 +15519,15 @@
         <v>39.40545</v>
       </c>
       <c r="F503" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H503" t="n">
-        <v>229.178044449383</v>
+        <v>399.6670938287053</v>
       </c>
     </row>
     <row r="504">
@@ -15549,15 +15549,15 @@
         <v>51.32812</v>
       </c>
       <c r="F504" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H504" t="n">
-        <v>216.9896041973278</v>
+        <v>429.5073032500679</v>
       </c>
     </row>
     <row r="505">
@@ -15587,7 +15587,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>112.4827109906133</v>
+        <v>394.7884522559071</v>
       </c>
     </row>
   </sheetData>

--- a/clustered_output.xlsx
+++ b/clustered_output.xlsx
@@ -489,15 +489,15 @@
         <v>41.29720544</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>312.3476429270801</v>
+        <v>293.8460057247369</v>
       </c>
     </row>
     <row r="3">
@@ -519,15 +519,15 @@
         <v>55.87958479999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>141.5567884198512</v>
+        <v>122.4928162679067</v>
       </c>
     </row>
     <row r="4">
@@ -549,15 +549,15 @@
         <v>33.26804828</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>375.2133947621184</v>
+        <v>365.5697738719786</v>
       </c>
     </row>
     <row r="5">
@@ -579,15 +579,15 @@
         <v>93.98859224</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>118.9018437587613</v>
+        <v>137.1836921009171</v>
       </c>
     </row>
     <row r="6">
@@ -609,15 +609,15 @@
         <v>40.42737347999999</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>386.3087422339807</v>
+        <v>370.9274282971861</v>
       </c>
     </row>
     <row r="7">
@@ -639,15 +639,15 @@
         <v>63.74664785</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>118.9558925056448</v>
+        <v>135.1668889158399</v>
       </c>
     </row>
     <row r="8">
@@ -669,15 +669,15 @@
         <v>86.27647392</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>328.2730746713401</v>
+        <v>245.074598671275</v>
       </c>
     </row>
     <row r="9">
@@ -699,15 +699,15 @@
         <v>91.16850180000002</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>388.3345797490471</v>
+        <v>304.8226550499002</v>
       </c>
     </row>
     <row r="10">
@@ -729,15 +729,15 @@
         <v>86.99766654</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>485.78077300261</v>
+        <v>466.4283882980909</v>
       </c>
     </row>
     <row r="11">
@@ -759,15 +759,15 @@
         <v>82.87167607000001</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>492.8602485423139</v>
+        <v>472.7473727202855</v>
       </c>
     </row>
     <row r="12">
@@ -789,15 +789,15 @@
         <v>113.41016794</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>133.5075553693926</v>
+        <v>151.0314023786419</v>
       </c>
     </row>
     <row r="13">
@@ -819,15 +819,15 @@
         <v>90.7568601</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>138.8671569739272</v>
+        <v>155.8689391528941</v>
       </c>
     </row>
     <row r="14">
@@ -849,15 +849,15 @@
         <v>129.90572294</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>153.4618793634799</v>
+        <v>170.9279161682704</v>
       </c>
     </row>
     <row r="15">
@@ -879,15 +879,15 @@
         <v>39.66574248000001</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>431.3442798376877</v>
+        <v>413.5495142717604</v>
       </c>
     </row>
     <row r="16">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>424.6636155876099</v>
+        <v>414.1680610379193</v>
       </c>
     </row>
     <row r="17">
@@ -939,15 +939,15 @@
         <v>71.55889309999998</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>139.2049227489753</v>
+        <v>155.8711978103603</v>
       </c>
     </row>
     <row r="18">
@@ -969,15 +969,15 @@
         <v>112.80354775</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>277.9779084992091</v>
+        <v>197.3786891663952</v>
       </c>
     </row>
     <row r="19">
@@ -999,15 +999,15 @@
         <v>73.57074283999999</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>133.0509347923777</v>
+        <v>150.8606934652393</v>
       </c>
     </row>
     <row r="20">
@@ -1029,15 +1029,15 @@
         <v>48.18771840000001</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>168.2999938886427</v>
+        <v>147.942072551742</v>
       </c>
     </row>
     <row r="21">
@@ -1059,15 +1059,15 @@
         <v>137.72677575</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>241.286644854991</v>
+        <v>170.0748304559448</v>
       </c>
     </row>
     <row r="22">
@@ -1089,15 +1089,15 @@
         <v>61.96439013000001</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>254.3489777477395</v>
+        <v>274.7525032714101</v>
       </c>
     </row>
     <row r="23">
@@ -1119,15 +1119,15 @@
         <v>57.01195806</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>439.8981805465693</v>
+        <v>422.7970840515572</v>
       </c>
     </row>
     <row r="24">
@@ -1149,15 +1149,15 @@
         <v>75.03426994</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>114.9129726884635</v>
+        <v>44.80763566563145</v>
       </c>
     </row>
     <row r="25">
@@ -1179,15 +1179,15 @@
         <v>45.991</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>408.5855438226462</v>
+        <v>392.7470920930622</v>
       </c>
     </row>
     <row r="26">
@@ -1209,15 +1209,15 @@
         <v>69.51707707</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>379.9781482388589</v>
+        <v>296.4696464613529</v>
       </c>
     </row>
     <row r="27">
@@ -1239,15 +1239,15 @@
         <v>118.63043667</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>144.8833393517898</v>
+        <v>162.1806222902383</v>
       </c>
     </row>
     <row r="28">
@@ -1269,15 +1269,15 @@
         <v>39.05642559</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>406.3401413649697</v>
+        <v>390.3002980085579</v>
       </c>
     </row>
     <row r="29">
@@ -1299,15 +1299,15 @@
         <v>51.11150699</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>183.7395365549781</v>
+        <v>106.6790260503075</v>
       </c>
     </row>
     <row r="30">
@@ -1329,15 +1329,15 @@
         <v>90.55661511999999</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>280.1001551232182</v>
+        <v>260.1363480138145</v>
       </c>
     </row>
     <row r="31">
@@ -1359,15 +1359,15 @@
         <v>80.49179736000001</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>137.9850073898567</v>
+        <v>156.190021202696</v>
       </c>
     </row>
     <row r="32">
@@ -1389,15 +1389,15 @@
         <v>137.7462625</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>143.1370130472784</v>
+        <v>160.9219624355327</v>
       </c>
     </row>
     <row r="33">
@@ -1419,15 +1419,15 @@
         <v>82.06561287</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>414.6563633974813</v>
+        <v>398.7773663232627</v>
       </c>
     </row>
     <row r="34">
@@ -1449,15 +1449,15 @@
         <v>40.91439332</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>231.6252831067762</v>
+        <v>159.2187052602542</v>
       </c>
     </row>
     <row r="35">
@@ -1479,15 +1479,15 @@
         <v>94.20747311999999</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>141.5202761549733</v>
+        <v>159.2061091161018</v>
       </c>
     </row>
     <row r="36">
@@ -1509,15 +1509,15 @@
         <v>51.34208147000001</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>486.7713001932132</v>
+        <v>467.3803848016624</v>
       </c>
     </row>
     <row r="37">
@@ -1539,15 +1539,15 @@
         <v>89.43269527999999</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>115.9067835773086</v>
+        <v>44.22068792538425</v>
       </c>
     </row>
     <row r="38">
@@ -1569,15 +1569,15 @@
         <v>87.62353223</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>137.8672753703998</v>
+        <v>155.3531487189899</v>
       </c>
     </row>
     <row r="39">
@@ -1599,15 +1599,15 @@
         <v>113.62947597</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>400.3943203558753</v>
+        <v>384.5306082334927</v>
       </c>
     </row>
     <row r="40">
@@ -1629,15 +1629,15 @@
         <v>97.86042042</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>367.7369200108809</v>
+        <v>284.4129910582891</v>
       </c>
     </row>
     <row r="41">
@@ -1659,15 +1659,15 @@
         <v>120.70724466</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>98.15468437307703</v>
+        <v>24.49259868729828</v>
       </c>
     </row>
     <row r="42">
@@ -1689,15 +1689,15 @@
         <v>63.64605510000001</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>249.876798128665</v>
+        <v>230.7789116574628</v>
       </c>
     </row>
     <row r="43">
@@ -1719,15 +1719,15 @@
         <v>79.88549751000001</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>139.6700844491425</v>
+        <v>94.04767826631056</v>
       </c>
     </row>
     <row r="44">
@@ -1749,15 +1749,15 @@
         <v>75.97018895000001</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>392.3383289461026</v>
+        <v>382.7309042653473</v>
       </c>
     </row>
     <row r="45">
@@ -1779,15 +1779,15 @@
         <v>58.83139722999999</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>360.733750681989</v>
+        <v>277.0434321345084</v>
       </c>
     </row>
     <row r="46">
@@ -1809,15 +1809,15 @@
         <v>24.03516849</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>380.3280875652389</v>
+        <v>363.3676583725137</v>
       </c>
     </row>
     <row r="47">
@@ -1839,15 +1839,15 @@
         <v>17.60890872</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>384.2953851204009</v>
+        <v>367.859288993661</v>
       </c>
     </row>
     <row r="48">
@@ -1869,15 +1869,15 @@
         <v>82.63783919000001</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>131.7915489876928</v>
+        <v>148.5993207899491</v>
       </c>
     </row>
     <row r="49">
@@ -1899,15 +1899,15 @@
         <v>56.29949515999999</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>410.0957017648079</v>
+        <v>394.3261874511825</v>
       </c>
     </row>
     <row r="50">
@@ -1929,15 +1929,15 @@
         <v>47.27391910999999</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>486.3552966158776</v>
+        <v>466.862664902199</v>
       </c>
     </row>
     <row r="51">
@@ -1959,15 +1959,15 @@
         <v>55.12580752</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>327.371843717464</v>
+        <v>244.0476712680346</v>
       </c>
     </row>
     <row r="52">
@@ -1989,15 +1989,15 @@
         <v>70.25959358</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>126.6884221680908</v>
+        <v>105.0335556921193</v>
       </c>
     </row>
     <row r="53">
@@ -2019,15 +2019,15 @@
         <v>62.59155026999998</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>93.8415059481957</v>
+        <v>109.7389620112709</v>
       </c>
     </row>
     <row r="54">
@@ -2049,15 +2049,15 @@
         <v>78.94616125999998</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>176.4470644623666</v>
+        <v>108.6104453741741</v>
       </c>
     </row>
     <row r="55">
@@ -2079,15 +2079,15 @@
         <v>101.76988238</v>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>146.7189630432425</v>
+        <v>164.3915028407905</v>
       </c>
     </row>
     <row r="56">
@@ -2109,15 +2109,15 @@
         <v>44.19095989</v>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>481.7271018753432</v>
+        <v>462.2694883273145</v>
       </c>
     </row>
     <row r="57">
@@ -2139,15 +2139,15 @@
         <v>93.80458936000001</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>399.3315282450388</v>
+        <v>378.9423803573275</v>
       </c>
     </row>
     <row r="58">
@@ -2169,15 +2169,15 @@
         <v>49.10406079999999</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>108.7848638752269</v>
+        <v>100.7259767775823</v>
       </c>
     </row>
     <row r="59">
@@ -2199,15 +2199,15 @@
         <v>99.07280474</v>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>147.1540323338647</v>
+        <v>165.351606625248</v>
       </c>
     </row>
     <row r="60">
@@ -2229,15 +2229,15 @@
         <v>69.66181495000001</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>137.4222979025599</v>
+        <v>155.0573123555761</v>
       </c>
     </row>
     <row r="61">
@@ -2259,15 +2259,15 @@
         <v>157.49350527</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>131.6200947203843</v>
+        <v>109.6785426341018</v>
       </c>
     </row>
     <row r="62">
@@ -2289,15 +2289,15 @@
         <v>69.61420304000001</v>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>129.47271130013</v>
+        <v>146.6430460690046</v>
       </c>
     </row>
     <row r="63">
@@ -2319,15 +2319,15 @@
         <v>15.037</v>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>409.142576533964</v>
+        <v>393.1682837749015</v>
       </c>
     </row>
     <row r="64">
@@ -2349,15 +2349,15 @@
         <v>33.56141599999999</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>328.2671538715692</v>
+        <v>245.079558964301</v>
       </c>
     </row>
     <row r="65">
@@ -2379,15 +2379,15 @@
         <v>122.2742197</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>137.775968778899</v>
+        <v>92.73717022738394</v>
       </c>
     </row>
     <row r="66">
@@ -2409,15 +2409,15 @@
         <v>29.31689904</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>382.7725994990877</v>
+        <v>299.3569840336716</v>
       </c>
     </row>
     <row r="67">
@@ -2439,15 +2439,15 @@
         <v>24.08448896</v>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>127.2148671715527</v>
+        <v>144.2270060908566</v>
       </c>
     </row>
     <row r="68">
@@ -2469,15 +2469,15 @@
         <v>59.56919848</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>187.1173891728598</v>
+        <v>103.496349890505</v>
       </c>
     </row>
     <row r="69">
@@ -2499,15 +2499,15 @@
         <v>61.17361757</v>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>75.96318517921419</v>
+        <v>68.27692687408248</v>
       </c>
     </row>
     <row r="70">
@@ -2529,15 +2529,15 @@
         <v>45.19398898999999</v>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>143.1079901005895</v>
+        <v>160.2128384245894</v>
       </c>
     </row>
     <row r="71">
@@ -2559,15 +2559,15 @@
         <v>8.5903492</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>108.7848638752269</v>
+        <v>100.7259767775823</v>
       </c>
     </row>
     <row r="72">
@@ -2589,15 +2589,15 @@
         <v>77.60705583999999</v>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>136.4020147685627</v>
+        <v>153.1285040266745</v>
       </c>
     </row>
     <row r="73">
@@ -2619,15 +2619,15 @@
         <v>27.84522936</v>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>426.8029932126655</v>
+        <v>409.2001225630211</v>
       </c>
     </row>
     <row r="74">
@@ -2649,15 +2649,15 @@
         <v>121.24150382</v>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>134.4832099001436</v>
+        <v>151.6020550227136</v>
       </c>
     </row>
     <row r="75">
@@ -2679,15 +2679,15 @@
         <v>109.77473927</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>124.5019625679025</v>
+        <v>96.58126533093416</v>
       </c>
     </row>
     <row r="76">
@@ -2709,15 +2709,15 @@
         <v>27.96024677</v>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>468.7426850661527</v>
+        <v>450.0229442223006</v>
       </c>
     </row>
     <row r="77">
@@ -2739,15 +2739,15 @@
         <v>127.09983192</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>120.9179947370747</v>
+        <v>103.6119916373755</v>
       </c>
     </row>
     <row r="78">
@@ -2769,15 +2769,15 @@
         <v>40.97559472</v>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>211.1051461597017</v>
+        <v>190.6825132721265</v>
       </c>
     </row>
     <row r="79">
@@ -2799,15 +2799,15 @@
         <v>55.95136335999999</v>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>244.3990735124999</v>
+        <v>223.9844703950944</v>
       </c>
     </row>
     <row r="80">
@@ -2829,15 +2829,15 @@
         <v>99.95687511999999</v>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>151.0245141196881</v>
+        <v>168.4133991841169</v>
       </c>
     </row>
     <row r="81">
@@ -2859,15 +2859,15 @@
         <v>171.25894002</v>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>142.94381580362</v>
+        <v>159.9084196272836</v>
       </c>
     </row>
     <row r="82">
@@ -2889,15 +2889,15 @@
         <v>108.25222513</v>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>138.2916456117689</v>
+        <v>155.1193933778405</v>
       </c>
     </row>
     <row r="83">
@@ -2919,15 +2919,15 @@
         <v>152.37332232</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>130.4725566339279</v>
+        <v>109.7499568719103</v>
       </c>
     </row>
     <row r="84">
@@ -2949,15 +2949,15 @@
         <v>137.64539505</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>128.654547153294</v>
+        <v>103.1628998334891</v>
       </c>
     </row>
     <row r="85">
@@ -2979,15 +2979,15 @@
         <v>98.88650038</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>137.7742062609717</v>
+        <v>93.89827386045394</v>
       </c>
     </row>
     <row r="86">
@@ -3009,15 +3009,15 @@
         <v>174.43258149</v>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>137.1832339917709</v>
+        <v>154.4089620521199</v>
       </c>
     </row>
     <row r="87">
@@ -3039,15 +3039,15 @@
         <v>131.72022438</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>381.4141464317108</v>
+        <v>297.954671485222</v>
       </c>
     </row>
     <row r="88">
@@ -3069,15 +3069,15 @@
         <v>128.67002752</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>328.2324482195975</v>
+        <v>244.9376359487637</v>
       </c>
     </row>
     <row r="89">
@@ -3099,15 +3099,15 @@
         <v>151.83197394</v>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>141.0311183501512</v>
+        <v>158.5499688032886</v>
       </c>
     </row>
     <row r="90">
@@ -3129,15 +3129,15 @@
         <v>70.43858698000003</v>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>141.2722471438568</v>
+        <v>158.4325457480821</v>
       </c>
     </row>
     <row r="91">
@@ -3159,15 +3159,15 @@
         <v>165.86665209</v>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>133.2782084515678</v>
+        <v>150.0773248273609</v>
       </c>
     </row>
     <row r="92">
@@ -3189,15 +3189,15 @@
         <v>160.7944185</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>128.5974961593128</v>
+        <v>111.1930211145544</v>
       </c>
     </row>
     <row r="93">
@@ -3219,15 +3219,15 @@
         <v>114.30460316</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>126.5993037082896</v>
+        <v>103.1395370676297</v>
       </c>
     </row>
     <row r="94">
@@ -3249,15 +3249,15 @@
         <v>27.65862036</v>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>140.2315491170268</v>
+        <v>157.2643207295644</v>
       </c>
     </row>
     <row r="95">
@@ -3279,15 +3279,15 @@
         <v>107.20581291</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>130.3110932076192</v>
+        <v>110.9238212584267</v>
       </c>
     </row>
     <row r="96">
@@ -3309,15 +3309,15 @@
         <v>132.81126806</v>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>136.5442645586296</v>
+        <v>154.3148811061609</v>
       </c>
     </row>
     <row r="97">
@@ -3339,15 +3339,15 @@
         <v>151.87199567</v>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>143.4825259368347</v>
+        <v>160.7866229667267</v>
       </c>
     </row>
     <row r="98">
@@ -3369,15 +3369,15 @@
         <v>97.51930487999999</v>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>135.7900799156238</v>
+        <v>153.2436065110408</v>
       </c>
     </row>
     <row r="99">
@@ -3399,15 +3399,15 @@
         <v>62.68683512</v>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>410.3726253648458</v>
+        <v>394.5056466031788</v>
       </c>
     </row>
     <row r="100">
@@ -3429,15 +3429,15 @@
         <v>164.09465016</v>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>145.7555976740724</v>
+        <v>163.2868500698719</v>
       </c>
     </row>
     <row r="101">
@@ -3459,15 +3459,15 @@
         <v>115.75139108</v>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>132.978317893762</v>
+        <v>150.4724269081669</v>
       </c>
     </row>
     <row r="102">
@@ -3489,15 +3489,15 @@
         <v>112.73454219</v>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>123.4723396428809</v>
+        <v>140.3539978684227</v>
       </c>
     </row>
     <row r="103">
@@ -3519,15 +3519,15 @@
         <v>165.16716377</v>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>131.2088258437179</v>
+        <v>147.6036965257908</v>
       </c>
     </row>
     <row r="104">
@@ -3549,15 +3549,15 @@
         <v>98.30353936999998</v>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>123.8725865372433</v>
+        <v>140.9713963838633</v>
       </c>
     </row>
     <row r="105">
@@ -3579,15 +3579,15 @@
         <v>64.32811749000001</v>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>392.2861529735245</v>
+        <v>382.5222745361521</v>
       </c>
     </row>
     <row r="106">
@@ -3609,15 +3609,15 @@
         <v>143.1621979</v>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>282.7352857594362</v>
+        <v>262.7324413613346</v>
       </c>
     </row>
     <row r="107">
@@ -3639,15 +3639,15 @@
         <v>62.72158742000001</v>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>483.0990667625962</v>
+        <v>463.6203705187395</v>
       </c>
     </row>
     <row r="108">
@@ -3669,15 +3669,15 @@
         <v>135.79601133</v>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>406.0315877170019</v>
+        <v>390.2487772391969</v>
       </c>
     </row>
     <row r="109">
@@ -3699,15 +3699,15 @@
         <v>67.78453388</v>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>136.4895373399047</v>
+        <v>153.539195695105</v>
       </c>
     </row>
     <row r="110">
@@ -3729,15 +3729,15 @@
         <v>135.40894881</v>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>380.8965900937883</v>
+        <v>297.4728206135632</v>
       </c>
     </row>
     <row r="111">
@@ -3759,15 +3759,15 @@
         <v>134.30264618</v>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>140.8386301032752</v>
+        <v>157.7435654334739</v>
       </c>
     </row>
     <row r="112">
@@ -3789,15 +3789,15 @@
         <v>107.39169483</v>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>129.4578906436336</v>
+        <v>146.3339933783038</v>
       </c>
     </row>
     <row r="113">
@@ -3819,15 +3819,15 @@
         <v>92.21966651000001</v>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>133.6366603171619</v>
+        <v>149.9757318464934</v>
       </c>
     </row>
     <row r="114">
@@ -3849,15 +3849,15 @@
         <v>46.65942816</v>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>293.4967601443832</v>
+        <v>275.4336495404298</v>
       </c>
     </row>
     <row r="115">
@@ -3879,15 +3879,15 @@
         <v>61.25313789</v>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>380.9416346172154</v>
+        <v>367.0969959282192</v>
       </c>
     </row>
     <row r="116">
@@ -3909,15 +3909,15 @@
         <v>95.79522047999998</v>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>126.9811181546085</v>
+        <v>143.5474732221657</v>
       </c>
     </row>
     <row r="117">
@@ -3939,15 +3939,15 @@
         <v>131.4488539</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>133.5964249022822</v>
+        <v>106.0711509208065</v>
       </c>
     </row>
     <row r="118">
@@ -3969,15 +3969,15 @@
         <v>139.22461155</v>
       </c>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>140.7173414264341</v>
+        <v>158.0974000785128</v>
       </c>
     </row>
     <row r="119">
@@ -3999,15 +3999,15 @@
         <v>69.87724643999999</v>
       </c>
       <c r="F119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>483.3104400018008</v>
+        <v>463.8843261091552</v>
       </c>
     </row>
     <row r="120">
@@ -4029,15 +4029,15 @@
         <v>26.29534809</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>381.2386282180768</v>
+        <v>297.8104472791561</v>
       </c>
     </row>
     <row r="121">
@@ -4059,15 +4059,15 @@
         <v>124.64185643</v>
       </c>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>144.4670761581502</v>
+        <v>162.1540802945918</v>
       </c>
     </row>
     <row r="122">
@@ -4089,15 +4089,15 @@
         <v>67.21328875</v>
       </c>
       <c r="F122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>133.0423815907709</v>
+        <v>150.4196753751032</v>
       </c>
     </row>
     <row r="123">
@@ -4119,15 +4119,15 @@
         <v>104.41013483</v>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>114.1266628728534</v>
+        <v>40.73116379217367</v>
       </c>
     </row>
     <row r="124">
@@ -4149,15 +4149,15 @@
         <v>55.17039302000001</v>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>134.3485696562654</v>
+        <v>151.2941074551429</v>
       </c>
     </row>
     <row r="125">
@@ -4179,15 +4179,15 @@
         <v>156.16160591</v>
       </c>
       <c r="F125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>120.4872005564761</v>
+        <v>137.6423599800942</v>
       </c>
     </row>
     <row r="126">
@@ -4209,15 +4209,15 @@
         <v>86.21620850000002</v>
       </c>
       <c r="F126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>125.9371768049107</v>
+        <v>141.7442910967588</v>
       </c>
     </row>
     <row r="127">
@@ -4239,15 +4239,15 @@
         <v>71.97972833</v>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>134.3759538513394</v>
+        <v>152.1140732346485</v>
       </c>
     </row>
     <row r="128">
@@ -4269,15 +4269,15 @@
         <v>116.03335498</v>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>131.3698777549343</v>
+        <v>148.417679040193</v>
       </c>
     </row>
     <row r="129">
@@ -4299,15 +4299,15 @@
         <v>87.04857329000001</v>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>137.9526950784186</v>
+        <v>155.2912736366582</v>
       </c>
     </row>
     <row r="130">
@@ -4329,15 +4329,15 @@
         <v>141.72703296</v>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>136.3894994966892</v>
+        <v>153.7467056988309</v>
       </c>
     </row>
     <row r="131">
@@ -4359,15 +4359,15 @@
         <v>145.58214742</v>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>70.25768122189537</v>
+        <v>68.55822665796128</v>
       </c>
     </row>
     <row r="132">
@@ -4389,15 +4389,15 @@
         <v>148.1403535</v>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>49.97972614757656</v>
+        <v>47.08708195175153</v>
       </c>
     </row>
     <row r="133">
@@ -4419,15 +4419,15 @@
         <v>39.35975862000001</v>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>407.7414728579811</v>
+        <v>391.8184530774033</v>
       </c>
     </row>
     <row r="134">
@@ -4449,15 +4449,15 @@
         <v>121.18436646</v>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>140.6749761342152</v>
+        <v>157.8095881689238</v>
       </c>
     </row>
     <row r="135">
@@ -4479,15 +4479,15 @@
         <v>174.54029805</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>242.8897244503717</v>
+        <v>171.5590778179512</v>
       </c>
     </row>
     <row r="136">
@@ -4509,15 +4509,15 @@
         <v>71.22344247000001</v>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>135.8054469712873</v>
+        <v>102.338791598857</v>
       </c>
     </row>
     <row r="137">
@@ -4539,15 +4539,15 @@
         <v>86.91646299999999</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>137.3146338603078</v>
+        <v>105.4461159483704</v>
       </c>
     </row>
     <row r="138">
@@ -4569,15 +4569,15 @@
         <v>113.58351808</v>
       </c>
       <c r="F138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>137.5980426536427</v>
+        <v>154.3020684321744</v>
       </c>
     </row>
     <row r="139">
@@ -4599,15 +4599,15 @@
         <v>130.82707128</v>
       </c>
       <c r="F139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>126.7735021255614</v>
+        <v>144.0207040191272</v>
       </c>
     </row>
     <row r="140">
@@ -4629,15 +4629,15 @@
         <v>83.83990669000001</v>
       </c>
       <c r="F140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>404.208875401731</v>
+        <v>388.4867996322367</v>
       </c>
     </row>
     <row r="141">
@@ -4659,15 +4659,15 @@
         <v>66.93223488999999</v>
       </c>
       <c r="F141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>143.2619700296298</v>
+        <v>160.4530529800002</v>
       </c>
     </row>
     <row r="142">
@@ -4689,15 +4689,15 @@
         <v>94.84938579</v>
       </c>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>259.3122659168254</v>
+        <v>279.7075176862222</v>
       </c>
     </row>
     <row r="143">
@@ -4719,15 +4719,15 @@
         <v>145.91838293</v>
       </c>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>122.5537646253599</v>
+        <v>137.8802470023848</v>
       </c>
     </row>
     <row r="144">
@@ -4749,15 +4749,15 @@
         <v>148.16292628</v>
       </c>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>108.9835170149182</v>
+        <v>125.8355096270716</v>
       </c>
     </row>
     <row r="145">
@@ -4779,15 +4779,15 @@
         <v>22.03899181</v>
       </c>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>382.9364609623582</v>
+        <v>369.1622100435767</v>
       </c>
     </row>
     <row r="146">
@@ -4809,15 +4809,15 @@
         <v>169.43078549</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>112.9323050997713</v>
+        <v>40.93402369732947</v>
       </c>
     </row>
     <row r="147">
@@ -4839,15 +4839,15 @@
         <v>115.96496099</v>
       </c>
       <c r="F147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>129.9286643047488</v>
+        <v>146.5562506993173</v>
       </c>
     </row>
     <row r="148">
@@ -4869,15 +4869,15 @@
         <v>97.54827051999999</v>
       </c>
       <c r="F148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>126.9603102938765</v>
+        <v>145.0353621763646</v>
       </c>
     </row>
     <row r="149">
@@ -4899,15 +4899,15 @@
         <v>171.24941356</v>
       </c>
       <c r="F149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>139.0718628370146</v>
+        <v>157.1304892525723</v>
       </c>
     </row>
     <row r="150">
@@ -4929,15 +4929,15 @@
         <v>79.48337347</v>
       </c>
       <c r="F150" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>104.3207321729001</v>
+        <v>121.03539755116</v>
       </c>
     </row>
     <row r="151">
@@ -4959,15 +4959,15 @@
         <v>21.38957457</v>
       </c>
       <c r="F151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>394.1735633146689</v>
+        <v>378.6092271739076</v>
       </c>
     </row>
     <row r="152">
@@ -4989,15 +4989,15 @@
         <v>56.00126308</v>
       </c>
       <c r="F152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>471.6729480562649</v>
+        <v>453.0618631701936</v>
       </c>
     </row>
     <row r="153">
@@ -5019,15 +5019,15 @@
         <v>116.54724109</v>
       </c>
       <c r="F153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>134.3986826020986</v>
+        <v>150.9465552515387</v>
       </c>
     </row>
     <row r="154">
@@ -5049,15 +5049,15 @@
         <v>136.56314483</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>100.2591398725851</v>
+        <v>26.39503825315914</v>
       </c>
     </row>
     <row r="155">
@@ -5079,15 +5079,15 @@
         <v>132.34473269</v>
       </c>
       <c r="F155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>122.8495905764372</v>
+        <v>139.6648102466222</v>
       </c>
     </row>
     <row r="156">
@@ -5109,15 +5109,15 @@
         <v>127.67648195</v>
       </c>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>130.088061613333</v>
+        <v>147.6298806526679</v>
       </c>
     </row>
     <row r="157">
@@ -5139,15 +5139,15 @@
         <v>101.97064253</v>
       </c>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>485.9871884773702</v>
+        <v>466.5173357135325</v>
       </c>
     </row>
     <row r="158">
@@ -5169,15 +5169,15 @@
         <v>64.40666220000001</v>
       </c>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>388.4173225360324</v>
+        <v>378.5505972995411</v>
       </c>
     </row>
     <row r="159">
@@ -5199,15 +5199,15 @@
         <v>133.79668708</v>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>149.1025029821664</v>
+        <v>166.3585398305499</v>
       </c>
     </row>
     <row r="160">
@@ -5229,15 +5229,15 @@
         <v>138.15013296</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>378.5419582096303</v>
+        <v>295.1284815246919</v>
       </c>
     </row>
     <row r="161">
@@ -5259,15 +5259,15 @@
         <v>150.50007586</v>
       </c>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>130.6475561507304</v>
+        <v>148.430521977768</v>
       </c>
     </row>
     <row r="162">
@@ -5289,15 +5289,15 @@
         <v>93.60651496</v>
       </c>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>143.4355450702218</v>
+        <v>160.9527014377235</v>
       </c>
     </row>
     <row r="163">
@@ -5319,15 +5319,15 @@
         <v>129.31327658</v>
       </c>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>68.20923825105052</v>
+        <v>66.16610374030769</v>
       </c>
     </row>
     <row r="164">
@@ -5349,15 +5349,15 @@
         <v>106.88348563</v>
       </c>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>423.5281084764496</v>
+        <v>403.3770685462418</v>
       </c>
     </row>
     <row r="165">
@@ -5379,15 +5379,15 @@
         <v>42.43144776</v>
       </c>
       <c r="F165" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>383.5877977344479</v>
+        <v>369.9360371615572</v>
       </c>
     </row>
     <row r="166">
@@ -5409,15 +5409,15 @@
         <v>60.79293023</v>
       </c>
       <c r="F166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>326.0226848177935</v>
+        <v>312.3121417069709</v>
       </c>
     </row>
     <row r="167">
@@ -5439,15 +5439,15 @@
         <v>77.59270448000001</v>
       </c>
       <c r="F167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>140.1897991510045</v>
+        <v>157.9650373618147</v>
       </c>
     </row>
     <row r="168">
@@ -5469,15 +5469,15 @@
         <v>53.785478</v>
       </c>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>141.3235570287463</v>
+        <v>97.45824180501572</v>
       </c>
     </row>
     <row r="169">
@@ -5499,15 +5499,15 @@
         <v>145.0125221</v>
       </c>
       <c r="F169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>55.30319905350883</v>
+        <v>43.97404253119719</v>
       </c>
     </row>
     <row r="170">
@@ -5529,15 +5529,15 @@
         <v>134.76338509</v>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>125.1863571233696</v>
+        <v>140.7851946362896</v>
       </c>
     </row>
     <row r="171">
@@ -5559,15 +5559,15 @@
         <v>34.09060356</v>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>416.8347839584198</v>
+        <v>399.5083708833428</v>
       </c>
     </row>
     <row r="172">
@@ -5589,15 +5589,15 @@
         <v>103.95516876</v>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>144.4377989386378</v>
+        <v>161.5314469475466</v>
       </c>
     </row>
     <row r="173">
@@ -5619,15 +5619,15 @@
         <v>129.96221128</v>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>134.3534034235337</v>
+        <v>152.6882497958964</v>
       </c>
     </row>
     <row r="174">
@@ -5649,15 +5649,15 @@
         <v>123.25258422</v>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H174" t="n">
-        <v>114.0055451393923</v>
+        <v>130.9552456548431</v>
       </c>
     </row>
     <row r="175">
@@ -5679,15 +5679,15 @@
         <v>114.2480122</v>
       </c>
       <c r="F175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H175" t="n">
-        <v>124.7308673591305</v>
+        <v>110.1578374848856</v>
       </c>
     </row>
     <row r="176">
@@ -5709,15 +5709,15 @@
         <v>148.70392757</v>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H176" t="n">
-        <v>279.5492674223455</v>
+        <v>198.8890780199291</v>
       </c>
     </row>
     <row r="177">
@@ -5739,15 +5739,15 @@
         <v>164.48669544</v>
       </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>286.2681725369665</v>
+        <v>266.3355288928579</v>
       </c>
     </row>
     <row r="178">
@@ -5769,15 +5769,15 @@
         <v>149.1072418</v>
       </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H178" t="n">
-        <v>403.3875092325755</v>
+        <v>387.6774496753766</v>
       </c>
     </row>
     <row r="179">
@@ -5799,15 +5799,15 @@
         <v>114.08940098</v>
       </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>127.4899347416196</v>
+        <v>143.8721470076325</v>
       </c>
     </row>
     <row r="180">
@@ -5829,15 +5829,15 @@
         <v>112.05923696</v>
       </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H180" t="n">
-        <v>161.0626768672974</v>
+        <v>140.9664354752053</v>
       </c>
     </row>
     <row r="181">
@@ -5859,15 +5859,15 @@
         <v>64.98465548</v>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>127.0267048232512</v>
+        <v>142.7213522013847</v>
       </c>
     </row>
     <row r="182">
@@ -5889,15 +5889,15 @@
         <v>72.72579613999999</v>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H182" t="n">
-        <v>139.3757855483318</v>
+        <v>156.9633839319166</v>
       </c>
     </row>
     <row r="183">
@@ -5919,15 +5919,15 @@
         <v>103.13068804</v>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>139.1174159018112</v>
+        <v>156.7968949445768</v>
       </c>
     </row>
     <row r="184">
@@ -5949,15 +5949,15 @@
         <v>88.39244152999999</v>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H184" t="n">
-        <v>129.1647804488381</v>
+        <v>145.3817134522845</v>
       </c>
     </row>
     <row r="185">
@@ -5979,15 +5979,15 @@
         <v>111.28124526</v>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H185" t="n">
-        <v>147.3991022417724</v>
+        <v>164.8960223765515</v>
       </c>
     </row>
     <row r="186">
@@ -6009,15 +6009,15 @@
         <v>77.23146711</v>
       </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H186" t="n">
-        <v>143.0036862149796</v>
+        <v>160.1367601744726</v>
       </c>
     </row>
     <row r="187">
@@ -6039,15 +6039,15 @@
         <v>87.69854039000001</v>
       </c>
       <c r="F187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H187" t="n">
-        <v>131.8219351489301</v>
+        <v>94.57825916665728</v>
       </c>
     </row>
     <row r="188">
@@ -6069,15 +6069,15 @@
         <v>104.07446787</v>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H188" t="n">
-        <v>132.0778531307195</v>
+        <v>149.0413074483496</v>
       </c>
     </row>
     <row r="189">
@@ -6099,15 +6099,15 @@
         <v>135.95829359</v>
       </c>
       <c r="F189" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H189" t="n">
-        <v>123.3606496386461</v>
+        <v>105.1204904123371</v>
       </c>
     </row>
     <row r="190">
@@ -6129,15 +6129,15 @@
         <v>14.04523848</v>
       </c>
       <c r="F190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H190" t="n">
-        <v>403.4008878879773</v>
+        <v>388.2139984601232</v>
       </c>
     </row>
     <row r="191">
@@ -6159,15 +6159,15 @@
         <v>84.03368023</v>
       </c>
       <c r="F191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H191" t="n">
-        <v>52.44417237728874</v>
+        <v>46.05181255247427</v>
       </c>
     </row>
     <row r="192">
@@ -6189,15 +6189,15 @@
         <v>37.35482578</v>
       </c>
       <c r="F192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>410.8985883498559</v>
+        <v>393.715675009759</v>
       </c>
     </row>
     <row r="193">
@@ -6219,15 +6219,15 @@
         <v>29.02313882999999</v>
       </c>
       <c r="F193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>379.5971643506353</v>
+        <v>365.5773635412867</v>
       </c>
     </row>
     <row r="194">
@@ -6249,15 +6249,15 @@
         <v>69.75723010999999</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H194" t="n">
-        <v>139.1021731415539</v>
+        <v>90.42836908835832</v>
       </c>
     </row>
     <row r="195">
@@ -6279,15 +6279,15 @@
         <v>106.29918689</v>
       </c>
       <c r="F195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H195" t="n">
-        <v>115.6713272323911</v>
+        <v>132.9341213620754</v>
       </c>
     </row>
     <row r="196">
@@ -6309,15 +6309,15 @@
         <v>68.10364146999999</v>
       </c>
       <c r="F196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H196" t="n">
-        <v>129.9353063725652</v>
+        <v>148.6479009466308</v>
       </c>
     </row>
     <row r="197">
@@ -6339,15 +6339,15 @@
         <v>51.23457499999999</v>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H197" t="n">
-        <v>112.8438318657794</v>
+        <v>90.66046051512869</v>
       </c>
     </row>
     <row r="198">
@@ -6369,15 +6369,15 @@
         <v>62.39533672</v>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H198" t="n">
-        <v>212.7765634214703</v>
+        <v>138.4670632375975</v>
       </c>
     </row>
     <row r="199">
@@ -6399,15 +6399,15 @@
         <v>81.51284326</v>
       </c>
       <c r="F199" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>128.0801182035454</v>
+        <v>144.8737354091315</v>
       </c>
     </row>
     <row r="200">
@@ -6429,15 +6429,15 @@
         <v>83.68685203999999</v>
       </c>
       <c r="F200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>133.1566648141351</v>
+        <v>150.6046320137467</v>
       </c>
     </row>
     <row r="201">
@@ -6459,15 +6459,15 @@
         <v>68.18522616</v>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H201" t="n">
-        <v>124.8652061847382</v>
+        <v>141.2826203035115</v>
       </c>
     </row>
     <row r="202">
@@ -6489,15 +6489,15 @@
         <v>80.24099302</v>
       </c>
       <c r="F202" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H202" t="n">
-        <v>133.5168727607165</v>
+        <v>151.6595942303774</v>
       </c>
     </row>
     <row r="203">
@@ -6519,15 +6519,15 @@
         <v>42.55748138000001</v>
       </c>
       <c r="F203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H203" t="n">
-        <v>20.05921122465895</v>
+        <v>68.87397011120331</v>
       </c>
     </row>
     <row r="204">
@@ -6549,15 +6549,15 @@
         <v>66.30837547</v>
       </c>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H204" t="n">
-        <v>108.2994590509213</v>
+        <v>125.0677805919528</v>
       </c>
     </row>
     <row r="205">
@@ -6579,15 +6579,15 @@
         <v>72.1073177</v>
       </c>
       <c r="F205" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H205" t="n">
-        <v>109.4976212011855</v>
+        <v>81.78595913441407</v>
       </c>
     </row>
     <row r="206">
@@ -6609,15 +6609,15 @@
         <v>61.94020108000001</v>
       </c>
       <c r="F206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H206" t="n">
-        <v>176.3651706464888</v>
+        <v>140.0590297326085</v>
       </c>
     </row>
     <row r="207">
@@ -6639,15 +6639,15 @@
         <v>116.30465114</v>
       </c>
       <c r="F207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H207" t="n">
-        <v>133.315265358216</v>
+        <v>98.7323172694025</v>
       </c>
     </row>
     <row r="208">
@@ -6669,15 +6669,15 @@
         <v>66.85576336</v>
       </c>
       <c r="F208" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H208" t="n">
-        <v>170.4833860549217</v>
+        <v>150.0719903546772</v>
       </c>
     </row>
     <row r="209">
@@ -6699,15 +6699,15 @@
         <v>88.47867821</v>
       </c>
       <c r="F209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H209" t="n">
-        <v>138.0374803401048</v>
+        <v>156.0220450976014</v>
       </c>
     </row>
     <row r="210">
@@ -6729,15 +6729,15 @@
         <v>75.59825791</v>
       </c>
       <c r="F210" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H210" t="n">
-        <v>150.5124814610589</v>
+        <v>168.2216933394938</v>
       </c>
     </row>
     <row r="211">
@@ -6759,15 +6759,15 @@
         <v>112.48154805</v>
       </c>
       <c r="F211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H211" t="n">
-        <v>124.7669286489615</v>
+        <v>142.4573195186641</v>
       </c>
     </row>
     <row r="212">
@@ -6789,15 +6789,15 @@
         <v>105.4919814</v>
       </c>
       <c r="F212" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H212" t="n">
-        <v>130.7285006445507</v>
+        <v>87.98069974649448</v>
       </c>
     </row>
     <row r="213">
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>237.3450700802627</v>
+        <v>244.4547600179641</v>
       </c>
     </row>
     <row r="214">
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>142.4209975774765</v>
+        <v>224.1347950788545</v>
       </c>
     </row>
     <row r="215">
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>251.3431037068348</v>
+        <v>383.9683452505717</v>
       </c>
     </row>
     <row r="216">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>76.24503928516523</v>
+        <v>358.6786998752949</v>
       </c>
     </row>
     <row r="217">
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>265.8952897520346</v>
+        <v>405.3050657897217</v>
       </c>
     </row>
     <row r="218">
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>240.9662567092115</v>
+        <v>343.1529027900015</v>
       </c>
     </row>
     <row r="219">
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>232.8831422498661</v>
+        <v>192.2969368458551</v>
       </c>
     </row>
     <row r="220">
@@ -7037,7 +7037,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>247.7738698315432</v>
+        <v>379.5007289420488</v>
       </c>
     </row>
     <row r="221">
@@ -7067,7 +7067,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>112.6602580518521</v>
+        <v>170.9482929019636</v>
       </c>
     </row>
     <row r="222">
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>212.0819758215432</v>
+        <v>277.5254540437227</v>
       </c>
     </row>
     <row r="223">
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>293.709077172085</v>
+        <v>346.976523051831</v>
       </c>
     </row>
     <row r="224">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>115.5900301533268</v>
+        <v>167.7758876733445</v>
       </c>
     </row>
     <row r="225">
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>271.5611334846315</v>
+        <v>405.4342490665469</v>
       </c>
     </row>
     <row r="226">
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>97.24423539040143</v>
+        <v>342.2257220137689</v>
       </c>
     </row>
     <row r="227">
@@ -7239,15 +7239,15 @@
         <v>65.836</v>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H227" t="n">
-        <v>313.550423294308</v>
+        <v>511.3525973892623</v>
       </c>
     </row>
     <row r="228">
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>108.4127441231689</v>
+        <v>331.1662139980003</v>
       </c>
     </row>
     <row r="229">
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>250.6758741271072</v>
+        <v>381.7256943903093</v>
       </c>
     </row>
     <row r="230">
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>75.04265743794267</v>
+        <v>357.0246673916196</v>
       </c>
     </row>
     <row r="231">
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>246.1432344133759</v>
+        <v>377.0267809314404</v>
       </c>
     </row>
     <row r="232">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>114.30192697602</v>
+        <v>169.5897000840959</v>
       </c>
     </row>
     <row r="233">
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>111.4629059928046</v>
+        <v>336.4473247808326</v>
       </c>
     </row>
     <row r="234">
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>297.2711195324988</v>
+        <v>349.4569968094802</v>
       </c>
     </row>
     <row r="235">
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>139.6136387191068</v>
+        <v>223.0922603127969</v>
       </c>
     </row>
     <row r="236">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>110.9698302473184</v>
+        <v>172.9088095760513</v>
       </c>
     </row>
     <row r="237">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>248.3393938035115</v>
+        <v>378.5427318889581</v>
       </c>
     </row>
     <row r="238">
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>178.8354266787257</v>
+        <v>181.6944955579513</v>
       </c>
     </row>
     <row r="239">
@@ -7599,15 +7599,15 @@
         <v>111.0064</v>
       </c>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H239" t="n">
-        <v>312.1361089671532</v>
+        <v>510.8703195477742</v>
       </c>
     </row>
     <row r="240">
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>301.6611093529174</v>
+        <v>353.6441013146468</v>
       </c>
     </row>
     <row r="241">
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>269.1674756142003</v>
+        <v>405.779922177717</v>
       </c>
     </row>
     <row r="242">
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>72.72870510989631</v>
+        <v>354.4869959095565</v>
       </c>
     </row>
     <row r="243">
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>248.0490537632104</v>
+        <v>378.7680856783614</v>
       </c>
     </row>
     <row r="244">
@@ -7757,7 +7757,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>171.9775088426673</v>
+        <v>449.7335626017817</v>
       </c>
     </row>
     <row r="245">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>106.9333808471959</v>
+        <v>176.5776307618488</v>
       </c>
     </row>
     <row r="246">
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>113.2379343681344</v>
+        <v>341.5759657726773</v>
       </c>
     </row>
     <row r="247">
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>105.4632331842252</v>
+        <v>178.9192601996842</v>
       </c>
     </row>
     <row r="248">
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>114.3491596408315</v>
+        <v>337.8575499479376</v>
       </c>
     </row>
     <row r="249">
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>245.1275395793918</v>
+        <v>375.1955729779149</v>
       </c>
     </row>
     <row r="250">
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>260.1915026413278</v>
+        <v>414.9905506571422</v>
       </c>
     </row>
     <row r="251">
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>171.6099279259731</v>
+        <v>449.8968435611127</v>
       </c>
     </row>
     <row r="252">
@@ -7989,15 +7989,15 @@
         <v>22.082508</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H252" t="n">
-        <v>550.2335312616356</v>
+        <v>128.9049887187745</v>
       </c>
     </row>
     <row r="253">
@@ -8019,15 +8019,15 @@
         <v>26.1654</v>
       </c>
       <c r="F253" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H253" t="n">
-        <v>561.5482385892683</v>
+        <v>199.9453164122694</v>
       </c>
     </row>
     <row r="254">
@@ -8049,15 +8049,15 @@
         <v>41.9052</v>
       </c>
       <c r="F254" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H254" t="n">
-        <v>557.0579250598742</v>
+        <v>295.4992140148996</v>
       </c>
     </row>
     <row r="255">
@@ -8079,15 +8079,15 @@
         <v>898.0380000000002</v>
       </c>
       <c r="F255" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H255" t="n">
-        <v>700.0507512815924</v>
+        <v>379.6069181231939</v>
       </c>
     </row>
     <row r="256">
@@ -8109,15 +8109,15 @@
         <v>13.4594</v>
       </c>
       <c r="F256" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H256" t="n">
-        <v>698.2315230580112</v>
+        <v>380.258306252376</v>
       </c>
     </row>
     <row r="257">
@@ -8139,15 +8139,15 @@
         <v>109.8696</v>
       </c>
       <c r="F257" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H257" t="n">
-        <v>579.0433028806783</v>
+        <v>198.7566561597725</v>
       </c>
     </row>
     <row r="258">
@@ -8169,15 +8169,15 @@
         <v>128.60566</v>
       </c>
       <c r="F258" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H258" t="n">
-        <v>509.5702225252728</v>
+        <v>157.6723325326645</v>
       </c>
     </row>
     <row r="259">
@@ -8199,15 +8199,15 @@
         <v>571.5419999999999</v>
       </c>
       <c r="F259" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H259" t="n">
-        <v>844.261714845871</v>
+        <v>403.5081622823314</v>
       </c>
     </row>
     <row r="260">
@@ -8229,15 +8229,15 @@
         <v>122.977441</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H260" t="n">
-        <v>1046.468721910672</v>
+        <v>475.9405988279751</v>
       </c>
     </row>
     <row r="261">
@@ -8259,15 +8259,15 @@
         <v>131.0654675</v>
       </c>
       <c r="F261" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H261" t="n">
-        <v>508.6605462586443</v>
+        <v>195.7083783065673</v>
       </c>
     </row>
     <row r="262">
@@ -8289,15 +8289,15 @@
         <v>95.62609999999999</v>
       </c>
       <c r="F262" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H262" t="n">
-        <v>996.6799687422387</v>
+        <v>438.5077834249905</v>
       </c>
     </row>
     <row r="263">
@@ -8319,15 +8319,15 @@
         <v>106.7479</v>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H263" t="n">
-        <v>510.4480584785989</v>
+        <v>188.2066440310786</v>
       </c>
     </row>
     <row r="264">
@@ -8349,15 +8349,15 @@
         <v>123.2049255</v>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H264" t="n">
-        <v>513.2035290608322</v>
+        <v>190.9071943197909</v>
       </c>
     </row>
     <row r="265">
@@ -8379,15 +8379,15 @@
         <v>284.046</v>
       </c>
       <c r="F265" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H265" t="n">
-        <v>843.5142465454093</v>
+        <v>405.0565056120583</v>
       </c>
     </row>
     <row r="266">
@@ -8409,15 +8409,15 @@
         <v>995.3472000000002</v>
       </c>
       <c r="F266" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H266" t="n">
-        <v>553.8226352550597</v>
+        <v>301.8636096550673</v>
       </c>
     </row>
     <row r="267">
@@ -8439,15 +8439,15 @@
         <v>56.9948</v>
       </c>
       <c r="F267" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H267" t="n">
-        <v>576.614965605559</v>
+        <v>198.4266612290852</v>
       </c>
     </row>
     <row r="268">
@@ -8469,15 +8469,15 @@
         <v>162.227688</v>
       </c>
       <c r="F268" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H268" t="n">
-        <v>1085.208121862374</v>
+        <v>518.4040578096872</v>
       </c>
     </row>
     <row r="269">
@@ -8499,15 +8499,15 @@
         <v>93.85904950000001</v>
       </c>
       <c r="F269" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H269" t="n">
-        <v>1074.234516578657</v>
+        <v>510.6400033426321</v>
       </c>
     </row>
     <row r="270">
@@ -8529,15 +8529,15 @@
         <v>72.16600000000001</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H270" t="n">
-        <v>548.1254464247796</v>
+        <v>197.6583203948707</v>
       </c>
     </row>
     <row r="271">
@@ -8559,15 +8559,15 @@
         <v>77.25859999999999</v>
       </c>
       <c r="F271" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H271" t="n">
-        <v>582.3262762458045</v>
+        <v>200.1952793995961</v>
       </c>
     </row>
     <row r="272">
@@ -8589,15 +8589,15 @@
         <v>72.49699999999999</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H272" t="n">
-        <v>537.2466317410754</v>
+        <v>215.1429120314576</v>
       </c>
     </row>
     <row r="273">
@@ -8619,15 +8619,15 @@
         <v>186.4224215</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H273" t="n">
-        <v>515.9199484804882</v>
+        <v>189.4037922176628</v>
       </c>
     </row>
     <row r="274">
@@ -8649,15 +8649,15 @@
         <v>150.1102</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H274" t="n">
-        <v>581.0252119959074</v>
+        <v>198.7324288034695</v>
       </c>
     </row>
     <row r="275">
@@ -8679,15 +8679,15 @@
         <v>71.23049999999999</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H275" t="n">
-        <v>536.8600299106262</v>
+        <v>215.2126130343853</v>
       </c>
     </row>
     <row r="276">
@@ -8709,15 +8709,15 @@
         <v>222.122161</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H276" t="n">
-        <v>511.7048207086222</v>
+        <v>193.0481946178191</v>
       </c>
     </row>
     <row r="277">
@@ -8739,15 +8739,15 @@
         <v>243.76794</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H277" t="n">
-        <v>510.6325809729246</v>
+        <v>190.414855387531</v>
       </c>
     </row>
     <row r="278">
@@ -8769,15 +8769,15 @@
         <v>59.30860000000001</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H278" t="n">
-        <v>562.142259489176</v>
+        <v>197.1251076937621</v>
       </c>
     </row>
     <row r="279">
@@ -8799,15 +8799,15 @@
         <v>200.4813</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H279" t="n">
-        <v>512.6701910738842</v>
+        <v>189.8007120211021</v>
       </c>
     </row>
     <row r="280">
@@ -8829,15 +8829,15 @@
         <v>152.1270185</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1044.817507221502</v>
+        <v>474.2739396380379</v>
       </c>
     </row>
     <row r="281">
@@ -8859,15 +8859,15 @@
         <v>100.023278</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H281" t="n">
-        <v>577.4516136517115</v>
+        <v>106.1462563154388</v>
       </c>
     </row>
     <row r="282">
@@ -8889,15 +8889,15 @@
         <v>65.61912249999999</v>
       </c>
       <c r="F282" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H282" t="n">
-        <v>516.5020371147132</v>
+        <v>189.5541092308563</v>
       </c>
     </row>
     <row r="283">
@@ -8919,15 +8919,15 @@
         <v>59.61479999999999</v>
       </c>
       <c r="F283" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H283" t="n">
-        <v>555.6912913684956</v>
+        <v>297.7463062317671</v>
       </c>
     </row>
     <row r="284">
@@ -8949,15 +8949,15 @@
         <v>92.10120000000001</v>
       </c>
       <c r="F284" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H284" t="n">
-        <v>557.0309337825607</v>
+        <v>295.1508308036504</v>
       </c>
     </row>
     <row r="285">
@@ -8979,15 +8979,15 @@
         <v>87.2212</v>
       </c>
       <c r="F285" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H285" t="n">
-        <v>515.1266831373199</v>
+        <v>195.2004775661288</v>
       </c>
     </row>
     <row r="286">
@@ -9009,15 +9009,15 @@
         <v>44.383</v>
       </c>
       <c r="F286" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H286" t="n">
-        <v>581.1236556189809</v>
+        <v>198.792485816512</v>
       </c>
     </row>
     <row r="287">
@@ -9039,15 +9039,15 @@
         <v>72.4555</v>
       </c>
       <c r="F287" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H287" t="n">
-        <v>553.5205715866714</v>
+        <v>211.7593814876636</v>
       </c>
     </row>
     <row r="288">
@@ -9069,15 +9069,15 @@
         <v>228.606</v>
       </c>
       <c r="F288" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H288" t="n">
-        <v>807.3513364050648</v>
+        <v>409.3578444052795</v>
       </c>
     </row>
     <row r="289">
@@ -9099,15 +9099,15 @@
         <v>106.680992</v>
       </c>
       <c r="F289" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H289" t="n">
-        <v>962.5966753539426</v>
+        <v>390.9140081015669</v>
       </c>
     </row>
     <row r="290">
@@ -9129,15 +9129,15 @@
         <v>118.29098</v>
       </c>
       <c r="F290" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H290" t="n">
-        <v>195.8294926826765</v>
+        <v>260.0725060296554</v>
       </c>
     </row>
     <row r="291">
@@ -9159,15 +9159,15 @@
         <v>56.55883999999998</v>
       </c>
       <c r="F291" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H291" t="n">
-        <v>537.9737707618008</v>
+        <v>478.6929063561986</v>
       </c>
     </row>
     <row r="292">
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>325.7527379481806</v>
+        <v>317.4733968405083</v>
       </c>
     </row>
     <row r="293">
@@ -9219,15 +9219,15 @@
         <v>76.35709999999999</v>
       </c>
       <c r="F293" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H293" t="n">
-        <v>213.6074034689326</v>
+        <v>174.1455252776595</v>
       </c>
     </row>
     <row r="294">
@@ -9249,15 +9249,15 @@
         <v>65.98963999999999</v>
       </c>
       <c r="F294" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H294" t="n">
-        <v>536.0748695206678</v>
+        <v>483.6949449878604</v>
       </c>
     </row>
     <row r="295">
@@ -9279,15 +9279,15 @@
         <v>70.17684000000001</v>
       </c>
       <c r="F295" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H295" t="n">
-        <v>374.8062599792478</v>
+        <v>395.2279755294658</v>
       </c>
     </row>
     <row r="296">
@@ -9309,15 +9309,15 @@
         <v>80.12326000000002</v>
       </c>
       <c r="F296" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H296" t="n">
-        <v>66.89312229177543</v>
+        <v>139.904278070824</v>
       </c>
     </row>
     <row r="297">
@@ -9339,15 +9339,15 @@
         <v>73.27007999999999</v>
       </c>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H297" t="n">
-        <v>497.6277549216953</v>
+        <v>518.017243909774</v>
       </c>
     </row>
     <row r="298">
@@ -9369,15 +9369,15 @@
         <v>113.30992</v>
       </c>
       <c r="F298" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H298" t="n">
-        <v>123.1188905675009</v>
+        <v>171.8836861734805</v>
       </c>
     </row>
     <row r="299">
@@ -9399,15 +9399,15 @@
         <v>43.52612</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H299" t="n">
-        <v>627.4253330784752</v>
+        <v>305.6066734773577</v>
       </c>
     </row>
     <row r="300">
@@ -9429,15 +9429,15 @@
         <v>108.32342</v>
       </c>
       <c r="F300" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H300" t="n">
-        <v>61.47167162779635</v>
+        <v>145.1818212920968</v>
       </c>
     </row>
     <row r="301">
@@ -9459,15 +9459,15 @@
         <v>51.79328</v>
       </c>
       <c r="F301" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H301" t="n">
-        <v>597.7896412243185</v>
+        <v>419.036129462474</v>
       </c>
     </row>
     <row r="302">
@@ -9489,15 +9489,15 @@
         <v>68.9781</v>
       </c>
       <c r="F302" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H302" t="n">
-        <v>615.8969959031837</v>
+        <v>407.1102990416741</v>
       </c>
     </row>
     <row r="303">
@@ -9519,15 +9519,15 @@
         <v>69.73756</v>
       </c>
       <c r="F303" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H303" t="n">
-        <v>616.3496102117134</v>
+        <v>295.353133364184</v>
       </c>
     </row>
     <row r="304">
@@ -9549,15 +9549,15 @@
         <v>116.13984</v>
       </c>
       <c r="F304" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H304" t="n">
-        <v>618.4095869413236</v>
+        <v>302.21659388239</v>
       </c>
     </row>
     <row r="305">
@@ -9579,15 +9579,15 @@
         <v>100.22104</v>
       </c>
       <c r="F305" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H305" t="n">
-        <v>616.0961971153129</v>
+        <v>299.2683693566714</v>
       </c>
     </row>
     <row r="306">
@@ -9609,15 +9609,15 @@
         <v>124.95866</v>
       </c>
       <c r="F306" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H306" t="n">
-        <v>200.2053993384051</v>
+        <v>265.2849324520069</v>
       </c>
     </row>
     <row r="307">
@@ -9639,15 +9639,15 @@
         <v>106.6222</v>
       </c>
       <c r="F307" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H307" t="n">
-        <v>271.365017209034</v>
+        <v>234.1539906552349</v>
       </c>
     </row>
     <row r="308">
@@ -9669,15 +9669,15 @@
         <v>37.92908</v>
       </c>
       <c r="F308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H308" t="n">
-        <v>62.69887471408907</v>
+        <v>137.9645027339064</v>
       </c>
     </row>
     <row r="309">
@@ -9699,15 +9699,15 @@
         <v>76.79181999999999</v>
       </c>
       <c r="F309" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H309" t="n">
-        <v>573.8387765074733</v>
+        <v>213.5800407661942</v>
       </c>
     </row>
     <row r="310">
@@ -9729,15 +9729,15 @@
         <v>47.35968</v>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H310" t="n">
-        <v>485.7432394022453</v>
+        <v>505.864554707247</v>
       </c>
     </row>
     <row r="311">
@@ -9759,15 +9759,15 @@
         <v>153.85138</v>
       </c>
       <c r="F311" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H311" t="n">
-        <v>66.0268932691002</v>
+        <v>140.4766831106095</v>
       </c>
     </row>
     <row r="312">
@@ -9789,15 +9789,15 @@
         <v>178.5294</v>
       </c>
       <c r="F312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H312" t="n">
-        <v>198.7592680572442</v>
+        <v>263.2808293594302</v>
       </c>
     </row>
     <row r="313">
@@ -9819,15 +9819,15 @@
         <v>138.3113</v>
       </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H313" t="n">
-        <v>63.30485937058388</v>
+        <v>146.8970220930177</v>
       </c>
     </row>
     <row r="314">
@@ -9849,15 +9849,15 @@
         <v>148.35608</v>
       </c>
       <c r="F314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H314" t="n">
-        <v>171.2780401337388</v>
+        <v>252.0220765832538</v>
       </c>
     </row>
     <row r="315">
@@ -9879,15 +9879,15 @@
         <v>137.84592</v>
       </c>
       <c r="F315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H315" t="n">
-        <v>207.2118431361766</v>
+        <v>290.8446586327354</v>
       </c>
     </row>
     <row r="316">
@@ -9909,15 +9909,15 @@
         <v>71.19014000000001</v>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H316" t="n">
-        <v>596.9053902497836</v>
+        <v>419.8748338969282</v>
       </c>
     </row>
     <row r="317">
@@ -9939,15 +9939,15 @@
         <v>106.50236</v>
       </c>
       <c r="F317" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H317" t="n">
-        <v>121.7310041555266</v>
+        <v>202.3745627430987</v>
       </c>
     </row>
     <row r="318">
@@ -9969,15 +9969,15 @@
         <v>97.77134</v>
       </c>
       <c r="F318" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H318" t="n">
-        <v>49.89652576347511</v>
+        <v>131.3767754580934</v>
       </c>
     </row>
     <row r="319">
@@ -9999,15 +9999,15 @@
         <v>80.68743999999998</v>
       </c>
       <c r="F319" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H319" t="n">
-        <v>617.4279070361644</v>
+        <v>405.4616480532131</v>
       </c>
     </row>
     <row r="320">
@@ -10029,15 +10029,15 @@
         <v>92.23769999999999</v>
       </c>
       <c r="F320" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H320" t="n">
-        <v>575.0112439592498</v>
+        <v>257.7202175042919</v>
       </c>
     </row>
     <row r="321">
@@ -10059,15 +10059,15 @@
         <v>111.7828</v>
       </c>
       <c r="F321" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H321" t="n">
-        <v>619.2269057530879</v>
+        <v>299.2069770829289</v>
       </c>
     </row>
     <row r="322">
@@ -10089,15 +10089,15 @@
         <v>120.6901</v>
       </c>
       <c r="F322" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H322" t="n">
-        <v>167.0822270632482</v>
+        <v>225.2118983559744</v>
       </c>
     </row>
     <row r="323">
@@ -10119,15 +10119,15 @@
         <v>51.7548</v>
       </c>
       <c r="F323" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H323" t="n">
-        <v>270.1330052516413</v>
+        <v>233.1156151535796</v>
       </c>
     </row>
     <row r="324">
@@ -10149,15 +10149,15 @@
         <v>162.11432</v>
       </c>
       <c r="F324" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H324" t="n">
-        <v>123.9640433675536</v>
+        <v>174.6437031880509</v>
       </c>
     </row>
     <row r="325">
@@ -10179,15 +10179,15 @@
         <v>70.43834</v>
       </c>
       <c r="F325" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H325" t="n">
-        <v>185.6342827243591</v>
+        <v>258.0969226234916</v>
       </c>
     </row>
     <row r="326">
@@ -10209,15 +10209,15 @@
         <v>97.17318</v>
       </c>
       <c r="F326" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H326" t="n">
-        <v>59.72511885034409</v>
+        <v>143.4559287228808</v>
       </c>
     </row>
     <row r="327">
@@ -10239,15 +10239,15 @@
         <v>96.64926</v>
       </c>
       <c r="F327" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H327" t="n">
-        <v>614.1876446764838</v>
+        <v>298.5405184854939</v>
       </c>
     </row>
     <row r="328">
@@ -10269,15 +10269,15 @@
         <v>136.70414</v>
       </c>
       <c r="F328" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H328" t="n">
-        <v>607.6027114558465</v>
+        <v>291.9125166681933</v>
       </c>
     </row>
     <row r="329">
@@ -10299,15 +10299,15 @@
         <v>55.98389999999999</v>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H329" t="n">
-        <v>241.5798000792561</v>
+        <v>201.6634020843782</v>
       </c>
     </row>
     <row r="330">
@@ -10329,15 +10329,15 @@
         <v>57.27579999999999</v>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H330" t="n">
-        <v>218.3636872097339</v>
+        <v>187.3472114739193</v>
       </c>
     </row>
     <row r="331">
@@ -10359,15 +10359,15 @@
         <v>100.51814</v>
       </c>
       <c r="F331" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H331" t="n">
-        <v>626.661873619375</v>
+        <v>306.1498650987936</v>
       </c>
     </row>
     <row r="332">
@@ -10389,15 +10389,15 @@
         <v>72.68213999999999</v>
       </c>
       <c r="F332" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H332" t="n">
-        <v>533.6077234554629</v>
+        <v>240.6553957539271</v>
       </c>
     </row>
     <row r="333">
@@ -10419,15 +10419,15 @@
         <v>53.00724</v>
       </c>
       <c r="F333" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H333" t="n">
-        <v>623.878251310231</v>
+        <v>305.5297858281983</v>
       </c>
     </row>
     <row r="334">
@@ -10449,15 +10449,15 @@
         <v>84.78078000000001</v>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H334" t="n">
-        <v>201.3426454253737</v>
+        <v>265.5314730786209</v>
       </c>
     </row>
     <row r="335">
@@ -10479,15 +10479,15 @@
         <v>97.36683999999997</v>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H335" t="n">
-        <v>103.1380002652348</v>
+        <v>115.8620035916273</v>
       </c>
     </row>
     <row r="336">
@@ -10509,15 +10509,15 @@
         <v>81.07180000000001</v>
       </c>
       <c r="F336" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H336" t="n">
-        <v>256.7168714137835</v>
+        <v>325.2162572181462</v>
       </c>
     </row>
     <row r="337">
@@ -10539,15 +10539,15 @@
         <v>51.87629999999999</v>
       </c>
       <c r="F337" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H337" t="n">
-        <v>95.76639060961472</v>
+        <v>176.0201727541978</v>
       </c>
     </row>
     <row r="338">
@@ -10569,15 +10569,15 @@
         <v>164.81286</v>
       </c>
       <c r="F338" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H338" t="n">
-        <v>260.3496983421461</v>
+        <v>242.8334230268776</v>
       </c>
     </row>
     <row r="339">
@@ -10599,15 +10599,15 @@
         <v>137.11044</v>
       </c>
       <c r="F339" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H339" t="n">
-        <v>339.5078169732922</v>
+        <v>262.5364558361898</v>
       </c>
     </row>
     <row r="340">
@@ -10629,15 +10629,15 @@
         <v>105.60097665</v>
       </c>
       <c r="F340" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H340" t="n">
-        <v>268.4852574352886</v>
+        <v>244.4815171214456</v>
       </c>
     </row>
     <row r="341">
@@ -10659,15 +10659,15 @@
         <v>85.30447965</v>
       </c>
       <c r="F341" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H341" t="n">
-        <v>246.0994041861252</v>
+        <v>249.0720943022942</v>
       </c>
     </row>
     <row r="342">
@@ -10689,15 +10689,15 @@
         <v>105.13692</v>
       </c>
       <c r="F342" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H342" t="n">
-        <v>244.0803400677385</v>
+        <v>130.0982456924606</v>
       </c>
     </row>
     <row r="343">
@@ -10719,15 +10719,15 @@
         <v>119.39315505</v>
       </c>
       <c r="F343" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H343" t="n">
-        <v>265.1235430500931</v>
+        <v>244.7649577139401</v>
       </c>
     </row>
     <row r="344">
@@ -10749,15 +10749,15 @@
         <v>135.2097</v>
       </c>
       <c r="F344" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H344" t="n">
-        <v>220.5164664270967</v>
+        <v>170.4849151475579</v>
       </c>
     </row>
     <row r="345">
@@ -10779,15 +10779,15 @@
         <v>103.2224895</v>
       </c>
       <c r="F345" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H345" t="n">
-        <v>266.4253604948988</v>
+        <v>247.3589627515343</v>
       </c>
     </row>
     <row r="346">
@@ -10809,15 +10809,15 @@
         <v>105.68844</v>
       </c>
       <c r="F346" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H346" t="n">
-        <v>262.1499381849978</v>
+        <v>250.7518419947306</v>
       </c>
     </row>
     <row r="347">
@@ -10839,15 +10839,15 @@
         <v>92.92085999999999</v>
       </c>
       <c r="F347" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H347" t="n">
-        <v>256.6376844413774</v>
+        <v>245.2020554131428</v>
       </c>
     </row>
     <row r="348">
@@ -10869,15 +10869,15 @@
         <v>105.6147144</v>
       </c>
       <c r="F348" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H348" t="n">
-        <v>272.121281660024</v>
+        <v>247.1939855447183</v>
       </c>
     </row>
     <row r="349">
@@ -10899,15 +10899,15 @@
         <v>96.36005999999999</v>
       </c>
       <c r="F349" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H349" t="n">
-        <v>123.9955394119936</v>
+        <v>248.9481718440073</v>
       </c>
     </row>
     <row r="350">
@@ -10929,15 +10929,15 @@
         <v>81.90635999999998</v>
       </c>
       <c r="F350" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H350" t="n">
-        <v>338.753579945603</v>
+        <v>262.8258537407512</v>
       </c>
     </row>
     <row r="351">
@@ -10959,15 +10959,15 @@
         <v>103.29378</v>
       </c>
       <c r="F351" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H351" t="n">
-        <v>244.9481478563077</v>
+        <v>243.9905079930992</v>
       </c>
     </row>
     <row r="352">
@@ -10989,15 +10989,15 @@
         <v>69.66414</v>
       </c>
       <c r="F352" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H352" t="n">
-        <v>128.1288650973908</v>
+        <v>245.7263957483557</v>
       </c>
     </row>
     <row r="353">
@@ -11019,15 +11019,15 @@
         <v>133.07976</v>
       </c>
       <c r="F353" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H353" t="n">
-        <v>270.1477232966168</v>
+        <v>241.3758450983825</v>
       </c>
     </row>
     <row r="354">
@@ -11049,15 +11049,15 @@
         <v>99.53225999999999</v>
       </c>
       <c r="F354" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H354" t="n">
-        <v>224.5097660238579</v>
+        <v>173.6480917764453</v>
       </c>
     </row>
     <row r="355">
@@ -11079,15 +11079,15 @@
         <v>174.81366</v>
       </c>
       <c r="F355" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H355" t="n">
-        <v>319.9119139195989</v>
+        <v>255.3696671481475</v>
       </c>
     </row>
     <row r="356">
@@ -11109,15 +11109,15 @@
         <v>123.87336</v>
       </c>
       <c r="F356" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H356" t="n">
-        <v>127.30602726443</v>
+        <v>245.2199955591135</v>
       </c>
     </row>
     <row r="357">
@@ -11139,15 +11139,15 @@
         <v>147.74808</v>
       </c>
       <c r="F357" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H357" t="n">
-        <v>247.0030921458697</v>
+        <v>127.1680167975757</v>
       </c>
     </row>
     <row r="358">
@@ -11169,15 +11169,15 @@
         <v>148.73862</v>
       </c>
       <c r="F358" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H358" t="n">
-        <v>245.8723846358603</v>
+        <v>251.8859543154234</v>
       </c>
     </row>
     <row r="359">
@@ -11199,15 +11199,15 @@
         <v>273.06534</v>
       </c>
       <c r="F359" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H359" t="n">
-        <v>259.1175712553428</v>
+        <v>244.6616573423616</v>
       </c>
     </row>
     <row r="360">
@@ -11229,15 +11229,15 @@
         <v>108.07158</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H360" t="n">
-        <v>267.5215536520797</v>
+        <v>242.2130875979642</v>
       </c>
     </row>
     <row r="361">
@@ -11259,15 +11259,15 @@
         <v>154.62948</v>
       </c>
       <c r="F361" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H361" t="n">
-        <v>394.2085802884727</v>
+        <v>184.1323231692768</v>
       </c>
     </row>
     <row r="362">
@@ -11289,15 +11289,15 @@
         <v>133.61611575</v>
       </c>
       <c r="F362" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H362" t="n">
-        <v>269.2177499230888</v>
+        <v>247.2555998483565</v>
       </c>
     </row>
     <row r="363">
@@ -11319,15 +11319,15 @@
         <v>107.2794</v>
       </c>
       <c r="F363" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H363" t="n">
-        <v>265.7120377715198</v>
+        <v>248.2500861193687</v>
       </c>
     </row>
     <row r="364">
@@ -11349,15 +11349,15 @@
         <v>90.89004</v>
       </c>
       <c r="F364" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H364" t="n">
-        <v>272.0407614309759</v>
+        <v>238.6138624870473</v>
       </c>
     </row>
     <row r="365">
@@ -11379,15 +11379,15 @@
         <v>65.39706</v>
       </c>
       <c r="F365" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H365" t="n">
-        <v>267.1609274923284</v>
+        <v>248.2464578486703</v>
       </c>
     </row>
     <row r="366">
@@ -11409,15 +11409,15 @@
         <v>93.90606000000002</v>
       </c>
       <c r="F366" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H366" t="n">
-        <v>119.9739091585612</v>
+        <v>251.572927532271</v>
       </c>
     </row>
     <row r="367">
@@ -11439,15 +11439,15 @@
         <v>102.0003</v>
       </c>
       <c r="F367" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H367" t="n">
-        <v>393.9184922121719</v>
+        <v>230.4299203347763</v>
       </c>
     </row>
     <row r="368">
@@ -11469,15 +11469,15 @@
         <v>69.34979999999999</v>
       </c>
       <c r="F368" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H368" t="n">
-        <v>283.3056721743233</v>
+        <v>230.0711370582394</v>
       </c>
     </row>
     <row r="369">
@@ -11499,15 +11499,15 @@
         <v>147.48796146</v>
       </c>
       <c r="F369" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H369" t="n">
-        <v>755.4364692614545</v>
+        <v>66.73815255783093</v>
       </c>
     </row>
     <row r="370">
@@ -11529,15 +11529,15 @@
         <v>81.62645259999999</v>
       </c>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H370" t="n">
-        <v>737.0602738658094</v>
+        <v>34.52345300414044</v>
       </c>
     </row>
     <row r="371">
@@ -11559,15 +11559,15 @@
         <v>125.7125763</v>
       </c>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H371" t="n">
-        <v>407.9443120675884</v>
+        <v>317.946630304663</v>
       </c>
     </row>
     <row r="372">
@@ -11589,15 +11589,15 @@
         <v>118.30654686</v>
       </c>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H372" t="n">
-        <v>879.9928298660333</v>
+        <v>176.6888667503275</v>
       </c>
     </row>
     <row r="373">
@@ -11619,15 +11619,15 @@
         <v>46.7992934</v>
       </c>
       <c r="F373" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H373" t="n">
-        <v>762.9026211265187</v>
+        <v>63.09525674037218</v>
       </c>
     </row>
     <row r="374">
@@ -11649,15 +11649,15 @@
         <v>135.638204</v>
       </c>
       <c r="F374" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H374" t="n">
-        <v>767.4385075145673</v>
+        <v>67.88592045568444</v>
       </c>
     </row>
     <row r="375">
@@ -11679,15 +11679,15 @@
         <v>82.8659857</v>
       </c>
       <c r="F375" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H375" t="n">
-        <v>737.3593294495913</v>
+        <v>34.2181840897848</v>
       </c>
     </row>
     <row r="376">
@@ -11709,15 +11709,15 @@
         <v>105.553257</v>
       </c>
       <c r="F376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H376" t="n">
-        <v>732.0924029321508</v>
+        <v>32.70858238462002</v>
       </c>
     </row>
     <row r="377">
@@ -11739,15 +11739,15 @@
         <v>71.35351295999999</v>
       </c>
       <c r="F377" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H377" t="n">
-        <v>885.0784624488344</v>
+        <v>181.5158062914187</v>
       </c>
     </row>
     <row r="378">
@@ -11769,15 +11769,15 @@
         <v>102.73411212</v>
       </c>
       <c r="F378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H378" t="n">
-        <v>883.3096566025587</v>
+        <v>180.1765995943753</v>
       </c>
     </row>
     <row r="379">
@@ -11799,15 +11799,15 @@
         <v>128.5971056</v>
       </c>
       <c r="F379" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H379" t="n">
-        <v>736.889207163484</v>
+        <v>35.38984638379532</v>
       </c>
     </row>
     <row r="380">
@@ -11829,15 +11829,15 @@
         <v>62.78045063999999</v>
       </c>
       <c r="F380" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H380" t="n">
-        <v>844.8787435615096</v>
+        <v>148.9146243709701</v>
       </c>
     </row>
     <row r="381">
@@ -11859,15 +11859,15 @@
         <v>109.3731514</v>
       </c>
       <c r="F381" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H381" t="n">
-        <v>455.5450121192576</v>
+        <v>292.1082656735446</v>
       </c>
     </row>
     <row r="382">
@@ -11889,15 +11889,15 @@
         <v>119.1499458</v>
       </c>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H382" t="n">
-        <v>734.8010227130336</v>
+        <v>33.3796757686011</v>
       </c>
     </row>
     <row r="383">
@@ -11919,15 +11919,15 @@
         <v>213.5551645</v>
       </c>
       <c r="F383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H383" t="n">
-        <v>732.5636727352477</v>
+        <v>31.90591786876936</v>
       </c>
     </row>
     <row r="384">
@@ -11949,15 +11949,15 @@
         <v>187.0876349</v>
       </c>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H384" t="n">
-        <v>735.2834981467736</v>
+        <v>33.24458419572206</v>
       </c>
     </row>
     <row r="385">
@@ -11979,15 +11979,15 @@
         <v>149.1235557</v>
       </c>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H385" t="n">
-        <v>763.5216114415061</v>
+        <v>63.43243743125071</v>
       </c>
     </row>
     <row r="386">
@@ -12009,15 +12009,15 @@
         <v>170.141426</v>
       </c>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H386" t="n">
-        <v>453.3744570574661</v>
+        <v>293.4508617519292</v>
       </c>
     </row>
     <row r="387">
@@ -12039,15 +12039,15 @@
         <v>168.952343</v>
       </c>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H387" t="n">
-        <v>739.4024454744151</v>
+        <v>37.08142664821583</v>
       </c>
     </row>
     <row r="388">
@@ -12069,15 +12069,15 @@
         <v>107.310147</v>
       </c>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H388" t="n">
-        <v>728.3554642433388</v>
+        <v>29.33806901372546</v>
       </c>
     </row>
     <row r="389">
@@ -12099,15 +12099,15 @@
         <v>111.302101</v>
       </c>
       <c r="F389" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H389" t="n">
-        <v>728.7075752636654</v>
+        <v>28.37001636872408</v>
       </c>
     </row>
     <row r="390">
@@ -12129,15 +12129,15 @@
         <v>77.23364369999999</v>
       </c>
       <c r="F390" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H390" t="n">
-        <v>738.2112070147015</v>
+        <v>39.11561759641163</v>
       </c>
     </row>
     <row r="391">
@@ -12159,15 +12159,15 @@
         <v>53.22112451999999</v>
       </c>
       <c r="F391" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H391" t="n">
-        <v>909.2151633942545</v>
+        <v>203.8019484784353</v>
       </c>
     </row>
     <row r="392">
@@ -12189,15 +12189,15 @@
         <v>110.9159485</v>
       </c>
       <c r="F392" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H392" t="n">
-        <v>730.4862665823251</v>
+        <v>31.02089893886271</v>
       </c>
     </row>
     <row r="393">
@@ -12219,15 +12219,15 @@
         <v>95.37692682000001</v>
       </c>
       <c r="F393" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H393" t="n">
-        <v>887.7534123901355</v>
+        <v>184.6131265113243</v>
       </c>
     </row>
     <row r="394">
@@ -12249,15 +12249,15 @@
         <v>54.18531179999999</v>
       </c>
       <c r="F394" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H394" t="n">
-        <v>725.6101542216179</v>
+        <v>27.58568935880062</v>
       </c>
     </row>
     <row r="395">
@@ -12279,15 +12279,15 @@
         <v>111.9413228</v>
       </c>
       <c r="F395" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H395" t="n">
-        <v>715.8419916078705</v>
+        <v>30.56895919515435</v>
       </c>
     </row>
     <row r="396">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>707.3848536348678</v>
+        <v>599.7685658275938</v>
       </c>
     </row>
     <row r="397">
@@ -12339,15 +12339,15 @@
         <v>120.77989</v>
       </c>
       <c r="F397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H397" t="n">
-        <v>402.8528284779557</v>
+        <v>418.910619457074</v>
       </c>
     </row>
     <row r="398">
@@ -12369,15 +12369,15 @@
         <v>88.73139999999999</v>
       </c>
       <c r="F398" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H398" t="n">
-        <v>318.7461283580383</v>
+        <v>395.1452104601061</v>
       </c>
     </row>
     <row r="399">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>660.8614547036476</v>
+        <v>580.0655393103883</v>
       </c>
     </row>
     <row r="400">
@@ -12429,15 +12429,15 @@
         <v>27.36499</v>
       </c>
       <c r="F400" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H400" t="n">
-        <v>415.0220367356314</v>
+        <v>419.2014824656533</v>
       </c>
     </row>
     <row r="401">
@@ -12459,15 +12459,15 @@
         <v>116.77227</v>
       </c>
       <c r="F401" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H401" t="n">
-        <v>404.0941521558714</v>
+        <v>417.7719448167981</v>
       </c>
     </row>
     <row r="402">
@@ -12489,15 +12489,15 @@
         <v>75.02567782</v>
       </c>
       <c r="F402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H402" t="n">
-        <v>531.9172069611084</v>
+        <v>290.1088194372147</v>
       </c>
     </row>
     <row r="403">
@@ -12519,15 +12519,15 @@
         <v>59.45515</v>
       </c>
       <c r="F403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H403" t="n">
-        <v>408.0188493815209</v>
+        <v>413.7000010176697</v>
       </c>
     </row>
     <row r="404">
@@ -12549,15 +12549,15 @@
         <v>126.89930723</v>
       </c>
       <c r="F404" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H404" t="n">
-        <v>539.6096633611475</v>
+        <v>286.2644628689006</v>
       </c>
     </row>
     <row r="405">
@@ -12587,7 +12587,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>703.1264574838835</v>
+        <v>596.4055858326795</v>
       </c>
     </row>
     <row r="406">
@@ -12609,15 +12609,15 @@
         <v>118.61613</v>
       </c>
       <c r="F406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H406" t="n">
-        <v>799.0464878757987</v>
+        <v>667.4815881169878</v>
       </c>
     </row>
     <row r="407">
@@ -12639,15 +12639,15 @@
         <v>99.67066999999997</v>
       </c>
       <c r="F407" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H407" t="n">
-        <v>403.6412926718086</v>
+        <v>418.0305093436396</v>
       </c>
     </row>
     <row r="408">
@@ -12677,7 +12677,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>658.928053837548</v>
+        <v>577.1715434059126</v>
       </c>
     </row>
     <row r="409">
@@ -12699,15 +12699,15 @@
         <v>221.48973368</v>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H409" t="n">
-        <v>531.1964786528766</v>
+        <v>291.0608337402675</v>
       </c>
     </row>
     <row r="410">
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>702.5680044936581</v>
+        <v>596.9387958350218</v>
       </c>
     </row>
     <row r="411">
@@ -12759,15 +12759,15 @@
         <v>12.82508</v>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H411" t="n">
-        <v>404.3147527355172</v>
+        <v>417.601541343521</v>
       </c>
     </row>
     <row r="412">
@@ -12789,15 +12789,15 @@
         <v>104.69023</v>
       </c>
       <c r="F412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H412" t="n">
-        <v>731.1957182903645</v>
+        <v>592.2228066044695</v>
       </c>
     </row>
     <row r="413">
@@ -12819,15 +12819,15 @@
         <v>131.63062668</v>
       </c>
       <c r="F413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H413" t="n">
-        <v>513.4781853654288</v>
+        <v>316.9706336802632</v>
       </c>
     </row>
     <row r="414">
@@ -12857,7 +12857,7 @@
         </is>
       </c>
       <c r="H414" t="n">
-        <v>691.0893860919261</v>
+        <v>623.8236912874983</v>
       </c>
     </row>
     <row r="415">
@@ -12879,15 +12879,15 @@
         <v>57.31582</v>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H415" t="n">
-        <v>689.0716245778688</v>
+        <v>631.3880668617128</v>
       </c>
     </row>
     <row r="416">
@@ -12909,15 +12909,15 @@
         <v>53.89304</v>
       </c>
       <c r="F416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H416" t="n">
-        <v>733.8647042878714</v>
+        <v>594.4100784430385</v>
       </c>
     </row>
     <row r="417">
@@ -12947,7 +12947,7 @@
         </is>
       </c>
       <c r="H417" t="n">
-        <v>687.9706222615004</v>
+        <v>620.2615824043411</v>
       </c>
     </row>
     <row r="418">
@@ -12969,15 +12969,15 @@
         <v>44.69123999999999</v>
       </c>
       <c r="F418" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H418" t="n">
-        <v>471.9688111199325</v>
+        <v>204.5305974443592</v>
       </c>
     </row>
     <row r="419">
@@ -13007,7 +13007,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>392.8925776521635</v>
+        <v>110.2827409697895</v>
       </c>
     </row>
     <row r="420">
@@ -13029,15 +13029,15 @@
         <v>30.97999</v>
       </c>
       <c r="F420" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H420" t="n">
-        <v>468.1659299344697</v>
+        <v>204.4596365169506</v>
       </c>
     </row>
     <row r="421">
@@ -13059,15 +13059,15 @@
         <v>38.67852</v>
       </c>
       <c r="F421" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H421" t="n">
-        <v>437.6301333322829</v>
+        <v>163.7742200848483</v>
       </c>
     </row>
     <row r="422">
@@ -13089,15 +13089,15 @@
         <v>22.78917</v>
       </c>
       <c r="F422" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H422" t="n">
-        <v>469.3464139810218</v>
+        <v>208.7913962749197</v>
       </c>
     </row>
     <row r="423">
@@ -13127,7 +13127,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>404.1736028081135</v>
+        <v>121.5759418094487</v>
       </c>
     </row>
     <row r="424">
@@ -13149,15 +13149,15 @@
         <v>125.73253</v>
       </c>
       <c r="F424" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H424" t="n">
-        <v>475.7548095131403</v>
+        <v>213.2182452585202</v>
       </c>
     </row>
     <row r="425">
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>374.4568889247058</v>
+        <v>176.2503739454197</v>
       </c>
     </row>
     <row r="426">
@@ -13209,15 +13209,15 @@
         <v>144.26477</v>
       </c>
       <c r="F426" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H426" t="n">
-        <v>398.5444258603678</v>
+        <v>231.1188408667959</v>
       </c>
     </row>
     <row r="427">
@@ -13239,15 +13239,15 @@
         <v>109.89436</v>
       </c>
       <c r="F427" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H427" t="n">
-        <v>477.6547662961582</v>
+        <v>213.4509778017186</v>
       </c>
     </row>
     <row r="428">
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>372.3583100653588</v>
+        <v>181.948223952247</v>
       </c>
     </row>
     <row r="429">
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>376.8661815300433</v>
+        <v>94.86397367730432</v>
       </c>
     </row>
     <row r="430">
@@ -13337,7 +13337,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>382.8441201566035</v>
+        <v>100.5714524373624</v>
       </c>
     </row>
     <row r="431">
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>330.9711404490843</v>
+        <v>48.39588948557887</v>
       </c>
     </row>
     <row r="432">
@@ -13389,15 +13389,15 @@
         <v>49.8474</v>
       </c>
       <c r="F432" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H432" t="n">
-        <v>396.4694872636811</v>
+        <v>463.4459507527332</v>
       </c>
     </row>
     <row r="433">
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>548.1075770880702</v>
+        <v>433.5621327582323</v>
       </c>
     </row>
     <row r="434">
@@ -13449,15 +13449,15 @@
         <v>138.73463</v>
       </c>
       <c r="F434" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H434" t="n">
-        <v>338.3448745348402</v>
+        <v>229.0852832585927</v>
       </c>
     </row>
     <row r="435">
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>364.9139797676369</v>
+        <v>172.6159711788848</v>
       </c>
     </row>
     <row r="436">
@@ -13517,7 +13517,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>400.3918586212197</v>
+        <v>117.7951780549381</v>
       </c>
     </row>
     <row r="437">
@@ -13547,7 +13547,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>379.8599159448746</v>
+        <v>97.45745982829436</v>
       </c>
     </row>
     <row r="438">
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>383.8761460419659</v>
+        <v>101.481381795035</v>
       </c>
     </row>
     <row r="439">
@@ -13599,15 +13599,15 @@
         <v>95.54351964</v>
       </c>
       <c r="F439" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H439" t="n">
-        <v>523.1538446003622</v>
+        <v>510.997654198796</v>
       </c>
     </row>
     <row r="440">
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>540.4447070157765</v>
+        <v>429.4902768901852</v>
       </c>
     </row>
     <row r="441">
@@ -13667,7 +13667,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>541.063100766626</v>
+        <v>260.2853585002077</v>
       </c>
     </row>
     <row r="442">
@@ -13697,7 +13697,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>361.7951034920814</v>
+        <v>208.5962880424154</v>
       </c>
     </row>
     <row r="443">
@@ -13727,7 +13727,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>379.865662713909</v>
+        <v>98.25808763279977</v>
       </c>
     </row>
     <row r="444">
@@ -13749,15 +13749,15 @@
         <v>86.38211000000001</v>
       </c>
       <c r="F444" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H444" t="n">
-        <v>472.3741090501651</v>
+        <v>208.4277253435319</v>
       </c>
     </row>
     <row r="445">
@@ -13779,15 +13779,15 @@
         <v>90.25793999999999</v>
       </c>
       <c r="F445" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H445" t="n">
-        <v>478.0656556116565</v>
+        <v>212.3386261781216</v>
       </c>
     </row>
     <row r="446">
@@ -13809,15 +13809,15 @@
         <v>142.70429</v>
       </c>
       <c r="F446" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H446" t="n">
-        <v>470.8794772176558</v>
+        <v>209.6504118209775</v>
       </c>
     </row>
     <row r="447">
@@ -13847,7 +13847,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>376.3643359901362</v>
+        <v>182.7667459903581</v>
       </c>
     </row>
     <row r="448">
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>539.3000932963816</v>
+        <v>423.5769488863627</v>
       </c>
     </row>
     <row r="449">
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>377.8027639282422</v>
+        <v>95.67790461919937</v>
       </c>
     </row>
     <row r="450">
@@ -13929,15 +13929,15 @@
         <v>81.9524</v>
       </c>
       <c r="F450" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H450" t="n">
-        <v>423.1133016556792</v>
+        <v>484.1532863787845</v>
       </c>
     </row>
     <row r="451">
@@ -13959,15 +13959,15 @@
         <v>129.72508</v>
       </c>
       <c r="F451" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H451" t="n">
-        <v>398.4308918550063</v>
+        <v>228.5218675824255</v>
       </c>
     </row>
     <row r="452">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>384.5226986211789</v>
+        <v>102.6353178628117</v>
       </c>
     </row>
     <row r="453">
@@ -14019,15 +14019,15 @@
         <v>137.67475</v>
       </c>
       <c r="F453" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H453" t="n">
-        <v>289.6683614717405</v>
+        <v>301.0507133735346</v>
       </c>
     </row>
     <row r="454">
@@ -14049,15 +14049,15 @@
         <v>91.25033126999999</v>
       </c>
       <c r="F454" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H454" t="n">
-        <v>476.671625154577</v>
+        <v>386.2146034980639</v>
       </c>
     </row>
     <row r="455">
@@ -14087,7 +14087,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>379.2930854802572</v>
+        <v>97.23843853479993</v>
       </c>
     </row>
     <row r="456">
@@ -14117,7 +14117,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>384.8164371505356</v>
+        <v>102.4918480857375</v>
       </c>
     </row>
     <row r="457">
@@ -14139,15 +14139,15 @@
         <v>33.4468</v>
       </c>
       <c r="F457" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H457" t="n">
-        <v>471.1318091223583</v>
+        <v>207.4009137645875</v>
       </c>
     </row>
     <row r="458">
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>544.1825747253724</v>
+        <v>428.9279411296831</v>
       </c>
     </row>
     <row r="459">
@@ -14199,15 +14199,15 @@
         <v>99.37579999999998</v>
       </c>
       <c r="F459" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H459" t="n">
-        <v>399.465320450838</v>
+        <v>229.5591365467445</v>
       </c>
     </row>
     <row r="460">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>369.0119065625322</v>
+        <v>175.6247251323167</v>
       </c>
     </row>
     <row r="461">
@@ -14267,7 +14267,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>370.650238082961</v>
+        <v>175.3296764752763</v>
       </c>
     </row>
     <row r="462">
@@ -14297,7 +14297,7 @@
         </is>
       </c>
       <c r="H462" t="n">
-        <v>333.6557619236073</v>
+        <v>51.09998502013926</v>
       </c>
     </row>
     <row r="463">
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>382.0640370627376</v>
+        <v>99.97599824829125</v>
       </c>
     </row>
     <row r="464">
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>362.2230741759088</v>
+        <v>168.7811319371953</v>
       </c>
     </row>
     <row r="465">
@@ -14379,15 +14379,15 @@
         <v>97.37148000000001</v>
       </c>
       <c r="F465" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H465" t="n">
-        <v>474.2378592001739</v>
+        <v>211.6732813870892</v>
       </c>
     </row>
     <row r="466">
@@ -14409,15 +14409,15 @@
         <v>130.5938</v>
       </c>
       <c r="F466" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H466" t="n">
-        <v>401.665465879754</v>
+        <v>232.6220725104062</v>
       </c>
     </row>
     <row r="467">
@@ -14447,7 +14447,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>382.3170143239886</v>
+        <v>100.092607826785</v>
       </c>
     </row>
     <row r="468">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>379.0448476203267</v>
+        <v>96.94585824993405</v>
       </c>
     </row>
     <row r="469">
@@ -14507,7 +14507,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>374.9042615607714</v>
+        <v>178.0547726996159</v>
       </c>
     </row>
     <row r="470">
@@ -14529,15 +14529,15 @@
         <v>123.36434</v>
       </c>
       <c r="F470" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H470" t="n">
-        <v>473.324159641636</v>
+        <v>209.6007710482695</v>
       </c>
     </row>
     <row r="471">
@@ -14559,15 +14559,15 @@
         <v>173.58828</v>
       </c>
       <c r="F471" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H471" t="n">
-        <v>480.2135545670378</v>
+        <v>217.769738655443</v>
       </c>
     </row>
     <row r="472">
@@ -14597,7 +14597,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>385.2222955395411</v>
+        <v>102.700602997662</v>
       </c>
     </row>
     <row r="473">
@@ -14627,7 +14627,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>367.3860009118215</v>
+        <v>172.7706883374275</v>
       </c>
     </row>
     <row r="474">
@@ -14657,7 +14657,7 @@
         </is>
       </c>
       <c r="H474" t="n">
-        <v>542.1827885381606</v>
+        <v>429.3340900803877</v>
       </c>
     </row>
     <row r="475">
@@ -14687,7 +14687,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>381.8848835748896</v>
+        <v>99.365783649566</v>
       </c>
     </row>
     <row r="476">
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>538.5790438625913</v>
+        <v>426.3835440125061</v>
       </c>
     </row>
     <row r="477">
@@ -14747,7 +14747,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>368.6459573800726</v>
+        <v>178.0194198959729</v>
       </c>
     </row>
     <row r="478">
@@ -14769,15 +14769,15 @@
         <v>115.35392</v>
       </c>
       <c r="F478" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H478" t="n">
-        <v>474.7514143995931</v>
+        <v>208.9435669676058</v>
       </c>
     </row>
     <row r="479">
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>373.9469958264402</v>
+        <v>178.8457234807114</v>
       </c>
     </row>
     <row r="480">
@@ -14837,7 +14837,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>389.8667975757295</v>
+        <v>107.3145602966586</v>
       </c>
     </row>
     <row r="481">
@@ -14867,7 +14867,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>356.9198182307821</v>
+        <v>78.34448568653632</v>
       </c>
     </row>
     <row r="482">
@@ -14889,15 +14889,15 @@
         <v>133.14993041</v>
       </c>
       <c r="F482" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H482" t="n">
-        <v>538.4207338192327</v>
+        <v>494.2465546328309</v>
       </c>
     </row>
     <row r="483">
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>486.8211826868632</v>
+        <v>208.6719006944995</v>
       </c>
     </row>
     <row r="484">
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>361.6643405946432</v>
+        <v>173.0380180324195</v>
       </c>
     </row>
     <row r="485">
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>401.930851393678</v>
+        <v>306.8243085037814</v>
       </c>
     </row>
     <row r="486">
@@ -15009,15 +15009,15 @@
         <v>175.2077001</v>
       </c>
       <c r="F486" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H486" t="n">
-        <v>519.2538226536985</v>
+        <v>509.5008732297528</v>
       </c>
     </row>
     <row r="487">
@@ -15039,15 +15039,15 @@
         <v>168.87164</v>
       </c>
       <c r="F487" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H487" t="n">
-        <v>279.902734174244</v>
+        <v>163.7335498059527</v>
       </c>
     </row>
     <row r="488">
@@ -15069,15 +15069,15 @@
         <v>66.75664999999999</v>
       </c>
       <c r="F488" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H488" t="n">
-        <v>421.8829865894261</v>
+        <v>482.7255904190506</v>
       </c>
     </row>
     <row r="489">
@@ -15107,7 +15107,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>369.4452532027314</v>
+        <v>176.3452400412433</v>
       </c>
     </row>
     <row r="490">
@@ -15137,7 +15137,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>378.3849475489089</v>
+        <v>96.72437721924653</v>
       </c>
     </row>
     <row r="491">
@@ -15159,15 +15159,15 @@
         <v>89.62715</v>
       </c>
       <c r="F491" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H491" t="n">
-        <v>421.4524250593868</v>
+        <v>482.017426840228</v>
       </c>
     </row>
     <row r="492">
@@ -15189,15 +15189,15 @@
         <v>43.78264999999999</v>
       </c>
       <c r="F492" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H492" t="n">
-        <v>495.327109267422</v>
+        <v>228.9300086027407</v>
       </c>
     </row>
     <row r="493">
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>357.2115310266433</v>
+        <v>144.5352295904483</v>
       </c>
     </row>
     <row r="494">
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>399.4831107472828</v>
+        <v>304.1258562519051</v>
       </c>
     </row>
     <row r="495">
@@ -15287,7 +15287,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>370.8772421201244</v>
+        <v>176.328593549544</v>
       </c>
     </row>
     <row r="496">
@@ -15309,15 +15309,15 @@
         <v>59.60680000000001</v>
       </c>
       <c r="F496" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H496" t="n">
-        <v>496.2179314352944</v>
+        <v>345.6396454305997</v>
       </c>
     </row>
     <row r="497">
@@ -15339,15 +15339,15 @@
         <v>61.33865</v>
       </c>
       <c r="F497" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H497" t="n">
-        <v>508.6165235388352</v>
+        <v>204.2468831622038</v>
       </c>
     </row>
     <row r="498">
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>320.0585897987742</v>
+        <v>78.46596702303529</v>
       </c>
     </row>
     <row r="499">
@@ -15407,7 +15407,7 @@
         </is>
       </c>
       <c r="H499" t="n">
-        <v>301.6603319138252</v>
+        <v>38.42670238202552</v>
       </c>
     </row>
     <row r="500">
@@ -15429,15 +15429,15 @@
         <v>97.11096000000002</v>
       </c>
       <c r="F500" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H500" t="n">
-        <v>399.3228032090287</v>
+        <v>228.1579527766796</v>
       </c>
     </row>
     <row r="501">
@@ -15459,15 +15459,15 @@
         <v>77.12655000000001</v>
       </c>
       <c r="F501" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H501" t="n">
-        <v>396.5711271812636</v>
+        <v>229.1174983035737</v>
       </c>
     </row>
     <row r="502">
@@ -15497,7 +15497,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>403.9857614874821</v>
+        <v>121.9724126682299</v>
       </c>
     </row>
     <row r="503">
@@ -15519,15 +15519,15 @@
         <v>39.40545</v>
       </c>
       <c r="F503" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H503" t="n">
-        <v>399.6670938287053</v>
+        <v>229.178044449383</v>
       </c>
     </row>
     <row r="504">
@@ -15549,15 +15549,15 @@
         <v>51.32812</v>
       </c>
       <c r="F504" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H504" t="n">
-        <v>429.5073032500679</v>
+        <v>216.9896041973278</v>
       </c>
     </row>
     <row r="505">
@@ -15587,7 +15587,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>394.7884522559071</v>
+        <v>112.4827109906133</v>
       </c>
     </row>
   </sheetData>

--- a/clustered_output.xlsx
+++ b/clustered_output.xlsx
@@ -489,15 +489,15 @@
         <v>41.29720544</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>293.8460057247369</v>
+        <v>330.9635282855404</v>
       </c>
     </row>
     <row r="3">
@@ -519,15 +519,15 @@
         <v>55.87958479999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>122.4928162679067</v>
+        <v>117.9924090723754</v>
       </c>
     </row>
     <row r="4">
@@ -549,15 +549,15 @@
         <v>33.26804828</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>365.5697738719786</v>
+        <v>426.9669887847988</v>
       </c>
     </row>
     <row r="5">
@@ -579,15 +579,15 @@
         <v>93.98859224</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>137.1836921009171</v>
+        <v>121.6518811104223</v>
       </c>
     </row>
     <row r="6">
@@ -609,15 +609,15 @@
         <v>40.42737347999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>370.9274282971861</v>
+        <v>420.4712712853633</v>
       </c>
     </row>
     <row r="7">
@@ -639,15 +639,15 @@
         <v>63.74664785</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>135.1668889158399</v>
+        <v>108.1103102442499</v>
       </c>
     </row>
     <row r="8">
@@ -669,15 +669,15 @@
         <v>86.27647392</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>245.074598671275</v>
+        <v>236.9722186769305</v>
       </c>
     </row>
     <row r="9">
@@ -699,15 +699,15 @@
         <v>91.16850180000002</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>304.8226550499002</v>
+        <v>295.3716828864031</v>
       </c>
     </row>
     <row r="10">
@@ -729,15 +729,15 @@
         <v>86.99766654</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>466.4283882980909</v>
+        <v>495.1232190037021</v>
       </c>
     </row>
     <row r="11">
@@ -759,15 +759,15 @@
         <v>82.87167607000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>472.7473727202855</v>
+        <v>492.2082518359087</v>
       </c>
     </row>
     <row r="12">
@@ -789,15 +789,15 @@
         <v>113.41016794</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>151.0314023786419</v>
+        <v>128.9441347688719</v>
       </c>
     </row>
     <row r="13">
@@ -819,15 +819,15 @@
         <v>90.7568601</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>155.8689391528941</v>
+        <v>130.2855787087994</v>
       </c>
     </row>
     <row r="14">
@@ -849,15 +849,15 @@
         <v>129.90572294</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>170.9279161682704</v>
+        <v>146.4901253335264</v>
       </c>
     </row>
     <row r="15">
@@ -879,15 +879,15 @@
         <v>39.66574248000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>413.5495142717604</v>
+        <v>453.1047927312811</v>
       </c>
     </row>
     <row r="16">
@@ -909,15 +909,15 @@
         <v>76.75563604999999</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>414.1680610379193</v>
+        <v>401.849670130051</v>
       </c>
     </row>
     <row r="17">
@@ -939,15 +939,15 @@
         <v>71.55889309999998</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>155.8711978103603</v>
+        <v>128.5054911990155</v>
       </c>
     </row>
     <row r="18">
@@ -969,15 +969,15 @@
         <v>112.80354775</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>197.3786891663952</v>
+        <v>179.8330479062113</v>
       </c>
     </row>
     <row r="19">
@@ -999,15 +999,15 @@
         <v>73.57074283999999</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>150.8606934652393</v>
+        <v>130.5207868271966</v>
       </c>
     </row>
     <row r="20">
@@ -1029,15 +1029,15 @@
         <v>48.18771840000001</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>147.942072551742</v>
+        <v>170.3468154702016</v>
       </c>
     </row>
     <row r="21">
@@ -1059,15 +1059,15 @@
         <v>137.72677575</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>170.0748304559448</v>
+        <v>147.6369671603444</v>
       </c>
     </row>
     <row r="22">
@@ -1089,15 +1089,15 @@
         <v>61.96439013000001</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>274.7525032714101</v>
+        <v>276.1174878980499</v>
       </c>
     </row>
     <row r="23">
@@ -1119,15 +1119,15 @@
         <v>57.01195806</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>422.7970840515572</v>
+        <v>465.5664978287974</v>
       </c>
     </row>
     <row r="24">
@@ -1149,15 +1149,15 @@
         <v>75.03426994</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>44.80763566563145</v>
+        <v>20.47034300213973</v>
       </c>
     </row>
     <row r="25">
@@ -1179,15 +1179,15 @@
         <v>45.991</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>392.7470920930622</v>
+        <v>440.6263987667413</v>
       </c>
     </row>
     <row r="26">
@@ -1209,15 +1209,15 @@
         <v>69.51707707</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>296.4696464613529</v>
+        <v>287.0633257945925</v>
       </c>
     </row>
     <row r="27">
@@ -1239,15 +1239,15 @@
         <v>118.63043667</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>162.1806222902383</v>
+        <v>137.5875559259532</v>
       </c>
     </row>
     <row r="28">
@@ -1269,15 +1269,15 @@
         <v>39.05642559</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>390.3002980085579</v>
+        <v>437.5011742973805</v>
       </c>
     </row>
     <row r="29">
@@ -1299,15 +1299,15 @@
         <v>51.11150699</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>106.6790260503075</v>
+        <v>86.28571933028022</v>
       </c>
     </row>
     <row r="30">
@@ -1329,15 +1329,15 @@
         <v>90.55661511999999</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>260.1363480138145</v>
+        <v>285.2711516650368</v>
       </c>
     </row>
     <row r="31">
@@ -1359,15 +1359,15 @@
         <v>80.49179736000001</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>156.190021202696</v>
+        <v>137.8003887622026</v>
       </c>
     </row>
     <row r="32">
@@ -1389,15 +1389,15 @@
         <v>137.7462625</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>160.9219624355327</v>
+        <v>139.3399391111659</v>
       </c>
     </row>
     <row r="33">
@@ -1419,15 +1419,15 @@
         <v>82.06561287</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>398.7773663232627</v>
+        <v>446.4715004339711</v>
       </c>
     </row>
     <row r="34">
@@ -1449,15 +1449,15 @@
         <v>40.91439332</v>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>159.2187052602542</v>
+        <v>137.0910817780116</v>
       </c>
     </row>
     <row r="35">
@@ -1479,15 +1479,15 @@
         <v>94.20747311999999</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>159.2061091161018</v>
+        <v>137.1927821035483</v>
       </c>
     </row>
     <row r="36">
@@ -1509,15 +1509,15 @@
         <v>51.34208147000001</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>467.3803848016624</v>
+        <v>495.716185770717</v>
       </c>
     </row>
     <row r="37">
@@ -1539,15 +1539,15 @@
         <v>89.43269527999999</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>44.22068792538425</v>
+        <v>20.19869826917071</v>
       </c>
     </row>
     <row r="38">
@@ -1569,15 +1569,15 @@
         <v>87.62353223</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>155.3531487189899</v>
+        <v>132.5567661736015</v>
       </c>
     </row>
     <row r="39">
@@ -1599,15 +1599,15 @@
         <v>113.62947597</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>384.5306082334927</v>
+        <v>432.38924585193</v>
       </c>
     </row>
     <row r="40">
@@ -1629,15 +1629,15 @@
         <v>97.86042042</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>284.4129910582891</v>
+        <v>275.726143177566</v>
       </c>
     </row>
     <row r="41">
@@ -1659,15 +1659,15 @@
         <v>120.70724466</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>24.49259868729828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1689,15 +1689,15 @@
         <v>63.64605510000001</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>230.7789116574628</v>
+        <v>265.3216686549943</v>
       </c>
     </row>
     <row r="43">
@@ -1719,15 +1719,15 @@
         <v>79.88549751000001</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>94.04767826631056</v>
+        <v>113.2095459182907</v>
       </c>
     </row>
     <row r="44">
@@ -1749,15 +1749,15 @@
         <v>75.97018895000001</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>382.7309042653473</v>
+        <v>444.1175443051316</v>
       </c>
     </row>
     <row r="45">
@@ -1779,15 +1779,15 @@
         <v>58.83139722999999</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>277.0434321345084</v>
+        <v>266.6468275894603</v>
       </c>
     </row>
     <row r="46">
@@ -1809,15 +1809,15 @@
         <v>24.03516849</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>363.3676583725137</v>
+        <v>407.277294246931</v>
       </c>
     </row>
     <row r="47">
@@ -1839,15 +1839,15 @@
         <v>17.60890872</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>367.859288993661</v>
+        <v>413.8102117955148</v>
       </c>
     </row>
     <row r="48">
@@ -1869,15 +1869,15 @@
         <v>82.63783919000001</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>148.5993207899491</v>
+        <v>122.8011678761479</v>
       </c>
     </row>
     <row r="49">
@@ -1899,15 +1899,15 @@
         <v>56.29949515999999</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>394.3261874511825</v>
+        <v>442.4265618572776</v>
       </c>
     </row>
     <row r="50">
@@ -1929,15 +1929,15 @@
         <v>47.27391910999999</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>466.862664902199</v>
+        <v>494.2392037869573</v>
       </c>
     </row>
     <row r="51">
@@ -1959,15 +1959,15 @@
         <v>55.12580752</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>244.0476712680346</v>
+        <v>235.567208404973</v>
       </c>
     </row>
     <row r="52">
@@ -1989,15 +1989,15 @@
         <v>70.25959358</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>105.0335556921193</v>
+        <v>127.9311147058719</v>
       </c>
     </row>
     <row r="53">
@@ -2019,15 +2019,15 @@
         <v>62.59155026999998</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>109.7389620112709</v>
+        <v>85.96947799636601</v>
       </c>
     </row>
     <row r="54">
@@ -2049,15 +2049,15 @@
         <v>78.94616125999998</v>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>108.6104453741741</v>
+        <v>118.4108809723095</v>
       </c>
     </row>
     <row r="55">
@@ -2079,15 +2079,15 @@
         <v>101.76988238</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>164.3915028407905</v>
+        <v>141.7811728221151</v>
       </c>
     </row>
     <row r="56">
@@ -2109,15 +2109,15 @@
         <v>44.19095989</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>462.2694883273145</v>
+        <v>490.0243432034919</v>
       </c>
     </row>
     <row r="57">
@@ -2139,15 +2139,15 @@
         <v>93.80458936000001</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>378.9423803573275</v>
+        <v>392.1441159670266</v>
       </c>
     </row>
     <row r="58">
@@ -2169,15 +2169,15 @@
         <v>49.10406079999999</v>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>100.7259767775823</v>
+        <v>124.8455044460658</v>
       </c>
     </row>
     <row r="59">
@@ -2199,15 +2199,15 @@
         <v>99.07280474</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>165.351606625248</v>
+        <v>145.9883362263176</v>
       </c>
     </row>
     <row r="60">
@@ -2229,15 +2229,15 @@
         <v>69.66181495000001</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>155.0573123555761</v>
+        <v>133.1781377095647</v>
       </c>
     </row>
     <row r="61">
@@ -2259,15 +2259,15 @@
         <v>157.49350527</v>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>109.6785426341018</v>
+        <v>132.4012953218188</v>
       </c>
     </row>
     <row r="62">
@@ -2289,15 +2289,15 @@
         <v>69.61420304000001</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>146.6430460690046</v>
+        <v>123.0549928591128</v>
       </c>
     </row>
     <row r="63">
@@ -2319,15 +2319,15 @@
         <v>15.037</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>393.1682837749015</v>
+        <v>440.5761630353377</v>
       </c>
     </row>
     <row r="64">
@@ -2349,15 +2349,15 @@
         <v>33.56141599999999</v>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>245.079558964301</v>
+        <v>237.0082605430272</v>
       </c>
     </row>
     <row r="65">
@@ -2379,15 +2379,15 @@
         <v>122.2742197</v>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>92.73717022738394</v>
+        <v>112.1216799225184</v>
       </c>
     </row>
     <row r="66">
@@ -2409,15 +2409,15 @@
         <v>29.31689904</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>299.3569840336716</v>
+        <v>290.2997824974207</v>
       </c>
     </row>
     <row r="67">
@@ -2439,15 +2439,15 @@
         <v>24.08448896</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>144.2270060908566</v>
+        <v>120.0711060212944</v>
       </c>
     </row>
     <row r="68">
@@ -2469,15 +2469,15 @@
         <v>59.56919848</v>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>103.496349890505</v>
+        <v>95.52643598416643</v>
       </c>
     </row>
     <row r="69">
@@ -2499,15 +2499,15 @@
         <v>61.17361757</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>68.27692687408248</v>
+        <v>20.41596783227257</v>
       </c>
     </row>
     <row r="70">
@@ -2529,15 +2529,15 @@
         <v>45.19398898999999</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>160.2128384245894</v>
+        <v>134.7397854755224</v>
       </c>
     </row>
     <row r="71">
@@ -2559,15 +2559,15 @@
         <v>8.5903492</v>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>100.7259767775823</v>
+        <v>124.8455044460658</v>
       </c>
     </row>
     <row r="72">
@@ -2589,15 +2589,15 @@
         <v>77.60705583999999</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>153.1285040266745</v>
+        <v>126.3772556143692</v>
       </c>
     </row>
     <row r="73">
@@ -2619,15 +2619,15 @@
         <v>27.84522936</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>409.2001225630211</v>
+        <v>449.7586404666938</v>
       </c>
     </row>
     <row r="74">
@@ -2649,15 +2649,15 @@
         <v>121.24150382</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>151.6020550227136</v>
+        <v>127.1359911457164</v>
       </c>
     </row>
     <row r="75">
@@ -2679,15 +2679,15 @@
         <v>109.77473927</v>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>96.58126533093416</v>
+        <v>118.9906694931409</v>
       </c>
     </row>
     <row r="76">
@@ -2709,15 +2709,15 @@
         <v>27.96024677</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>450.0229442223006</v>
+        <v>483.7945945807476</v>
       </c>
     </row>
     <row r="77">
@@ -2739,15 +2739,15 @@
         <v>127.09983192</v>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>103.6119916373755</v>
+        <v>127.0006139161995</v>
       </c>
     </row>
     <row r="78">
@@ -2769,15 +2769,15 @@
         <v>40.97559472</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>190.6825132721265</v>
+        <v>203.6346669013843</v>
       </c>
     </row>
     <row r="79">
@@ -2799,15 +2799,15 @@
         <v>55.95136335999999</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>223.9844703950944</v>
+        <v>234.5085396974142</v>
       </c>
     </row>
     <row r="80">
@@ -2829,15 +2829,15 @@
         <v>99.95687511999999</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>168.4133991841169</v>
+        <v>143.7534492312146</v>
       </c>
     </row>
     <row r="81">
@@ -2859,15 +2859,15 @@
         <v>171.25894002</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>159.9084196272836</v>
+        <v>133.7006511831521</v>
       </c>
     </row>
     <row r="82">
@@ -2889,15 +2889,15 @@
         <v>108.25222513</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>155.1193933778405</v>
+        <v>128.6823365844351</v>
       </c>
     </row>
     <row r="83">
@@ -2919,15 +2919,15 @@
         <v>152.37332232</v>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>109.7499568719103</v>
+        <v>132.6130702067358</v>
       </c>
     </row>
     <row r="84">
@@ -2949,15 +2949,15 @@
         <v>137.64539505</v>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>103.1628998334891</v>
+        <v>125.6521233991047</v>
       </c>
     </row>
     <row r="85">
@@ -2979,15 +2979,15 @@
         <v>98.88650038</v>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>93.89827386045394</v>
+        <v>113.4975601647661</v>
       </c>
     </row>
     <row r="86">
@@ -3009,15 +3009,15 @@
         <v>174.43258149</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>154.4089620521199</v>
+        <v>130.2231289710547</v>
       </c>
     </row>
     <row r="87">
@@ -3039,15 +3039,15 @@
         <v>131.72022438</v>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>297.954671485222</v>
+        <v>288.7402552400748</v>
       </c>
     </row>
     <row r="88">
@@ -3069,15 +3069,15 @@
         <v>128.67002752</v>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>244.9376359487637</v>
+        <v>236.5461713897413</v>
       </c>
     </row>
     <row r="89">
@@ -3099,15 +3099,15 @@
         <v>151.83197394</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>158.5499688032886</v>
+        <v>135.6068269194521</v>
       </c>
     </row>
     <row r="90">
@@ -3129,15 +3129,15 @@
         <v>70.43858698000003</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>158.4325457480821</v>
+        <v>133.4495554787986</v>
       </c>
     </row>
     <row r="91">
@@ -3159,15 +3159,15 @@
         <v>165.86665209</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>150.0773248273609</v>
+        <v>124.0579963162462</v>
       </c>
     </row>
     <row r="92">
@@ -3189,15 +3189,15 @@
         <v>160.7944185</v>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>111.1930211145544</v>
+        <v>134.3726052010849</v>
       </c>
     </row>
     <row r="93">
@@ -3219,15 +3219,15 @@
         <v>114.30460316</v>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>103.1395370676297</v>
+        <v>125.8855478394724</v>
       </c>
     </row>
     <row r="94">
@@ -3249,15 +3249,15 @@
         <v>27.65862036</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>157.2643207295644</v>
+        <v>131.7009008617561</v>
       </c>
     </row>
     <row r="95">
@@ -3279,15 +3279,15 @@
         <v>107.20581291</v>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>110.9238212584267</v>
+        <v>133.9028375627812</v>
       </c>
     </row>
     <row r="96">
@@ -3309,15 +3309,15 @@
         <v>132.81126806</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>154.3148811061609</v>
+        <v>133.3419133050184</v>
       </c>
     </row>
     <row r="97">
@@ -3339,15 +3339,15 @@
         <v>151.87199567</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>160.7866229667267</v>
+        <v>136.3714144979849</v>
       </c>
     </row>
     <row r="98">
@@ -3369,15 +3369,15 @@
         <v>97.51930487999999</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>153.2436065110408</v>
+        <v>130.4915498302243</v>
       </c>
     </row>
     <row r="99">
@@ -3399,15 +3399,15 @@
         <v>62.68683512</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>394.5056466031788</v>
+        <v>442.2738823209808</v>
       </c>
     </row>
     <row r="100">
@@ -3429,15 +3429,15 @@
         <v>164.09465016</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>163.2868500698719</v>
+        <v>139.9394903277591</v>
       </c>
     </row>
     <row r="101">
@@ -3459,15 +3459,15 @@
         <v>115.75139108</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>150.4724269081669</v>
+        <v>128.2753586164148</v>
       </c>
     </row>
     <row r="102">
@@ -3489,15 +3489,15 @@
         <v>112.73454219</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>140.3539978684227</v>
+        <v>116.0060286591594</v>
       </c>
     </row>
     <row r="103">
@@ -3519,15 +3519,15 @@
         <v>165.16716377</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>147.6036965257908</v>
+        <v>119.7946518548475</v>
       </c>
     </row>
     <row r="104">
@@ -3549,15 +3549,15 @@
         <v>98.30353936999998</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>140.9713963838633</v>
+        <v>117.7208691827655</v>
       </c>
     </row>
     <row r="105">
@@ -3579,15 +3579,15 @@
         <v>64.32811749000001</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>382.5222745361521</v>
+        <v>443.7056571528461</v>
       </c>
     </row>
     <row r="106">
@@ -3609,15 +3609,15 @@
         <v>143.1621979</v>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>262.7324413613346</v>
+        <v>287.2407268146017</v>
       </c>
     </row>
     <row r="107">
@@ -3639,15 +3639,15 @@
         <v>62.72158742000001</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>463.6203705187395</v>
+        <v>491.1606421189047</v>
       </c>
     </row>
     <row r="108">
@@ -3669,15 +3669,15 @@
         <v>135.79601133</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>390.2487772391969</v>
+        <v>438.3360268021133</v>
       </c>
     </row>
     <row r="109">
@@ -3699,15 +3699,15 @@
         <v>67.78453388</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>153.539195695105</v>
+        <v>128.4727129154797</v>
       </c>
     </row>
     <row r="110">
@@ -3729,15 +3729,15 @@
         <v>135.40894881</v>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>297.4728206135632</v>
+        <v>288.3934749946374</v>
       </c>
     </row>
     <row r="111">
@@ -3759,15 +3759,15 @@
         <v>134.30264618</v>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>157.7435654334739</v>
+        <v>131.4380690737538</v>
       </c>
     </row>
     <row r="112">
@@ -3789,15 +3789,15 @@
         <v>107.39169483</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>146.3339933783038</v>
+        <v>121.1765276823574</v>
       </c>
     </row>
     <row r="113">
@@ -3819,15 +3819,15 @@
         <v>92.21966651000001</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>149.9757318464934</v>
+        <v>121.6051186359468</v>
       </c>
     </row>
     <row r="114">
@@ -3849,15 +3849,15 @@
         <v>46.65942816</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>275.4336495404298</v>
+        <v>315.3898871045468</v>
       </c>
     </row>
     <row r="115">
@@ -3879,15 +3879,15 @@
         <v>61.25313789</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>367.0969959282192</v>
+        <v>420.9097798142605</v>
       </c>
     </row>
     <row r="116">
@@ -3909,15 +3909,15 @@
         <v>95.79522047999998</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>143.5474732221657</v>
+        <v>117.1189359683959</v>
       </c>
     </row>
     <row r="117">
@@ -3939,15 +3939,15 @@
         <v>131.4488539</v>
       </c>
       <c r="F117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>106.0711509208065</v>
+        <v>128.1772702393585</v>
       </c>
     </row>
     <row r="118">
@@ -3969,15 +3969,15 @@
         <v>139.22461155</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>158.0974000785128</v>
+        <v>134.3931990270278</v>
       </c>
     </row>
     <row r="119">
@@ -3999,15 +3999,15 @@
         <v>69.87724643999999</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>463.8843261091552</v>
+        <v>491.9232670955004</v>
       </c>
     </row>
     <row r="120">
@@ -4029,15 +4029,15 @@
         <v>26.29534809</v>
       </c>
       <c r="F120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>297.8104472791561</v>
+        <v>288.7137580132629</v>
       </c>
     </row>
     <row r="121">
@@ -4059,15 +4059,15 @@
         <v>124.64185643</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>162.1540802945918</v>
+        <v>139.8497216179582</v>
       </c>
     </row>
     <row r="122">
@@ -4089,15 +4089,15 @@
         <v>67.21328875</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>150.4196753751032</v>
+        <v>127.549787869981</v>
       </c>
     </row>
     <row r="123">
@@ -4119,15 +4119,15 @@
         <v>104.41013483</v>
       </c>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>40.73116379217367</v>
+        <v>17.16754590109464</v>
       </c>
     </row>
     <row r="124">
@@ -4149,15 +4149,15 @@
         <v>55.17039302000001</v>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>151.2941074551429</v>
+        <v>125.9160263320814</v>
       </c>
     </row>
     <row r="125">
@@ -4179,15 +4179,15 @@
         <v>156.16160591</v>
       </c>
       <c r="F125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>137.6423599800942</v>
+        <v>115.1672335283907</v>
       </c>
     </row>
     <row r="126">
@@ -4209,15 +4209,15 @@
         <v>86.21620850000002</v>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>141.7442910967588</v>
+        <v>111.8178194902709</v>
       </c>
     </row>
     <row r="127">
@@ -4239,15 +4239,15 @@
         <v>71.97972833</v>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>152.1140732346485</v>
+        <v>131.1888744670751</v>
       </c>
     </row>
     <row r="128">
@@ -4269,15 +4269,15 @@
         <v>116.03335498</v>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>148.417679040193</v>
+        <v>123.935072258068</v>
       </c>
     </row>
     <row r="129">
@@ -4299,15 +4299,15 @@
         <v>87.04857329000001</v>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>155.2912736366582</v>
+        <v>131.6487906909689</v>
       </c>
     </row>
     <row r="130">
@@ -4329,15 +4329,15 @@
         <v>141.72703296</v>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>153.7467056988309</v>
+        <v>130.381237786289</v>
       </c>
     </row>
     <row r="131">
@@ -4359,15 +4359,15 @@
         <v>145.58214742</v>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>68.55822665796128</v>
+        <v>2.524349787145492</v>
       </c>
     </row>
     <row r="132">
@@ -4389,15 +4389,15 @@
         <v>148.1403535</v>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>47.08708195175153</v>
+        <v>69.52376245901762</v>
       </c>
     </row>
     <row r="133">
@@ -4419,15 +4419,15 @@
         <v>39.35975862000001</v>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>391.8184530774033</v>
+        <v>439.4150303327746</v>
       </c>
     </row>
     <row r="134">
@@ -4449,15 +4449,15 @@
         <v>121.18436646</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>157.8095881689238</v>
+        <v>132.7490468314282</v>
       </c>
     </row>
     <row r="135">
@@ -4479,15 +4479,15 @@
         <v>174.54029805</v>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>171.5590778179512</v>
+        <v>149.1626153246674</v>
       </c>
     </row>
     <row r="136">
@@ -4509,15 +4509,15 @@
         <v>71.22344247000001</v>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>102.338791598857</v>
+        <v>123.6480037344783</v>
       </c>
     </row>
     <row r="137">
@@ -4539,15 +4539,15 @@
         <v>86.91646299999999</v>
       </c>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>105.4461159483704</v>
+        <v>126.8999961435841</v>
       </c>
     </row>
     <row r="138">
@@ -4569,15 +4569,15 @@
         <v>113.58351808</v>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>154.3020684321744</v>
+        <v>127.3032429697211</v>
       </c>
     </row>
     <row r="139">
@@ -4599,15 +4599,15 @@
         <v>130.82707128</v>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>144.0207040191272</v>
+        <v>121.1956400146447</v>
       </c>
     </row>
     <row r="140">
@@ -4629,15 +4629,15 @@
         <v>83.83990669000001</v>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>388.4867996322367</v>
+        <v>436.7912830403555</v>
       </c>
     </row>
     <row r="141">
@@ -4659,15 +4659,15 @@
         <v>66.93223488999999</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>160.4530529800002</v>
+        <v>135.4344329345909</v>
       </c>
     </row>
     <row r="142">
@@ -4689,15 +4689,15 @@
         <v>94.84938579</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>279.7075176862222</v>
+        <v>280.444170825078</v>
       </c>
     </row>
     <row r="143">
@@ -4719,15 +4719,15 @@
         <v>145.91838293</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>137.8802470023848</v>
+        <v>106.2678263285794</v>
       </c>
     </row>
     <row r="144">
@@ -4749,15 +4749,15 @@
         <v>148.16292628</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>125.8355096270716</v>
+        <v>103.5750652214989</v>
       </c>
     </row>
     <row r="145">
@@ -4779,15 +4779,15 @@
         <v>22.03899181</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>369.1622100435767</v>
+        <v>423.1317561742813</v>
       </c>
     </row>
     <row r="146">
@@ -4809,15 +4809,15 @@
         <v>169.43078549</v>
       </c>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>40.93402369732947</v>
+        <v>16.86922051279774</v>
       </c>
     </row>
     <row r="147">
@@ -4839,15 +4839,15 @@
         <v>115.96496099</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>146.5562506993173</v>
+        <v>120.0628786795913</v>
       </c>
     </row>
     <row r="148">
@@ -4869,15 +4869,15 @@
         <v>97.54827051999999</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>145.0353621763646</v>
+        <v>127.0843658238061</v>
       </c>
     </row>
     <row r="149">
@@ -4899,15 +4899,15 @@
         <v>171.24941356</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>157.1304892525723</v>
+        <v>137.6740764380879</v>
       </c>
     </row>
     <row r="150">
@@ -4929,15 +4929,15 @@
         <v>79.48337347</v>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>121.03539755116</v>
+        <v>98.92679672304133</v>
       </c>
     </row>
     <row r="151">
@@ -4959,15 +4959,15 @@
         <v>21.38957457</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>378.6092271739076</v>
+        <v>427.5095658720282</v>
       </c>
     </row>
     <row r="152">
@@ -4989,15 +4989,15 @@
         <v>56.00126308</v>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>453.0618631701936</v>
+        <v>487.5368227657868</v>
       </c>
     </row>
     <row r="153">
@@ -5019,15 +5019,15 @@
         <v>116.54724109</v>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>150.9465552515387</v>
+        <v>123.5184011830669</v>
       </c>
     </row>
     <row r="154">
@@ -5049,15 +5049,15 @@
         <v>136.56314483</v>
       </c>
       <c r="F154" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>26.39503825315914</v>
+        <v>2.195284483350534</v>
       </c>
     </row>
     <row r="155">
@@ -5079,15 +5079,15 @@
         <v>132.34473269</v>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>139.6648102466222</v>
+        <v>115.0570084748459</v>
       </c>
     </row>
     <row r="156">
@@ -5109,15 +5109,15 @@
         <v>127.67648195</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>147.6298806526679</v>
+        <v>126.05341869692</v>
       </c>
     </row>
     <row r="157">
@@ -5139,15 +5139,15 @@
         <v>101.97064253</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>466.5173357135325</v>
+        <v>494.1176797046688</v>
       </c>
     </row>
     <row r="158">
@@ -5169,15 +5169,15 @@
         <v>64.40666220000001</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>378.5505972995411</v>
+        <v>439.6105513810847</v>
       </c>
     </row>
     <row r="159">
@@ -5199,15 +5199,15 @@
         <v>133.79668708</v>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>166.3585398305499</v>
+        <v>141.1308776121495</v>
       </c>
     </row>
     <row r="160">
@@ -5229,15 +5229,15 @@
         <v>138.15013296</v>
       </c>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>295.1284815246919</v>
+        <v>286.0952964076756</v>
       </c>
     </row>
     <row r="161">
@@ -5259,15 +5259,15 @@
         <v>150.50007586</v>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>148.430521977768</v>
+        <v>128.2123748624244</v>
       </c>
     </row>
     <row r="162">
@@ -5289,15 +5289,15 @@
         <v>93.60651496</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>160.9527014377235</v>
+        <v>137.7535479338831</v>
       </c>
     </row>
     <row r="163">
@@ -5319,15 +5319,15 @@
         <v>129.31327658</v>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>66.16610374030769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -5349,15 +5349,15 @@
         <v>106.88348563</v>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>403.3770685462418</v>
+        <v>422.87760814889</v>
       </c>
     </row>
     <row r="165">
@@ -5379,15 +5379,15 @@
         <v>42.43144776</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>369.9360371615572</v>
+        <v>424.1932020833065</v>
       </c>
     </row>
     <row r="166">
@@ -5409,15 +5409,15 @@
         <v>60.79293023</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>312.3121417069709</v>
+        <v>366.8659341721198</v>
       </c>
     </row>
     <row r="167">
@@ -5439,15 +5439,15 @@
         <v>77.59270448000001</v>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>157.9650373618147</v>
+        <v>136.6273011118156</v>
       </c>
     </row>
     <row r="168">
@@ -5469,15 +5469,15 @@
         <v>53.785478</v>
       </c>
       <c r="F168" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>97.45824180501572</v>
+        <v>116.8619030719691</v>
       </c>
     </row>
     <row r="169">
@@ -5499,15 +5499,15 @@
         <v>145.0125221</v>
       </c>
       <c r="F169" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>43.97404253119719</v>
+        <v>67.14739972868296</v>
       </c>
     </row>
     <row r="170">
@@ -5529,15 +5529,15 @@
         <v>134.76338509</v>
       </c>
       <c r="F170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>140.7851946362896</v>
+        <v>110.0155394868578</v>
       </c>
     </row>
     <row r="171">
@@ -5559,15 +5559,15 @@
         <v>34.09060356</v>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>399.5083708833428</v>
+        <v>441.4650566886497</v>
       </c>
     </row>
     <row r="172">
@@ -5589,15 +5589,15 @@
         <v>103.95516876</v>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>161.5314469475466</v>
+        <v>135.8642245783005</v>
       </c>
     </row>
     <row r="173">
@@ -5619,15 +5619,15 @@
         <v>129.96221128</v>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>152.6882497958964</v>
+        <v>135.5652887863286</v>
       </c>
     </row>
     <row r="174">
@@ -5649,15 +5649,15 @@
         <v>123.25258422</v>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H174" t="n">
-        <v>130.9552456548431</v>
+        <v>108.3634492007963</v>
       </c>
     </row>
     <row r="175">
@@ -5679,15 +5679,15 @@
         <v>114.2480122</v>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H175" t="n">
-        <v>110.1578374848856</v>
+        <v>133.6289924038313</v>
       </c>
     </row>
     <row r="176">
@@ -5709,15 +5709,15 @@
         <v>148.70392757</v>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H176" t="n">
-        <v>198.8890780199291</v>
+        <v>181.4012272520388</v>
       </c>
     </row>
     <row r="177">
@@ -5739,15 +5739,15 @@
         <v>164.48669544</v>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>266.3355288928579</v>
+        <v>291.7330142189344</v>
       </c>
     </row>
     <row r="178">
@@ -5769,15 +5769,15 @@
         <v>149.1072418</v>
       </c>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H178" t="n">
-        <v>387.6774496753766</v>
+        <v>436.0282594747227</v>
       </c>
     </row>
     <row r="179">
@@ -5799,15 +5799,15 @@
         <v>114.08940098</v>
       </c>
       <c r="F179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>143.8721470076325</v>
+        <v>116.4654686920483</v>
       </c>
     </row>
     <row r="180">
@@ -5829,15 +5829,15 @@
         <v>112.05923696</v>
       </c>
       <c r="F180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H180" t="n">
-        <v>140.9664354752053</v>
+        <v>147.1133911629679</v>
       </c>
     </row>
     <row r="181">
@@ -5859,15 +5859,15 @@
         <v>64.98465548</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>142.7213522013847</v>
+        <v>112.1407207819316</v>
       </c>
     </row>
     <row r="182">
@@ -5889,15 +5889,15 @@
         <v>72.72579613999999</v>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H182" t="n">
-        <v>156.9633839319166</v>
+        <v>134.5946867737809</v>
       </c>
     </row>
     <row r="183">
@@ -5919,15 +5919,15 @@
         <v>103.13068804</v>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>156.7968949445768</v>
+        <v>134.9979401079424</v>
       </c>
     </row>
     <row r="184">
@@ -5949,15 +5949,15 @@
         <v>88.39244152999999</v>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H184" t="n">
-        <v>145.3817134522845</v>
+        <v>116.9610396796634</v>
       </c>
     </row>
     <row r="185">
@@ -5979,15 +5979,15 @@
         <v>111.28124526</v>
       </c>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H185" t="n">
-        <v>164.8960223765515</v>
+        <v>141.1914671328136</v>
       </c>
     </row>
     <row r="186">
@@ -6009,15 +6009,15 @@
         <v>77.23146711</v>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H186" t="n">
-        <v>160.1367601744726</v>
+        <v>134.8274477844502</v>
       </c>
     </row>
     <row r="187">
@@ -6039,15 +6039,15 @@
         <v>87.69854039000001</v>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H187" t="n">
-        <v>94.57825916665728</v>
+        <v>115.5589954023719</v>
       </c>
     </row>
     <row r="188">
@@ -6069,15 +6069,15 @@
         <v>104.07446787</v>
       </c>
       <c r="F188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H188" t="n">
-        <v>149.0413074483496</v>
+        <v>124.0243692895168</v>
       </c>
     </row>
     <row r="189">
@@ -6099,15 +6099,15 @@
         <v>135.95829359</v>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H189" t="n">
-        <v>105.1204904123371</v>
+        <v>128.3784927693047</v>
       </c>
     </row>
     <row r="190">
@@ -6129,15 +6129,15 @@
         <v>14.04523848</v>
       </c>
       <c r="F190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H190" t="n">
-        <v>388.2139984601232</v>
+        <v>438.2231249765429</v>
       </c>
     </row>
     <row r="191">
@@ -6159,15 +6159,15 @@
         <v>84.03368023</v>
       </c>
       <c r="F191" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H191" t="n">
-        <v>46.05181255247427</v>
+        <v>68.87078381624423</v>
       </c>
     </row>
     <row r="192">
@@ -6189,15 +6189,15 @@
         <v>37.35482578</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>393.715675009759</v>
+        <v>436.3721841702692</v>
       </c>
     </row>
     <row r="193">
@@ -6219,15 +6219,15 @@
         <v>29.02313882999999</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>365.5773635412867</v>
+        <v>418.9682152063426</v>
       </c>
     </row>
     <row r="194">
@@ -6249,15 +6249,15 @@
         <v>69.75723010999999</v>
       </c>
       <c r="F194" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H194" t="n">
-        <v>90.42836908835832</v>
+        <v>66.87147235620471</v>
       </c>
     </row>
     <row r="195">
@@ -6279,15 +6279,15 @@
         <v>106.29918689</v>
       </c>
       <c r="F195" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H195" t="n">
-        <v>132.9341213620754</v>
+        <v>111.7612942561259</v>
       </c>
     </row>
     <row r="196">
@@ -6309,15 +6309,15 @@
         <v>68.10364146999999</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H196" t="n">
-        <v>148.6479009466308</v>
+        <v>134.711526205172</v>
       </c>
     </row>
     <row r="197">
@@ -6339,15 +6339,15 @@
         <v>51.23457499999999</v>
       </c>
       <c r="F197" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H197" t="n">
-        <v>90.66046051512869</v>
+        <v>113.9739665090551</v>
       </c>
     </row>
     <row r="198">
@@ -6369,15 +6369,15 @@
         <v>62.39533672</v>
       </c>
       <c r="F198" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H198" t="n">
-        <v>138.4670632375975</v>
+        <v>116.9153879128728</v>
       </c>
     </row>
     <row r="199">
@@ -6399,15 +6399,15 @@
         <v>81.51284326</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>144.8737354091315</v>
+        <v>119.4607446504558</v>
       </c>
     </row>
     <row r="200">
@@ -6429,15 +6429,15 @@
         <v>83.68685203999999</v>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>150.6046320137467</v>
+        <v>128.1223886851244</v>
       </c>
     </row>
     <row r="201">
@@ -6459,15 +6459,15 @@
         <v>68.18522616</v>
       </c>
       <c r="F201" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H201" t="n">
-        <v>141.2826203035115</v>
+        <v>114.3936628670256</v>
       </c>
     </row>
     <row r="202">
@@ -6489,15 +6489,15 @@
         <v>80.24099302</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H202" t="n">
-        <v>151.6595942303774</v>
+        <v>133.3570028934936</v>
       </c>
     </row>
     <row r="203">
@@ -6519,15 +6519,15 @@
         <v>42.55748138000001</v>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H203" t="n">
-        <v>68.87397011120331</v>
+        <v>80.39050753268133</v>
       </c>
     </row>
     <row r="204">
@@ -6549,15 +6549,15 @@
         <v>66.30837547</v>
       </c>
       <c r="F204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H204" t="n">
-        <v>125.0677805919528</v>
+        <v>102.4988016091568</v>
       </c>
     </row>
     <row r="205">
@@ -6579,15 +6579,15 @@
         <v>72.1073177</v>
       </c>
       <c r="F205" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H205" t="n">
-        <v>81.78595913441407</v>
+        <v>104.8494011357226</v>
       </c>
     </row>
     <row r="206">
@@ -6609,15 +6609,15 @@
         <v>61.94020108000001</v>
       </c>
       <c r="F206" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H206" t="n">
-        <v>140.0590297326085</v>
+        <v>159.4643923886767</v>
       </c>
     </row>
     <row r="207">
@@ -6639,15 +6639,15 @@
         <v>116.30465114</v>
       </c>
       <c r="F207" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H207" t="n">
-        <v>98.7323172694025</v>
+        <v>120.0040682159923</v>
       </c>
     </row>
     <row r="208">
@@ -6669,15 +6669,15 @@
         <v>66.85576336</v>
       </c>
       <c r="F208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H208" t="n">
-        <v>150.0719903546772</v>
+        <v>169.6926348159986</v>
       </c>
     </row>
     <row r="209">
@@ -6699,15 +6699,15 @@
         <v>88.47867821</v>
       </c>
       <c r="F209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H209" t="n">
-        <v>156.0220450976014</v>
+        <v>136.2060012010795</v>
       </c>
     </row>
     <row r="210">
@@ -6729,15 +6729,15 @@
         <v>75.59825791</v>
       </c>
       <c r="F210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H210" t="n">
-        <v>168.2216933394938</v>
+        <v>145.4749115339448</v>
       </c>
     </row>
     <row r="211">
@@ -6759,15 +6759,15 @@
         <v>112.48154805</v>
       </c>
       <c r="F211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H211" t="n">
-        <v>142.4573195186641</v>
+        <v>122.4259668926803</v>
       </c>
     </row>
     <row r="212">
@@ -6789,15 +6789,15 @@
         <v>105.4919814</v>
       </c>
       <c r="F212" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H212" t="n">
-        <v>87.98069974649448</v>
+        <v>108.1882747316393</v>
       </c>
     </row>
     <row r="213">
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>244.4547600179641</v>
+        <v>229.8607558359462</v>
       </c>
     </row>
     <row r="214">
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>224.1347950788545</v>
+        <v>225.064995129652</v>
       </c>
     </row>
     <row r="215">
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>383.9683452505717</v>
+        <v>419.672814067605</v>
       </c>
     </row>
     <row r="216">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>358.6786998752949</v>
+        <v>377.8634954661895</v>
       </c>
     </row>
     <row r="217">
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>405.3050657897217</v>
+        <v>397.4782412309082</v>
       </c>
     </row>
     <row r="218">
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>343.1529027900015</v>
+        <v>333.5404278771352</v>
       </c>
     </row>
     <row r="219">
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>192.2969368458551</v>
+        <v>230.3482592715248</v>
       </c>
     </row>
     <row r="220">
@@ -7037,7 +7037,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>379.5007289420488</v>
+        <v>415.1807710422817</v>
       </c>
     </row>
     <row r="221">
@@ -7067,7 +7067,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>170.9482929019636</v>
+        <v>193.1966175896344</v>
       </c>
     </row>
     <row r="222">
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>277.5254540437227</v>
+        <v>314.0855088794886</v>
       </c>
     </row>
     <row r="223">
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>346.976523051831</v>
+        <v>384.9642702937756</v>
       </c>
     </row>
     <row r="224">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>167.7758876733445</v>
+        <v>189.8516782079799</v>
       </c>
     </row>
     <row r="225">
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>405.4342490665469</v>
+        <v>396.8570901951181</v>
       </c>
     </row>
     <row r="226">
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>342.2257220137689</v>
+        <v>352.345793583056</v>
       </c>
     </row>
     <row r="227">
@@ -7239,15 +7239,15 @@
         <v>65.836</v>
       </c>
       <c r="F227" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H227" t="n">
-        <v>511.3525973892623</v>
+        <v>537.3485840089204</v>
       </c>
     </row>
     <row r="228">
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>331.1662139980003</v>
+        <v>338.7538155998406</v>
       </c>
     </row>
     <row r="229">
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>381.7256943903093</v>
+        <v>417.4720974985719</v>
       </c>
     </row>
     <row r="230">
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>357.0246673916196</v>
+        <v>376.6730883738524</v>
       </c>
     </row>
     <row r="231">
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>377.0267809314404</v>
+        <v>412.7090821028135</v>
       </c>
     </row>
     <row r="232">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>169.5897000840959</v>
+        <v>192.1475305672869</v>
       </c>
     </row>
     <row r="233">
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>336.4473247808326</v>
+        <v>344.0143888267083</v>
       </c>
     </row>
     <row r="234">
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>349.4569968094802</v>
+        <v>387.4842357033926</v>
       </c>
     </row>
     <row r="235">
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>223.0922603127969</v>
+        <v>224.5517052120445</v>
       </c>
     </row>
     <row r="236">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>172.9088095760513</v>
+        <v>195.3516669208213</v>
       </c>
     </row>
     <row r="237">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>378.5427318889581</v>
+        <v>414.2812049218847</v>
       </c>
     </row>
     <row r="238">
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>181.6944955579513</v>
+        <v>177.962552569528</v>
       </c>
     </row>
     <row r="239">
@@ -7599,15 +7599,15 @@
         <v>111.0064</v>
       </c>
       <c r="F239" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H239" t="n">
-        <v>510.8703195477742</v>
+        <v>536.8344550885704</v>
       </c>
     </row>
     <row r="240">
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>353.6441013146468</v>
+        <v>391.7037606540575</v>
       </c>
     </row>
     <row r="241">
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>405.779922177717</v>
+        <v>397.5562571974353</v>
       </c>
     </row>
     <row r="242">
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>354.4869959095565</v>
+        <v>374.2917936817031</v>
       </c>
     </row>
     <row r="243">
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>378.7680856783614</v>
+        <v>414.4853399375517</v>
       </c>
     </row>
     <row r="244">
@@ -7757,7 +7757,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>449.7335626017817</v>
+        <v>464.1934089637818</v>
       </c>
     </row>
     <row r="245">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>176.5776307618488</v>
+        <v>198.5647588025095</v>
       </c>
     </row>
     <row r="246">
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>341.5759657726773</v>
+        <v>349.3139158828723</v>
       </c>
     </row>
     <row r="247">
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>178.9192601996842</v>
+        <v>201.5696038015792</v>
       </c>
     </row>
     <row r="248">
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>337.8575499479376</v>
+        <v>345.1333457202122</v>
       </c>
     </row>
     <row r="249">
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>375.1955729779149</v>
+        <v>410.8883422646456</v>
       </c>
     </row>
     <row r="250">
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>414.9905506571422</v>
+        <v>408.8581684202446</v>
       </c>
     </row>
     <row r="251">
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>449.8968435611127</v>
+        <v>464.582298371576</v>
       </c>
     </row>
     <row r="252">
@@ -7997,7 +7997,7 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>128.9049887187745</v>
+        <v>32.60451440507697</v>
       </c>
     </row>
     <row r="253">
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>199.9453164122694</v>
+        <v>94.35960271226369</v>
       </c>
     </row>
     <row r="254">
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>295.4992140148996</v>
+        <v>384.5799275406081</v>
       </c>
     </row>
     <row r="255">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>379.6069181231939</v>
+        <v>482.00735820496</v>
       </c>
     </row>
     <row r="256">
@@ -8117,7 +8117,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>380.258306252376</v>
+        <v>482.4906943718859</v>
       </c>
     </row>
     <row r="257">
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>198.7566561597725</v>
+        <v>92.64544990077594</v>
       </c>
     </row>
     <row r="258">
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>157.6723325326645</v>
+        <v>75.2899228366535</v>
       </c>
     </row>
     <row r="259">
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>403.5081622823314</v>
+        <v>508.8891223415916</v>
       </c>
     </row>
     <row r="260">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>475.9405988279751</v>
+        <v>552.3573847787909</v>
       </c>
     </row>
     <row r="261">
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>195.7083783065673</v>
+        <v>102.3489899239865</v>
       </c>
     </row>
     <row r="262">
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>438.5077834249905</v>
+        <v>522.1664319142777</v>
       </c>
     </row>
     <row r="263">
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>188.2066440310786</v>
+        <v>95.57020709971071</v>
       </c>
     </row>
     <row r="264">
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>190.9071943197909</v>
+        <v>96.70476762895548</v>
       </c>
     </row>
     <row r="265">
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>405.0565056120583</v>
+        <v>510.5175932013258</v>
       </c>
     </row>
     <row r="266">
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>301.8636096550673</v>
+        <v>390.1597548737963</v>
       </c>
     </row>
     <row r="267">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>198.4266612290852</v>
+        <v>92.28373519837209</v>
       </c>
     </row>
     <row r="268">
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>518.4040578096872</v>
+        <v>595.7184877137429</v>
       </c>
     </row>
     <row r="269">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>510.6400033426321</v>
+        <v>589.7659034972133</v>
       </c>
     </row>
     <row r="270">
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>197.6583203948707</v>
+        <v>93.68564527290076</v>
       </c>
     </row>
     <row r="271">
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>200.1952793995961</v>
+        <v>94.17527792394209</v>
       </c>
     </row>
     <row r="272">
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>215.1429120314576</v>
+        <v>112.4783746360528</v>
       </c>
     </row>
     <row r="273">
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>189.4037922176628</v>
+        <v>94.45839254828898</v>
       </c>
     </row>
     <row r="274">
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>198.7324288034695</v>
+        <v>92.67265559598945</v>
       </c>
     </row>
     <row r="275">
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>215.2126130343853</v>
+        <v>112.6132028265503</v>
       </c>
     </row>
     <row r="276">
@@ -8717,7 +8717,7 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>193.0481946178191</v>
+        <v>99.02980389832064</v>
       </c>
     </row>
     <row r="277">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="H277" t="n">
-        <v>190.414855387531</v>
+        <v>97.27427688122583</v>
       </c>
     </row>
     <row r="278">
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>197.1251076937621</v>
+        <v>91.50333000873195</v>
       </c>
     </row>
     <row r="279">
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>189.8007120211021</v>
+        <v>95.99397161868814</v>
       </c>
     </row>
     <row r="280">
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>474.2739396380379</v>
+        <v>550.7295808016556</v>
       </c>
     </row>
     <row r="281">
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>106.1462563154388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>189.5541092308563</v>
+        <v>94.37343372652148</v>
       </c>
     </row>
     <row r="283">
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>297.7463062317671</v>
+        <v>386.5114632433878</v>
       </c>
     </row>
     <row r="284">
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>295.1508308036504</v>
+        <v>384.2393599367526</v>
       </c>
     </row>
     <row r="285">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>195.2004775661288</v>
+        <v>99.63501088455672</v>
       </c>
     </row>
     <row r="286">
@@ -9017,7 +9017,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>198.792485816512</v>
+        <v>92.73566034601555</v>
       </c>
     </row>
     <row r="287">
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>211.7593814876636</v>
+        <v>106.8588974613416</v>
       </c>
     </row>
     <row r="288">
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>409.3578444052795</v>
+        <v>515.496387359597</v>
       </c>
     </row>
     <row r="289">
@@ -9107,7 +9107,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>390.9140081015669</v>
+        <v>469.4482391051256</v>
       </c>
     </row>
     <row r="290">
@@ -9129,15 +9129,15 @@
         <v>118.29098</v>
       </c>
       <c r="F290" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H290" t="n">
-        <v>260.0725060296554</v>
+        <v>259.5176719658174</v>
       </c>
     </row>
     <row r="291">
@@ -9159,15 +9159,15 @@
         <v>56.55883999999998</v>
       </c>
       <c r="F291" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H291" t="n">
-        <v>478.6929063561986</v>
+        <v>605.7632706899564</v>
       </c>
     </row>
     <row r="292">
@@ -9189,15 +9189,15 @@
         <v>99.75030000000001</v>
       </c>
       <c r="F292" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H292" t="n">
-        <v>317.4733968405083</v>
+        <v>293.1002567845545</v>
       </c>
     </row>
     <row r="293">
@@ -9219,15 +9219,15 @@
         <v>76.35709999999999</v>
       </c>
       <c r="F293" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H293" t="n">
-        <v>174.1455252776595</v>
+        <v>150.3854486811032</v>
       </c>
     </row>
     <row r="294">
@@ -9249,15 +9249,15 @@
         <v>65.98963999999999</v>
       </c>
       <c r="F294" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H294" t="n">
-        <v>483.6949449878604</v>
+        <v>609.8136359579141</v>
       </c>
     </row>
     <row r="295">
@@ -9279,15 +9279,15 @@
         <v>70.17684000000001</v>
       </c>
       <c r="F295" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H295" t="n">
-        <v>395.2279755294658</v>
+        <v>398.8320502782476</v>
       </c>
     </row>
     <row r="296">
@@ -9309,15 +9309,15 @@
         <v>80.12326000000002</v>
       </c>
       <c r="F296" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H296" t="n">
-        <v>139.904278070824</v>
+        <v>159.1709720886669</v>
       </c>
     </row>
     <row r="297">
@@ -9339,15 +9339,15 @@
         <v>73.27007999999999</v>
       </c>
       <c r="F297" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H297" t="n">
-        <v>518.017243909774</v>
+        <v>514.7670845213308</v>
       </c>
     </row>
     <row r="298">
@@ -9369,15 +9369,15 @@
         <v>113.30992</v>
       </c>
       <c r="F298" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H298" t="n">
-        <v>171.8836861734805</v>
+        <v>168.3179946113131</v>
       </c>
     </row>
     <row r="299">
@@ -9399,15 +9399,15 @@
         <v>43.52612</v>
       </c>
       <c r="F299" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H299" t="n">
-        <v>305.6066734773577</v>
+        <v>428.7166743978141</v>
       </c>
     </row>
     <row r="300">
@@ -9429,15 +9429,15 @@
         <v>108.32342</v>
       </c>
       <c r="F300" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H300" t="n">
-        <v>145.1818212920968</v>
+        <v>159.0016671290651</v>
       </c>
     </row>
     <row r="301">
@@ -9459,15 +9459,15 @@
         <v>51.79328</v>
       </c>
       <c r="F301" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H301" t="n">
-        <v>419.036129462474</v>
+        <v>546.1529639801837</v>
       </c>
     </row>
     <row r="302">
@@ -9489,15 +9489,15 @@
         <v>68.9781</v>
       </c>
       <c r="F302" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H302" t="n">
-        <v>407.1102990416741</v>
+        <v>533.9820761041468</v>
       </c>
     </row>
     <row r="303">
@@ -9519,15 +9519,15 @@
         <v>69.73756</v>
       </c>
       <c r="F303" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H303" t="n">
-        <v>295.353133364184</v>
+        <v>418.1241507146969</v>
       </c>
     </row>
     <row r="304">
@@ -9549,15 +9549,15 @@
         <v>116.13984</v>
       </c>
       <c r="F304" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H304" t="n">
-        <v>302.21659388239</v>
+        <v>423.8519858386172</v>
       </c>
     </row>
     <row r="305">
@@ -9579,15 +9579,15 @@
         <v>100.22104</v>
       </c>
       <c r="F305" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H305" t="n">
-        <v>299.2683693566714</v>
+        <v>421.0250492420701</v>
       </c>
     </row>
     <row r="306">
@@ -9609,15 +9609,15 @@
         <v>124.95866</v>
       </c>
       <c r="F306" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H306" t="n">
-        <v>265.2849324520069</v>
+        <v>264.9868752387629</v>
       </c>
     </row>
     <row r="307">
@@ -9639,15 +9639,15 @@
         <v>106.6222</v>
       </c>
       <c r="F307" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H307" t="n">
-        <v>234.1539906552349</v>
+        <v>210.2618162320152</v>
       </c>
     </row>
     <row r="308">
@@ -9669,15 +9669,15 @@
         <v>37.92908</v>
       </c>
       <c r="F308" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H308" t="n">
-        <v>137.9645027339064</v>
+        <v>156.6116107346159</v>
       </c>
     </row>
     <row r="309">
@@ -9699,15 +9699,15 @@
         <v>76.79181999999999</v>
       </c>
       <c r="F309" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H309" t="n">
-        <v>213.5800407661942</v>
+        <v>334.4914004993488</v>
       </c>
     </row>
     <row r="310">
@@ -9729,15 +9729,15 @@
         <v>47.35968</v>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H310" t="n">
-        <v>505.864554707247</v>
+        <v>495.4572343240575</v>
       </c>
     </row>
     <row r="311">
@@ -9759,15 +9759,15 @@
         <v>153.85138</v>
       </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H311" t="n">
-        <v>140.4766831106095</v>
+        <v>159.3858112034838</v>
       </c>
     </row>
     <row r="312">
@@ -9789,15 +9789,15 @@
         <v>178.5294</v>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H312" t="n">
-        <v>263.2808293594302</v>
+        <v>262.7876734784617</v>
       </c>
     </row>
     <row r="313">
@@ -9819,15 +9819,15 @@
         <v>138.3113</v>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H313" t="n">
-        <v>146.8970220930177</v>
+        <v>161.1344693495137</v>
       </c>
     </row>
     <row r="314">
@@ -9849,15 +9849,15 @@
         <v>148.35608</v>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H314" t="n">
-        <v>252.0220765832538</v>
+        <v>269.070535269441</v>
       </c>
     </row>
     <row r="315">
@@ -9879,15 +9879,15 @@
         <v>137.84592</v>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H315" t="n">
-        <v>290.8446586327354</v>
+        <v>302.8133964563956</v>
       </c>
     </row>
     <row r="316">
@@ -9909,15 +9909,15 @@
         <v>71.19014000000001</v>
       </c>
       <c r="F316" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H316" t="n">
-        <v>419.8748338969282</v>
+        <v>546.9836780811395</v>
       </c>
     </row>
     <row r="317">
@@ -9939,15 +9939,15 @@
         <v>106.50236</v>
       </c>
       <c r="F317" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H317" t="n">
-        <v>202.3745627430987</v>
+        <v>219.3930996632319</v>
       </c>
     </row>
     <row r="318">
@@ -9969,15 +9969,15 @@
         <v>97.77134</v>
       </c>
       <c r="F318" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H318" t="n">
-        <v>131.3767754580934</v>
+        <v>147.6196537445319</v>
       </c>
     </row>
     <row r="319">
@@ -9999,15 +9999,15 @@
         <v>80.68743999999998</v>
       </c>
       <c r="F319" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H319" t="n">
-        <v>405.4616480532131</v>
+        <v>532.3398390756205</v>
       </c>
     </row>
     <row r="320">
@@ -10029,15 +10029,15 @@
         <v>92.23769999999999</v>
       </c>
       <c r="F320" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H320" t="n">
-        <v>257.7202175042919</v>
+        <v>378.8590788971603</v>
       </c>
     </row>
     <row r="321">
@@ -10059,15 +10059,15 @@
         <v>111.7828</v>
       </c>
       <c r="F321" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H321" t="n">
-        <v>299.2069770829289</v>
+        <v>421.7867030321074</v>
       </c>
     </row>
     <row r="322">
@@ -10089,15 +10089,15 @@
         <v>120.6901</v>
       </c>
       <c r="F322" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H322" t="n">
-        <v>225.2118983559744</v>
+        <v>247.9904061596499</v>
       </c>
     </row>
     <row r="323">
@@ -10119,15 +10119,15 @@
         <v>51.7548</v>
       </c>
       <c r="F323" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H323" t="n">
-        <v>233.1156151535796</v>
+        <v>209.2437086968674</v>
       </c>
     </row>
     <row r="324">
@@ -10149,15 +10149,15 @@
         <v>162.11432</v>
       </c>
       <c r="F324" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H324" t="n">
-        <v>174.6437031880509</v>
+        <v>171.5610975856906</v>
       </c>
     </row>
     <row r="325">
@@ -10179,15 +10179,15 @@
         <v>70.43834</v>
       </c>
       <c r="F325" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H325" t="n">
-        <v>258.0969226234916</v>
+        <v>278.4183922634941</v>
       </c>
     </row>
     <row r="326">
@@ -10209,15 +10209,15 @@
         <v>97.17318</v>
       </c>
       <c r="F326" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H326" t="n">
-        <v>143.4559287228808</v>
+        <v>156.8727092762293</v>
       </c>
     </row>
     <row r="327">
@@ -10239,15 +10239,15 @@
         <v>96.64926</v>
       </c>
       <c r="F327" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H327" t="n">
-        <v>298.5405184854939</v>
+        <v>419.9714842742374</v>
       </c>
     </row>
     <row r="328">
@@ -10269,15 +10269,15 @@
         <v>136.70414</v>
       </c>
       <c r="F328" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H328" t="n">
-        <v>291.9125166681933</v>
+        <v>413.2442366380896</v>
       </c>
     </row>
     <row r="329">
@@ -10299,15 +10299,15 @@
         <v>55.98389999999999</v>
       </c>
       <c r="F329" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H329" t="n">
-        <v>201.6634020843782</v>
+        <v>177.6925516581376</v>
       </c>
     </row>
     <row r="330">
@@ -10329,15 +10329,15 @@
         <v>57.27579999999999</v>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H330" t="n">
-        <v>187.3472114739193</v>
+        <v>164.433344750549</v>
       </c>
     </row>
     <row r="331">
@@ -10359,15 +10359,15 @@
         <v>100.51814</v>
       </c>
       <c r="F331" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H331" t="n">
-        <v>306.1498650987936</v>
+        <v>428.9474955583875</v>
       </c>
     </row>
     <row r="332">
@@ -10389,15 +10389,15 @@
         <v>72.68213999999999</v>
       </c>
       <c r="F332" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H332" t="n">
-        <v>240.6553957539271</v>
+        <v>353.350985394453</v>
       </c>
     </row>
     <row r="333">
@@ -10419,15 +10419,15 @@
         <v>53.00724</v>
       </c>
       <c r="F333" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H333" t="n">
-        <v>305.5297858281983</v>
+        <v>427.7753898421324</v>
       </c>
     </row>
     <row r="334">
@@ -10449,15 +10449,15 @@
         <v>84.78078000000001</v>
       </c>
       <c r="F334" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H334" t="n">
-        <v>265.5314730786209</v>
+        <v>264.8709808666407</v>
       </c>
     </row>
     <row r="335">
@@ -10479,15 +10479,15 @@
         <v>97.36683999999997</v>
       </c>
       <c r="F335" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H335" t="n">
-        <v>115.8620035916273</v>
+        <v>105.7153231447665</v>
       </c>
     </row>
     <row r="336">
@@ -10509,15 +10509,15 @@
         <v>81.07180000000001</v>
       </c>
       <c r="F336" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H336" t="n">
-        <v>325.2162572181462</v>
+        <v>325.683184610459</v>
       </c>
     </row>
     <row r="337">
@@ -10539,15 +10539,15 @@
         <v>51.87629999999999</v>
       </c>
       <c r="F337" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H337" t="n">
-        <v>176.0201727541978</v>
+        <v>193.1659403726651</v>
       </c>
     </row>
     <row r="338">
@@ -10569,15 +10569,15 @@
         <v>164.81286</v>
       </c>
       <c r="F338" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H338" t="n">
-        <v>242.8334230268776</v>
+        <v>228.6386816114776</v>
       </c>
     </row>
     <row r="339">
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>262.5364558361898</v>
+        <v>239.9271333422346</v>
       </c>
     </row>
     <row r="340">
@@ -10629,15 +10629,15 @@
         <v>105.60097665</v>
       </c>
       <c r="F340" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H340" t="n">
-        <v>244.4815171214456</v>
+        <v>234.2369337173518</v>
       </c>
     </row>
     <row r="341">
@@ -10659,15 +10659,15 @@
         <v>85.30447965</v>
       </c>
       <c r="F341" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H341" t="n">
-        <v>249.0720943022942</v>
+        <v>226.8159864422877</v>
       </c>
     </row>
     <row r="342">
@@ -10689,15 +10689,15 @@
         <v>105.13692</v>
       </c>
       <c r="F342" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H342" t="n">
-        <v>130.0982456924606</v>
+        <v>3.05245814029515</v>
       </c>
     </row>
     <row r="343">
@@ -10719,15 +10719,15 @@
         <v>119.39315505</v>
       </c>
       <c r="F343" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H343" t="n">
-        <v>244.7649577139401</v>
+        <v>232.7606295976149</v>
       </c>
     </row>
     <row r="344">
@@ -10749,15 +10749,15 @@
         <v>135.2097</v>
       </c>
       <c r="F344" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H344" t="n">
-        <v>170.4849151475579</v>
+        <v>44.63230629408451</v>
       </c>
     </row>
     <row r="345">
@@ -10779,15 +10779,15 @@
         <v>103.2224895</v>
       </c>
       <c r="F345" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H345" t="n">
-        <v>247.3589627515343</v>
+        <v>235.6425339063696</v>
       </c>
     </row>
     <row r="346">
@@ -10809,15 +10809,15 @@
         <v>105.68844</v>
       </c>
       <c r="F346" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H346" t="n">
-        <v>250.7518419947306</v>
+        <v>236.3926209841623</v>
       </c>
     </row>
     <row r="347">
@@ -10839,15 +10839,15 @@
         <v>92.92085999999999</v>
       </c>
       <c r="F347" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H347" t="n">
-        <v>245.2020554131428</v>
+        <v>228.7898553040338</v>
       </c>
     </row>
     <row r="348">
@@ -10869,15 +10869,15 @@
         <v>105.6147144</v>
       </c>
       <c r="F348" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H348" t="n">
-        <v>247.1939855447183</v>
+        <v>238.3826140048343</v>
       </c>
     </row>
     <row r="349">
@@ -10899,15 +10899,15 @@
         <v>96.36005999999999</v>
       </c>
       <c r="F349" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H349" t="n">
-        <v>248.9481718440073</v>
+        <v>126.9259514787582</v>
       </c>
     </row>
     <row r="350">
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>262.8258537407512</v>
+        <v>240.990457513337</v>
       </c>
     </row>
     <row r="351">
@@ -10959,15 +10959,15 @@
         <v>103.29378</v>
       </c>
       <c r="F351" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H351" t="n">
-        <v>243.9905079930992</v>
+        <v>221.672979833551</v>
       </c>
     </row>
     <row r="352">
@@ -10989,15 +10989,15 @@
         <v>69.66414</v>
       </c>
       <c r="F352" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H352" t="n">
-        <v>245.7263957483557</v>
+        <v>123.2451849638042</v>
       </c>
     </row>
     <row r="353">
@@ -11019,15 +11019,15 @@
         <v>133.07976</v>
       </c>
       <c r="F353" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H353" t="n">
-        <v>241.3758450983825</v>
+        <v>232.446583431369</v>
       </c>
     </row>
     <row r="354">
@@ -11049,15 +11049,15 @@
         <v>99.53225999999999</v>
       </c>
       <c r="F354" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H354" t="n">
-        <v>173.6480917764453</v>
+        <v>135.9227728142532</v>
       </c>
     </row>
     <row r="355">
@@ -11079,15 +11079,15 @@
         <v>174.81366</v>
       </c>
       <c r="F355" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H355" t="n">
-        <v>255.3696671481475</v>
+        <v>268.5129992494262</v>
       </c>
     </row>
     <row r="356">
@@ -11109,15 +11109,15 @@
         <v>123.87336</v>
       </c>
       <c r="F356" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H356" t="n">
-        <v>245.2199955591135</v>
+        <v>123.2245237075969</v>
       </c>
     </row>
     <row r="357">
@@ -11139,15 +11139,15 @@
         <v>147.74808</v>
       </c>
       <c r="F357" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H357" t="n">
-        <v>127.1680167975757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -11169,15 +11169,15 @@
         <v>148.73862</v>
       </c>
       <c r="F358" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H358" t="n">
-        <v>251.8859543154234</v>
+        <v>229.2048316902433</v>
       </c>
     </row>
     <row r="359">
@@ -11199,15 +11199,15 @@
         <v>273.06534</v>
       </c>
       <c r="F359" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H359" t="n">
-        <v>244.6616573423616</v>
+        <v>229.5926036582196</v>
       </c>
     </row>
     <row r="360">
@@ -11229,15 +11229,15 @@
         <v>108.07158</v>
       </c>
       <c r="F360" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H360" t="n">
-        <v>242.2130875979642</v>
+        <v>231.8062255945751</v>
       </c>
     </row>
     <row r="361">
@@ -11259,15 +11259,15 @@
         <v>154.62948</v>
       </c>
       <c r="F361" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H361" t="n">
-        <v>184.1323231692768</v>
+        <v>254.7217919902353</v>
       </c>
     </row>
     <row r="362">
@@ -11289,15 +11289,15 @@
         <v>133.61611575</v>
       </c>
       <c r="F362" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H362" t="n">
-        <v>247.2555998483565</v>
+        <v>236.9675286822333</v>
       </c>
     </row>
     <row r="363">
@@ -11319,15 +11319,15 @@
         <v>107.2794</v>
       </c>
       <c r="F363" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H363" t="n">
-        <v>248.2500861193687</v>
+        <v>236.042639746664</v>
       </c>
     </row>
     <row r="364">
@@ -11349,15 +11349,15 @@
         <v>90.89004</v>
       </c>
       <c r="F364" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H364" t="n">
-        <v>238.6138624870473</v>
+        <v>231.0797650168059</v>
       </c>
     </row>
     <row r="365">
@@ -11379,15 +11379,15 @@
         <v>65.39706</v>
       </c>
       <c r="F365" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H365" t="n">
-        <v>248.2464578486703</v>
+        <v>236.7708126174289</v>
       </c>
     </row>
     <row r="366">
@@ -11409,15 +11409,15 @@
         <v>93.90606000000002</v>
       </c>
       <c r="F366" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H366" t="n">
-        <v>251.572927532271</v>
+        <v>130.1980141958676</v>
       </c>
     </row>
     <row r="367">
@@ -11447,7 +11447,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>230.4299203347763</v>
+        <v>184.798244502207</v>
       </c>
     </row>
     <row r="368">
@@ -11469,15 +11469,15 @@
         <v>69.34979999999999</v>
       </c>
       <c r="F368" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H368" t="n">
-        <v>230.0711370582394</v>
+        <v>229.820113327984</v>
       </c>
     </row>
     <row r="369">
@@ -11499,15 +11499,15 @@
         <v>147.48796146</v>
       </c>
       <c r="F369" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H369" t="n">
-        <v>66.73815255783093</v>
+        <v>39.15438497735472</v>
       </c>
     </row>
     <row r="370">
@@ -11529,15 +11529,15 @@
         <v>81.62645259999999</v>
       </c>
       <c r="F370" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H370" t="n">
-        <v>34.52345300414044</v>
+        <v>12.57090271495102</v>
       </c>
     </row>
     <row r="371">
@@ -11559,15 +11559,15 @@
         <v>125.7125763</v>
       </c>
       <c r="F371" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H371" t="n">
-        <v>317.946630304663</v>
+        <v>342.4939796860908</v>
       </c>
     </row>
     <row r="372">
@@ -11589,15 +11589,15 @@
         <v>118.30654686</v>
       </c>
       <c r="F372" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H372" t="n">
-        <v>176.6888667503275</v>
+        <v>154.5296365267789</v>
       </c>
     </row>
     <row r="373">
@@ -11619,15 +11619,15 @@
         <v>46.7992934</v>
       </c>
       <c r="F373" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H373" t="n">
-        <v>63.09525674037218</v>
+        <v>37.91710526660902</v>
       </c>
     </row>
     <row r="374">
@@ -11649,15 +11649,15 @@
         <v>135.638204</v>
       </c>
       <c r="F374" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H374" t="n">
-        <v>67.88592045568444</v>
+        <v>42.66602307691792</v>
       </c>
     </row>
     <row r="375">
@@ -11679,15 +11679,15 @@
         <v>82.8659857</v>
       </c>
       <c r="F375" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H375" t="n">
-        <v>34.2181840897848</v>
+        <v>13.54667643358147</v>
       </c>
     </row>
     <row r="376">
@@ -11709,15 +11709,15 @@
         <v>105.553257</v>
       </c>
       <c r="F376" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H376" t="n">
-        <v>32.70858238462002</v>
+        <v>6.482501230056271</v>
       </c>
     </row>
     <row r="377">
@@ -11739,15 +11739,15 @@
         <v>71.35351295999999</v>
       </c>
       <c r="F377" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H377" t="n">
-        <v>181.5158062914187</v>
+        <v>159.5564405282327</v>
       </c>
     </row>
     <row r="378">
@@ -11769,15 +11769,15 @@
         <v>102.73411212</v>
       </c>
       <c r="F378" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H378" t="n">
-        <v>180.1765995943753</v>
+        <v>157.9057503839281</v>
       </c>
     </row>
     <row r="379">
@@ -11799,15 +11799,15 @@
         <v>128.5971056</v>
       </c>
       <c r="F379" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H379" t="n">
-        <v>35.38984638379532</v>
+        <v>11.61629237416503</v>
       </c>
     </row>
     <row r="380">
@@ -11829,15 +11829,15 @@
         <v>62.78045063999999</v>
       </c>
       <c r="F380" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H380" t="n">
-        <v>148.9146243709701</v>
+        <v>123.5969250984457</v>
       </c>
     </row>
     <row r="381">
@@ -11859,15 +11859,15 @@
         <v>109.3731514</v>
       </c>
       <c r="F381" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H381" t="n">
-        <v>292.1082656735446</v>
+        <v>318.263518593437</v>
       </c>
     </row>
     <row r="382">
@@ -11889,15 +11889,15 @@
         <v>119.1499458</v>
       </c>
       <c r="F382" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H382" t="n">
-        <v>33.3796757686011</v>
+        <v>9.701676387079416</v>
       </c>
     </row>
     <row r="383">
@@ -11919,15 +11919,15 @@
         <v>213.5551645</v>
       </c>
       <c r="F383" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H383" t="n">
-        <v>31.90591786876936</v>
+        <v>7.275330297290545</v>
       </c>
     </row>
     <row r="384">
@@ -11949,15 +11949,15 @@
         <v>187.0876349</v>
       </c>
       <c r="F384" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H384" t="n">
-        <v>33.24458419572206</v>
+        <v>10.61135848297473</v>
       </c>
     </row>
     <row r="385">
@@ -11979,15 +11979,15 @@
         <v>149.1235557</v>
       </c>
       <c r="F385" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H385" t="n">
-        <v>63.43243743125071</v>
+        <v>38.42775221604786</v>
       </c>
     </row>
     <row r="386">
@@ -12009,15 +12009,15 @@
         <v>170.141426</v>
       </c>
       <c r="F386" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H386" t="n">
-        <v>293.4508617519292</v>
+        <v>319.5538914584326</v>
       </c>
     </row>
     <row r="387">
@@ -12039,15 +12039,15 @@
         <v>168.952343</v>
       </c>
       <c r="F387" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H387" t="n">
-        <v>37.08142664821583</v>
+        <v>14.41067480414424</v>
       </c>
     </row>
     <row r="388">
@@ -12069,15 +12069,15 @@
         <v>107.310147</v>
       </c>
       <c r="F388" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H388" t="n">
-        <v>29.33806901372546</v>
+        <v>2.798523869312165</v>
       </c>
     </row>
     <row r="389">
@@ -12099,15 +12099,15 @@
         <v>111.302101</v>
       </c>
       <c r="F389" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H389" t="n">
-        <v>28.37001636872408</v>
+        <v>4.086812362410984</v>
       </c>
     </row>
     <row r="390">
@@ -12129,15 +12129,15 @@
         <v>77.23364369999999</v>
       </c>
       <c r="F390" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H390" t="n">
-        <v>39.11561759641163</v>
+        <v>12.82877227690499</v>
       </c>
     </row>
     <row r="391">
@@ -12159,15 +12159,15 @@
         <v>53.22112451999999</v>
       </c>
       <c r="F391" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H391" t="n">
-        <v>203.8019484784353</v>
+        <v>184.5265200028921</v>
       </c>
     </row>
     <row r="392">
@@ -12189,15 +12189,15 @@
         <v>110.9159485</v>
       </c>
       <c r="F392" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H392" t="n">
-        <v>31.02089893886271</v>
+        <v>4.91155522905192</v>
       </c>
     </row>
     <row r="393">
@@ -12219,15 +12219,15 @@
         <v>95.37692682000001</v>
       </c>
       <c r="F393" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H393" t="n">
-        <v>184.6131265113243</v>
+        <v>162.3569820648295</v>
       </c>
     </row>
     <row r="394">
@@ -12249,15 +12249,15 @@
         <v>54.18531179999999</v>
       </c>
       <c r="F394" t="n">
+        <v>5</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>DC_6</t>
+        </is>
+      </c>
+      <c r="H394" t="n">
         <v>0</v>
-      </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>DC_1</t>
-        </is>
-      </c>
-      <c r="H394" t="n">
-        <v>27.58568935880062</v>
       </c>
     </row>
     <row r="395">
@@ -12279,15 +12279,15 @@
         <v>111.9413228</v>
       </c>
       <c r="F395" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="H395" t="n">
-        <v>30.56895919515435</v>
+        <v>14.12354157257625</v>
       </c>
     </row>
     <row r="396">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="H396" t="n">
-        <v>599.7685658275938</v>
+        <v>562.9329183211324</v>
       </c>
     </row>
     <row r="397">
@@ -12347,7 +12347,7 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>418.910619457074</v>
+        <v>399.0386805781686</v>
       </c>
     </row>
     <row r="398">
@@ -12369,15 +12369,15 @@
         <v>88.73139999999999</v>
       </c>
       <c r="F398" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H398" t="n">
-        <v>395.1452104601061</v>
+        <v>399.2933407902202</v>
       </c>
     </row>
     <row r="399">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>580.0655393103883</v>
+        <v>544.8395540952689</v>
       </c>
     </row>
     <row r="400">
@@ -12437,7 +12437,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>419.2014824656533</v>
+        <v>404.1985816893753</v>
       </c>
     </row>
     <row r="401">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>417.7719448167981</v>
+        <v>398.0133220468219</v>
       </c>
     </row>
     <row r="402">
@@ -12497,7 +12497,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>290.1088194372147</v>
+        <v>271.698348756485</v>
       </c>
     </row>
     <row r="403">
@@ -12527,7 +12527,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>413.7000010176697</v>
+        <v>393.8114777969823</v>
       </c>
     </row>
     <row r="404">
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>286.2644628689006</v>
+        <v>270.9129282531802</v>
       </c>
     </row>
     <row r="405">
@@ -12587,7 +12587,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>596.4055858326795</v>
+        <v>559.6269996577513</v>
       </c>
     </row>
     <row r="406">
@@ -12617,7 +12617,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>667.4815881169878</v>
+        <v>629.6244910605436</v>
       </c>
     </row>
     <row r="407">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>418.0305093436396</v>
+        <v>398.0612564570309</v>
       </c>
     </row>
     <row r="408">
@@ -12677,7 +12677,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>577.1715434059126</v>
+        <v>541.9030864968256</v>
       </c>
     </row>
     <row r="409">
@@ -12707,7 +12707,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>291.0608337402675</v>
+        <v>272.9139635372408</v>
       </c>
     </row>
     <row r="410">
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>596.9387958350218</v>
+        <v>560.2114394204164</v>
       </c>
     </row>
     <row r="411">
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>417.601541343521</v>
+        <v>397.8931264225789</v>
       </c>
     </row>
     <row r="412">
@@ -12797,7 +12797,7 @@
         </is>
       </c>
       <c r="H412" t="n">
-        <v>592.2228066044695</v>
+        <v>553.9746287176301</v>
       </c>
     </row>
     <row r="413">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>316.9706336802632</v>
+        <v>290.325695922037</v>
       </c>
     </row>
     <row r="414">
@@ -12857,7 +12857,7 @@
         </is>
       </c>
       <c r="H414" t="n">
-        <v>623.8236912874983</v>
+        <v>589.205834795844</v>
       </c>
     </row>
     <row r="415">
@@ -12887,7 +12887,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>631.3880668617128</v>
+        <v>592.9623348517237</v>
       </c>
     </row>
     <row r="416">
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>594.4100784430385</v>
+        <v>556.1763395240313</v>
       </c>
     </row>
     <row r="417">
@@ -12947,7 +12947,7 @@
         </is>
       </c>
       <c r="H417" t="n">
-        <v>620.2615824043411</v>
+        <v>585.6363666275724</v>
       </c>
     </row>
     <row r="418">
@@ -12969,15 +12969,15 @@
         <v>44.69123999999999</v>
       </c>
       <c r="F418" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H418" t="n">
-        <v>204.5305974443592</v>
+        <v>237.6201381750443</v>
       </c>
     </row>
     <row r="419">
@@ -13007,7 +13007,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>110.2827409697895</v>
+        <v>99.7038613045038</v>
       </c>
     </row>
     <row r="420">
@@ -13029,15 +13029,15 @@
         <v>30.97999</v>
       </c>
       <c r="F420" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H420" t="n">
-        <v>204.4596365169506</v>
+        <v>234.764391484706</v>
       </c>
     </row>
     <row r="421">
@@ -13059,15 +13059,15 @@
         <v>38.67852</v>
       </c>
       <c r="F421" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H421" t="n">
-        <v>163.7742200848483</v>
+        <v>198.7765567384305</v>
       </c>
     </row>
     <row r="422">
@@ -13089,15 +13089,15 @@
         <v>22.78917</v>
       </c>
       <c r="F422" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H422" t="n">
-        <v>208.7913962749197</v>
+        <v>237.0983883977419</v>
       </c>
     </row>
     <row r="423">
@@ -13127,7 +13127,7 @@
         </is>
       </c>
       <c r="H423" t="n">
-        <v>121.5759418094487</v>
+        <v>109.2974339087442</v>
       </c>
     </row>
     <row r="424">
@@ -13149,15 +13149,15 @@
         <v>125.73253</v>
       </c>
       <c r="F424" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H424" t="n">
-        <v>213.2182452585202</v>
+        <v>243.3057882043767</v>
       </c>
     </row>
     <row r="425">
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>176.2503739454197</v>
+        <v>205.8332451562206</v>
       </c>
     </row>
     <row r="426">
@@ -13209,15 +13209,15 @@
         <v>144.26477</v>
       </c>
       <c r="F426" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H426" t="n">
-        <v>231.1188408667959</v>
+        <v>199.5832316516953</v>
       </c>
     </row>
     <row r="427">
@@ -13239,15 +13239,15 @@
         <v>109.89436</v>
       </c>
       <c r="F427" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H427" t="n">
-        <v>213.4509778017186</v>
+        <v>244.77544899438</v>
       </c>
     </row>
     <row r="428">
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>181.948223952247</v>
+        <v>212.5040539822774</v>
       </c>
     </row>
     <row r="429">
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>94.86397367730432</v>
+        <v>90.0980258920742</v>
       </c>
     </row>
     <row r="430">
@@ -13337,7 +13337,7 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>100.5714524373624</v>
+        <v>93.9900122522893</v>
       </c>
     </row>
     <row r="431">
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>48.39588948557887</v>
+        <v>48.06033700014402</v>
       </c>
     </row>
     <row r="432">
@@ -13389,15 +13389,15 @@
         <v>49.8474</v>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H432" t="n">
-        <v>463.4459507527332</v>
+        <v>462.3370152351604</v>
       </c>
     </row>
     <row r="433">
@@ -13419,15 +13419,15 @@
         <v>56.77137180999998</v>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H433" t="n">
-        <v>433.5621327582323</v>
+        <v>449.9853559453078</v>
       </c>
     </row>
     <row r="434">
@@ -13449,15 +13449,15 @@
         <v>138.73463</v>
       </c>
       <c r="F434" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H434" t="n">
-        <v>229.0852832585927</v>
+        <v>162.993792613938</v>
       </c>
     </row>
     <row r="435">
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>172.6159711788848</v>
+        <v>203.4341665162504</v>
       </c>
     </row>
     <row r="436">
@@ -13517,7 +13517,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>117.7951780549381</v>
+        <v>105.6809195503245</v>
       </c>
     </row>
     <row r="437">
@@ -13547,7 +13547,7 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>97.45745982829436</v>
+        <v>90.3683577034153</v>
       </c>
     </row>
     <row r="438">
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>101.481381795035</v>
+        <v>94.08847476823729</v>
       </c>
     </row>
     <row r="439">
@@ -13599,15 +13599,15 @@
         <v>95.54351964</v>
       </c>
       <c r="F439" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H439" t="n">
-        <v>510.997654198796</v>
+        <v>439.1031686450011</v>
       </c>
     </row>
     <row r="440">
@@ -13629,15 +13629,15 @@
         <v>79.42373506000001</v>
       </c>
       <c r="F440" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H440" t="n">
-        <v>429.4902768901852</v>
+        <v>456.135414208522</v>
       </c>
     </row>
     <row r="441">
@@ -13667,7 +13667,7 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>260.2853585002077</v>
+        <v>251.7742107462432</v>
       </c>
     </row>
     <row r="442">
@@ -13697,7 +13697,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>208.5962880424154</v>
+        <v>242.6207437871402</v>
       </c>
     </row>
     <row r="443">
@@ -13727,7 +13727,7 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>98.25808763279977</v>
+        <v>94.55157049759576</v>
       </c>
     </row>
     <row r="444">
@@ -13749,15 +13749,15 @@
         <v>86.38211000000001</v>
       </c>
       <c r="F444" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H444" t="n">
-        <v>208.4277253435319</v>
+        <v>239.2033432876943</v>
       </c>
     </row>
     <row r="445">
@@ -13779,15 +13779,15 @@
         <v>90.25793999999999</v>
       </c>
       <c r="F445" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H445" t="n">
-        <v>212.3386261781216</v>
+        <v>244.7042980601115</v>
       </c>
     </row>
     <row r="446">
@@ -13809,15 +13809,15 @@
         <v>142.70429</v>
       </c>
       <c r="F446" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H446" t="n">
-        <v>209.6504118209775</v>
+        <v>238.517141078303</v>
       </c>
     </row>
     <row r="447">
@@ -13847,7 +13847,7 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>182.7667459903581</v>
+        <v>212.7492079575601</v>
       </c>
     </row>
     <row r="448">
@@ -13869,15 +13869,15 @@
         <v>119.03817194</v>
       </c>
       <c r="F448" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H448" t="n">
-        <v>423.5769488863627</v>
+        <v>459.7575073825284</v>
       </c>
     </row>
     <row r="449">
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="H449" t="n">
-        <v>95.67790461919937</v>
+        <v>90.29583703329229</v>
       </c>
     </row>
     <row r="450">
@@ -13929,15 +13929,15 @@
         <v>81.9524</v>
       </c>
       <c r="F450" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H450" t="n">
-        <v>484.1532863787845</v>
+        <v>480.4430992225687</v>
       </c>
     </row>
     <row r="451">
@@ -13959,15 +13959,15 @@
         <v>129.72508</v>
       </c>
       <c r="F451" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H451" t="n">
-        <v>228.5218675824255</v>
+        <v>198.0643498726504</v>
       </c>
     </row>
     <row r="452">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="H452" t="n">
-        <v>102.6353178628117</v>
+        <v>97.55387968687192</v>
       </c>
     </row>
     <row r="453">
@@ -14019,15 +14019,15 @@
         <v>137.67475</v>
       </c>
       <c r="F453" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H453" t="n">
-        <v>301.0507133735346</v>
+        <v>199.5974651940966</v>
       </c>
     </row>
     <row r="454">
@@ -14049,15 +14049,15 @@
         <v>91.25033126999999</v>
       </c>
       <c r="F454" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H454" t="n">
-        <v>386.2146034980639</v>
+        <v>335.0619337748118</v>
       </c>
     </row>
     <row r="455">
@@ -14087,7 +14087,7 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>97.23843853479993</v>
+        <v>92.01053017070051</v>
       </c>
     </row>
     <row r="456">
@@ -14117,7 +14117,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>102.4918480857375</v>
+        <v>95.45167583039947</v>
       </c>
     </row>
     <row r="457">
@@ -14139,15 +14139,15 @@
         <v>33.4468</v>
       </c>
       <c r="F457" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H457" t="n">
-        <v>207.4009137645875</v>
+        <v>237.9422131497212</v>
       </c>
     </row>
     <row r="458">
@@ -14169,15 +14169,15 @@
         <v>124.24486528</v>
       </c>
       <c r="F458" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H458" t="n">
-        <v>428.9279411296831</v>
+        <v>454.4354598273687</v>
       </c>
     </row>
     <row r="459">
@@ -14199,15 +14199,15 @@
         <v>99.37579999999998</v>
       </c>
       <c r="F459" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H459" t="n">
-        <v>229.5591365467445</v>
+        <v>199.2811750116876</v>
       </c>
     </row>
     <row r="460">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>175.6247251323167</v>
+        <v>206.0759102960201</v>
       </c>
     </row>
     <row r="461">
@@ -14267,7 +14267,7 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>175.3296764752763</v>
+        <v>205.4737074015495</v>
       </c>
     </row>
     <row r="462">
@@ -14297,7 +14297,7 @@
         </is>
       </c>
       <c r="H462" t="n">
-        <v>51.09998502013926</v>
+        <v>50.25644795082248</v>
       </c>
     </row>
     <row r="463">
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>99.97599824829125</v>
+        <v>94.34029263720771</v>
       </c>
     </row>
     <row r="464">
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>168.7811319371953</v>
+        <v>199.6572089693678</v>
       </c>
     </row>
     <row r="465">
@@ -14379,15 +14379,15 @@
         <v>97.37148000000001</v>
       </c>
       <c r="F465" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H465" t="n">
-        <v>211.6732813870892</v>
+        <v>241.6691407618989</v>
       </c>
     </row>
     <row r="466">
@@ -14409,15 +14409,15 @@
         <v>130.5938</v>
       </c>
       <c r="F466" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H466" t="n">
-        <v>232.6220725104062</v>
+        <v>202.3400634650289</v>
       </c>
     </row>
     <row r="467">
@@ -14447,7 +14447,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>100.092607826785</v>
+        <v>93.80687191812108</v>
       </c>
     </row>
     <row r="468">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>96.94585824993405</v>
+        <v>91.55369369176938</v>
       </c>
     </row>
     <row r="469">
@@ -14507,7 +14507,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>178.0547726996159</v>
+        <v>207.7644881052486</v>
       </c>
     </row>
     <row r="470">
@@ -14529,15 +14529,15 @@
         <v>123.36434</v>
       </c>
       <c r="F470" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H470" t="n">
-        <v>209.6007710482695</v>
+        <v>240.297222012738</v>
       </c>
     </row>
     <row r="471">
@@ -14559,15 +14559,15 @@
         <v>173.58828</v>
       </c>
       <c r="F471" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H471" t="n">
-        <v>217.769738655443</v>
+        <v>248.1144254000412</v>
       </c>
     </row>
     <row r="472">
@@ -14597,7 +14597,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>102.700602997662</v>
+        <v>94.17249277637561</v>
       </c>
     </row>
     <row r="473">
@@ -14627,7 +14627,7 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>172.7706883374275</v>
+        <v>203.1957489360825</v>
       </c>
     </row>
     <row r="474">
@@ -14649,15 +14649,15 @@
         <v>156.22850862</v>
       </c>
       <c r="F474" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H474" t="n">
-        <v>429.3340900803877</v>
+        <v>455.2583033426945</v>
       </c>
     </row>
     <row r="475">
@@ -14687,7 +14687,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>99.365783649566</v>
+        <v>91.13841375349979</v>
       </c>
     </row>
     <row r="476">
@@ -14709,15 +14709,15 @@
         <v>147.33710398</v>
       </c>
       <c r="F476" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H476" t="n">
-        <v>426.3835440125061</v>
+        <v>458.674922905298</v>
       </c>
     </row>
     <row r="477">
@@ -14747,7 +14747,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>178.0194198959729</v>
+        <v>208.7746257080976</v>
       </c>
     </row>
     <row r="478">
@@ -14769,15 +14769,15 @@
         <v>115.35392</v>
       </c>
       <c r="F478" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H478" t="n">
-        <v>208.9435669676058</v>
+        <v>241.1319183450053</v>
       </c>
     </row>
     <row r="479">
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>178.8457234807114</v>
+        <v>208.8093372115301</v>
       </c>
     </row>
     <row r="480">
@@ -14837,7 +14837,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>107.3145602966586</v>
+        <v>98.09423920156364</v>
       </c>
     </row>
     <row r="481">
@@ -14867,7 +14867,7 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>78.34448568653632</v>
+        <v>83.86170948034218</v>
       </c>
     </row>
     <row r="482">
@@ -14889,15 +14889,15 @@
         <v>133.14993041</v>
       </c>
       <c r="F482" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H482" t="n">
-        <v>494.2465546328309</v>
+        <v>451.2518729527299</v>
       </c>
     </row>
     <row r="483">
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>208.6719006944995</v>
+        <v>205.0075027925476</v>
       </c>
     </row>
     <row r="484">
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>173.0380180324195</v>
+        <v>204.411680816876</v>
       </c>
     </row>
     <row r="485">
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>306.8243085037814</v>
+        <v>342.6902945712899</v>
       </c>
     </row>
     <row r="486">
@@ -15009,15 +15009,15 @@
         <v>175.2077001</v>
       </c>
       <c r="F486" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H486" t="n">
-        <v>509.5008732297528</v>
+        <v>436.7125282091822</v>
       </c>
     </row>
     <row r="487">
@@ -15039,15 +15039,15 @@
         <v>168.87164</v>
       </c>
       <c r="F487" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H487" t="n">
-        <v>163.7335498059527</v>
+        <v>75.4651024189595</v>
       </c>
     </row>
     <row r="488">
@@ -15069,15 +15069,15 @@
         <v>66.75664999999999</v>
       </c>
       <c r="F488" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H488" t="n">
-        <v>482.7255904190506</v>
+        <v>478.9435636984282</v>
       </c>
     </row>
     <row r="489">
@@ -15107,7 +15107,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>176.3452400412433</v>
+        <v>206.7994832782831</v>
       </c>
     </row>
     <row r="490">
@@ -15137,7 +15137,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>96.72437721924653</v>
+        <v>93.00717953846529</v>
       </c>
     </row>
     <row r="491">
@@ -15159,15 +15159,15 @@
         <v>89.62715</v>
       </c>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H491" t="n">
-        <v>482.017426840228</v>
+        <v>478.129089313604</v>
       </c>
     </row>
     <row r="492">
@@ -15189,15 +15189,15 @@
         <v>43.78264999999999</v>
       </c>
       <c r="F492" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H492" t="n">
-        <v>228.9300086027407</v>
+        <v>262.869810262483</v>
       </c>
     </row>
     <row r="493">
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>144.5352295904483</v>
+        <v>173.614929625572</v>
       </c>
     </row>
     <row r="494">
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>304.1258562519051</v>
+        <v>340.0263864003297</v>
       </c>
     </row>
     <row r="495">
@@ -15287,7 +15287,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>176.328593549544</v>
+        <v>206.5414340971641</v>
       </c>
     </row>
     <row r="496">
@@ -15317,7 +15317,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>345.6396454305997</v>
+        <v>334.3077432722394</v>
       </c>
     </row>
     <row r="497">
@@ -15339,15 +15339,15 @@
         <v>61.33865</v>
       </c>
       <c r="F497" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H497" t="n">
-        <v>204.2468831622038</v>
+        <v>265.9757361101167</v>
       </c>
     </row>
     <row r="498">
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>78.46596702303529</v>
+        <v>40.28803578428388</v>
       </c>
     </row>
     <row r="499">
@@ -15407,7 +15407,7 @@
         </is>
       </c>
       <c r="H499" t="n">
-        <v>38.42670238202552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500">
@@ -15429,15 +15429,15 @@
         <v>97.11096000000002</v>
       </c>
       <c r="F500" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H500" t="n">
-        <v>228.1579527766796</v>
+        <v>198.4169489828125</v>
       </c>
     </row>
     <row r="501">
@@ -15459,15 +15459,15 @@
         <v>77.12655000000001</v>
       </c>
       <c r="F501" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H501" t="n">
-        <v>229.1174983035737</v>
+        <v>197.2457940055387</v>
       </c>
     </row>
     <row r="502">
@@ -15497,7 +15497,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>121.9724126682299</v>
+        <v>114.9391757734247</v>
       </c>
     </row>
     <row r="503">
@@ -15519,15 +15519,15 @@
         <v>39.40545</v>
       </c>
       <c r="F503" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H503" t="n">
-        <v>229.178044449383</v>
+        <v>199.1949041175324</v>
       </c>
     </row>
     <row r="504">
@@ -15549,15 +15549,15 @@
         <v>51.32812</v>
       </c>
       <c r="F504" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H504" t="n">
-        <v>216.9896041973278</v>
+        <v>212.3623313996765</v>
       </c>
     </row>
     <row r="505">
@@ -15587,7 +15587,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>112.4827109906133</v>
+        <v>98.10985974597351</v>
       </c>
     </row>
   </sheetData>

--- a/clustered_output.xlsx
+++ b/clustered_output.xlsx
@@ -489,11 +489,11 @@
         <v>41.29720544</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -519,11 +519,11 @@
         <v>55.87958479999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -549,11 +549,11 @@
         <v>33.26804828</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -573,17 +573,17 @@
         <v>80.005</v>
       </c>
       <c r="D5" t="n">
-        <v>10000</v>
+        <v>2819658</v>
       </c>
       <c r="E5" t="n">
         <v>93.98859224</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -609,11 +609,11 @@
         <v>40.42737347999999</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -639,11 +639,11 @@
         <v>63.74664785</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -669,11 +669,11 @@
         <v>86.27647392</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -699,11 +699,11 @@
         <v>91.16850180000002</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -729,11 +729,11 @@
         <v>86.99766654</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -759,11 +759,11 @@
         <v>82.87167607000001</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -789,11 +789,11 @@
         <v>113.41016794</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -819,11 +819,11 @@
         <v>90.7568601</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -849,11 +849,11 @@
         <v>129.90572294</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -879,11 +879,11 @@
         <v>39.66574248000001</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -909,11 +909,11 @@
         <v>76.75563604999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -939,11 +939,11 @@
         <v>71.55889309999998</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -969,11 +969,11 @@
         <v>112.80354775</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -999,11 +999,11 @@
         <v>73.57074283999999</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1029,11 +1029,11 @@
         <v>48.18771840000001</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1059,11 +1059,11 @@
         <v>137.72677575</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1089,11 +1089,11 @@
         <v>61.96439013000001</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1119,11 +1119,11 @@
         <v>57.01195806</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1149,11 +1149,11 @@
         <v>75.03426994</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1179,11 +1179,11 @@
         <v>45.991</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1209,11 +1209,11 @@
         <v>69.51707707</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1239,11 +1239,11 @@
         <v>118.63043667</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1269,11 +1269,11 @@
         <v>39.05642559</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1299,11 +1299,11 @@
         <v>51.11150699</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1329,11 +1329,11 @@
         <v>90.55661511999999</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1359,11 +1359,11 @@
         <v>80.49179736000001</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1389,11 +1389,11 @@
         <v>137.7462625</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1419,11 +1419,11 @@
         <v>82.06561287</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1449,11 +1449,11 @@
         <v>40.91439332</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1479,11 +1479,11 @@
         <v>94.20747311999999</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1509,11 +1509,11 @@
         <v>51.34208147000001</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -1539,11 +1539,11 @@
         <v>89.43269527999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1569,11 +1569,11 @@
         <v>87.62353223</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -1599,11 +1599,11 @@
         <v>113.62947597</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -1629,11 +1629,11 @@
         <v>97.86042042</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -1659,11 +1659,11 @@
         <v>120.70724466</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -1689,11 +1689,11 @@
         <v>63.64605510000001</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -1719,11 +1719,11 @@
         <v>79.88549751000001</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -1749,11 +1749,11 @@
         <v>75.97018895000001</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -1779,11 +1779,11 @@
         <v>58.83139722999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -1809,11 +1809,11 @@
         <v>24.03516849</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -1839,11 +1839,11 @@
         <v>17.60890872</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -1869,11 +1869,11 @@
         <v>82.63783919000001</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -1899,11 +1899,11 @@
         <v>56.29949515999999</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -1929,11 +1929,11 @@
         <v>47.27391910999999</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -1959,11 +1959,11 @@
         <v>55.12580752</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -1989,11 +1989,11 @@
         <v>70.25959358</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -2019,11 +2019,11 @@
         <v>62.59155026999998</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -2049,11 +2049,11 @@
         <v>78.94616125999998</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -2079,11 +2079,11 @@
         <v>101.76988238</v>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -2109,11 +2109,11 @@
         <v>44.19095989</v>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -2139,11 +2139,11 @@
         <v>93.80458936000001</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -2169,11 +2169,11 @@
         <v>49.10406079999999</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -2199,11 +2199,11 @@
         <v>99.07280474</v>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -2229,11 +2229,11 @@
         <v>69.66181495000001</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -2259,11 +2259,11 @@
         <v>157.49350527</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -2289,11 +2289,11 @@
         <v>69.61420304000001</v>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -2319,11 +2319,11 @@
         <v>15.037</v>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -2349,11 +2349,11 @@
         <v>33.56141599999999</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -2379,11 +2379,11 @@
         <v>122.2742197</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -2409,11 +2409,11 @@
         <v>29.31689904</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -2439,11 +2439,11 @@
         <v>24.08448896</v>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -2469,11 +2469,11 @@
         <v>59.56919848</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -2499,11 +2499,11 @@
         <v>61.17361757</v>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -2529,11 +2529,11 @@
         <v>45.19398898999999</v>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -2559,11 +2559,11 @@
         <v>8.5903492</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -2589,11 +2589,11 @@
         <v>77.60705583999999</v>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -2619,11 +2619,11 @@
         <v>27.84522936</v>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -2649,11 +2649,11 @@
         <v>121.24150382</v>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -2679,11 +2679,11 @@
         <v>109.77473927</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -2709,11 +2709,11 @@
         <v>27.96024677</v>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -2739,11 +2739,11 @@
         <v>127.09983192</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H77" t="n">
@@ -2769,11 +2769,11 @@
         <v>40.97559472</v>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -2799,11 +2799,11 @@
         <v>55.95136335999999</v>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -2829,11 +2829,11 @@
         <v>99.95687511999999</v>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -2859,11 +2859,11 @@
         <v>171.25894002</v>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -2889,11 +2889,11 @@
         <v>108.25222513</v>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -2919,11 +2919,11 @@
         <v>152.37332232</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -2949,11 +2949,11 @@
         <v>137.64539505</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -2979,11 +2979,11 @@
         <v>98.88650038</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -3009,11 +3009,11 @@
         <v>174.43258149</v>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -3039,11 +3039,11 @@
         <v>131.72022438</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -3069,11 +3069,11 @@
         <v>128.67002752</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -3099,11 +3099,11 @@
         <v>151.83197394</v>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -3129,11 +3129,11 @@
         <v>70.43858698000003</v>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -3159,11 +3159,11 @@
         <v>165.86665209</v>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -3189,11 +3189,11 @@
         <v>160.7944185</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -3219,11 +3219,11 @@
         <v>114.30460316</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -3249,11 +3249,11 @@
         <v>27.65862036</v>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -3279,11 +3279,11 @@
         <v>107.20581291</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -3309,11 +3309,11 @@
         <v>132.81126806</v>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -3339,11 +3339,11 @@
         <v>151.87199567</v>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -3369,11 +3369,11 @@
         <v>97.51930487999999</v>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -3399,11 +3399,11 @@
         <v>62.68683512</v>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -3429,11 +3429,11 @@
         <v>164.09465016</v>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -3459,11 +3459,11 @@
         <v>115.75139108</v>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -3489,11 +3489,11 @@
         <v>112.73454219</v>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H102" t="n">
@@ -3519,11 +3519,11 @@
         <v>165.16716377</v>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -3549,11 +3549,11 @@
         <v>98.30353936999998</v>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -3579,11 +3579,11 @@
         <v>64.32811749000001</v>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -3609,11 +3609,11 @@
         <v>143.1621979</v>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -3639,11 +3639,11 @@
         <v>62.72158742000001</v>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H107" t="n">
@@ -3669,11 +3669,11 @@
         <v>135.79601133</v>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -3699,11 +3699,11 @@
         <v>67.78453388</v>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H109" t="n">
@@ -3729,11 +3729,11 @@
         <v>135.40894881</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -3759,11 +3759,11 @@
         <v>134.30264618</v>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -3789,11 +3789,11 @@
         <v>107.39169483</v>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H112" t="n">
@@ -3819,11 +3819,11 @@
         <v>92.21966651000001</v>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -3849,11 +3849,11 @@
         <v>46.65942816</v>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -3879,11 +3879,11 @@
         <v>61.25313789</v>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -3909,11 +3909,11 @@
         <v>95.79522047999998</v>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -3939,11 +3939,11 @@
         <v>131.4488539</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -3969,11 +3969,11 @@
         <v>139.22461155</v>
       </c>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -3999,11 +3999,11 @@
         <v>69.87724643999999</v>
       </c>
       <c r="F119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -4029,11 +4029,11 @@
         <v>26.29534809</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -4059,11 +4059,11 @@
         <v>124.64185643</v>
       </c>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -4089,11 +4089,11 @@
         <v>67.21328875</v>
       </c>
       <c r="F122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H122" t="n">
@@ -4119,11 +4119,11 @@
         <v>104.41013483</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -4149,11 +4149,11 @@
         <v>55.17039302000001</v>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -4179,11 +4179,11 @@
         <v>156.16160591</v>
       </c>
       <c r="F125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H125" t="n">
@@ -4209,11 +4209,11 @@
         <v>86.21620850000002</v>
       </c>
       <c r="F126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H126" t="n">
@@ -4239,11 +4239,11 @@
         <v>71.97972833</v>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H127" t="n">
@@ -4269,11 +4269,11 @@
         <v>116.03335498</v>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H128" t="n">
@@ -4299,11 +4299,11 @@
         <v>87.04857329000001</v>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -4329,11 +4329,11 @@
         <v>141.72703296</v>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -4359,11 +4359,11 @@
         <v>145.58214742</v>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -4389,11 +4389,11 @@
         <v>148.1403535</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -4419,11 +4419,11 @@
         <v>39.35975862000001</v>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -4449,11 +4449,11 @@
         <v>121.18436646</v>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -4479,11 +4479,11 @@
         <v>174.54029805</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -4509,11 +4509,11 @@
         <v>71.22344247000001</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -4539,11 +4539,11 @@
         <v>86.91646299999999</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -4569,11 +4569,11 @@
         <v>113.58351808</v>
       </c>
       <c r="F138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -4599,11 +4599,11 @@
         <v>130.82707128</v>
       </c>
       <c r="F139" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -4629,11 +4629,11 @@
         <v>83.83990669000001</v>
       </c>
       <c r="F140" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H140" t="n">
@@ -4659,11 +4659,11 @@
         <v>66.93223488999999</v>
       </c>
       <c r="F141" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -4689,11 +4689,11 @@
         <v>94.84938579</v>
       </c>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H142" t="n">
@@ -4719,11 +4719,11 @@
         <v>145.91838293</v>
       </c>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H143" t="n">
@@ -4749,11 +4749,11 @@
         <v>148.16292628</v>
       </c>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H144" t="n">
@@ -4779,11 +4779,11 @@
         <v>22.03899181</v>
       </c>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H145" t="n">
@@ -4809,11 +4809,11 @@
         <v>169.43078549</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H146" t="n">
@@ -4839,11 +4839,11 @@
         <v>115.96496099</v>
       </c>
       <c r="F147" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H147" t="n">
@@ -4869,11 +4869,11 @@
         <v>97.54827051999999</v>
       </c>
       <c r="F148" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H148" t="n">
@@ -4899,11 +4899,11 @@
         <v>171.24941356</v>
       </c>
       <c r="F149" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H149" t="n">
@@ -4929,11 +4929,11 @@
         <v>79.48337347</v>
       </c>
       <c r="F150" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H150" t="n">
@@ -4959,11 +4959,11 @@
         <v>21.38957457</v>
       </c>
       <c r="F151" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H151" t="n">
@@ -4989,11 +4989,11 @@
         <v>56.00126308</v>
       </c>
       <c r="F152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H152" t="n">
@@ -5019,11 +5019,11 @@
         <v>116.54724109</v>
       </c>
       <c r="F153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H153" t="n">
@@ -5049,11 +5049,11 @@
         <v>136.56314483</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H154" t="n">
@@ -5079,11 +5079,11 @@
         <v>132.34473269</v>
       </c>
       <c r="F155" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H155" t="n">
@@ -5109,11 +5109,11 @@
         <v>127.67648195</v>
       </c>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H156" t="n">
@@ -5139,11 +5139,11 @@
         <v>101.97064253</v>
       </c>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H157" t="n">
@@ -5169,11 +5169,11 @@
         <v>64.40666220000001</v>
       </c>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H158" t="n">
@@ -5199,11 +5199,11 @@
         <v>133.79668708</v>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H159" t="n">
@@ -5229,11 +5229,11 @@
         <v>138.15013296</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H160" t="n">
@@ -5259,11 +5259,11 @@
         <v>150.50007586</v>
       </c>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H161" t="n">
@@ -5289,11 +5289,11 @@
         <v>93.60651496</v>
       </c>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H162" t="n">
@@ -5319,11 +5319,11 @@
         <v>129.31327658</v>
       </c>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H163" t="n">
@@ -5349,11 +5349,11 @@
         <v>106.88348563</v>
       </c>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H164" t="n">
@@ -5379,11 +5379,11 @@
         <v>42.43144776</v>
       </c>
       <c r="F165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H165" t="n">
@@ -5409,11 +5409,11 @@
         <v>60.79293023</v>
       </c>
       <c r="F166" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H166" t="n">
@@ -5439,11 +5439,11 @@
         <v>77.59270448000001</v>
       </c>
       <c r="F167" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H167" t="n">
@@ -5469,11 +5469,11 @@
         <v>53.785478</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H168" t="n">
@@ -5499,11 +5499,11 @@
         <v>145.0125221</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H169" t="n">
@@ -5529,11 +5529,11 @@
         <v>134.76338509</v>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H170" t="n">
@@ -5559,11 +5559,11 @@
         <v>34.09060356</v>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H171" t="n">
@@ -5589,11 +5589,11 @@
         <v>103.95516876</v>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H172" t="n">
@@ -5619,11 +5619,11 @@
         <v>129.96221128</v>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H173" t="n">
@@ -5649,11 +5649,11 @@
         <v>123.25258422</v>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H174" t="n">
@@ -5679,11 +5679,11 @@
         <v>114.2480122</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H175" t="n">
@@ -5709,11 +5709,11 @@
         <v>148.70392757</v>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H176" t="n">
@@ -5739,11 +5739,11 @@
         <v>164.48669544</v>
       </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H177" t="n">
@@ -5769,11 +5769,11 @@
         <v>149.1072418</v>
       </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H178" t="n">
@@ -5799,11 +5799,11 @@
         <v>114.08940098</v>
       </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H179" t="n">
@@ -5829,11 +5829,11 @@
         <v>112.05923696</v>
       </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H180" t="n">
@@ -5859,11 +5859,11 @@
         <v>64.98465548</v>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H181" t="n">
@@ -5889,11 +5889,11 @@
         <v>72.72579613999999</v>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H182" t="n">
@@ -5919,11 +5919,11 @@
         <v>103.13068804</v>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H183" t="n">
@@ -5949,11 +5949,11 @@
         <v>88.39244152999999</v>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H184" t="n">
@@ -5979,11 +5979,11 @@
         <v>111.28124526</v>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H185" t="n">
@@ -6009,11 +6009,11 @@
         <v>77.23146711</v>
       </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H186" t="n">
@@ -6039,11 +6039,11 @@
         <v>87.69854039000001</v>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H187" t="n">
@@ -6069,11 +6069,11 @@
         <v>104.07446787</v>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H188" t="n">
@@ -6099,11 +6099,11 @@
         <v>135.95829359</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H189" t="n">
@@ -6129,11 +6129,11 @@
         <v>14.04523848</v>
       </c>
       <c r="F190" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H190" t="n">
@@ -6159,11 +6159,11 @@
         <v>84.03368023</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H191" t="n">
@@ -6189,11 +6189,11 @@
         <v>37.35482578</v>
       </c>
       <c r="F192" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H192" t="n">
@@ -6219,11 +6219,11 @@
         <v>29.02313882999999</v>
       </c>
       <c r="F193" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H193" t="n">
@@ -6249,11 +6249,11 @@
         <v>69.75723010999999</v>
       </c>
       <c r="F194" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H194" t="n">
@@ -6279,11 +6279,11 @@
         <v>106.29918689</v>
       </c>
       <c r="F195" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H195" t="n">
@@ -6309,11 +6309,11 @@
         <v>68.10364146999999</v>
       </c>
       <c r="F196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H196" t="n">
@@ -6339,11 +6339,11 @@
         <v>51.23457499999999</v>
       </c>
       <c r="F197" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H197" t="n">
@@ -6369,11 +6369,11 @@
         <v>62.39533672</v>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H198" t="n">
@@ -6399,11 +6399,11 @@
         <v>81.51284326</v>
       </c>
       <c r="F199" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H199" t="n">
@@ -6429,11 +6429,11 @@
         <v>83.68685203999999</v>
       </c>
       <c r="F200" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H200" t="n">
@@ -6459,11 +6459,11 @@
         <v>68.18522616</v>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H201" t="n">
@@ -6489,11 +6489,11 @@
         <v>80.24099302</v>
       </c>
       <c r="F202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H202" t="n">
@@ -6519,11 +6519,11 @@
         <v>42.55748138000001</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H203" t="n">
@@ -6549,11 +6549,11 @@
         <v>66.30837547</v>
       </c>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H204" t="n">
@@ -6579,11 +6579,11 @@
         <v>72.1073177</v>
       </c>
       <c r="F205" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H205" t="n">
@@ -6609,11 +6609,11 @@
         <v>61.94020108000001</v>
       </c>
       <c r="F206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H206" t="n">
@@ -6639,11 +6639,11 @@
         <v>116.30465114</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H207" t="n">
@@ -6669,11 +6669,11 @@
         <v>66.85576336</v>
       </c>
       <c r="F208" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H208" t="n">
@@ -6699,11 +6699,11 @@
         <v>88.47867821</v>
       </c>
       <c r="F209" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H209" t="n">
@@ -6729,11 +6729,11 @@
         <v>75.59825791</v>
       </c>
       <c r="F210" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H210" t="n">
@@ -6759,11 +6759,11 @@
         <v>112.48154805</v>
       </c>
       <c r="F211" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H211" t="n">
@@ -6789,11 +6789,11 @@
         <v>105.4919814</v>
       </c>
       <c r="F212" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H212" t="n">
@@ -6819,11 +6819,11 @@
         <v>42.46075999999999</v>
       </c>
       <c r="F213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H213" t="n">
@@ -6849,11 +6849,11 @@
         <v>46.7305</v>
       </c>
       <c r="F214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H214" t="n">
@@ -6879,11 +6879,11 @@
         <v>131.7189</v>
       </c>
       <c r="F215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H215" t="n">
@@ -6909,11 +6909,11 @@
         <v>114.2557</v>
       </c>
       <c r="F216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H216" t="n">
@@ -6939,11 +6939,11 @@
         <v>84.18970000000002</v>
       </c>
       <c r="F217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H217" t="n">
@@ -6969,11 +6969,11 @@
         <v>91.4577</v>
       </c>
       <c r="F218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H218" t="n">
@@ -6999,11 +6999,11 @@
         <v>70.68070499999999</v>
       </c>
       <c r="F219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H219" t="n">
@@ -7029,11 +7029,11 @@
         <v>126.098</v>
       </c>
       <c r="F220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H220" t="n">
@@ -7059,11 +7059,11 @@
         <v>82.72490000000002</v>
       </c>
       <c r="F221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H221" t="n">
@@ -7089,11 +7089,11 @@
         <v>86.91192750000002</v>
       </c>
       <c r="F222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H222" t="n">
@@ -7119,11 +7119,11 @@
         <v>111.2847575</v>
       </c>
       <c r="F223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H223" t="n">
@@ -7149,11 +7149,11 @@
         <v>56.31709999999999</v>
       </c>
       <c r="F224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H224" t="n">
@@ -7179,11 +7179,11 @@
         <v>83.71700000000001</v>
       </c>
       <c r="F225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H225" t="n">
@@ -7209,11 +7209,11 @@
         <v>86.1181</v>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H226" t="n">
@@ -7269,11 +7269,11 @@
         <v>93.57170000000001</v>
       </c>
       <c r="F228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H228" t="n">
@@ -7299,11 +7299,11 @@
         <v>84.7475</v>
       </c>
       <c r="F229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H229" t="n">
@@ -7329,11 +7329,11 @@
         <v>107.6923</v>
       </c>
       <c r="F230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H230" t="n">
@@ -7359,11 +7359,11 @@
         <v>139.3029</v>
       </c>
       <c r="F231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H231" t="n">
@@ -7389,11 +7389,11 @@
         <v>157.0891</v>
       </c>
       <c r="F232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H232" t="n">
@@ -7419,11 +7419,11 @@
         <v>136.7598</v>
       </c>
       <c r="F233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H233" t="n">
@@ -7449,11 +7449,11 @@
         <v>165.7064075</v>
       </c>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H234" t="n">
@@ -7479,11 +7479,11 @@
         <v>75.54960000000001</v>
       </c>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H235" t="n">
@@ -7509,11 +7509,11 @@
         <v>78.35300000000001</v>
       </c>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H236" t="n">
@@ -7539,11 +7539,11 @@
         <v>200.3232</v>
       </c>
       <c r="F237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H237" t="n">
@@ -7569,11 +7569,11 @@
         <v>68.56739999999999</v>
       </c>
       <c r="F238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H238" t="n">
@@ -7629,11 +7629,11 @@
         <v>126.10768</v>
       </c>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H240" t="n">
@@ -7659,11 +7659,11 @@
         <v>115.5759</v>
       </c>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H241" t="n">
@@ -7689,11 +7689,11 @@
         <v>215.0096</v>
       </c>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H242" t="n">
@@ -7719,11 +7719,11 @@
         <v>83.30775</v>
       </c>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H243" t="n">
@@ -7749,11 +7749,11 @@
         <v>101.468</v>
       </c>
       <c r="F244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H244" t="n">
@@ -7779,11 +7779,11 @@
         <v>102.4148</v>
       </c>
       <c r="F245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H245" t="n">
@@ -7809,11 +7809,11 @@
         <v>85.72189999999999</v>
       </c>
       <c r="F246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H246" t="n">
@@ -7839,11 +7839,11 @@
         <v>75.19390000000001</v>
       </c>
       <c r="F247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H247" t="n">
@@ -7869,11 +7869,11 @@
         <v>60.35279999999999</v>
       </c>
       <c r="F248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H248" t="n">
@@ -7899,11 +7899,11 @@
         <v>77.68439999999998</v>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H249" t="n">
@@ -7929,11 +7929,11 @@
         <v>56.0851</v>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H250" t="n">
@@ -7959,11 +7959,11 @@
         <v>53.74859999999999</v>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H251" t="n">
@@ -7989,11 +7989,11 @@
         <v>22.082508</v>
       </c>
       <c r="F252" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H252" t="n">
@@ -8019,11 +8019,11 @@
         <v>26.1654</v>
       </c>
       <c r="F253" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H253" t="n">
@@ -8049,11 +8049,11 @@
         <v>41.9052</v>
       </c>
       <c r="F254" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H254" t="n">
@@ -8079,11 +8079,11 @@
         <v>898.0380000000002</v>
       </c>
       <c r="F255" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H255" t="n">
@@ -8109,11 +8109,11 @@
         <v>13.4594</v>
       </c>
       <c r="F256" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H256" t="n">
@@ -8139,11 +8139,11 @@
         <v>109.8696</v>
       </c>
       <c r="F257" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H257" t="n">
@@ -8169,11 +8169,11 @@
         <v>128.60566</v>
       </c>
       <c r="F258" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H258" t="n">
@@ -8199,11 +8199,11 @@
         <v>571.5419999999999</v>
       </c>
       <c r="F259" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H259" t="n">
@@ -8229,11 +8229,11 @@
         <v>122.977441</v>
       </c>
       <c r="F260" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H260" t="n">
@@ -8259,11 +8259,11 @@
         <v>131.0654675</v>
       </c>
       <c r="F261" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H261" t="n">
@@ -8289,11 +8289,11 @@
         <v>95.62609999999999</v>
       </c>
       <c r="F262" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H262" t="n">
@@ -8319,11 +8319,11 @@
         <v>106.7479</v>
       </c>
       <c r="F263" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H263" t="n">
@@ -8349,11 +8349,11 @@
         <v>123.2049255</v>
       </c>
       <c r="F264" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H264" t="n">
@@ -8379,11 +8379,11 @@
         <v>284.046</v>
       </c>
       <c r="F265" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H265" t="n">
@@ -8406,14 +8406,14 @@
         <v>1194645.255</v>
       </c>
       <c r="E266" t="n">
-        <v>995.3472000000002</v>
+        <v>980</v>
       </c>
       <c r="F266" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H266" t="n">
@@ -8439,11 +8439,11 @@
         <v>56.9948</v>
       </c>
       <c r="F267" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H267" t="n">
@@ -8469,11 +8469,11 @@
         <v>162.227688</v>
       </c>
       <c r="F268" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H268" t="n">
@@ -8499,11 +8499,11 @@
         <v>93.85904950000001</v>
       </c>
       <c r="F269" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H269" t="n">
@@ -8529,11 +8529,11 @@
         <v>72.16600000000001</v>
       </c>
       <c r="F270" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H270" t="n">
@@ -8559,11 +8559,11 @@
         <v>77.25859999999999</v>
       </c>
       <c r="F271" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H271" t="n">
@@ -8589,11 +8589,11 @@
         <v>72.49699999999999</v>
       </c>
       <c r="F272" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H272" t="n">
@@ -8619,11 +8619,11 @@
         <v>186.4224215</v>
       </c>
       <c r="F273" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H273" t="n">
@@ -8649,11 +8649,11 @@
         <v>150.1102</v>
       </c>
       <c r="F274" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H274" t="n">
@@ -8679,11 +8679,11 @@
         <v>71.23049999999999</v>
       </c>
       <c r="F275" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H275" t="n">
@@ -8709,11 +8709,11 @@
         <v>222.122161</v>
       </c>
       <c r="F276" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H276" t="n">
@@ -8739,11 +8739,11 @@
         <v>243.76794</v>
       </c>
       <c r="F277" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H277" t="n">
@@ -8769,11 +8769,11 @@
         <v>59.30860000000001</v>
       </c>
       <c r="F278" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H278" t="n">
@@ -8799,11 +8799,11 @@
         <v>200.4813</v>
       </c>
       <c r="F279" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H279" t="n">
@@ -8829,11 +8829,11 @@
         <v>152.1270185</v>
       </c>
       <c r="F280" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H280" t="n">
@@ -8859,11 +8859,11 @@
         <v>100.023278</v>
       </c>
       <c r="F281" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H281" t="n">
@@ -8889,11 +8889,11 @@
         <v>65.61912249999999</v>
       </c>
       <c r="F282" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H282" t="n">
@@ -8919,11 +8919,11 @@
         <v>59.61479999999999</v>
       </c>
       <c r="F283" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H283" t="n">
@@ -8949,11 +8949,11 @@
         <v>92.10120000000001</v>
       </c>
       <c r="F284" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H284" t="n">
@@ -8979,11 +8979,11 @@
         <v>87.2212</v>
       </c>
       <c r="F285" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H285" t="n">
@@ -9009,11 +9009,11 @@
         <v>44.383</v>
       </c>
       <c r="F286" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H286" t="n">
@@ -9039,11 +9039,11 @@
         <v>72.4555</v>
       </c>
       <c r="F287" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H287" t="n">
@@ -9069,11 +9069,11 @@
         <v>228.606</v>
       </c>
       <c r="F288" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H288" t="n">
@@ -9099,11 +9099,11 @@
         <v>106.680992</v>
       </c>
       <c r="F289" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H289" t="n">
@@ -9129,11 +9129,11 @@
         <v>118.29098</v>
       </c>
       <c r="F290" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H290" t="n">
@@ -9159,11 +9159,11 @@
         <v>56.55883999999998</v>
       </c>
       <c r="F291" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H291" t="n">
@@ -9189,11 +9189,11 @@
         <v>99.75030000000001</v>
       </c>
       <c r="F292" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H292" t="n">
@@ -9219,11 +9219,11 @@
         <v>76.35709999999999</v>
       </c>
       <c r="F293" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H293" t="n">
@@ -9249,11 +9249,11 @@
         <v>65.98963999999999</v>
       </c>
       <c r="F294" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H294" t="n">
@@ -9279,11 +9279,11 @@
         <v>70.17684000000001</v>
       </c>
       <c r="F295" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H295" t="n">
@@ -9309,11 +9309,11 @@
         <v>80.12326000000002</v>
       </c>
       <c r="F296" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H296" t="n">
@@ -9339,11 +9339,11 @@
         <v>73.27007999999999</v>
       </c>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H297" t="n">
@@ -9369,11 +9369,11 @@
         <v>113.30992</v>
       </c>
       <c r="F298" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H298" t="n">
@@ -9399,11 +9399,11 @@
         <v>43.52612</v>
       </c>
       <c r="F299" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H299" t="n">
@@ -9429,11 +9429,11 @@
         <v>108.32342</v>
       </c>
       <c r="F300" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H300" t="n">
@@ -9459,11 +9459,11 @@
         <v>51.79328</v>
       </c>
       <c r="F301" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H301" t="n">
@@ -9489,11 +9489,11 @@
         <v>68.9781</v>
       </c>
       <c r="F302" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H302" t="n">
@@ -9519,11 +9519,11 @@
         <v>69.73756</v>
       </c>
       <c r="F303" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H303" t="n">
@@ -9549,11 +9549,11 @@
         <v>116.13984</v>
       </c>
       <c r="F304" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H304" t="n">
@@ -9579,11 +9579,11 @@
         <v>100.22104</v>
       </c>
       <c r="F305" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H305" t="n">
@@ -9609,11 +9609,11 @@
         <v>124.95866</v>
       </c>
       <c r="F306" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H306" t="n">
@@ -9639,11 +9639,11 @@
         <v>106.6222</v>
       </c>
       <c r="F307" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H307" t="n">
@@ -9669,11 +9669,11 @@
         <v>37.92908</v>
       </c>
       <c r="F308" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H308" t="n">
@@ -9699,11 +9699,11 @@
         <v>76.79181999999999</v>
       </c>
       <c r="F309" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H309" t="n">
@@ -9729,11 +9729,11 @@
         <v>47.35968</v>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="H310" t="n">
@@ -9759,11 +9759,11 @@
         <v>153.85138</v>
       </c>
       <c r="F311" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H311" t="n">
@@ -9789,11 +9789,11 @@
         <v>178.5294</v>
       </c>
       <c r="F312" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H312" t="n">
@@ -9819,11 +9819,11 @@
         <v>138.3113</v>
       </c>
       <c r="F313" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H313" t="n">
@@ -9849,11 +9849,11 @@
         <v>148.35608</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H314" t="n">
@@ -9879,11 +9879,11 @@
         <v>137.84592</v>
       </c>
       <c r="F315" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H315" t="n">
@@ -9909,11 +9909,11 @@
         <v>71.19014000000001</v>
       </c>
       <c r="F316" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H316" t="n">
@@ -9939,11 +9939,11 @@
         <v>106.50236</v>
       </c>
       <c r="F317" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H317" t="n">
@@ -9969,11 +9969,11 @@
         <v>97.77134</v>
       </c>
       <c r="F318" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H318" t="n">
@@ -9999,11 +9999,11 @@
         <v>80.68743999999998</v>
       </c>
       <c r="F319" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H319" t="n">
@@ -10029,11 +10029,11 @@
         <v>92.23769999999999</v>
       </c>
       <c r="F320" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H320" t="n">
@@ -10059,11 +10059,11 @@
         <v>111.7828</v>
       </c>
       <c r="F321" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H321" t="n">
@@ -10089,11 +10089,11 @@
         <v>120.6901</v>
       </c>
       <c r="F322" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H322" t="n">
@@ -10119,11 +10119,11 @@
         <v>51.7548</v>
       </c>
       <c r="F323" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H323" t="n">
@@ -10149,11 +10149,11 @@
         <v>162.11432</v>
       </c>
       <c r="F324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H324" t="n">
@@ -10179,11 +10179,11 @@
         <v>70.43834</v>
       </c>
       <c r="F325" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H325" t="n">
@@ -10209,11 +10209,11 @@
         <v>97.17318</v>
       </c>
       <c r="F326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H326" t="n">
@@ -10239,11 +10239,11 @@
         <v>96.64926</v>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H327" t="n">
@@ -10269,11 +10269,11 @@
         <v>136.70414</v>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H328" t="n">
@@ -10299,11 +10299,11 @@
         <v>55.98389999999999</v>
       </c>
       <c r="F329" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H329" t="n">
@@ -10329,11 +10329,11 @@
         <v>57.27579999999999</v>
       </c>
       <c r="F330" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H330" t="n">
@@ -10359,11 +10359,11 @@
         <v>100.51814</v>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H331" t="n">
@@ -10389,11 +10389,11 @@
         <v>72.68213999999999</v>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H332" t="n">
@@ -10419,11 +10419,11 @@
         <v>53.00724</v>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H333" t="n">
@@ -10449,11 +10449,11 @@
         <v>84.78078000000001</v>
       </c>
       <c r="F334" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H334" t="n">
@@ -10479,11 +10479,11 @@
         <v>97.36683999999997</v>
       </c>
       <c r="F335" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H335" t="n">
@@ -10509,11 +10509,11 @@
         <v>81.07180000000001</v>
       </c>
       <c r="F336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H336" t="n">
@@ -10539,11 +10539,11 @@
         <v>51.87629999999999</v>
       </c>
       <c r="F337" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H337" t="n">
@@ -10569,11 +10569,11 @@
         <v>164.81286</v>
       </c>
       <c r="F338" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H338" t="n">
@@ -10599,11 +10599,11 @@
         <v>137.11044</v>
       </c>
       <c r="F339" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H339" t="n">
@@ -10629,11 +10629,11 @@
         <v>105.60097665</v>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H340" t="n">
@@ -10659,11 +10659,11 @@
         <v>85.30447965</v>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H341" t="n">
@@ -10689,11 +10689,11 @@
         <v>105.13692</v>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H342" t="n">
@@ -10719,11 +10719,11 @@
         <v>119.39315505</v>
       </c>
       <c r="F343" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H343" t="n">
@@ -10749,11 +10749,11 @@
         <v>135.2097</v>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H344" t="n">
@@ -10779,11 +10779,11 @@
         <v>103.2224895</v>
       </c>
       <c r="F345" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H345" t="n">
@@ -10809,11 +10809,11 @@
         <v>105.68844</v>
       </c>
       <c r="F346" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H346" t="n">
@@ -10839,11 +10839,11 @@
         <v>92.92085999999999</v>
       </c>
       <c r="F347" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H347" t="n">
@@ -10869,11 +10869,11 @@
         <v>105.6147144</v>
       </c>
       <c r="F348" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H348" t="n">
@@ -10899,11 +10899,11 @@
         <v>96.36005999999999</v>
       </c>
       <c r="F349" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H349" t="n">
@@ -10929,11 +10929,11 @@
         <v>81.90635999999998</v>
       </c>
       <c r="F350" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H350" t="n">
@@ -10959,11 +10959,11 @@
         <v>103.29378</v>
       </c>
       <c r="F351" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H351" t="n">
@@ -10989,11 +10989,11 @@
         <v>69.66414</v>
       </c>
       <c r="F352" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H352" t="n">
@@ -11019,11 +11019,11 @@
         <v>133.07976</v>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H353" t="n">
@@ -11049,11 +11049,11 @@
         <v>99.53225999999999</v>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H354" t="n">
@@ -11079,11 +11079,11 @@
         <v>174.81366</v>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H355" t="n">
@@ -11109,11 +11109,11 @@
         <v>123.87336</v>
       </c>
       <c r="F356" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H356" t="n">
@@ -11139,11 +11139,11 @@
         <v>147.74808</v>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H357" t="n">
@@ -11169,11 +11169,11 @@
         <v>148.73862</v>
       </c>
       <c r="F358" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H358" t="n">
@@ -11199,11 +11199,11 @@
         <v>273.06534</v>
       </c>
       <c r="F359" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H359" t="n">
@@ -11229,11 +11229,11 @@
         <v>108.07158</v>
       </c>
       <c r="F360" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H360" t="n">
@@ -11259,11 +11259,11 @@
         <v>154.62948</v>
       </c>
       <c r="F361" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H361" t="n">
@@ -11289,11 +11289,11 @@
         <v>133.61611575</v>
       </c>
       <c r="F362" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H362" t="n">
@@ -11319,11 +11319,11 @@
         <v>107.2794</v>
       </c>
       <c r="F363" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H363" t="n">
@@ -11349,11 +11349,11 @@
         <v>90.89004</v>
       </c>
       <c r="F364" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H364" t="n">
@@ -11379,11 +11379,11 @@
         <v>65.39706</v>
       </c>
       <c r="F365" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H365" t="n">
@@ -11409,11 +11409,11 @@
         <v>93.90606000000002</v>
       </c>
       <c r="F366" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H366" t="n">
@@ -11439,11 +11439,11 @@
         <v>102.0003</v>
       </c>
       <c r="F367" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="H367" t="n">
@@ -11469,11 +11469,11 @@
         <v>69.34979999999999</v>
       </c>
       <c r="F368" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H368" t="n">
@@ -12309,11 +12309,11 @@
         <v>38.27594000000001</v>
       </c>
       <c r="F396" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H396" t="n">
@@ -12339,11 +12339,11 @@
         <v>120.77989</v>
       </c>
       <c r="F397" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H397" t="n">
@@ -12369,11 +12369,11 @@
         <v>88.73139999999999</v>
       </c>
       <c r="F398" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H398" t="n">
@@ -12399,11 +12399,11 @@
         <v>161.85019</v>
       </c>
       <c r="F399" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H399" t="n">
@@ -12429,11 +12429,11 @@
         <v>27.36499</v>
       </c>
       <c r="F400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H400" t="n">
@@ -12459,11 +12459,11 @@
         <v>116.77227</v>
       </c>
       <c r="F401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H401" t="n">
@@ -12489,11 +12489,11 @@
         <v>75.02567782</v>
       </c>
       <c r="F402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H402" t="n">
@@ -12519,11 +12519,11 @@
         <v>59.45515</v>
       </c>
       <c r="F403" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H403" t="n">
@@ -12549,11 +12549,11 @@
         <v>126.89930723</v>
       </c>
       <c r="F404" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H404" t="n">
@@ -12579,11 +12579,11 @@
         <v>186.60781</v>
       </c>
       <c r="F405" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H405" t="n">
@@ -12609,11 +12609,11 @@
         <v>118.61613</v>
       </c>
       <c r="F406" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H406" t="n">
@@ -12639,11 +12639,11 @@
         <v>99.67066999999997</v>
       </c>
       <c r="F407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H407" t="n">
@@ -12669,11 +12669,11 @@
         <v>156.26261</v>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H408" t="n">
@@ -12699,11 +12699,11 @@
         <v>221.48973368</v>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H409" t="n">
@@ -12729,11 +12729,11 @@
         <v>200.46183</v>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H410" t="n">
@@ -12759,11 +12759,11 @@
         <v>12.82508</v>
       </c>
       <c r="F411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H411" t="n">
@@ -12789,11 +12789,11 @@
         <v>104.69023</v>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H412" t="n">
@@ -12819,11 +12819,11 @@
         <v>131.63062668</v>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H413" t="n">
@@ -12849,11 +12849,11 @@
         <v>136.36787</v>
       </c>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H414" t="n">
@@ -12879,11 +12879,11 @@
         <v>57.31582</v>
       </c>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H415" t="n">
@@ -12909,11 +12909,11 @@
         <v>53.89304</v>
       </c>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H416" t="n">
@@ -12939,11 +12939,11 @@
         <v>65.84545999999999</v>
       </c>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H417" t="n">
@@ -12969,11 +12969,11 @@
         <v>44.69123999999999</v>
       </c>
       <c r="F418" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H418" t="n">
@@ -12999,11 +12999,11 @@
         <v>26.44715</v>
       </c>
       <c r="F419" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H419" t="n">
@@ -13029,11 +13029,11 @@
         <v>30.97999</v>
       </c>
       <c r="F420" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H420" t="n">
@@ -13059,11 +13059,11 @@
         <v>38.67852</v>
       </c>
       <c r="F421" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H421" t="n">
@@ -13089,11 +13089,11 @@
         <v>22.78917</v>
       </c>
       <c r="F422" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H422" t="n">
@@ -13119,11 +13119,11 @@
         <v>35.23107055</v>
       </c>
       <c r="F423" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H423" t="n">
@@ -13149,11 +13149,11 @@
         <v>125.73253</v>
       </c>
       <c r="F424" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H424" t="n">
@@ -13179,11 +13179,11 @@
         <v>130.00548581</v>
       </c>
       <c r="F425" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H425" t="n">
@@ -13209,11 +13209,11 @@
         <v>144.26477</v>
       </c>
       <c r="F426" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H426" t="n">
@@ -13239,11 +13239,11 @@
         <v>109.89436</v>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H427" t="n">
@@ -13269,11 +13269,11 @@
         <v>108.37224</v>
       </c>
       <c r="F428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H428" t="n">
@@ -13299,11 +13299,11 @@
         <v>120.83489913</v>
       </c>
       <c r="F429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H429" t="n">
@@ -13329,11 +13329,11 @@
         <v>98.41355000000001</v>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H430" t="n">
@@ -13359,11 +13359,11 @@
         <v>192.78007139</v>
       </c>
       <c r="F431" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H431" t="n">
@@ -13389,11 +13389,11 @@
         <v>49.8474</v>
       </c>
       <c r="F432" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H432" t="n">
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>449.9853559453078</v>
+        <v>465.8953011676563</v>
       </c>
     </row>
     <row r="434">
@@ -13449,11 +13449,11 @@
         <v>138.73463</v>
       </c>
       <c r="F434" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H434" t="n">
@@ -13479,11 +13479,11 @@
         <v>79.70254</v>
       </c>
       <c r="F435" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H435" t="n">
@@ -13509,11 +13509,11 @@
         <v>79.38280632999999</v>
       </c>
       <c r="F436" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H436" t="n">
@@ -13539,11 +13539,11 @@
         <v>52.55348000000001</v>
       </c>
       <c r="F437" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H437" t="n">
@@ -13569,11 +13569,11 @@
         <v>99.50590866000003</v>
       </c>
       <c r="F438" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H438" t="n">
@@ -13599,11 +13599,11 @@
         <v>95.54351964</v>
       </c>
       <c r="F439" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H439" t="n">
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>456.135414208522</v>
+        <v>462.1981527260011</v>
       </c>
     </row>
     <row r="441">
@@ -13659,11 +13659,11 @@
         <v>72.21539426</v>
       </c>
       <c r="F441" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H441" t="n">
@@ -13689,11 +13689,11 @@
         <v>78.73100000000001</v>
       </c>
       <c r="F442" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H442" t="n">
@@ -13719,11 +13719,11 @@
         <v>49.06175000000001</v>
       </c>
       <c r="F443" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H443" t="n">
@@ -13749,11 +13749,11 @@
         <v>86.38211000000001</v>
       </c>
       <c r="F444" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H444" t="n">
@@ -13779,11 +13779,11 @@
         <v>90.25793999999999</v>
       </c>
       <c r="F445" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H445" t="n">
@@ -13809,11 +13809,11 @@
         <v>142.70429</v>
       </c>
       <c r="F446" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H446" t="n">
@@ -13839,11 +13839,11 @@
         <v>96.81982000000001</v>
       </c>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H447" t="n">
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>459.7575073825284</v>
+        <v>455.943847080418</v>
       </c>
     </row>
     <row r="449">
@@ -13899,11 +13899,11 @@
         <v>88.97014999999999</v>
       </c>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H449" t="n">
@@ -13929,11 +13929,11 @@
         <v>81.9524</v>
       </c>
       <c r="F450" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H450" t="n">
@@ -13959,11 +13959,11 @@
         <v>129.72508</v>
       </c>
       <c r="F451" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H451" t="n">
@@ -13989,11 +13989,11 @@
         <v>97.62965</v>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H452" t="n">
@@ -14019,11 +14019,11 @@
         <v>137.67475</v>
       </c>
       <c r="F453" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H453" t="n">
@@ -14049,11 +14049,11 @@
         <v>91.25033126999999</v>
       </c>
       <c r="F454" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H454" t="n">
@@ -14079,11 +14079,11 @@
         <v>114.76295</v>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H455" t="n">
@@ -14109,11 +14109,11 @@
         <v>182.79795222</v>
       </c>
       <c r="F456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H456" t="n">
@@ -14139,11 +14139,11 @@
         <v>33.4468</v>
       </c>
       <c r="F457" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H457" t="n">
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="H458" t="n">
-        <v>454.4354598273687</v>
+        <v>461.2613982587158</v>
       </c>
     </row>
     <row r="459">
@@ -14199,11 +14199,11 @@
         <v>99.37579999999998</v>
       </c>
       <c r="F459" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H459" t="n">
@@ -14229,11 +14229,11 @@
         <v>97.32721341</v>
       </c>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H460" t="n">
@@ -14259,11 +14259,11 @@
         <v>73.07991107000001</v>
       </c>
       <c r="F461" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H461" t="n">
@@ -14289,11 +14289,11 @@
         <v>130.30602041</v>
       </c>
       <c r="F462" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H462" t="n">
@@ -14319,11 +14319,11 @@
         <v>187.41045626</v>
       </c>
       <c r="F463" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H463" t="n">
@@ -14349,11 +14349,11 @@
         <v>121.20383</v>
       </c>
       <c r="F464" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H464" t="n">
@@ -14379,11 +14379,11 @@
         <v>97.37148000000001</v>
       </c>
       <c r="F465" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H465" t="n">
@@ -14409,11 +14409,11 @@
         <v>130.5938</v>
       </c>
       <c r="F466" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H466" t="n">
@@ -14439,11 +14439,11 @@
         <v>38.55294999999999</v>
       </c>
       <c r="F467" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H467" t="n">
@@ -14469,11 +14469,11 @@
         <v>125.94</v>
       </c>
       <c r="F468" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H468" t="n">
@@ -14499,11 +14499,11 @@
         <v>124.82256731</v>
       </c>
       <c r="F469" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H469" t="n">
@@ -14529,11 +14529,11 @@
         <v>123.36434</v>
       </c>
       <c r="F470" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H470" t="n">
@@ -14559,11 +14559,11 @@
         <v>173.58828</v>
       </c>
       <c r="F471" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H471" t="n">
@@ -14589,11 +14589,11 @@
         <v>131.28461</v>
       </c>
       <c r="F472" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H472" t="n">
@@ -14619,11 +14619,11 @@
         <v>98.05121718000002</v>
       </c>
       <c r="F473" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H473" t="n">
@@ -14657,7 +14657,7 @@
         </is>
       </c>
       <c r="H474" t="n">
-        <v>455.2583033426945</v>
+        <v>461.8776223578468</v>
       </c>
     </row>
     <row r="475">
@@ -14679,11 +14679,11 @@
         <v>108.78155</v>
       </c>
       <c r="F475" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H475" t="n">
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>458.674922905298</v>
+        <v>459.0257982920651</v>
       </c>
     </row>
     <row r="477">
@@ -14739,11 +14739,11 @@
         <v>191.04122</v>
       </c>
       <c r="F477" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H477" t="n">
@@ -14769,11 +14769,11 @@
         <v>115.35392</v>
       </c>
       <c r="F478" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H478" t="n">
@@ -14799,11 +14799,11 @@
         <v>125.61114</v>
       </c>
       <c r="F479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H479" t="n">
@@ -14829,11 +14829,11 @@
         <v>142.23318404</v>
       </c>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H480" t="n">
@@ -14859,11 +14859,11 @@
         <v>90.83478997000002</v>
       </c>
       <c r="F481" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H481" t="n">
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>451.2518729527299</v>
+        <v>506.1233495929659</v>
       </c>
     </row>
     <row r="483">
@@ -14919,11 +14919,11 @@
         <v>127.76054</v>
       </c>
       <c r="F483" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H483" t="n">
@@ -14949,11 +14949,11 @@
         <v>109.79968</v>
       </c>
       <c r="F484" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H484" t="n">
@@ -14979,11 +14979,11 @@
         <v>131.96288887</v>
       </c>
       <c r="F485" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H485" t="n">
@@ -15009,11 +15009,11 @@
         <v>175.2077001</v>
       </c>
       <c r="F486" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H486" t="n">
@@ -15039,11 +15039,11 @@
         <v>168.87164</v>
       </c>
       <c r="F487" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H487" t="n">
@@ -15069,11 +15069,11 @@
         <v>66.75664999999999</v>
       </c>
       <c r="F488" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H488" t="n">
@@ -15099,11 +15099,11 @@
         <v>126.85732686</v>
       </c>
       <c r="F489" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H489" t="n">
@@ -15129,11 +15129,11 @@
         <v>115.03028</v>
       </c>
       <c r="F490" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H490" t="n">
@@ -15159,11 +15159,11 @@
         <v>89.62715</v>
       </c>
       <c r="F491" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="H491" t="n">
@@ -15189,11 +15189,11 @@
         <v>43.78264999999999</v>
       </c>
       <c r="F492" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H492" t="n">
@@ -15219,11 +15219,11 @@
         <v>60.0933</v>
       </c>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H493" t="n">
@@ -15249,11 +15249,11 @@
         <v>76.39164923000001</v>
       </c>
       <c r="F494" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H494" t="n">
@@ -15279,11 +15279,11 @@
         <v>54.11192668</v>
       </c>
       <c r="F495" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H495" t="n">
@@ -15309,11 +15309,11 @@
         <v>59.60680000000001</v>
       </c>
       <c r="F496" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H496" t="n">
@@ -15339,11 +15339,11 @@
         <v>61.33865</v>
       </c>
       <c r="F497" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H497" t="n">
@@ -15369,11 +15369,11 @@
         <v>64.45888206000001</v>
       </c>
       <c r="F498" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H498" t="n">
@@ -15399,11 +15399,11 @@
         <v>63.66179793000001</v>
       </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H499" t="n">
@@ -15429,11 +15429,11 @@
         <v>97.11096000000002</v>
       </c>
       <c r="F500" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H500" t="n">
@@ -15459,11 +15459,11 @@
         <v>77.12655000000001</v>
       </c>
       <c r="F501" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H501" t="n">
@@ -15489,11 +15489,11 @@
         <v>63.69543999999999</v>
       </c>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H502" t="n">
@@ -15519,11 +15519,11 @@
         <v>39.40545</v>
       </c>
       <c r="F503" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H503" t="n">
@@ -15549,11 +15549,11 @@
         <v>51.32812</v>
       </c>
       <c r="F504" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="H504" t="n">
@@ -15579,11 +15579,11 @@
         <v>48.43592</v>
       </c>
       <c r="F505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="H505" t="n">

--- a/clustered_output.xlsx
+++ b/clustered_output.xlsx
@@ -8076,7 +8076,7 @@
         <v>1069336.49</v>
       </c>
       <c r="E255" t="n">
-        <v>898.0380000000002</v>
+        <v>199.564</v>
       </c>
       <c r="F255" t="n">
         <v>2</v>
@@ -8196,7 +8196,7 @@
         <v>2434991.280000001</v>
       </c>
       <c r="E259" t="n">
-        <v>571.5419999999999</v>
+        <v>285.771</v>
       </c>
       <c r="F259" t="n">
         <v>2</v>
@@ -8406,7 +8406,7 @@
         <v>1194645.255</v>
       </c>
       <c r="E266" t="n">
-        <v>980</v>
+        <v>248.8368</v>
       </c>
       <c r="F266" t="n">
         <v>2</v>
